--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -641,50 +644,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69288.91</v>
+        <v>69005.88</v>
       </c>
       <c r="C2" t="n">
-        <v>70020.67999999999</v>
+        <v>70125.75</v>
       </c>
       <c r="D2" t="n">
-        <v>69095.67</v>
+        <v>68985.63</v>
       </c>
       <c r="E2" t="n">
-        <v>69404.5</v>
+        <v>69902.25</v>
       </c>
       <c r="F2" t="n">
-        <v>87</v>
+        <v>497.75</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0072</v>
       </c>
       <c r="H2" t="n">
-        <v>925.01</v>
+        <v>1140.12</v>
       </c>
       <c r="I2" t="n">
-        <v>63884.21</v>
+        <v>68170.66</v>
       </c>
       <c r="J2" t="n">
-        <v>66960.88</v>
+        <v>68402.64999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>67868</v>
+        <v>68942</v>
       </c>
       <c r="L2" t="n">
-        <v>68775.11</v>
+        <v>69481.34</v>
       </c>
       <c r="M2" t="n">
-        <v>70767</v>
+        <v>69867</v>
       </c>
       <c r="N2" t="n">
-        <v>72758.89999999999</v>
+        <v>70252.67</v>
       </c>
       <c r="O2" t="n">
-        <v>72581.23</v>
+        <v>70945.69</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -697,11 +700,13 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -714,55 +719,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69005.88</v>
+        <v>70163.71000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>70125.75</v>
+        <v>71398.58</v>
       </c>
       <c r="D3" t="n">
-        <v>68985.63</v>
+        <v>70092.94</v>
       </c>
       <c r="E3" t="n">
-        <v>69902.25</v>
+        <v>71053.49000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>497.75</v>
+        <v>1151.24</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0072</v>
+        <v>0.0165</v>
       </c>
       <c r="H3" t="n">
-        <v>1140.12</v>
+        <v>1305.64</v>
       </c>
       <c r="I3" t="n">
-        <v>68170.66</v>
+        <v>67845.52</v>
       </c>
       <c r="J3" t="n">
-        <v>68402.64999999999</v>
+        <v>68935.41</v>
       </c>
       <c r="K3" t="n">
-        <v>68942</v>
+        <v>69332.19</v>
       </c>
       <c r="L3" t="n">
-        <v>69481.34</v>
+        <v>69728.97</v>
       </c>
       <c r="M3" t="n">
-        <v>69867</v>
+        <v>70472.31</v>
       </c>
       <c r="N3" t="n">
-        <v>70252.67</v>
+        <v>71215.64999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>70945.69</v>
+        <v>71265.87</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -780,73 +789,73 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70163.71000000001</v>
+        <v>71551.03</v>
       </c>
       <c r="C4" t="n">
-        <v>71398.58</v>
+        <v>71952.99000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>70092.94</v>
+        <v>70517.98</v>
       </c>
       <c r="E4" t="n">
-        <v>71053.49000000001</v>
+        <v>71250.06</v>
       </c>
       <c r="F4" t="n">
-        <v>1151.24</v>
+        <v>196.57</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0028</v>
       </c>
       <c r="H4" t="n">
-        <v>1305.64</v>
+        <v>1435.02</v>
       </c>
       <c r="I4" t="n">
-        <v>67845.52</v>
+        <v>68787.3</v>
       </c>
       <c r="J4" t="n">
-        <v>68935.41</v>
+        <v>69901.72</v>
       </c>
       <c r="K4" t="n">
-        <v>69332.19</v>
+        <v>70400.67</v>
       </c>
       <c r="L4" t="n">
-        <v>69728.97</v>
+        <v>70899.62</v>
       </c>
       <c r="M4" t="n">
-        <v>70472.31</v>
+        <v>71706.31</v>
       </c>
       <c r="N4" t="n">
-        <v>71215.64999999999</v>
+        <v>72513</v>
       </c>
       <c r="O4" t="n">
-        <v>71265.87</v>
+        <v>72704.22</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -859,7 +868,7 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
@@ -867,15 +876,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -887,50 +892,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71551.03</v>
+        <v>71067.14999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>71952.99000000001</v>
+        <v>72831.73</v>
       </c>
       <c r="D5" t="n">
-        <v>70517.98</v>
+        <v>71009.52</v>
       </c>
       <c r="E5" t="n">
-        <v>71250.06</v>
+        <v>72353.96000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>196.57</v>
+        <v>1103.9</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0155</v>
       </c>
       <c r="H5" t="n">
-        <v>1435.02</v>
+        <v>1822.2</v>
       </c>
       <c r="I5" t="n">
-        <v>68787.3</v>
+        <v>69082.96000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>69901.72</v>
+        <v>69822.34</v>
       </c>
       <c r="K5" t="n">
-        <v>70400.67</v>
+        <v>70532.55</v>
       </c>
       <c r="L5" t="n">
-        <v>70899.62</v>
+        <v>71242.77</v>
       </c>
       <c r="M5" t="n">
-        <v>71706.31</v>
+        <v>71967.57000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>72513</v>
+        <v>72692.37</v>
       </c>
       <c r="O5" t="n">
-        <v>72704.22</v>
+        <v>73388.00999999999</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -943,7 +948,7 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -951,8 +956,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="n">
-        <v/>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -967,81 +974,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>71067.14999999999</v>
+        <v>72404.37</v>
       </c>
       <c r="C6" t="n">
-        <v>72831.73</v>
+        <v>72618.44</v>
       </c>
       <c r="D6" t="n">
-        <v>71009.52</v>
+        <v>69788.38</v>
       </c>
       <c r="E6" t="n">
-        <v>72353.96000000001</v>
+        <v>69788.38</v>
       </c>
       <c r="F6" t="n">
-        <v>1103.9</v>
+        <v>-2565.58</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0155</v>
+        <v>-0.0355</v>
       </c>
       <c r="H6" t="n">
-        <v>1822.2</v>
+        <v>2830.05</v>
       </c>
       <c r="I6" t="n">
-        <v>69082.96000000001</v>
+        <v>69187.32000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>69822.34</v>
+        <v>70748.42999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>70532.55</v>
+        <v>71442.86</v>
       </c>
       <c r="L6" t="n">
-        <v>71242.77</v>
+        <v>72137.28999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>71967.57000000001</v>
+        <v>73265.06</v>
       </c>
       <c r="N6" t="n">
-        <v>72692.37</v>
+        <v>74392.83</v>
       </c>
       <c r="O6" t="n">
-        <v>73388.00999999999</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
+        <v>74653.92999999999</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1049,64 +1058,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>72404.37</v>
+        <v>69615.08</v>
       </c>
       <c r="C7" t="n">
-        <v>72618.44</v>
+        <v>70218.71000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>69788.38</v>
+        <v>68461.10000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>69788.38</v>
+        <v>69174.97</v>
       </c>
       <c r="F7" t="n">
-        <v>-2565.58</v>
+        <v>-613.41</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0355</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>2830.05</v>
+        <v>1757.61</v>
       </c>
       <c r="I7" t="n">
-        <v>69187.32000000001</v>
+        <v>66958.33</v>
       </c>
       <c r="J7" t="n">
-        <v>70748.42999999999</v>
+        <v>66250.81</v>
       </c>
       <c r="K7" t="n">
-        <v>71442.86</v>
+        <v>68373.36</v>
       </c>
       <c r="L7" t="n">
-        <v>72137.28999999999</v>
+        <v>70495.89999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>73265.06</v>
+        <v>71203.41</v>
       </c>
       <c r="N7" t="n">
-        <v>74392.83</v>
+        <v>71910.92</v>
       </c>
       <c r="O7" t="n">
-        <v>74653.92999999999</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>75448.49000000001</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
@@ -1133,50 +1138,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69615.08</v>
+        <v>70114.09</v>
       </c>
       <c r="C8" t="n">
-        <v>70218.71000000001</v>
+        <v>72594.22</v>
       </c>
       <c r="D8" t="n">
-        <v>68461.10000000001</v>
+        <v>69982.67</v>
       </c>
       <c r="E8" t="n">
-        <v>69174.97</v>
+        <v>72366.34</v>
       </c>
       <c r="F8" t="n">
-        <v>-613.41</v>
+        <v>3191.38</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0461</v>
       </c>
       <c r="H8" t="n">
-        <v>1757.61</v>
+        <v>2611.55</v>
       </c>
       <c r="I8" t="n">
-        <v>66958.33</v>
+        <v>66703.49000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>66250.81</v>
+        <v>67334.89</v>
       </c>
       <c r="K8" t="n">
-        <v>68373.36</v>
+        <v>68296.16</v>
       </c>
       <c r="L8" t="n">
-        <v>70495.89999999999</v>
+        <v>69257.44</v>
       </c>
       <c r="M8" t="n">
-        <v>71203.41</v>
+        <v>70053.77</v>
       </c>
       <c r="N8" t="n">
-        <v>71910.92</v>
+        <v>70850.11</v>
       </c>
       <c r="O8" t="n">
-        <v>75448.49000000001</v>
+        <v>71976.32000000001</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1184,28 +1189,32 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W8" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1213,83 +1222,81 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70114.09</v>
+        <v>71587.71000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>72594.22</v>
+        <v>71786.28</v>
       </c>
       <c r="D9" t="n">
-        <v>69982.67</v>
+        <v>68639.84</v>
       </c>
       <c r="E9" t="n">
-        <v>72366.34</v>
+        <v>69360.88</v>
       </c>
       <c r="F9" t="n">
-        <v>3191.38</v>
+        <v>-3005.46</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0461</v>
+        <v>-0.0415</v>
       </c>
       <c r="H9" t="n">
-        <v>2611.55</v>
+        <v>3146.44</v>
       </c>
       <c r="I9" t="n">
-        <v>66703.49000000001</v>
+        <v>67371.12</v>
       </c>
       <c r="J9" t="n">
-        <v>67334.89</v>
+        <v>70293.75</v>
       </c>
       <c r="K9" t="n">
-        <v>68296.16</v>
+        <v>71060.57000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>69257.44</v>
+        <v>71827.39</v>
       </c>
       <c r="M9" t="n">
-        <v>70053.77</v>
+        <v>73672.12</v>
       </c>
       <c r="N9" t="n">
-        <v>70850.11</v>
+        <v>75516.84</v>
       </c>
       <c r="O9" t="n">
-        <v>71976.32000000001</v>
+        <v>75205.77</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W9" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W9" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1297,67 +1304,63 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71587.71000000001</v>
+        <v>69609.88</v>
       </c>
       <c r="C10" t="n">
-        <v>71786.28</v>
+        <v>69609.88</v>
       </c>
       <c r="D10" t="n">
-        <v>68639.84</v>
+        <v>67997.57000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>69360.88</v>
+        <v>69468.11</v>
       </c>
       <c r="F10" t="n">
-        <v>-3005.46</v>
+        <v>107.23</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0415</v>
+        <v>0.0015</v>
       </c>
       <c r="H10" t="n">
-        <v>3146.44</v>
+        <v>1612.31</v>
       </c>
       <c r="I10" t="n">
-        <v>67371.12</v>
+        <v>65493.41</v>
       </c>
       <c r="J10" t="n">
-        <v>70293.75</v>
+        <v>65788.36</v>
       </c>
       <c r="K10" t="n">
-        <v>71060.57000000001</v>
+        <v>67787.66</v>
       </c>
       <c r="L10" t="n">
-        <v>71827.39</v>
+        <v>69786.97</v>
       </c>
       <c r="M10" t="n">
-        <v>73672.12</v>
+        <v>70934.10000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>75516.84</v>
+        <v>72081.23</v>
       </c>
       <c r="O10" t="n">
-        <v>75205.77</v>
+        <v>74932.72</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1374,55 +1377,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>69609.88</v>
+        <v>70085.60000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>69609.88</v>
+        <v>70667</v>
       </c>
       <c r="D11" t="n">
-        <v>67997.57000000001</v>
+        <v>69302.19</v>
       </c>
       <c r="E11" t="n">
-        <v>69468.11</v>
+        <v>70062.32000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>107.23</v>
+        <v>594.21</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0086</v>
       </c>
       <c r="H11" t="n">
-        <v>1612.31</v>
+        <v>1364.81</v>
       </c>
       <c r="I11" t="n">
-        <v>65493.41</v>
+        <v>66385.25999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>65788.36</v>
+        <v>68187.99000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>67787.66</v>
+        <v>68661.95</v>
       </c>
       <c r="L11" t="n">
-        <v>69786.97</v>
+        <v>69135.92</v>
       </c>
       <c r="M11" t="n">
-        <v>70934.10000000001</v>
+        <v>70274.27</v>
       </c>
       <c r="N11" t="n">
-        <v>72081.23</v>
+        <v>71412.61</v>
       </c>
       <c r="O11" t="n">
-        <v>74932.72</v>
+        <v>71222.2</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1433,13 +1440,15 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1454,57 +1463,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>70085.60000000001</v>
+        <v>70774.28</v>
       </c>
       <c r="C12" t="n">
-        <v>70667</v>
+        <v>71962.34</v>
       </c>
       <c r="D12" t="n">
-        <v>69302.19</v>
+        <v>70126.14</v>
       </c>
       <c r="E12" t="n">
-        <v>70062.32000000001</v>
+        <v>70474.96000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>594.21</v>
+        <v>412.64</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0059</v>
       </c>
       <c r="H12" t="n">
-        <v>1364.81</v>
+        <v>1836.2</v>
       </c>
       <c r="I12" t="n">
-        <v>66385.25999999999</v>
+        <v>67937.38</v>
       </c>
       <c r="J12" t="n">
-        <v>68187.99000000001</v>
+        <v>68736.37</v>
       </c>
       <c r="K12" t="n">
-        <v>68661.95</v>
+        <v>69379.91</v>
       </c>
       <c r="L12" t="n">
-        <v>69135.92</v>
+        <v>70023.46000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>70274.27</v>
+        <v>70744.73</v>
       </c>
       <c r="N12" t="n">
-        <v>71412.61</v>
+        <v>71466</v>
       </c>
       <c r="O12" t="n">
-        <v>71222.2</v>
+        <v>72031.81</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1525,8 +1534,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1545,74 +1556,74 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>70774.28</v>
+        <v>70039.89</v>
       </c>
       <c r="C13" t="n">
-        <v>71962.34</v>
+        <v>70081.39</v>
       </c>
       <c r="D13" t="n">
-        <v>70126.14</v>
+        <v>68676.25999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>70474.96000000001</v>
+        <v>68733.14999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>412.64</v>
+        <v>-1741.81</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0247</v>
       </c>
       <c r="H13" t="n">
-        <v>1836.2</v>
+        <v>1405.13</v>
       </c>
       <c r="I13" t="n">
-        <v>67937.38</v>
+        <v>68289.94</v>
       </c>
       <c r="J13" t="n">
-        <v>68736.37</v>
+        <v>68354.12</v>
       </c>
       <c r="K13" t="n">
-        <v>69379.91</v>
+        <v>69556.86</v>
       </c>
       <c r="L13" t="n">
-        <v>70023.46000000001</v>
+        <v>70759.60000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>70744.73</v>
+        <v>71393.06</v>
       </c>
       <c r="N13" t="n">
-        <v>71466</v>
+        <v>72026.52</v>
       </c>
       <c r="O13" t="n">
-        <v>72031.81</v>
+        <v>73798.55</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
+      <c r="Q13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1622,84 +1633,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>70039.89</v>
+        <v>68676.06</v>
       </c>
       <c r="C14" t="n">
-        <v>70081.39</v>
+        <v>69788.03</v>
       </c>
       <c r="D14" t="n">
-        <v>68676.25999999999</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>68733.14999999999</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1741.81</v>
+        <v>1010.92</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0147</v>
       </c>
       <c r="H14" t="n">
-        <v>1405.13</v>
+        <v>2178.54</v>
       </c>
       <c r="I14" t="n">
-        <v>68289.94</v>
+        <v>67271.12</v>
       </c>
       <c r="J14" t="n">
-        <v>68354.12</v>
+        <v>67005.17999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>69556.86</v>
+        <v>68030.58</v>
       </c>
       <c r="L14" t="n">
-        <v>70759.60000000001</v>
+        <v>69055.99000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>71393.06</v>
+        <v>69435.71000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>72026.52</v>
+        <v>69815.44</v>
       </c>
       <c r="O14" t="n">
-        <v>73798.55</v>
+        <v>71486.52</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
@@ -1708,55 +1717,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>68676.06</v>
+        <v>69973.34</v>
       </c>
       <c r="C15" t="n">
-        <v>69788.03</v>
+        <v>70384.59</v>
       </c>
       <c r="D15" t="n">
-        <v>67609.49000000001</v>
+        <v>68904.41</v>
       </c>
       <c r="E15" t="n">
-        <v>69744.07000000001</v>
+        <v>69737.69</v>
       </c>
       <c r="F15" t="n">
-        <v>1010.92</v>
+        <v>-6.38</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0001</v>
       </c>
       <c r="H15" t="n">
-        <v>2178.54</v>
+        <v>1480.19</v>
       </c>
       <c r="I15" t="n">
-        <v>67271.12</v>
+        <v>65430.95</v>
       </c>
       <c r="J15" t="n">
-        <v>67005.17999999999</v>
+        <v>68088.19</v>
       </c>
       <c r="K15" t="n">
-        <v>68030.58</v>
+        <v>68654.8</v>
       </c>
       <c r="L15" t="n">
-        <v>69055.99000000001</v>
+        <v>69221.42</v>
       </c>
       <c r="M15" t="n">
-        <v>69435.71000000001</v>
+        <v>70833.34</v>
       </c>
       <c r="N15" t="n">
-        <v>69815.44</v>
+        <v>72445.25999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>71486.52</v>
+        <v>71966.57000000001</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1764,25 +1777,19 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1794,70 +1801,74 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>69973.34</v>
+        <v>69460.08</v>
       </c>
       <c r="C16" t="n">
-        <v>70384.59</v>
+        <v>69957.50999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>68904.41</v>
+        <v>68003.92</v>
       </c>
       <c r="E16" t="n">
-        <v>69737.69</v>
+        <v>68256.96000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.38</v>
+        <v>-1480.73</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0212</v>
       </c>
       <c r="H16" t="n">
-        <v>1480.19</v>
+        <v>1953.59</v>
       </c>
       <c r="I16" t="n">
-        <v>65430.95</v>
+        <v>67424.22</v>
       </c>
       <c r="J16" t="n">
-        <v>68088.19</v>
+        <v>68304.09</v>
       </c>
       <c r="K16" t="n">
-        <v>68654.8</v>
+        <v>68997.59</v>
       </c>
       <c r="L16" t="n">
-        <v>69221.42</v>
+        <v>69691.09</v>
       </c>
       <c r="M16" t="n">
-        <v>70833.34</v>
+        <v>70477.78</v>
       </c>
       <c r="N16" t="n">
-        <v>72445.25999999999</v>
+        <v>71264.47</v>
       </c>
       <c r="O16" t="n">
-        <v>71966.57000000001</v>
+        <v>71864.78</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1874,71 +1885,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>69460.08</v>
+        <v>67704.16</v>
       </c>
       <c r="C17" t="n">
-        <v>69957.50999999999</v>
+        <v>68432.67999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>68003.92</v>
+        <v>66819.05</v>
       </c>
       <c r="E17" t="n">
-        <v>68256.96000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="F17" t="n">
-        <v>-1480.73</v>
+        <v>-1437.91</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="H17" t="n">
-        <v>1953.59</v>
+        <v>1613.63</v>
       </c>
       <c r="I17" t="n">
-        <v>67424.22</v>
+        <v>66050.34</v>
       </c>
       <c r="J17" t="n">
-        <v>68304.09</v>
+        <v>65941.5</v>
       </c>
       <c r="K17" t="n">
-        <v>68997.59</v>
+        <v>67280.17</v>
       </c>
       <c r="L17" t="n">
-        <v>69691.09</v>
+        <v>68618.84</v>
       </c>
       <c r="M17" t="n">
-        <v>70477.78</v>
+        <v>69233.75</v>
       </c>
       <c r="N17" t="n">
-        <v>71264.47</v>
+        <v>69848.67</v>
       </c>
       <c r="O17" t="n">
-        <v>71864.78</v>
+        <v>71911.09</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
@@ -1965,50 +1970,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>67704.16</v>
+        <v>67046.37</v>
       </c>
       <c r="C18" t="n">
-        <v>68432.67999999999</v>
+        <v>68447.89</v>
       </c>
       <c r="D18" t="n">
-        <v>66819.05</v>
+        <v>67008.89</v>
       </c>
       <c r="E18" t="n">
-        <v>66819.05</v>
+        <v>67743.85000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-1437.91</v>
+        <v>924.8</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0211</v>
+        <v>0.0138</v>
       </c>
       <c r="H18" t="n">
-        <v>1613.63</v>
+        <v>1439</v>
       </c>
       <c r="I18" t="n">
-        <v>66050.34</v>
+        <v>65205.41</v>
       </c>
       <c r="J18" t="n">
-        <v>65941.5</v>
+        <v>64802.01</v>
       </c>
       <c r="K18" t="n">
-        <v>67280.17</v>
+        <v>66012.23</v>
       </c>
       <c r="L18" t="n">
-        <v>68618.84</v>
+        <v>67222.46000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>69233.75</v>
+        <v>67625.86</v>
       </c>
       <c r="N18" t="n">
-        <v>69848.67</v>
+        <v>68029.27</v>
       </c>
       <c r="O18" t="n">
-        <v>71911.09</v>
+        <v>70046.31</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2016,21 +2021,23 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2040,55 +2047,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>67046.37</v>
+        <v>68526.72</v>
       </c>
       <c r="C19" t="n">
-        <v>68447.89</v>
+        <v>69374.86</v>
       </c>
       <c r="D19" t="n">
-        <v>67008.89</v>
+        <v>68271.91</v>
       </c>
       <c r="E19" t="n">
-        <v>67743.85000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F19" t="n">
-        <v>924.8</v>
+        <v>813.88</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.012</v>
       </c>
       <c r="H19" t="n">
-        <v>1439</v>
+        <v>1102.95</v>
       </c>
       <c r="I19" t="n">
-        <v>65205.41</v>
+        <v>65569.89</v>
       </c>
       <c r="J19" t="n">
-        <v>64802.01</v>
+        <v>66312.58</v>
       </c>
       <c r="K19" t="n">
-        <v>66012.23</v>
+        <v>67024.35000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>67222.46000000001</v>
+        <v>67736.12</v>
       </c>
       <c r="M19" t="n">
-        <v>67625.86</v>
+        <v>68463.35000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>68029.27</v>
+        <v>69190.58</v>
       </c>
       <c r="O19" t="n">
-        <v>70046.31</v>
+        <v>69886.89</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2131,74 +2142,76 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>68526.72</v>
+        <v>68410.63</v>
       </c>
       <c r="C20" t="n">
-        <v>69374.86</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>68271.91</v>
+        <v>66653.11</v>
       </c>
       <c r="E20" t="n">
-        <v>68557.73</v>
+        <v>67242.73</v>
       </c>
       <c r="F20" t="n">
-        <v>813.88</v>
+        <v>-1315</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0192</v>
       </c>
       <c r="H20" t="n">
-        <v>1102.95</v>
+        <v>2425.1</v>
       </c>
       <c r="I20" t="n">
-        <v>65569.89</v>
+        <v>67168.95</v>
       </c>
       <c r="J20" t="n">
-        <v>66312.58</v>
+        <v>67321.95</v>
       </c>
       <c r="K20" t="n">
-        <v>67024.35000000001</v>
+        <v>68006.25</v>
       </c>
       <c r="L20" t="n">
-        <v>67736.12</v>
+        <v>68690.55</v>
       </c>
       <c r="M20" t="n">
-        <v>68463.35000000001</v>
+        <v>69109.2</v>
       </c>
       <c r="N20" t="n">
-        <v>69190.58</v>
+        <v>69527.85000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>69886.89</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+        <v>70477.81</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2208,78 +2221,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>68410.63</v>
+        <v>67002.94</v>
       </c>
       <c r="C21" t="n">
-        <v>69078.21000000001</v>
+        <v>67800.17999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>66653.11</v>
+        <v>66268.60000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>67242.73</v>
+        <v>67743.5</v>
       </c>
       <c r="F21" t="n">
-        <v>-1315</v>
+        <v>500.77</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0074</v>
       </c>
       <c r="H21" t="n">
-        <v>2425.1</v>
+        <v>1531.58</v>
       </c>
       <c r="I21" t="n">
-        <v>67168.95</v>
+        <v>64228.01</v>
       </c>
       <c r="J21" t="n">
-        <v>67321.95</v>
+        <v>64506.16</v>
       </c>
       <c r="K21" t="n">
-        <v>68006.25</v>
+        <v>66030.17999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>68690.55</v>
+        <v>67554.19</v>
       </c>
       <c r="M21" t="n">
-        <v>69109.2</v>
+        <v>68455.28</v>
       </c>
       <c r="N21" t="n">
-        <v>69527.85000000001</v>
+        <v>69356.36</v>
       </c>
       <c r="O21" t="n">
-        <v>70477.81</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>71503.31</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2296,55 +2299,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>67002.94</v>
+        <v>67989.74000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>67800.17999999999</v>
+        <v>68798.24000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>66268.60000000001</v>
+        <v>67833.17</v>
       </c>
       <c r="E22" t="n">
-        <v>67743.5</v>
+        <v>68751.50999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>500.77</v>
+        <v>1008.01</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0149</v>
       </c>
       <c r="H22" t="n">
-        <v>1531.58</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>64228.01</v>
+        <v>64737.02</v>
       </c>
       <c r="J22" t="n">
-        <v>64506.16</v>
+        <v>66566.48</v>
       </c>
       <c r="K22" t="n">
-        <v>66030.17999999999</v>
+        <v>66977.71000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>67554.19</v>
+        <v>67388.95</v>
       </c>
       <c r="M22" t="n">
-        <v>68455.28</v>
+        <v>68509.28999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>69356.36</v>
+        <v>69629.63</v>
       </c>
       <c r="O22" t="n">
-        <v>71503.31</v>
+        <v>69331.75999999999</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2357,11 +2364,13 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2376,77 +2385,81 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>67989.74000000001</v>
+        <v>67900.42999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>68798.24000000001</v>
+        <v>68069.82000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>67833.17</v>
+        <v>66499.49000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>68751.50999999999</v>
+        <v>66835.53999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>1008.01</v>
+        <v>-1915.97</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0279</v>
       </c>
       <c r="H23" t="n">
-        <v>965.0700000000001</v>
+        <v>1570.33</v>
       </c>
       <c r="I23" t="n">
-        <v>64737.02</v>
+        <v>66868.10000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>66566.48</v>
+        <v>68004.34</v>
       </c>
       <c r="K23" t="n">
-        <v>66977.71000000001</v>
+        <v>68268.97</v>
       </c>
       <c r="L23" t="n">
-        <v>67388.95</v>
+        <v>68533.61</v>
       </c>
       <c r="M23" t="n">
-        <v>68509.28999999999</v>
+        <v>69234.03999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>69629.63</v>
+        <v>69934.48</v>
       </c>
       <c r="O23" t="n">
-        <v>69331.75999999999</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+        <v>69763.31</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2458,59 +2471,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>67900.42999999999</v>
+        <v>66339.85000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>68069.82000000001</v>
+        <v>66441.77</v>
       </c>
       <c r="D24" t="n">
-        <v>66499.49000000001</v>
+        <v>62704.6</v>
       </c>
       <c r="E24" t="n">
-        <v>66835.53999999999</v>
+        <v>64141.12</v>
       </c>
       <c r="F24" t="n">
-        <v>-1915.97</v>
+        <v>-2694.42</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0403</v>
       </c>
       <c r="H24" t="n">
-        <v>1570.33</v>
+        <v>3737.17</v>
       </c>
       <c r="I24" t="n">
-        <v>66868.10000000001</v>
+        <v>64929.16</v>
       </c>
       <c r="J24" t="n">
-        <v>68004.34</v>
+        <v>65040.65</v>
       </c>
       <c r="K24" t="n">
-        <v>68268.97</v>
+        <v>66050.38</v>
       </c>
       <c r="L24" t="n">
-        <v>68533.61</v>
+        <v>67060.10000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>69234.03999999999</v>
+        <v>67620.7</v>
       </c>
       <c r="N24" t="n">
-        <v>69934.48</v>
+        <v>68181.31</v>
       </c>
       <c r="O24" t="n">
-        <v>69763.31</v>
+        <v>69640.14999999999</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
@@ -2551,74 +2560,70 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>66339.85000000001</v>
+        <v>64544.05</v>
       </c>
       <c r="C25" t="n">
-        <v>66441.77</v>
+        <v>66232.19</v>
       </c>
       <c r="D25" t="n">
-        <v>62704.6</v>
+        <v>64203.47</v>
       </c>
       <c r="E25" t="n">
-        <v>64141.12</v>
+        <v>66232.19</v>
       </c>
       <c r="F25" t="n">
-        <v>-2694.42</v>
+        <v>2091.07</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0326</v>
       </c>
       <c r="H25" t="n">
-        <v>3737.17</v>
+        <v>2028.72</v>
       </c>
       <c r="I25" t="n">
-        <v>64929.16</v>
+        <v>58967.43</v>
       </c>
       <c r="J25" t="n">
-        <v>65040.65</v>
+        <v>60187.92</v>
       </c>
       <c r="K25" t="n">
-        <v>66050.38</v>
+        <v>62272.54</v>
       </c>
       <c r="L25" t="n">
-        <v>67060.10000000001</v>
+        <v>64357.15</v>
       </c>
       <c r="M25" t="n">
-        <v>67620.7</v>
+        <v>66009.71000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>68181.31</v>
+        <v>67662.25999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>69640.14999999999</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>70178.95</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2630,55 +2635,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>64544.05</v>
+        <v>66449.27</v>
       </c>
       <c r="C26" t="n">
-        <v>66232.19</v>
+        <v>67592.2</v>
       </c>
       <c r="D26" t="n">
-        <v>64203.47</v>
+        <v>65955.60000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>66232.19</v>
+        <v>66115.60000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>2091.07</v>
+        <v>-116.59</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0326</v>
+        <v>-0.0018</v>
       </c>
       <c r="H26" t="n">
-        <v>2028.72</v>
+        <v>1636.6</v>
       </c>
       <c r="I26" t="n">
-        <v>58967.43</v>
+        <v>62174.75</v>
       </c>
       <c r="J26" t="n">
-        <v>60187.92</v>
+        <v>64710.65</v>
       </c>
       <c r="K26" t="n">
-        <v>62272.54</v>
+        <v>65217.83</v>
       </c>
       <c r="L26" t="n">
-        <v>64357.15</v>
+        <v>65725.00999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>66009.71000000001</v>
+        <v>67246.55</v>
       </c>
       <c r="N26" t="n">
-        <v>67662.25999999999</v>
+        <v>68768.09</v>
       </c>
       <c r="O26" t="n">
-        <v>70178.95</v>
+        <v>68260.91</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2691,12 +2700,12 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U26" s="8" t="n">
@@ -2719,50 +2728,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>66449.27</v>
+        <v>66421.00999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>67592.2</v>
+        <v>67022.37</v>
       </c>
       <c r="D27" t="n">
-        <v>65955.60000000001</v>
+        <v>66208.66</v>
       </c>
       <c r="E27" t="n">
-        <v>66115.60000000001</v>
+        <v>66422.60000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-116.59</v>
+        <v>307</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0046</v>
       </c>
       <c r="H27" t="n">
-        <v>1636.6</v>
+        <v>813.71</v>
       </c>
       <c r="I27" t="n">
-        <v>62174.75</v>
+        <v>64319</v>
       </c>
       <c r="J27" t="n">
-        <v>64710.65</v>
+        <v>64149.85</v>
       </c>
       <c r="K27" t="n">
-        <v>65217.83</v>
+        <v>65297.3</v>
       </c>
       <c r="L27" t="n">
-        <v>65725.00999999999</v>
+        <v>66444.75</v>
       </c>
       <c r="M27" t="n">
-        <v>67246.55</v>
+        <v>66933.89999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>68768.09</v>
+        <v>67423.05</v>
       </c>
       <c r="O27" t="n">
-        <v>68260.91</v>
+        <v>69228.8</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2773,9 +2782,9 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2803,69 +2812,73 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>66421.00999999999</v>
+        <v>65584.25</v>
       </c>
       <c r="C28" t="n">
-        <v>67022.37</v>
+        <v>65720.81</v>
       </c>
       <c r="D28" t="n">
-        <v>66208.66</v>
+        <v>64201.03</v>
       </c>
       <c r="E28" t="n">
-        <v>66422.60000000001</v>
+        <v>64611.15</v>
       </c>
       <c r="F28" t="n">
-        <v>307</v>
+        <v>-1811.45</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0273</v>
       </c>
       <c r="H28" t="n">
-        <v>813.71</v>
+        <v>1519.78</v>
       </c>
       <c r="I28" t="n">
-        <v>64319</v>
+        <v>65394.95</v>
       </c>
       <c r="J28" t="n">
-        <v>64149.85</v>
+        <v>65512.44</v>
       </c>
       <c r="K28" t="n">
-        <v>65297.3</v>
+        <v>66015.75</v>
       </c>
       <c r="L28" t="n">
-        <v>66444.75</v>
+        <v>66519.06</v>
       </c>
       <c r="M28" t="n">
-        <v>66933.89999999999</v>
+        <v>66829.46000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>67423.05</v>
+        <v>67139.86</v>
       </c>
       <c r="O28" t="n">
-        <v>69228.8</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+        <v>67836.08</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2878,78 +2891,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>65584.25</v>
+        <v>65164.98</v>
       </c>
       <c r="C29" t="n">
-        <v>65720.81</v>
+        <v>65220.69</v>
       </c>
       <c r="D29" t="n">
-        <v>64201.03</v>
+        <v>64123.4</v>
       </c>
       <c r="E29" t="n">
-        <v>64611.15</v>
+        <v>64931.19</v>
       </c>
       <c r="F29" t="n">
-        <v>-1811.45</v>
+        <v>320.04</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.005</v>
       </c>
       <c r="H29" t="n">
-        <v>1519.78</v>
+        <v>1097.29</v>
       </c>
       <c r="I29" t="n">
-        <v>65394.95</v>
+        <v>62681.25</v>
       </c>
       <c r="J29" t="n">
-        <v>65512.44</v>
+        <v>62916.48</v>
       </c>
       <c r="K29" t="n">
-        <v>66015.75</v>
+        <v>63851.26</v>
       </c>
       <c r="L29" t="n">
-        <v>66519.06</v>
+        <v>64786.04</v>
       </c>
       <c r="M29" t="n">
-        <v>66829.46000000001</v>
+        <v>65371.04</v>
       </c>
       <c r="N29" t="n">
-        <v>67139.86</v>
+        <v>65956.03999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>67836.08</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>67240.59</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2966,68 +2969,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>65164.98</v>
+        <v>64539.92</v>
       </c>
       <c r="C30" t="n">
-        <v>65220.69</v>
+        <v>64573.18</v>
       </c>
       <c r="D30" t="n">
-        <v>64123.4</v>
+        <v>61923.6</v>
       </c>
       <c r="E30" t="n">
-        <v>64931.19</v>
+        <v>62364.92</v>
       </c>
       <c r="F30" t="n">
-        <v>320.04</v>
+        <v>-2566.27</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0395</v>
       </c>
       <c r="H30" t="n">
-        <v>1097.29</v>
+        <v>2649.58</v>
       </c>
       <c r="I30" t="n">
-        <v>62681.25</v>
+        <v>63026.11</v>
       </c>
       <c r="J30" t="n">
-        <v>62916.48</v>
+        <v>63963.47</v>
       </c>
       <c r="K30" t="n">
-        <v>63851.26</v>
+        <v>64382.54</v>
       </c>
       <c r="L30" t="n">
-        <v>64786.04</v>
+        <v>64801.62</v>
       </c>
       <c r="M30" t="n">
-        <v>65371.04</v>
+        <v>65479.84</v>
       </c>
       <c r="N30" t="n">
-        <v>65956.03999999999</v>
+        <v>66158.06</v>
       </c>
       <c r="O30" t="n">
-        <v>67240.59</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>66317.98</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3044,73 +3057,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>64539.92</v>
+        <v>62734.68</v>
       </c>
       <c r="C31" t="n">
-        <v>64573.18</v>
+        <v>63138.04</v>
       </c>
       <c r="D31" t="n">
-        <v>61923.6</v>
+        <v>60448.9</v>
       </c>
       <c r="E31" t="n">
-        <v>62364.92</v>
+        <v>61434.19</v>
       </c>
       <c r="F31" t="n">
-        <v>-2566.27</v>
+        <v>-930.73</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0149</v>
       </c>
       <c r="H31" t="n">
-        <v>2649.58</v>
+        <v>2689.14</v>
       </c>
       <c r="I31" t="n">
-        <v>63026.11</v>
+        <v>59274.02</v>
       </c>
       <c r="J31" t="n">
-        <v>63963.47</v>
+        <v>59273.61</v>
       </c>
       <c r="K31" t="n">
-        <v>64382.54</v>
+        <v>61040.13</v>
       </c>
       <c r="L31" t="n">
-        <v>64801.62</v>
+        <v>62806.66</v>
       </c>
       <c r="M31" t="n">
-        <v>65479.84</v>
+        <v>63689.71</v>
       </c>
       <c r="N31" t="n">
-        <v>66158.06</v>
+        <v>64572.77</v>
       </c>
       <c r="O31" t="n">
-        <v>66317.98</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
+        <v>67222.75999999999</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
@@ -3137,50 +3142,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>62734.68</v>
+        <v>61258.34</v>
       </c>
       <c r="C32" t="n">
-        <v>63138.04</v>
+        <v>62924.84</v>
       </c>
       <c r="D32" t="n">
-        <v>60448.9</v>
+        <v>61049.7</v>
       </c>
       <c r="E32" t="n">
-        <v>61434.19</v>
+        <v>61867.43</v>
       </c>
       <c r="F32" t="n">
-        <v>-930.73</v>
+        <v>433.24</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0071</v>
       </c>
       <c r="H32" t="n">
-        <v>2689.14</v>
+        <v>1875.14</v>
       </c>
       <c r="I32" t="n">
-        <v>59274.02</v>
+        <v>57759.76</v>
       </c>
       <c r="J32" t="n">
-        <v>59273.61</v>
+        <v>58565.41</v>
       </c>
       <c r="K32" t="n">
-        <v>61040.13</v>
+        <v>60089.62</v>
       </c>
       <c r="L32" t="n">
-        <v>62806.66</v>
+        <v>61613.83</v>
       </c>
       <c r="M32" t="n">
-        <v>63689.71</v>
+        <v>62778.76</v>
       </c>
       <c r="N32" t="n">
-        <v>64572.77</v>
+        <v>63943.69</v>
       </c>
       <c r="O32" t="n">
-        <v>67222.75999999999</v>
+        <v>65827.17999999999</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3188,18 +3193,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3212,55 +3217,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>61258.34</v>
+        <v>61957.1</v>
       </c>
       <c r="C33" t="n">
-        <v>62924.84</v>
+        <v>65364.73</v>
       </c>
       <c r="D33" t="n">
-        <v>61049.7</v>
+        <v>61948.23</v>
       </c>
       <c r="E33" t="n">
-        <v>61867.43</v>
+        <v>64362.02</v>
       </c>
       <c r="F33" t="n">
-        <v>433.24</v>
+        <v>2494.59</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0403</v>
       </c>
       <c r="H33" t="n">
-        <v>1875.14</v>
+        <v>3416.5</v>
       </c>
       <c r="I33" t="n">
-        <v>57759.76</v>
+        <v>59174.56</v>
       </c>
       <c r="J33" t="n">
-        <v>58565.41</v>
+        <v>59932.37</v>
       </c>
       <c r="K33" t="n">
-        <v>60089.62</v>
+        <v>60929.86</v>
       </c>
       <c r="L33" t="n">
-        <v>61613.83</v>
+        <v>61927.35</v>
       </c>
       <c r="M33" t="n">
-        <v>62778.76</v>
+        <v>62805</v>
       </c>
       <c r="N33" t="n">
-        <v>63943.69</v>
+        <v>63682.65</v>
       </c>
       <c r="O33" t="n">
-        <v>65827.17999999999</v>
+        <v>64799.98</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3273,7 +3282,7 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -3281,70 +3290,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>61957.1</v>
+        <v>63834.95</v>
       </c>
       <c r="C34" t="n">
-        <v>65364.73</v>
+        <v>63905.12</v>
       </c>
       <c r="D34" t="n">
-        <v>61948.23</v>
+        <v>62703.47</v>
       </c>
       <c r="E34" t="n">
-        <v>64362.02</v>
+        <v>63754.9</v>
       </c>
       <c r="F34" t="n">
-        <v>2494.59</v>
+        <v>-607.12</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0403</v>
+        <v>-0.0094</v>
       </c>
       <c r="H34" t="n">
-        <v>3416.5</v>
+        <v>1201.65</v>
       </c>
       <c r="I34" t="n">
-        <v>59174.56</v>
+        <v>58531.73</v>
       </c>
       <c r="J34" t="n">
-        <v>59932.37</v>
+        <v>61298.29</v>
       </c>
       <c r="K34" t="n">
-        <v>60929.86</v>
+        <v>62653.77</v>
       </c>
       <c r="L34" t="n">
-        <v>61927.35</v>
+        <v>64009.25</v>
       </c>
       <c r="M34" t="n">
-        <v>62805</v>
+        <v>66070.27</v>
       </c>
       <c r="N34" t="n">
-        <v>63682.65</v>
+        <v>68131.28999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>64799.98</v>
+        <v>68781.23</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3355,80 +3364,78 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>63834.95</v>
+        <v>63995.28</v>
       </c>
       <c r="C35" t="n">
-        <v>63905.12</v>
+        <v>64240.5</v>
       </c>
       <c r="D35" t="n">
-        <v>62703.47</v>
+        <v>62864.43</v>
       </c>
       <c r="E35" t="n">
-        <v>63754.9</v>
+        <v>63957.53</v>
       </c>
       <c r="F35" t="n">
-        <v>-607.12</v>
+        <v>202.63</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0032</v>
       </c>
       <c r="H35" t="n">
-        <v>1201.65</v>
+        <v>1376.07</v>
       </c>
       <c r="I35" t="n">
-        <v>58531.73</v>
+        <v>61501.82</v>
       </c>
       <c r="J35" t="n">
-        <v>61298.29</v>
+        <v>62778.55</v>
       </c>
       <c r="K35" t="n">
-        <v>62653.77</v>
+        <v>63154.07</v>
       </c>
       <c r="L35" t="n">
-        <v>64009.25</v>
+        <v>63529.6</v>
       </c>
       <c r="M35" t="n">
-        <v>66070.27</v>
+        <v>64355.72</v>
       </c>
       <c r="N35" t="n">
-        <v>68131.28999999999</v>
+        <v>65181.85</v>
       </c>
       <c r="O35" t="n">
-        <v>68781.23</v>
+        <v>65106.77</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3436,16 +3443,20 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3458,59 +3469,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>63995.28</v>
+        <v>64565.27</v>
       </c>
       <c r="C36" t="n">
-        <v>64240.5</v>
+        <v>66302.52</v>
       </c>
       <c r="D36" t="n">
-        <v>62864.43</v>
+        <v>64555.52</v>
       </c>
       <c r="E36" t="n">
-        <v>63957.53</v>
+        <v>66300.44</v>
       </c>
       <c r="F36" t="n">
-        <v>202.63</v>
+        <v>2342.91</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0366</v>
       </c>
       <c r="H36" t="n">
-        <v>1376.07</v>
+        <v>1747</v>
       </c>
       <c r="I36" t="n">
-        <v>61501.82</v>
+        <v>61488.36</v>
       </c>
       <c r="J36" t="n">
-        <v>62778.55</v>
+        <v>62783.99</v>
       </c>
       <c r="K36" t="n">
-        <v>63154.07</v>
+        <v>63269.5</v>
       </c>
       <c r="L36" t="n">
-        <v>63529.6</v>
+        <v>63755</v>
       </c>
       <c r="M36" t="n">
-        <v>64355.72</v>
+        <v>64645.57</v>
       </c>
       <c r="N36" t="n">
-        <v>65181.85</v>
+        <v>65536.13</v>
       </c>
       <c r="O36" t="n">
-        <v>65106.77</v>
+        <v>65616.57000000001</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3518,10 +3525,8 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
@@ -3530,14 +3535,18 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3549,134 +3558,136 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>64565.27</v>
+        <v>65896</v>
       </c>
       <c r="C37" t="n">
-        <v>66302.52</v>
+        <v>65983.13</v>
       </c>
       <c r="D37" t="n">
-        <v>64555.52</v>
+        <v>64942.07</v>
       </c>
       <c r="E37" t="n">
-        <v>66300.44</v>
+        <v>65683.25999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>2342.91</v>
+        <v>-617.1799999999999</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0366</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>1747</v>
+        <v>1041.06</v>
       </c>
       <c r="I37" t="n">
-        <v>61488.36</v>
+        <v>62808.52</v>
       </c>
       <c r="J37" t="n">
-        <v>62783.99</v>
+        <v>64989.14</v>
       </c>
       <c r="K37" t="n">
-        <v>63269.5</v>
+        <v>65426.94</v>
       </c>
       <c r="L37" t="n">
-        <v>63755</v>
+        <v>65864.73</v>
       </c>
       <c r="M37" t="n">
-        <v>64645.57</v>
+        <v>67173.94</v>
       </c>
       <c r="N37" t="n">
-        <v>65536.13</v>
+        <v>68483.14999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>65616.57000000001</v>
+        <v>68049.53</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>65896</v>
+        <v>65746.13</v>
       </c>
       <c r="C38" t="n">
-        <v>65983.13</v>
+        <v>65990.72</v>
       </c>
       <c r="D38" t="n">
-        <v>64942.07</v>
+        <v>64651.49</v>
       </c>
       <c r="E38" t="n">
-        <v>65683.25999999999</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-617.1799999999999</v>
+        <v>-76.55</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="H38" t="n">
-        <v>1041.06</v>
+        <v>1339.23</v>
       </c>
       <c r="I38" t="n">
-        <v>62808.52</v>
+        <v>63901.01</v>
       </c>
       <c r="J38" t="n">
-        <v>64989.14</v>
+        <v>64752.52</v>
       </c>
       <c r="K38" t="n">
-        <v>65426.94</v>
+        <v>65162.73</v>
       </c>
       <c r="L38" t="n">
-        <v>65864.73</v>
+        <v>65572.92999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>67173.94</v>
+        <v>66203.78999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>68483.14999999999</v>
+        <v>66834.64999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>68049.53</v>
+        <v>67024.2</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3691,9 +3702,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3719,74 +3730,74 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>65746.13</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>65990.72</v>
+        <v>67006.84</v>
       </c>
       <c r="D39" t="n">
-        <v>64651.49</v>
+        <v>65848.58</v>
       </c>
       <c r="E39" t="n">
-        <v>65606.71000000001</v>
+        <v>66970.22</v>
       </c>
       <c r="F39" t="n">
-        <v>-76.55</v>
+        <v>1363.51</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0208</v>
       </c>
       <c r="H39" t="n">
-        <v>1339.23</v>
+        <v>1158.27</v>
       </c>
       <c r="I39" t="n">
-        <v>63901.01</v>
+        <v>63312.26</v>
       </c>
       <c r="J39" t="n">
-        <v>64752.52</v>
+        <v>64410.28</v>
       </c>
       <c r="K39" t="n">
-        <v>65162.73</v>
+        <v>64937.1</v>
       </c>
       <c r="L39" t="n">
-        <v>65572.92999999999</v>
+        <v>65463.91</v>
       </c>
       <c r="M39" t="n">
-        <v>66203.78999999999</v>
+        <v>66276.33</v>
       </c>
       <c r="N39" t="n">
-        <v>66834.64999999999</v>
+        <v>67088.75</v>
       </c>
       <c r="O39" t="n">
-        <v>67024.2</v>
+        <v>67329.95</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3796,59 +3807,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>65905.10000000001</v>
+        <v>66994.05</v>
       </c>
       <c r="C40" t="n">
-        <v>67006.84</v>
+        <v>67569.36</v>
       </c>
       <c r="D40" t="n">
-        <v>65848.58</v>
+        <v>66735.75999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>66970.22</v>
+        <v>67524.06</v>
       </c>
       <c r="F40" t="n">
-        <v>1363.51</v>
+        <v>553.84</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="H40" t="n">
-        <v>1158.27</v>
+        <v>833.6</v>
       </c>
       <c r="I40" t="n">
-        <v>63312.26</v>
+        <v>64690.31</v>
       </c>
       <c r="J40" t="n">
-        <v>64410.28</v>
+        <v>66083.21000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>64937.1</v>
+        <v>66391.09</v>
       </c>
       <c r="L40" t="n">
-        <v>65463.91</v>
+        <v>66698.96000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>66276.33</v>
+        <v>67549.35000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>67088.75</v>
+        <v>68399.74000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>67329.95</v>
+        <v>68165.11</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3866,13 +3873,11 @@
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3887,50 +3892,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>66994.05</v>
+        <v>68033.17</v>
       </c>
       <c r="C41" t="n">
-        <v>67569.36</v>
+        <v>68799.71000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>66735.75999999999</v>
+        <v>68006.17</v>
       </c>
       <c r="E41" t="n">
-        <v>67524.06</v>
+        <v>68308.59</v>
       </c>
       <c r="F41" t="n">
-        <v>553.84</v>
+        <v>784.53</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0116</v>
       </c>
       <c r="H41" t="n">
-        <v>833.6</v>
+        <v>793.54</v>
       </c>
       <c r="I41" t="n">
-        <v>64690.31</v>
+        <v>65902.16</v>
       </c>
       <c r="J41" t="n">
-        <v>66083.21000000001</v>
+        <v>66876.21000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>66391.09</v>
+        <v>67107.25999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>66698.96000000001</v>
+        <v>67338.31</v>
       </c>
       <c r="M41" t="n">
-        <v>67549.35000000001</v>
+        <v>67940.86</v>
       </c>
       <c r="N41" t="n">
-        <v>68399.74000000001</v>
+        <v>68543.42</v>
       </c>
       <c r="O41" t="n">
-        <v>68165.11</v>
+        <v>68402.96000000001</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3948,14 +3953,18 @@
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
@@ -3967,50 +3976,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>68033.17</v>
+        <v>68811.17</v>
       </c>
       <c r="C42" t="n">
-        <v>68799.71000000001</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>68006.17</v>
+        <v>68471.14999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>68308.59</v>
+        <v>68713.8</v>
       </c>
       <c r="F42" t="n">
-        <v>784.53</v>
+        <v>405.2</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0059</v>
       </c>
       <c r="H42" t="n">
-        <v>793.54</v>
+        <v>1137.09</v>
       </c>
       <c r="I42" t="n">
-        <v>65902.16</v>
+        <v>67212.63</v>
       </c>
       <c r="J42" t="n">
-        <v>66876.21000000001</v>
+        <v>67467.88</v>
       </c>
       <c r="K42" t="n">
-        <v>67107.25999999999</v>
+        <v>67911.82000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>67338.31</v>
+        <v>68355.77</v>
       </c>
       <c r="M42" t="n">
-        <v>67940.86</v>
+        <v>68705.36</v>
       </c>
       <c r="N42" t="n">
-        <v>68543.42</v>
+        <v>69054.96000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>68402.96000000001</v>
+        <v>69593.25</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4028,7 +4037,7 @@
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U42" s="8" t="inlineStr">
@@ -4038,7 +4047,7 @@
       </c>
       <c r="V42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W42" s="9" t="inlineStr">
@@ -4051,50 +4060,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>68811.17</v>
+        <v>68882.06</v>
       </c>
       <c r="C43" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>68471.14999999999</v>
+        <v>68492.03999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>68713.8</v>
+        <v>69220.25</v>
       </c>
       <c r="F43" t="n">
-        <v>405.2</v>
+        <v>506.45</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="H43" t="n">
-        <v>1137.09</v>
+        <v>733.53</v>
       </c>
       <c r="I43" t="n">
-        <v>67212.63</v>
+        <v>67334.05</v>
       </c>
       <c r="J43" t="n">
-        <v>67467.88</v>
+        <v>67413.75</v>
       </c>
       <c r="K43" t="n">
-        <v>67911.82000000001</v>
+        <v>68145.25</v>
       </c>
       <c r="L43" t="n">
-        <v>68355.77</v>
+        <v>68876.75</v>
       </c>
       <c r="M43" t="n">
-        <v>68705.36</v>
+        <v>69282.34</v>
       </c>
       <c r="N43" t="n">
-        <v>69054.96000000001</v>
+        <v>69687.94</v>
       </c>
       <c r="O43" t="n">
-        <v>69593.25</v>
+        <v>70745.34</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4115,163 +4124,163 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>68882.06</v>
+        <v>68847.35000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>69225.57000000001</v>
+        <v>69093.2</v>
       </c>
       <c r="D44" t="n">
-        <v>68492.03999999999</v>
+        <v>67368.96000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>69220.25</v>
+        <v>67460.73</v>
       </c>
       <c r="F44" t="n">
-        <v>506.45</v>
+        <v>-1759.52</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0254</v>
       </c>
       <c r="H44" t="n">
-        <v>733.53</v>
+        <v>1724.24</v>
       </c>
       <c r="I44" t="n">
-        <v>67334.05</v>
+        <v>67758.50999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>67413.75</v>
+        <v>68667.44</v>
       </c>
       <c r="K44" t="n">
-        <v>68145.25</v>
+        <v>68853.48</v>
       </c>
       <c r="L44" t="n">
-        <v>68876.75</v>
+        <v>69039.53</v>
       </c>
       <c r="M44" t="n">
-        <v>69282.34</v>
+        <v>69587.02</v>
       </c>
       <c r="N44" t="n">
-        <v>69687.94</v>
+        <v>70134.5</v>
       </c>
       <c r="O44" t="n">
-        <v>70745.34</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+        <v>69959.10000000001</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>68847.35000000001</v>
+        <v>66812.27</v>
       </c>
       <c r="C45" t="n">
-        <v>69093.2</v>
+        <v>66833.50999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>67368.96000000001</v>
+        <v>65133.98</v>
       </c>
       <c r="E45" t="n">
-        <v>67460.73</v>
+        <v>65326.42</v>
       </c>
       <c r="F45" t="n">
-        <v>-1759.52</v>
+        <v>-2134.3</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="H45" t="n">
-        <v>1724.24</v>
+        <v>1699.53</v>
       </c>
       <c r="I45" t="n">
-        <v>67758.50999999999</v>
+        <v>65644.72</v>
       </c>
       <c r="J45" t="n">
-        <v>68667.44</v>
+        <v>65351.31</v>
       </c>
       <c r="K45" t="n">
-        <v>68853.48</v>
+        <v>66598.61</v>
       </c>
       <c r="L45" t="n">
-        <v>69039.53</v>
+        <v>67845.89999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>69587.02</v>
+        <v>68322.85000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>70134.5</v>
+        <v>68799.78999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>69959.10000000001</v>
+        <v>70817.45</v>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
@@ -4303,74 +4312,70 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>66812.27</v>
+        <v>65732.78999999999</v>
       </c>
       <c r="C46" t="n">
-        <v>66833.50999999999</v>
+        <v>66325.32000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>65133.98</v>
+        <v>65652.25</v>
       </c>
       <c r="E46" t="n">
-        <v>65326.42</v>
+        <v>66216.78999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>-2134.3</v>
+        <v>890.37</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H46" t="n">
-        <v>1699.53</v>
+        <v>673.0700000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>65644.72</v>
+        <v>63434.45</v>
       </c>
       <c r="J46" t="n">
-        <v>65351.31</v>
+        <v>63298.23</v>
       </c>
       <c r="K46" t="n">
-        <v>66598.61</v>
+        <v>64476.66</v>
       </c>
       <c r="L46" t="n">
-        <v>67845.89999999999</v>
+        <v>65655.08</v>
       </c>
       <c r="M46" t="n">
-        <v>68322.85000000001</v>
+        <v>66176.19</v>
       </c>
       <c r="N46" t="n">
-        <v>68799.78999999999</v>
+        <v>66697.28999999999</v>
       </c>
       <c r="O46" t="n">
-        <v>70817.45</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
+        <v>68533.03999999999</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4382,74 +4387,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65732.78999999999</v>
+        <v>65427.69</v>
       </c>
       <c r="C47" t="n">
-        <v>66325.32000000001</v>
+        <v>66125.88</v>
       </c>
       <c r="D47" t="n">
-        <v>65652.25</v>
+        <v>65260.22</v>
       </c>
       <c r="E47" t="n">
-        <v>66216.78999999999</v>
+        <v>66016.36</v>
       </c>
       <c r="F47" t="n">
-        <v>890.37</v>
+        <v>-200.43</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.003</v>
       </c>
       <c r="H47" t="n">
-        <v>673.0700000000001</v>
+        <v>865.66</v>
       </c>
       <c r="I47" t="n">
-        <v>63434.45</v>
+        <v>64979.18</v>
       </c>
       <c r="J47" t="n">
-        <v>63298.23</v>
+        <v>65657.72</v>
       </c>
       <c r="K47" t="n">
-        <v>64476.66</v>
+        <v>65880.25</v>
       </c>
       <c r="L47" t="n">
-        <v>65655.08</v>
+        <v>66102.78999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>66176.19</v>
+        <v>66553.32000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>66697.28999999999</v>
+        <v>67003.86</v>
       </c>
       <c r="O47" t="n">
-        <v>68533.03999999999</v>
+        <v>66998.39</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4462,76 +4473,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65427.69</v>
+        <v>65978.95</v>
       </c>
       <c r="C48" t="n">
-        <v>66125.88</v>
+        <v>66257.73</v>
       </c>
       <c r="D48" t="n">
-        <v>65260.22</v>
+        <v>65470.95</v>
       </c>
       <c r="E48" t="n">
-        <v>66016.36</v>
+        <v>65528.09</v>
       </c>
       <c r="F48" t="n">
-        <v>-200.43</v>
+        <v>-488.27</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0074</v>
       </c>
       <c r="H48" t="n">
-        <v>865.66</v>
+        <v>786.78</v>
       </c>
       <c r="I48" t="n">
-        <v>64979.18</v>
+        <v>64394.55</v>
       </c>
       <c r="J48" t="n">
-        <v>65657.72</v>
+        <v>65312.35</v>
       </c>
       <c r="K48" t="n">
-        <v>65880.25</v>
+        <v>65583.53</v>
       </c>
       <c r="L48" t="n">
-        <v>66102.78999999999</v>
+        <v>65854.71000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>66553.32000000001</v>
+        <v>66449.19</v>
       </c>
       <c r="N48" t="n">
-        <v>67003.86</v>
+        <v>67043.67999999999</v>
       </c>
       <c r="O48" t="n">
-        <v>66998.39</v>
+        <v>66991.55</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q48" s="6" t="n">
+        <v/>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4548,75 +4553,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65978.95</v>
+        <v>65195.26</v>
       </c>
       <c r="C49" t="n">
-        <v>66257.73</v>
+        <v>65904.24000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>65470.95</v>
+        <v>64609.47</v>
       </c>
       <c r="E49" t="n">
-        <v>65528.09</v>
+        <v>65856.42999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>-488.27</v>
+        <v>328.34</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.005</v>
       </c>
       <c r="H49" t="n">
-        <v>786.78</v>
+        <v>1294.77</v>
       </c>
       <c r="I49" t="n">
-        <v>64394.55</v>
+        <v>64684.17</v>
       </c>
       <c r="J49" t="n">
-        <v>65312.35</v>
+        <v>64573.19</v>
       </c>
       <c r="K49" t="n">
-        <v>65583.53</v>
+        <v>65134.7</v>
       </c>
       <c r="L49" t="n">
-        <v>65854.71000000001</v>
+        <v>65696.21000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>66449.19</v>
+        <v>65921.48</v>
       </c>
       <c r="N49" t="n">
-        <v>67043.67999999999</v>
+        <v>66146.74000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>66991.55</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
+        <v>67044.5</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
@@ -4630,70 +4643,66 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65195.26</v>
+        <v>65604.49000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>65904.24000000001</v>
+        <v>66442.34</v>
       </c>
       <c r="D50" t="n">
-        <v>64609.47</v>
+        <v>65390.55</v>
       </c>
       <c r="E50" t="n">
-        <v>65856.42999999999</v>
+        <v>66262.16</v>
       </c>
       <c r="F50" t="n">
-        <v>328.34</v>
+        <v>405.73</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0062</v>
       </c>
       <c r="H50" t="n">
-        <v>1294.77</v>
+        <v>1051.79</v>
       </c>
       <c r="I50" t="n">
-        <v>64684.17</v>
+        <v>63314.7</v>
       </c>
       <c r="J50" t="n">
-        <v>64573.19</v>
+        <v>64861.44</v>
       </c>
       <c r="K50" t="n">
-        <v>65134.7</v>
+        <v>65209.04</v>
       </c>
       <c r="L50" t="n">
-        <v>65696.21000000001</v>
+        <v>65556.64</v>
       </c>
       <c r="M50" t="n">
-        <v>65921.48</v>
+        <v>66503.82000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>66146.74000000001</v>
+        <v>67450.99000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>67044.5</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67199.02</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
       </c>
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
@@ -4718,57 +4727,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65604.49000000001</v>
+        <v>66775.78</v>
       </c>
       <c r="C51" t="n">
-        <v>66442.34</v>
+        <v>66954.69</v>
       </c>
       <c r="D51" t="n">
-        <v>65390.55</v>
+        <v>65782.59</v>
       </c>
       <c r="E51" t="n">
-        <v>66262.16</v>
+        <v>66131.98</v>
       </c>
       <c r="F51" t="n">
-        <v>405.73</v>
+        <v>-130.18</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.002</v>
       </c>
       <c r="H51" t="n">
-        <v>1051.79</v>
+        <v>1172.09</v>
       </c>
       <c r="I51" t="n">
-        <v>63314.7</v>
+        <v>64338.76</v>
       </c>
       <c r="J51" t="n">
-        <v>64861.44</v>
+        <v>65383.22</v>
       </c>
       <c r="K51" t="n">
-        <v>65209.04</v>
+        <v>65736.25999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>65556.64</v>
+        <v>66089.3</v>
       </c>
       <c r="M51" t="n">
-        <v>66503.82000000001</v>
+        <v>66788.05</v>
       </c>
       <c r="N51" t="n">
-        <v>67450.99000000001</v>
+        <v>67486.8</v>
       </c>
       <c r="O51" t="n">
-        <v>67199.02</v>
+        <v>67494.14</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4781,12 +4790,12 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U51" s="8" t="n">
@@ -4802,57 +4811,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>66775.78</v>
+        <v>66104.49000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>66954.69</v>
+        <v>66842.82000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>65782.59</v>
+        <v>66012.2</v>
       </c>
       <c r="E52" t="n">
-        <v>66131.98</v>
+        <v>66405.56</v>
       </c>
       <c r="F52" t="n">
-        <v>-130.18</v>
+        <v>273.59</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0041</v>
       </c>
       <c r="H52" t="n">
-        <v>1172.09</v>
+        <v>830.62</v>
       </c>
       <c r="I52" t="n">
-        <v>64338.76</v>
+        <v>64610.5</v>
       </c>
       <c r="J52" t="n">
-        <v>65383.22</v>
+        <v>64841.55</v>
       </c>
       <c r="K52" t="n">
-        <v>65736.25999999999</v>
+        <v>65545.92999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>66089.3</v>
+        <v>66250.31</v>
       </c>
       <c r="M52" t="n">
-        <v>66788.05</v>
+        <v>66718.02</v>
       </c>
       <c r="N52" t="n">
-        <v>67486.8</v>
+        <v>67185.74000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>67494.14</v>
+        <v>68126.78</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4893,69 +4902,73 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>66104.49000000001</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C53" t="n">
-        <v>66842.82000000001</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>66012.2</v>
+        <v>64832.1</v>
       </c>
       <c r="E53" t="n">
-        <v>66405.56</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>273.59</v>
+        <v>-93.63</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0014</v>
       </c>
       <c r="H53" t="n">
-        <v>830.62</v>
+        <v>1479.83</v>
       </c>
       <c r="I53" t="n">
-        <v>64610.5</v>
+        <v>65181.59</v>
       </c>
       <c r="J53" t="n">
-        <v>64841.55</v>
+        <v>65563.97</v>
       </c>
       <c r="K53" t="n">
-        <v>65545.92999999999</v>
+        <v>65990.25</v>
       </c>
       <c r="L53" t="n">
-        <v>66250.31</v>
+        <v>66416.53999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>66718.02</v>
+        <v>66820.87</v>
       </c>
       <c r="N53" t="n">
-        <v>67185.74000000001</v>
+        <v>67225.21000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>68126.78</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67673.44</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4968,78 +4981,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>65668.50999999999</v>
+        <v>65885.47</v>
       </c>
       <c r="C54" t="n">
-        <v>66311.92999999999</v>
+        <v>66525.7</v>
       </c>
       <c r="D54" t="n">
-        <v>64832.1</v>
+        <v>65576.61</v>
       </c>
       <c r="E54" t="n">
-        <v>66311.92999999999</v>
+        <v>66215.34</v>
       </c>
       <c r="F54" t="n">
-        <v>-93.63</v>
+        <v>-96.59</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0015</v>
       </c>
       <c r="H54" t="n">
-        <v>1479.83</v>
+        <v>949.09</v>
       </c>
       <c r="I54" t="n">
-        <v>65181.59</v>
+        <v>63352.27</v>
       </c>
       <c r="J54" t="n">
-        <v>65563.97</v>
+        <v>65202.06</v>
       </c>
       <c r="K54" t="n">
-        <v>65990.25</v>
+        <v>65572.02</v>
       </c>
       <c r="L54" t="n">
-        <v>66416.53999999999</v>
+        <v>65941.97</v>
       </c>
       <c r="M54" t="n">
-        <v>66820.87</v>
+        <v>67051.84</v>
       </c>
       <c r="N54" t="n">
-        <v>67225.21000000001</v>
+        <v>68161.71000000001</v>
       </c>
       <c r="O54" t="n">
-        <v>67673.44</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>67791.75999999999</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5056,68 +5059,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>65885.47</v>
+        <v>65195.43</v>
       </c>
       <c r="C55" t="n">
-        <v>66525.7</v>
+        <v>65195.43</v>
       </c>
       <c r="D55" t="n">
-        <v>65576.61</v>
+        <v>64215.47</v>
       </c>
       <c r="E55" t="n">
-        <v>66215.34</v>
+        <v>64325.64</v>
       </c>
       <c r="F55" t="n">
-        <v>-96.59</v>
+        <v>-1889.7</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0285</v>
       </c>
       <c r="H55" t="n">
-        <v>949.09</v>
+        <v>979.96</v>
       </c>
       <c r="I55" t="n">
-        <v>63352.27</v>
+        <v>64627.52</v>
       </c>
       <c r="J55" t="n">
-        <v>65202.06</v>
+        <v>65348.34</v>
       </c>
       <c r="K55" t="n">
-        <v>65572.02</v>
+        <v>65740.8</v>
       </c>
       <c r="L55" t="n">
-        <v>65941.97</v>
+        <v>66133.25</v>
       </c>
       <c r="M55" t="n">
-        <v>67051.84</v>
+        <v>66689.89</v>
       </c>
       <c r="N55" t="n">
-        <v>68161.71000000001</v>
+        <v>67246.53</v>
       </c>
       <c r="O55" t="n">
-        <v>67791.75999999999</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>67474.8</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5134,69 +5147,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="C56" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="D56" t="n">
-        <v>64215.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E56" t="n">
-        <v>64325.64</v>
+        <v>64214.48</v>
       </c>
       <c r="F56" t="n">
-        <v>-1889.7</v>
+        <v>-111.16</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0017</v>
       </c>
       <c r="H56" t="n">
-        <v>979.96</v>
+        <v>952.01</v>
       </c>
       <c r="I56" t="n">
-        <v>64627.52</v>
+        <v>63235.51</v>
       </c>
       <c r="J56" t="n">
-        <v>65348.34</v>
+        <v>63155.78</v>
       </c>
       <c r="K56" t="n">
-        <v>65740.8</v>
+        <v>63835.66</v>
       </c>
       <c r="L56" t="n">
-        <v>66133.25</v>
+        <v>64515.54</v>
       </c>
       <c r="M56" t="n">
-        <v>66689.89</v>
+        <v>64815.62</v>
       </c>
       <c r="N56" t="n">
-        <v>67246.53</v>
+        <v>65115.7</v>
       </c>
       <c r="O56" t="n">
-        <v>67474.8</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66175.39</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
@@ -5205,7 +5210,7 @@
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5227,50 +5232,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>64724.81</v>
+        <v>64498.94</v>
       </c>
       <c r="C57" t="n">
-        <v>64724.81</v>
+        <v>65182.45</v>
       </c>
       <c r="D57" t="n">
-        <v>63772.8</v>
+        <v>64228.47</v>
       </c>
       <c r="E57" t="n">
-        <v>64214.48</v>
+        <v>65020.94</v>
       </c>
       <c r="F57" t="n">
-        <v>-111.16</v>
+        <v>806.46</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="H57" t="n">
-        <v>952.01</v>
+        <v>953.98</v>
       </c>
       <c r="I57" t="n">
-        <v>63235.51</v>
+        <v>62820.79</v>
       </c>
       <c r="J57" t="n">
-        <v>63155.78</v>
+        <v>63245.31</v>
       </c>
       <c r="K57" t="n">
-        <v>63835.66</v>
+        <v>63738.48</v>
       </c>
       <c r="L57" t="n">
-        <v>64515.54</v>
+        <v>64231.64</v>
       </c>
       <c r="M57" t="n">
-        <v>64815.62</v>
+        <v>64690.48</v>
       </c>
       <c r="N57" t="n">
-        <v>65115.7</v>
+        <v>65149.33</v>
       </c>
       <c r="O57" t="n">
-        <v>66175.39</v>
+        <v>65676.82000000001</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5278,21 +5283,23 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5302,55 +5309,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>64498.94</v>
+        <v>65600.42</v>
       </c>
       <c r="C58" t="n">
-        <v>65182.45</v>
+        <v>66668.71000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>64228.47</v>
+        <v>65600.42</v>
       </c>
       <c r="E58" t="n">
-        <v>65020.94</v>
+        <v>66399.84</v>
       </c>
       <c r="F58" t="n">
-        <v>806.46</v>
+        <v>1378.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="H58" t="n">
-        <v>953.98</v>
+        <v>1068.29</v>
       </c>
       <c r="I58" t="n">
-        <v>62820.79</v>
+        <v>63274.49</v>
       </c>
       <c r="J58" t="n">
-        <v>63245.31</v>
+        <v>64224.7</v>
       </c>
       <c r="K58" t="n">
-        <v>63738.48</v>
+        <v>64543.95</v>
       </c>
       <c r="L58" t="n">
-        <v>64231.64</v>
+        <v>64863.2</v>
       </c>
       <c r="M58" t="n">
-        <v>64690.48</v>
+        <v>65497.93</v>
       </c>
       <c r="N58" t="n">
-        <v>65149.33</v>
+        <v>66132.66</v>
       </c>
       <c r="O58" t="n">
-        <v>65676.82000000001</v>
+        <v>66136.42999999999</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5373,171 +5384,167 @@
       </c>
       <c r="U58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>65600.42</v>
+        <v>65843.69</v>
       </c>
       <c r="C59" t="n">
-        <v>66668.71000000001</v>
+        <v>66791.84</v>
       </c>
       <c r="D59" t="n">
-        <v>65600.42</v>
+        <v>65269.33</v>
       </c>
       <c r="E59" t="n">
-        <v>66399.84</v>
+        <v>65269.33</v>
       </c>
       <c r="F59" t="n">
-        <v>1378.9</v>
+        <v>-1130.52</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.017</v>
       </c>
       <c r="H59" t="n">
-        <v>1068.29</v>
+        <v>1522.52</v>
       </c>
       <c r="I59" t="n">
-        <v>63274.49</v>
+        <v>64532.13</v>
       </c>
       <c r="J59" t="n">
-        <v>64224.7</v>
+        <v>65464.19</v>
       </c>
       <c r="K59" t="n">
-        <v>64543.95</v>
+        <v>65865.7</v>
       </c>
       <c r="L59" t="n">
-        <v>64863.2</v>
+        <v>66267.21000000001</v>
       </c>
       <c r="M59" t="n">
-        <v>65497.93</v>
+        <v>66933.99000000001</v>
       </c>
       <c r="N59" t="n">
-        <v>66132.66</v>
+        <v>67600.77</v>
       </c>
       <c r="O59" t="n">
-        <v>66136.42999999999</v>
+        <v>67737</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
+      <c r="Q59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W59" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W59" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>65843.69</v>
+        <v>65087.22</v>
       </c>
       <c r="C60" t="n">
-        <v>66791.84</v>
+        <v>65794.03</v>
       </c>
       <c r="D60" t="n">
-        <v>65269.33</v>
+        <v>65017.68</v>
       </c>
       <c r="E60" t="n">
-        <v>65269.33</v>
+        <v>65142.78</v>
       </c>
       <c r="F60" t="n">
-        <v>-1130.52</v>
+        <v>-126.55</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0019</v>
       </c>
       <c r="H60" t="n">
-        <v>1522.52</v>
+        <v>776.35</v>
       </c>
       <c r="I60" t="n">
-        <v>64532.13</v>
+        <v>63746.81</v>
       </c>
       <c r="J60" t="n">
-        <v>65464.19</v>
+        <v>63366.18</v>
       </c>
       <c r="K60" t="n">
-        <v>65865.7</v>
+        <v>64508.07</v>
       </c>
       <c r="L60" t="n">
-        <v>66267.21000000001</v>
+        <v>65649.96000000001</v>
       </c>
       <c r="M60" t="n">
-        <v>66933.99000000001</v>
+        <v>66030.59</v>
       </c>
       <c r="N60" t="n">
-        <v>67600.77</v>
+        <v>66411.21000000001</v>
       </c>
       <c r="O60" t="n">
-        <v>67737</v>
+        <v>68314.36</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5554,68 +5561,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>65087.22</v>
+        <v>64768.53</v>
       </c>
       <c r="C61" t="n">
-        <v>65794.03</v>
+        <v>65270.95</v>
       </c>
       <c r="D61" t="n">
-        <v>65017.68</v>
+        <v>64186.68</v>
       </c>
       <c r="E61" t="n">
-        <v>65142.78</v>
+        <v>65270.95</v>
       </c>
       <c r="F61" t="n">
-        <v>-126.55</v>
+        <v>128.17</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="H61" t="n">
-        <v>776.35</v>
+        <v>1084.27</v>
       </c>
       <c r="I61" t="n">
-        <v>63746.81</v>
+        <v>64241.33</v>
       </c>
       <c r="J61" t="n">
-        <v>63366.18</v>
+        <v>64234.89</v>
       </c>
       <c r="K61" t="n">
-        <v>64508.07</v>
+        <v>64754.61</v>
       </c>
       <c r="L61" t="n">
-        <v>65649.96000000001</v>
+        <v>65274.32</v>
       </c>
       <c r="M61" t="n">
-        <v>66030.59</v>
+        <v>65530.96</v>
       </c>
       <c r="N61" t="n">
-        <v>66411.21000000001</v>
+        <v>65787.60000000001</v>
       </c>
       <c r="O61" t="n">
-        <v>68314.36</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+        <v>66570.38</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
@@ -5636,64 +5645,66 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>64768.53</v>
+        <v>64276.82</v>
       </c>
       <c r="C62" t="n">
-        <v>65270.95</v>
+        <v>64312.02</v>
       </c>
       <c r="D62" t="n">
-        <v>64186.68</v>
+        <v>63208.63</v>
       </c>
       <c r="E62" t="n">
-        <v>65270.95</v>
+        <v>64011.34</v>
       </c>
       <c r="F62" t="n">
-        <v>128.17</v>
+        <v>-1259.61</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H62" t="n">
-        <v>1084.27</v>
+        <v>1103.39</v>
       </c>
       <c r="I62" t="n">
-        <v>64241.33</v>
+        <v>63102.41</v>
       </c>
       <c r="J62" t="n">
-        <v>64234.89</v>
+        <v>64457.75</v>
       </c>
       <c r="K62" t="n">
-        <v>64754.61</v>
+        <v>64728.81</v>
       </c>
       <c r="L62" t="n">
-        <v>65274.32</v>
+        <v>64999.88</v>
       </c>
       <c r="M62" t="n">
-        <v>65530.96</v>
+        <v>65813.08</v>
       </c>
       <c r="N62" t="n">
-        <v>65787.60000000001</v>
+        <v>66626.28999999999</v>
       </c>
       <c r="O62" t="n">
-        <v>66570.38</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66355.22</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
@@ -5703,7 +5714,7 @@
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5720,66 +5731,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>64276.82</v>
+        <v>63659.53</v>
       </c>
       <c r="C63" t="n">
-        <v>64312.02</v>
+        <v>63691.53</v>
       </c>
       <c r="D63" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E63" t="n">
-        <v>64011.34</v>
+        <v/>
       </c>
       <c r="F63" t="n">
-        <v>-1259.61</v>
+        <v/>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0193</v>
+        <v/>
       </c>
       <c r="H63" t="n">
-        <v>1103.39</v>
+        <v>965.35</v>
       </c>
       <c r="I63" t="n">
-        <v>63102.41</v>
+        <v>62105.24</v>
       </c>
       <c r="J63" t="n">
-        <v>64457.75</v>
+        <v>63033.46</v>
       </c>
       <c r="K63" t="n">
-        <v>64728.81</v>
+        <v>63459.64</v>
       </c>
       <c r="L63" t="n">
-        <v>64999.88</v>
+        <v>63885.83</v>
       </c>
       <c r="M63" t="n">
-        <v>65813.08</v>
+        <v>64563.04</v>
       </c>
       <c r="N63" t="n">
-        <v>66626.28999999999</v>
+        <v>65240.24</v>
       </c>
       <c r="O63" t="n">
-        <v>66355.22</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
+        <v>65415.41</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
@@ -5787,9 +5796,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S63" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5809,31 +5818,31 @@
       <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="13" t="n">
-        <v>62105.24</v>
-      </c>
-      <c r="J64" s="13" t="n">
-        <v>63033.46</v>
-      </c>
-      <c r="K64" s="13" t="n">
-        <v>63459.64</v>
-      </c>
-      <c r="L64" s="13" t="n">
-        <v>63885.83</v>
-      </c>
-      <c r="M64" s="13" t="n">
-        <v>64563.04</v>
-      </c>
-      <c r="N64" s="13" t="n">
-        <v>65240.24</v>
-      </c>
-      <c r="O64" s="13" t="n">
-        <v>65415.41</v>
+      <c r="I64" s="14" t="n">
+        <v>61760.83</v>
+      </c>
+      <c r="J64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O64" s="14" t="n">
+        <v>64656.88</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -490,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69005.88</v>
+        <v>70163.71000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>70125.75</v>
+        <v>71398.58</v>
       </c>
       <c r="D2" t="n">
-        <v>68985.63</v>
+        <v>70092.94</v>
       </c>
       <c r="E2" t="n">
-        <v>69902.25</v>
+        <v>71053.49000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>497.75</v>
+        <v>1151.24</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0072</v>
+        <v>0.0165</v>
       </c>
       <c r="H2" t="n">
-        <v>1140.12</v>
+        <v>1305.64</v>
       </c>
       <c r="I2" t="n">
-        <v>68170.66</v>
+        <v>67845.52</v>
       </c>
       <c r="J2" t="n">
-        <v>68402.64999999999</v>
+        <v>68935.41</v>
       </c>
       <c r="K2" t="n">
-        <v>68942</v>
+        <v>69332.19</v>
       </c>
       <c r="L2" t="n">
-        <v>69481.34</v>
+        <v>69728.97</v>
       </c>
       <c r="M2" t="n">
-        <v>69867</v>
+        <v>70472.31</v>
       </c>
       <c r="N2" t="n">
-        <v>70252.67</v>
+        <v>71215.64999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>70945.69</v>
+        <v>71265.87</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -705,73 +702,73 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70163.71000000001</v>
+        <v>71551.03</v>
       </c>
       <c r="C3" t="n">
-        <v>71398.58</v>
+        <v>71952.99000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>70092.94</v>
+        <v>70517.98</v>
       </c>
       <c r="E3" t="n">
-        <v>71053.49000000001</v>
+        <v>71250.06</v>
       </c>
       <c r="F3" t="n">
-        <v>1151.24</v>
+        <v>196.57</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0028</v>
       </c>
       <c r="H3" t="n">
-        <v>1305.64</v>
+        <v>1435.02</v>
       </c>
       <c r="I3" t="n">
-        <v>67845.52</v>
+        <v>68787.3</v>
       </c>
       <c r="J3" t="n">
-        <v>68935.41</v>
+        <v>69901.72</v>
       </c>
       <c r="K3" t="n">
-        <v>69332.19</v>
+        <v>70400.67</v>
       </c>
       <c r="L3" t="n">
-        <v>69728.97</v>
+        <v>70899.62</v>
       </c>
       <c r="M3" t="n">
-        <v>70472.31</v>
+        <v>71706.31</v>
       </c>
       <c r="N3" t="n">
-        <v>71215.64999999999</v>
+        <v>72513</v>
       </c>
       <c r="O3" t="n">
-        <v>71265.87</v>
+        <v>72704.22</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -784,7 +781,7 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
@@ -792,15 +789,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -812,50 +805,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71551.03</v>
+        <v>71067.14999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>71952.99000000001</v>
+        <v>72831.73</v>
       </c>
       <c r="D4" t="n">
-        <v>70517.98</v>
+        <v>71009.52</v>
       </c>
       <c r="E4" t="n">
-        <v>71250.06</v>
+        <v>72353.96000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>196.57</v>
+        <v>1103.9</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0155</v>
       </c>
       <c r="H4" t="n">
-        <v>1435.02</v>
+        <v>1822.2</v>
       </c>
       <c r="I4" t="n">
-        <v>68787.3</v>
+        <v>69082.96000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>69901.72</v>
+        <v>69822.34</v>
       </c>
       <c r="K4" t="n">
-        <v>70400.67</v>
+        <v>70532.55</v>
       </c>
       <c r="L4" t="n">
-        <v>70899.62</v>
+        <v>71242.77</v>
       </c>
       <c r="M4" t="n">
-        <v>71706.31</v>
+        <v>71967.57000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>72513</v>
+        <v>72692.37</v>
       </c>
       <c r="O4" t="n">
-        <v>72704.22</v>
+        <v>73388.00999999999</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -868,7 +861,7 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
@@ -876,8 +869,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="n">
-        <v/>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -892,81 +887,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71067.14999999999</v>
+        <v>72404.37</v>
       </c>
       <c r="C5" t="n">
-        <v>72831.73</v>
+        <v>72618.44</v>
       </c>
       <c r="D5" t="n">
-        <v>71009.52</v>
+        <v>69788.38</v>
       </c>
       <c r="E5" t="n">
-        <v>72353.96000000001</v>
+        <v>69788.38</v>
       </c>
       <c r="F5" t="n">
-        <v>1103.9</v>
+        <v>-2565.58</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0155</v>
+        <v>-0.0355</v>
       </c>
       <c r="H5" t="n">
-        <v>1822.2</v>
+        <v>2830.05</v>
       </c>
       <c r="I5" t="n">
-        <v>69082.96000000001</v>
+        <v>69187.32000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>69822.34</v>
+        <v>70748.42999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>70532.55</v>
+        <v>71442.86</v>
       </c>
       <c r="L5" t="n">
-        <v>71242.77</v>
+        <v>72137.28999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>71967.57000000001</v>
+        <v>73265.06</v>
       </c>
       <c r="N5" t="n">
-        <v>72692.37</v>
+        <v>74392.83</v>
       </c>
       <c r="O5" t="n">
-        <v>73388.00999999999</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
+        <v>74653.92999999999</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -974,64 +971,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72404.37</v>
+        <v>69615.08</v>
       </c>
       <c r="C6" t="n">
-        <v>72618.44</v>
+        <v>70218.71000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>69788.38</v>
+        <v>68461.10000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>69788.38</v>
+        <v>69174.97</v>
       </c>
       <c r="F6" t="n">
-        <v>-2565.58</v>
+        <v>-613.41</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0355</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>2830.05</v>
+        <v>1757.61</v>
       </c>
       <c r="I6" t="n">
-        <v>69187.32000000001</v>
+        <v>66958.33</v>
       </c>
       <c r="J6" t="n">
-        <v>70748.42999999999</v>
+        <v>66250.81</v>
       </c>
       <c r="K6" t="n">
-        <v>71442.86</v>
+        <v>68373.36</v>
       </c>
       <c r="L6" t="n">
-        <v>72137.28999999999</v>
+        <v>70495.89999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>73265.06</v>
+        <v>71203.41</v>
       </c>
       <c r="N6" t="n">
-        <v>74392.83</v>
+        <v>71910.92</v>
       </c>
       <c r="O6" t="n">
-        <v>74653.92999999999</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+        <v>75448.49000000001</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
@@ -1058,50 +1051,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69615.08</v>
+        <v>70114.09</v>
       </c>
       <c r="C7" t="n">
-        <v>70218.71000000001</v>
+        <v>72594.22</v>
       </c>
       <c r="D7" t="n">
-        <v>68461.10000000001</v>
+        <v>69982.67</v>
       </c>
       <c r="E7" t="n">
-        <v>69174.97</v>
+        <v>72366.34</v>
       </c>
       <c r="F7" t="n">
-        <v>-613.41</v>
+        <v>3191.38</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0461</v>
       </c>
       <c r="H7" t="n">
-        <v>1757.61</v>
+        <v>2611.55</v>
       </c>
       <c r="I7" t="n">
-        <v>66958.33</v>
+        <v>66703.49000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>66250.81</v>
+        <v>67334.89</v>
       </c>
       <c r="K7" t="n">
-        <v>68373.36</v>
+        <v>68296.16</v>
       </c>
       <c r="L7" t="n">
-        <v>70495.89999999999</v>
+        <v>69257.44</v>
       </c>
       <c r="M7" t="n">
-        <v>71203.41</v>
+        <v>70053.77</v>
       </c>
       <c r="N7" t="n">
-        <v>71910.92</v>
+        <v>70850.11</v>
       </c>
       <c r="O7" t="n">
-        <v>75448.49000000001</v>
+        <v>71976.32000000001</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1109,28 +1102,32 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W7" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W7" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1138,83 +1135,81 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70114.09</v>
+        <v>71587.71000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>72594.22</v>
+        <v>71786.28</v>
       </c>
       <c r="D8" t="n">
-        <v>69982.67</v>
+        <v>68639.84</v>
       </c>
       <c r="E8" t="n">
-        <v>72366.34</v>
+        <v>69360.88</v>
       </c>
       <c r="F8" t="n">
-        <v>3191.38</v>
+        <v>-3005.46</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0461</v>
+        <v>-0.0415</v>
       </c>
       <c r="H8" t="n">
-        <v>2611.55</v>
+        <v>3146.44</v>
       </c>
       <c r="I8" t="n">
-        <v>66703.49000000001</v>
+        <v>67371.12</v>
       </c>
       <c r="J8" t="n">
-        <v>67334.89</v>
+        <v>70293.75</v>
       </c>
       <c r="K8" t="n">
-        <v>68296.16</v>
+        <v>71060.57000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>69257.44</v>
+        <v>71827.39</v>
       </c>
       <c r="M8" t="n">
-        <v>70053.77</v>
+        <v>73672.12</v>
       </c>
       <c r="N8" t="n">
-        <v>70850.11</v>
+        <v>75516.84</v>
       </c>
       <c r="O8" t="n">
-        <v>71976.32000000001</v>
+        <v>75205.77</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1222,67 +1217,63 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71587.71000000001</v>
+        <v>69609.88</v>
       </c>
       <c r="C9" t="n">
-        <v>71786.28</v>
+        <v>69609.88</v>
       </c>
       <c r="D9" t="n">
-        <v>68639.84</v>
+        <v>67997.57000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>69360.88</v>
+        <v>69468.11</v>
       </c>
       <c r="F9" t="n">
-        <v>-3005.46</v>
+        <v>107.23</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0415</v>
+        <v>0.0015</v>
       </c>
       <c r="H9" t="n">
-        <v>3146.44</v>
+        <v>1612.31</v>
       </c>
       <c r="I9" t="n">
-        <v>67371.12</v>
+        <v>65493.41</v>
       </c>
       <c r="J9" t="n">
-        <v>70293.75</v>
+        <v>65788.36</v>
       </c>
       <c r="K9" t="n">
-        <v>71060.57000000001</v>
+        <v>67787.66</v>
       </c>
       <c r="L9" t="n">
-        <v>71827.39</v>
+        <v>69786.97</v>
       </c>
       <c r="M9" t="n">
-        <v>73672.12</v>
+        <v>70934.10000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>75516.84</v>
+        <v>72081.23</v>
       </c>
       <c r="O9" t="n">
-        <v>75205.77</v>
+        <v>74932.72</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1299,55 +1290,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69609.88</v>
+        <v>70085.60000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>69609.88</v>
+        <v>70667</v>
       </c>
       <c r="D10" t="n">
-        <v>67997.57000000001</v>
+        <v>69302.19</v>
       </c>
       <c r="E10" t="n">
-        <v>69468.11</v>
+        <v>70062.32000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>107.23</v>
+        <v>594.21</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0086</v>
       </c>
       <c r="H10" t="n">
-        <v>1612.31</v>
+        <v>1364.81</v>
       </c>
       <c r="I10" t="n">
-        <v>65493.41</v>
+        <v>66385.25999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>65788.36</v>
+        <v>68187.99000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>67787.66</v>
+        <v>68661.95</v>
       </c>
       <c r="L10" t="n">
-        <v>69786.97</v>
+        <v>69135.92</v>
       </c>
       <c r="M10" t="n">
-        <v>70934.10000000001</v>
+        <v>70274.27</v>
       </c>
       <c r="N10" t="n">
-        <v>72081.23</v>
+        <v>71412.61</v>
       </c>
       <c r="O10" t="n">
-        <v>74932.72</v>
+        <v>71222.2</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1358,13 +1353,15 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1379,57 +1376,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70085.60000000001</v>
+        <v>70774.28</v>
       </c>
       <c r="C11" t="n">
-        <v>70667</v>
+        <v>71962.34</v>
       </c>
       <c r="D11" t="n">
-        <v>69302.19</v>
+        <v>70126.14</v>
       </c>
       <c r="E11" t="n">
-        <v>70062.32000000001</v>
+        <v>70474.96000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>594.21</v>
+        <v>412.64</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0059</v>
       </c>
       <c r="H11" t="n">
-        <v>1364.81</v>
+        <v>1836.2</v>
       </c>
       <c r="I11" t="n">
-        <v>66385.25999999999</v>
+        <v>67937.38</v>
       </c>
       <c r="J11" t="n">
-        <v>68187.99000000001</v>
+        <v>68736.37</v>
       </c>
       <c r="K11" t="n">
-        <v>68661.95</v>
+        <v>69379.91</v>
       </c>
       <c r="L11" t="n">
-        <v>69135.92</v>
+        <v>70023.46000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>70274.27</v>
+        <v>70744.73</v>
       </c>
       <c r="N11" t="n">
-        <v>71412.61</v>
+        <v>71466</v>
       </c>
       <c r="O11" t="n">
-        <v>71222.2</v>
+        <v>72031.81</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1450,8 +1447,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1470,74 +1469,74 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>70774.28</v>
+        <v>70039.89</v>
       </c>
       <c r="C12" t="n">
-        <v>71962.34</v>
+        <v>70081.39</v>
       </c>
       <c r="D12" t="n">
-        <v>70126.14</v>
+        <v>68676.25999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>70474.96000000001</v>
+        <v>68733.14999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>412.64</v>
+        <v>-1741.81</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0247</v>
       </c>
       <c r="H12" t="n">
-        <v>1836.2</v>
+        <v>1405.13</v>
       </c>
       <c r="I12" t="n">
-        <v>67937.38</v>
+        <v>68289.94</v>
       </c>
       <c r="J12" t="n">
-        <v>68736.37</v>
+        <v>68354.12</v>
       </c>
       <c r="K12" t="n">
-        <v>69379.91</v>
+        <v>69556.86</v>
       </c>
       <c r="L12" t="n">
-        <v>70023.46000000001</v>
+        <v>70759.60000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>70744.73</v>
+        <v>71393.06</v>
       </c>
       <c r="N12" t="n">
-        <v>71466</v>
+        <v>72026.52</v>
       </c>
       <c r="O12" t="n">
-        <v>72031.81</v>
+        <v>73798.55</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1547,84 +1546,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>70039.89</v>
+        <v>68676.06</v>
       </c>
       <c r="C13" t="n">
-        <v>70081.39</v>
+        <v>69788.03</v>
       </c>
       <c r="D13" t="n">
-        <v>68676.25999999999</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>68733.14999999999</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-1741.81</v>
+        <v>1010.92</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0147</v>
       </c>
       <c r="H13" t="n">
-        <v>1405.13</v>
+        <v>2178.54</v>
       </c>
       <c r="I13" t="n">
-        <v>68289.94</v>
+        <v>67271.12</v>
       </c>
       <c r="J13" t="n">
-        <v>68354.12</v>
+        <v>67005.17999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>69556.86</v>
+        <v>68030.58</v>
       </c>
       <c r="L13" t="n">
-        <v>70759.60000000001</v>
+        <v>69055.99000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>71393.06</v>
+        <v>69435.71000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>72026.52</v>
+        <v>69815.44</v>
       </c>
       <c r="O13" t="n">
-        <v>73798.55</v>
+        <v>71486.52</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1633,55 +1630,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>68676.06</v>
+        <v>69973.34</v>
       </c>
       <c r="C14" t="n">
-        <v>69788.03</v>
+        <v>70384.59</v>
       </c>
       <c r="D14" t="n">
-        <v>67609.49000000001</v>
+        <v>68904.41</v>
       </c>
       <c r="E14" t="n">
-        <v>69744.07000000001</v>
+        <v>69737.69</v>
       </c>
       <c r="F14" t="n">
-        <v>1010.92</v>
+        <v>-6.38</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0001</v>
       </c>
       <c r="H14" t="n">
-        <v>2178.54</v>
+        <v>1480.19</v>
       </c>
       <c r="I14" t="n">
-        <v>67271.12</v>
+        <v>65430.95</v>
       </c>
       <c r="J14" t="n">
-        <v>67005.17999999999</v>
+        <v>68088.19</v>
       </c>
       <c r="K14" t="n">
-        <v>68030.58</v>
+        <v>68654.8</v>
       </c>
       <c r="L14" t="n">
-        <v>69055.99000000001</v>
+        <v>69221.42</v>
       </c>
       <c r="M14" t="n">
-        <v>69435.71000000001</v>
+        <v>70833.34</v>
       </c>
       <c r="N14" t="n">
-        <v>69815.44</v>
+        <v>72445.25999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>71486.52</v>
+        <v>71966.57000000001</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1689,25 +1690,19 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1719,70 +1714,74 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>69973.34</v>
+        <v>69460.08</v>
       </c>
       <c r="C15" t="n">
-        <v>70384.59</v>
+        <v>69957.50999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>68904.41</v>
+        <v>68003.92</v>
       </c>
       <c r="E15" t="n">
-        <v>69737.69</v>
+        <v>68256.96000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.38</v>
+        <v>-1480.73</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0212</v>
       </c>
       <c r="H15" t="n">
-        <v>1480.19</v>
+        <v>1953.59</v>
       </c>
       <c r="I15" t="n">
-        <v>65430.95</v>
+        <v>67424.22</v>
       </c>
       <c r="J15" t="n">
-        <v>68088.19</v>
+        <v>68304.09</v>
       </c>
       <c r="K15" t="n">
-        <v>68654.8</v>
+        <v>68997.59</v>
       </c>
       <c r="L15" t="n">
-        <v>69221.42</v>
+        <v>69691.09</v>
       </c>
       <c r="M15" t="n">
-        <v>70833.34</v>
+        <v>70477.78</v>
       </c>
       <c r="N15" t="n">
-        <v>72445.25999999999</v>
+        <v>71264.47</v>
       </c>
       <c r="O15" t="n">
-        <v>71966.57000000001</v>
+        <v>71864.78</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1799,71 +1798,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>69460.08</v>
+        <v>67704.16</v>
       </c>
       <c r="C16" t="n">
-        <v>69957.50999999999</v>
+        <v>68432.67999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>68003.92</v>
+        <v>66819.05</v>
       </c>
       <c r="E16" t="n">
-        <v>68256.96000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="F16" t="n">
-        <v>-1480.73</v>
+        <v>-1437.91</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="H16" t="n">
-        <v>1953.59</v>
+        <v>1613.63</v>
       </c>
       <c r="I16" t="n">
-        <v>67424.22</v>
+        <v>66050.34</v>
       </c>
       <c r="J16" t="n">
-        <v>68304.09</v>
+        <v>65941.5</v>
       </c>
       <c r="K16" t="n">
-        <v>68997.59</v>
+        <v>67280.17</v>
       </c>
       <c r="L16" t="n">
-        <v>69691.09</v>
+        <v>68618.84</v>
       </c>
       <c r="M16" t="n">
-        <v>70477.78</v>
+        <v>69233.75</v>
       </c>
       <c r="N16" t="n">
-        <v>71264.47</v>
+        <v>69848.67</v>
       </c>
       <c r="O16" t="n">
-        <v>71864.78</v>
+        <v>71911.09</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
@@ -1890,50 +1883,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>67704.16</v>
+        <v>67046.37</v>
       </c>
       <c r="C17" t="n">
-        <v>68432.67999999999</v>
+        <v>68447.89</v>
       </c>
       <c r="D17" t="n">
-        <v>66819.05</v>
+        <v>67008.89</v>
       </c>
       <c r="E17" t="n">
-        <v>66819.05</v>
+        <v>67743.85000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-1437.91</v>
+        <v>924.8</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0211</v>
+        <v>0.0138</v>
       </c>
       <c r="H17" t="n">
-        <v>1613.63</v>
+        <v>1439</v>
       </c>
       <c r="I17" t="n">
-        <v>66050.34</v>
+        <v>65205.41</v>
       </c>
       <c r="J17" t="n">
-        <v>65941.5</v>
+        <v>64802.01</v>
       </c>
       <c r="K17" t="n">
-        <v>67280.17</v>
+        <v>66012.23</v>
       </c>
       <c r="L17" t="n">
-        <v>68618.84</v>
+        <v>67222.46000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>69233.75</v>
+        <v>67625.86</v>
       </c>
       <c r="N17" t="n">
-        <v>69848.67</v>
+        <v>68029.27</v>
       </c>
       <c r="O17" t="n">
-        <v>71911.09</v>
+        <v>70046.31</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1941,21 +1934,23 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1965,55 +1960,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>67046.37</v>
+        <v>68526.72</v>
       </c>
       <c r="C18" t="n">
-        <v>68447.89</v>
+        <v>69374.86</v>
       </c>
       <c r="D18" t="n">
-        <v>67008.89</v>
+        <v>68271.91</v>
       </c>
       <c r="E18" t="n">
-        <v>67743.85000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F18" t="n">
-        <v>924.8</v>
+        <v>813.88</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.012</v>
       </c>
       <c r="H18" t="n">
-        <v>1439</v>
+        <v>1102.95</v>
       </c>
       <c r="I18" t="n">
-        <v>65205.41</v>
+        <v>65569.89</v>
       </c>
       <c r="J18" t="n">
-        <v>64802.01</v>
+        <v>66312.58</v>
       </c>
       <c r="K18" t="n">
-        <v>66012.23</v>
+        <v>67024.35000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>67222.46000000001</v>
+        <v>67736.12</v>
       </c>
       <c r="M18" t="n">
-        <v>67625.86</v>
+        <v>68463.35000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>68029.27</v>
+        <v>69190.58</v>
       </c>
       <c r="O18" t="n">
-        <v>70046.31</v>
+        <v>69886.89</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2056,74 +2055,76 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>68526.72</v>
+        <v>68410.63</v>
       </c>
       <c r="C19" t="n">
-        <v>69374.86</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>68271.91</v>
+        <v>66653.11</v>
       </c>
       <c r="E19" t="n">
-        <v>68557.73</v>
+        <v>67242.73</v>
       </c>
       <c r="F19" t="n">
-        <v>813.88</v>
+        <v>-1315</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0192</v>
       </c>
       <c r="H19" t="n">
-        <v>1102.95</v>
+        <v>2425.1</v>
       </c>
       <c r="I19" t="n">
-        <v>65569.89</v>
+        <v>67168.95</v>
       </c>
       <c r="J19" t="n">
-        <v>66312.58</v>
+        <v>67321.95</v>
       </c>
       <c r="K19" t="n">
-        <v>67024.35000000001</v>
+        <v>68006.25</v>
       </c>
       <c r="L19" t="n">
-        <v>67736.12</v>
+        <v>68690.55</v>
       </c>
       <c r="M19" t="n">
-        <v>68463.35000000001</v>
+        <v>69109.2</v>
       </c>
       <c r="N19" t="n">
-        <v>69190.58</v>
+        <v>69527.85000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>69886.89</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+        <v>70477.81</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2133,78 +2134,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>68410.63</v>
+        <v>67002.94</v>
       </c>
       <c r="C20" t="n">
-        <v>69078.21000000001</v>
+        <v>67800.17999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>66653.11</v>
+        <v>66268.60000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>67242.73</v>
+        <v>67743.5</v>
       </c>
       <c r="F20" t="n">
-        <v>-1315</v>
+        <v>500.77</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0074</v>
       </c>
       <c r="H20" t="n">
-        <v>2425.1</v>
+        <v>1531.58</v>
       </c>
       <c r="I20" t="n">
-        <v>67168.95</v>
+        <v>64228.01</v>
       </c>
       <c r="J20" t="n">
-        <v>67321.95</v>
+        <v>64506.16</v>
       </c>
       <c r="K20" t="n">
-        <v>68006.25</v>
+        <v>66030.17999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>68690.55</v>
+        <v>67554.19</v>
       </c>
       <c r="M20" t="n">
-        <v>69109.2</v>
+        <v>68455.28</v>
       </c>
       <c r="N20" t="n">
-        <v>69527.85000000001</v>
+        <v>69356.36</v>
       </c>
       <c r="O20" t="n">
-        <v>70477.81</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>71503.31</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2221,55 +2212,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>67002.94</v>
+        <v>67989.74000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>67800.17999999999</v>
+        <v>68798.24000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>66268.60000000001</v>
+        <v>67833.17</v>
       </c>
       <c r="E21" t="n">
-        <v>67743.5</v>
+        <v>68751.50999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>500.77</v>
+        <v>1008.01</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0149</v>
       </c>
       <c r="H21" t="n">
-        <v>1531.58</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>64228.01</v>
+        <v>64737.02</v>
       </c>
       <c r="J21" t="n">
-        <v>64506.16</v>
+        <v>66566.48</v>
       </c>
       <c r="K21" t="n">
-        <v>66030.17999999999</v>
+        <v>66977.71000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>67554.19</v>
+        <v>67388.95</v>
       </c>
       <c r="M21" t="n">
-        <v>68455.28</v>
+        <v>68509.28999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>69356.36</v>
+        <v>69629.63</v>
       </c>
       <c r="O21" t="n">
-        <v>71503.31</v>
+        <v>69331.75999999999</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2282,11 +2277,13 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2301,77 +2298,81 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>67989.74000000001</v>
+        <v>67900.42999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>68798.24000000001</v>
+        <v>68069.82000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>67833.17</v>
+        <v>66499.49000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>68751.50999999999</v>
+        <v>66835.53999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>1008.01</v>
+        <v>-1915.97</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0279</v>
       </c>
       <c r="H22" t="n">
-        <v>965.0700000000001</v>
+        <v>1570.33</v>
       </c>
       <c r="I22" t="n">
-        <v>64737.02</v>
+        <v>66868.10000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>66566.48</v>
+        <v>68004.34</v>
       </c>
       <c r="K22" t="n">
-        <v>66977.71000000001</v>
+        <v>68268.97</v>
       </c>
       <c r="L22" t="n">
-        <v>67388.95</v>
+        <v>68533.61</v>
       </c>
       <c r="M22" t="n">
-        <v>68509.28999999999</v>
+        <v>69234.03999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>69629.63</v>
+        <v>69934.48</v>
       </c>
       <c r="O22" t="n">
-        <v>69331.75999999999</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+        <v>69763.31</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2383,59 +2384,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>67900.42999999999</v>
+        <v>66339.85000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>68069.82000000001</v>
+        <v>66441.77</v>
       </c>
       <c r="D23" t="n">
-        <v>66499.49000000001</v>
+        <v>62704.6</v>
       </c>
       <c r="E23" t="n">
-        <v>66835.53999999999</v>
+        <v>64141.12</v>
       </c>
       <c r="F23" t="n">
-        <v>-1915.97</v>
+        <v>-2694.42</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0403</v>
       </c>
       <c r="H23" t="n">
-        <v>1570.33</v>
+        <v>3737.17</v>
       </c>
       <c r="I23" t="n">
-        <v>66868.10000000001</v>
+        <v>64929.16</v>
       </c>
       <c r="J23" t="n">
-        <v>68004.34</v>
+        <v>65040.65</v>
       </c>
       <c r="K23" t="n">
-        <v>68268.97</v>
+        <v>66050.38</v>
       </c>
       <c r="L23" t="n">
-        <v>68533.61</v>
+        <v>67060.10000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>69234.03999999999</v>
+        <v>67620.7</v>
       </c>
       <c r="N23" t="n">
-        <v>69934.48</v>
+        <v>68181.31</v>
       </c>
       <c r="O23" t="n">
-        <v>69763.31</v>
+        <v>69640.14999999999</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -2476,74 +2473,70 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>66339.85000000001</v>
+        <v>64544.05</v>
       </c>
       <c r="C24" t="n">
-        <v>66441.77</v>
+        <v>66232.19</v>
       </c>
       <c r="D24" t="n">
-        <v>62704.6</v>
+        <v>64203.47</v>
       </c>
       <c r="E24" t="n">
-        <v>64141.12</v>
+        <v>66232.19</v>
       </c>
       <c r="F24" t="n">
-        <v>-2694.42</v>
+        <v>2091.07</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0326</v>
       </c>
       <c r="H24" t="n">
-        <v>3737.17</v>
+        <v>2028.72</v>
       </c>
       <c r="I24" t="n">
-        <v>64929.16</v>
+        <v>58967.43</v>
       </c>
       <c r="J24" t="n">
-        <v>65040.65</v>
+        <v>60187.92</v>
       </c>
       <c r="K24" t="n">
-        <v>66050.38</v>
+        <v>62272.54</v>
       </c>
       <c r="L24" t="n">
-        <v>67060.10000000001</v>
+        <v>64357.15</v>
       </c>
       <c r="M24" t="n">
-        <v>67620.7</v>
+        <v>66009.71000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>68181.31</v>
+        <v>67662.25999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>69640.14999999999</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>70178.95</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2555,55 +2548,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>64544.05</v>
+        <v>66449.27</v>
       </c>
       <c r="C25" t="n">
-        <v>66232.19</v>
+        <v>67592.2</v>
       </c>
       <c r="D25" t="n">
-        <v>64203.47</v>
+        <v>65955.60000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>66232.19</v>
+        <v>66115.60000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>2091.07</v>
+        <v>-116.59</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0326</v>
+        <v>-0.0018</v>
       </c>
       <c r="H25" t="n">
-        <v>2028.72</v>
+        <v>1636.6</v>
       </c>
       <c r="I25" t="n">
-        <v>58967.43</v>
+        <v>62174.75</v>
       </c>
       <c r="J25" t="n">
-        <v>60187.92</v>
+        <v>64710.65</v>
       </c>
       <c r="K25" t="n">
-        <v>62272.54</v>
+        <v>65217.83</v>
       </c>
       <c r="L25" t="n">
-        <v>64357.15</v>
+        <v>65725.00999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>66009.71000000001</v>
+        <v>67246.55</v>
       </c>
       <c r="N25" t="n">
-        <v>67662.25999999999</v>
+        <v>68768.09</v>
       </c>
       <c r="O25" t="n">
-        <v>70178.95</v>
+        <v>68260.91</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2616,12 +2613,12 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U25" s="8" t="n">
@@ -2644,50 +2641,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>66449.27</v>
+        <v>66421.00999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>67592.2</v>
+        <v>67022.37</v>
       </c>
       <c r="D26" t="n">
-        <v>65955.60000000001</v>
+        <v>66208.66</v>
       </c>
       <c r="E26" t="n">
-        <v>66115.60000000001</v>
+        <v>66422.60000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-116.59</v>
+        <v>307</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0046</v>
       </c>
       <c r="H26" t="n">
-        <v>1636.6</v>
+        <v>813.71</v>
       </c>
       <c r="I26" t="n">
-        <v>62174.75</v>
+        <v>64319</v>
       </c>
       <c r="J26" t="n">
-        <v>64710.65</v>
+        <v>64149.85</v>
       </c>
       <c r="K26" t="n">
-        <v>65217.83</v>
+        <v>65297.3</v>
       </c>
       <c r="L26" t="n">
-        <v>65725.00999999999</v>
+        <v>66444.75</v>
       </c>
       <c r="M26" t="n">
-        <v>67246.55</v>
+        <v>66933.89999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>68768.09</v>
+        <v>67423.05</v>
       </c>
       <c r="O26" t="n">
-        <v>68260.91</v>
+        <v>69228.8</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2698,9 +2695,9 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2728,69 +2725,73 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>66421.00999999999</v>
+        <v>65584.25</v>
       </c>
       <c r="C27" t="n">
-        <v>67022.37</v>
+        <v>65720.81</v>
       </c>
       <c r="D27" t="n">
-        <v>66208.66</v>
+        <v>64201.03</v>
       </c>
       <c r="E27" t="n">
-        <v>66422.60000000001</v>
+        <v>64611.15</v>
       </c>
       <c r="F27" t="n">
-        <v>307</v>
+        <v>-1811.45</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0273</v>
       </c>
       <c r="H27" t="n">
-        <v>813.71</v>
+        <v>1519.78</v>
       </c>
       <c r="I27" t="n">
-        <v>64319</v>
+        <v>65394.95</v>
       </c>
       <c r="J27" t="n">
-        <v>64149.85</v>
+        <v>65512.44</v>
       </c>
       <c r="K27" t="n">
-        <v>65297.3</v>
+        <v>66015.75</v>
       </c>
       <c r="L27" t="n">
-        <v>66444.75</v>
+        <v>66519.06</v>
       </c>
       <c r="M27" t="n">
-        <v>66933.89999999999</v>
+        <v>66829.46000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>67423.05</v>
+        <v>67139.86</v>
       </c>
       <c r="O27" t="n">
-        <v>69228.8</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+        <v>67836.08</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2803,78 +2804,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>65584.25</v>
+        <v>65164.98</v>
       </c>
       <c r="C28" t="n">
-        <v>65720.81</v>
+        <v>65220.69</v>
       </c>
       <c r="D28" t="n">
-        <v>64201.03</v>
+        <v>64123.4</v>
       </c>
       <c r="E28" t="n">
-        <v>64611.15</v>
+        <v>64931.19</v>
       </c>
       <c r="F28" t="n">
-        <v>-1811.45</v>
+        <v>320.04</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.005</v>
       </c>
       <c r="H28" t="n">
-        <v>1519.78</v>
+        <v>1097.29</v>
       </c>
       <c r="I28" t="n">
-        <v>65394.95</v>
+        <v>62681.25</v>
       </c>
       <c r="J28" t="n">
-        <v>65512.44</v>
+        <v>62916.48</v>
       </c>
       <c r="K28" t="n">
-        <v>66015.75</v>
+        <v>63851.26</v>
       </c>
       <c r="L28" t="n">
-        <v>66519.06</v>
+        <v>64786.04</v>
       </c>
       <c r="M28" t="n">
-        <v>66829.46000000001</v>
+        <v>65371.04</v>
       </c>
       <c r="N28" t="n">
-        <v>67139.86</v>
+        <v>65956.03999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>67836.08</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>67240.59</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2891,68 +2882,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>65164.98</v>
+        <v>64539.92</v>
       </c>
       <c r="C29" t="n">
-        <v>65220.69</v>
+        <v>64573.18</v>
       </c>
       <c r="D29" t="n">
-        <v>64123.4</v>
+        <v>61923.6</v>
       </c>
       <c r="E29" t="n">
-        <v>64931.19</v>
+        <v>62364.92</v>
       </c>
       <c r="F29" t="n">
-        <v>320.04</v>
+        <v>-2566.27</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0395</v>
       </c>
       <c r="H29" t="n">
-        <v>1097.29</v>
+        <v>2649.58</v>
       </c>
       <c r="I29" t="n">
-        <v>62681.25</v>
+        <v>63026.11</v>
       </c>
       <c r="J29" t="n">
-        <v>62916.48</v>
+        <v>63963.47</v>
       </c>
       <c r="K29" t="n">
-        <v>63851.26</v>
+        <v>64382.54</v>
       </c>
       <c r="L29" t="n">
-        <v>64786.04</v>
+        <v>64801.62</v>
       </c>
       <c r="M29" t="n">
-        <v>65371.04</v>
+        <v>65479.84</v>
       </c>
       <c r="N29" t="n">
-        <v>65956.03999999999</v>
+        <v>66158.06</v>
       </c>
       <c r="O29" t="n">
-        <v>67240.59</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>66317.98</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2969,73 +2970,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>64539.92</v>
+        <v>62734.68</v>
       </c>
       <c r="C30" t="n">
-        <v>64573.18</v>
+        <v>63138.04</v>
       </c>
       <c r="D30" t="n">
-        <v>61923.6</v>
+        <v>60448.9</v>
       </c>
       <c r="E30" t="n">
-        <v>62364.92</v>
+        <v>61434.19</v>
       </c>
       <c r="F30" t="n">
-        <v>-2566.27</v>
+        <v>-930.73</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0149</v>
       </c>
       <c r="H30" t="n">
-        <v>2649.58</v>
+        <v>2689.14</v>
       </c>
       <c r="I30" t="n">
-        <v>63026.11</v>
+        <v>59274.02</v>
       </c>
       <c r="J30" t="n">
-        <v>63963.47</v>
+        <v>59273.61</v>
       </c>
       <c r="K30" t="n">
-        <v>64382.54</v>
+        <v>61040.13</v>
       </c>
       <c r="L30" t="n">
-        <v>64801.62</v>
+        <v>62806.66</v>
       </c>
       <c r="M30" t="n">
-        <v>65479.84</v>
+        <v>63689.71</v>
       </c>
       <c r="N30" t="n">
-        <v>66158.06</v>
+        <v>64572.77</v>
       </c>
       <c r="O30" t="n">
-        <v>66317.98</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
+        <v>67222.75999999999</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
@@ -3062,50 +3055,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>62734.68</v>
+        <v>61258.34</v>
       </c>
       <c r="C31" t="n">
-        <v>63138.04</v>
+        <v>62924.84</v>
       </c>
       <c r="D31" t="n">
-        <v>60448.9</v>
+        <v>61049.7</v>
       </c>
       <c r="E31" t="n">
-        <v>61434.19</v>
+        <v>61867.43</v>
       </c>
       <c r="F31" t="n">
-        <v>-930.73</v>
+        <v>433.24</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0071</v>
       </c>
       <c r="H31" t="n">
-        <v>2689.14</v>
+        <v>1875.14</v>
       </c>
       <c r="I31" t="n">
-        <v>59274.02</v>
+        <v>57759.76</v>
       </c>
       <c r="J31" t="n">
-        <v>59273.61</v>
+        <v>58565.41</v>
       </c>
       <c r="K31" t="n">
-        <v>61040.13</v>
+        <v>60089.62</v>
       </c>
       <c r="L31" t="n">
-        <v>62806.66</v>
+        <v>61613.83</v>
       </c>
       <c r="M31" t="n">
-        <v>63689.71</v>
+        <v>62778.76</v>
       </c>
       <c r="N31" t="n">
-        <v>64572.77</v>
+        <v>63943.69</v>
       </c>
       <c r="O31" t="n">
-        <v>67222.75999999999</v>
+        <v>65827.17999999999</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3113,18 +3106,18 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3137,55 +3130,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>61258.34</v>
+        <v>61957.1</v>
       </c>
       <c r="C32" t="n">
-        <v>62924.84</v>
+        <v>65364.73</v>
       </c>
       <c r="D32" t="n">
-        <v>61049.7</v>
+        <v>61948.23</v>
       </c>
       <c r="E32" t="n">
-        <v>61867.43</v>
+        <v>64362.02</v>
       </c>
       <c r="F32" t="n">
-        <v>433.24</v>
+        <v>2494.59</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0403</v>
       </c>
       <c r="H32" t="n">
-        <v>1875.14</v>
+        <v>3416.5</v>
       </c>
       <c r="I32" t="n">
-        <v>57759.76</v>
+        <v>59174.56</v>
       </c>
       <c r="J32" t="n">
-        <v>58565.41</v>
+        <v>59932.37</v>
       </c>
       <c r="K32" t="n">
-        <v>60089.62</v>
+        <v>60929.86</v>
       </c>
       <c r="L32" t="n">
-        <v>61613.83</v>
+        <v>61927.35</v>
       </c>
       <c r="M32" t="n">
-        <v>62778.76</v>
+        <v>62805</v>
       </c>
       <c r="N32" t="n">
-        <v>63943.69</v>
+        <v>63682.65</v>
       </c>
       <c r="O32" t="n">
-        <v>65827.17999999999</v>
+        <v>64799.98</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3198,7 +3195,7 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -3206,70 +3203,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>61957.1</v>
+        <v>63834.95</v>
       </c>
       <c r="C33" t="n">
-        <v>65364.73</v>
+        <v>63905.12</v>
       </c>
       <c r="D33" t="n">
-        <v>61948.23</v>
+        <v>62703.47</v>
       </c>
       <c r="E33" t="n">
-        <v>64362.02</v>
+        <v>63754.9</v>
       </c>
       <c r="F33" t="n">
-        <v>2494.59</v>
+        <v>-607.12</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0403</v>
+        <v>-0.0094</v>
       </c>
       <c r="H33" t="n">
-        <v>3416.5</v>
+        <v>1201.65</v>
       </c>
       <c r="I33" t="n">
-        <v>59174.56</v>
+        <v>58531.73</v>
       </c>
       <c r="J33" t="n">
-        <v>59932.37</v>
+        <v>61298.29</v>
       </c>
       <c r="K33" t="n">
-        <v>60929.86</v>
+        <v>62653.77</v>
       </c>
       <c r="L33" t="n">
-        <v>61927.35</v>
+        <v>64009.25</v>
       </c>
       <c r="M33" t="n">
-        <v>62805</v>
+        <v>66070.27</v>
       </c>
       <c r="N33" t="n">
-        <v>63682.65</v>
+        <v>68131.28999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>64799.98</v>
+        <v>68781.23</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3280,80 +3277,78 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>63834.95</v>
+        <v>63995.28</v>
       </c>
       <c r="C34" t="n">
-        <v>63905.12</v>
+        <v>64240.5</v>
       </c>
       <c r="D34" t="n">
-        <v>62703.47</v>
+        <v>62864.43</v>
       </c>
       <c r="E34" t="n">
-        <v>63754.9</v>
+        <v>63957.53</v>
       </c>
       <c r="F34" t="n">
-        <v>-607.12</v>
+        <v>202.63</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0032</v>
       </c>
       <c r="H34" t="n">
-        <v>1201.65</v>
+        <v>1376.07</v>
       </c>
       <c r="I34" t="n">
-        <v>58531.73</v>
+        <v>61501.82</v>
       </c>
       <c r="J34" t="n">
-        <v>61298.29</v>
+        <v>62778.55</v>
       </c>
       <c r="K34" t="n">
-        <v>62653.77</v>
+        <v>63154.07</v>
       </c>
       <c r="L34" t="n">
-        <v>64009.25</v>
+        <v>63529.6</v>
       </c>
       <c r="M34" t="n">
-        <v>66070.27</v>
+        <v>64355.72</v>
       </c>
       <c r="N34" t="n">
-        <v>68131.28999999999</v>
+        <v>65181.85</v>
       </c>
       <c r="O34" t="n">
-        <v>68781.23</v>
+        <v>65106.77</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3361,16 +3356,20 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3383,59 +3382,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>63995.28</v>
+        <v>64565.27</v>
       </c>
       <c r="C35" t="n">
-        <v>64240.5</v>
+        <v>66302.52</v>
       </c>
       <c r="D35" t="n">
-        <v>62864.43</v>
+        <v>64555.52</v>
       </c>
       <c r="E35" t="n">
-        <v>63957.53</v>
+        <v>66300.44</v>
       </c>
       <c r="F35" t="n">
-        <v>202.63</v>
+        <v>2342.91</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0366</v>
       </c>
       <c r="H35" t="n">
-        <v>1376.07</v>
+        <v>1747</v>
       </c>
       <c r="I35" t="n">
-        <v>61501.82</v>
+        <v>61488.36</v>
       </c>
       <c r="J35" t="n">
-        <v>62778.55</v>
+        <v>62783.99</v>
       </c>
       <c r="K35" t="n">
-        <v>63154.07</v>
+        <v>63269.5</v>
       </c>
       <c r="L35" t="n">
-        <v>63529.6</v>
+        <v>63755</v>
       </c>
       <c r="M35" t="n">
-        <v>64355.72</v>
+        <v>64645.57</v>
       </c>
       <c r="N35" t="n">
-        <v>65181.85</v>
+        <v>65536.13</v>
       </c>
       <c r="O35" t="n">
-        <v>65106.77</v>
+        <v>65616.57000000001</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3443,10 +3438,8 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
@@ -3455,14 +3448,18 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3474,134 +3471,136 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>64565.27</v>
+        <v>65896</v>
       </c>
       <c r="C36" t="n">
-        <v>66302.52</v>
+        <v>65983.13</v>
       </c>
       <c r="D36" t="n">
-        <v>64555.52</v>
+        <v>64942.07</v>
       </c>
       <c r="E36" t="n">
-        <v>66300.44</v>
+        <v>65683.25999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>2342.91</v>
+        <v>-617.1799999999999</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0366</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>1747</v>
+        <v>1041.06</v>
       </c>
       <c r="I36" t="n">
-        <v>61488.36</v>
+        <v>62808.52</v>
       </c>
       <c r="J36" t="n">
-        <v>62783.99</v>
+        <v>64989.14</v>
       </c>
       <c r="K36" t="n">
-        <v>63269.5</v>
+        <v>65426.94</v>
       </c>
       <c r="L36" t="n">
-        <v>63755</v>
+        <v>65864.73</v>
       </c>
       <c r="M36" t="n">
-        <v>64645.57</v>
+        <v>67173.94</v>
       </c>
       <c r="N36" t="n">
-        <v>65536.13</v>
+        <v>68483.14999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>65616.57000000001</v>
+        <v>68049.53</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>65896</v>
+        <v>65746.13</v>
       </c>
       <c r="C37" t="n">
-        <v>65983.13</v>
+        <v>65990.72</v>
       </c>
       <c r="D37" t="n">
-        <v>64942.07</v>
+        <v>64651.49</v>
       </c>
       <c r="E37" t="n">
-        <v>65683.25999999999</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-617.1799999999999</v>
+        <v>-76.55</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="H37" t="n">
-        <v>1041.06</v>
+        <v>1339.23</v>
       </c>
       <c r="I37" t="n">
-        <v>62808.52</v>
+        <v>63901.01</v>
       </c>
       <c r="J37" t="n">
-        <v>64989.14</v>
+        <v>64752.52</v>
       </c>
       <c r="K37" t="n">
-        <v>65426.94</v>
+        <v>65162.73</v>
       </c>
       <c r="L37" t="n">
-        <v>65864.73</v>
+        <v>65572.92999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>67173.94</v>
+        <v>66203.78999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>68483.14999999999</v>
+        <v>66834.64999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>68049.53</v>
+        <v>67024.2</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3616,9 +3615,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3644,74 +3643,74 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>65746.13</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>65990.72</v>
+        <v>67006.84</v>
       </c>
       <c r="D38" t="n">
-        <v>64651.49</v>
+        <v>65848.58</v>
       </c>
       <c r="E38" t="n">
-        <v>65606.71000000001</v>
+        <v>66970.22</v>
       </c>
       <c r="F38" t="n">
-        <v>-76.55</v>
+        <v>1363.51</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0208</v>
       </c>
       <c r="H38" t="n">
-        <v>1339.23</v>
+        <v>1158.27</v>
       </c>
       <c r="I38" t="n">
-        <v>63901.01</v>
+        <v>63312.26</v>
       </c>
       <c r="J38" t="n">
-        <v>64752.52</v>
+        <v>64410.28</v>
       </c>
       <c r="K38" t="n">
-        <v>65162.73</v>
+        <v>64937.1</v>
       </c>
       <c r="L38" t="n">
-        <v>65572.92999999999</v>
+        <v>65463.91</v>
       </c>
       <c r="M38" t="n">
-        <v>66203.78999999999</v>
+        <v>66276.33</v>
       </c>
       <c r="N38" t="n">
-        <v>66834.64999999999</v>
+        <v>67088.75</v>
       </c>
       <c r="O38" t="n">
-        <v>67024.2</v>
+        <v>67329.95</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3721,59 +3720,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>65905.10000000001</v>
+        <v>66994.05</v>
       </c>
       <c r="C39" t="n">
-        <v>67006.84</v>
+        <v>67569.36</v>
       </c>
       <c r="D39" t="n">
-        <v>65848.58</v>
+        <v>66735.75999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>66970.22</v>
+        <v>67524.06</v>
       </c>
       <c r="F39" t="n">
-        <v>1363.51</v>
+        <v>553.84</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="H39" t="n">
-        <v>1158.27</v>
+        <v>833.6</v>
       </c>
       <c r="I39" t="n">
-        <v>63312.26</v>
+        <v>64690.31</v>
       </c>
       <c r="J39" t="n">
-        <v>64410.28</v>
+        <v>66083.21000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>64937.1</v>
+        <v>66391.09</v>
       </c>
       <c r="L39" t="n">
-        <v>65463.91</v>
+        <v>66698.96000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>66276.33</v>
+        <v>67549.35000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>67088.75</v>
+        <v>68399.74000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>67329.95</v>
+        <v>68165.11</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3791,13 +3786,11 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3812,50 +3805,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>66994.05</v>
+        <v>68033.17</v>
       </c>
       <c r="C40" t="n">
-        <v>67569.36</v>
+        <v>68799.71000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>66735.75999999999</v>
+        <v>68006.17</v>
       </c>
       <c r="E40" t="n">
-        <v>67524.06</v>
+        <v>68308.59</v>
       </c>
       <c r="F40" t="n">
-        <v>553.84</v>
+        <v>784.53</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0116</v>
       </c>
       <c r="H40" t="n">
-        <v>833.6</v>
+        <v>793.54</v>
       </c>
       <c r="I40" t="n">
-        <v>64690.31</v>
+        <v>65902.16</v>
       </c>
       <c r="J40" t="n">
-        <v>66083.21000000001</v>
+        <v>66876.21000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>66391.09</v>
+        <v>67107.25999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>66698.96000000001</v>
+        <v>67338.31</v>
       </c>
       <c r="M40" t="n">
-        <v>67549.35000000001</v>
+        <v>67940.86</v>
       </c>
       <c r="N40" t="n">
-        <v>68399.74000000001</v>
+        <v>68543.42</v>
       </c>
       <c r="O40" t="n">
-        <v>68165.11</v>
+        <v>68402.96000000001</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3873,14 +3866,18 @@
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
@@ -3892,50 +3889,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>68033.17</v>
+        <v>68811.17</v>
       </c>
       <c r="C41" t="n">
-        <v>68799.71000000001</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>68006.17</v>
+        <v>68471.14999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>68308.59</v>
+        <v>68713.8</v>
       </c>
       <c r="F41" t="n">
-        <v>784.53</v>
+        <v>405.2</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0059</v>
       </c>
       <c r="H41" t="n">
-        <v>793.54</v>
+        <v>1137.09</v>
       </c>
       <c r="I41" t="n">
-        <v>65902.16</v>
+        <v>67212.63</v>
       </c>
       <c r="J41" t="n">
-        <v>66876.21000000001</v>
+        <v>67467.88</v>
       </c>
       <c r="K41" t="n">
-        <v>67107.25999999999</v>
+        <v>67911.82000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>67338.31</v>
+        <v>68355.77</v>
       </c>
       <c r="M41" t="n">
-        <v>67940.86</v>
+        <v>68705.36</v>
       </c>
       <c r="N41" t="n">
-        <v>68543.42</v>
+        <v>69054.96000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>68402.96000000001</v>
+        <v>69593.25</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3953,7 +3950,7 @@
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U41" s="8" t="inlineStr">
@@ -3963,7 +3960,7 @@
       </c>
       <c r="V41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W41" s="9" t="inlineStr">
@@ -3976,50 +3973,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>68811.17</v>
+        <v>68882.06</v>
       </c>
       <c r="C42" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>68471.14999999999</v>
+        <v>68492.03999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>68713.8</v>
+        <v>69220.25</v>
       </c>
       <c r="F42" t="n">
-        <v>405.2</v>
+        <v>506.45</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="H42" t="n">
-        <v>1137.09</v>
+        <v>733.53</v>
       </c>
       <c r="I42" t="n">
-        <v>67212.63</v>
+        <v>67334.05</v>
       </c>
       <c r="J42" t="n">
-        <v>67467.88</v>
+        <v>67413.75</v>
       </c>
       <c r="K42" t="n">
-        <v>67911.82000000001</v>
+        <v>68145.25</v>
       </c>
       <c r="L42" t="n">
-        <v>68355.77</v>
+        <v>68876.75</v>
       </c>
       <c r="M42" t="n">
-        <v>68705.36</v>
+        <v>69282.34</v>
       </c>
       <c r="N42" t="n">
-        <v>69054.96000000001</v>
+        <v>69687.94</v>
       </c>
       <c r="O42" t="n">
-        <v>69593.25</v>
+        <v>70745.34</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4040,163 +4037,163 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>68882.06</v>
+        <v>68847.35000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>69225.57000000001</v>
+        <v>69093.2</v>
       </c>
       <c r="D43" t="n">
-        <v>68492.03999999999</v>
+        <v>67368.96000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>69220.25</v>
+        <v>67460.73</v>
       </c>
       <c r="F43" t="n">
-        <v>506.45</v>
+        <v>-1759.52</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0254</v>
       </c>
       <c r="H43" t="n">
-        <v>733.53</v>
+        <v>1724.24</v>
       </c>
       <c r="I43" t="n">
-        <v>67334.05</v>
+        <v>67758.50999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>67413.75</v>
+        <v>68667.44</v>
       </c>
       <c r="K43" t="n">
-        <v>68145.25</v>
+        <v>68853.48</v>
       </c>
       <c r="L43" t="n">
-        <v>68876.75</v>
+        <v>69039.53</v>
       </c>
       <c r="M43" t="n">
-        <v>69282.34</v>
+        <v>69587.02</v>
       </c>
       <c r="N43" t="n">
-        <v>69687.94</v>
+        <v>70134.5</v>
       </c>
       <c r="O43" t="n">
-        <v>70745.34</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
+        <v>69959.10000000001</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>68847.35000000001</v>
+        <v>66812.27</v>
       </c>
       <c r="C44" t="n">
-        <v>69093.2</v>
+        <v>66833.50999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>67368.96000000001</v>
+        <v>65133.98</v>
       </c>
       <c r="E44" t="n">
-        <v>67460.73</v>
+        <v>65326.42</v>
       </c>
       <c r="F44" t="n">
-        <v>-1759.52</v>
+        <v>-2134.3</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="H44" t="n">
-        <v>1724.24</v>
+        <v>1699.53</v>
       </c>
       <c r="I44" t="n">
-        <v>67758.50999999999</v>
+        <v>65644.72</v>
       </c>
       <c r="J44" t="n">
-        <v>68667.44</v>
+        <v>65351.31</v>
       </c>
       <c r="K44" t="n">
-        <v>68853.48</v>
+        <v>66598.61</v>
       </c>
       <c r="L44" t="n">
-        <v>69039.53</v>
+        <v>67845.89999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>69587.02</v>
+        <v>68322.85000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>70134.5</v>
+        <v>68799.78999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>69959.10000000001</v>
+        <v>70817.45</v>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
@@ -4228,74 +4225,70 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>66812.27</v>
+        <v>65732.78999999999</v>
       </c>
       <c r="C45" t="n">
-        <v>66833.50999999999</v>
+        <v>66325.32000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>65133.98</v>
+        <v>65652.25</v>
       </c>
       <c r="E45" t="n">
-        <v>65326.42</v>
+        <v>66216.78999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>-2134.3</v>
+        <v>890.37</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H45" t="n">
-        <v>1699.53</v>
+        <v>673.0700000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>65644.72</v>
+        <v>63434.45</v>
       </c>
       <c r="J45" t="n">
-        <v>65351.31</v>
+        <v>63298.23</v>
       </c>
       <c r="K45" t="n">
-        <v>66598.61</v>
+        <v>64476.66</v>
       </c>
       <c r="L45" t="n">
-        <v>67845.89999999999</v>
+        <v>65655.08</v>
       </c>
       <c r="M45" t="n">
-        <v>68322.85000000001</v>
+        <v>66176.19</v>
       </c>
       <c r="N45" t="n">
-        <v>68799.78999999999</v>
+        <v>66697.28999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>70817.45</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
+        <v>68533.03999999999</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4307,74 +4300,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>65732.78999999999</v>
+        <v>65427.69</v>
       </c>
       <c r="C46" t="n">
-        <v>66325.32000000001</v>
+        <v>66125.88</v>
       </c>
       <c r="D46" t="n">
-        <v>65652.25</v>
+        <v>65260.22</v>
       </c>
       <c r="E46" t="n">
-        <v>66216.78999999999</v>
+        <v>66016.36</v>
       </c>
       <c r="F46" t="n">
-        <v>890.37</v>
+        <v>-200.43</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.003</v>
       </c>
       <c r="H46" t="n">
-        <v>673.0700000000001</v>
+        <v>865.66</v>
       </c>
       <c r="I46" t="n">
-        <v>63434.45</v>
+        <v>64979.18</v>
       </c>
       <c r="J46" t="n">
-        <v>63298.23</v>
+        <v>65657.72</v>
       </c>
       <c r="K46" t="n">
-        <v>64476.66</v>
+        <v>65880.25</v>
       </c>
       <c r="L46" t="n">
-        <v>65655.08</v>
+        <v>66102.78999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>66176.19</v>
+        <v>66553.32000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>66697.28999999999</v>
+        <v>67003.86</v>
       </c>
       <c r="O46" t="n">
-        <v>68533.03999999999</v>
+        <v>66998.39</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4387,76 +4386,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65427.69</v>
+        <v>65978.95</v>
       </c>
       <c r="C47" t="n">
-        <v>66125.88</v>
+        <v>66257.73</v>
       </c>
       <c r="D47" t="n">
-        <v>65260.22</v>
+        <v>65470.95</v>
       </c>
       <c r="E47" t="n">
-        <v>66016.36</v>
+        <v>65528.09</v>
       </c>
       <c r="F47" t="n">
-        <v>-200.43</v>
+        <v>-488.27</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0074</v>
       </c>
       <c r="H47" t="n">
-        <v>865.66</v>
+        <v>786.78</v>
       </c>
       <c r="I47" t="n">
-        <v>64979.18</v>
+        <v>64394.55</v>
       </c>
       <c r="J47" t="n">
-        <v>65657.72</v>
+        <v>65312.35</v>
       </c>
       <c r="K47" t="n">
-        <v>65880.25</v>
+        <v>65583.53</v>
       </c>
       <c r="L47" t="n">
-        <v>66102.78999999999</v>
+        <v>65854.71000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>66553.32000000001</v>
+        <v>66449.19</v>
       </c>
       <c r="N47" t="n">
-        <v>67003.86</v>
+        <v>67043.67999999999</v>
       </c>
       <c r="O47" t="n">
-        <v>66998.39</v>
+        <v>66991.55</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q47" s="6" t="n">
+        <v/>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4473,75 +4466,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65978.95</v>
+        <v>65195.26</v>
       </c>
       <c r="C48" t="n">
-        <v>66257.73</v>
+        <v>65904.24000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>65470.95</v>
+        <v>64609.47</v>
       </c>
       <c r="E48" t="n">
-        <v>65528.09</v>
+        <v>65856.42999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>-488.27</v>
+        <v>328.34</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.005</v>
       </c>
       <c r="H48" t="n">
-        <v>786.78</v>
+        <v>1294.77</v>
       </c>
       <c r="I48" t="n">
-        <v>64394.55</v>
+        <v>64684.17</v>
       </c>
       <c r="J48" t="n">
-        <v>65312.35</v>
+        <v>64573.19</v>
       </c>
       <c r="K48" t="n">
-        <v>65583.53</v>
+        <v>65134.7</v>
       </c>
       <c r="L48" t="n">
-        <v>65854.71000000001</v>
+        <v>65696.21000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>66449.19</v>
+        <v>65921.48</v>
       </c>
       <c r="N48" t="n">
-        <v>67043.67999999999</v>
+        <v>66146.74000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>66991.55</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
+        <v>67044.5</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4555,70 +4556,66 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65195.26</v>
+        <v>65604.49000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>65904.24000000001</v>
+        <v>66442.34</v>
       </c>
       <c r="D49" t="n">
-        <v>64609.47</v>
+        <v>65390.55</v>
       </c>
       <c r="E49" t="n">
-        <v>65856.42999999999</v>
+        <v>66262.16</v>
       </c>
       <c r="F49" t="n">
-        <v>328.34</v>
+        <v>405.73</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0062</v>
       </c>
       <c r="H49" t="n">
-        <v>1294.77</v>
+        <v>1051.79</v>
       </c>
       <c r="I49" t="n">
-        <v>64684.17</v>
+        <v>63314.7</v>
       </c>
       <c r="J49" t="n">
-        <v>64573.19</v>
+        <v>64861.44</v>
       </c>
       <c r="K49" t="n">
-        <v>65134.7</v>
+        <v>65209.04</v>
       </c>
       <c r="L49" t="n">
-        <v>65696.21000000001</v>
+        <v>65556.64</v>
       </c>
       <c r="M49" t="n">
-        <v>65921.48</v>
+        <v>66503.82000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>66146.74000000001</v>
+        <v>67450.99000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>67044.5</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67199.02</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
       </c>
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
@@ -4643,57 +4640,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65604.49000000001</v>
+        <v>66775.78</v>
       </c>
       <c r="C50" t="n">
-        <v>66442.34</v>
+        <v>66954.69</v>
       </c>
       <c r="D50" t="n">
-        <v>65390.55</v>
+        <v>65782.59</v>
       </c>
       <c r="E50" t="n">
-        <v>66262.16</v>
+        <v>66131.98</v>
       </c>
       <c r="F50" t="n">
-        <v>405.73</v>
+        <v>-130.18</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.002</v>
       </c>
       <c r="H50" t="n">
-        <v>1051.79</v>
+        <v>1172.09</v>
       </c>
       <c r="I50" t="n">
-        <v>63314.7</v>
+        <v>64338.76</v>
       </c>
       <c r="J50" t="n">
-        <v>64861.44</v>
+        <v>65383.22</v>
       </c>
       <c r="K50" t="n">
-        <v>65209.04</v>
+        <v>65736.25999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>65556.64</v>
+        <v>66089.3</v>
       </c>
       <c r="M50" t="n">
-        <v>66503.82000000001</v>
+        <v>66788.05</v>
       </c>
       <c r="N50" t="n">
-        <v>67450.99000000001</v>
+        <v>67486.8</v>
       </c>
       <c r="O50" t="n">
-        <v>67199.02</v>
+        <v>67494.14</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4706,12 +4703,12 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U50" s="8" t="n">
@@ -4727,57 +4724,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>66775.78</v>
+        <v>66104.49000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>66954.69</v>
+        <v>66842.82000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>65782.59</v>
+        <v>66012.2</v>
       </c>
       <c r="E51" t="n">
-        <v>66131.98</v>
+        <v>66405.56</v>
       </c>
       <c r="F51" t="n">
-        <v>-130.18</v>
+        <v>273.59</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0041</v>
       </c>
       <c r="H51" t="n">
-        <v>1172.09</v>
+        <v>830.62</v>
       </c>
       <c r="I51" t="n">
-        <v>64338.76</v>
+        <v>64610.5</v>
       </c>
       <c r="J51" t="n">
-        <v>65383.22</v>
+        <v>64841.55</v>
       </c>
       <c r="K51" t="n">
-        <v>65736.25999999999</v>
+        <v>65545.92999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>66089.3</v>
+        <v>66250.31</v>
       </c>
       <c r="M51" t="n">
-        <v>66788.05</v>
+        <v>66718.02</v>
       </c>
       <c r="N51" t="n">
-        <v>67486.8</v>
+        <v>67185.74000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>67494.14</v>
+        <v>68126.78</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4818,69 +4815,73 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>66104.49000000001</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C52" t="n">
-        <v>66842.82000000001</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>66012.2</v>
+        <v>64832.1</v>
       </c>
       <c r="E52" t="n">
-        <v>66405.56</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>273.59</v>
+        <v>-93.63</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0014</v>
       </c>
       <c r="H52" t="n">
-        <v>830.62</v>
+        <v>1479.83</v>
       </c>
       <c r="I52" t="n">
-        <v>64610.5</v>
+        <v>65181.59</v>
       </c>
       <c r="J52" t="n">
-        <v>64841.55</v>
+        <v>65563.97</v>
       </c>
       <c r="K52" t="n">
-        <v>65545.92999999999</v>
+        <v>65990.25</v>
       </c>
       <c r="L52" t="n">
-        <v>66250.31</v>
+        <v>66416.53999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>66718.02</v>
+        <v>66820.87</v>
       </c>
       <c r="N52" t="n">
-        <v>67185.74000000001</v>
+        <v>67225.21000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>68126.78</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67673.44</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4893,78 +4894,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65668.50999999999</v>
+        <v>65885.47</v>
       </c>
       <c r="C53" t="n">
-        <v>66311.92999999999</v>
+        <v>66525.7</v>
       </c>
       <c r="D53" t="n">
-        <v>64832.1</v>
+        <v>65576.61</v>
       </c>
       <c r="E53" t="n">
-        <v>66311.92999999999</v>
+        <v>66215.34</v>
       </c>
       <c r="F53" t="n">
-        <v>-93.63</v>
+        <v>-96.59</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0015</v>
       </c>
       <c r="H53" t="n">
-        <v>1479.83</v>
+        <v>949.09</v>
       </c>
       <c r="I53" t="n">
-        <v>65181.59</v>
+        <v>63352.27</v>
       </c>
       <c r="J53" t="n">
-        <v>65563.97</v>
+        <v>65202.06</v>
       </c>
       <c r="K53" t="n">
-        <v>65990.25</v>
+        <v>65572.02</v>
       </c>
       <c r="L53" t="n">
-        <v>66416.53999999999</v>
+        <v>65941.97</v>
       </c>
       <c r="M53" t="n">
-        <v>66820.87</v>
+        <v>67051.84</v>
       </c>
       <c r="N53" t="n">
-        <v>67225.21000000001</v>
+        <v>68161.71000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>67673.44</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>67791.75999999999</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4981,68 +4972,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>65885.47</v>
+        <v>65195.43</v>
       </c>
       <c r="C54" t="n">
-        <v>66525.7</v>
+        <v>65195.43</v>
       </c>
       <c r="D54" t="n">
-        <v>65576.61</v>
+        <v>64215.47</v>
       </c>
       <c r="E54" t="n">
-        <v>66215.34</v>
+        <v>64325.64</v>
       </c>
       <c r="F54" t="n">
-        <v>-96.59</v>
+        <v>-1889.7</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0285</v>
       </c>
       <c r="H54" t="n">
-        <v>949.09</v>
+        <v>979.96</v>
       </c>
       <c r="I54" t="n">
-        <v>63352.27</v>
+        <v>64627.52</v>
       </c>
       <c r="J54" t="n">
-        <v>65202.06</v>
+        <v>65348.34</v>
       </c>
       <c r="K54" t="n">
-        <v>65572.02</v>
+        <v>65740.8</v>
       </c>
       <c r="L54" t="n">
-        <v>65941.97</v>
+        <v>66133.25</v>
       </c>
       <c r="M54" t="n">
-        <v>67051.84</v>
+        <v>66689.89</v>
       </c>
       <c r="N54" t="n">
-        <v>68161.71000000001</v>
+        <v>67246.53</v>
       </c>
       <c r="O54" t="n">
-        <v>67791.75999999999</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>67474.8</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5059,69 +5060,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="C55" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="D55" t="n">
-        <v>64215.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E55" t="n">
-        <v>64325.64</v>
+        <v>64214.48</v>
       </c>
       <c r="F55" t="n">
-        <v>-1889.7</v>
+        <v>-111.16</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0017</v>
       </c>
       <c r="H55" t="n">
-        <v>979.96</v>
+        <v>952.01</v>
       </c>
       <c r="I55" t="n">
-        <v>64627.52</v>
+        <v>63235.51</v>
       </c>
       <c r="J55" t="n">
-        <v>65348.34</v>
+        <v>63155.78</v>
       </c>
       <c r="K55" t="n">
-        <v>65740.8</v>
+        <v>63835.66</v>
       </c>
       <c r="L55" t="n">
-        <v>66133.25</v>
+        <v>64515.54</v>
       </c>
       <c r="M55" t="n">
-        <v>66689.89</v>
+        <v>64815.62</v>
       </c>
       <c r="N55" t="n">
-        <v>67246.53</v>
+        <v>65115.7</v>
       </c>
       <c r="O55" t="n">
-        <v>67474.8</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66175.39</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
@@ -5130,7 +5123,7 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5152,50 +5145,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>64724.81</v>
+        <v>64498.94</v>
       </c>
       <c r="C56" t="n">
-        <v>64724.81</v>
+        <v>65182.45</v>
       </c>
       <c r="D56" t="n">
-        <v>63772.8</v>
+        <v>64228.47</v>
       </c>
       <c r="E56" t="n">
-        <v>64214.48</v>
+        <v>65020.94</v>
       </c>
       <c r="F56" t="n">
-        <v>-111.16</v>
+        <v>806.46</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="H56" t="n">
-        <v>952.01</v>
+        <v>953.98</v>
       </c>
       <c r="I56" t="n">
-        <v>63235.51</v>
+        <v>62820.79</v>
       </c>
       <c r="J56" t="n">
-        <v>63155.78</v>
+        <v>63245.31</v>
       </c>
       <c r="K56" t="n">
-        <v>63835.66</v>
+        <v>63738.48</v>
       </c>
       <c r="L56" t="n">
-        <v>64515.54</v>
+        <v>64231.64</v>
       </c>
       <c r="M56" t="n">
-        <v>64815.62</v>
+        <v>64690.48</v>
       </c>
       <c r="N56" t="n">
-        <v>65115.7</v>
+        <v>65149.33</v>
       </c>
       <c r="O56" t="n">
-        <v>66175.39</v>
+        <v>65676.82000000001</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5203,21 +5196,23 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5227,55 +5222,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>64498.94</v>
+        <v>65600.42</v>
       </c>
       <c r="C57" t="n">
-        <v>65182.45</v>
+        <v>66668.71000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>64228.47</v>
+        <v>65600.42</v>
       </c>
       <c r="E57" t="n">
-        <v>65020.94</v>
+        <v>66399.84</v>
       </c>
       <c r="F57" t="n">
-        <v>806.46</v>
+        <v>1378.9</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="H57" t="n">
-        <v>953.98</v>
+        <v>1068.29</v>
       </c>
       <c r="I57" t="n">
-        <v>62820.79</v>
+        <v>63274.49</v>
       </c>
       <c r="J57" t="n">
-        <v>63245.31</v>
+        <v>64224.7</v>
       </c>
       <c r="K57" t="n">
-        <v>63738.48</v>
+        <v>64543.95</v>
       </c>
       <c r="L57" t="n">
-        <v>64231.64</v>
+        <v>64863.2</v>
       </c>
       <c r="M57" t="n">
-        <v>64690.48</v>
+        <v>65497.93</v>
       </c>
       <c r="N57" t="n">
-        <v>65149.33</v>
+        <v>66132.66</v>
       </c>
       <c r="O57" t="n">
-        <v>65676.82000000001</v>
+        <v>66136.42999999999</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5298,171 +5297,167 @@
       </c>
       <c r="U57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>65600.42</v>
+        <v>65843.69</v>
       </c>
       <c r="C58" t="n">
-        <v>66668.71000000001</v>
+        <v>66791.84</v>
       </c>
       <c r="D58" t="n">
-        <v>65600.42</v>
+        <v>65269.33</v>
       </c>
       <c r="E58" t="n">
-        <v>66399.84</v>
+        <v>65269.33</v>
       </c>
       <c r="F58" t="n">
-        <v>1378.9</v>
+        <v>-1130.52</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.017</v>
       </c>
       <c r="H58" t="n">
-        <v>1068.29</v>
+        <v>1522.52</v>
       </c>
       <c r="I58" t="n">
-        <v>63274.49</v>
+        <v>64532.13</v>
       </c>
       <c r="J58" t="n">
-        <v>64224.7</v>
+        <v>65464.19</v>
       </c>
       <c r="K58" t="n">
-        <v>64543.95</v>
+        <v>65865.7</v>
       </c>
       <c r="L58" t="n">
-        <v>64863.2</v>
+        <v>66267.21000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>65497.93</v>
+        <v>66933.99000000001</v>
       </c>
       <c r="N58" t="n">
-        <v>66132.66</v>
+        <v>67600.77</v>
       </c>
       <c r="O58" t="n">
-        <v>66136.42999999999</v>
+        <v>67737</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
+      <c r="Q58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>65843.69</v>
+        <v>65087.22</v>
       </c>
       <c r="C59" t="n">
-        <v>66791.84</v>
+        <v>65794.03</v>
       </c>
       <c r="D59" t="n">
-        <v>65269.33</v>
+        <v>65017.68</v>
       </c>
       <c r="E59" t="n">
-        <v>65269.33</v>
+        <v>65142.78</v>
       </c>
       <c r="F59" t="n">
-        <v>-1130.52</v>
+        <v>-126.55</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0019</v>
       </c>
       <c r="H59" t="n">
-        <v>1522.52</v>
+        <v>776.35</v>
       </c>
       <c r="I59" t="n">
-        <v>64532.13</v>
+        <v>63746.81</v>
       </c>
       <c r="J59" t="n">
-        <v>65464.19</v>
+        <v>63366.18</v>
       </c>
       <c r="K59" t="n">
-        <v>65865.7</v>
+        <v>64508.07</v>
       </c>
       <c r="L59" t="n">
-        <v>66267.21000000001</v>
+        <v>65649.96000000001</v>
       </c>
       <c r="M59" t="n">
-        <v>66933.99000000001</v>
+        <v>66030.59</v>
       </c>
       <c r="N59" t="n">
-        <v>67600.77</v>
+        <v>66411.21000000001</v>
       </c>
       <c r="O59" t="n">
-        <v>67737</v>
+        <v>68314.36</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5479,68 +5474,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>65087.22</v>
+        <v>64768.53</v>
       </c>
       <c r="C60" t="n">
-        <v>65794.03</v>
+        <v>65270.95</v>
       </c>
       <c r="D60" t="n">
-        <v>65017.68</v>
+        <v>64186.68</v>
       </c>
       <c r="E60" t="n">
-        <v>65142.78</v>
+        <v>65270.95</v>
       </c>
       <c r="F60" t="n">
-        <v>-126.55</v>
+        <v>128.17</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="H60" t="n">
-        <v>776.35</v>
+        <v>1084.27</v>
       </c>
       <c r="I60" t="n">
-        <v>63746.81</v>
+        <v>64241.33</v>
       </c>
       <c r="J60" t="n">
-        <v>63366.18</v>
+        <v>64234.89</v>
       </c>
       <c r="K60" t="n">
-        <v>64508.07</v>
+        <v>64754.61</v>
       </c>
       <c r="L60" t="n">
-        <v>65649.96000000001</v>
+        <v>65274.32</v>
       </c>
       <c r="M60" t="n">
-        <v>66030.59</v>
+        <v>65530.96</v>
       </c>
       <c r="N60" t="n">
-        <v>66411.21000000001</v>
+        <v>65787.60000000001</v>
       </c>
       <c r="O60" t="n">
-        <v>68314.36</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+        <v>66570.38</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
@@ -5561,64 +5558,66 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>64768.53</v>
+        <v>64276.82</v>
       </c>
       <c r="C61" t="n">
-        <v>65270.95</v>
+        <v>64312.02</v>
       </c>
       <c r="D61" t="n">
-        <v>64186.68</v>
+        <v>63208.63</v>
       </c>
       <c r="E61" t="n">
-        <v>65270.95</v>
+        <v>64011.34</v>
       </c>
       <c r="F61" t="n">
-        <v>128.17</v>
+        <v>-1259.61</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H61" t="n">
-        <v>1084.27</v>
+        <v>1103.39</v>
       </c>
       <c r="I61" t="n">
-        <v>64241.33</v>
+        <v>63102.41</v>
       </c>
       <c r="J61" t="n">
-        <v>64234.89</v>
+        <v>64457.75</v>
       </c>
       <c r="K61" t="n">
-        <v>64754.61</v>
+        <v>64728.81</v>
       </c>
       <c r="L61" t="n">
-        <v>65274.32</v>
+        <v>64999.88</v>
       </c>
       <c r="M61" t="n">
-        <v>65530.96</v>
+        <v>65813.08</v>
       </c>
       <c r="N61" t="n">
-        <v>65787.60000000001</v>
+        <v>66626.28999999999</v>
       </c>
       <c r="O61" t="n">
-        <v>66570.38</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66355.22</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
@@ -5628,7 +5627,7 @@
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5645,73 +5644,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>64276.82</v>
+        <v>63659.53</v>
       </c>
       <c r="C62" t="n">
-        <v>64312.02</v>
+        <v>63691.53</v>
       </c>
       <c r="D62" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E62" t="n">
-        <v>64011.34</v>
+        <v>63492.99</v>
       </c>
       <c r="F62" t="n">
-        <v>-1259.61</v>
+        <v>-518.35</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0081</v>
       </c>
       <c r="H62" t="n">
-        <v>1103.39</v>
+        <v>965.35</v>
       </c>
       <c r="I62" t="n">
-        <v>63102.41</v>
+        <v>62105.24</v>
       </c>
       <c r="J62" t="n">
-        <v>64457.75</v>
+        <v>63033.46</v>
       </c>
       <c r="K62" t="n">
-        <v>64728.81</v>
+        <v>63459.64</v>
       </c>
       <c r="L62" t="n">
-        <v>64999.88</v>
+        <v>63885.83</v>
       </c>
       <c r="M62" t="n">
-        <v>65813.08</v>
+        <v>64563.04</v>
       </c>
       <c r="N62" t="n">
-        <v>66626.28999999999</v>
+        <v>65240.24</v>
       </c>
       <c r="O62" t="n">
-        <v>66355.22</v>
+        <v>65415.41</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5734,114 +5729,30 @@
       <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>63659.53</v>
-      </c>
-      <c r="C63" t="n">
-        <v>63691.53</v>
-      </c>
-      <c r="D63" t="n">
-        <v>62726.18</v>
-      </c>
-      <c r="E63" t="n">
-        <v/>
-      </c>
-      <c r="F63" t="n">
-        <v/>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H63" t="n">
-        <v>965.35</v>
-      </c>
-      <c r="I63" t="n">
-        <v>62105.24</v>
-      </c>
-      <c r="J63" t="n">
-        <v>63033.46</v>
-      </c>
-      <c r="K63" t="n">
-        <v>63459.64</v>
-      </c>
-      <c r="L63" t="n">
-        <v>63885.83</v>
-      </c>
-      <c r="M63" t="n">
-        <v>64563.04</v>
-      </c>
-      <c r="N63" t="n">
-        <v>65240.24</v>
-      </c>
-      <c r="O63" t="n">
-        <v>65415.41</v>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="14" t="n">
+      <c r="I63" s="13" t="n">
         <v>61760.83</v>
       </c>
-      <c r="J64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="14" t="n">
+      <c r="J63" s="13" t="n">
+        <v>62669.7</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>63010.31</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>63350.92</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>63975.66</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>64600.41</v>
+      </c>
+      <c r="O63" s="13" t="n">
         <v>64656.88</v>
       </c>
     </row>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5729,31 +5732,117 @@
       <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>63190.37</v>
+      </c>
+      <c r="C63" t="n">
+        <v>64101</v>
+      </c>
+      <c r="D63" t="n">
+        <v>63067.18</v>
+      </c>
+      <c r="E63" t="n">
+        <v/>
+      </c>
+      <c r="F63" t="n">
+        <v/>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H63" t="n">
+        <v>1033.82</v>
+      </c>
+      <c r="I63" t="n">
+        <v>61760.83</v>
+      </c>
+      <c r="J63" t="n">
+        <v>62669.7</v>
+      </c>
+      <c r="K63" t="n">
+        <v>63010.31</v>
+      </c>
+      <c r="L63" t="n">
+        <v>63350.92</v>
+      </c>
+      <c r="M63" t="n">
+        <v>63975.66</v>
+      </c>
+      <c r="N63" t="n">
+        <v>64600.41</v>
+      </c>
+      <c r="O63" t="n">
+        <v>64656.88</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
-        <v>61760.83</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>62669.7</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>63010.31</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>63350.92</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>63975.66</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>64600.41</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>64656.88</v>
+      <c r="I64" s="14" t="n">
+        <v>62033.36</v>
+      </c>
+      <c r="J64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O64" s="14" t="n">
+        <v>65134.82</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,50 +644,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70163.71000000001</v>
+        <v>71551.03</v>
       </c>
       <c r="C2" t="n">
-        <v>71398.58</v>
+        <v>71952.99000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>70092.94</v>
+        <v>70517.98</v>
       </c>
       <c r="E2" t="n">
-        <v>71053.49000000001</v>
+        <v>71250.06</v>
       </c>
       <c r="F2" t="n">
-        <v>1151.24</v>
+        <v>196.57</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0028</v>
       </c>
       <c r="H2" t="n">
-        <v>1305.64</v>
+        <v>1435.02</v>
       </c>
       <c r="I2" t="n">
-        <v>67845.52</v>
+        <v>68787.3</v>
       </c>
       <c r="J2" t="n">
-        <v>68935.41</v>
+        <v>69901.72</v>
       </c>
       <c r="K2" t="n">
-        <v>69332.19</v>
+        <v>70400.67</v>
       </c>
       <c r="L2" t="n">
-        <v>69728.97</v>
+        <v>70899.62</v>
       </c>
       <c r="M2" t="n">
-        <v>70472.31</v>
+        <v>71706.31</v>
       </c>
       <c r="N2" t="n">
-        <v>71215.64999999999</v>
+        <v>72513</v>
       </c>
       <c r="O2" t="n">
-        <v>71265.87</v>
+        <v>72704.22</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,7 +700,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -708,15 +708,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -728,50 +724,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71551.03</v>
+        <v>71067.14999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>71952.99000000001</v>
+        <v>72831.73</v>
       </c>
       <c r="D3" t="n">
-        <v>70517.98</v>
+        <v>71009.52</v>
       </c>
       <c r="E3" t="n">
-        <v>71250.06</v>
+        <v>72353.96000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>196.57</v>
+        <v>1103.9</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0155</v>
       </c>
       <c r="H3" t="n">
-        <v>1435.02</v>
+        <v>1822.2</v>
       </c>
       <c r="I3" t="n">
-        <v>68787.3</v>
+        <v>69082.96000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>69901.72</v>
+        <v>69822.34</v>
       </c>
       <c r="K3" t="n">
-        <v>70400.67</v>
+        <v>70532.55</v>
       </c>
       <c r="L3" t="n">
-        <v>70899.62</v>
+        <v>71242.77</v>
       </c>
       <c r="M3" t="n">
-        <v>71706.31</v>
+        <v>71967.57000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>72513</v>
+        <v>72692.37</v>
       </c>
       <c r="O3" t="n">
-        <v>72704.22</v>
+        <v>73388.00999999999</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -784,7 +780,7 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
@@ -792,8 +788,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="n">
-        <v/>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -808,81 +806,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71067.14999999999</v>
+        <v>72404.37</v>
       </c>
       <c r="C4" t="n">
-        <v>72831.73</v>
+        <v>72618.44</v>
       </c>
       <c r="D4" t="n">
-        <v>71009.52</v>
+        <v>69788.38</v>
       </c>
       <c r="E4" t="n">
-        <v>72353.96000000001</v>
+        <v>69788.38</v>
       </c>
       <c r="F4" t="n">
-        <v>1103.9</v>
+        <v>-2565.58</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0155</v>
+        <v>-0.0355</v>
       </c>
       <c r="H4" t="n">
-        <v>1822.2</v>
+        <v>2830.05</v>
       </c>
       <c r="I4" t="n">
-        <v>69082.96000000001</v>
+        <v>69187.32000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>69822.34</v>
+        <v>70748.42999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>70532.55</v>
+        <v>71442.86</v>
       </c>
       <c r="L4" t="n">
-        <v>71242.77</v>
+        <v>72137.28999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>71967.57000000001</v>
+        <v>73265.06</v>
       </c>
       <c r="N4" t="n">
-        <v>72692.37</v>
+        <v>74392.83</v>
       </c>
       <c r="O4" t="n">
-        <v>73388.00999999999</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
+        <v>74653.92999999999</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -890,64 +890,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72404.37</v>
+        <v>69615.08</v>
       </c>
       <c r="C5" t="n">
-        <v>72618.44</v>
+        <v>70218.71000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>69788.38</v>
+        <v>68461.10000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>69788.38</v>
+        <v>69174.97</v>
       </c>
       <c r="F5" t="n">
-        <v>-2565.58</v>
+        <v>-613.41</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0355</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>2830.05</v>
+        <v>1757.61</v>
       </c>
       <c r="I5" t="n">
-        <v>69187.32000000001</v>
+        <v>66958.33</v>
       </c>
       <c r="J5" t="n">
-        <v>70748.42999999999</v>
+        <v>66250.81</v>
       </c>
       <c r="K5" t="n">
-        <v>71442.86</v>
+        <v>68373.36</v>
       </c>
       <c r="L5" t="n">
-        <v>72137.28999999999</v>
+        <v>70495.89999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>73265.06</v>
+        <v>71203.41</v>
       </c>
       <c r="N5" t="n">
-        <v>74392.83</v>
+        <v>71910.92</v>
       </c>
       <c r="O5" t="n">
-        <v>74653.92999999999</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
+        <v>75448.49000000001</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
@@ -974,50 +970,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69615.08</v>
+        <v>70114.09</v>
       </c>
       <c r="C6" t="n">
-        <v>70218.71000000001</v>
+        <v>72594.22</v>
       </c>
       <c r="D6" t="n">
-        <v>68461.10000000001</v>
+        <v>69982.67</v>
       </c>
       <c r="E6" t="n">
-        <v>69174.97</v>
+        <v>72366.34</v>
       </c>
       <c r="F6" t="n">
-        <v>-613.41</v>
+        <v>3191.38</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0461</v>
       </c>
       <c r="H6" t="n">
-        <v>1757.61</v>
+        <v>2611.55</v>
       </c>
       <c r="I6" t="n">
-        <v>66958.33</v>
+        <v>66703.49000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>66250.81</v>
+        <v>67334.89</v>
       </c>
       <c r="K6" t="n">
-        <v>68373.36</v>
+        <v>68296.16</v>
       </c>
       <c r="L6" t="n">
-        <v>70495.89999999999</v>
+        <v>69257.44</v>
       </c>
       <c r="M6" t="n">
-        <v>71203.41</v>
+        <v>70053.77</v>
       </c>
       <c r="N6" t="n">
-        <v>71910.92</v>
+        <v>70850.11</v>
       </c>
       <c r="O6" t="n">
-        <v>75448.49000000001</v>
+        <v>71976.32000000001</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1025,28 +1021,32 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W6" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W6" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1054,83 +1054,81 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70114.09</v>
+        <v>71587.71000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>72594.22</v>
+        <v>71786.28</v>
       </c>
       <c r="D7" t="n">
-        <v>69982.67</v>
+        <v>68639.84</v>
       </c>
       <c r="E7" t="n">
-        <v>72366.34</v>
+        <v>69360.88</v>
       </c>
       <c r="F7" t="n">
-        <v>3191.38</v>
+        <v>-3005.46</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0461</v>
+        <v>-0.0415</v>
       </c>
       <c r="H7" t="n">
-        <v>2611.55</v>
+        <v>3146.44</v>
       </c>
       <c r="I7" t="n">
-        <v>66703.49000000001</v>
+        <v>67371.12</v>
       </c>
       <c r="J7" t="n">
-        <v>67334.89</v>
+        <v>70293.75</v>
       </c>
       <c r="K7" t="n">
-        <v>68296.16</v>
+        <v>71060.57000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>69257.44</v>
+        <v>71827.39</v>
       </c>
       <c r="M7" t="n">
-        <v>70053.77</v>
+        <v>73672.12</v>
       </c>
       <c r="N7" t="n">
-        <v>70850.11</v>
+        <v>75516.84</v>
       </c>
       <c r="O7" t="n">
-        <v>71976.32000000001</v>
+        <v>75205.77</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1138,67 +1136,63 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>71587.71000000001</v>
+        <v>69609.88</v>
       </c>
       <c r="C8" t="n">
-        <v>71786.28</v>
+        <v>69609.88</v>
       </c>
       <c r="D8" t="n">
-        <v>68639.84</v>
+        <v>67997.57000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>69360.88</v>
+        <v>69468.11</v>
       </c>
       <c r="F8" t="n">
-        <v>-3005.46</v>
+        <v>107.23</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0415</v>
+        <v>0.0015</v>
       </c>
       <c r="H8" t="n">
-        <v>3146.44</v>
+        <v>1612.31</v>
       </c>
       <c r="I8" t="n">
-        <v>67371.12</v>
+        <v>65493.41</v>
       </c>
       <c r="J8" t="n">
-        <v>70293.75</v>
+        <v>65788.36</v>
       </c>
       <c r="K8" t="n">
-        <v>71060.57000000001</v>
+        <v>67787.66</v>
       </c>
       <c r="L8" t="n">
-        <v>71827.39</v>
+        <v>69786.97</v>
       </c>
       <c r="M8" t="n">
-        <v>73672.12</v>
+        <v>70934.10000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>75516.84</v>
+        <v>72081.23</v>
       </c>
       <c r="O8" t="n">
-        <v>75205.77</v>
+        <v>74932.72</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1215,55 +1209,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69609.88</v>
+        <v>70085.60000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>69609.88</v>
+        <v>70667</v>
       </c>
       <c r="D9" t="n">
-        <v>67997.57000000001</v>
+        <v>69302.19</v>
       </c>
       <c r="E9" t="n">
-        <v>69468.11</v>
+        <v>70062.32000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>107.23</v>
+        <v>594.21</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0086</v>
       </c>
       <c r="H9" t="n">
-        <v>1612.31</v>
+        <v>1364.81</v>
       </c>
       <c r="I9" t="n">
-        <v>65493.41</v>
+        <v>66385.25999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>65788.36</v>
+        <v>68187.99000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>67787.66</v>
+        <v>68661.95</v>
       </c>
       <c r="L9" t="n">
-        <v>69786.97</v>
+        <v>69135.92</v>
       </c>
       <c r="M9" t="n">
-        <v>70934.10000000001</v>
+        <v>70274.27</v>
       </c>
       <c r="N9" t="n">
-        <v>72081.23</v>
+        <v>71412.61</v>
       </c>
       <c r="O9" t="n">
-        <v>74932.72</v>
+        <v>71222.2</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1274,13 +1272,15 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1295,57 +1295,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70085.60000000001</v>
+        <v>70774.28</v>
       </c>
       <c r="C10" t="n">
-        <v>70667</v>
+        <v>71962.34</v>
       </c>
       <c r="D10" t="n">
-        <v>69302.19</v>
+        <v>70126.14</v>
       </c>
       <c r="E10" t="n">
-        <v>70062.32000000001</v>
+        <v>70474.96000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>594.21</v>
+        <v>412.64</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0059</v>
       </c>
       <c r="H10" t="n">
-        <v>1364.81</v>
+        <v>1836.2</v>
       </c>
       <c r="I10" t="n">
-        <v>66385.25999999999</v>
+        <v>67937.38</v>
       </c>
       <c r="J10" t="n">
-        <v>68187.99000000001</v>
+        <v>68736.37</v>
       </c>
       <c r="K10" t="n">
-        <v>68661.95</v>
+        <v>69379.91</v>
       </c>
       <c r="L10" t="n">
-        <v>69135.92</v>
+        <v>70023.46000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>70274.27</v>
+        <v>70744.73</v>
       </c>
       <c r="N10" t="n">
-        <v>71412.61</v>
+        <v>71466</v>
       </c>
       <c r="O10" t="n">
-        <v>71222.2</v>
+        <v>72031.81</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1366,8 +1366,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1386,74 +1388,74 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70774.28</v>
+        <v>70039.89</v>
       </c>
       <c r="C11" t="n">
-        <v>71962.34</v>
+        <v>70081.39</v>
       </c>
       <c r="D11" t="n">
-        <v>70126.14</v>
+        <v>68676.25999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>70474.96000000001</v>
+        <v>68733.14999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>412.64</v>
+        <v>-1741.81</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0247</v>
       </c>
       <c r="H11" t="n">
-        <v>1836.2</v>
+        <v>1405.13</v>
       </c>
       <c r="I11" t="n">
-        <v>67937.38</v>
+        <v>68289.94</v>
       </c>
       <c r="J11" t="n">
-        <v>68736.37</v>
+        <v>68354.12</v>
       </c>
       <c r="K11" t="n">
-        <v>69379.91</v>
+        <v>69556.86</v>
       </c>
       <c r="L11" t="n">
-        <v>70023.46000000001</v>
+        <v>70759.60000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>70744.73</v>
+        <v>71393.06</v>
       </c>
       <c r="N11" t="n">
-        <v>71466</v>
+        <v>72026.52</v>
       </c>
       <c r="O11" t="n">
-        <v>72031.81</v>
+        <v>73798.55</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1463,84 +1465,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>70039.89</v>
+        <v>68676.06</v>
       </c>
       <c r="C12" t="n">
-        <v>70081.39</v>
+        <v>69788.03</v>
       </c>
       <c r="D12" t="n">
-        <v>68676.25999999999</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>68733.14999999999</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1741.81</v>
+        <v>1010.92</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0147</v>
       </c>
       <c r="H12" t="n">
-        <v>1405.13</v>
+        <v>2178.54</v>
       </c>
       <c r="I12" t="n">
-        <v>68289.94</v>
+        <v>67271.12</v>
       </c>
       <c r="J12" t="n">
-        <v>68354.12</v>
+        <v>67005.17999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>69556.86</v>
+        <v>68030.58</v>
       </c>
       <c r="L12" t="n">
-        <v>70759.60000000001</v>
+        <v>69055.99000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>71393.06</v>
+        <v>69435.71000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>72026.52</v>
+        <v>69815.44</v>
       </c>
       <c r="O12" t="n">
-        <v>73798.55</v>
+        <v>71486.52</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1549,55 +1549,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68676.06</v>
+        <v>69973.34</v>
       </c>
       <c r="C13" t="n">
-        <v>69788.03</v>
+        <v>70384.59</v>
       </c>
       <c r="D13" t="n">
-        <v>67609.49000000001</v>
+        <v>68904.41</v>
       </c>
       <c r="E13" t="n">
-        <v>69744.07000000001</v>
+        <v>69737.69</v>
       </c>
       <c r="F13" t="n">
-        <v>1010.92</v>
+        <v>-6.38</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0001</v>
       </c>
       <c r="H13" t="n">
-        <v>2178.54</v>
+        <v>1480.19</v>
       </c>
       <c r="I13" t="n">
-        <v>67271.12</v>
+        <v>65430.95</v>
       </c>
       <c r="J13" t="n">
-        <v>67005.17999999999</v>
+        <v>68088.19</v>
       </c>
       <c r="K13" t="n">
-        <v>68030.58</v>
+        <v>68654.8</v>
       </c>
       <c r="L13" t="n">
-        <v>69055.99000000001</v>
+        <v>69221.42</v>
       </c>
       <c r="M13" t="n">
-        <v>69435.71000000001</v>
+        <v>70833.34</v>
       </c>
       <c r="N13" t="n">
-        <v>69815.44</v>
+        <v>72445.25999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>71486.52</v>
+        <v>71966.57000000001</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1605,25 +1609,19 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1635,70 +1633,74 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>69973.34</v>
+        <v>69460.08</v>
       </c>
       <c r="C14" t="n">
-        <v>70384.59</v>
+        <v>69957.50999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>68904.41</v>
+        <v>68003.92</v>
       </c>
       <c r="E14" t="n">
-        <v>69737.69</v>
+        <v>68256.96000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.38</v>
+        <v>-1480.73</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0212</v>
       </c>
       <c r="H14" t="n">
-        <v>1480.19</v>
+        <v>1953.59</v>
       </c>
       <c r="I14" t="n">
-        <v>65430.95</v>
+        <v>67424.22</v>
       </c>
       <c r="J14" t="n">
-        <v>68088.19</v>
+        <v>68304.09</v>
       </c>
       <c r="K14" t="n">
-        <v>68654.8</v>
+        <v>68997.59</v>
       </c>
       <c r="L14" t="n">
-        <v>69221.42</v>
+        <v>69691.09</v>
       </c>
       <c r="M14" t="n">
-        <v>70833.34</v>
+        <v>70477.78</v>
       </c>
       <c r="N14" t="n">
-        <v>72445.25999999999</v>
+        <v>71264.47</v>
       </c>
       <c r="O14" t="n">
-        <v>71966.57000000001</v>
+        <v>71864.78</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1715,71 +1717,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>69460.08</v>
+        <v>67704.16</v>
       </c>
       <c r="C15" t="n">
-        <v>69957.50999999999</v>
+        <v>68432.67999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>68003.92</v>
+        <v>66819.05</v>
       </c>
       <c r="E15" t="n">
-        <v>68256.96000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="F15" t="n">
-        <v>-1480.73</v>
+        <v>-1437.91</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="H15" t="n">
-        <v>1953.59</v>
+        <v>1613.63</v>
       </c>
       <c r="I15" t="n">
-        <v>67424.22</v>
+        <v>66050.34</v>
       </c>
       <c r="J15" t="n">
-        <v>68304.09</v>
+        <v>65941.5</v>
       </c>
       <c r="K15" t="n">
-        <v>68997.59</v>
+        <v>67280.17</v>
       </c>
       <c r="L15" t="n">
-        <v>69691.09</v>
+        <v>68618.84</v>
       </c>
       <c r="M15" t="n">
-        <v>70477.78</v>
+        <v>69233.75</v>
       </c>
       <c r="N15" t="n">
-        <v>71264.47</v>
+        <v>69848.67</v>
       </c>
       <c r="O15" t="n">
-        <v>71864.78</v>
+        <v>71911.09</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
@@ -1806,50 +1802,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>67704.16</v>
+        <v>67046.37</v>
       </c>
       <c r="C16" t="n">
-        <v>68432.67999999999</v>
+        <v>68447.89</v>
       </c>
       <c r="D16" t="n">
-        <v>66819.05</v>
+        <v>67008.89</v>
       </c>
       <c r="E16" t="n">
-        <v>66819.05</v>
+        <v>67743.85000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-1437.91</v>
+        <v>924.8</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0211</v>
+        <v>0.0138</v>
       </c>
       <c r="H16" t="n">
-        <v>1613.63</v>
+        <v>1439</v>
       </c>
       <c r="I16" t="n">
-        <v>66050.34</v>
+        <v>65205.41</v>
       </c>
       <c r="J16" t="n">
-        <v>65941.5</v>
+        <v>64802.01</v>
       </c>
       <c r="K16" t="n">
-        <v>67280.17</v>
+        <v>66012.23</v>
       </c>
       <c r="L16" t="n">
-        <v>68618.84</v>
+        <v>67222.46000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>69233.75</v>
+        <v>67625.86</v>
       </c>
       <c r="N16" t="n">
-        <v>69848.67</v>
+        <v>68029.27</v>
       </c>
       <c r="O16" t="n">
-        <v>71911.09</v>
+        <v>70046.31</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1857,21 +1853,23 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1881,55 +1879,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>67046.37</v>
+        <v>68526.72</v>
       </c>
       <c r="C17" t="n">
-        <v>68447.89</v>
+        <v>69374.86</v>
       </c>
       <c r="D17" t="n">
-        <v>67008.89</v>
+        <v>68271.91</v>
       </c>
       <c r="E17" t="n">
-        <v>67743.85000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F17" t="n">
-        <v>924.8</v>
+        <v>813.88</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.012</v>
       </c>
       <c r="H17" t="n">
-        <v>1439</v>
+        <v>1102.95</v>
       </c>
       <c r="I17" t="n">
-        <v>65205.41</v>
+        <v>65569.89</v>
       </c>
       <c r="J17" t="n">
-        <v>64802.01</v>
+        <v>66312.58</v>
       </c>
       <c r="K17" t="n">
-        <v>66012.23</v>
+        <v>67024.35000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>67222.46000000001</v>
+        <v>67736.12</v>
       </c>
       <c r="M17" t="n">
-        <v>67625.86</v>
+        <v>68463.35000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>68029.27</v>
+        <v>69190.58</v>
       </c>
       <c r="O17" t="n">
-        <v>70046.31</v>
+        <v>69886.89</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1972,74 +1974,76 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>68526.72</v>
+        <v>68410.63</v>
       </c>
       <c r="C18" t="n">
-        <v>69374.86</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>68271.91</v>
+        <v>66653.11</v>
       </c>
       <c r="E18" t="n">
-        <v>68557.73</v>
+        <v>67242.73</v>
       </c>
       <c r="F18" t="n">
-        <v>813.88</v>
+        <v>-1315</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0192</v>
       </c>
       <c r="H18" t="n">
-        <v>1102.95</v>
+        <v>2425.1</v>
       </c>
       <c r="I18" t="n">
-        <v>65569.89</v>
+        <v>67168.95</v>
       </c>
       <c r="J18" t="n">
-        <v>66312.58</v>
+        <v>67321.95</v>
       </c>
       <c r="K18" t="n">
-        <v>67024.35000000001</v>
+        <v>68006.25</v>
       </c>
       <c r="L18" t="n">
-        <v>67736.12</v>
+        <v>68690.55</v>
       </c>
       <c r="M18" t="n">
-        <v>68463.35000000001</v>
+        <v>69109.2</v>
       </c>
       <c r="N18" t="n">
-        <v>69190.58</v>
+        <v>69527.85000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>69886.89</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+        <v>70477.81</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2049,78 +2053,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>68410.63</v>
+        <v>67002.94</v>
       </c>
       <c r="C19" t="n">
-        <v>69078.21000000001</v>
+        <v>67800.17999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>66653.11</v>
+        <v>66268.60000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>67242.73</v>
+        <v>67743.5</v>
       </c>
       <c r="F19" t="n">
-        <v>-1315</v>
+        <v>500.77</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0074</v>
       </c>
       <c r="H19" t="n">
-        <v>2425.1</v>
+        <v>1531.58</v>
       </c>
       <c r="I19" t="n">
-        <v>67168.95</v>
+        <v>64228.01</v>
       </c>
       <c r="J19" t="n">
-        <v>67321.95</v>
+        <v>64506.16</v>
       </c>
       <c r="K19" t="n">
-        <v>68006.25</v>
+        <v>66030.17999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>68690.55</v>
+        <v>67554.19</v>
       </c>
       <c r="M19" t="n">
-        <v>69109.2</v>
+        <v>68455.28</v>
       </c>
       <c r="N19" t="n">
-        <v>69527.85000000001</v>
+        <v>69356.36</v>
       </c>
       <c r="O19" t="n">
-        <v>70477.81</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>71503.31</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2137,55 +2131,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>67002.94</v>
+        <v>67989.74000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>67800.17999999999</v>
+        <v>68798.24000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>66268.60000000001</v>
+        <v>67833.17</v>
       </c>
       <c r="E20" t="n">
-        <v>67743.5</v>
+        <v>68751.50999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>500.77</v>
+        <v>1008.01</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0149</v>
       </c>
       <c r="H20" t="n">
-        <v>1531.58</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>64228.01</v>
+        <v>64737.02</v>
       </c>
       <c r="J20" t="n">
-        <v>64506.16</v>
+        <v>66566.48</v>
       </c>
       <c r="K20" t="n">
-        <v>66030.17999999999</v>
+        <v>66977.71000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>67554.19</v>
+        <v>67388.95</v>
       </c>
       <c r="M20" t="n">
-        <v>68455.28</v>
+        <v>68509.28999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>69356.36</v>
+        <v>69629.63</v>
       </c>
       <c r="O20" t="n">
-        <v>71503.31</v>
+        <v>69331.75999999999</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2198,11 +2196,13 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2217,77 +2217,81 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>67989.74000000001</v>
+        <v>67900.42999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>68798.24000000001</v>
+        <v>68069.82000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>67833.17</v>
+        <v>66499.49000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>68751.50999999999</v>
+        <v>66835.53999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>1008.01</v>
+        <v>-1915.97</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0279</v>
       </c>
       <c r="H21" t="n">
-        <v>965.0700000000001</v>
+        <v>1570.33</v>
       </c>
       <c r="I21" t="n">
-        <v>64737.02</v>
+        <v>66868.10000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>66566.48</v>
+        <v>68004.34</v>
       </c>
       <c r="K21" t="n">
-        <v>66977.71000000001</v>
+        <v>68268.97</v>
       </c>
       <c r="L21" t="n">
-        <v>67388.95</v>
+        <v>68533.61</v>
       </c>
       <c r="M21" t="n">
-        <v>68509.28999999999</v>
+        <v>69234.03999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>69629.63</v>
+        <v>69934.48</v>
       </c>
       <c r="O21" t="n">
-        <v>69331.75999999999</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+        <v>69763.31</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2299,59 +2303,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>67900.42999999999</v>
+        <v>66339.85000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>68069.82000000001</v>
+        <v>66441.77</v>
       </c>
       <c r="D22" t="n">
-        <v>66499.49000000001</v>
+        <v>62704.6</v>
       </c>
       <c r="E22" t="n">
-        <v>66835.53999999999</v>
+        <v>64141.12</v>
       </c>
       <c r="F22" t="n">
-        <v>-1915.97</v>
+        <v>-2694.42</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0403</v>
       </c>
       <c r="H22" t="n">
-        <v>1570.33</v>
+        <v>3737.17</v>
       </c>
       <c r="I22" t="n">
-        <v>66868.10000000001</v>
+        <v>64929.16</v>
       </c>
       <c r="J22" t="n">
-        <v>68004.34</v>
+        <v>65040.65</v>
       </c>
       <c r="K22" t="n">
-        <v>68268.97</v>
+        <v>66050.38</v>
       </c>
       <c r="L22" t="n">
-        <v>68533.61</v>
+        <v>67060.10000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>69234.03999999999</v>
+        <v>67620.7</v>
       </c>
       <c r="N22" t="n">
-        <v>69934.48</v>
+        <v>68181.31</v>
       </c>
       <c r="O22" t="n">
-        <v>69763.31</v>
+        <v>69640.14999999999</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
@@ -2392,74 +2392,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>66339.85000000001</v>
+        <v>64544.05</v>
       </c>
       <c r="C23" t="n">
-        <v>66441.77</v>
+        <v>66232.19</v>
       </c>
       <c r="D23" t="n">
-        <v>62704.6</v>
+        <v>64203.47</v>
       </c>
       <c r="E23" t="n">
-        <v>64141.12</v>
+        <v>66232.19</v>
       </c>
       <c r="F23" t="n">
-        <v>-2694.42</v>
+        <v>2091.07</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0326</v>
       </c>
       <c r="H23" t="n">
-        <v>3737.17</v>
+        <v>2028.72</v>
       </c>
       <c r="I23" t="n">
-        <v>64929.16</v>
+        <v>58967.43</v>
       </c>
       <c r="J23" t="n">
-        <v>65040.65</v>
+        <v>60187.92</v>
       </c>
       <c r="K23" t="n">
-        <v>66050.38</v>
+        <v>62272.54</v>
       </c>
       <c r="L23" t="n">
-        <v>67060.10000000001</v>
+        <v>64357.15</v>
       </c>
       <c r="M23" t="n">
-        <v>67620.7</v>
+        <v>66009.71000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>68181.31</v>
+        <v>67662.25999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>69640.14999999999</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>70178.95</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2471,55 +2467,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>64544.05</v>
+        <v>66449.27</v>
       </c>
       <c r="C24" t="n">
-        <v>66232.19</v>
+        <v>67592.2</v>
       </c>
       <c r="D24" t="n">
-        <v>64203.47</v>
+        <v>65955.60000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>66232.19</v>
+        <v>66115.60000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>2091.07</v>
+        <v>-116.59</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0326</v>
+        <v>-0.0018</v>
       </c>
       <c r="H24" t="n">
-        <v>2028.72</v>
+        <v>1636.6</v>
       </c>
       <c r="I24" t="n">
-        <v>58967.43</v>
+        <v>62174.75</v>
       </c>
       <c r="J24" t="n">
-        <v>60187.92</v>
+        <v>64710.65</v>
       </c>
       <c r="K24" t="n">
-        <v>62272.54</v>
+        <v>65217.83</v>
       </c>
       <c r="L24" t="n">
-        <v>64357.15</v>
+        <v>65725.00999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>66009.71000000001</v>
+        <v>67246.55</v>
       </c>
       <c r="N24" t="n">
-        <v>67662.25999999999</v>
+        <v>68768.09</v>
       </c>
       <c r="O24" t="n">
-        <v>70178.95</v>
+        <v>68260.91</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2532,12 +2532,12 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U24" s="8" t="n">
@@ -2560,50 +2560,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>66449.27</v>
+        <v>66421.00999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>67592.2</v>
+        <v>67022.37</v>
       </c>
       <c r="D25" t="n">
-        <v>65955.60000000001</v>
+        <v>66208.66</v>
       </c>
       <c r="E25" t="n">
-        <v>66115.60000000001</v>
+        <v>66422.60000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-116.59</v>
+        <v>307</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0046</v>
       </c>
       <c r="H25" t="n">
-        <v>1636.6</v>
+        <v>813.71</v>
       </c>
       <c r="I25" t="n">
-        <v>62174.75</v>
+        <v>64319</v>
       </c>
       <c r="J25" t="n">
-        <v>64710.65</v>
+        <v>64149.85</v>
       </c>
       <c r="K25" t="n">
-        <v>65217.83</v>
+        <v>65297.3</v>
       </c>
       <c r="L25" t="n">
-        <v>65725.00999999999</v>
+        <v>66444.75</v>
       </c>
       <c r="M25" t="n">
-        <v>67246.55</v>
+        <v>66933.89999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>68768.09</v>
+        <v>67423.05</v>
       </c>
       <c r="O25" t="n">
-        <v>68260.91</v>
+        <v>69228.8</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2614,9 +2614,9 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2644,69 +2644,73 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>66421.00999999999</v>
+        <v>65584.25</v>
       </c>
       <c r="C26" t="n">
-        <v>67022.37</v>
+        <v>65720.81</v>
       </c>
       <c r="D26" t="n">
-        <v>66208.66</v>
+        <v>64201.03</v>
       </c>
       <c r="E26" t="n">
-        <v>66422.60000000001</v>
+        <v>64611.15</v>
       </c>
       <c r="F26" t="n">
-        <v>307</v>
+        <v>-1811.45</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0273</v>
       </c>
       <c r="H26" t="n">
-        <v>813.71</v>
+        <v>1519.78</v>
       </c>
       <c r="I26" t="n">
-        <v>64319</v>
+        <v>65394.95</v>
       </c>
       <c r="J26" t="n">
-        <v>64149.85</v>
+        <v>65512.44</v>
       </c>
       <c r="K26" t="n">
-        <v>65297.3</v>
+        <v>66015.75</v>
       </c>
       <c r="L26" t="n">
-        <v>66444.75</v>
+        <v>66519.06</v>
       </c>
       <c r="M26" t="n">
-        <v>66933.89999999999</v>
+        <v>66829.46000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>67423.05</v>
+        <v>67139.86</v>
       </c>
       <c r="O26" t="n">
-        <v>69228.8</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+        <v>67836.08</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2719,78 +2723,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>65584.25</v>
+        <v>65164.98</v>
       </c>
       <c r="C27" t="n">
-        <v>65720.81</v>
+        <v>65220.69</v>
       </c>
       <c r="D27" t="n">
-        <v>64201.03</v>
+        <v>64123.4</v>
       </c>
       <c r="E27" t="n">
-        <v>64611.15</v>
+        <v>64931.19</v>
       </c>
       <c r="F27" t="n">
-        <v>-1811.45</v>
+        <v>320.04</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.005</v>
       </c>
       <c r="H27" t="n">
-        <v>1519.78</v>
+        <v>1097.29</v>
       </c>
       <c r="I27" t="n">
-        <v>65394.95</v>
+        <v>62681.25</v>
       </c>
       <c r="J27" t="n">
-        <v>65512.44</v>
+        <v>62916.48</v>
       </c>
       <c r="K27" t="n">
-        <v>66015.75</v>
+        <v>63851.26</v>
       </c>
       <c r="L27" t="n">
-        <v>66519.06</v>
+        <v>64786.04</v>
       </c>
       <c r="M27" t="n">
-        <v>66829.46000000001</v>
+        <v>65371.04</v>
       </c>
       <c r="N27" t="n">
-        <v>67139.86</v>
+        <v>65956.03999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>67836.08</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>67240.59</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2807,68 +2801,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>65164.98</v>
+        <v>64539.92</v>
       </c>
       <c r="C28" t="n">
-        <v>65220.69</v>
+        <v>64573.18</v>
       </c>
       <c r="D28" t="n">
-        <v>64123.4</v>
+        <v>61923.6</v>
       </c>
       <c r="E28" t="n">
-        <v>64931.19</v>
+        <v>62364.92</v>
       </c>
       <c r="F28" t="n">
-        <v>320.04</v>
+        <v>-2566.27</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0395</v>
       </c>
       <c r="H28" t="n">
-        <v>1097.29</v>
+        <v>2649.58</v>
       </c>
       <c r="I28" t="n">
-        <v>62681.25</v>
+        <v>63026.11</v>
       </c>
       <c r="J28" t="n">
-        <v>62916.48</v>
+        <v>63963.47</v>
       </c>
       <c r="K28" t="n">
-        <v>63851.26</v>
+        <v>64382.54</v>
       </c>
       <c r="L28" t="n">
-        <v>64786.04</v>
+        <v>64801.62</v>
       </c>
       <c r="M28" t="n">
-        <v>65371.04</v>
+        <v>65479.84</v>
       </c>
       <c r="N28" t="n">
-        <v>65956.03999999999</v>
+        <v>66158.06</v>
       </c>
       <c r="O28" t="n">
-        <v>67240.59</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>66317.98</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2885,73 +2889,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>64539.92</v>
+        <v>62734.68</v>
       </c>
       <c r="C29" t="n">
-        <v>64573.18</v>
+        <v>63138.04</v>
       </c>
       <c r="D29" t="n">
-        <v>61923.6</v>
+        <v>60448.9</v>
       </c>
       <c r="E29" t="n">
-        <v>62364.92</v>
+        <v>61434.19</v>
       </c>
       <c r="F29" t="n">
-        <v>-2566.27</v>
+        <v>-930.73</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0149</v>
       </c>
       <c r="H29" t="n">
-        <v>2649.58</v>
+        <v>2689.14</v>
       </c>
       <c r="I29" t="n">
-        <v>63026.11</v>
+        <v>59274.02</v>
       </c>
       <c r="J29" t="n">
-        <v>63963.47</v>
+        <v>59273.61</v>
       </c>
       <c r="K29" t="n">
-        <v>64382.54</v>
+        <v>61040.13</v>
       </c>
       <c r="L29" t="n">
-        <v>64801.62</v>
+        <v>62806.66</v>
       </c>
       <c r="M29" t="n">
-        <v>65479.84</v>
+        <v>63689.71</v>
       </c>
       <c r="N29" t="n">
-        <v>66158.06</v>
+        <v>64572.77</v>
       </c>
       <c r="O29" t="n">
-        <v>66317.98</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
+        <v>67222.75999999999</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
@@ -2978,50 +2974,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>62734.68</v>
+        <v>61258.34</v>
       </c>
       <c r="C30" t="n">
-        <v>63138.04</v>
+        <v>62924.84</v>
       </c>
       <c r="D30" t="n">
-        <v>60448.9</v>
+        <v>61049.7</v>
       </c>
       <c r="E30" t="n">
-        <v>61434.19</v>
+        <v>61867.43</v>
       </c>
       <c r="F30" t="n">
-        <v>-930.73</v>
+        <v>433.24</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0071</v>
       </c>
       <c r="H30" t="n">
-        <v>2689.14</v>
+        <v>1875.14</v>
       </c>
       <c r="I30" t="n">
-        <v>59274.02</v>
+        <v>57759.76</v>
       </c>
       <c r="J30" t="n">
-        <v>59273.61</v>
+        <v>58565.41</v>
       </c>
       <c r="K30" t="n">
-        <v>61040.13</v>
+        <v>60089.62</v>
       </c>
       <c r="L30" t="n">
-        <v>62806.66</v>
+        <v>61613.83</v>
       </c>
       <c r="M30" t="n">
-        <v>63689.71</v>
+        <v>62778.76</v>
       </c>
       <c r="N30" t="n">
-        <v>64572.77</v>
+        <v>63943.69</v>
       </c>
       <c r="O30" t="n">
-        <v>67222.75999999999</v>
+        <v>65827.17999999999</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3029,18 +3025,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3053,55 +3049,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>61258.34</v>
+        <v>61957.1</v>
       </c>
       <c r="C31" t="n">
-        <v>62924.84</v>
+        <v>65364.73</v>
       </c>
       <c r="D31" t="n">
-        <v>61049.7</v>
+        <v>61948.23</v>
       </c>
       <c r="E31" t="n">
-        <v>61867.43</v>
+        <v>64362.02</v>
       </c>
       <c r="F31" t="n">
-        <v>433.24</v>
+        <v>2494.59</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0403</v>
       </c>
       <c r="H31" t="n">
-        <v>1875.14</v>
+        <v>3416.5</v>
       </c>
       <c r="I31" t="n">
-        <v>57759.76</v>
+        <v>59174.56</v>
       </c>
       <c r="J31" t="n">
-        <v>58565.41</v>
+        <v>59932.37</v>
       </c>
       <c r="K31" t="n">
-        <v>60089.62</v>
+        <v>60929.86</v>
       </c>
       <c r="L31" t="n">
-        <v>61613.83</v>
+        <v>61927.35</v>
       </c>
       <c r="M31" t="n">
-        <v>62778.76</v>
+        <v>62805</v>
       </c>
       <c r="N31" t="n">
-        <v>63943.69</v>
+        <v>63682.65</v>
       </c>
       <c r="O31" t="n">
-        <v>65827.17999999999</v>
+        <v>64799.98</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -3122,70 +3122,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>61957.1</v>
+        <v>63834.95</v>
       </c>
       <c r="C32" t="n">
-        <v>65364.73</v>
+        <v>63905.12</v>
       </c>
       <c r="D32" t="n">
-        <v>61948.23</v>
+        <v>62703.47</v>
       </c>
       <c r="E32" t="n">
-        <v>64362.02</v>
+        <v>63754.9</v>
       </c>
       <c r="F32" t="n">
-        <v>2494.59</v>
+        <v>-607.12</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0403</v>
+        <v>-0.0094</v>
       </c>
       <c r="H32" t="n">
-        <v>3416.5</v>
+        <v>1201.65</v>
       </c>
       <c r="I32" t="n">
-        <v>59174.56</v>
+        <v>58531.73</v>
       </c>
       <c r="J32" t="n">
-        <v>59932.37</v>
+        <v>61298.29</v>
       </c>
       <c r="K32" t="n">
-        <v>60929.86</v>
+        <v>62653.77</v>
       </c>
       <c r="L32" t="n">
-        <v>61927.35</v>
+        <v>64009.25</v>
       </c>
       <c r="M32" t="n">
-        <v>62805</v>
+        <v>66070.27</v>
       </c>
       <c r="N32" t="n">
-        <v>63682.65</v>
+        <v>68131.28999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>64799.98</v>
+        <v>68781.23</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3196,80 +3196,78 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63834.95</v>
+        <v>63995.28</v>
       </c>
       <c r="C33" t="n">
-        <v>63905.12</v>
+        <v>64240.5</v>
       </c>
       <c r="D33" t="n">
-        <v>62703.47</v>
+        <v>62864.43</v>
       </c>
       <c r="E33" t="n">
-        <v>63754.9</v>
+        <v>63957.53</v>
       </c>
       <c r="F33" t="n">
-        <v>-607.12</v>
+        <v>202.63</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0032</v>
       </c>
       <c r="H33" t="n">
-        <v>1201.65</v>
+        <v>1376.07</v>
       </c>
       <c r="I33" t="n">
-        <v>58531.73</v>
+        <v>61501.82</v>
       </c>
       <c r="J33" t="n">
-        <v>61298.29</v>
+        <v>62778.55</v>
       </c>
       <c r="K33" t="n">
-        <v>62653.77</v>
+        <v>63154.07</v>
       </c>
       <c r="L33" t="n">
-        <v>64009.25</v>
+        <v>63529.6</v>
       </c>
       <c r="M33" t="n">
-        <v>66070.27</v>
+        <v>64355.72</v>
       </c>
       <c r="N33" t="n">
-        <v>68131.28999999999</v>
+        <v>65181.85</v>
       </c>
       <c r="O33" t="n">
-        <v>68781.23</v>
+        <v>65106.77</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3277,16 +3275,20 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3299,59 +3301,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>63995.28</v>
+        <v>64565.27</v>
       </c>
       <c r="C34" t="n">
-        <v>64240.5</v>
+        <v>66302.52</v>
       </c>
       <c r="D34" t="n">
-        <v>62864.43</v>
+        <v>64555.52</v>
       </c>
       <c r="E34" t="n">
-        <v>63957.53</v>
+        <v>66300.44</v>
       </c>
       <c r="F34" t="n">
-        <v>202.63</v>
+        <v>2342.91</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0366</v>
       </c>
       <c r="H34" t="n">
-        <v>1376.07</v>
+        <v>1747</v>
       </c>
       <c r="I34" t="n">
-        <v>61501.82</v>
+        <v>61488.36</v>
       </c>
       <c r="J34" t="n">
-        <v>62778.55</v>
+        <v>62783.99</v>
       </c>
       <c r="K34" t="n">
-        <v>63154.07</v>
+        <v>63269.5</v>
       </c>
       <c r="L34" t="n">
-        <v>63529.6</v>
+        <v>63755</v>
       </c>
       <c r="M34" t="n">
-        <v>64355.72</v>
+        <v>64645.57</v>
       </c>
       <c r="N34" t="n">
-        <v>65181.85</v>
+        <v>65536.13</v>
       </c>
       <c r="O34" t="n">
-        <v>65106.77</v>
+        <v>65616.57000000001</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3359,10 +3357,8 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
@@ -3371,14 +3367,18 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
@@ -3390,134 +3390,136 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>64565.27</v>
+        <v>65896</v>
       </c>
       <c r="C35" t="n">
-        <v>66302.52</v>
+        <v>65983.13</v>
       </c>
       <c r="D35" t="n">
-        <v>64555.52</v>
+        <v>64942.07</v>
       </c>
       <c r="E35" t="n">
-        <v>66300.44</v>
+        <v>65683.25999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>2342.91</v>
+        <v>-617.1799999999999</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0366</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>1747</v>
+        <v>1041.06</v>
       </c>
       <c r="I35" t="n">
-        <v>61488.36</v>
+        <v>62808.52</v>
       </c>
       <c r="J35" t="n">
-        <v>62783.99</v>
+        <v>64989.14</v>
       </c>
       <c r="K35" t="n">
-        <v>63269.5</v>
+        <v>65426.94</v>
       </c>
       <c r="L35" t="n">
-        <v>63755</v>
+        <v>65864.73</v>
       </c>
       <c r="M35" t="n">
-        <v>64645.57</v>
+        <v>67173.94</v>
       </c>
       <c r="N35" t="n">
-        <v>65536.13</v>
+        <v>68483.14999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>65616.57000000001</v>
+        <v>68049.53</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>65896</v>
+        <v>65746.13</v>
       </c>
       <c r="C36" t="n">
-        <v>65983.13</v>
+        <v>65990.72</v>
       </c>
       <c r="D36" t="n">
-        <v>64942.07</v>
+        <v>64651.49</v>
       </c>
       <c r="E36" t="n">
-        <v>65683.25999999999</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-617.1799999999999</v>
+        <v>-76.55</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="H36" t="n">
-        <v>1041.06</v>
+        <v>1339.23</v>
       </c>
       <c r="I36" t="n">
-        <v>62808.52</v>
+        <v>63901.01</v>
       </c>
       <c r="J36" t="n">
-        <v>64989.14</v>
+        <v>64752.52</v>
       </c>
       <c r="K36" t="n">
-        <v>65426.94</v>
+        <v>65162.73</v>
       </c>
       <c r="L36" t="n">
-        <v>65864.73</v>
+        <v>65572.92999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>67173.94</v>
+        <v>66203.78999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>68483.14999999999</v>
+        <v>66834.64999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>68049.53</v>
+        <v>67024.2</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3532,9 +3534,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3560,74 +3562,74 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>65746.13</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>65990.72</v>
+        <v>67006.84</v>
       </c>
       <c r="D37" t="n">
-        <v>64651.49</v>
+        <v>65848.58</v>
       </c>
       <c r="E37" t="n">
-        <v>65606.71000000001</v>
+        <v>66970.22</v>
       </c>
       <c r="F37" t="n">
-        <v>-76.55</v>
+        <v>1363.51</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0208</v>
       </c>
       <c r="H37" t="n">
-        <v>1339.23</v>
+        <v>1158.27</v>
       </c>
       <c r="I37" t="n">
-        <v>63901.01</v>
+        <v>63312.26</v>
       </c>
       <c r="J37" t="n">
-        <v>64752.52</v>
+        <v>64410.28</v>
       </c>
       <c r="K37" t="n">
-        <v>65162.73</v>
+        <v>64937.1</v>
       </c>
       <c r="L37" t="n">
-        <v>65572.92999999999</v>
+        <v>65463.91</v>
       </c>
       <c r="M37" t="n">
-        <v>66203.78999999999</v>
+        <v>66276.33</v>
       </c>
       <c r="N37" t="n">
-        <v>66834.64999999999</v>
+        <v>67088.75</v>
       </c>
       <c r="O37" t="n">
-        <v>67024.2</v>
+        <v>67329.95</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3637,59 +3639,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>65905.10000000001</v>
+        <v>66994.05</v>
       </c>
       <c r="C38" t="n">
-        <v>67006.84</v>
+        <v>67569.36</v>
       </c>
       <c r="D38" t="n">
-        <v>65848.58</v>
+        <v>66735.75999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>66970.22</v>
+        <v>67524.06</v>
       </c>
       <c r="F38" t="n">
-        <v>1363.51</v>
+        <v>553.84</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="H38" t="n">
-        <v>1158.27</v>
+        <v>833.6</v>
       </c>
       <c r="I38" t="n">
-        <v>63312.26</v>
+        <v>64690.31</v>
       </c>
       <c r="J38" t="n">
-        <v>64410.28</v>
+        <v>66083.21000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>64937.1</v>
+        <v>66391.09</v>
       </c>
       <c r="L38" t="n">
-        <v>65463.91</v>
+        <v>66698.96000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>66276.33</v>
+        <v>67549.35000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>67088.75</v>
+        <v>68399.74000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>67329.95</v>
+        <v>68165.11</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3707,13 +3705,11 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3728,50 +3724,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>66994.05</v>
+        <v>68033.17</v>
       </c>
       <c r="C39" t="n">
-        <v>67569.36</v>
+        <v>68799.71000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>66735.75999999999</v>
+        <v>68006.17</v>
       </c>
       <c r="E39" t="n">
-        <v>67524.06</v>
+        <v>68308.59</v>
       </c>
       <c r="F39" t="n">
-        <v>553.84</v>
+        <v>784.53</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0116</v>
       </c>
       <c r="H39" t="n">
-        <v>833.6</v>
+        <v>793.54</v>
       </c>
       <c r="I39" t="n">
-        <v>64690.31</v>
+        <v>65902.16</v>
       </c>
       <c r="J39" t="n">
-        <v>66083.21000000001</v>
+        <v>66876.21000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>66391.09</v>
+        <v>67107.25999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>66698.96000000001</v>
+        <v>67338.31</v>
       </c>
       <c r="M39" t="n">
-        <v>67549.35000000001</v>
+        <v>67940.86</v>
       </c>
       <c r="N39" t="n">
-        <v>68399.74000000001</v>
+        <v>68543.42</v>
       </c>
       <c r="O39" t="n">
-        <v>68165.11</v>
+        <v>68402.96000000001</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3789,14 +3785,18 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
@@ -3808,50 +3808,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>68033.17</v>
+        <v>68811.17</v>
       </c>
       <c r="C40" t="n">
-        <v>68799.71000000001</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>68006.17</v>
+        <v>68471.14999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>68308.59</v>
+        <v>68713.8</v>
       </c>
       <c r="F40" t="n">
-        <v>784.53</v>
+        <v>405.2</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0059</v>
       </c>
       <c r="H40" t="n">
-        <v>793.54</v>
+        <v>1137.09</v>
       </c>
       <c r="I40" t="n">
-        <v>65902.16</v>
+        <v>67212.63</v>
       </c>
       <c r="J40" t="n">
-        <v>66876.21000000001</v>
+        <v>67467.88</v>
       </c>
       <c r="K40" t="n">
-        <v>67107.25999999999</v>
+        <v>67911.82000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>67338.31</v>
+        <v>68355.77</v>
       </c>
       <c r="M40" t="n">
-        <v>67940.86</v>
+        <v>68705.36</v>
       </c>
       <c r="N40" t="n">
-        <v>68543.42</v>
+        <v>69054.96000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>68402.96000000001</v>
+        <v>69593.25</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U40" s="8" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="V40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W40" s="9" t="inlineStr">
@@ -3892,50 +3892,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>68811.17</v>
+        <v>68882.06</v>
       </c>
       <c r="C41" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>68471.14999999999</v>
+        <v>68492.03999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>68713.8</v>
+        <v>69220.25</v>
       </c>
       <c r="F41" t="n">
-        <v>405.2</v>
+        <v>506.45</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="H41" t="n">
-        <v>1137.09</v>
+        <v>733.53</v>
       </c>
       <c r="I41" t="n">
-        <v>67212.63</v>
+        <v>67334.05</v>
       </c>
       <c r="J41" t="n">
-        <v>67467.88</v>
+        <v>67413.75</v>
       </c>
       <c r="K41" t="n">
-        <v>67911.82000000001</v>
+        <v>68145.25</v>
       </c>
       <c r="L41" t="n">
-        <v>68355.77</v>
+        <v>68876.75</v>
       </c>
       <c r="M41" t="n">
-        <v>68705.36</v>
+        <v>69282.34</v>
       </c>
       <c r="N41" t="n">
-        <v>69054.96000000001</v>
+        <v>69687.94</v>
       </c>
       <c r="O41" t="n">
-        <v>69593.25</v>
+        <v>70745.34</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3956,163 +3956,163 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>68882.06</v>
+        <v>68847.35000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>69225.57000000001</v>
+        <v>69093.2</v>
       </c>
       <c r="D42" t="n">
-        <v>68492.03999999999</v>
+        <v>67368.96000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>69220.25</v>
+        <v>67460.73</v>
       </c>
       <c r="F42" t="n">
-        <v>506.45</v>
+        <v>-1759.52</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0254</v>
       </c>
       <c r="H42" t="n">
-        <v>733.53</v>
+        <v>1724.24</v>
       </c>
       <c r="I42" t="n">
-        <v>67334.05</v>
+        <v>67758.50999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>67413.75</v>
+        <v>68667.44</v>
       </c>
       <c r="K42" t="n">
-        <v>68145.25</v>
+        <v>68853.48</v>
       </c>
       <c r="L42" t="n">
-        <v>68876.75</v>
+        <v>69039.53</v>
       </c>
       <c r="M42" t="n">
-        <v>69282.34</v>
+        <v>69587.02</v>
       </c>
       <c r="N42" t="n">
-        <v>69687.94</v>
+        <v>70134.5</v>
       </c>
       <c r="O42" t="n">
-        <v>70745.34</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+        <v>69959.10000000001</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>68847.35000000001</v>
+        <v>66812.27</v>
       </c>
       <c r="C43" t="n">
-        <v>69093.2</v>
+        <v>66833.50999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>67368.96000000001</v>
+        <v>65133.98</v>
       </c>
       <c r="E43" t="n">
-        <v>67460.73</v>
+        <v>65326.42</v>
       </c>
       <c r="F43" t="n">
-        <v>-1759.52</v>
+        <v>-2134.3</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="H43" t="n">
-        <v>1724.24</v>
+        <v>1699.53</v>
       </c>
       <c r="I43" t="n">
-        <v>67758.50999999999</v>
+        <v>65644.72</v>
       </c>
       <c r="J43" t="n">
-        <v>68667.44</v>
+        <v>65351.31</v>
       </c>
       <c r="K43" t="n">
-        <v>68853.48</v>
+        <v>66598.61</v>
       </c>
       <c r="L43" t="n">
-        <v>69039.53</v>
+        <v>67845.89999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>69587.02</v>
+        <v>68322.85000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>70134.5</v>
+        <v>68799.78999999999</v>
       </c>
       <c r="O43" t="n">
-        <v>69959.10000000001</v>
+        <v>70817.45</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -4144,74 +4144,70 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>66812.27</v>
+        <v>65732.78999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>66833.50999999999</v>
+        <v>66325.32000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>65133.98</v>
+        <v>65652.25</v>
       </c>
       <c r="E44" t="n">
-        <v>65326.42</v>
+        <v>66216.78999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>-2134.3</v>
+        <v>890.37</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H44" t="n">
-        <v>1699.53</v>
+        <v>673.0700000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>65644.72</v>
+        <v>63434.45</v>
       </c>
       <c r="J44" t="n">
-        <v>65351.31</v>
+        <v>63298.23</v>
       </c>
       <c r="K44" t="n">
-        <v>66598.61</v>
+        <v>64476.66</v>
       </c>
       <c r="L44" t="n">
-        <v>67845.89999999999</v>
+        <v>65655.08</v>
       </c>
       <c r="M44" t="n">
-        <v>68322.85000000001</v>
+        <v>66176.19</v>
       </c>
       <c r="N44" t="n">
-        <v>68799.78999999999</v>
+        <v>66697.28999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>70817.45</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
+        <v>68533.03999999999</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4223,74 +4219,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>65732.78999999999</v>
+        <v>65427.69</v>
       </c>
       <c r="C45" t="n">
-        <v>66325.32000000001</v>
+        <v>66125.88</v>
       </c>
       <c r="D45" t="n">
-        <v>65652.25</v>
+        <v>65260.22</v>
       </c>
       <c r="E45" t="n">
-        <v>66216.78999999999</v>
+        <v>66016.36</v>
       </c>
       <c r="F45" t="n">
-        <v>890.37</v>
+        <v>-200.43</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.003</v>
       </c>
       <c r="H45" t="n">
-        <v>673.0700000000001</v>
+        <v>865.66</v>
       </c>
       <c r="I45" t="n">
-        <v>63434.45</v>
+        <v>64979.18</v>
       </c>
       <c r="J45" t="n">
-        <v>63298.23</v>
+        <v>65657.72</v>
       </c>
       <c r="K45" t="n">
-        <v>64476.66</v>
+        <v>65880.25</v>
       </c>
       <c r="L45" t="n">
-        <v>65655.08</v>
+        <v>66102.78999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>66176.19</v>
+        <v>66553.32000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>66697.28999999999</v>
+        <v>67003.86</v>
       </c>
       <c r="O45" t="n">
-        <v>68533.03999999999</v>
+        <v>66998.39</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4303,76 +4305,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>65427.69</v>
+        <v>65978.95</v>
       </c>
       <c r="C46" t="n">
-        <v>66125.88</v>
+        <v>66257.73</v>
       </c>
       <c r="D46" t="n">
-        <v>65260.22</v>
+        <v>65470.95</v>
       </c>
       <c r="E46" t="n">
-        <v>66016.36</v>
+        <v>65528.09</v>
       </c>
       <c r="F46" t="n">
-        <v>-200.43</v>
+        <v>-488.27</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0074</v>
       </c>
       <c r="H46" t="n">
-        <v>865.66</v>
+        <v>786.78</v>
       </c>
       <c r="I46" t="n">
-        <v>64979.18</v>
+        <v>64394.55</v>
       </c>
       <c r="J46" t="n">
-        <v>65657.72</v>
+        <v>65312.35</v>
       </c>
       <c r="K46" t="n">
-        <v>65880.25</v>
+        <v>65583.53</v>
       </c>
       <c r="L46" t="n">
-        <v>66102.78999999999</v>
+        <v>65854.71000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>66553.32000000001</v>
+        <v>66449.19</v>
       </c>
       <c r="N46" t="n">
-        <v>67003.86</v>
+        <v>67043.67999999999</v>
       </c>
       <c r="O46" t="n">
-        <v>66998.39</v>
+        <v>66991.55</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q46" s="6" t="n">
+        <v/>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4389,75 +4385,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65978.95</v>
+        <v>65195.26</v>
       </c>
       <c r="C47" t="n">
-        <v>66257.73</v>
+        <v>65904.24000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>65470.95</v>
+        <v>64609.47</v>
       </c>
       <c r="E47" t="n">
-        <v>65528.09</v>
+        <v>65856.42999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>-488.27</v>
+        <v>328.34</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.005</v>
       </c>
       <c r="H47" t="n">
-        <v>786.78</v>
+        <v>1294.77</v>
       </c>
       <c r="I47" t="n">
-        <v>64394.55</v>
+        <v>64684.17</v>
       </c>
       <c r="J47" t="n">
-        <v>65312.35</v>
+        <v>64573.19</v>
       </c>
       <c r="K47" t="n">
-        <v>65583.53</v>
+        <v>65134.7</v>
       </c>
       <c r="L47" t="n">
-        <v>65854.71000000001</v>
+        <v>65696.21000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>66449.19</v>
+        <v>65921.48</v>
       </c>
       <c r="N47" t="n">
-        <v>67043.67999999999</v>
+        <v>66146.74000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>66991.55</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
+        <v>67044.5</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4471,70 +4475,66 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65195.26</v>
+        <v>65604.49000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>65904.24000000001</v>
+        <v>66442.34</v>
       </c>
       <c r="D48" t="n">
-        <v>64609.47</v>
+        <v>65390.55</v>
       </c>
       <c r="E48" t="n">
-        <v>65856.42999999999</v>
+        <v>66262.16</v>
       </c>
       <c r="F48" t="n">
-        <v>328.34</v>
+        <v>405.73</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0062</v>
       </c>
       <c r="H48" t="n">
-        <v>1294.77</v>
+        <v>1051.79</v>
       </c>
       <c r="I48" t="n">
-        <v>64684.17</v>
+        <v>63314.7</v>
       </c>
       <c r="J48" t="n">
-        <v>64573.19</v>
+        <v>64861.44</v>
       </c>
       <c r="K48" t="n">
-        <v>65134.7</v>
+        <v>65209.04</v>
       </c>
       <c r="L48" t="n">
-        <v>65696.21000000001</v>
+        <v>65556.64</v>
       </c>
       <c r="M48" t="n">
-        <v>65921.48</v>
+        <v>66503.82000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>66146.74000000001</v>
+        <v>67450.99000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>67044.5</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67199.02</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
       </c>
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
@@ -4559,57 +4559,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65604.49000000001</v>
+        <v>66775.78</v>
       </c>
       <c r="C49" t="n">
-        <v>66442.34</v>
+        <v>66954.69</v>
       </c>
       <c r="D49" t="n">
-        <v>65390.55</v>
+        <v>65782.59</v>
       </c>
       <c r="E49" t="n">
-        <v>66262.16</v>
+        <v>66131.98</v>
       </c>
       <c r="F49" t="n">
-        <v>405.73</v>
+        <v>-130.18</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.002</v>
       </c>
       <c r="H49" t="n">
-        <v>1051.79</v>
+        <v>1172.09</v>
       </c>
       <c r="I49" t="n">
-        <v>63314.7</v>
+        <v>64338.76</v>
       </c>
       <c r="J49" t="n">
-        <v>64861.44</v>
+        <v>65383.22</v>
       </c>
       <c r="K49" t="n">
-        <v>65209.04</v>
+        <v>65736.25999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>65556.64</v>
+        <v>66089.3</v>
       </c>
       <c r="M49" t="n">
-        <v>66503.82000000001</v>
+        <v>66788.05</v>
       </c>
       <c r="N49" t="n">
-        <v>67450.99000000001</v>
+        <v>67486.8</v>
       </c>
       <c r="O49" t="n">
-        <v>67199.02</v>
+        <v>67494.14</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4622,12 +4622,12 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U49" s="8" t="n">
@@ -4643,57 +4643,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>66775.78</v>
+        <v>66104.49000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>66954.69</v>
+        <v>66842.82000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>65782.59</v>
+        <v>66012.2</v>
       </c>
       <c r="E50" t="n">
-        <v>66131.98</v>
+        <v>66405.56</v>
       </c>
       <c r="F50" t="n">
-        <v>-130.18</v>
+        <v>273.59</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0041</v>
       </c>
       <c r="H50" t="n">
-        <v>1172.09</v>
+        <v>830.62</v>
       </c>
       <c r="I50" t="n">
-        <v>64338.76</v>
+        <v>64610.5</v>
       </c>
       <c r="J50" t="n">
-        <v>65383.22</v>
+        <v>64841.55</v>
       </c>
       <c r="K50" t="n">
-        <v>65736.25999999999</v>
+        <v>65545.92999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>66089.3</v>
+        <v>66250.31</v>
       </c>
       <c r="M50" t="n">
-        <v>66788.05</v>
+        <v>66718.02</v>
       </c>
       <c r="N50" t="n">
-        <v>67486.8</v>
+        <v>67185.74000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>67494.14</v>
+        <v>68126.78</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4734,69 +4734,73 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>66104.49000000001</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C51" t="n">
-        <v>66842.82000000001</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>66012.2</v>
+        <v>64832.1</v>
       </c>
       <c r="E51" t="n">
-        <v>66405.56</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>273.59</v>
+        <v>-93.63</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0014</v>
       </c>
       <c r="H51" t="n">
-        <v>830.62</v>
+        <v>1479.83</v>
       </c>
       <c r="I51" t="n">
-        <v>64610.5</v>
+        <v>65181.59</v>
       </c>
       <c r="J51" t="n">
-        <v>64841.55</v>
+        <v>65563.97</v>
       </c>
       <c r="K51" t="n">
-        <v>65545.92999999999</v>
+        <v>65990.25</v>
       </c>
       <c r="L51" t="n">
-        <v>66250.31</v>
+        <v>66416.53999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>66718.02</v>
+        <v>66820.87</v>
       </c>
       <c r="N51" t="n">
-        <v>67185.74000000001</v>
+        <v>67225.21000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>68126.78</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67673.44</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4809,78 +4813,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>65668.50999999999</v>
+        <v>65885.47</v>
       </c>
       <c r="C52" t="n">
-        <v>66311.92999999999</v>
+        <v>66525.7</v>
       </c>
       <c r="D52" t="n">
-        <v>64832.1</v>
+        <v>65576.61</v>
       </c>
       <c r="E52" t="n">
-        <v>66311.92999999999</v>
+        <v>66215.34</v>
       </c>
       <c r="F52" t="n">
-        <v>-93.63</v>
+        <v>-96.59</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0015</v>
       </c>
       <c r="H52" t="n">
-        <v>1479.83</v>
+        <v>949.09</v>
       </c>
       <c r="I52" t="n">
-        <v>65181.59</v>
+        <v>63352.27</v>
       </c>
       <c r="J52" t="n">
-        <v>65563.97</v>
+        <v>65202.06</v>
       </c>
       <c r="K52" t="n">
-        <v>65990.25</v>
+        <v>65572.02</v>
       </c>
       <c r="L52" t="n">
-        <v>66416.53999999999</v>
+        <v>65941.97</v>
       </c>
       <c r="M52" t="n">
-        <v>66820.87</v>
+        <v>67051.84</v>
       </c>
       <c r="N52" t="n">
-        <v>67225.21000000001</v>
+        <v>68161.71000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>67673.44</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>67791.75999999999</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4897,68 +4891,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65885.47</v>
+        <v>65195.43</v>
       </c>
       <c r="C53" t="n">
-        <v>66525.7</v>
+        <v>65195.43</v>
       </c>
       <c r="D53" t="n">
-        <v>65576.61</v>
+        <v>64215.47</v>
       </c>
       <c r="E53" t="n">
-        <v>66215.34</v>
+        <v>64325.64</v>
       </c>
       <c r="F53" t="n">
-        <v>-96.59</v>
+        <v>-1889.7</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0285</v>
       </c>
       <c r="H53" t="n">
-        <v>949.09</v>
+        <v>979.96</v>
       </c>
       <c r="I53" t="n">
-        <v>63352.27</v>
+        <v>64627.52</v>
       </c>
       <c r="J53" t="n">
-        <v>65202.06</v>
+        <v>65348.34</v>
       </c>
       <c r="K53" t="n">
-        <v>65572.02</v>
+        <v>65740.8</v>
       </c>
       <c r="L53" t="n">
-        <v>65941.97</v>
+        <v>66133.25</v>
       </c>
       <c r="M53" t="n">
-        <v>67051.84</v>
+        <v>66689.89</v>
       </c>
       <c r="N53" t="n">
-        <v>68161.71000000001</v>
+        <v>67246.53</v>
       </c>
       <c r="O53" t="n">
-        <v>67791.75999999999</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>67474.8</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4975,69 +4979,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="C54" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="D54" t="n">
-        <v>64215.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E54" t="n">
-        <v>64325.64</v>
+        <v>64214.48</v>
       </c>
       <c r="F54" t="n">
-        <v>-1889.7</v>
+        <v>-111.16</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0017</v>
       </c>
       <c r="H54" t="n">
-        <v>979.96</v>
+        <v>952.01</v>
       </c>
       <c r="I54" t="n">
-        <v>64627.52</v>
+        <v>63235.51</v>
       </c>
       <c r="J54" t="n">
-        <v>65348.34</v>
+        <v>63155.78</v>
       </c>
       <c r="K54" t="n">
-        <v>65740.8</v>
+        <v>63835.66</v>
       </c>
       <c r="L54" t="n">
-        <v>66133.25</v>
+        <v>64515.54</v>
       </c>
       <c r="M54" t="n">
-        <v>66689.89</v>
+        <v>64815.62</v>
       </c>
       <c r="N54" t="n">
-        <v>67246.53</v>
+        <v>65115.7</v>
       </c>
       <c r="O54" t="n">
-        <v>67474.8</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66175.39</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
@@ -5046,7 +5042,7 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5068,50 +5064,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>64724.81</v>
+        <v>64498.94</v>
       </c>
       <c r="C55" t="n">
-        <v>64724.81</v>
+        <v>65182.45</v>
       </c>
       <c r="D55" t="n">
-        <v>63772.8</v>
+        <v>64228.47</v>
       </c>
       <c r="E55" t="n">
-        <v>64214.48</v>
+        <v>65020.94</v>
       </c>
       <c r="F55" t="n">
-        <v>-111.16</v>
+        <v>806.46</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="H55" t="n">
-        <v>952.01</v>
+        <v>953.98</v>
       </c>
       <c r="I55" t="n">
-        <v>63235.51</v>
+        <v>62820.79</v>
       </c>
       <c r="J55" t="n">
-        <v>63155.78</v>
+        <v>63245.31</v>
       </c>
       <c r="K55" t="n">
-        <v>63835.66</v>
+        <v>63738.48</v>
       </c>
       <c r="L55" t="n">
-        <v>64515.54</v>
+        <v>64231.64</v>
       </c>
       <c r="M55" t="n">
-        <v>64815.62</v>
+        <v>64690.48</v>
       </c>
       <c r="N55" t="n">
-        <v>65115.7</v>
+        <v>65149.33</v>
       </c>
       <c r="O55" t="n">
-        <v>66175.39</v>
+        <v>65676.82000000001</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5119,21 +5115,23 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5143,55 +5141,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>64498.94</v>
+        <v>65600.42</v>
       </c>
       <c r="C56" t="n">
-        <v>65182.45</v>
+        <v>66668.71000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>64228.47</v>
+        <v>65600.42</v>
       </c>
       <c r="E56" t="n">
-        <v>65020.94</v>
+        <v>66399.84</v>
       </c>
       <c r="F56" t="n">
-        <v>806.46</v>
+        <v>1378.9</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="H56" t="n">
-        <v>953.98</v>
+        <v>1068.29</v>
       </c>
       <c r="I56" t="n">
-        <v>62820.79</v>
+        <v>63274.49</v>
       </c>
       <c r="J56" t="n">
-        <v>63245.31</v>
+        <v>64224.7</v>
       </c>
       <c r="K56" t="n">
-        <v>63738.48</v>
+        <v>64543.95</v>
       </c>
       <c r="L56" t="n">
-        <v>64231.64</v>
+        <v>64863.2</v>
       </c>
       <c r="M56" t="n">
-        <v>64690.48</v>
+        <v>65497.93</v>
       </c>
       <c r="N56" t="n">
-        <v>65149.33</v>
+        <v>66132.66</v>
       </c>
       <c r="O56" t="n">
-        <v>65676.82000000001</v>
+        <v>66136.42999999999</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5214,171 +5216,167 @@
       </c>
       <c r="U56" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>65600.42</v>
+        <v>65843.69</v>
       </c>
       <c r="C57" t="n">
-        <v>66668.71000000001</v>
+        <v>66791.84</v>
       </c>
       <c r="D57" t="n">
-        <v>65600.42</v>
+        <v>65269.33</v>
       </c>
       <c r="E57" t="n">
-        <v>66399.84</v>
+        <v>65269.33</v>
       </c>
       <c r="F57" t="n">
-        <v>1378.9</v>
+        <v>-1130.52</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.017</v>
       </c>
       <c r="H57" t="n">
-        <v>1068.29</v>
+        <v>1522.52</v>
       </c>
       <c r="I57" t="n">
-        <v>63274.49</v>
+        <v>64532.13</v>
       </c>
       <c r="J57" t="n">
-        <v>64224.7</v>
+        <v>65464.19</v>
       </c>
       <c r="K57" t="n">
-        <v>64543.95</v>
+        <v>65865.7</v>
       </c>
       <c r="L57" t="n">
-        <v>64863.2</v>
+        <v>66267.21000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>65497.93</v>
+        <v>66933.99000000001</v>
       </c>
       <c r="N57" t="n">
-        <v>66132.66</v>
+        <v>67600.77</v>
       </c>
       <c r="O57" t="n">
-        <v>66136.42999999999</v>
+        <v>67737</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
+      <c r="Q57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>65843.69</v>
+        <v>65087.22</v>
       </c>
       <c r="C58" t="n">
-        <v>66791.84</v>
+        <v>65794.03</v>
       </c>
       <c r="D58" t="n">
-        <v>65269.33</v>
+        <v>65017.68</v>
       </c>
       <c r="E58" t="n">
-        <v>65269.33</v>
+        <v>65142.78</v>
       </c>
       <c r="F58" t="n">
-        <v>-1130.52</v>
+        <v>-126.55</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0019</v>
       </c>
       <c r="H58" t="n">
-        <v>1522.52</v>
+        <v>776.35</v>
       </c>
       <c r="I58" t="n">
-        <v>64532.13</v>
+        <v>63746.81</v>
       </c>
       <c r="J58" t="n">
-        <v>65464.19</v>
+        <v>63366.18</v>
       </c>
       <c r="K58" t="n">
-        <v>65865.7</v>
+        <v>64508.07</v>
       </c>
       <c r="L58" t="n">
-        <v>66267.21000000001</v>
+        <v>65649.96000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>66933.99000000001</v>
+        <v>66030.59</v>
       </c>
       <c r="N58" t="n">
-        <v>67600.77</v>
+        <v>66411.21000000001</v>
       </c>
       <c r="O58" t="n">
-        <v>67737</v>
+        <v>68314.36</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5395,68 +5393,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>65087.22</v>
+        <v>64768.53</v>
       </c>
       <c r="C59" t="n">
-        <v>65794.03</v>
+        <v>65270.95</v>
       </c>
       <c r="D59" t="n">
-        <v>65017.68</v>
+        <v>64186.68</v>
       </c>
       <c r="E59" t="n">
-        <v>65142.78</v>
+        <v>65270.95</v>
       </c>
       <c r="F59" t="n">
-        <v>-126.55</v>
+        <v>128.17</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="H59" t="n">
-        <v>776.35</v>
+        <v>1084.27</v>
       </c>
       <c r="I59" t="n">
-        <v>63746.81</v>
+        <v>64241.33</v>
       </c>
       <c r="J59" t="n">
-        <v>63366.18</v>
+        <v>64234.89</v>
       </c>
       <c r="K59" t="n">
-        <v>64508.07</v>
+        <v>64754.61</v>
       </c>
       <c r="L59" t="n">
-        <v>65649.96000000001</v>
+        <v>65274.32</v>
       </c>
       <c r="M59" t="n">
-        <v>66030.59</v>
+        <v>65530.96</v>
       </c>
       <c r="N59" t="n">
-        <v>66411.21000000001</v>
+        <v>65787.60000000001</v>
       </c>
       <c r="O59" t="n">
-        <v>68314.36</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+        <v>66570.38</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
@@ -5477,64 +5477,66 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>64768.53</v>
+        <v>64276.82</v>
       </c>
       <c r="C60" t="n">
-        <v>65270.95</v>
+        <v>64312.02</v>
       </c>
       <c r="D60" t="n">
-        <v>64186.68</v>
+        <v>63208.63</v>
       </c>
       <c r="E60" t="n">
-        <v>65270.95</v>
+        <v>64011.34</v>
       </c>
       <c r="F60" t="n">
-        <v>128.17</v>
+        <v>-1259.61</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H60" t="n">
-        <v>1084.27</v>
+        <v>1103.39</v>
       </c>
       <c r="I60" t="n">
-        <v>64241.33</v>
+        <v>63102.41</v>
       </c>
       <c r="J60" t="n">
-        <v>64234.89</v>
+        <v>64457.75</v>
       </c>
       <c r="K60" t="n">
-        <v>64754.61</v>
+        <v>64728.81</v>
       </c>
       <c r="L60" t="n">
-        <v>65274.32</v>
+        <v>64999.88</v>
       </c>
       <c r="M60" t="n">
-        <v>65530.96</v>
+        <v>65813.08</v>
       </c>
       <c r="N60" t="n">
-        <v>65787.60000000001</v>
+        <v>66626.28999999999</v>
       </c>
       <c r="O60" t="n">
-        <v>66570.38</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66355.22</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
       </c>
       <c r="Q60" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
@@ -5544,7 +5546,7 @@
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5561,71 +5563,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>64276.82</v>
+        <v>63659.53</v>
       </c>
       <c r="C61" t="n">
-        <v>64312.02</v>
+        <v>63691.53</v>
       </c>
       <c r="D61" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E61" t="n">
-        <v>64011.34</v>
+        <v>63492.99</v>
       </c>
       <c r="F61" t="n">
-        <v>-1259.61</v>
+        <v>-518.35</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0081</v>
       </c>
       <c r="H61" t="n">
-        <v>1103.39</v>
+        <v>965.35</v>
       </c>
       <c r="I61" t="n">
-        <v>63102.41</v>
+        <v>62105.24</v>
       </c>
       <c r="J61" t="n">
-        <v>64457.75</v>
+        <v>63033.46</v>
       </c>
       <c r="K61" t="n">
-        <v>64728.81</v>
+        <v>63459.64</v>
       </c>
       <c r="L61" t="n">
-        <v>64999.88</v>
+        <v>63885.83</v>
       </c>
       <c r="M61" t="n">
-        <v>65813.08</v>
+        <v>64563.04</v>
       </c>
       <c r="N61" t="n">
-        <v>66626.28999999999</v>
+        <v>65240.24</v>
       </c>
       <c r="O61" t="n">
-        <v>66355.22</v>
+        <v>65415.41</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S61" s="10" t="inlineStr">
@@ -5652,67 +5650,65 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>63659.53</v>
+        <v>63672.13</v>
       </c>
       <c r="C62" t="n">
-        <v>63691.53</v>
+        <v>63672.13</v>
       </c>
       <c r="D62" t="n">
-        <v>62726.18</v>
+        <v>63268.72</v>
       </c>
       <c r="E62" t="n">
-        <v>63492.99</v>
+        <v/>
       </c>
       <c r="F62" t="n">
-        <v>-518.35</v>
+        <v/>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0081</v>
+        <v/>
       </c>
       <c r="H62" t="n">
-        <v>965.35</v>
+        <v>403.41</v>
       </c>
       <c r="I62" t="n">
-        <v>62105.24</v>
+        <v>61760.83</v>
       </c>
       <c r="J62" t="n">
-        <v>63033.46</v>
+        <v>62669.7</v>
       </c>
       <c r="K62" t="n">
-        <v>63459.64</v>
+        <v>63010.31</v>
       </c>
       <c r="L62" t="n">
-        <v>63885.83</v>
+        <v>63350.92</v>
       </c>
       <c r="M62" t="n">
-        <v>64563.04</v>
+        <v>63975.66</v>
       </c>
       <c r="N62" t="n">
-        <v>65240.24</v>
+        <v>64600.41</v>
       </c>
       <c r="O62" t="n">
-        <v>65415.41</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
+        <v>64656.88</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5729,120 +5725,38 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>63190.37</v>
-      </c>
-      <c r="C63" t="n">
-        <v>64101</v>
-      </c>
-      <c r="D63" t="n">
-        <v>63067.18</v>
-      </c>
-      <c r="E63" t="n">
-        <v/>
-      </c>
-      <c r="F63" t="n">
-        <v/>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H63" t="n">
-        <v>1033.82</v>
-      </c>
-      <c r="I63" t="n">
-        <v>61760.83</v>
-      </c>
-      <c r="J63" t="n">
-        <v>62669.7</v>
-      </c>
-      <c r="K63" t="n">
-        <v>63010.31</v>
-      </c>
-      <c r="L63" t="n">
-        <v>63350.92</v>
-      </c>
-      <c r="M63" t="n">
-        <v>63975.66</v>
-      </c>
-      <c r="N63" t="n">
-        <v>64600.41</v>
-      </c>
-      <c r="O63" t="n">
-        <v>64656.88</v>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="14" t="n">
-        <v>62033.36</v>
-      </c>
-      <c r="J64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="14" t="n">
-        <v>65134.82</v>
+      <c r="I63" s="14" t="n">
+        <v>62865.31</v>
+      </c>
+      <c r="J63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O63" s="14" t="n">
+        <v>64075.54</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5654,25 +5651,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>63672.13</v>
+        <v>63190.37</v>
       </c>
       <c r="C62" t="n">
-        <v>63672.13</v>
+        <v>64101</v>
       </c>
       <c r="D62" t="n">
-        <v>63268.72</v>
+        <v>63067.18</v>
       </c>
       <c r="E62" t="n">
-        <v/>
+        <v>63484.1</v>
       </c>
       <c r="F62" t="n">
-        <v/>
+        <v>-8.890000000000001</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v/>
+        <v>-0.0001</v>
       </c>
       <c r="H62" t="n">
-        <v>403.41</v>
+        <v>1033.82</v>
       </c>
       <c r="I62" t="n">
         <v>61760.83</v>
@@ -5695,10 +5692,8 @@
       <c r="O62" t="n">
         <v>64656.88</v>
       </c>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P62" s="6" t="n">
+        <v/>
       </c>
       <c r="Q62" s="6" t="n">
         <v/>
@@ -5706,13 +5701,15 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5727,36 +5724,36 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="14" t="n">
-        <v>62865.31</v>
-      </c>
-      <c r="J63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O63" s="14" t="n">
-        <v>64075.54</v>
+      <c r="I63" s="13" t="n">
+        <v>62033.36</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>62400.29</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>62967.19</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>63534.1</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>64001.01</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>64467.93</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>65134.82</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5729,31 +5729,115 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>63672.13</v>
+      </c>
+      <c r="C63" t="n">
+        <v>63923</v>
+      </c>
+      <c r="D63" t="n">
+        <v>63209.92</v>
+      </c>
+      <c r="E63" t="n">
+        <v>63923</v>
+      </c>
+      <c r="F63" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="H63" t="n">
+        <v>713.08</v>
+      </c>
+      <c r="I63" t="n">
+        <v>62033.36</v>
+      </c>
+      <c r="J63" t="n">
+        <v>62400.29</v>
+      </c>
+      <c r="K63" t="n">
+        <v>62967.19</v>
+      </c>
+      <c r="L63" t="n">
+        <v>63534.1</v>
+      </c>
+      <c r="M63" t="n">
+        <v>64001.01</v>
+      </c>
+      <c r="N63" t="n">
+        <v>64467.93</v>
+      </c>
+      <c r="O63" t="n">
+        <v>65134.82</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
-        <v>62033.36</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>62400.29</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>62967.19</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>63534.1</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>64001.01</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>64467.93</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>65134.82</v>
+      <c r="I64" s="13" t="n">
+        <v>62496.84</v>
+      </c>
+      <c r="J64" s="13" t="n">
+        <v>63388.19</v>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>63566.46</v>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>63744.73</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>64279.54</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>64814.35</v>
+      </c>
+      <c r="O64" s="13" t="n">
+        <v>64636.08</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5744,13 +5747,13 @@
         <v>63209.92</v>
       </c>
       <c r="E63" t="n">
-        <v>63923</v>
+        <v/>
       </c>
       <c r="F63" t="n">
-        <v>438.9</v>
+        <v/>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0069</v>
+        <v/>
       </c>
       <c r="H63" t="n">
         <v>713.08</v>
@@ -5776,8 +5779,10 @@
       <c r="O63" t="n">
         <v>65134.82</v>
       </c>
-      <c r="P63" s="6" t="n">
-        <v/>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q63" s="6" t="n">
         <v/>
@@ -5785,15 +5790,13 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S63" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
       </c>
       <c r="U63" s="8" t="n">
         <v/>
@@ -5808,35 +5811,35 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="13" t="n">
+      <c r="I64" s="14" t="n">
         <v>62496.84</v>
       </c>
-      <c r="J64" s="13" t="n">
-        <v>63388.19</v>
-      </c>
-      <c r="K64" s="13" t="n">
-        <v>63566.46</v>
-      </c>
-      <c r="L64" s="13" t="n">
-        <v>63744.73</v>
-      </c>
-      <c r="M64" s="13" t="n">
-        <v>64279.54</v>
-      </c>
-      <c r="N64" s="13" t="n">
-        <v>64814.35</v>
-      </c>
-      <c r="O64" s="13" t="n">
+      <c r="J64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O64" s="14" t="n">
         <v>64636.08</v>
       </c>
     </row>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,50 +644,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71551.03</v>
+        <v>71067.14999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>71952.99000000001</v>
+        <v>72831.73</v>
       </c>
       <c r="D2" t="n">
-        <v>70517.98</v>
+        <v>71009.52</v>
       </c>
       <c r="E2" t="n">
-        <v>71250.06</v>
+        <v>72353.96000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>196.57</v>
+        <v>1103.9</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0155</v>
       </c>
       <c r="H2" t="n">
-        <v>1435.02</v>
+        <v>1822.2</v>
       </c>
       <c r="I2" t="n">
-        <v>68787.3</v>
+        <v>69082.96000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>69901.72</v>
+        <v>69822.34</v>
       </c>
       <c r="K2" t="n">
-        <v>70400.67</v>
+        <v>70532.55</v>
       </c>
       <c r="L2" t="n">
-        <v>70899.62</v>
+        <v>71242.77</v>
       </c>
       <c r="M2" t="n">
-        <v>71706.31</v>
+        <v>71967.57000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>72513</v>
+        <v>72692.37</v>
       </c>
       <c r="O2" t="n">
-        <v>72704.22</v>
+        <v>73388.00999999999</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,7 +700,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -708,8 +708,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -724,81 +726,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71067.14999999999</v>
+        <v>72404.37</v>
       </c>
       <c r="C3" t="n">
-        <v>72831.73</v>
+        <v>72618.44</v>
       </c>
       <c r="D3" t="n">
-        <v>71009.52</v>
+        <v>69788.38</v>
       </c>
       <c r="E3" t="n">
-        <v>72353.96000000001</v>
+        <v>69788.38</v>
       </c>
       <c r="F3" t="n">
-        <v>1103.9</v>
+        <v>-2565.58</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0155</v>
+        <v>-0.0355</v>
       </c>
       <c r="H3" t="n">
-        <v>1822.2</v>
+        <v>2830.05</v>
       </c>
       <c r="I3" t="n">
-        <v>69082.96000000001</v>
+        <v>69187.32000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>69822.34</v>
+        <v>70748.42999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>70532.55</v>
+        <v>71442.86</v>
       </c>
       <c r="L3" t="n">
-        <v>71242.77</v>
+        <v>72137.28999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>71967.57000000001</v>
+        <v>73265.06</v>
       </c>
       <c r="N3" t="n">
-        <v>72692.37</v>
+        <v>74392.83</v>
       </c>
       <c r="O3" t="n">
-        <v>73388.00999999999</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
+        <v>74653.92999999999</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -806,64 +810,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72404.37</v>
+        <v>69615.08</v>
       </c>
       <c r="C4" t="n">
-        <v>72618.44</v>
+        <v>70218.71000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>69788.38</v>
+        <v>68461.10000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>69788.38</v>
+        <v>69174.97</v>
       </c>
       <c r="F4" t="n">
-        <v>-2565.58</v>
+        <v>-613.41</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0355</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>2830.05</v>
+        <v>1757.61</v>
       </c>
       <c r="I4" t="n">
-        <v>69187.32000000001</v>
+        <v>66958.33</v>
       </c>
       <c r="J4" t="n">
-        <v>70748.42999999999</v>
+        <v>66250.81</v>
       </c>
       <c r="K4" t="n">
-        <v>71442.86</v>
+        <v>68373.36</v>
       </c>
       <c r="L4" t="n">
-        <v>72137.28999999999</v>
+        <v>70495.89999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>73265.06</v>
+        <v>71203.41</v>
       </c>
       <c r="N4" t="n">
-        <v>74392.83</v>
+        <v>71910.92</v>
       </c>
       <c r="O4" t="n">
-        <v>74653.92999999999</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+        <v>75448.49000000001</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
@@ -890,50 +890,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69615.08</v>
+        <v>70114.09</v>
       </c>
       <c r="C5" t="n">
-        <v>70218.71000000001</v>
+        <v>72594.22</v>
       </c>
       <c r="D5" t="n">
-        <v>68461.10000000001</v>
+        <v>69982.67</v>
       </c>
       <c r="E5" t="n">
-        <v>69174.97</v>
+        <v>72366.34</v>
       </c>
       <c r="F5" t="n">
-        <v>-613.41</v>
+        <v>3191.38</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0461</v>
       </c>
       <c r="H5" t="n">
-        <v>1757.61</v>
+        <v>2611.55</v>
       </c>
       <c r="I5" t="n">
-        <v>66958.33</v>
+        <v>66703.49000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>66250.81</v>
+        <v>67334.89</v>
       </c>
       <c r="K5" t="n">
-        <v>68373.36</v>
+        <v>68296.16</v>
       </c>
       <c r="L5" t="n">
-        <v>70495.89999999999</v>
+        <v>69257.44</v>
       </c>
       <c r="M5" t="n">
-        <v>71203.41</v>
+        <v>70053.77</v>
       </c>
       <c r="N5" t="n">
-        <v>71910.92</v>
+        <v>70850.11</v>
       </c>
       <c r="O5" t="n">
-        <v>75448.49000000001</v>
+        <v>71976.32000000001</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -941,28 +941,32 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W5" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W5" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -970,83 +974,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70114.09</v>
+        <v>71587.71000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>72594.22</v>
+        <v>71786.28</v>
       </c>
       <c r="D6" t="n">
-        <v>69982.67</v>
+        <v>68639.84</v>
       </c>
       <c r="E6" t="n">
-        <v>72366.34</v>
+        <v>69360.88</v>
       </c>
       <c r="F6" t="n">
-        <v>3191.38</v>
+        <v>-3005.46</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0461</v>
+        <v>-0.0415</v>
       </c>
       <c r="H6" t="n">
-        <v>2611.55</v>
+        <v>3146.44</v>
       </c>
       <c r="I6" t="n">
-        <v>66703.49000000001</v>
+        <v>67371.12</v>
       </c>
       <c r="J6" t="n">
-        <v>67334.89</v>
+        <v>70293.75</v>
       </c>
       <c r="K6" t="n">
-        <v>68296.16</v>
+        <v>71060.57000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>69257.44</v>
+        <v>71827.39</v>
       </c>
       <c r="M6" t="n">
-        <v>70053.77</v>
+        <v>73672.12</v>
       </c>
       <c r="N6" t="n">
-        <v>70850.11</v>
+        <v>75516.84</v>
       </c>
       <c r="O6" t="n">
-        <v>71976.32000000001</v>
+        <v>75205.77</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1054,67 +1056,63 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>71587.71000000001</v>
+        <v>69609.88</v>
       </c>
       <c r="C7" t="n">
-        <v>71786.28</v>
+        <v>69609.88</v>
       </c>
       <c r="D7" t="n">
-        <v>68639.84</v>
+        <v>67997.57000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>69360.88</v>
+        <v>69468.11</v>
       </c>
       <c r="F7" t="n">
-        <v>-3005.46</v>
+        <v>107.23</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0415</v>
+        <v>0.0015</v>
       </c>
       <c r="H7" t="n">
-        <v>3146.44</v>
+        <v>1612.31</v>
       </c>
       <c r="I7" t="n">
-        <v>67371.12</v>
+        <v>65493.41</v>
       </c>
       <c r="J7" t="n">
-        <v>70293.75</v>
+        <v>65788.36</v>
       </c>
       <c r="K7" t="n">
-        <v>71060.57000000001</v>
+        <v>67787.66</v>
       </c>
       <c r="L7" t="n">
-        <v>71827.39</v>
+        <v>69786.97</v>
       </c>
       <c r="M7" t="n">
-        <v>73672.12</v>
+        <v>70934.10000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>75516.84</v>
+        <v>72081.23</v>
       </c>
       <c r="O7" t="n">
-        <v>75205.77</v>
+        <v>74932.72</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1131,55 +1129,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69609.88</v>
+        <v>70085.60000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>69609.88</v>
+        <v>70667</v>
       </c>
       <c r="D8" t="n">
-        <v>67997.57000000001</v>
+        <v>69302.19</v>
       </c>
       <c r="E8" t="n">
-        <v>69468.11</v>
+        <v>70062.32000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>107.23</v>
+        <v>594.21</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0086</v>
       </c>
       <c r="H8" t="n">
-        <v>1612.31</v>
+        <v>1364.81</v>
       </c>
       <c r="I8" t="n">
-        <v>65493.41</v>
+        <v>66385.25999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>65788.36</v>
+        <v>68187.99000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>67787.66</v>
+        <v>68661.95</v>
       </c>
       <c r="L8" t="n">
-        <v>69786.97</v>
+        <v>69135.92</v>
       </c>
       <c r="M8" t="n">
-        <v>70934.10000000001</v>
+        <v>70274.27</v>
       </c>
       <c r="N8" t="n">
-        <v>72081.23</v>
+        <v>71412.61</v>
       </c>
       <c r="O8" t="n">
-        <v>74932.72</v>
+        <v>71222.2</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1190,13 +1192,15 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1211,57 +1215,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70085.60000000001</v>
+        <v>70774.28</v>
       </c>
       <c r="C9" t="n">
-        <v>70667</v>
+        <v>71962.34</v>
       </c>
       <c r="D9" t="n">
-        <v>69302.19</v>
+        <v>70126.14</v>
       </c>
       <c r="E9" t="n">
-        <v>70062.32000000001</v>
+        <v>70474.96000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>594.21</v>
+        <v>412.64</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0059</v>
       </c>
       <c r="H9" t="n">
-        <v>1364.81</v>
+        <v>1836.2</v>
       </c>
       <c r="I9" t="n">
-        <v>66385.25999999999</v>
+        <v>67937.38</v>
       </c>
       <c r="J9" t="n">
-        <v>68187.99000000001</v>
+        <v>68736.37</v>
       </c>
       <c r="K9" t="n">
-        <v>68661.95</v>
+        <v>69379.91</v>
       </c>
       <c r="L9" t="n">
-        <v>69135.92</v>
+        <v>70023.46000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>70274.27</v>
+        <v>70744.73</v>
       </c>
       <c r="N9" t="n">
-        <v>71412.61</v>
+        <v>71466</v>
       </c>
       <c r="O9" t="n">
-        <v>71222.2</v>
+        <v>72031.81</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1282,8 +1286,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U9" s="8" t="n">
-        <v/>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1302,74 +1308,74 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70774.28</v>
+        <v>70039.89</v>
       </c>
       <c r="C10" t="n">
-        <v>71962.34</v>
+        <v>70081.39</v>
       </c>
       <c r="D10" t="n">
-        <v>70126.14</v>
+        <v>68676.25999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>70474.96000000001</v>
+        <v>68733.14999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>412.64</v>
+        <v>-1741.81</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0247</v>
       </c>
       <c r="H10" t="n">
-        <v>1836.2</v>
+        <v>1405.13</v>
       </c>
       <c r="I10" t="n">
-        <v>67937.38</v>
+        <v>68289.94</v>
       </c>
       <c r="J10" t="n">
-        <v>68736.37</v>
+        <v>68354.12</v>
       </c>
       <c r="K10" t="n">
-        <v>69379.91</v>
+        <v>69556.86</v>
       </c>
       <c r="L10" t="n">
-        <v>70023.46000000001</v>
+        <v>70759.60000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>70744.73</v>
+        <v>71393.06</v>
       </c>
       <c r="N10" t="n">
-        <v>71466</v>
+        <v>72026.52</v>
       </c>
       <c r="O10" t="n">
-        <v>72031.81</v>
+        <v>73798.55</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1379,84 +1385,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70039.89</v>
+        <v>68676.06</v>
       </c>
       <c r="C11" t="n">
-        <v>70081.39</v>
+        <v>69788.03</v>
       </c>
       <c r="D11" t="n">
-        <v>68676.25999999999</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>68733.14999999999</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1741.81</v>
+        <v>1010.92</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0147</v>
       </c>
       <c r="H11" t="n">
-        <v>1405.13</v>
+        <v>2178.54</v>
       </c>
       <c r="I11" t="n">
-        <v>68289.94</v>
+        <v>67271.12</v>
       </c>
       <c r="J11" t="n">
-        <v>68354.12</v>
+        <v>67005.17999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>69556.86</v>
+        <v>68030.58</v>
       </c>
       <c r="L11" t="n">
-        <v>70759.60000000001</v>
+        <v>69055.99000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>71393.06</v>
+        <v>69435.71000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>72026.52</v>
+        <v>69815.44</v>
       </c>
       <c r="O11" t="n">
-        <v>73798.55</v>
+        <v>71486.52</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1465,55 +1469,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>68676.06</v>
+        <v>69973.34</v>
       </c>
       <c r="C12" t="n">
-        <v>69788.03</v>
+        <v>70384.59</v>
       </c>
       <c r="D12" t="n">
-        <v>67609.49000000001</v>
+        <v>68904.41</v>
       </c>
       <c r="E12" t="n">
-        <v>69744.07000000001</v>
+        <v>69737.69</v>
       </c>
       <c r="F12" t="n">
-        <v>1010.92</v>
+        <v>-6.38</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0001</v>
       </c>
       <c r="H12" t="n">
-        <v>2178.54</v>
+        <v>1480.19</v>
       </c>
       <c r="I12" t="n">
-        <v>67271.12</v>
+        <v>65430.95</v>
       </c>
       <c r="J12" t="n">
-        <v>67005.17999999999</v>
+        <v>68088.19</v>
       </c>
       <c r="K12" t="n">
-        <v>68030.58</v>
+        <v>68654.8</v>
       </c>
       <c r="L12" t="n">
-        <v>69055.99000000001</v>
+        <v>69221.42</v>
       </c>
       <c r="M12" t="n">
-        <v>69435.71000000001</v>
+        <v>70833.34</v>
       </c>
       <c r="N12" t="n">
-        <v>69815.44</v>
+        <v>72445.25999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>71486.52</v>
+        <v>71966.57000000001</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1521,25 +1529,19 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1551,70 +1553,74 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69973.34</v>
+        <v>69460.08</v>
       </c>
       <c r="C13" t="n">
-        <v>70384.59</v>
+        <v>69957.50999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>68904.41</v>
+        <v>68003.92</v>
       </c>
       <c r="E13" t="n">
-        <v>69737.69</v>
+        <v>68256.96000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.38</v>
+        <v>-1480.73</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0212</v>
       </c>
       <c r="H13" t="n">
-        <v>1480.19</v>
+        <v>1953.59</v>
       </c>
       <c r="I13" t="n">
-        <v>65430.95</v>
+        <v>67424.22</v>
       </c>
       <c r="J13" t="n">
-        <v>68088.19</v>
+        <v>68304.09</v>
       </c>
       <c r="K13" t="n">
-        <v>68654.8</v>
+        <v>68997.59</v>
       </c>
       <c r="L13" t="n">
-        <v>69221.42</v>
+        <v>69691.09</v>
       </c>
       <c r="M13" t="n">
-        <v>70833.34</v>
+        <v>70477.78</v>
       </c>
       <c r="N13" t="n">
-        <v>72445.25999999999</v>
+        <v>71264.47</v>
       </c>
       <c r="O13" t="n">
-        <v>71966.57000000001</v>
+        <v>71864.78</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1631,71 +1637,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>69460.08</v>
+        <v>67704.16</v>
       </c>
       <c r="C14" t="n">
-        <v>69957.50999999999</v>
+        <v>68432.67999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>68003.92</v>
+        <v>66819.05</v>
       </c>
       <c r="E14" t="n">
-        <v>68256.96000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="F14" t="n">
-        <v>-1480.73</v>
+        <v>-1437.91</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="H14" t="n">
-        <v>1953.59</v>
+        <v>1613.63</v>
       </c>
       <c r="I14" t="n">
-        <v>67424.22</v>
+        <v>66050.34</v>
       </c>
       <c r="J14" t="n">
-        <v>68304.09</v>
+        <v>65941.5</v>
       </c>
       <c r="K14" t="n">
-        <v>68997.59</v>
+        <v>67280.17</v>
       </c>
       <c r="L14" t="n">
-        <v>69691.09</v>
+        <v>68618.84</v>
       </c>
       <c r="M14" t="n">
-        <v>70477.78</v>
+        <v>69233.75</v>
       </c>
       <c r="N14" t="n">
-        <v>71264.47</v>
+        <v>69848.67</v>
       </c>
       <c r="O14" t="n">
-        <v>71864.78</v>
+        <v>71911.09</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
@@ -1722,50 +1722,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67704.16</v>
+        <v>67046.37</v>
       </c>
       <c r="C15" t="n">
-        <v>68432.67999999999</v>
+        <v>68447.89</v>
       </c>
       <c r="D15" t="n">
-        <v>66819.05</v>
+        <v>67008.89</v>
       </c>
       <c r="E15" t="n">
-        <v>66819.05</v>
+        <v>67743.85000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-1437.91</v>
+        <v>924.8</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0211</v>
+        <v>0.0138</v>
       </c>
       <c r="H15" t="n">
-        <v>1613.63</v>
+        <v>1439</v>
       </c>
       <c r="I15" t="n">
-        <v>66050.34</v>
+        <v>65205.41</v>
       </c>
       <c r="J15" t="n">
-        <v>65941.5</v>
+        <v>64802.01</v>
       </c>
       <c r="K15" t="n">
-        <v>67280.17</v>
+        <v>66012.23</v>
       </c>
       <c r="L15" t="n">
-        <v>68618.84</v>
+        <v>67222.46000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>69233.75</v>
+        <v>67625.86</v>
       </c>
       <c r="N15" t="n">
-        <v>69848.67</v>
+        <v>68029.27</v>
       </c>
       <c r="O15" t="n">
-        <v>71911.09</v>
+        <v>70046.31</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1773,21 +1773,23 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1797,55 +1799,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>67046.37</v>
+        <v>68526.72</v>
       </c>
       <c r="C16" t="n">
-        <v>68447.89</v>
+        <v>69374.86</v>
       </c>
       <c r="D16" t="n">
-        <v>67008.89</v>
+        <v>68271.91</v>
       </c>
       <c r="E16" t="n">
-        <v>67743.85000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F16" t="n">
-        <v>924.8</v>
+        <v>813.88</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.012</v>
       </c>
       <c r="H16" t="n">
-        <v>1439</v>
+        <v>1102.95</v>
       </c>
       <c r="I16" t="n">
-        <v>65205.41</v>
+        <v>65569.89</v>
       </c>
       <c r="J16" t="n">
-        <v>64802.01</v>
+        <v>66312.58</v>
       </c>
       <c r="K16" t="n">
-        <v>66012.23</v>
+        <v>67024.35000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>67222.46000000001</v>
+        <v>67736.12</v>
       </c>
       <c r="M16" t="n">
-        <v>67625.86</v>
+        <v>68463.35000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>68029.27</v>
+        <v>69190.58</v>
       </c>
       <c r="O16" t="n">
-        <v>70046.31</v>
+        <v>69886.89</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1888,74 +1894,76 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>68526.72</v>
+        <v>68410.63</v>
       </c>
       <c r="C17" t="n">
-        <v>69374.86</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>68271.91</v>
+        <v>66653.11</v>
       </c>
       <c r="E17" t="n">
-        <v>68557.73</v>
+        <v>67242.73</v>
       </c>
       <c r="F17" t="n">
-        <v>813.88</v>
+        <v>-1315</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0192</v>
       </c>
       <c r="H17" t="n">
-        <v>1102.95</v>
+        <v>2425.1</v>
       </c>
       <c r="I17" t="n">
-        <v>65569.89</v>
+        <v>67168.95</v>
       </c>
       <c r="J17" t="n">
-        <v>66312.58</v>
+        <v>67321.95</v>
       </c>
       <c r="K17" t="n">
-        <v>67024.35000000001</v>
+        <v>68006.25</v>
       </c>
       <c r="L17" t="n">
-        <v>67736.12</v>
+        <v>68690.55</v>
       </c>
       <c r="M17" t="n">
-        <v>68463.35000000001</v>
+        <v>69109.2</v>
       </c>
       <c r="N17" t="n">
-        <v>69190.58</v>
+        <v>69527.85000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>69886.89</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+        <v>70477.81</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1965,78 +1973,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>68410.63</v>
+        <v>67002.94</v>
       </c>
       <c r="C18" t="n">
-        <v>69078.21000000001</v>
+        <v>67800.17999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>66653.11</v>
+        <v>66268.60000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>67242.73</v>
+        <v>67743.5</v>
       </c>
       <c r="F18" t="n">
-        <v>-1315</v>
+        <v>500.77</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0074</v>
       </c>
       <c r="H18" t="n">
-        <v>2425.1</v>
+        <v>1531.58</v>
       </c>
       <c r="I18" t="n">
-        <v>67168.95</v>
+        <v>64228.01</v>
       </c>
       <c r="J18" t="n">
-        <v>67321.95</v>
+        <v>64506.16</v>
       </c>
       <c r="K18" t="n">
-        <v>68006.25</v>
+        <v>66030.17999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>68690.55</v>
+        <v>67554.19</v>
       </c>
       <c r="M18" t="n">
-        <v>69109.2</v>
+        <v>68455.28</v>
       </c>
       <c r="N18" t="n">
-        <v>69527.85000000001</v>
+        <v>69356.36</v>
       </c>
       <c r="O18" t="n">
-        <v>70477.81</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>71503.31</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2053,55 +2051,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>67002.94</v>
+        <v>67989.74000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>67800.17999999999</v>
+        <v>68798.24000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>66268.60000000001</v>
+        <v>67833.17</v>
       </c>
       <c r="E19" t="n">
-        <v>67743.5</v>
+        <v>68751.50999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>500.77</v>
+        <v>1008.01</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0149</v>
       </c>
       <c r="H19" t="n">
-        <v>1531.58</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>64228.01</v>
+        <v>64737.02</v>
       </c>
       <c r="J19" t="n">
-        <v>64506.16</v>
+        <v>66566.48</v>
       </c>
       <c r="K19" t="n">
-        <v>66030.17999999999</v>
+        <v>66977.71000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>67554.19</v>
+        <v>67388.95</v>
       </c>
       <c r="M19" t="n">
-        <v>68455.28</v>
+        <v>68509.28999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>69356.36</v>
+        <v>69629.63</v>
       </c>
       <c r="O19" t="n">
-        <v>71503.31</v>
+        <v>69331.75999999999</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2114,11 +2116,13 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2133,77 +2137,81 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>67989.74000000001</v>
+        <v>67900.42999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>68798.24000000001</v>
+        <v>68069.82000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>67833.17</v>
+        <v>66499.49000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>68751.50999999999</v>
+        <v>66835.53999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>1008.01</v>
+        <v>-1915.97</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0279</v>
       </c>
       <c r="H20" t="n">
-        <v>965.0700000000001</v>
+        <v>1570.33</v>
       </c>
       <c r="I20" t="n">
-        <v>64737.02</v>
+        <v>66868.10000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>66566.48</v>
+        <v>68004.34</v>
       </c>
       <c r="K20" t="n">
-        <v>66977.71000000001</v>
+        <v>68268.97</v>
       </c>
       <c r="L20" t="n">
-        <v>67388.95</v>
+        <v>68533.61</v>
       </c>
       <c r="M20" t="n">
-        <v>68509.28999999999</v>
+        <v>69234.03999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>69629.63</v>
+        <v>69934.48</v>
       </c>
       <c r="O20" t="n">
-        <v>69331.75999999999</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+        <v>69763.31</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2215,59 +2223,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>67900.42999999999</v>
+        <v>66339.85000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>68069.82000000001</v>
+        <v>66441.77</v>
       </c>
       <c r="D21" t="n">
-        <v>66499.49000000001</v>
+        <v>62704.6</v>
       </c>
       <c r="E21" t="n">
-        <v>66835.53999999999</v>
+        <v>64141.12</v>
       </c>
       <c r="F21" t="n">
-        <v>-1915.97</v>
+        <v>-2694.42</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0403</v>
       </c>
       <c r="H21" t="n">
-        <v>1570.33</v>
+        <v>3737.17</v>
       </c>
       <c r="I21" t="n">
-        <v>66868.10000000001</v>
+        <v>64929.16</v>
       </c>
       <c r="J21" t="n">
-        <v>68004.34</v>
+        <v>65040.65</v>
       </c>
       <c r="K21" t="n">
-        <v>68268.97</v>
+        <v>66050.38</v>
       </c>
       <c r="L21" t="n">
-        <v>68533.61</v>
+        <v>67060.10000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>69234.03999999999</v>
+        <v>67620.7</v>
       </c>
       <c r="N21" t="n">
-        <v>69934.48</v>
+        <v>68181.31</v>
       </c>
       <c r="O21" t="n">
-        <v>69763.31</v>
+        <v>69640.14999999999</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
@@ -2308,74 +2312,70 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>66339.85000000001</v>
+        <v>64544.05</v>
       </c>
       <c r="C22" t="n">
-        <v>66441.77</v>
+        <v>66232.19</v>
       </c>
       <c r="D22" t="n">
-        <v>62704.6</v>
+        <v>64203.47</v>
       </c>
       <c r="E22" t="n">
-        <v>64141.12</v>
+        <v>66232.19</v>
       </c>
       <c r="F22" t="n">
-        <v>-2694.42</v>
+        <v>2091.07</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0326</v>
       </c>
       <c r="H22" t="n">
-        <v>3737.17</v>
+        <v>2028.72</v>
       </c>
       <c r="I22" t="n">
-        <v>64929.16</v>
+        <v>58967.43</v>
       </c>
       <c r="J22" t="n">
-        <v>65040.65</v>
+        <v>60187.92</v>
       </c>
       <c r="K22" t="n">
-        <v>66050.38</v>
+        <v>62272.54</v>
       </c>
       <c r="L22" t="n">
-        <v>67060.10000000001</v>
+        <v>64357.15</v>
       </c>
       <c r="M22" t="n">
-        <v>67620.7</v>
+        <v>66009.71000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>68181.31</v>
+        <v>67662.25999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>69640.14999999999</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>70178.95</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2387,55 +2387,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>64544.05</v>
+        <v>66449.27</v>
       </c>
       <c r="C23" t="n">
-        <v>66232.19</v>
+        <v>67592.2</v>
       </c>
       <c r="D23" t="n">
-        <v>64203.47</v>
+        <v>65955.60000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>66232.19</v>
+        <v>66115.60000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>2091.07</v>
+        <v>-116.59</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0326</v>
+        <v>-0.0018</v>
       </c>
       <c r="H23" t="n">
-        <v>2028.72</v>
+        <v>1636.6</v>
       </c>
       <c r="I23" t="n">
-        <v>58967.43</v>
+        <v>62174.75</v>
       </c>
       <c r="J23" t="n">
-        <v>60187.92</v>
+        <v>64710.65</v>
       </c>
       <c r="K23" t="n">
-        <v>62272.54</v>
+        <v>65217.83</v>
       </c>
       <c r="L23" t="n">
-        <v>64357.15</v>
+        <v>65725.00999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>66009.71000000001</v>
+        <v>67246.55</v>
       </c>
       <c r="N23" t="n">
-        <v>67662.25999999999</v>
+        <v>68768.09</v>
       </c>
       <c r="O23" t="n">
-        <v>70178.95</v>
+        <v>68260.91</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2448,12 +2452,12 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U23" s="8" t="n">
@@ -2476,50 +2480,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>66449.27</v>
+        <v>66421.00999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>67592.2</v>
+        <v>67022.37</v>
       </c>
       <c r="D24" t="n">
-        <v>65955.60000000001</v>
+        <v>66208.66</v>
       </c>
       <c r="E24" t="n">
-        <v>66115.60000000001</v>
+        <v>66422.60000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-116.59</v>
+        <v>307</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0046</v>
       </c>
       <c r="H24" t="n">
-        <v>1636.6</v>
+        <v>813.71</v>
       </c>
       <c r="I24" t="n">
-        <v>62174.75</v>
+        <v>64319</v>
       </c>
       <c r="J24" t="n">
-        <v>64710.65</v>
+        <v>64149.85</v>
       </c>
       <c r="K24" t="n">
-        <v>65217.83</v>
+        <v>65297.3</v>
       </c>
       <c r="L24" t="n">
-        <v>65725.00999999999</v>
+        <v>66444.75</v>
       </c>
       <c r="M24" t="n">
-        <v>67246.55</v>
+        <v>66933.89999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>68768.09</v>
+        <v>67423.05</v>
       </c>
       <c r="O24" t="n">
-        <v>68260.91</v>
+        <v>69228.8</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2530,9 +2534,9 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2560,69 +2564,73 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>66421.00999999999</v>
+        <v>65584.25</v>
       </c>
       <c r="C25" t="n">
-        <v>67022.37</v>
+        <v>65720.81</v>
       </c>
       <c r="D25" t="n">
-        <v>66208.66</v>
+        <v>64201.03</v>
       </c>
       <c r="E25" t="n">
-        <v>66422.60000000001</v>
+        <v>64611.15</v>
       </c>
       <c r="F25" t="n">
-        <v>307</v>
+        <v>-1811.45</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0273</v>
       </c>
       <c r="H25" t="n">
-        <v>813.71</v>
+        <v>1519.78</v>
       </c>
       <c r="I25" t="n">
-        <v>64319</v>
+        <v>65394.95</v>
       </c>
       <c r="J25" t="n">
-        <v>64149.85</v>
+        <v>65512.44</v>
       </c>
       <c r="K25" t="n">
-        <v>65297.3</v>
+        <v>66015.75</v>
       </c>
       <c r="L25" t="n">
-        <v>66444.75</v>
+        <v>66519.06</v>
       </c>
       <c r="M25" t="n">
-        <v>66933.89999999999</v>
+        <v>66829.46000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>67423.05</v>
+        <v>67139.86</v>
       </c>
       <c r="O25" t="n">
-        <v>69228.8</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+        <v>67836.08</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2635,78 +2643,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>65584.25</v>
+        <v>65164.98</v>
       </c>
       <c r="C26" t="n">
-        <v>65720.81</v>
+        <v>65220.69</v>
       </c>
       <c r="D26" t="n">
-        <v>64201.03</v>
+        <v>64123.4</v>
       </c>
       <c r="E26" t="n">
-        <v>64611.15</v>
+        <v>64931.19</v>
       </c>
       <c r="F26" t="n">
-        <v>-1811.45</v>
+        <v>320.04</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.005</v>
       </c>
       <c r="H26" t="n">
-        <v>1519.78</v>
+        <v>1097.29</v>
       </c>
       <c r="I26" t="n">
-        <v>65394.95</v>
+        <v>62681.25</v>
       </c>
       <c r="J26" t="n">
-        <v>65512.44</v>
+        <v>62916.48</v>
       </c>
       <c r="K26" t="n">
-        <v>66015.75</v>
+        <v>63851.26</v>
       </c>
       <c r="L26" t="n">
-        <v>66519.06</v>
+        <v>64786.04</v>
       </c>
       <c r="M26" t="n">
-        <v>66829.46000000001</v>
+        <v>65371.04</v>
       </c>
       <c r="N26" t="n">
-        <v>67139.86</v>
+        <v>65956.03999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>67836.08</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>67240.59</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2723,68 +2721,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>65164.98</v>
+        <v>64539.92</v>
       </c>
       <c r="C27" t="n">
-        <v>65220.69</v>
+        <v>64573.18</v>
       </c>
       <c r="D27" t="n">
-        <v>64123.4</v>
+        <v>61923.6</v>
       </c>
       <c r="E27" t="n">
-        <v>64931.19</v>
+        <v>62364.92</v>
       </c>
       <c r="F27" t="n">
-        <v>320.04</v>
+        <v>-2566.27</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0395</v>
       </c>
       <c r="H27" t="n">
-        <v>1097.29</v>
+        <v>2649.58</v>
       </c>
       <c r="I27" t="n">
-        <v>62681.25</v>
+        <v>63026.11</v>
       </c>
       <c r="J27" t="n">
-        <v>62916.48</v>
+        <v>63963.47</v>
       </c>
       <c r="K27" t="n">
-        <v>63851.26</v>
+        <v>64382.54</v>
       </c>
       <c r="L27" t="n">
-        <v>64786.04</v>
+        <v>64801.62</v>
       </c>
       <c r="M27" t="n">
-        <v>65371.04</v>
+        <v>65479.84</v>
       </c>
       <c r="N27" t="n">
-        <v>65956.03999999999</v>
+        <v>66158.06</v>
       </c>
       <c r="O27" t="n">
-        <v>67240.59</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>66317.98</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2801,73 +2809,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>64539.92</v>
+        <v>62734.68</v>
       </c>
       <c r="C28" t="n">
-        <v>64573.18</v>
+        <v>63138.04</v>
       </c>
       <c r="D28" t="n">
-        <v>61923.6</v>
+        <v>60448.9</v>
       </c>
       <c r="E28" t="n">
-        <v>62364.92</v>
+        <v>61434.19</v>
       </c>
       <c r="F28" t="n">
-        <v>-2566.27</v>
+        <v>-930.73</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0149</v>
       </c>
       <c r="H28" t="n">
-        <v>2649.58</v>
+        <v>2689.14</v>
       </c>
       <c r="I28" t="n">
-        <v>63026.11</v>
+        <v>59274.02</v>
       </c>
       <c r="J28" t="n">
-        <v>63963.47</v>
+        <v>59273.61</v>
       </c>
       <c r="K28" t="n">
-        <v>64382.54</v>
+        <v>61040.13</v>
       </c>
       <c r="L28" t="n">
-        <v>64801.62</v>
+        <v>62806.66</v>
       </c>
       <c r="M28" t="n">
-        <v>65479.84</v>
+        <v>63689.71</v>
       </c>
       <c r="N28" t="n">
-        <v>66158.06</v>
+        <v>64572.77</v>
       </c>
       <c r="O28" t="n">
-        <v>66317.98</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
+        <v>67222.75999999999</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
@@ -2894,50 +2894,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>62734.68</v>
+        <v>61258.34</v>
       </c>
       <c r="C29" t="n">
-        <v>63138.04</v>
+        <v>62924.84</v>
       </c>
       <c r="D29" t="n">
-        <v>60448.9</v>
+        <v>61049.7</v>
       </c>
       <c r="E29" t="n">
-        <v>61434.19</v>
+        <v>61867.43</v>
       </c>
       <c r="F29" t="n">
-        <v>-930.73</v>
+        <v>433.24</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0071</v>
       </c>
       <c r="H29" t="n">
-        <v>2689.14</v>
+        <v>1875.14</v>
       </c>
       <c r="I29" t="n">
-        <v>59274.02</v>
+        <v>57759.76</v>
       </c>
       <c r="J29" t="n">
-        <v>59273.61</v>
+        <v>58565.41</v>
       </c>
       <c r="K29" t="n">
-        <v>61040.13</v>
+        <v>60089.62</v>
       </c>
       <c r="L29" t="n">
-        <v>62806.66</v>
+        <v>61613.83</v>
       </c>
       <c r="M29" t="n">
-        <v>63689.71</v>
+        <v>62778.76</v>
       </c>
       <c r="N29" t="n">
-        <v>64572.77</v>
+        <v>63943.69</v>
       </c>
       <c r="O29" t="n">
-        <v>67222.75999999999</v>
+        <v>65827.17999999999</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2945,18 +2945,18 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2969,55 +2969,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>61258.34</v>
+        <v>61957.1</v>
       </c>
       <c r="C30" t="n">
-        <v>62924.84</v>
+        <v>65364.73</v>
       </c>
       <c r="D30" t="n">
-        <v>61049.7</v>
+        <v>61948.23</v>
       </c>
       <c r="E30" t="n">
-        <v>61867.43</v>
+        <v>64362.02</v>
       </c>
       <c r="F30" t="n">
-        <v>433.24</v>
+        <v>2494.59</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0403</v>
       </c>
       <c r="H30" t="n">
-        <v>1875.14</v>
+        <v>3416.5</v>
       </c>
       <c r="I30" t="n">
-        <v>57759.76</v>
+        <v>59174.56</v>
       </c>
       <c r="J30" t="n">
-        <v>58565.41</v>
+        <v>59932.37</v>
       </c>
       <c r="K30" t="n">
-        <v>60089.62</v>
+        <v>60929.86</v>
       </c>
       <c r="L30" t="n">
-        <v>61613.83</v>
+        <v>61927.35</v>
       </c>
       <c r="M30" t="n">
-        <v>62778.76</v>
+        <v>62805</v>
       </c>
       <c r="N30" t="n">
-        <v>63943.69</v>
+        <v>63682.65</v>
       </c>
       <c r="O30" t="n">
-        <v>65827.17999999999</v>
+        <v>64799.98</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3030,7 +3034,7 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -3038,70 +3042,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W30" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W30" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>61957.1</v>
+        <v>63834.95</v>
       </c>
       <c r="C31" t="n">
-        <v>65364.73</v>
+        <v>63905.12</v>
       </c>
       <c r="D31" t="n">
-        <v>61948.23</v>
+        <v>62703.47</v>
       </c>
       <c r="E31" t="n">
-        <v>64362.02</v>
+        <v>63754.9</v>
       </c>
       <c r="F31" t="n">
-        <v>2494.59</v>
+        <v>-607.12</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0403</v>
+        <v>-0.0094</v>
       </c>
       <c r="H31" t="n">
-        <v>3416.5</v>
+        <v>1201.65</v>
       </c>
       <c r="I31" t="n">
-        <v>59174.56</v>
+        <v>58531.73</v>
       </c>
       <c r="J31" t="n">
-        <v>59932.37</v>
+        <v>61298.29</v>
       </c>
       <c r="K31" t="n">
-        <v>60929.86</v>
+        <v>62653.77</v>
       </c>
       <c r="L31" t="n">
-        <v>61927.35</v>
+        <v>64009.25</v>
       </c>
       <c r="M31" t="n">
-        <v>62805</v>
+        <v>66070.27</v>
       </c>
       <c r="N31" t="n">
-        <v>63682.65</v>
+        <v>68131.28999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>64799.98</v>
+        <v>68781.23</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3112,80 +3116,78 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>63834.95</v>
+        <v>63995.28</v>
       </c>
       <c r="C32" t="n">
-        <v>63905.12</v>
+        <v>64240.5</v>
       </c>
       <c r="D32" t="n">
-        <v>62703.47</v>
+        <v>62864.43</v>
       </c>
       <c r="E32" t="n">
-        <v>63754.9</v>
+        <v>63957.53</v>
       </c>
       <c r="F32" t="n">
-        <v>-607.12</v>
+        <v>202.63</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0032</v>
       </c>
       <c r="H32" t="n">
-        <v>1201.65</v>
+        <v>1376.07</v>
       </c>
       <c r="I32" t="n">
-        <v>58531.73</v>
+        <v>61501.82</v>
       </c>
       <c r="J32" t="n">
-        <v>61298.29</v>
+        <v>62778.55</v>
       </c>
       <c r="K32" t="n">
-        <v>62653.77</v>
+        <v>63154.07</v>
       </c>
       <c r="L32" t="n">
-        <v>64009.25</v>
+        <v>63529.6</v>
       </c>
       <c r="M32" t="n">
-        <v>66070.27</v>
+        <v>64355.72</v>
       </c>
       <c r="N32" t="n">
-        <v>68131.28999999999</v>
+        <v>65181.85</v>
       </c>
       <c r="O32" t="n">
-        <v>68781.23</v>
+        <v>65106.77</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3193,16 +3195,20 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3215,59 +3221,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63995.28</v>
+        <v>64565.27</v>
       </c>
       <c r="C33" t="n">
-        <v>64240.5</v>
+        <v>66302.52</v>
       </c>
       <c r="D33" t="n">
-        <v>62864.43</v>
+        <v>64555.52</v>
       </c>
       <c r="E33" t="n">
-        <v>63957.53</v>
+        <v>66300.44</v>
       </c>
       <c r="F33" t="n">
-        <v>202.63</v>
+        <v>2342.91</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0366</v>
       </c>
       <c r="H33" t="n">
-        <v>1376.07</v>
+        <v>1747</v>
       </c>
       <c r="I33" t="n">
-        <v>61501.82</v>
+        <v>61488.36</v>
       </c>
       <c r="J33" t="n">
-        <v>62778.55</v>
+        <v>62783.99</v>
       </c>
       <c r="K33" t="n">
-        <v>63154.07</v>
+        <v>63269.5</v>
       </c>
       <c r="L33" t="n">
-        <v>63529.6</v>
+        <v>63755</v>
       </c>
       <c r="M33" t="n">
-        <v>64355.72</v>
+        <v>64645.57</v>
       </c>
       <c r="N33" t="n">
-        <v>65181.85</v>
+        <v>65536.13</v>
       </c>
       <c r="O33" t="n">
-        <v>65106.77</v>
+        <v>65616.57000000001</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3275,10 +3277,8 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
@@ -3287,14 +3287,18 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
@@ -3306,134 +3310,136 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>64565.27</v>
+        <v>65896</v>
       </c>
       <c r="C34" t="n">
-        <v>66302.52</v>
+        <v>65983.13</v>
       </c>
       <c r="D34" t="n">
-        <v>64555.52</v>
+        <v>64942.07</v>
       </c>
       <c r="E34" t="n">
-        <v>66300.44</v>
+        <v>65683.25999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>2342.91</v>
+        <v>-617.1799999999999</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0366</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>1747</v>
+        <v>1041.06</v>
       </c>
       <c r="I34" t="n">
-        <v>61488.36</v>
+        <v>62808.52</v>
       </c>
       <c r="J34" t="n">
-        <v>62783.99</v>
+        <v>64989.14</v>
       </c>
       <c r="K34" t="n">
-        <v>63269.5</v>
+        <v>65426.94</v>
       </c>
       <c r="L34" t="n">
-        <v>63755</v>
+        <v>65864.73</v>
       </c>
       <c r="M34" t="n">
-        <v>64645.57</v>
+        <v>67173.94</v>
       </c>
       <c r="N34" t="n">
-        <v>65536.13</v>
+        <v>68483.14999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>65616.57000000001</v>
+        <v>68049.53</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>65896</v>
+        <v>65746.13</v>
       </c>
       <c r="C35" t="n">
-        <v>65983.13</v>
+        <v>65990.72</v>
       </c>
       <c r="D35" t="n">
-        <v>64942.07</v>
+        <v>64651.49</v>
       </c>
       <c r="E35" t="n">
-        <v>65683.25999999999</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-617.1799999999999</v>
+        <v>-76.55</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="H35" t="n">
-        <v>1041.06</v>
+        <v>1339.23</v>
       </c>
       <c r="I35" t="n">
-        <v>62808.52</v>
+        <v>63901.01</v>
       </c>
       <c r="J35" t="n">
-        <v>64989.14</v>
+        <v>64752.52</v>
       </c>
       <c r="K35" t="n">
-        <v>65426.94</v>
+        <v>65162.73</v>
       </c>
       <c r="L35" t="n">
-        <v>65864.73</v>
+        <v>65572.92999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>67173.94</v>
+        <v>66203.78999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>68483.14999999999</v>
+        <v>66834.64999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>68049.53</v>
+        <v>67024.2</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3448,9 +3454,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3476,74 +3482,74 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>65746.13</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>65990.72</v>
+        <v>67006.84</v>
       </c>
       <c r="D36" t="n">
-        <v>64651.49</v>
+        <v>65848.58</v>
       </c>
       <c r="E36" t="n">
-        <v>65606.71000000001</v>
+        <v>66970.22</v>
       </c>
       <c r="F36" t="n">
-        <v>-76.55</v>
+        <v>1363.51</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0208</v>
       </c>
       <c r="H36" t="n">
-        <v>1339.23</v>
+        <v>1158.27</v>
       </c>
       <c r="I36" t="n">
-        <v>63901.01</v>
+        <v>63312.26</v>
       </c>
       <c r="J36" t="n">
-        <v>64752.52</v>
+        <v>64410.28</v>
       </c>
       <c r="K36" t="n">
-        <v>65162.73</v>
+        <v>64937.1</v>
       </c>
       <c r="L36" t="n">
-        <v>65572.92999999999</v>
+        <v>65463.91</v>
       </c>
       <c r="M36" t="n">
-        <v>66203.78999999999</v>
+        <v>66276.33</v>
       </c>
       <c r="N36" t="n">
-        <v>66834.64999999999</v>
+        <v>67088.75</v>
       </c>
       <c r="O36" t="n">
-        <v>67024.2</v>
+        <v>67329.95</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3553,59 +3559,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>65905.10000000001</v>
+        <v>66994.05</v>
       </c>
       <c r="C37" t="n">
-        <v>67006.84</v>
+        <v>67569.36</v>
       </c>
       <c r="D37" t="n">
-        <v>65848.58</v>
+        <v>66735.75999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>66970.22</v>
+        <v>67524.06</v>
       </c>
       <c r="F37" t="n">
-        <v>1363.51</v>
+        <v>553.84</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="H37" t="n">
-        <v>1158.27</v>
+        <v>833.6</v>
       </c>
       <c r="I37" t="n">
-        <v>63312.26</v>
+        <v>64690.31</v>
       </c>
       <c r="J37" t="n">
-        <v>64410.28</v>
+        <v>66083.21000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>64937.1</v>
+        <v>66391.09</v>
       </c>
       <c r="L37" t="n">
-        <v>65463.91</v>
+        <v>66698.96000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>66276.33</v>
+        <v>67549.35000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>67088.75</v>
+        <v>68399.74000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>67329.95</v>
+        <v>68165.11</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3623,13 +3625,11 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3644,50 +3644,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>66994.05</v>
+        <v>68033.17</v>
       </c>
       <c r="C38" t="n">
-        <v>67569.36</v>
+        <v>68799.71000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>66735.75999999999</v>
+        <v>68006.17</v>
       </c>
       <c r="E38" t="n">
-        <v>67524.06</v>
+        <v>68308.59</v>
       </c>
       <c r="F38" t="n">
-        <v>553.84</v>
+        <v>784.53</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0116</v>
       </c>
       <c r="H38" t="n">
-        <v>833.6</v>
+        <v>793.54</v>
       </c>
       <c r="I38" t="n">
-        <v>64690.31</v>
+        <v>65902.16</v>
       </c>
       <c r="J38" t="n">
-        <v>66083.21000000001</v>
+        <v>66876.21000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>66391.09</v>
+        <v>67107.25999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>66698.96000000001</v>
+        <v>67338.31</v>
       </c>
       <c r="M38" t="n">
-        <v>67549.35000000001</v>
+        <v>67940.86</v>
       </c>
       <c r="N38" t="n">
-        <v>68399.74000000001</v>
+        <v>68543.42</v>
       </c>
       <c r="O38" t="n">
-        <v>68165.11</v>
+        <v>68402.96000000001</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3705,14 +3705,18 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
@@ -3724,50 +3728,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>68033.17</v>
+        <v>68811.17</v>
       </c>
       <c r="C39" t="n">
-        <v>68799.71000000001</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>68006.17</v>
+        <v>68471.14999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>68308.59</v>
+        <v>68713.8</v>
       </c>
       <c r="F39" t="n">
-        <v>784.53</v>
+        <v>405.2</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0059</v>
       </c>
       <c r="H39" t="n">
-        <v>793.54</v>
+        <v>1137.09</v>
       </c>
       <c r="I39" t="n">
-        <v>65902.16</v>
+        <v>67212.63</v>
       </c>
       <c r="J39" t="n">
-        <v>66876.21000000001</v>
+        <v>67467.88</v>
       </c>
       <c r="K39" t="n">
-        <v>67107.25999999999</v>
+        <v>67911.82000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>67338.31</v>
+        <v>68355.77</v>
       </c>
       <c r="M39" t="n">
-        <v>67940.86</v>
+        <v>68705.36</v>
       </c>
       <c r="N39" t="n">
-        <v>68543.42</v>
+        <v>69054.96000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>68402.96000000001</v>
+        <v>69593.25</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3785,7 +3789,7 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U39" s="8" t="inlineStr">
@@ -3795,7 +3799,7 @@
       </c>
       <c r="V39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W39" s="9" t="inlineStr">
@@ -3808,50 +3812,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>68811.17</v>
+        <v>68882.06</v>
       </c>
       <c r="C40" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>68471.14999999999</v>
+        <v>68492.03999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>68713.8</v>
+        <v>69220.25</v>
       </c>
       <c r="F40" t="n">
-        <v>405.2</v>
+        <v>506.45</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="H40" t="n">
-        <v>1137.09</v>
+        <v>733.53</v>
       </c>
       <c r="I40" t="n">
-        <v>67212.63</v>
+        <v>67334.05</v>
       </c>
       <c r="J40" t="n">
-        <v>67467.88</v>
+        <v>67413.75</v>
       </c>
       <c r="K40" t="n">
-        <v>67911.82000000001</v>
+        <v>68145.25</v>
       </c>
       <c r="L40" t="n">
-        <v>68355.77</v>
+        <v>68876.75</v>
       </c>
       <c r="M40" t="n">
-        <v>68705.36</v>
+        <v>69282.34</v>
       </c>
       <c r="N40" t="n">
-        <v>69054.96000000001</v>
+        <v>69687.94</v>
       </c>
       <c r="O40" t="n">
-        <v>69593.25</v>
+        <v>70745.34</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3872,163 +3876,163 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>68882.06</v>
+        <v>68847.35000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>69225.57000000001</v>
+        <v>69093.2</v>
       </c>
       <c r="D41" t="n">
-        <v>68492.03999999999</v>
+        <v>67368.96000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>69220.25</v>
+        <v>67460.73</v>
       </c>
       <c r="F41" t="n">
-        <v>506.45</v>
+        <v>-1759.52</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0254</v>
       </c>
       <c r="H41" t="n">
-        <v>733.53</v>
+        <v>1724.24</v>
       </c>
       <c r="I41" t="n">
-        <v>67334.05</v>
+        <v>67758.50999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>67413.75</v>
+        <v>68667.44</v>
       </c>
       <c r="K41" t="n">
-        <v>68145.25</v>
+        <v>68853.48</v>
       </c>
       <c r="L41" t="n">
-        <v>68876.75</v>
+        <v>69039.53</v>
       </c>
       <c r="M41" t="n">
-        <v>69282.34</v>
+        <v>69587.02</v>
       </c>
       <c r="N41" t="n">
-        <v>69687.94</v>
+        <v>70134.5</v>
       </c>
       <c r="O41" t="n">
-        <v>70745.34</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+        <v>69959.10000000001</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>68847.35000000001</v>
+        <v>66812.27</v>
       </c>
       <c r="C42" t="n">
-        <v>69093.2</v>
+        <v>66833.50999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>67368.96000000001</v>
+        <v>65133.98</v>
       </c>
       <c r="E42" t="n">
-        <v>67460.73</v>
+        <v>65326.42</v>
       </c>
       <c r="F42" t="n">
-        <v>-1759.52</v>
+        <v>-2134.3</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="H42" t="n">
-        <v>1724.24</v>
+        <v>1699.53</v>
       </c>
       <c r="I42" t="n">
-        <v>67758.50999999999</v>
+        <v>65644.72</v>
       </c>
       <c r="J42" t="n">
-        <v>68667.44</v>
+        <v>65351.31</v>
       </c>
       <c r="K42" t="n">
-        <v>68853.48</v>
+        <v>66598.61</v>
       </c>
       <c r="L42" t="n">
-        <v>69039.53</v>
+        <v>67845.89999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>69587.02</v>
+        <v>68322.85000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>70134.5</v>
+        <v>68799.78999999999</v>
       </c>
       <c r="O42" t="n">
-        <v>69959.10000000001</v>
+        <v>70817.45</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
@@ -4060,74 +4064,70 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>66812.27</v>
+        <v>65732.78999999999</v>
       </c>
       <c r="C43" t="n">
-        <v>66833.50999999999</v>
+        <v>66325.32000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>65133.98</v>
+        <v>65652.25</v>
       </c>
       <c r="E43" t="n">
-        <v>65326.42</v>
+        <v>66216.78999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>-2134.3</v>
+        <v>890.37</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H43" t="n">
-        <v>1699.53</v>
+        <v>673.0700000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>65644.72</v>
+        <v>63434.45</v>
       </c>
       <c r="J43" t="n">
-        <v>65351.31</v>
+        <v>63298.23</v>
       </c>
       <c r="K43" t="n">
-        <v>66598.61</v>
+        <v>64476.66</v>
       </c>
       <c r="L43" t="n">
-        <v>67845.89999999999</v>
+        <v>65655.08</v>
       </c>
       <c r="M43" t="n">
-        <v>68322.85000000001</v>
+        <v>66176.19</v>
       </c>
       <c r="N43" t="n">
-        <v>68799.78999999999</v>
+        <v>66697.28999999999</v>
       </c>
       <c r="O43" t="n">
-        <v>70817.45</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
+        <v>68533.03999999999</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4139,74 +4139,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>65732.78999999999</v>
+        <v>65427.69</v>
       </c>
       <c r="C44" t="n">
-        <v>66325.32000000001</v>
+        <v>66125.88</v>
       </c>
       <c r="D44" t="n">
-        <v>65652.25</v>
+        <v>65260.22</v>
       </c>
       <c r="E44" t="n">
-        <v>66216.78999999999</v>
+        <v>66016.36</v>
       </c>
       <c r="F44" t="n">
-        <v>890.37</v>
+        <v>-200.43</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.003</v>
       </c>
       <c r="H44" t="n">
-        <v>673.0700000000001</v>
+        <v>865.66</v>
       </c>
       <c r="I44" t="n">
-        <v>63434.45</v>
+        <v>64979.18</v>
       </c>
       <c r="J44" t="n">
-        <v>63298.23</v>
+        <v>65657.72</v>
       </c>
       <c r="K44" t="n">
-        <v>64476.66</v>
+        <v>65880.25</v>
       </c>
       <c r="L44" t="n">
-        <v>65655.08</v>
+        <v>66102.78999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>66176.19</v>
+        <v>66553.32000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>66697.28999999999</v>
+        <v>67003.86</v>
       </c>
       <c r="O44" t="n">
-        <v>68533.03999999999</v>
+        <v>66998.39</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4219,76 +4225,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>65427.69</v>
+        <v>65978.95</v>
       </c>
       <c r="C45" t="n">
-        <v>66125.88</v>
+        <v>66257.73</v>
       </c>
       <c r="D45" t="n">
-        <v>65260.22</v>
+        <v>65470.95</v>
       </c>
       <c r="E45" t="n">
-        <v>66016.36</v>
+        <v>65528.09</v>
       </c>
       <c r="F45" t="n">
-        <v>-200.43</v>
+        <v>-488.27</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0074</v>
       </c>
       <c r="H45" t="n">
-        <v>865.66</v>
+        <v>786.78</v>
       </c>
       <c r="I45" t="n">
-        <v>64979.18</v>
+        <v>64394.55</v>
       </c>
       <c r="J45" t="n">
-        <v>65657.72</v>
+        <v>65312.35</v>
       </c>
       <c r="K45" t="n">
-        <v>65880.25</v>
+        <v>65583.53</v>
       </c>
       <c r="L45" t="n">
-        <v>66102.78999999999</v>
+        <v>65854.71000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>66553.32000000001</v>
+        <v>66449.19</v>
       </c>
       <c r="N45" t="n">
-        <v>67003.86</v>
+        <v>67043.67999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>66998.39</v>
+        <v>66991.55</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q45" s="6" t="n">
+        <v/>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4305,75 +4305,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>65978.95</v>
+        <v>65195.26</v>
       </c>
       <c r="C46" t="n">
-        <v>66257.73</v>
+        <v>65904.24000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>65470.95</v>
+        <v>64609.47</v>
       </c>
       <c r="E46" t="n">
-        <v>65528.09</v>
+        <v>65856.42999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>-488.27</v>
+        <v>328.34</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.005</v>
       </c>
       <c r="H46" t="n">
-        <v>786.78</v>
+        <v>1294.77</v>
       </c>
       <c r="I46" t="n">
-        <v>64394.55</v>
+        <v>64684.17</v>
       </c>
       <c r="J46" t="n">
-        <v>65312.35</v>
+        <v>64573.19</v>
       </c>
       <c r="K46" t="n">
-        <v>65583.53</v>
+        <v>65134.7</v>
       </c>
       <c r="L46" t="n">
-        <v>65854.71000000001</v>
+        <v>65696.21000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>66449.19</v>
+        <v>65921.48</v>
       </c>
       <c r="N46" t="n">
-        <v>67043.67999999999</v>
+        <v>66146.74000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>66991.55</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
+        <v>67044.5</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4387,70 +4395,66 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65195.26</v>
+        <v>65604.49000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>65904.24000000001</v>
+        <v>66442.34</v>
       </c>
       <c r="D47" t="n">
-        <v>64609.47</v>
+        <v>65390.55</v>
       </c>
       <c r="E47" t="n">
-        <v>65856.42999999999</v>
+        <v>66262.16</v>
       </c>
       <c r="F47" t="n">
-        <v>328.34</v>
+        <v>405.73</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0062</v>
       </c>
       <c r="H47" t="n">
-        <v>1294.77</v>
+        <v>1051.79</v>
       </c>
       <c r="I47" t="n">
-        <v>64684.17</v>
+        <v>63314.7</v>
       </c>
       <c r="J47" t="n">
-        <v>64573.19</v>
+        <v>64861.44</v>
       </c>
       <c r="K47" t="n">
-        <v>65134.7</v>
+        <v>65209.04</v>
       </c>
       <c r="L47" t="n">
-        <v>65696.21000000001</v>
+        <v>65556.64</v>
       </c>
       <c r="M47" t="n">
-        <v>65921.48</v>
+        <v>66503.82000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>66146.74000000001</v>
+        <v>67450.99000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>67044.5</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67199.02</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
       </c>
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
@@ -4475,57 +4479,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65604.49000000001</v>
+        <v>66775.78</v>
       </c>
       <c r="C48" t="n">
-        <v>66442.34</v>
+        <v>66954.69</v>
       </c>
       <c r="D48" t="n">
-        <v>65390.55</v>
+        <v>65782.59</v>
       </c>
       <c r="E48" t="n">
-        <v>66262.16</v>
+        <v>66131.98</v>
       </c>
       <c r="F48" t="n">
-        <v>405.73</v>
+        <v>-130.18</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.002</v>
       </c>
       <c r="H48" t="n">
-        <v>1051.79</v>
+        <v>1172.09</v>
       </c>
       <c r="I48" t="n">
-        <v>63314.7</v>
+        <v>64338.76</v>
       </c>
       <c r="J48" t="n">
-        <v>64861.44</v>
+        <v>65383.22</v>
       </c>
       <c r="K48" t="n">
-        <v>65209.04</v>
+        <v>65736.25999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>65556.64</v>
+        <v>66089.3</v>
       </c>
       <c r="M48" t="n">
-        <v>66503.82000000001</v>
+        <v>66788.05</v>
       </c>
       <c r="N48" t="n">
-        <v>67450.99000000001</v>
+        <v>67486.8</v>
       </c>
       <c r="O48" t="n">
-        <v>67199.02</v>
+        <v>67494.14</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4538,12 +4542,12 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U48" s="8" t="n">
@@ -4559,57 +4563,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>66775.78</v>
+        <v>66104.49000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>66954.69</v>
+        <v>66842.82000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>65782.59</v>
+        <v>66012.2</v>
       </c>
       <c r="E49" t="n">
-        <v>66131.98</v>
+        <v>66405.56</v>
       </c>
       <c r="F49" t="n">
-        <v>-130.18</v>
+        <v>273.59</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0041</v>
       </c>
       <c r="H49" t="n">
-        <v>1172.09</v>
+        <v>830.62</v>
       </c>
       <c r="I49" t="n">
-        <v>64338.76</v>
+        <v>64610.5</v>
       </c>
       <c r="J49" t="n">
-        <v>65383.22</v>
+        <v>64841.55</v>
       </c>
       <c r="K49" t="n">
-        <v>65736.25999999999</v>
+        <v>65545.92999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>66089.3</v>
+        <v>66250.31</v>
       </c>
       <c r="M49" t="n">
-        <v>66788.05</v>
+        <v>66718.02</v>
       </c>
       <c r="N49" t="n">
-        <v>67486.8</v>
+        <v>67185.74000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>67494.14</v>
+        <v>68126.78</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4650,69 +4654,73 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>66104.49000000001</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C50" t="n">
-        <v>66842.82000000001</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>66012.2</v>
+        <v>64832.1</v>
       </c>
       <c r="E50" t="n">
-        <v>66405.56</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>273.59</v>
+        <v>-93.63</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0014</v>
       </c>
       <c r="H50" t="n">
-        <v>830.62</v>
+        <v>1479.83</v>
       </c>
       <c r="I50" t="n">
-        <v>64610.5</v>
+        <v>65181.59</v>
       </c>
       <c r="J50" t="n">
-        <v>64841.55</v>
+        <v>65563.97</v>
       </c>
       <c r="K50" t="n">
-        <v>65545.92999999999</v>
+        <v>65990.25</v>
       </c>
       <c r="L50" t="n">
-        <v>66250.31</v>
+        <v>66416.53999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>66718.02</v>
+        <v>66820.87</v>
       </c>
       <c r="N50" t="n">
-        <v>67185.74000000001</v>
+        <v>67225.21000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>68126.78</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67673.44</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4725,78 +4733,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65668.50999999999</v>
+        <v>65885.47</v>
       </c>
       <c r="C51" t="n">
-        <v>66311.92999999999</v>
+        <v>66525.7</v>
       </c>
       <c r="D51" t="n">
-        <v>64832.1</v>
+        <v>65576.61</v>
       </c>
       <c r="E51" t="n">
-        <v>66311.92999999999</v>
+        <v>66215.34</v>
       </c>
       <c r="F51" t="n">
-        <v>-93.63</v>
+        <v>-96.59</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0015</v>
       </c>
       <c r="H51" t="n">
-        <v>1479.83</v>
+        <v>949.09</v>
       </c>
       <c r="I51" t="n">
-        <v>65181.59</v>
+        <v>63352.27</v>
       </c>
       <c r="J51" t="n">
-        <v>65563.97</v>
+        <v>65202.06</v>
       </c>
       <c r="K51" t="n">
-        <v>65990.25</v>
+        <v>65572.02</v>
       </c>
       <c r="L51" t="n">
-        <v>66416.53999999999</v>
+        <v>65941.97</v>
       </c>
       <c r="M51" t="n">
-        <v>66820.87</v>
+        <v>67051.84</v>
       </c>
       <c r="N51" t="n">
-        <v>67225.21000000001</v>
+        <v>68161.71000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>67673.44</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>67791.75999999999</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4813,68 +4811,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>65885.47</v>
+        <v>65195.43</v>
       </c>
       <c r="C52" t="n">
-        <v>66525.7</v>
+        <v>65195.43</v>
       </c>
       <c r="D52" t="n">
-        <v>65576.61</v>
+        <v>64215.47</v>
       </c>
       <c r="E52" t="n">
-        <v>66215.34</v>
+        <v>64325.64</v>
       </c>
       <c r="F52" t="n">
-        <v>-96.59</v>
+        <v>-1889.7</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0285</v>
       </c>
       <c r="H52" t="n">
-        <v>949.09</v>
+        <v>979.96</v>
       </c>
       <c r="I52" t="n">
-        <v>63352.27</v>
+        <v>64627.52</v>
       </c>
       <c r="J52" t="n">
-        <v>65202.06</v>
+        <v>65348.34</v>
       </c>
       <c r="K52" t="n">
-        <v>65572.02</v>
+        <v>65740.8</v>
       </c>
       <c r="L52" t="n">
-        <v>65941.97</v>
+        <v>66133.25</v>
       </c>
       <c r="M52" t="n">
-        <v>67051.84</v>
+        <v>66689.89</v>
       </c>
       <c r="N52" t="n">
-        <v>68161.71000000001</v>
+        <v>67246.53</v>
       </c>
       <c r="O52" t="n">
-        <v>67791.75999999999</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>67474.8</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4891,69 +4899,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="C53" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="D53" t="n">
-        <v>64215.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E53" t="n">
-        <v>64325.64</v>
+        <v>64214.48</v>
       </c>
       <c r="F53" t="n">
-        <v>-1889.7</v>
+        <v>-111.16</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0017</v>
       </c>
       <c r="H53" t="n">
-        <v>979.96</v>
+        <v>952.01</v>
       </c>
       <c r="I53" t="n">
-        <v>64627.52</v>
+        <v>63235.51</v>
       </c>
       <c r="J53" t="n">
-        <v>65348.34</v>
+        <v>63155.78</v>
       </c>
       <c r="K53" t="n">
-        <v>65740.8</v>
+        <v>63835.66</v>
       </c>
       <c r="L53" t="n">
-        <v>66133.25</v>
+        <v>64515.54</v>
       </c>
       <c r="M53" t="n">
-        <v>66689.89</v>
+        <v>64815.62</v>
       </c>
       <c r="N53" t="n">
-        <v>67246.53</v>
+        <v>65115.7</v>
       </c>
       <c r="O53" t="n">
-        <v>67474.8</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66175.39</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4984,50 +4984,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>64724.81</v>
+        <v>64498.94</v>
       </c>
       <c r="C54" t="n">
-        <v>64724.81</v>
+        <v>65182.45</v>
       </c>
       <c r="D54" t="n">
-        <v>63772.8</v>
+        <v>64228.47</v>
       </c>
       <c r="E54" t="n">
-        <v>64214.48</v>
+        <v>65020.94</v>
       </c>
       <c r="F54" t="n">
-        <v>-111.16</v>
+        <v>806.46</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="H54" t="n">
-        <v>952.01</v>
+        <v>953.98</v>
       </c>
       <c r="I54" t="n">
-        <v>63235.51</v>
+        <v>62820.79</v>
       </c>
       <c r="J54" t="n">
-        <v>63155.78</v>
+        <v>63245.31</v>
       </c>
       <c r="K54" t="n">
-        <v>63835.66</v>
+        <v>63738.48</v>
       </c>
       <c r="L54" t="n">
-        <v>64515.54</v>
+        <v>64231.64</v>
       </c>
       <c r="M54" t="n">
-        <v>64815.62</v>
+        <v>64690.48</v>
       </c>
       <c r="N54" t="n">
-        <v>65115.7</v>
+        <v>65149.33</v>
       </c>
       <c r="O54" t="n">
-        <v>66175.39</v>
+        <v>65676.82000000001</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5035,21 +5035,23 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5059,55 +5061,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>64498.94</v>
+        <v>65600.42</v>
       </c>
       <c r="C55" t="n">
-        <v>65182.45</v>
+        <v>66668.71000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>64228.47</v>
+        <v>65600.42</v>
       </c>
       <c r="E55" t="n">
-        <v>65020.94</v>
+        <v>66399.84</v>
       </c>
       <c r="F55" t="n">
-        <v>806.46</v>
+        <v>1378.9</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="H55" t="n">
-        <v>953.98</v>
+        <v>1068.29</v>
       </c>
       <c r="I55" t="n">
-        <v>62820.79</v>
+        <v>63274.49</v>
       </c>
       <c r="J55" t="n">
-        <v>63245.31</v>
+        <v>64224.7</v>
       </c>
       <c r="K55" t="n">
-        <v>63738.48</v>
+        <v>64543.95</v>
       </c>
       <c r="L55" t="n">
-        <v>64231.64</v>
+        <v>64863.2</v>
       </c>
       <c r="M55" t="n">
-        <v>64690.48</v>
+        <v>65497.93</v>
       </c>
       <c r="N55" t="n">
-        <v>65149.33</v>
+        <v>66132.66</v>
       </c>
       <c r="O55" t="n">
-        <v>65676.82000000001</v>
+        <v>66136.42999999999</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5130,171 +5136,167 @@
       </c>
       <c r="U55" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>65600.42</v>
+        <v>65843.69</v>
       </c>
       <c r="C56" t="n">
-        <v>66668.71000000001</v>
+        <v>66791.84</v>
       </c>
       <c r="D56" t="n">
-        <v>65600.42</v>
+        <v>65269.33</v>
       </c>
       <c r="E56" t="n">
-        <v>66399.84</v>
+        <v>65269.33</v>
       </c>
       <c r="F56" t="n">
-        <v>1378.9</v>
+        <v>-1130.52</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.017</v>
       </c>
       <c r="H56" t="n">
-        <v>1068.29</v>
+        <v>1522.52</v>
       </c>
       <c r="I56" t="n">
-        <v>63274.49</v>
+        <v>64532.13</v>
       </c>
       <c r="J56" t="n">
-        <v>64224.7</v>
+        <v>65464.19</v>
       </c>
       <c r="K56" t="n">
-        <v>64543.95</v>
+        <v>65865.7</v>
       </c>
       <c r="L56" t="n">
-        <v>64863.2</v>
+        <v>66267.21000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>65497.93</v>
+        <v>66933.99000000001</v>
       </c>
       <c r="N56" t="n">
-        <v>66132.66</v>
+        <v>67600.77</v>
       </c>
       <c r="O56" t="n">
-        <v>66136.42999999999</v>
+        <v>67737</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
+      <c r="Q56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W56" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>65843.69</v>
+        <v>65087.22</v>
       </c>
       <c r="C57" t="n">
-        <v>66791.84</v>
+        <v>65794.03</v>
       </c>
       <c r="D57" t="n">
-        <v>65269.33</v>
+        <v>65017.68</v>
       </c>
       <c r="E57" t="n">
-        <v>65269.33</v>
+        <v>65142.78</v>
       </c>
       <c r="F57" t="n">
-        <v>-1130.52</v>
+        <v>-126.55</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0019</v>
       </c>
       <c r="H57" t="n">
-        <v>1522.52</v>
+        <v>776.35</v>
       </c>
       <c r="I57" t="n">
-        <v>64532.13</v>
+        <v>63746.81</v>
       </c>
       <c r="J57" t="n">
-        <v>65464.19</v>
+        <v>63366.18</v>
       </c>
       <c r="K57" t="n">
-        <v>65865.7</v>
+        <v>64508.07</v>
       </c>
       <c r="L57" t="n">
-        <v>66267.21000000001</v>
+        <v>65649.96000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>66933.99000000001</v>
+        <v>66030.59</v>
       </c>
       <c r="N57" t="n">
-        <v>67600.77</v>
+        <v>66411.21000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>67737</v>
+        <v>68314.36</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5311,68 +5313,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>65087.22</v>
+        <v>64768.53</v>
       </c>
       <c r="C58" t="n">
-        <v>65794.03</v>
+        <v>65270.95</v>
       </c>
       <c r="D58" t="n">
-        <v>65017.68</v>
+        <v>64186.68</v>
       </c>
       <c r="E58" t="n">
-        <v>65142.78</v>
+        <v>65270.95</v>
       </c>
       <c r="F58" t="n">
-        <v>-126.55</v>
+        <v>128.17</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="H58" t="n">
-        <v>776.35</v>
+        <v>1084.27</v>
       </c>
       <c r="I58" t="n">
-        <v>63746.81</v>
+        <v>64241.33</v>
       </c>
       <c r="J58" t="n">
-        <v>63366.18</v>
+        <v>64234.89</v>
       </c>
       <c r="K58" t="n">
-        <v>64508.07</v>
+        <v>64754.61</v>
       </c>
       <c r="L58" t="n">
-        <v>65649.96000000001</v>
+        <v>65274.32</v>
       </c>
       <c r="M58" t="n">
-        <v>66030.59</v>
+        <v>65530.96</v>
       </c>
       <c r="N58" t="n">
-        <v>66411.21000000001</v>
+        <v>65787.60000000001</v>
       </c>
       <c r="O58" t="n">
-        <v>68314.36</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+        <v>66570.38</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
@@ -5393,64 +5397,66 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>64768.53</v>
+        <v>64276.82</v>
       </c>
       <c r="C59" t="n">
-        <v>65270.95</v>
+        <v>64312.02</v>
       </c>
       <c r="D59" t="n">
-        <v>64186.68</v>
+        <v>63208.63</v>
       </c>
       <c r="E59" t="n">
-        <v>65270.95</v>
+        <v>64011.34</v>
       </c>
       <c r="F59" t="n">
-        <v>128.17</v>
+        <v>-1259.61</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H59" t="n">
-        <v>1084.27</v>
+        <v>1103.39</v>
       </c>
       <c r="I59" t="n">
-        <v>64241.33</v>
+        <v>63102.41</v>
       </c>
       <c r="J59" t="n">
-        <v>64234.89</v>
+        <v>64457.75</v>
       </c>
       <c r="K59" t="n">
-        <v>64754.61</v>
+        <v>64728.81</v>
       </c>
       <c r="L59" t="n">
-        <v>65274.32</v>
+        <v>64999.88</v>
       </c>
       <c r="M59" t="n">
-        <v>65530.96</v>
+        <v>65813.08</v>
       </c>
       <c r="N59" t="n">
-        <v>65787.60000000001</v>
+        <v>66626.28999999999</v>
       </c>
       <c r="O59" t="n">
-        <v>66570.38</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66355.22</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
@@ -5460,7 +5466,7 @@
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5477,71 +5483,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>64276.82</v>
+        <v>63659.53</v>
       </c>
       <c r="C60" t="n">
-        <v>64312.02</v>
+        <v>63691.53</v>
       </c>
       <c r="D60" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E60" t="n">
-        <v>64011.34</v>
+        <v>63492.99</v>
       </c>
       <c r="F60" t="n">
-        <v>-1259.61</v>
+        <v>-518.35</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0081</v>
       </c>
       <c r="H60" t="n">
-        <v>1103.39</v>
+        <v>965.35</v>
       </c>
       <c r="I60" t="n">
-        <v>63102.41</v>
+        <v>62105.24</v>
       </c>
       <c r="J60" t="n">
-        <v>64457.75</v>
+        <v>63033.46</v>
       </c>
       <c r="K60" t="n">
-        <v>64728.81</v>
+        <v>63459.64</v>
       </c>
       <c r="L60" t="n">
-        <v>64999.88</v>
+        <v>63885.83</v>
       </c>
       <c r="M60" t="n">
-        <v>65813.08</v>
+        <v>64563.04</v>
       </c>
       <c r="N60" t="n">
-        <v>66626.28999999999</v>
+        <v>65240.24</v>
       </c>
       <c r="O60" t="n">
-        <v>66355.22</v>
+        <v>65415.41</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
       <c r="Q60" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
@@ -5568,71 +5570,69 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>63659.53</v>
+        <v>63190.37</v>
       </c>
       <c r="C61" t="n">
-        <v>63691.53</v>
+        <v>64101</v>
       </c>
       <c r="D61" t="n">
-        <v>62726.18</v>
+        <v>63067.18</v>
       </c>
       <c r="E61" t="n">
-        <v>63492.99</v>
+        <v>63484.1</v>
       </c>
       <c r="F61" t="n">
-        <v>-518.35</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0001</v>
       </c>
       <c r="H61" t="n">
-        <v>965.35</v>
+        <v>1033.82</v>
       </c>
       <c r="I61" t="n">
-        <v>62105.24</v>
+        <v>61760.83</v>
       </c>
       <c r="J61" t="n">
-        <v>63033.46</v>
+        <v>62669.7</v>
       </c>
       <c r="K61" t="n">
-        <v>63459.64</v>
+        <v>63010.31</v>
       </c>
       <c r="L61" t="n">
-        <v>63885.83</v>
+        <v>63350.92</v>
       </c>
       <c r="M61" t="n">
-        <v>64563.04</v>
+        <v>63975.66</v>
       </c>
       <c r="N61" t="n">
-        <v>65240.24</v>
+        <v>64600.41</v>
       </c>
       <c r="O61" t="n">
-        <v>65415.41</v>
+        <v>64656.88</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5645,58 +5645,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>63190.37</v>
+        <v>64643.58</v>
       </c>
       <c r="C62" t="n">
-        <v>64101</v>
+        <v>64643.58</v>
       </c>
       <c r="D62" t="n">
-        <v>63067.18</v>
+        <v>64003.66</v>
       </c>
       <c r="E62" t="n">
-        <v>63484.1</v>
+        <v/>
       </c>
       <c r="F62" t="n">
-        <v>-8.890000000000001</v>
+        <v/>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0001</v>
+        <v/>
       </c>
       <c r="H62" t="n">
-        <v>1033.82</v>
+        <v>639.92</v>
       </c>
       <c r="I62" t="n">
-        <v>61760.83</v>
+        <v>62033.36</v>
       </c>
       <c r="J62" t="n">
-        <v>62669.7</v>
+        <v>62400.29</v>
       </c>
       <c r="K62" t="n">
-        <v>63010.31</v>
+        <v>62967.19</v>
       </c>
       <c r="L62" t="n">
-        <v>63350.92</v>
+        <v>63534.1</v>
       </c>
       <c r="M62" t="n">
-        <v>63975.66</v>
+        <v>64001.01</v>
       </c>
       <c r="N62" t="n">
-        <v>64600.41</v>
+        <v>64467.93</v>
       </c>
       <c r="O62" t="n">
-        <v>64656.88</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
+        <v>65134.82</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q62" s="6" t="n">
         <v/>
@@ -5704,9 +5710,9 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S62" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
@@ -5714,8 +5720,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U62" s="8" t="n">
-        <v/>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5732,115 +5740,31 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>63672.13</v>
-      </c>
-      <c r="C63" t="n">
-        <v>63923</v>
-      </c>
-      <c r="D63" t="n">
-        <v>63209.92</v>
-      </c>
-      <c r="E63" t="n">
-        <v/>
-      </c>
-      <c r="F63" t="n">
-        <v/>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H63" t="n">
-        <v>713.08</v>
-      </c>
-      <c r="I63" t="n">
-        <v>62033.36</v>
-      </c>
-      <c r="J63" t="n">
-        <v>62400.29</v>
-      </c>
-      <c r="K63" t="n">
-        <v>62967.19</v>
-      </c>
-      <c r="L63" t="n">
-        <v>63534.1</v>
-      </c>
-      <c r="M63" t="n">
-        <v>64001.01</v>
-      </c>
-      <c r="N63" t="n">
-        <v>64467.93</v>
-      </c>
-      <c r="O63" t="n">
-        <v>65134.82</v>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="14" t="n">
-        <v>62496.84</v>
-      </c>
-      <c r="J64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="14" t="n">
-        <v>64636.08</v>
+      <c r="I63" s="14" t="n">
+        <v>63363.74</v>
+      </c>
+      <c r="J63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O63" s="14" t="n">
+        <v>65283.5</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5658,25 +5658,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>64643.58</v>
+        <v>63672.13</v>
       </c>
       <c r="C62" t="n">
-        <v>64643.58</v>
+        <v>63923</v>
       </c>
       <c r="D62" t="n">
-        <v>64003.66</v>
+        <v>63209.92</v>
       </c>
       <c r="E62" t="n">
-        <v/>
+        <v>63923</v>
       </c>
       <c r="F62" t="n">
-        <v/>
+        <v>438.9</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v/>
+        <v>0.0069</v>
       </c>
       <c r="H62" t="n">
-        <v>639.92</v>
+        <v>713.08</v>
       </c>
       <c r="I62" t="n">
         <v>62033.36</v>
@@ -5699,72 +5699,156 @@
       <c r="O62" t="n">
         <v>65134.82</v>
       </c>
-      <c r="P62" s="6" t="inlineStr">
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="12" t="inlineStr">
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>64643.58</v>
+      </c>
+      <c r="C63" t="n">
+        <v>64643.58</v>
+      </c>
+      <c r="D63" t="n">
+        <v>63824.56</v>
+      </c>
+      <c r="E63" t="n">
+        <v/>
+      </c>
+      <c r="F63" t="n">
+        <v/>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H63" t="n">
+        <v>819.02</v>
+      </c>
+      <c r="I63" t="n">
+        <v>62496.84</v>
+      </c>
+      <c r="J63" t="n">
+        <v>63388.19</v>
+      </c>
+      <c r="K63" t="n">
+        <v>63566.46</v>
+      </c>
+      <c r="L63" t="n">
+        <v>63744.73</v>
+      </c>
+      <c r="M63" t="n">
+        <v>64279.54</v>
+      </c>
+      <c r="N63" t="n">
+        <v>64814.35</v>
+      </c>
+      <c r="O63" t="n">
+        <v>64636.08</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="12" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="13" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="14" t="n">
-        <v>63363.74</v>
-      </c>
-      <c r="J63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O63" s="14" t="n">
-        <v>65283.5</v>
+      <c r="I64" s="14" t="n">
+        <v>63005.54</v>
+      </c>
+      <c r="J64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O64" s="14" t="n">
+        <v>65462.6</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,22 +104,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,81 +637,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71067.14999999999</v>
+        <v>72404.37</v>
       </c>
       <c r="C2" t="n">
-        <v>72831.73</v>
+        <v>72618.44</v>
       </c>
       <c r="D2" t="n">
-        <v>71009.52</v>
+        <v>69788.38</v>
       </c>
       <c r="E2" t="n">
-        <v>72353.96000000001</v>
+        <v>69788.38</v>
       </c>
       <c r="F2" t="n">
-        <v>1103.9</v>
+        <v>-2565.58</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0155</v>
+        <v>-0.0355</v>
       </c>
       <c r="H2" t="n">
-        <v>1822.2</v>
+        <v>2830.05</v>
       </c>
       <c r="I2" t="n">
-        <v>69082.96000000001</v>
+        <v>69187.32000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>69822.34</v>
+        <v>70748.42999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>70532.55</v>
+        <v>71442.86</v>
       </c>
       <c r="L2" t="n">
-        <v>71242.77</v>
+        <v>72137.28999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>71967.57000000001</v>
+        <v>73265.06</v>
       </c>
       <c r="N2" t="n">
-        <v>72692.37</v>
+        <v>74392.83</v>
       </c>
       <c r="O2" t="n">
-        <v>73388.00999999999</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+        <v>74653.92999999999</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -726,67 +721,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72404.37</v>
+        <v>69615.08</v>
       </c>
       <c r="C3" t="n">
-        <v>72618.44</v>
+        <v>70218.71000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>69788.38</v>
+        <v>68461.10000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>69788.38</v>
+        <v>69174.97</v>
       </c>
       <c r="F3" t="n">
-        <v>-2565.58</v>
+        <v>-613.41</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0355</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>2830.05</v>
+        <v>1757.61</v>
       </c>
       <c r="I3" t="n">
-        <v>69187.32000000001</v>
+        <v>66958.33</v>
       </c>
       <c r="J3" t="n">
-        <v>70748.42999999999</v>
+        <v>66250.81</v>
       </c>
       <c r="K3" t="n">
-        <v>71442.86</v>
+        <v>68373.36</v>
       </c>
       <c r="L3" t="n">
-        <v>72137.28999999999</v>
+        <v>70495.89999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>73265.06</v>
+        <v>71203.41</v>
       </c>
       <c r="N3" t="n">
-        <v>74392.83</v>
+        <v>71910.92</v>
       </c>
       <c r="O3" t="n">
-        <v>74653.92999999999</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+        <v>75448.49000000001</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -800,7 +791,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -810,50 +801,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69615.08</v>
+        <v>70114.09</v>
       </c>
       <c r="C4" t="n">
-        <v>70218.71000000001</v>
+        <v>72594.22</v>
       </c>
       <c r="D4" t="n">
-        <v>68461.10000000001</v>
+        <v>69982.67</v>
       </c>
       <c r="E4" t="n">
-        <v>69174.97</v>
+        <v>72366.34</v>
       </c>
       <c r="F4" t="n">
-        <v>-613.41</v>
+        <v>3191.38</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0461</v>
       </c>
       <c r="H4" t="n">
-        <v>1757.61</v>
+        <v>2611.55</v>
       </c>
       <c r="I4" t="n">
-        <v>66958.33</v>
+        <v>66703.49000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>66250.81</v>
+        <v>67334.89</v>
       </c>
       <c r="K4" t="n">
-        <v>68373.36</v>
+        <v>68296.16</v>
       </c>
       <c r="L4" t="n">
-        <v>70495.89999999999</v>
+        <v>69257.44</v>
       </c>
       <c r="M4" t="n">
-        <v>71203.41</v>
+        <v>70053.77</v>
       </c>
       <c r="N4" t="n">
-        <v>71910.92</v>
+        <v>70850.11</v>
       </c>
       <c r="O4" t="n">
-        <v>75448.49000000001</v>
+        <v>71976.32000000001</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -861,28 +852,32 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
-      </c>
       <c r="W4" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -890,83 +885,81 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70114.09</v>
+        <v>71587.71000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>72594.22</v>
+        <v>71786.28</v>
       </c>
       <c r="D5" t="n">
-        <v>69982.67</v>
+        <v>68639.84</v>
       </c>
       <c r="E5" t="n">
-        <v>72366.34</v>
+        <v>69360.88</v>
       </c>
       <c r="F5" t="n">
-        <v>3191.38</v>
+        <v>-3005.46</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0461</v>
+        <v>-0.0415</v>
       </c>
       <c r="H5" t="n">
-        <v>2611.55</v>
+        <v>3146.44</v>
       </c>
       <c r="I5" t="n">
-        <v>66703.49000000001</v>
+        <v>67371.12</v>
       </c>
       <c r="J5" t="n">
-        <v>67334.89</v>
+        <v>70293.75</v>
       </c>
       <c r="K5" t="n">
-        <v>68296.16</v>
+        <v>71060.57000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>69257.44</v>
+        <v>71827.39</v>
       </c>
       <c r="M5" t="n">
-        <v>70053.77</v>
+        <v>73672.12</v>
       </c>
       <c r="N5" t="n">
-        <v>70850.11</v>
+        <v>75516.84</v>
       </c>
       <c r="O5" t="n">
-        <v>71976.32000000001</v>
+        <v>75205.77</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -974,67 +967,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>71587.71000000001</v>
+        <v>69609.88</v>
       </c>
       <c r="C6" t="n">
-        <v>71786.28</v>
+        <v>69609.88</v>
       </c>
       <c r="D6" t="n">
-        <v>68639.84</v>
+        <v>67997.57000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>69360.88</v>
+        <v>69468.11</v>
       </c>
       <c r="F6" t="n">
-        <v>-3005.46</v>
+        <v>107.23</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0415</v>
+        <v>0.0015</v>
       </c>
       <c r="H6" t="n">
-        <v>3146.44</v>
+        <v>1612.31</v>
       </c>
       <c r="I6" t="n">
-        <v>67371.12</v>
+        <v>65493.41</v>
       </c>
       <c r="J6" t="n">
-        <v>70293.75</v>
+        <v>65788.36</v>
       </c>
       <c r="K6" t="n">
-        <v>71060.57000000001</v>
+        <v>67787.66</v>
       </c>
       <c r="L6" t="n">
-        <v>71827.39</v>
+        <v>69786.97</v>
       </c>
       <c r="M6" t="n">
-        <v>73672.12</v>
+        <v>70934.10000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>75516.84</v>
+        <v>72081.23</v>
       </c>
       <c r="O6" t="n">
-        <v>75205.77</v>
+        <v>74932.72</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1046,60 +1035,64 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69609.88</v>
+        <v>70085.60000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>69609.88</v>
+        <v>70667</v>
       </c>
       <c r="D7" t="n">
-        <v>67997.57000000001</v>
+        <v>69302.19</v>
       </c>
       <c r="E7" t="n">
-        <v>69468.11</v>
+        <v>70062.32000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>107.23</v>
+        <v>594.21</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0086</v>
       </c>
       <c r="H7" t="n">
-        <v>1612.31</v>
+        <v>1364.81</v>
       </c>
       <c r="I7" t="n">
-        <v>65493.41</v>
+        <v>66385.25999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>65788.36</v>
+        <v>68187.99000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>67787.66</v>
+        <v>68661.95</v>
       </c>
       <c r="L7" t="n">
-        <v>69786.97</v>
+        <v>69135.92</v>
       </c>
       <c r="M7" t="n">
-        <v>70934.10000000001</v>
+        <v>70274.27</v>
       </c>
       <c r="N7" t="n">
-        <v>72081.23</v>
+        <v>71412.61</v>
       </c>
       <c r="O7" t="n">
-        <v>74932.72</v>
+        <v>71222.2</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1112,11 +1105,13 @@
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1124,64 +1119,64 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70085.60000000001</v>
+        <v>70774.28</v>
       </c>
       <c r="C8" t="n">
-        <v>70667</v>
+        <v>71962.34</v>
       </c>
       <c r="D8" t="n">
-        <v>69302.19</v>
+        <v>70126.14</v>
       </c>
       <c r="E8" t="n">
-        <v>70062.32000000001</v>
+        <v>70474.96000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>594.21</v>
+        <v>412.64</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0059</v>
       </c>
       <c r="H8" t="n">
-        <v>1364.81</v>
+        <v>1836.2</v>
       </c>
       <c r="I8" t="n">
-        <v>66385.25999999999</v>
+        <v>67937.38</v>
       </c>
       <c r="J8" t="n">
-        <v>68187.99000000001</v>
+        <v>68736.37</v>
       </c>
       <c r="K8" t="n">
-        <v>68661.95</v>
+        <v>69379.91</v>
       </c>
       <c r="L8" t="n">
-        <v>69135.92</v>
+        <v>70023.46000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>70274.27</v>
+        <v>70744.73</v>
       </c>
       <c r="N8" t="n">
-        <v>71412.61</v>
+        <v>71466</v>
       </c>
       <c r="O8" t="n">
-        <v>71222.2</v>
+        <v>72031.81</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1192,7 +1187,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1202,13 +1197,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U8" s="8" t="n">
-        <v/>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1222,218 +1219,220 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70774.28</v>
+        <v>70039.89</v>
       </c>
       <c r="C9" t="n">
-        <v>71962.34</v>
+        <v>70081.39</v>
       </c>
       <c r="D9" t="n">
-        <v>70126.14</v>
+        <v>68676.25999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>70474.96000000001</v>
+        <v>68733.14999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>412.64</v>
+        <v>-1741.81</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0247</v>
       </c>
       <c r="H9" t="n">
-        <v>1836.2</v>
+        <v>1405.13</v>
       </c>
       <c r="I9" t="n">
-        <v>67937.38</v>
+        <v>68289.94</v>
       </c>
       <c r="J9" t="n">
-        <v>68736.37</v>
+        <v>68354.12</v>
       </c>
       <c r="K9" t="n">
-        <v>69379.91</v>
+        <v>69556.86</v>
       </c>
       <c r="L9" t="n">
-        <v>70023.46000000001</v>
+        <v>70759.60000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>70744.73</v>
+        <v>71393.06</v>
       </c>
       <c r="N9" t="n">
-        <v>71466</v>
+        <v>72026.52</v>
       </c>
       <c r="O9" t="n">
-        <v>72031.81</v>
+        <v>73798.55</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70039.89</v>
+        <v>68676.06</v>
       </c>
       <c r="C10" t="n">
-        <v>70081.39</v>
+        <v>69788.03</v>
       </c>
       <c r="D10" t="n">
-        <v>68676.25999999999</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>68733.14999999999</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-1741.81</v>
+        <v>1010.92</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0147</v>
       </c>
       <c r="H10" t="n">
-        <v>1405.13</v>
+        <v>2178.54</v>
       </c>
       <c r="I10" t="n">
-        <v>68289.94</v>
+        <v>67271.12</v>
       </c>
       <c r="J10" t="n">
-        <v>68354.12</v>
+        <v>67005.17999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>69556.86</v>
+        <v>68030.58</v>
       </c>
       <c r="L10" t="n">
-        <v>70759.60000000001</v>
+        <v>69055.99000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>71393.06</v>
+        <v>69435.71000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>72026.52</v>
+        <v>69815.44</v>
       </c>
       <c r="O10" t="n">
-        <v>73798.55</v>
+        <v>71486.52</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>68676.06</v>
+        <v>69973.34</v>
       </c>
       <c r="C11" t="n">
-        <v>69788.03</v>
+        <v>70384.59</v>
       </c>
       <c r="D11" t="n">
-        <v>67609.49000000001</v>
+        <v>68904.41</v>
       </c>
       <c r="E11" t="n">
-        <v>69744.07000000001</v>
+        <v>69737.69</v>
       </c>
       <c r="F11" t="n">
-        <v>1010.92</v>
+        <v>-6.38</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0001</v>
       </c>
       <c r="H11" t="n">
-        <v>2178.54</v>
+        <v>1480.19</v>
       </c>
       <c r="I11" t="n">
-        <v>67271.12</v>
+        <v>65430.95</v>
       </c>
       <c r="J11" t="n">
-        <v>67005.17999999999</v>
+        <v>68088.19</v>
       </c>
       <c r="K11" t="n">
-        <v>68030.58</v>
+        <v>68654.8</v>
       </c>
       <c r="L11" t="n">
-        <v>69055.99000000001</v>
+        <v>69221.42</v>
       </c>
       <c r="M11" t="n">
-        <v>69435.71000000001</v>
+        <v>70833.34</v>
       </c>
       <c r="N11" t="n">
-        <v>69815.44</v>
+        <v>72445.25999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>71486.52</v>
+        <v>71966.57000000001</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1441,100 +1440,98 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>69973.34</v>
+        <v>69460.08</v>
       </c>
       <c r="C12" t="n">
-        <v>70384.59</v>
+        <v>69957.50999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>68904.41</v>
+        <v>68003.92</v>
       </c>
       <c r="E12" t="n">
-        <v>69737.69</v>
+        <v>68256.96000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.38</v>
+        <v>-1480.73</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0212</v>
       </c>
       <c r="H12" t="n">
-        <v>1480.19</v>
+        <v>1953.59</v>
       </c>
       <c r="I12" t="n">
-        <v>65430.95</v>
+        <v>67424.22</v>
       </c>
       <c r="J12" t="n">
-        <v>68088.19</v>
+        <v>68304.09</v>
       </c>
       <c r="K12" t="n">
-        <v>68654.8</v>
+        <v>68997.59</v>
       </c>
       <c r="L12" t="n">
-        <v>69221.42</v>
+        <v>69691.09</v>
       </c>
       <c r="M12" t="n">
-        <v>70833.34</v>
+        <v>70477.78</v>
       </c>
       <c r="N12" t="n">
-        <v>72445.25999999999</v>
+        <v>71264.47</v>
       </c>
       <c r="O12" t="n">
-        <v>71966.57000000001</v>
+        <v>71864.78</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1546,79 +1543,73 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69460.08</v>
+        <v>67704.16</v>
       </c>
       <c r="C13" t="n">
-        <v>69957.50999999999</v>
+        <v>68432.67999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>68003.92</v>
+        <v>66819.05</v>
       </c>
       <c r="E13" t="n">
-        <v>68256.96000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="F13" t="n">
-        <v>-1480.73</v>
+        <v>-1437.91</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="H13" t="n">
-        <v>1953.59</v>
+        <v>1613.63</v>
       </c>
       <c r="I13" t="n">
-        <v>67424.22</v>
+        <v>66050.34</v>
       </c>
       <c r="J13" t="n">
-        <v>68304.09</v>
+        <v>65941.5</v>
       </c>
       <c r="K13" t="n">
-        <v>68997.59</v>
+        <v>67280.17</v>
       </c>
       <c r="L13" t="n">
-        <v>69691.09</v>
+        <v>68618.84</v>
       </c>
       <c r="M13" t="n">
-        <v>70477.78</v>
+        <v>69233.75</v>
       </c>
       <c r="N13" t="n">
-        <v>71264.47</v>
+        <v>69848.67</v>
       </c>
       <c r="O13" t="n">
-        <v>71864.78</v>
+        <v>71911.09</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1632,7 +1623,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1642,50 +1633,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>67704.16</v>
+        <v>67046.37</v>
       </c>
       <c r="C14" t="n">
-        <v>68432.67999999999</v>
+        <v>68447.89</v>
       </c>
       <c r="D14" t="n">
-        <v>66819.05</v>
+        <v>67008.89</v>
       </c>
       <c r="E14" t="n">
-        <v>66819.05</v>
+        <v>67743.85000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1437.91</v>
+        <v>924.8</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0211</v>
+        <v>0.0138</v>
       </c>
       <c r="H14" t="n">
-        <v>1613.63</v>
+        <v>1439</v>
       </c>
       <c r="I14" t="n">
-        <v>66050.34</v>
+        <v>65205.41</v>
       </c>
       <c r="J14" t="n">
-        <v>65941.5</v>
+        <v>64802.01</v>
       </c>
       <c r="K14" t="n">
-        <v>67280.17</v>
+        <v>66012.23</v>
       </c>
       <c r="L14" t="n">
-        <v>68618.84</v>
+        <v>67222.46000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>69233.75</v>
+        <v>67625.86</v>
       </c>
       <c r="N14" t="n">
-        <v>69848.67</v>
+        <v>68029.27</v>
       </c>
       <c r="O14" t="n">
-        <v>71911.09</v>
+        <v>70046.31</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1693,79 +1684,85 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67046.37</v>
+        <v>68526.72</v>
       </c>
       <c r="C15" t="n">
-        <v>68447.89</v>
+        <v>69374.86</v>
       </c>
       <c r="D15" t="n">
-        <v>67008.89</v>
+        <v>68271.91</v>
       </c>
       <c r="E15" t="n">
-        <v>67743.85000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F15" t="n">
-        <v>924.8</v>
+        <v>813.88</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.012</v>
       </c>
       <c r="H15" t="n">
-        <v>1439</v>
+        <v>1102.95</v>
       </c>
       <c r="I15" t="n">
-        <v>65205.41</v>
+        <v>65569.89</v>
       </c>
       <c r="J15" t="n">
-        <v>64802.01</v>
+        <v>66312.58</v>
       </c>
       <c r="K15" t="n">
-        <v>66012.23</v>
+        <v>67024.35000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>67222.46000000001</v>
+        <v>67736.12</v>
       </c>
       <c r="M15" t="n">
-        <v>67625.86</v>
+        <v>68463.35000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>68029.27</v>
+        <v>69190.58</v>
       </c>
       <c r="O15" t="n">
-        <v>70046.31</v>
+        <v>69886.89</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1776,7 +1773,7 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1794,7 +1791,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1808,155 +1805,147 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>68526.72</v>
+        <v>68410.63</v>
       </c>
       <c r="C16" t="n">
-        <v>69374.86</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>68271.91</v>
+        <v>66653.11</v>
       </c>
       <c r="E16" t="n">
-        <v>68557.73</v>
+        <v>67242.73</v>
       </c>
       <c r="F16" t="n">
-        <v>813.88</v>
+        <v>-1315</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0192</v>
       </c>
       <c r="H16" t="n">
-        <v>1102.95</v>
+        <v>2425.1</v>
       </c>
       <c r="I16" t="n">
-        <v>65569.89</v>
+        <v>67168.95</v>
       </c>
       <c r="J16" t="n">
-        <v>66312.58</v>
+        <v>67321.95</v>
       </c>
       <c r="K16" t="n">
-        <v>67024.35000000001</v>
+        <v>68006.25</v>
       </c>
       <c r="L16" t="n">
-        <v>67736.12</v>
+        <v>68690.55</v>
       </c>
       <c r="M16" t="n">
-        <v>68463.35000000001</v>
+        <v>69109.2</v>
       </c>
       <c r="N16" t="n">
-        <v>69190.58</v>
+        <v>69527.85000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>69886.89</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+        <v>70477.81</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>68410.63</v>
+        <v>67002.94</v>
       </c>
       <c r="C17" t="n">
-        <v>69078.21000000001</v>
+        <v>67800.17999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>66653.11</v>
+        <v>66268.60000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>67242.73</v>
+        <v>67743.5</v>
       </c>
       <c r="F17" t="n">
-        <v>-1315</v>
+        <v>500.77</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0074</v>
       </c>
       <c r="H17" t="n">
-        <v>2425.1</v>
+        <v>1531.58</v>
       </c>
       <c r="I17" t="n">
-        <v>67168.95</v>
+        <v>64228.01</v>
       </c>
       <c r="J17" t="n">
-        <v>67321.95</v>
+        <v>64506.16</v>
       </c>
       <c r="K17" t="n">
-        <v>68006.25</v>
+        <v>66030.17999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>68690.55</v>
+        <v>67554.19</v>
       </c>
       <c r="M17" t="n">
-        <v>69109.2</v>
+        <v>68455.28</v>
       </c>
       <c r="N17" t="n">
-        <v>69527.85000000001</v>
+        <v>69356.36</v>
       </c>
       <c r="O17" t="n">
-        <v>70477.81</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>71503.31</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1968,60 +1957,64 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>67002.94</v>
+        <v>67989.74000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>67800.17999999999</v>
+        <v>68798.24000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>66268.60000000001</v>
+        <v>67833.17</v>
       </c>
       <c r="E18" t="n">
-        <v>67743.5</v>
+        <v>68751.50999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>500.77</v>
+        <v>1008.01</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0149</v>
       </c>
       <c r="H18" t="n">
-        <v>1531.58</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>64228.01</v>
+        <v>64737.02</v>
       </c>
       <c r="J18" t="n">
-        <v>64506.16</v>
+        <v>66566.48</v>
       </c>
       <c r="K18" t="n">
-        <v>66030.17999999999</v>
+        <v>66977.71000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>67554.19</v>
+        <v>67388.95</v>
       </c>
       <c r="M18" t="n">
-        <v>68455.28</v>
+        <v>68509.28999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>69356.36</v>
+        <v>69629.63</v>
       </c>
       <c r="O18" t="n">
-        <v>71503.31</v>
+        <v>69331.75999999999</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2032,13 +2025,15 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2046,83 +2041,87 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>67989.74000000001</v>
+        <v>67900.42999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>68798.24000000001</v>
+        <v>68069.82000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>67833.17</v>
+        <v>66499.49000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>68751.50999999999</v>
+        <v>66835.53999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>1008.01</v>
+        <v>-1915.97</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0279</v>
       </c>
       <c r="H19" t="n">
-        <v>965.0700000000001</v>
+        <v>1570.33</v>
       </c>
       <c r="I19" t="n">
-        <v>64737.02</v>
+        <v>66868.10000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>66566.48</v>
+        <v>68004.34</v>
       </c>
       <c r="K19" t="n">
-        <v>66977.71000000001</v>
+        <v>68268.97</v>
       </c>
       <c r="L19" t="n">
-        <v>67388.95</v>
+        <v>68533.61</v>
       </c>
       <c r="M19" t="n">
-        <v>68509.28999999999</v>
+        <v>69234.03999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>69629.63</v>
+        <v>69934.48</v>
       </c>
       <c r="O19" t="n">
-        <v>69331.75999999999</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+        <v>69763.31</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2130,64 +2129,60 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>67900.42999999999</v>
+        <v>66339.85000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>68069.82000000001</v>
+        <v>66441.77</v>
       </c>
       <c r="D20" t="n">
-        <v>66499.49000000001</v>
+        <v>62704.6</v>
       </c>
       <c r="E20" t="n">
-        <v>66835.53999999999</v>
+        <v>64141.12</v>
       </c>
       <c r="F20" t="n">
-        <v>-1915.97</v>
+        <v>-2694.42</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0403</v>
       </c>
       <c r="H20" t="n">
-        <v>1570.33</v>
+        <v>3737.17</v>
       </c>
       <c r="I20" t="n">
-        <v>66868.10000000001</v>
+        <v>64929.16</v>
       </c>
       <c r="J20" t="n">
-        <v>68004.34</v>
+        <v>65040.65</v>
       </c>
       <c r="K20" t="n">
-        <v>68268.97</v>
+        <v>66050.38</v>
       </c>
       <c r="L20" t="n">
-        <v>68533.61</v>
+        <v>67060.10000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>69234.03999999999</v>
+        <v>67620.7</v>
       </c>
       <c r="N20" t="n">
-        <v>69934.48</v>
+        <v>68181.31</v>
       </c>
       <c r="O20" t="n">
-        <v>69763.31</v>
+        <v>69640.14999999999</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
@@ -2204,7 +2199,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2218,7 +2213,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2228,134 +2223,134 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>66339.85000000001</v>
+        <v>64544.05</v>
       </c>
       <c r="C21" t="n">
-        <v>66441.77</v>
+        <v>66232.19</v>
       </c>
       <c r="D21" t="n">
-        <v>62704.6</v>
+        <v>64203.47</v>
       </c>
       <c r="E21" t="n">
-        <v>64141.12</v>
+        <v>66232.19</v>
       </c>
       <c r="F21" t="n">
-        <v>-2694.42</v>
+        <v>2091.07</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0326</v>
       </c>
       <c r="H21" t="n">
-        <v>3737.17</v>
+        <v>2028.72</v>
       </c>
       <c r="I21" t="n">
-        <v>64929.16</v>
+        <v>58967.43</v>
       </c>
       <c r="J21" t="n">
-        <v>65040.65</v>
+        <v>60187.92</v>
       </c>
       <c r="K21" t="n">
-        <v>66050.38</v>
+        <v>62272.54</v>
       </c>
       <c r="L21" t="n">
-        <v>67060.10000000001</v>
+        <v>64357.15</v>
       </c>
       <c r="M21" t="n">
-        <v>67620.7</v>
+        <v>66009.71000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>68181.31</v>
+        <v>67662.25999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>69640.14999999999</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>70178.95</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>64544.05</v>
+        <v>66449.27</v>
       </c>
       <c r="C22" t="n">
-        <v>66232.19</v>
+        <v>67592.2</v>
       </c>
       <c r="D22" t="n">
-        <v>64203.47</v>
+        <v>65955.60000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>66232.19</v>
+        <v>66115.60000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>2091.07</v>
+        <v>-116.59</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0326</v>
+        <v>-0.0018</v>
       </c>
       <c r="H22" t="n">
-        <v>2028.72</v>
+        <v>1636.6</v>
       </c>
       <c r="I22" t="n">
-        <v>58967.43</v>
+        <v>62174.75</v>
       </c>
       <c r="J22" t="n">
-        <v>60187.92</v>
+        <v>64710.65</v>
       </c>
       <c r="K22" t="n">
-        <v>62272.54</v>
+        <v>65217.83</v>
       </c>
       <c r="L22" t="n">
-        <v>64357.15</v>
+        <v>65725.00999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>66009.71000000001</v>
+        <v>67246.55</v>
       </c>
       <c r="N22" t="n">
-        <v>67662.25999999999</v>
+        <v>68768.09</v>
       </c>
       <c r="O22" t="n">
-        <v>70178.95</v>
+        <v>68260.91</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2366,14 +2361,14 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U22" s="8" t="n">
@@ -2382,7 +2377,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2396,50 +2391,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>66449.27</v>
+        <v>66421.00999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>67592.2</v>
+        <v>67022.37</v>
       </c>
       <c r="D23" t="n">
-        <v>65955.60000000001</v>
+        <v>66208.66</v>
       </c>
       <c r="E23" t="n">
-        <v>66115.60000000001</v>
+        <v>66422.60000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-116.59</v>
+        <v>307</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0046</v>
       </c>
       <c r="H23" t="n">
-        <v>1636.6</v>
+        <v>813.71</v>
       </c>
       <c r="I23" t="n">
-        <v>62174.75</v>
+        <v>64319</v>
       </c>
       <c r="J23" t="n">
-        <v>64710.65</v>
+        <v>64149.85</v>
       </c>
       <c r="K23" t="n">
-        <v>65217.83</v>
+        <v>65297.3</v>
       </c>
       <c r="L23" t="n">
-        <v>65725.00999999999</v>
+        <v>66444.75</v>
       </c>
       <c r="M23" t="n">
-        <v>67246.55</v>
+        <v>66933.89999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>68768.09</v>
+        <v>67423.05</v>
       </c>
       <c r="O23" t="n">
-        <v>68260.91</v>
+        <v>69228.8</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2452,7 +2447,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2466,7 +2461,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2480,69 +2475,73 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>66421.00999999999</v>
+        <v>65584.25</v>
       </c>
       <c r="C24" t="n">
-        <v>67022.37</v>
+        <v>65720.81</v>
       </c>
       <c r="D24" t="n">
-        <v>66208.66</v>
+        <v>64201.03</v>
       </c>
       <c r="E24" t="n">
-        <v>66422.60000000001</v>
+        <v>64611.15</v>
       </c>
       <c r="F24" t="n">
-        <v>307</v>
+        <v>-1811.45</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0273</v>
       </c>
       <c r="H24" t="n">
-        <v>813.71</v>
+        <v>1519.78</v>
       </c>
       <c r="I24" t="n">
-        <v>64319</v>
+        <v>65394.95</v>
       </c>
       <c r="J24" t="n">
-        <v>64149.85</v>
+        <v>65512.44</v>
       </c>
       <c r="K24" t="n">
-        <v>65297.3</v>
+        <v>66015.75</v>
       </c>
       <c r="L24" t="n">
-        <v>66444.75</v>
+        <v>66519.06</v>
       </c>
       <c r="M24" t="n">
-        <v>66933.89999999999</v>
+        <v>66829.46000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>67423.05</v>
+        <v>67139.86</v>
       </c>
       <c r="O24" t="n">
-        <v>69228.8</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67836.08</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2550,83 +2549,73 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65584.25</v>
+        <v>65164.98</v>
       </c>
       <c r="C25" t="n">
-        <v>65720.81</v>
+        <v>65220.69</v>
       </c>
       <c r="D25" t="n">
-        <v>64201.03</v>
+        <v>64123.4</v>
       </c>
       <c r="E25" t="n">
-        <v>64611.15</v>
+        <v>64931.19</v>
       </c>
       <c r="F25" t="n">
-        <v>-1811.45</v>
+        <v>320.04</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.005</v>
       </c>
       <c r="H25" t="n">
-        <v>1519.78</v>
+        <v>1097.29</v>
       </c>
       <c r="I25" t="n">
-        <v>65394.95</v>
+        <v>62681.25</v>
       </c>
       <c r="J25" t="n">
-        <v>65512.44</v>
+        <v>62916.48</v>
       </c>
       <c r="K25" t="n">
-        <v>66015.75</v>
+        <v>63851.26</v>
       </c>
       <c r="L25" t="n">
-        <v>66519.06</v>
+        <v>64786.04</v>
       </c>
       <c r="M25" t="n">
-        <v>66829.46000000001</v>
+        <v>65371.04</v>
       </c>
       <c r="N25" t="n">
-        <v>67139.86</v>
+        <v>65956.03999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>67836.08</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67240.59</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2638,73 +2627,83 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>65164.98</v>
+        <v>64539.92</v>
       </c>
       <c r="C26" t="n">
-        <v>65220.69</v>
+        <v>64573.18</v>
       </c>
       <c r="D26" t="n">
-        <v>64123.4</v>
+        <v>61923.6</v>
       </c>
       <c r="E26" t="n">
-        <v>64931.19</v>
+        <v>62364.92</v>
       </c>
       <c r="F26" t="n">
-        <v>320.04</v>
+        <v>-2566.27</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0395</v>
       </c>
       <c r="H26" t="n">
-        <v>1097.29</v>
+        <v>2649.58</v>
       </c>
       <c r="I26" t="n">
-        <v>62681.25</v>
+        <v>63026.11</v>
       </c>
       <c r="J26" t="n">
-        <v>62916.48</v>
+        <v>63963.47</v>
       </c>
       <c r="K26" t="n">
-        <v>63851.26</v>
+        <v>64382.54</v>
       </c>
       <c r="L26" t="n">
-        <v>64786.04</v>
+        <v>64801.62</v>
       </c>
       <c r="M26" t="n">
-        <v>65371.04</v>
+        <v>65479.84</v>
       </c>
       <c r="N26" t="n">
-        <v>65956.03999999999</v>
+        <v>66158.06</v>
       </c>
       <c r="O26" t="n">
-        <v>67240.59</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+        <v>66317.98</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2716,81 +2715,73 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64539.92</v>
+        <v>62734.68</v>
       </c>
       <c r="C27" t="n">
-        <v>64573.18</v>
+        <v>63138.04</v>
       </c>
       <c r="D27" t="n">
-        <v>61923.6</v>
+        <v>60448.9</v>
       </c>
       <c r="E27" t="n">
-        <v>62364.92</v>
+        <v>61434.19</v>
       </c>
       <c r="F27" t="n">
-        <v>-2566.27</v>
+        <v>-930.73</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0149</v>
       </c>
       <c r="H27" t="n">
-        <v>2649.58</v>
+        <v>2689.14</v>
       </c>
       <c r="I27" t="n">
-        <v>63026.11</v>
+        <v>59274.02</v>
       </c>
       <c r="J27" t="n">
-        <v>63963.47</v>
+        <v>59273.61</v>
       </c>
       <c r="K27" t="n">
-        <v>64382.54</v>
+        <v>61040.13</v>
       </c>
       <c r="L27" t="n">
-        <v>64801.62</v>
+        <v>62806.66</v>
       </c>
       <c r="M27" t="n">
-        <v>65479.84</v>
+        <v>63689.71</v>
       </c>
       <c r="N27" t="n">
-        <v>66158.06</v>
+        <v>64572.77</v>
       </c>
       <c r="O27" t="n">
-        <v>66317.98</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>67222.75999999999</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2804,7 +2795,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2814,50 +2805,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>62734.68</v>
+        <v>61258.34</v>
       </c>
       <c r="C28" t="n">
-        <v>63138.04</v>
+        <v>62924.84</v>
       </c>
       <c r="D28" t="n">
-        <v>60448.9</v>
+        <v>61049.7</v>
       </c>
       <c r="E28" t="n">
-        <v>61434.19</v>
+        <v>61867.43</v>
       </c>
       <c r="F28" t="n">
-        <v>-930.73</v>
+        <v>433.24</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0071</v>
       </c>
       <c r="H28" t="n">
-        <v>2689.14</v>
+        <v>1875.14</v>
       </c>
       <c r="I28" t="n">
-        <v>59274.02</v>
+        <v>57759.76</v>
       </c>
       <c r="J28" t="n">
-        <v>59273.61</v>
+        <v>58565.41</v>
       </c>
       <c r="K28" t="n">
-        <v>61040.13</v>
+        <v>60089.62</v>
       </c>
       <c r="L28" t="n">
-        <v>62806.66</v>
+        <v>61613.83</v>
       </c>
       <c r="M28" t="n">
-        <v>63689.71</v>
+        <v>62778.76</v>
       </c>
       <c r="N28" t="n">
-        <v>64572.77</v>
+        <v>63943.69</v>
       </c>
       <c r="O28" t="n">
-        <v>67222.75999999999</v>
+        <v>65827.17999999999</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2865,18 +2856,18 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2884,60 +2875,64 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>61258.34</v>
+        <v>61957.1</v>
       </c>
       <c r="C29" t="n">
-        <v>62924.84</v>
+        <v>65364.73</v>
       </c>
       <c r="D29" t="n">
-        <v>61049.7</v>
+        <v>61948.23</v>
       </c>
       <c r="E29" t="n">
-        <v>61867.43</v>
+        <v>64362.02</v>
       </c>
       <c r="F29" t="n">
-        <v>433.24</v>
+        <v>2494.59</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0403</v>
       </c>
       <c r="H29" t="n">
-        <v>1875.14</v>
+        <v>3416.5</v>
       </c>
       <c r="I29" t="n">
-        <v>57759.76</v>
+        <v>59174.56</v>
       </c>
       <c r="J29" t="n">
-        <v>58565.41</v>
+        <v>59932.37</v>
       </c>
       <c r="K29" t="n">
-        <v>60089.62</v>
+        <v>60929.86</v>
       </c>
       <c r="L29" t="n">
-        <v>61613.83</v>
+        <v>61927.35</v>
       </c>
       <c r="M29" t="n">
-        <v>62778.76</v>
+        <v>62805</v>
       </c>
       <c r="N29" t="n">
-        <v>63943.69</v>
+        <v>63682.65</v>
       </c>
       <c r="O29" t="n">
-        <v>65827.17999999999</v>
+        <v>64799.98</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2948,9 +2943,9 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -2958,70 +2953,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W29" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>61957.1</v>
+        <v>63834.95</v>
       </c>
       <c r="C30" t="n">
-        <v>65364.73</v>
+        <v>63905.12</v>
       </c>
       <c r="D30" t="n">
-        <v>61948.23</v>
+        <v>62703.47</v>
       </c>
       <c r="E30" t="n">
-        <v>64362.02</v>
+        <v>63754.9</v>
       </c>
       <c r="F30" t="n">
-        <v>2494.59</v>
+        <v>-607.12</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0403</v>
+        <v>-0.0094</v>
       </c>
       <c r="H30" t="n">
-        <v>3416.5</v>
+        <v>1201.65</v>
       </c>
       <c r="I30" t="n">
-        <v>59174.56</v>
+        <v>58531.73</v>
       </c>
       <c r="J30" t="n">
-        <v>59932.37</v>
+        <v>61298.29</v>
       </c>
       <c r="K30" t="n">
-        <v>60929.86</v>
+        <v>62653.77</v>
       </c>
       <c r="L30" t="n">
-        <v>61927.35</v>
+        <v>64009.25</v>
       </c>
       <c r="M30" t="n">
-        <v>62805</v>
+        <v>66070.27</v>
       </c>
       <c r="N30" t="n">
-        <v>63682.65</v>
+        <v>68131.28999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>64799.98</v>
+        <v>68781.23</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3034,78 +3029,76 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W30" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>63834.95</v>
+        <v>63995.28</v>
       </c>
       <c r="C31" t="n">
-        <v>63905.12</v>
+        <v>64240.5</v>
       </c>
       <c r="D31" t="n">
-        <v>62703.47</v>
+        <v>62864.43</v>
       </c>
       <c r="E31" t="n">
-        <v>63754.9</v>
+        <v>63957.53</v>
       </c>
       <c r="F31" t="n">
-        <v>-607.12</v>
+        <v>202.63</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0032</v>
       </c>
       <c r="H31" t="n">
-        <v>1201.65</v>
+        <v>1376.07</v>
       </c>
       <c r="I31" t="n">
-        <v>58531.73</v>
+        <v>61501.82</v>
       </c>
       <c r="J31" t="n">
-        <v>61298.29</v>
+        <v>62778.55</v>
       </c>
       <c r="K31" t="n">
-        <v>62653.77</v>
+        <v>63154.07</v>
       </c>
       <c r="L31" t="n">
-        <v>64009.25</v>
+        <v>63529.6</v>
       </c>
       <c r="M31" t="n">
-        <v>66070.27</v>
+        <v>64355.72</v>
       </c>
       <c r="N31" t="n">
-        <v>68131.28999999999</v>
+        <v>65181.85</v>
       </c>
       <c r="O31" t="n">
-        <v>68781.23</v>
+        <v>65106.77</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3113,16 +3106,20 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3130,64 +3127,60 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>63995.28</v>
+        <v>64565.27</v>
       </c>
       <c r="C32" t="n">
-        <v>64240.5</v>
+        <v>66302.52</v>
       </c>
       <c r="D32" t="n">
-        <v>62864.43</v>
+        <v>64555.52</v>
       </c>
       <c r="E32" t="n">
-        <v>63957.53</v>
+        <v>66300.44</v>
       </c>
       <c r="F32" t="n">
-        <v>202.63</v>
+        <v>2342.91</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0366</v>
       </c>
       <c r="H32" t="n">
-        <v>1376.07</v>
+        <v>1747</v>
       </c>
       <c r="I32" t="n">
-        <v>61501.82</v>
+        <v>61488.36</v>
       </c>
       <c r="J32" t="n">
-        <v>62778.55</v>
+        <v>62783.99</v>
       </c>
       <c r="K32" t="n">
-        <v>63154.07</v>
+        <v>63269.5</v>
       </c>
       <c r="L32" t="n">
-        <v>63529.6</v>
+        <v>63755</v>
       </c>
       <c r="M32" t="n">
-        <v>64355.72</v>
+        <v>64645.57</v>
       </c>
       <c r="N32" t="n">
-        <v>65181.85</v>
+        <v>65536.13</v>
       </c>
       <c r="O32" t="n">
-        <v>65106.77</v>
+        <v>65616.57000000001</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3195,28 +3188,30 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3226,134 +3221,136 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>64565.27</v>
+        <v>65896</v>
       </c>
       <c r="C33" t="n">
-        <v>66302.52</v>
+        <v>65983.13</v>
       </c>
       <c r="D33" t="n">
-        <v>64555.52</v>
+        <v>64942.07</v>
       </c>
       <c r="E33" t="n">
-        <v>66300.44</v>
+        <v>65683.25999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>2342.91</v>
+        <v>-617.1799999999999</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0366</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>1747</v>
+        <v>1041.06</v>
       </c>
       <c r="I33" t="n">
-        <v>61488.36</v>
+        <v>62808.52</v>
       </c>
       <c r="J33" t="n">
-        <v>62783.99</v>
+        <v>64989.14</v>
       </c>
       <c r="K33" t="n">
-        <v>63269.5</v>
+        <v>65426.94</v>
       </c>
       <c r="L33" t="n">
-        <v>63755</v>
+        <v>65864.73</v>
       </c>
       <c r="M33" t="n">
-        <v>64645.57</v>
+        <v>67173.94</v>
       </c>
       <c r="N33" t="n">
-        <v>65536.13</v>
+        <v>68483.14999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>65616.57000000001</v>
+        <v>68049.53</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W33" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>65896</v>
+        <v>65746.13</v>
       </c>
       <c r="C34" t="n">
-        <v>65983.13</v>
+        <v>65990.72</v>
       </c>
       <c r="D34" t="n">
-        <v>64942.07</v>
+        <v>64651.49</v>
       </c>
       <c r="E34" t="n">
-        <v>65683.25999999999</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-617.1799999999999</v>
+        <v>-76.55</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="H34" t="n">
-        <v>1041.06</v>
+        <v>1339.23</v>
       </c>
       <c r="I34" t="n">
-        <v>62808.52</v>
+        <v>63901.01</v>
       </c>
       <c r="J34" t="n">
-        <v>64989.14</v>
+        <v>64752.52</v>
       </c>
       <c r="K34" t="n">
-        <v>65426.94</v>
+        <v>65162.73</v>
       </c>
       <c r="L34" t="n">
-        <v>65864.73</v>
+        <v>65572.92999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>67173.94</v>
+        <v>66203.78999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>68483.14999999999</v>
+        <v>66834.64999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>68049.53</v>
+        <v>67024.2</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3370,7 +3367,7 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3382,7 +3379,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3396,136 +3393,132 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>65746.13</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>65990.72</v>
+        <v>67006.84</v>
       </c>
       <c r="D35" t="n">
-        <v>64651.49</v>
+        <v>65848.58</v>
       </c>
       <c r="E35" t="n">
-        <v>65606.71000000001</v>
+        <v>66970.22</v>
       </c>
       <c r="F35" t="n">
-        <v>-76.55</v>
+        <v>1363.51</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0208</v>
       </c>
       <c r="H35" t="n">
-        <v>1339.23</v>
+        <v>1158.27</v>
       </c>
       <c r="I35" t="n">
-        <v>63901.01</v>
+        <v>63312.26</v>
       </c>
       <c r="J35" t="n">
-        <v>64752.52</v>
+        <v>64410.28</v>
       </c>
       <c r="K35" t="n">
-        <v>65162.73</v>
+        <v>64937.1</v>
       </c>
       <c r="L35" t="n">
-        <v>65572.92999999999</v>
+        <v>65463.91</v>
       </c>
       <c r="M35" t="n">
-        <v>66203.78999999999</v>
+        <v>66276.33</v>
       </c>
       <c r="N35" t="n">
-        <v>66834.64999999999</v>
+        <v>67088.75</v>
       </c>
       <c r="O35" t="n">
-        <v>67024.2</v>
+        <v>67329.95</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>65905.10000000001</v>
+        <v>66994.05</v>
       </c>
       <c r="C36" t="n">
-        <v>67006.84</v>
+        <v>67569.36</v>
       </c>
       <c r="D36" t="n">
-        <v>65848.58</v>
+        <v>66735.75999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>66970.22</v>
+        <v>67524.06</v>
       </c>
       <c r="F36" t="n">
-        <v>1363.51</v>
+        <v>553.84</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="H36" t="n">
-        <v>1158.27</v>
+        <v>833.6</v>
       </c>
       <c r="I36" t="n">
-        <v>63312.26</v>
+        <v>64690.31</v>
       </c>
       <c r="J36" t="n">
-        <v>64410.28</v>
+        <v>66083.21000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>64937.1</v>
+        <v>66391.09</v>
       </c>
       <c r="L36" t="n">
-        <v>65463.91</v>
+        <v>66698.96000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>66276.33</v>
+        <v>67549.35000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>67088.75</v>
+        <v>68399.74000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>67329.95</v>
+        <v>68165.11</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3536,25 +3529,23 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3564,50 +3555,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>66994.05</v>
+        <v>68033.17</v>
       </c>
       <c r="C37" t="n">
-        <v>67569.36</v>
+        <v>68799.71000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>66735.75999999999</v>
+        <v>68006.17</v>
       </c>
       <c r="E37" t="n">
-        <v>67524.06</v>
+        <v>68308.59</v>
       </c>
       <c r="F37" t="n">
-        <v>553.84</v>
+        <v>784.53</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0116</v>
       </c>
       <c r="H37" t="n">
-        <v>833.6</v>
+        <v>793.54</v>
       </c>
       <c r="I37" t="n">
-        <v>64690.31</v>
+        <v>65902.16</v>
       </c>
       <c r="J37" t="n">
-        <v>66083.21000000001</v>
+        <v>66876.21000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>66391.09</v>
+        <v>67107.25999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>66698.96000000001</v>
+        <v>67338.31</v>
       </c>
       <c r="M37" t="n">
-        <v>67549.35000000001</v>
+        <v>67940.86</v>
       </c>
       <c r="N37" t="n">
-        <v>68399.74000000001</v>
+        <v>68543.42</v>
       </c>
       <c r="O37" t="n">
-        <v>68165.11</v>
+        <v>68402.96000000001</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3618,23 +3609,27 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3644,50 +3639,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>68033.17</v>
+        <v>68811.17</v>
       </c>
       <c r="C38" t="n">
-        <v>68799.71000000001</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>68006.17</v>
+        <v>68471.14999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>68308.59</v>
+        <v>68713.8</v>
       </c>
       <c r="F38" t="n">
-        <v>784.53</v>
+        <v>405.2</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0059</v>
       </c>
       <c r="H38" t="n">
-        <v>793.54</v>
+        <v>1137.09</v>
       </c>
       <c r="I38" t="n">
-        <v>65902.16</v>
+        <v>67212.63</v>
       </c>
       <c r="J38" t="n">
-        <v>66876.21000000001</v>
+        <v>67467.88</v>
       </c>
       <c r="K38" t="n">
-        <v>67107.25999999999</v>
+        <v>67911.82000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>67338.31</v>
+        <v>68355.77</v>
       </c>
       <c r="M38" t="n">
-        <v>67940.86</v>
+        <v>68705.36</v>
       </c>
       <c r="N38" t="n">
-        <v>68543.42</v>
+        <v>69054.96000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>68402.96000000001</v>
+        <v>69593.25</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3698,14 +3693,14 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U38" s="8" t="inlineStr">
@@ -3715,10 +3710,10 @@
       </c>
       <c r="V38" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W38" s="9" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3728,50 +3723,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>68811.17</v>
+        <v>68882.06</v>
       </c>
       <c r="C39" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>68471.14999999999</v>
+        <v>68492.03999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>68713.8</v>
+        <v>69220.25</v>
       </c>
       <c r="F39" t="n">
-        <v>405.2</v>
+        <v>506.45</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="H39" t="n">
-        <v>1137.09</v>
+        <v>733.53</v>
       </c>
       <c r="I39" t="n">
-        <v>67212.63</v>
+        <v>67334.05</v>
       </c>
       <c r="J39" t="n">
-        <v>67467.88</v>
+        <v>67413.75</v>
       </c>
       <c r="K39" t="n">
-        <v>67911.82000000001</v>
+        <v>68145.25</v>
       </c>
       <c r="L39" t="n">
-        <v>68355.77</v>
+        <v>68876.75</v>
       </c>
       <c r="M39" t="n">
-        <v>68705.36</v>
+        <v>69282.34</v>
       </c>
       <c r="N39" t="n">
-        <v>69054.96000000001</v>
+        <v>69687.94</v>
       </c>
       <c r="O39" t="n">
-        <v>69593.25</v>
+        <v>70745.34</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3782,7 +3777,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3792,89 +3787,93 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>68882.06</v>
+        <v>68847.35000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>69225.57000000001</v>
+        <v>69093.2</v>
       </c>
       <c r="D40" t="n">
-        <v>68492.03999999999</v>
+        <v>67368.96000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>69220.25</v>
+        <v>67460.73</v>
       </c>
       <c r="F40" t="n">
-        <v>506.45</v>
+        <v>-1759.52</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0254</v>
       </c>
       <c r="H40" t="n">
-        <v>733.53</v>
+        <v>1724.24</v>
       </c>
       <c r="I40" t="n">
-        <v>67334.05</v>
+        <v>67758.50999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>67413.75</v>
+        <v>68667.44</v>
       </c>
       <c r="K40" t="n">
-        <v>68145.25</v>
+        <v>68853.48</v>
       </c>
       <c r="L40" t="n">
-        <v>68876.75</v>
+        <v>69039.53</v>
       </c>
       <c r="M40" t="n">
-        <v>69282.34</v>
+        <v>69587.02</v>
       </c>
       <c r="N40" t="n">
-        <v>69687.94</v>
+        <v>70134.5</v>
       </c>
       <c r="O40" t="n">
-        <v>70745.34</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+        <v>69959.10000000001</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3884,79 +3883,75 @@
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>68847.35000000001</v>
+        <v>66812.27</v>
       </c>
       <c r="C41" t="n">
-        <v>69093.2</v>
+        <v>66833.50999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>67368.96000000001</v>
+        <v>65133.98</v>
       </c>
       <c r="E41" t="n">
-        <v>67460.73</v>
+        <v>65326.42</v>
       </c>
       <c r="F41" t="n">
-        <v>-1759.52</v>
+        <v>-2134.3</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="H41" t="n">
-        <v>1724.24</v>
+        <v>1699.53</v>
       </c>
       <c r="I41" t="n">
-        <v>67758.50999999999</v>
+        <v>65644.72</v>
       </c>
       <c r="J41" t="n">
-        <v>68667.44</v>
+        <v>65351.31</v>
       </c>
       <c r="K41" t="n">
-        <v>68853.48</v>
+        <v>66598.61</v>
       </c>
       <c r="L41" t="n">
-        <v>69039.53</v>
+        <v>67845.89999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>69587.02</v>
+        <v>68322.85000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>70134.5</v>
+        <v>68799.78999999999</v>
       </c>
       <c r="O41" t="n">
-        <v>69959.10000000001</v>
+        <v>70817.45</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3970,7 +3965,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3980,153 +3975,155 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>66812.27</v>
+        <v>65732.78999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>66833.50999999999</v>
+        <v>66325.32000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>65133.98</v>
+        <v>65652.25</v>
       </c>
       <c r="E42" t="n">
-        <v>65326.42</v>
+        <v>66216.78999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>-2134.3</v>
+        <v>890.37</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H42" t="n">
-        <v>1699.53</v>
+        <v>673.0700000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>65644.72</v>
+        <v>63434.45</v>
       </c>
       <c r="J42" t="n">
-        <v>65351.31</v>
+        <v>63298.23</v>
       </c>
       <c r="K42" t="n">
-        <v>66598.61</v>
+        <v>64476.66</v>
       </c>
       <c r="L42" t="n">
-        <v>67845.89999999999</v>
+        <v>65655.08</v>
       </c>
       <c r="M42" t="n">
-        <v>68322.85000000001</v>
+        <v>66176.19</v>
       </c>
       <c r="N42" t="n">
-        <v>68799.78999999999</v>
+        <v>66697.28999999999</v>
       </c>
       <c r="O42" t="n">
-        <v>70817.45</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
+        <v>68533.03999999999</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>65732.78999999999</v>
+        <v>65427.69</v>
       </c>
       <c r="C43" t="n">
-        <v>66325.32000000001</v>
+        <v>66125.88</v>
       </c>
       <c r="D43" t="n">
-        <v>65652.25</v>
+        <v>65260.22</v>
       </c>
       <c r="E43" t="n">
-        <v>66216.78999999999</v>
+        <v>66016.36</v>
       </c>
       <c r="F43" t="n">
-        <v>890.37</v>
+        <v>-200.43</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.003</v>
       </c>
       <c r="H43" t="n">
-        <v>673.0700000000001</v>
+        <v>865.66</v>
       </c>
       <c r="I43" t="n">
-        <v>63434.45</v>
+        <v>64979.18</v>
       </c>
       <c r="J43" t="n">
-        <v>63298.23</v>
+        <v>65657.72</v>
       </c>
       <c r="K43" t="n">
-        <v>64476.66</v>
+        <v>65880.25</v>
       </c>
       <c r="L43" t="n">
-        <v>65655.08</v>
+        <v>66102.78999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>66176.19</v>
+        <v>66553.32000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>66697.28999999999</v>
+        <v>67003.86</v>
       </c>
       <c r="O43" t="n">
-        <v>68533.03999999999</v>
+        <v>66998.39</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4134,81 +4131,75 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>65427.69</v>
+        <v>65978.95</v>
       </c>
       <c r="C44" t="n">
-        <v>66125.88</v>
+        <v>66257.73</v>
       </c>
       <c r="D44" t="n">
-        <v>65260.22</v>
+        <v>65470.95</v>
       </c>
       <c r="E44" t="n">
-        <v>66016.36</v>
+        <v>65528.09</v>
       </c>
       <c r="F44" t="n">
-        <v>-200.43</v>
+        <v>-488.27</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0074</v>
       </c>
       <c r="H44" t="n">
-        <v>865.66</v>
+        <v>786.78</v>
       </c>
       <c r="I44" t="n">
-        <v>64979.18</v>
+        <v>64394.55</v>
       </c>
       <c r="J44" t="n">
-        <v>65657.72</v>
+        <v>65312.35</v>
       </c>
       <c r="K44" t="n">
-        <v>65880.25</v>
+        <v>65583.53</v>
       </c>
       <c r="L44" t="n">
-        <v>66102.78999999999</v>
+        <v>65854.71000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>66553.32000000001</v>
+        <v>66449.19</v>
       </c>
       <c r="N44" t="n">
-        <v>67003.86</v>
+        <v>67043.67999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>66998.39</v>
+        <v>66991.55</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q44" s="6" t="n">
+        <v/>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4220,159 +4211,163 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>65978.95</v>
+        <v>65195.26</v>
       </c>
       <c r="C45" t="n">
-        <v>66257.73</v>
+        <v>65904.24000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>65470.95</v>
+        <v>64609.47</v>
       </c>
       <c r="E45" t="n">
-        <v>65528.09</v>
+        <v>65856.42999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>-488.27</v>
+        <v>328.34</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.005</v>
       </c>
       <c r="H45" t="n">
-        <v>786.78</v>
+        <v>1294.77</v>
       </c>
       <c r="I45" t="n">
-        <v>64394.55</v>
+        <v>64684.17</v>
       </c>
       <c r="J45" t="n">
-        <v>65312.35</v>
+        <v>64573.19</v>
       </c>
       <c r="K45" t="n">
-        <v>65583.53</v>
+        <v>65134.7</v>
       </c>
       <c r="L45" t="n">
-        <v>65854.71000000001</v>
+        <v>65696.21000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>66449.19</v>
+        <v>65921.48</v>
       </c>
       <c r="N45" t="n">
-        <v>67043.67999999999</v>
+        <v>66146.74000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>66991.55</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
+        <v>67044.5</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>65195.26</v>
+        <v>65604.49000000001</v>
       </c>
       <c r="C46" t="n">
-        <v>65904.24000000001</v>
+        <v>66442.34</v>
       </c>
       <c r="D46" t="n">
-        <v>64609.47</v>
+        <v>65390.55</v>
       </c>
       <c r="E46" t="n">
-        <v>65856.42999999999</v>
+        <v>66262.16</v>
       </c>
       <c r="F46" t="n">
-        <v>328.34</v>
+        <v>405.73</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0062</v>
       </c>
       <c r="H46" t="n">
-        <v>1294.77</v>
+        <v>1051.79</v>
       </c>
       <c r="I46" t="n">
-        <v>64684.17</v>
+        <v>63314.7</v>
       </c>
       <c r="J46" t="n">
-        <v>64573.19</v>
+        <v>64861.44</v>
       </c>
       <c r="K46" t="n">
-        <v>65134.7</v>
+        <v>65209.04</v>
       </c>
       <c r="L46" t="n">
-        <v>65696.21000000001</v>
+        <v>65556.64</v>
       </c>
       <c r="M46" t="n">
-        <v>65921.48</v>
+        <v>66503.82000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>66146.74000000001</v>
+        <v>67450.99000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>67044.5</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67199.02</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
       </c>
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4388,64 +4383,64 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65604.49000000001</v>
+        <v>66775.78</v>
       </c>
       <c r="C47" t="n">
-        <v>66442.34</v>
+        <v>66954.69</v>
       </c>
       <c r="D47" t="n">
-        <v>65390.55</v>
+        <v>65782.59</v>
       </c>
       <c r="E47" t="n">
-        <v>66262.16</v>
+        <v>66131.98</v>
       </c>
       <c r="F47" t="n">
-        <v>405.73</v>
+        <v>-130.18</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.002</v>
       </c>
       <c r="H47" t="n">
-        <v>1051.79</v>
+        <v>1172.09</v>
       </c>
       <c r="I47" t="n">
-        <v>63314.7</v>
+        <v>64338.76</v>
       </c>
       <c r="J47" t="n">
-        <v>64861.44</v>
+        <v>65383.22</v>
       </c>
       <c r="K47" t="n">
-        <v>65209.04</v>
+        <v>65736.25999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>65556.64</v>
+        <v>66089.3</v>
       </c>
       <c r="M47" t="n">
-        <v>66503.82000000001</v>
+        <v>66788.05</v>
       </c>
       <c r="N47" t="n">
-        <v>67450.99000000001</v>
+        <v>67486.8</v>
       </c>
       <c r="O47" t="n">
-        <v>67199.02</v>
+        <v>67494.14</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4456,14 +4451,14 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U47" s="8" t="n">
@@ -4472,64 +4467,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>66775.78</v>
+        <v>66104.49000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>66954.69</v>
+        <v>66842.82000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>65782.59</v>
+        <v>66012.2</v>
       </c>
       <c r="E48" t="n">
-        <v>66131.98</v>
+        <v>66405.56</v>
       </c>
       <c r="F48" t="n">
-        <v>-130.18</v>
+        <v>273.59</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0041</v>
       </c>
       <c r="H48" t="n">
-        <v>1172.09</v>
+        <v>830.62</v>
       </c>
       <c r="I48" t="n">
-        <v>64338.76</v>
+        <v>64610.5</v>
       </c>
       <c r="J48" t="n">
-        <v>65383.22</v>
+        <v>64841.55</v>
       </c>
       <c r="K48" t="n">
-        <v>65736.25999999999</v>
+        <v>65545.92999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>66089.3</v>
+        <v>66250.31</v>
       </c>
       <c r="M48" t="n">
-        <v>66788.05</v>
+        <v>66718.02</v>
       </c>
       <c r="N48" t="n">
-        <v>67486.8</v>
+        <v>67185.74000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>67494.14</v>
+        <v>68126.78</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4540,7 +4535,7 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4556,7 +4551,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4570,69 +4565,73 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>66104.49000000001</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C49" t="n">
-        <v>66842.82000000001</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>66012.2</v>
+        <v>64832.1</v>
       </c>
       <c r="E49" t="n">
-        <v>66405.56</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>273.59</v>
+        <v>-93.63</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0014</v>
       </c>
       <c r="H49" t="n">
-        <v>830.62</v>
+        <v>1479.83</v>
       </c>
       <c r="I49" t="n">
-        <v>64610.5</v>
+        <v>65181.59</v>
       </c>
       <c r="J49" t="n">
-        <v>64841.55</v>
+        <v>65563.97</v>
       </c>
       <c r="K49" t="n">
-        <v>65545.92999999999</v>
+        <v>65990.25</v>
       </c>
       <c r="L49" t="n">
-        <v>66250.31</v>
+        <v>66416.53999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>66718.02</v>
+        <v>66820.87</v>
       </c>
       <c r="N49" t="n">
-        <v>67185.74000000001</v>
+        <v>67225.21000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>68126.78</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+        <v>67673.44</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4640,83 +4639,73 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65668.50999999999</v>
+        <v>65885.47</v>
       </c>
       <c r="C50" t="n">
-        <v>66311.92999999999</v>
+        <v>66525.7</v>
       </c>
       <c r="D50" t="n">
-        <v>64832.1</v>
+        <v>65576.61</v>
       </c>
       <c r="E50" t="n">
-        <v>66311.92999999999</v>
+        <v>66215.34</v>
       </c>
       <c r="F50" t="n">
-        <v>-93.63</v>
+        <v>-96.59</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0015</v>
       </c>
       <c r="H50" t="n">
-        <v>1479.83</v>
+        <v>949.09</v>
       </c>
       <c r="I50" t="n">
-        <v>65181.59</v>
+        <v>63352.27</v>
       </c>
       <c r="J50" t="n">
-        <v>65563.97</v>
+        <v>65202.06</v>
       </c>
       <c r="K50" t="n">
-        <v>65990.25</v>
+        <v>65572.02</v>
       </c>
       <c r="L50" t="n">
-        <v>66416.53999999999</v>
+        <v>65941.97</v>
       </c>
       <c r="M50" t="n">
-        <v>66820.87</v>
+        <v>67051.84</v>
       </c>
       <c r="N50" t="n">
-        <v>67225.21000000001</v>
+        <v>68161.71000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>67673.44</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67791.75999999999</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4728,73 +4717,83 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65885.47</v>
+        <v>65195.43</v>
       </c>
       <c r="C51" t="n">
-        <v>66525.7</v>
+        <v>65195.43</v>
       </c>
       <c r="D51" t="n">
-        <v>65576.61</v>
+        <v>64215.47</v>
       </c>
       <c r="E51" t="n">
-        <v>66215.34</v>
+        <v>64325.64</v>
       </c>
       <c r="F51" t="n">
-        <v>-96.59</v>
+        <v>-1889.7</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0285</v>
       </c>
       <c r="H51" t="n">
-        <v>949.09</v>
+        <v>979.96</v>
       </c>
       <c r="I51" t="n">
-        <v>63352.27</v>
+        <v>64627.52</v>
       </c>
       <c r="J51" t="n">
-        <v>65202.06</v>
+        <v>65348.34</v>
       </c>
       <c r="K51" t="n">
-        <v>65572.02</v>
+        <v>65740.8</v>
       </c>
       <c r="L51" t="n">
-        <v>65941.97</v>
+        <v>66133.25</v>
       </c>
       <c r="M51" t="n">
-        <v>67051.84</v>
+        <v>66689.89</v>
       </c>
       <c r="N51" t="n">
-        <v>68161.71000000001</v>
+        <v>67246.53</v>
       </c>
       <c r="O51" t="n">
-        <v>67791.75999999999</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+        <v>67474.8</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4806,83 +4805,75 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="C52" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="D52" t="n">
-        <v>64215.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E52" t="n">
-        <v>64325.64</v>
+        <v>64214.48</v>
       </c>
       <c r="F52" t="n">
-        <v>-1889.7</v>
+        <v>-111.16</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0017</v>
       </c>
       <c r="H52" t="n">
-        <v>979.96</v>
+        <v>952.01</v>
       </c>
       <c r="I52" t="n">
-        <v>64627.52</v>
+        <v>63235.51</v>
       </c>
       <c r="J52" t="n">
-        <v>65348.34</v>
+        <v>63155.78</v>
       </c>
       <c r="K52" t="n">
-        <v>65740.8</v>
+        <v>63835.66</v>
       </c>
       <c r="L52" t="n">
-        <v>66133.25</v>
+        <v>64515.54</v>
       </c>
       <c r="M52" t="n">
-        <v>66689.89</v>
+        <v>64815.62</v>
       </c>
       <c r="N52" t="n">
-        <v>67246.53</v>
+        <v>65115.7</v>
       </c>
       <c r="O52" t="n">
-        <v>67474.8</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66175.39</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4894,7 +4885,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4904,50 +4895,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64724.81</v>
+        <v>64498.94</v>
       </c>
       <c r="C53" t="n">
-        <v>64724.81</v>
+        <v>65182.45</v>
       </c>
       <c r="D53" t="n">
-        <v>63772.8</v>
+        <v>64228.47</v>
       </c>
       <c r="E53" t="n">
-        <v>64214.48</v>
+        <v>65020.94</v>
       </c>
       <c r="F53" t="n">
-        <v>-111.16</v>
+        <v>806.46</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="H53" t="n">
-        <v>952.01</v>
+        <v>953.98</v>
       </c>
       <c r="I53" t="n">
-        <v>63235.51</v>
+        <v>62820.79</v>
       </c>
       <c r="J53" t="n">
-        <v>63155.78</v>
+        <v>63245.31</v>
       </c>
       <c r="K53" t="n">
-        <v>63835.66</v>
+        <v>63738.48</v>
       </c>
       <c r="L53" t="n">
-        <v>64515.54</v>
+        <v>64231.64</v>
       </c>
       <c r="M53" t="n">
-        <v>64815.62</v>
+        <v>64690.48</v>
       </c>
       <c r="N53" t="n">
-        <v>65115.7</v>
+        <v>65149.33</v>
       </c>
       <c r="O53" t="n">
-        <v>66175.39</v>
+        <v>65676.82000000001</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4955,79 +4946,85 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>64498.94</v>
+        <v>65600.42</v>
       </c>
       <c r="C54" t="n">
-        <v>65182.45</v>
+        <v>66668.71000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>64228.47</v>
+        <v>65600.42</v>
       </c>
       <c r="E54" t="n">
-        <v>65020.94</v>
+        <v>66399.84</v>
       </c>
       <c r="F54" t="n">
-        <v>806.46</v>
+        <v>1378.9</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="H54" t="n">
-        <v>953.98</v>
+        <v>1068.29</v>
       </c>
       <c r="I54" t="n">
-        <v>62820.79</v>
+        <v>63274.49</v>
       </c>
       <c r="J54" t="n">
-        <v>63245.31</v>
+        <v>64224.7</v>
       </c>
       <c r="K54" t="n">
-        <v>63738.48</v>
+        <v>64543.95</v>
       </c>
       <c r="L54" t="n">
-        <v>64231.64</v>
+        <v>64863.2</v>
       </c>
       <c r="M54" t="n">
-        <v>64690.48</v>
+        <v>65497.93</v>
       </c>
       <c r="N54" t="n">
-        <v>65149.33</v>
+        <v>66132.66</v>
       </c>
       <c r="O54" t="n">
-        <v>65676.82000000001</v>
+        <v>66136.42999999999</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5038,7 +5035,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5050,171 +5047,167 @@
       </c>
       <c r="U54" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
       <c r="W54" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>65600.42</v>
+        <v>65843.69</v>
       </c>
       <c r="C55" t="n">
-        <v>66668.71000000001</v>
+        <v>66791.84</v>
       </c>
       <c r="D55" t="n">
-        <v>65600.42</v>
+        <v>65269.33</v>
       </c>
       <c r="E55" t="n">
-        <v>66399.84</v>
+        <v>65269.33</v>
       </c>
       <c r="F55" t="n">
-        <v>1378.9</v>
+        <v>-1130.52</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.017</v>
       </c>
       <c r="H55" t="n">
-        <v>1068.29</v>
+        <v>1522.52</v>
       </c>
       <c r="I55" t="n">
-        <v>63274.49</v>
+        <v>64532.13</v>
       </c>
       <c r="J55" t="n">
-        <v>64224.7</v>
+        <v>65464.19</v>
       </c>
       <c r="K55" t="n">
-        <v>64543.95</v>
+        <v>65865.7</v>
       </c>
       <c r="L55" t="n">
-        <v>64863.2</v>
+        <v>66267.21000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>65497.93</v>
+        <v>66933.99000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>66132.66</v>
+        <v>67600.77</v>
       </c>
       <c r="O55" t="n">
-        <v>66136.42999999999</v>
+        <v>67737</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>65843.69</v>
+        <v>65087.22</v>
       </c>
       <c r="C56" t="n">
-        <v>66791.84</v>
+        <v>65794.03</v>
       </c>
       <c r="D56" t="n">
-        <v>65269.33</v>
+        <v>65017.68</v>
       </c>
       <c r="E56" t="n">
-        <v>65269.33</v>
+        <v>65142.78</v>
       </c>
       <c r="F56" t="n">
-        <v>-1130.52</v>
+        <v>-126.55</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0019</v>
       </c>
       <c r="H56" t="n">
-        <v>1522.52</v>
+        <v>776.35</v>
       </c>
       <c r="I56" t="n">
-        <v>64532.13</v>
+        <v>63746.81</v>
       </c>
       <c r="J56" t="n">
-        <v>65464.19</v>
+        <v>63366.18</v>
       </c>
       <c r="K56" t="n">
-        <v>65865.7</v>
+        <v>64508.07</v>
       </c>
       <c r="L56" t="n">
-        <v>66267.21000000001</v>
+        <v>65649.96000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>66933.99000000001</v>
+        <v>66030.59</v>
       </c>
       <c r="N56" t="n">
-        <v>67600.77</v>
+        <v>66411.21000000001</v>
       </c>
       <c r="O56" t="n">
-        <v>67737</v>
+        <v>68314.36</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5226,75 +5219,77 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>65087.22</v>
+        <v>64768.53</v>
       </c>
       <c r="C57" t="n">
-        <v>65794.03</v>
+        <v>65270.95</v>
       </c>
       <c r="D57" t="n">
-        <v>65017.68</v>
+        <v>64186.68</v>
       </c>
       <c r="E57" t="n">
-        <v>65142.78</v>
+        <v>65270.95</v>
       </c>
       <c r="F57" t="n">
-        <v>-126.55</v>
+        <v>128.17</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="H57" t="n">
-        <v>776.35</v>
+        <v>1084.27</v>
       </c>
       <c r="I57" t="n">
-        <v>63746.81</v>
+        <v>64241.33</v>
       </c>
       <c r="J57" t="n">
-        <v>63366.18</v>
+        <v>64234.89</v>
       </c>
       <c r="K57" t="n">
-        <v>64508.07</v>
+        <v>64754.61</v>
       </c>
       <c r="L57" t="n">
-        <v>65649.96000000001</v>
+        <v>65274.32</v>
       </c>
       <c r="M57" t="n">
-        <v>66030.59</v>
+        <v>65530.96</v>
       </c>
       <c r="N57" t="n">
-        <v>66411.21000000001</v>
+        <v>65787.60000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>68314.36</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
+        <v>66570.38</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5308,69 +5303,71 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>64768.53</v>
+        <v>64276.82</v>
       </c>
       <c r="C58" t="n">
-        <v>65270.95</v>
+        <v>64312.02</v>
       </c>
       <c r="D58" t="n">
-        <v>64186.68</v>
+        <v>63208.63</v>
       </c>
       <c r="E58" t="n">
-        <v>65270.95</v>
+        <v>64011.34</v>
       </c>
       <c r="F58" t="n">
-        <v>128.17</v>
+        <v>-1259.61</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H58" t="n">
-        <v>1084.27</v>
+        <v>1103.39</v>
       </c>
       <c r="I58" t="n">
-        <v>64241.33</v>
+        <v>63102.41</v>
       </c>
       <c r="J58" t="n">
-        <v>64234.89</v>
+        <v>64457.75</v>
       </c>
       <c r="K58" t="n">
-        <v>64754.61</v>
+        <v>64728.81</v>
       </c>
       <c r="L58" t="n">
-        <v>65274.32</v>
+        <v>64999.88</v>
       </c>
       <c r="M58" t="n">
-        <v>65530.96</v>
+        <v>65813.08</v>
       </c>
       <c r="N58" t="n">
-        <v>65787.60000000001</v>
+        <v>66626.28999999999</v>
       </c>
       <c r="O58" t="n">
-        <v>66570.38</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66355.22</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
@@ -5378,9 +5375,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5392,79 +5389,75 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>64276.82</v>
+        <v>63659.53</v>
       </c>
       <c r="C59" t="n">
-        <v>64312.02</v>
+        <v>63691.53</v>
       </c>
       <c r="D59" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E59" t="n">
-        <v>64011.34</v>
+        <v>63492.99</v>
       </c>
       <c r="F59" t="n">
-        <v>-1259.61</v>
+        <v>-518.35</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0081</v>
       </c>
       <c r="H59" t="n">
-        <v>1103.39</v>
+        <v>965.35</v>
       </c>
       <c r="I59" t="n">
-        <v>63102.41</v>
+        <v>62105.24</v>
       </c>
       <c r="J59" t="n">
-        <v>64457.75</v>
+        <v>63033.46</v>
       </c>
       <c r="K59" t="n">
-        <v>64728.81</v>
+        <v>63459.64</v>
       </c>
       <c r="L59" t="n">
-        <v>64999.88</v>
+        <v>63885.83</v>
       </c>
       <c r="M59" t="n">
-        <v>65813.08</v>
+        <v>64563.04</v>
       </c>
       <c r="N59" t="n">
-        <v>66626.28999999999</v>
+        <v>65240.24</v>
       </c>
       <c r="O59" t="n">
-        <v>66355.22</v>
+        <v>65415.41</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5478,7 +5471,7 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5488,71 +5481,69 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>63659.53</v>
+        <v>63190.37</v>
       </c>
       <c r="C60" t="n">
-        <v>63691.53</v>
+        <v>64101</v>
       </c>
       <c r="D60" t="n">
-        <v>62726.18</v>
+        <v>63067.18</v>
       </c>
       <c r="E60" t="n">
-        <v>63492.99</v>
+        <v>63484.1</v>
       </c>
       <c r="F60" t="n">
-        <v>-518.35</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0001</v>
       </c>
       <c r="H60" t="n">
-        <v>965.35</v>
+        <v>1033.82</v>
       </c>
       <c r="I60" t="n">
-        <v>62105.24</v>
+        <v>61760.83</v>
       </c>
       <c r="J60" t="n">
-        <v>63033.46</v>
+        <v>62669.7</v>
       </c>
       <c r="K60" t="n">
-        <v>63459.64</v>
+        <v>63010.31</v>
       </c>
       <c r="L60" t="n">
-        <v>63885.83</v>
+        <v>63350.92</v>
       </c>
       <c r="M60" t="n">
-        <v>64563.04</v>
+        <v>63975.66</v>
       </c>
       <c r="N60" t="n">
-        <v>65240.24</v>
+        <v>64600.41</v>
       </c>
       <c r="O60" t="n">
-        <v>65415.41</v>
+        <v>64656.88</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5560,60 +5551,64 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>63190.37</v>
+        <v>63672.13</v>
       </c>
       <c r="C61" t="n">
-        <v>64101</v>
+        <v>63923</v>
       </c>
       <c r="D61" t="n">
-        <v>63067.18</v>
+        <v>63209.92</v>
       </c>
       <c r="E61" t="n">
-        <v>63484.1</v>
+        <v>63923</v>
       </c>
       <c r="F61" t="n">
-        <v>-8.890000000000001</v>
+        <v>438.9</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0069</v>
       </c>
       <c r="H61" t="n">
-        <v>1033.82</v>
+        <v>713.08</v>
       </c>
       <c r="I61" t="n">
-        <v>61760.83</v>
+        <v>62033.36</v>
       </c>
       <c r="J61" t="n">
-        <v>62669.7</v>
+        <v>62400.29</v>
       </c>
       <c r="K61" t="n">
-        <v>63010.31</v>
+        <v>62967.19</v>
       </c>
       <c r="L61" t="n">
-        <v>63350.92</v>
+        <v>63534.1</v>
       </c>
       <c r="M61" t="n">
-        <v>63975.66</v>
+        <v>64001.01</v>
       </c>
       <c r="N61" t="n">
-        <v>64600.41</v>
+        <v>64467.93</v>
       </c>
       <c r="O61" t="n">
-        <v>64656.88</v>
+        <v>65134.82</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5624,14 +5619,14 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U61" s="8" t="n">
@@ -5640,7 +5635,7 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5654,53 +5649,55 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>63672.13</v>
+        <v>64681.55</v>
       </c>
       <c r="C62" t="n">
-        <v>63923</v>
+        <v>64851.88</v>
       </c>
       <c r="D62" t="n">
-        <v>63209.92</v>
+        <v>64512.74</v>
       </c>
       <c r="E62" t="n">
-        <v>63923</v>
+        <v/>
       </c>
       <c r="F62" t="n">
-        <v>438.9</v>
+        <v/>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0069</v>
+        <v/>
       </c>
       <c r="H62" t="n">
-        <v>713.08</v>
+        <v>339.14</v>
       </c>
       <c r="I62" t="n">
-        <v>62033.36</v>
+        <v>62496.84</v>
       </c>
       <c r="J62" t="n">
-        <v>62400.29</v>
+        <v>63388.19</v>
       </c>
       <c r="K62" t="n">
-        <v>62967.19</v>
+        <v>63566.46</v>
       </c>
       <c r="L62" t="n">
-        <v>63534.1</v>
+        <v>63744.73</v>
       </c>
       <c r="M62" t="n">
-        <v>64001.01</v>
+        <v>64279.54</v>
       </c>
       <c r="N62" t="n">
-        <v>64467.93</v>
+        <v>64814.35</v>
       </c>
       <c r="O62" t="n">
-        <v>65134.82</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
+        <v>64636.08</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q62" s="6" t="n">
         <v/>
@@ -5708,23 +5705,27 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S62" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5733,122 +5734,6 @@
         <is>
           <t>中警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>64643.58</v>
-      </c>
-      <c r="C63" t="n">
-        <v>64643.58</v>
-      </c>
-      <c r="D63" t="n">
-        <v>63824.56</v>
-      </c>
-      <c r="E63" t="n">
-        <v/>
-      </c>
-      <c r="F63" t="n">
-        <v/>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H63" t="n">
-        <v>819.02</v>
-      </c>
-      <c r="I63" t="n">
-        <v>62496.84</v>
-      </c>
-      <c r="J63" t="n">
-        <v>63388.19</v>
-      </c>
-      <c r="K63" t="n">
-        <v>63566.46</v>
-      </c>
-      <c r="L63" t="n">
-        <v>63744.73</v>
-      </c>
-      <c r="M63" t="n">
-        <v>64279.54</v>
-      </c>
-      <c r="N63" t="n">
-        <v>64814.35</v>
-      </c>
-      <c r="O63" t="n">
-        <v>64636.08</v>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I64" s="14" t="n">
-        <v>63005.54</v>
-      </c>
-      <c r="J64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="14" t="n">
-        <v>65462.6</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5653,25 +5650,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>64681.55</v>
+        <v>64643.58</v>
       </c>
       <c r="C62" t="n">
-        <v>64851.88</v>
+        <v>64643.58</v>
       </c>
       <c r="D62" t="n">
-        <v>64512.74</v>
+        <v>63824.56</v>
       </c>
       <c r="E62" t="n">
-        <v/>
+        <v>64136.25</v>
       </c>
       <c r="F62" t="n">
-        <v/>
+        <v>213.25</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v/>
+        <v>0.0033</v>
       </c>
       <c r="H62" t="n">
-        <v>339.14</v>
+        <v>819.02</v>
       </c>
       <c r="I62" t="n">
         <v>62496.84</v>
@@ -5694,31 +5691,27 @@
       <c r="O62" t="n">
         <v>64636.08</v>
       </c>
-      <c r="P62" s="6" t="inlineStr">
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U62" s="8" t="n">
+        <v/>
       </c>
       <c r="V62" s="8" t="inlineStr">
         <is>
@@ -5732,9 +5725,91 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>64681.55</v>
+      </c>
+      <c r="C63" t="n">
+        <v>65436.57</v>
+      </c>
+      <c r="D63" t="n">
+        <v>64403.85</v>
+      </c>
+      <c r="E63" t="n">
+        <v>65018.95</v>
+      </c>
+      <c r="F63" t="n">
+        <v>882.7</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1032.72</v>
+      </c>
+      <c r="I63" t="n">
+        <v>63005.54</v>
+      </c>
+      <c r="J63" t="n">
+        <v>63268.32</v>
+      </c>
+      <c r="K63" t="n">
+        <v>63726.74</v>
+      </c>
+      <c r="L63" t="n">
+        <v>64185.16</v>
+      </c>
+      <c r="M63" t="n">
+        <v>64545.76</v>
+      </c>
+      <c r="N63" t="n">
+        <v>64906.36</v>
+      </c>
+      <c r="O63" t="n">
+        <v>65462.6</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,66 +634,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72404.37</v>
+        <v>69615.08</v>
       </c>
       <c r="C2" t="n">
-        <v>72618.44</v>
+        <v>70218.71000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>69788.38</v>
+        <v>68461.10000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>69788.38</v>
+        <v>69174.97</v>
       </c>
       <c r="F2" t="n">
-        <v>-2565.58</v>
+        <v>-613.41</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0355</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>2830.05</v>
+        <v>1757.61</v>
       </c>
       <c r="I2" t="n">
-        <v>69187.32000000001</v>
+        <v>66958.33</v>
       </c>
       <c r="J2" t="n">
-        <v>70748.42999999999</v>
+        <v>66250.81</v>
       </c>
       <c r="K2" t="n">
-        <v>71442.86</v>
+        <v>68373.36</v>
       </c>
       <c r="L2" t="n">
-        <v>72137.28999999999</v>
+        <v>70495.89999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>73265.06</v>
+        <v>71203.41</v>
       </c>
       <c r="N2" t="n">
-        <v>74392.83</v>
+        <v>71910.92</v>
       </c>
       <c r="O2" t="n">
-        <v>74653.92999999999</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>75448.49000000001</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -710,58 +706,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69615.08</v>
+        <v>70114.09</v>
       </c>
       <c r="C3" t="n">
-        <v>70218.71000000001</v>
+        <v>72594.22</v>
       </c>
       <c r="D3" t="n">
-        <v>68461.10000000001</v>
+        <v>69982.67</v>
       </c>
       <c r="E3" t="n">
-        <v>69174.97</v>
+        <v>72366.34</v>
       </c>
       <c r="F3" t="n">
-        <v>-613.41</v>
+        <v>3191.38</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0461</v>
       </c>
       <c r="H3" t="n">
-        <v>1757.61</v>
+        <v>2611.55</v>
       </c>
       <c r="I3" t="n">
-        <v>66958.33</v>
+        <v>66703.49000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>66250.81</v>
+        <v>67334.89</v>
       </c>
       <c r="K3" t="n">
-        <v>68373.36</v>
+        <v>68296.16</v>
       </c>
       <c r="L3" t="n">
-        <v>70495.89999999999</v>
+        <v>69257.44</v>
       </c>
       <c r="M3" t="n">
-        <v>71203.41</v>
+        <v>70053.77</v>
       </c>
       <c r="N3" t="n">
-        <v>71910.92</v>
+        <v>70850.11</v>
       </c>
       <c r="O3" t="n">
-        <v>75448.49000000001</v>
+        <v>71976.32000000001</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,28 +769,32 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
-      </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -798,83 +802,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70114.09</v>
+        <v>71587.71000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>72594.22</v>
+        <v>71786.28</v>
       </c>
       <c r="D4" t="n">
-        <v>69982.67</v>
+        <v>68639.84</v>
       </c>
       <c r="E4" t="n">
-        <v>72366.34</v>
+        <v>69360.88</v>
       </c>
       <c r="F4" t="n">
-        <v>3191.38</v>
+        <v>-3005.46</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0461</v>
+        <v>-0.0415</v>
       </c>
       <c r="H4" t="n">
-        <v>2611.55</v>
+        <v>3146.44</v>
       </c>
       <c r="I4" t="n">
-        <v>66703.49000000001</v>
+        <v>67371.12</v>
       </c>
       <c r="J4" t="n">
-        <v>67334.89</v>
+        <v>70293.75</v>
       </c>
       <c r="K4" t="n">
-        <v>68296.16</v>
+        <v>71060.57000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>69257.44</v>
+        <v>71827.39</v>
       </c>
       <c r="M4" t="n">
-        <v>70053.77</v>
+        <v>73672.12</v>
       </c>
       <c r="N4" t="n">
-        <v>70850.11</v>
+        <v>75516.84</v>
       </c>
       <c r="O4" t="n">
-        <v>71976.32000000001</v>
+        <v>75205.77</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
+      </c>
       <c r="W4" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -882,67 +884,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71587.71000000001</v>
+        <v>69609.88</v>
       </c>
       <c r="C5" t="n">
-        <v>71786.28</v>
+        <v>69609.88</v>
       </c>
       <c r="D5" t="n">
-        <v>68639.84</v>
+        <v>67997.57000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>69360.88</v>
+        <v>69468.11</v>
       </c>
       <c r="F5" t="n">
-        <v>-3005.46</v>
+        <v>107.23</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0415</v>
+        <v>0.0015</v>
       </c>
       <c r="H5" t="n">
-        <v>3146.44</v>
+        <v>1612.31</v>
       </c>
       <c r="I5" t="n">
-        <v>67371.12</v>
+        <v>65493.41</v>
       </c>
       <c r="J5" t="n">
-        <v>70293.75</v>
+        <v>65788.36</v>
       </c>
       <c r="K5" t="n">
-        <v>71060.57000000001</v>
+        <v>67787.66</v>
       </c>
       <c r="L5" t="n">
-        <v>71827.39</v>
+        <v>69786.97</v>
       </c>
       <c r="M5" t="n">
-        <v>73672.12</v>
+        <v>70934.10000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>75516.84</v>
+        <v>72081.23</v>
       </c>
       <c r="O5" t="n">
-        <v>75205.77</v>
+        <v>74932.72</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -954,60 +952,64 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69609.88</v>
+        <v>70085.60000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>69609.88</v>
+        <v>70667</v>
       </c>
       <c r="D6" t="n">
-        <v>67997.57000000001</v>
+        <v>69302.19</v>
       </c>
       <c r="E6" t="n">
-        <v>69468.11</v>
+        <v>70062.32000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>107.23</v>
+        <v>594.21</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0086</v>
       </c>
       <c r="H6" t="n">
-        <v>1612.31</v>
+        <v>1364.81</v>
       </c>
       <c r="I6" t="n">
-        <v>65493.41</v>
+        <v>66385.25999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>65788.36</v>
+        <v>68187.99000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>67787.66</v>
+        <v>68661.95</v>
       </c>
       <c r="L6" t="n">
-        <v>69786.97</v>
+        <v>69135.92</v>
       </c>
       <c r="M6" t="n">
-        <v>70934.10000000001</v>
+        <v>70274.27</v>
       </c>
       <c r="N6" t="n">
-        <v>72081.23</v>
+        <v>71412.61</v>
       </c>
       <c r="O6" t="n">
-        <v>74932.72</v>
+        <v>71222.2</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1018,13 +1020,15 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1032,64 +1036,64 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70085.60000000001</v>
+        <v>70774.28</v>
       </c>
       <c r="C7" t="n">
-        <v>70667</v>
+        <v>71962.34</v>
       </c>
       <c r="D7" t="n">
-        <v>69302.19</v>
+        <v>70126.14</v>
       </c>
       <c r="E7" t="n">
-        <v>70062.32000000001</v>
+        <v>70474.96000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>594.21</v>
+        <v>412.64</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0059</v>
       </c>
       <c r="H7" t="n">
-        <v>1364.81</v>
+        <v>1836.2</v>
       </c>
       <c r="I7" t="n">
-        <v>66385.25999999999</v>
+        <v>67937.38</v>
       </c>
       <c r="J7" t="n">
-        <v>68187.99000000001</v>
+        <v>68736.37</v>
       </c>
       <c r="K7" t="n">
-        <v>68661.95</v>
+        <v>69379.91</v>
       </c>
       <c r="L7" t="n">
-        <v>69135.92</v>
+        <v>70023.46000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>70274.27</v>
+        <v>70744.73</v>
       </c>
       <c r="N7" t="n">
-        <v>71412.61</v>
+        <v>71466</v>
       </c>
       <c r="O7" t="n">
-        <v>71222.2</v>
+        <v>72031.81</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1110,13 +1114,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U7" s="8" t="n">
-        <v/>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1130,218 +1136,220 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70774.28</v>
+        <v>70039.89</v>
       </c>
       <c r="C8" t="n">
-        <v>71962.34</v>
+        <v>70081.39</v>
       </c>
       <c r="D8" t="n">
-        <v>70126.14</v>
+        <v>68676.25999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>70474.96000000001</v>
+        <v>68733.14999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>412.64</v>
+        <v>-1741.81</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0247</v>
       </c>
       <c r="H8" t="n">
-        <v>1836.2</v>
+        <v>1405.13</v>
       </c>
       <c r="I8" t="n">
-        <v>67937.38</v>
+        <v>68289.94</v>
       </c>
       <c r="J8" t="n">
-        <v>68736.37</v>
+        <v>68354.12</v>
       </c>
       <c r="K8" t="n">
-        <v>69379.91</v>
+        <v>69556.86</v>
       </c>
       <c r="L8" t="n">
-        <v>70023.46000000001</v>
+        <v>70759.60000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>70744.73</v>
+        <v>71393.06</v>
       </c>
       <c r="N8" t="n">
-        <v>71466</v>
+        <v>72026.52</v>
       </c>
       <c r="O8" t="n">
-        <v>72031.81</v>
+        <v>73798.55</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70039.89</v>
+        <v>68676.06</v>
       </c>
       <c r="C9" t="n">
-        <v>70081.39</v>
+        <v>69788.03</v>
       </c>
       <c r="D9" t="n">
-        <v>68676.25999999999</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>68733.14999999999</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-1741.81</v>
+        <v>1010.92</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0147</v>
       </c>
       <c r="H9" t="n">
-        <v>1405.13</v>
+        <v>2178.54</v>
       </c>
       <c r="I9" t="n">
-        <v>68289.94</v>
+        <v>67271.12</v>
       </c>
       <c r="J9" t="n">
-        <v>68354.12</v>
+        <v>67005.17999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>69556.86</v>
+        <v>68030.58</v>
       </c>
       <c r="L9" t="n">
-        <v>70759.60000000001</v>
+        <v>69055.99000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>71393.06</v>
+        <v>69435.71000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>72026.52</v>
+        <v>69815.44</v>
       </c>
       <c r="O9" t="n">
-        <v>73798.55</v>
+        <v>71486.52</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68676.06</v>
+        <v>69973.34</v>
       </c>
       <c r="C10" t="n">
-        <v>69788.03</v>
+        <v>70384.59</v>
       </c>
       <c r="D10" t="n">
-        <v>67609.49000000001</v>
+        <v>68904.41</v>
       </c>
       <c r="E10" t="n">
-        <v>69744.07000000001</v>
+        <v>69737.69</v>
       </c>
       <c r="F10" t="n">
-        <v>1010.92</v>
+        <v>-6.38</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0001</v>
       </c>
       <c r="H10" t="n">
-        <v>2178.54</v>
+        <v>1480.19</v>
       </c>
       <c r="I10" t="n">
-        <v>67271.12</v>
+        <v>65430.95</v>
       </c>
       <c r="J10" t="n">
-        <v>67005.17999999999</v>
+        <v>68088.19</v>
       </c>
       <c r="K10" t="n">
-        <v>68030.58</v>
+        <v>68654.8</v>
       </c>
       <c r="L10" t="n">
-        <v>69055.99000000001</v>
+        <v>69221.42</v>
       </c>
       <c r="M10" t="n">
-        <v>69435.71000000001</v>
+        <v>70833.34</v>
       </c>
       <c r="N10" t="n">
-        <v>69815.44</v>
+        <v>72445.25999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>71486.52</v>
+        <v>71966.57000000001</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1349,100 +1357,98 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>69973.34</v>
+        <v>69460.08</v>
       </c>
       <c r="C11" t="n">
-        <v>70384.59</v>
+        <v>69957.50999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>68904.41</v>
+        <v>68003.92</v>
       </c>
       <c r="E11" t="n">
-        <v>69737.69</v>
+        <v>68256.96000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.38</v>
+        <v>-1480.73</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0212</v>
       </c>
       <c r="H11" t="n">
-        <v>1480.19</v>
+        <v>1953.59</v>
       </c>
       <c r="I11" t="n">
-        <v>65430.95</v>
+        <v>67424.22</v>
       </c>
       <c r="J11" t="n">
-        <v>68088.19</v>
+        <v>68304.09</v>
       </c>
       <c r="K11" t="n">
-        <v>68654.8</v>
+        <v>68997.59</v>
       </c>
       <c r="L11" t="n">
-        <v>69221.42</v>
+        <v>69691.09</v>
       </c>
       <c r="M11" t="n">
-        <v>70833.34</v>
+        <v>70477.78</v>
       </c>
       <c r="N11" t="n">
-        <v>72445.25999999999</v>
+        <v>71264.47</v>
       </c>
       <c r="O11" t="n">
-        <v>71966.57000000001</v>
+        <v>71864.78</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1454,78 +1460,72 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>69460.08</v>
+        <v>67704.16</v>
       </c>
       <c r="C12" t="n">
-        <v>69957.50999999999</v>
+        <v>68432.67999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>68003.92</v>
+        <v>66819.05</v>
       </c>
       <c r="E12" t="n">
-        <v>68256.96000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="F12" t="n">
-        <v>-1480.73</v>
+        <v>-1437.91</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="H12" t="n">
-        <v>1953.59</v>
+        <v>1613.63</v>
       </c>
       <c r="I12" t="n">
-        <v>67424.22</v>
+        <v>66050.34</v>
       </c>
       <c r="J12" t="n">
-        <v>68304.09</v>
+        <v>65941.5</v>
       </c>
       <c r="K12" t="n">
-        <v>68997.59</v>
+        <v>67280.17</v>
       </c>
       <c r="L12" t="n">
-        <v>69691.09</v>
+        <v>68618.84</v>
       </c>
       <c r="M12" t="n">
-        <v>70477.78</v>
+        <v>69233.75</v>
       </c>
       <c r="N12" t="n">
-        <v>71264.47</v>
+        <v>69848.67</v>
       </c>
       <c r="O12" t="n">
-        <v>71864.78</v>
+        <v>71911.09</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1540,7 +1540,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1550,50 +1550,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67704.16</v>
+        <v>67046.37</v>
       </c>
       <c r="C13" t="n">
-        <v>68432.67999999999</v>
+        <v>68447.89</v>
       </c>
       <c r="D13" t="n">
-        <v>66819.05</v>
+        <v>67008.89</v>
       </c>
       <c r="E13" t="n">
-        <v>66819.05</v>
+        <v>67743.85000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-1437.91</v>
+        <v>924.8</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0211</v>
+        <v>0.0138</v>
       </c>
       <c r="H13" t="n">
-        <v>1613.63</v>
+        <v>1439</v>
       </c>
       <c r="I13" t="n">
-        <v>66050.34</v>
+        <v>65205.41</v>
       </c>
       <c r="J13" t="n">
-        <v>65941.5</v>
+        <v>64802.01</v>
       </c>
       <c r="K13" t="n">
-        <v>67280.17</v>
+        <v>66012.23</v>
       </c>
       <c r="L13" t="n">
-        <v>68618.84</v>
+        <v>67222.46000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>69233.75</v>
+        <v>67625.86</v>
       </c>
       <c r="N13" t="n">
-        <v>69848.67</v>
+        <v>68029.27</v>
       </c>
       <c r="O13" t="n">
-        <v>71911.09</v>
+        <v>70046.31</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1601,79 +1601,85 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>67046.37</v>
+        <v>68526.72</v>
       </c>
       <c r="C14" t="n">
-        <v>68447.89</v>
+        <v>69374.86</v>
       </c>
       <c r="D14" t="n">
-        <v>67008.89</v>
+        <v>68271.91</v>
       </c>
       <c r="E14" t="n">
-        <v>67743.85000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F14" t="n">
-        <v>924.8</v>
+        <v>813.88</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.012</v>
       </c>
       <c r="H14" t="n">
-        <v>1439</v>
+        <v>1102.95</v>
       </c>
       <c r="I14" t="n">
-        <v>65205.41</v>
+        <v>65569.89</v>
       </c>
       <c r="J14" t="n">
-        <v>64802.01</v>
+        <v>66312.58</v>
       </c>
       <c r="K14" t="n">
-        <v>66012.23</v>
+        <v>67024.35000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>67222.46000000001</v>
+        <v>67736.12</v>
       </c>
       <c r="M14" t="n">
-        <v>67625.86</v>
+        <v>68463.35000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>68029.27</v>
+        <v>69190.58</v>
       </c>
       <c r="O14" t="n">
-        <v>70046.31</v>
+        <v>69886.89</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1702,7 +1708,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1716,155 +1722,147 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>68526.72</v>
+        <v>68410.63</v>
       </c>
       <c r="C15" t="n">
-        <v>69374.86</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>68271.91</v>
+        <v>66653.11</v>
       </c>
       <c r="E15" t="n">
-        <v>68557.73</v>
+        <v>67242.73</v>
       </c>
       <c r="F15" t="n">
-        <v>813.88</v>
+        <v>-1315</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0192</v>
       </c>
       <c r="H15" t="n">
-        <v>1102.95</v>
+        <v>2425.1</v>
       </c>
       <c r="I15" t="n">
-        <v>65569.89</v>
+        <v>67168.95</v>
       </c>
       <c r="J15" t="n">
-        <v>66312.58</v>
+        <v>67321.95</v>
       </c>
       <c r="K15" t="n">
-        <v>67024.35000000001</v>
+        <v>68006.25</v>
       </c>
       <c r="L15" t="n">
-        <v>67736.12</v>
+        <v>68690.55</v>
       </c>
       <c r="M15" t="n">
-        <v>68463.35000000001</v>
+        <v>69109.2</v>
       </c>
       <c r="N15" t="n">
-        <v>69190.58</v>
+        <v>69527.85000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>69886.89</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+        <v>70477.81</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>68410.63</v>
+        <v>67002.94</v>
       </c>
       <c r="C16" t="n">
-        <v>69078.21000000001</v>
+        <v>67800.17999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>66653.11</v>
+        <v>66268.60000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>67242.73</v>
+        <v>67743.5</v>
       </c>
       <c r="F16" t="n">
-        <v>-1315</v>
+        <v>500.77</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0074</v>
       </c>
       <c r="H16" t="n">
-        <v>2425.1</v>
+        <v>1531.58</v>
       </c>
       <c r="I16" t="n">
-        <v>67168.95</v>
+        <v>64228.01</v>
       </c>
       <c r="J16" t="n">
-        <v>67321.95</v>
+        <v>64506.16</v>
       </c>
       <c r="K16" t="n">
-        <v>68006.25</v>
+        <v>66030.17999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>68690.55</v>
+        <v>67554.19</v>
       </c>
       <c r="M16" t="n">
-        <v>69109.2</v>
+        <v>68455.28</v>
       </c>
       <c r="N16" t="n">
-        <v>69527.85000000001</v>
+        <v>69356.36</v>
       </c>
       <c r="O16" t="n">
-        <v>70477.81</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>71503.31</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1876,60 +1874,64 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>67002.94</v>
+        <v>67989.74000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>67800.17999999999</v>
+        <v>68798.24000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>66268.60000000001</v>
+        <v>67833.17</v>
       </c>
       <c r="E17" t="n">
-        <v>67743.5</v>
+        <v>68751.50999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>500.77</v>
+        <v>1008.01</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0149</v>
       </c>
       <c r="H17" t="n">
-        <v>1531.58</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>64228.01</v>
+        <v>64737.02</v>
       </c>
       <c r="J17" t="n">
-        <v>64506.16</v>
+        <v>66566.48</v>
       </c>
       <c r="K17" t="n">
-        <v>66030.17999999999</v>
+        <v>66977.71000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>67554.19</v>
+        <v>67388.95</v>
       </c>
       <c r="M17" t="n">
-        <v>68455.28</v>
+        <v>68509.28999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>69356.36</v>
+        <v>69629.63</v>
       </c>
       <c r="O17" t="n">
-        <v>71503.31</v>
+        <v>69331.75999999999</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1942,11 +1944,13 @@
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1954,148 +1958,148 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>67989.74000000001</v>
+        <v>67900.42999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>68798.24000000001</v>
+        <v>68069.82000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>67833.17</v>
+        <v>66499.49000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>68751.50999999999</v>
+        <v>66835.53999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1008.01</v>
+        <v>-1915.97</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0279</v>
       </c>
       <c r="H18" t="n">
-        <v>965.0700000000001</v>
+        <v>1570.33</v>
       </c>
       <c r="I18" t="n">
-        <v>64737.02</v>
+        <v>66868.10000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>66566.48</v>
+        <v>68004.34</v>
       </c>
       <c r="K18" t="n">
-        <v>66977.71000000001</v>
+        <v>68268.97</v>
       </c>
       <c r="L18" t="n">
-        <v>67388.95</v>
+        <v>68533.61</v>
       </c>
       <c r="M18" t="n">
-        <v>68509.28999999999</v>
+        <v>69234.03999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>69629.63</v>
+        <v>69934.48</v>
       </c>
       <c r="O18" t="n">
-        <v>69331.75999999999</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+        <v>69763.31</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>67900.42999999999</v>
+        <v>66339.85000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>68069.82000000001</v>
+        <v>66441.77</v>
       </c>
       <c r="D19" t="n">
-        <v>66499.49000000001</v>
+        <v>62704.6</v>
       </c>
       <c r="E19" t="n">
-        <v>66835.53999999999</v>
+        <v>64141.12</v>
       </c>
       <c r="F19" t="n">
-        <v>-1915.97</v>
+        <v>-2694.42</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0403</v>
       </c>
       <c r="H19" t="n">
-        <v>1570.33</v>
+        <v>3737.17</v>
       </c>
       <c r="I19" t="n">
-        <v>66868.10000000001</v>
+        <v>64929.16</v>
       </c>
       <c r="J19" t="n">
-        <v>68004.34</v>
+        <v>65040.65</v>
       </c>
       <c r="K19" t="n">
-        <v>68268.97</v>
+        <v>66050.38</v>
       </c>
       <c r="L19" t="n">
-        <v>68533.61</v>
+        <v>67060.10000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>69234.03999999999</v>
+        <v>67620.7</v>
       </c>
       <c r="N19" t="n">
-        <v>69934.48</v>
+        <v>68181.31</v>
       </c>
       <c r="O19" t="n">
-        <v>69763.31</v>
+        <v>69640.14999999999</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -2126,7 +2130,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2136,134 +2140,134 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>66339.85000000001</v>
+        <v>64544.05</v>
       </c>
       <c r="C20" t="n">
-        <v>66441.77</v>
+        <v>66232.19</v>
       </c>
       <c r="D20" t="n">
-        <v>62704.6</v>
+        <v>64203.47</v>
       </c>
       <c r="E20" t="n">
-        <v>64141.12</v>
+        <v>66232.19</v>
       </c>
       <c r="F20" t="n">
-        <v>-2694.42</v>
+        <v>2091.07</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0326</v>
       </c>
       <c r="H20" t="n">
-        <v>3737.17</v>
+        <v>2028.72</v>
       </c>
       <c r="I20" t="n">
-        <v>64929.16</v>
+        <v>58967.43</v>
       </c>
       <c r="J20" t="n">
-        <v>65040.65</v>
+        <v>60187.92</v>
       </c>
       <c r="K20" t="n">
-        <v>66050.38</v>
+        <v>62272.54</v>
       </c>
       <c r="L20" t="n">
-        <v>67060.10000000001</v>
+        <v>64357.15</v>
       </c>
       <c r="M20" t="n">
-        <v>67620.7</v>
+        <v>66009.71000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>68181.31</v>
+        <v>67662.25999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>69640.14999999999</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>70178.95</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>64544.05</v>
+        <v>66449.27</v>
       </c>
       <c r="C21" t="n">
-        <v>66232.19</v>
+        <v>67592.2</v>
       </c>
       <c r="D21" t="n">
-        <v>64203.47</v>
+        <v>65955.60000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>66232.19</v>
+        <v>66115.60000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>2091.07</v>
+        <v>-116.59</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0326</v>
+        <v>-0.0018</v>
       </c>
       <c r="H21" t="n">
-        <v>2028.72</v>
+        <v>1636.6</v>
       </c>
       <c r="I21" t="n">
-        <v>58967.43</v>
+        <v>62174.75</v>
       </c>
       <c r="J21" t="n">
-        <v>60187.92</v>
+        <v>64710.65</v>
       </c>
       <c r="K21" t="n">
-        <v>62272.54</v>
+        <v>65217.83</v>
       </c>
       <c r="L21" t="n">
-        <v>64357.15</v>
+        <v>65725.00999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>66009.71000000001</v>
+        <v>67246.55</v>
       </c>
       <c r="N21" t="n">
-        <v>67662.25999999999</v>
+        <v>68768.09</v>
       </c>
       <c r="O21" t="n">
-        <v>70178.95</v>
+        <v>68260.91</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2276,12 +2280,12 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U21" s="8" t="n">
@@ -2290,7 +2294,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2304,50 +2308,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>66449.27</v>
+        <v>66421.00999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>67592.2</v>
+        <v>67022.37</v>
       </c>
       <c r="D22" t="n">
-        <v>65955.60000000001</v>
+        <v>66208.66</v>
       </c>
       <c r="E22" t="n">
-        <v>66115.60000000001</v>
+        <v>66422.60000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-116.59</v>
+        <v>307</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0046</v>
       </c>
       <c r="H22" t="n">
-        <v>1636.6</v>
+        <v>813.71</v>
       </c>
       <c r="I22" t="n">
-        <v>62174.75</v>
+        <v>64319</v>
       </c>
       <c r="J22" t="n">
-        <v>64710.65</v>
+        <v>64149.85</v>
       </c>
       <c r="K22" t="n">
-        <v>65217.83</v>
+        <v>65297.3</v>
       </c>
       <c r="L22" t="n">
-        <v>65725.00999999999</v>
+        <v>66444.75</v>
       </c>
       <c r="M22" t="n">
-        <v>67246.55</v>
+        <v>66933.89999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>68768.09</v>
+        <v>67423.05</v>
       </c>
       <c r="O22" t="n">
-        <v>68260.91</v>
+        <v>69228.8</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2358,9 +2362,9 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2374,7 +2378,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2388,69 +2392,73 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>66421.00999999999</v>
+        <v>65584.25</v>
       </c>
       <c r="C23" t="n">
-        <v>67022.37</v>
+        <v>65720.81</v>
       </c>
       <c r="D23" t="n">
-        <v>66208.66</v>
+        <v>64201.03</v>
       </c>
       <c r="E23" t="n">
-        <v>66422.60000000001</v>
+        <v>64611.15</v>
       </c>
       <c r="F23" t="n">
-        <v>307</v>
+        <v>-1811.45</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0273</v>
       </c>
       <c r="H23" t="n">
-        <v>813.71</v>
+        <v>1519.78</v>
       </c>
       <c r="I23" t="n">
-        <v>64319</v>
+        <v>65394.95</v>
       </c>
       <c r="J23" t="n">
-        <v>64149.85</v>
+        <v>65512.44</v>
       </c>
       <c r="K23" t="n">
-        <v>65297.3</v>
+        <v>66015.75</v>
       </c>
       <c r="L23" t="n">
-        <v>66444.75</v>
+        <v>66519.06</v>
       </c>
       <c r="M23" t="n">
-        <v>66933.89999999999</v>
+        <v>66829.46000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>67423.05</v>
+        <v>67139.86</v>
       </c>
       <c r="O23" t="n">
-        <v>69228.8</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+        <v>67836.08</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2458,83 +2466,73 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>65584.25</v>
+        <v>65164.98</v>
       </c>
       <c r="C24" t="n">
-        <v>65720.81</v>
+        <v>65220.69</v>
       </c>
       <c r="D24" t="n">
-        <v>64201.03</v>
+        <v>64123.4</v>
       </c>
       <c r="E24" t="n">
-        <v>64611.15</v>
+        <v>64931.19</v>
       </c>
       <c r="F24" t="n">
-        <v>-1811.45</v>
+        <v>320.04</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.005</v>
       </c>
       <c r="H24" t="n">
-        <v>1519.78</v>
+        <v>1097.29</v>
       </c>
       <c r="I24" t="n">
-        <v>65394.95</v>
+        <v>62681.25</v>
       </c>
       <c r="J24" t="n">
-        <v>65512.44</v>
+        <v>62916.48</v>
       </c>
       <c r="K24" t="n">
-        <v>66015.75</v>
+        <v>63851.26</v>
       </c>
       <c r="L24" t="n">
-        <v>66519.06</v>
+        <v>64786.04</v>
       </c>
       <c r="M24" t="n">
-        <v>66829.46000000001</v>
+        <v>65371.04</v>
       </c>
       <c r="N24" t="n">
-        <v>67139.86</v>
+        <v>65956.03999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>67836.08</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>67240.59</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2546,73 +2544,83 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65164.98</v>
+        <v>64539.92</v>
       </c>
       <c r="C25" t="n">
-        <v>65220.69</v>
+        <v>64573.18</v>
       </c>
       <c r="D25" t="n">
-        <v>64123.4</v>
+        <v>61923.6</v>
       </c>
       <c r="E25" t="n">
-        <v>64931.19</v>
+        <v>62364.92</v>
       </c>
       <c r="F25" t="n">
-        <v>320.04</v>
+        <v>-2566.27</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0395</v>
       </c>
       <c r="H25" t="n">
-        <v>1097.29</v>
+        <v>2649.58</v>
       </c>
       <c r="I25" t="n">
-        <v>62681.25</v>
+        <v>63026.11</v>
       </c>
       <c r="J25" t="n">
-        <v>62916.48</v>
+        <v>63963.47</v>
       </c>
       <c r="K25" t="n">
-        <v>63851.26</v>
+        <v>64382.54</v>
       </c>
       <c r="L25" t="n">
-        <v>64786.04</v>
+        <v>64801.62</v>
       </c>
       <c r="M25" t="n">
-        <v>65371.04</v>
+        <v>65479.84</v>
       </c>
       <c r="N25" t="n">
-        <v>65956.03999999999</v>
+        <v>66158.06</v>
       </c>
       <c r="O25" t="n">
-        <v>67240.59</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>66317.98</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2624,80 +2632,72 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>64539.92</v>
+        <v>62734.68</v>
       </c>
       <c r="C26" t="n">
-        <v>64573.18</v>
+        <v>63138.04</v>
       </c>
       <c r="D26" t="n">
-        <v>61923.6</v>
+        <v>60448.9</v>
       </c>
       <c r="E26" t="n">
-        <v>62364.92</v>
+        <v>61434.19</v>
       </c>
       <c r="F26" t="n">
-        <v>-2566.27</v>
+        <v>-930.73</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0149</v>
       </c>
       <c r="H26" t="n">
-        <v>2649.58</v>
+        <v>2689.14</v>
       </c>
       <c r="I26" t="n">
-        <v>63026.11</v>
+        <v>59274.02</v>
       </c>
       <c r="J26" t="n">
-        <v>63963.47</v>
+        <v>59273.61</v>
       </c>
       <c r="K26" t="n">
-        <v>64382.54</v>
+        <v>61040.13</v>
       </c>
       <c r="L26" t="n">
-        <v>64801.62</v>
+        <v>62806.66</v>
       </c>
       <c r="M26" t="n">
-        <v>65479.84</v>
+        <v>63689.71</v>
       </c>
       <c r="N26" t="n">
-        <v>66158.06</v>
+        <v>64572.77</v>
       </c>
       <c r="O26" t="n">
-        <v>66317.98</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>67222.75999999999</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -2712,7 +2712,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2722,50 +2722,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>62734.68</v>
+        <v>61258.34</v>
       </c>
       <c r="C27" t="n">
-        <v>63138.04</v>
+        <v>62924.84</v>
       </c>
       <c r="D27" t="n">
-        <v>60448.9</v>
+        <v>61049.7</v>
       </c>
       <c r="E27" t="n">
-        <v>61434.19</v>
+        <v>61867.43</v>
       </c>
       <c r="F27" t="n">
-        <v>-930.73</v>
+        <v>433.24</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0071</v>
       </c>
       <c r="H27" t="n">
-        <v>2689.14</v>
+        <v>1875.14</v>
       </c>
       <c r="I27" t="n">
-        <v>59274.02</v>
+        <v>57759.76</v>
       </c>
       <c r="J27" t="n">
-        <v>59273.61</v>
+        <v>58565.41</v>
       </c>
       <c r="K27" t="n">
-        <v>61040.13</v>
+        <v>60089.62</v>
       </c>
       <c r="L27" t="n">
-        <v>62806.66</v>
+        <v>61613.83</v>
       </c>
       <c r="M27" t="n">
-        <v>63689.71</v>
+        <v>62778.76</v>
       </c>
       <c r="N27" t="n">
-        <v>64572.77</v>
+        <v>63943.69</v>
       </c>
       <c r="O27" t="n">
-        <v>67222.75999999999</v>
+        <v>65827.17999999999</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2773,18 +2773,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2792,60 +2792,64 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>61258.34</v>
+        <v>61957.1</v>
       </c>
       <c r="C28" t="n">
-        <v>62924.84</v>
+        <v>65364.73</v>
       </c>
       <c r="D28" t="n">
-        <v>61049.7</v>
+        <v>61948.23</v>
       </c>
       <c r="E28" t="n">
-        <v>61867.43</v>
+        <v>64362.02</v>
       </c>
       <c r="F28" t="n">
-        <v>433.24</v>
+        <v>2494.59</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0403</v>
       </c>
       <c r="H28" t="n">
-        <v>1875.14</v>
+        <v>3416.5</v>
       </c>
       <c r="I28" t="n">
-        <v>57759.76</v>
+        <v>59174.56</v>
       </c>
       <c r="J28" t="n">
-        <v>58565.41</v>
+        <v>59932.37</v>
       </c>
       <c r="K28" t="n">
-        <v>60089.62</v>
+        <v>60929.86</v>
       </c>
       <c r="L28" t="n">
-        <v>61613.83</v>
+        <v>61927.35</v>
       </c>
       <c r="M28" t="n">
-        <v>62778.76</v>
+        <v>62805</v>
       </c>
       <c r="N28" t="n">
-        <v>63943.69</v>
+        <v>63682.65</v>
       </c>
       <c r="O28" t="n">
-        <v>65827.17999999999</v>
+        <v>64799.98</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2858,7 +2862,7 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2866,70 +2870,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>61957.1</v>
+        <v>63834.95</v>
       </c>
       <c r="C29" t="n">
-        <v>65364.73</v>
+        <v>63905.12</v>
       </c>
       <c r="D29" t="n">
-        <v>61948.23</v>
+        <v>62703.47</v>
       </c>
       <c r="E29" t="n">
-        <v>64362.02</v>
+        <v>63754.9</v>
       </c>
       <c r="F29" t="n">
-        <v>2494.59</v>
+        <v>-607.12</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0403</v>
+        <v>-0.0094</v>
       </c>
       <c r="H29" t="n">
-        <v>3416.5</v>
+        <v>1201.65</v>
       </c>
       <c r="I29" t="n">
-        <v>59174.56</v>
+        <v>58531.73</v>
       </c>
       <c r="J29" t="n">
-        <v>59932.37</v>
+        <v>61298.29</v>
       </c>
       <c r="K29" t="n">
-        <v>60929.86</v>
+        <v>62653.77</v>
       </c>
       <c r="L29" t="n">
-        <v>61927.35</v>
+        <v>64009.25</v>
       </c>
       <c r="M29" t="n">
-        <v>62805</v>
+        <v>66070.27</v>
       </c>
       <c r="N29" t="n">
-        <v>63682.65</v>
+        <v>68131.28999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>64799.98</v>
+        <v>68781.23</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2940,80 +2944,78 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63834.95</v>
+        <v>63995.28</v>
       </c>
       <c r="C30" t="n">
-        <v>63905.12</v>
+        <v>64240.5</v>
       </c>
       <c r="D30" t="n">
-        <v>62703.47</v>
+        <v>62864.43</v>
       </c>
       <c r="E30" t="n">
-        <v>63754.9</v>
+        <v>63957.53</v>
       </c>
       <c r="F30" t="n">
-        <v>-607.12</v>
+        <v>202.63</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0032</v>
       </c>
       <c r="H30" t="n">
-        <v>1201.65</v>
+        <v>1376.07</v>
       </c>
       <c r="I30" t="n">
-        <v>58531.73</v>
+        <v>61501.82</v>
       </c>
       <c r="J30" t="n">
-        <v>61298.29</v>
+        <v>62778.55</v>
       </c>
       <c r="K30" t="n">
-        <v>62653.77</v>
+        <v>63154.07</v>
       </c>
       <c r="L30" t="n">
-        <v>64009.25</v>
+        <v>63529.6</v>
       </c>
       <c r="M30" t="n">
-        <v>66070.27</v>
+        <v>64355.72</v>
       </c>
       <c r="N30" t="n">
-        <v>68131.28999999999</v>
+        <v>65181.85</v>
       </c>
       <c r="O30" t="n">
-        <v>68781.23</v>
+        <v>65106.77</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3021,16 +3023,20 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3038,64 +3044,60 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>63995.28</v>
+        <v>64565.27</v>
       </c>
       <c r="C31" t="n">
-        <v>64240.5</v>
+        <v>66302.52</v>
       </c>
       <c r="D31" t="n">
-        <v>62864.43</v>
+        <v>64555.52</v>
       </c>
       <c r="E31" t="n">
-        <v>63957.53</v>
+        <v>66300.44</v>
       </c>
       <c r="F31" t="n">
-        <v>202.63</v>
+        <v>2342.91</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0366</v>
       </c>
       <c r="H31" t="n">
-        <v>1376.07</v>
+        <v>1747</v>
       </c>
       <c r="I31" t="n">
-        <v>61501.82</v>
+        <v>61488.36</v>
       </c>
       <c r="J31" t="n">
-        <v>62778.55</v>
+        <v>62783.99</v>
       </c>
       <c r="K31" t="n">
-        <v>63154.07</v>
+        <v>63269.5</v>
       </c>
       <c r="L31" t="n">
-        <v>63529.6</v>
+        <v>63755</v>
       </c>
       <c r="M31" t="n">
-        <v>64355.72</v>
+        <v>64645.57</v>
       </c>
       <c r="N31" t="n">
-        <v>65181.85</v>
+        <v>65536.13</v>
       </c>
       <c r="O31" t="n">
-        <v>65106.77</v>
+        <v>65616.57000000001</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3103,10 +3105,8 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
@@ -3115,16 +3115,20 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3134,134 +3138,136 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>64565.27</v>
+        <v>65896</v>
       </c>
       <c r="C32" t="n">
-        <v>66302.52</v>
+        <v>65983.13</v>
       </c>
       <c r="D32" t="n">
-        <v>64555.52</v>
+        <v>64942.07</v>
       </c>
       <c r="E32" t="n">
-        <v>66300.44</v>
+        <v>65683.25999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>2342.91</v>
+        <v>-617.1799999999999</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0366</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>1747</v>
+        <v>1041.06</v>
       </c>
       <c r="I32" t="n">
-        <v>61488.36</v>
+        <v>62808.52</v>
       </c>
       <c r="J32" t="n">
-        <v>62783.99</v>
+        <v>64989.14</v>
       </c>
       <c r="K32" t="n">
-        <v>63269.5</v>
+        <v>65426.94</v>
       </c>
       <c r="L32" t="n">
-        <v>63755</v>
+        <v>65864.73</v>
       </c>
       <c r="M32" t="n">
-        <v>64645.57</v>
+        <v>67173.94</v>
       </c>
       <c r="N32" t="n">
-        <v>65536.13</v>
+        <v>68483.14999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>65616.57000000001</v>
+        <v>68049.53</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65896</v>
+        <v>65746.13</v>
       </c>
       <c r="C33" t="n">
-        <v>65983.13</v>
+        <v>65990.72</v>
       </c>
       <c r="D33" t="n">
-        <v>64942.07</v>
+        <v>64651.49</v>
       </c>
       <c r="E33" t="n">
-        <v>65683.25999999999</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-617.1799999999999</v>
+        <v>-76.55</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="H33" t="n">
-        <v>1041.06</v>
+        <v>1339.23</v>
       </c>
       <c r="I33" t="n">
-        <v>62808.52</v>
+        <v>63901.01</v>
       </c>
       <c r="J33" t="n">
-        <v>64989.14</v>
+        <v>64752.52</v>
       </c>
       <c r="K33" t="n">
-        <v>65426.94</v>
+        <v>65162.73</v>
       </c>
       <c r="L33" t="n">
-        <v>65864.73</v>
+        <v>65572.92999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>67173.94</v>
+        <v>66203.78999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>68483.14999999999</v>
+        <v>66834.64999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>68049.53</v>
+        <v>67024.2</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3276,9 +3282,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3290,7 +3296,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3304,136 +3310,132 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>65746.13</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>65990.72</v>
+        <v>67006.84</v>
       </c>
       <c r="D34" t="n">
-        <v>64651.49</v>
+        <v>65848.58</v>
       </c>
       <c r="E34" t="n">
-        <v>65606.71000000001</v>
+        <v>66970.22</v>
       </c>
       <c r="F34" t="n">
-        <v>-76.55</v>
+        <v>1363.51</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0208</v>
       </c>
       <c r="H34" t="n">
-        <v>1339.23</v>
+        <v>1158.27</v>
       </c>
       <c r="I34" t="n">
-        <v>63901.01</v>
+        <v>63312.26</v>
       </c>
       <c r="J34" t="n">
-        <v>64752.52</v>
+        <v>64410.28</v>
       </c>
       <c r="K34" t="n">
-        <v>65162.73</v>
+        <v>64937.1</v>
       </c>
       <c r="L34" t="n">
-        <v>65572.92999999999</v>
+        <v>65463.91</v>
       </c>
       <c r="M34" t="n">
-        <v>66203.78999999999</v>
+        <v>66276.33</v>
       </c>
       <c r="N34" t="n">
-        <v>66834.64999999999</v>
+        <v>67088.75</v>
       </c>
       <c r="O34" t="n">
-        <v>67024.2</v>
+        <v>67329.95</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>65905.10000000001</v>
+        <v>66994.05</v>
       </c>
       <c r="C35" t="n">
-        <v>67006.84</v>
+        <v>67569.36</v>
       </c>
       <c r="D35" t="n">
-        <v>65848.58</v>
+        <v>66735.75999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>66970.22</v>
+        <v>67524.06</v>
       </c>
       <c r="F35" t="n">
-        <v>1363.51</v>
+        <v>553.84</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="H35" t="n">
-        <v>1158.27</v>
+        <v>833.6</v>
       </c>
       <c r="I35" t="n">
-        <v>63312.26</v>
+        <v>64690.31</v>
       </c>
       <c r="J35" t="n">
-        <v>64410.28</v>
+        <v>66083.21000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>64937.1</v>
+        <v>66391.09</v>
       </c>
       <c r="L35" t="n">
-        <v>65463.91</v>
+        <v>66698.96000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>66276.33</v>
+        <v>67549.35000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>67088.75</v>
+        <v>68399.74000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>67329.95</v>
+        <v>68165.11</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3451,18 +3453,16 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3472,50 +3472,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>66994.05</v>
+        <v>68033.17</v>
       </c>
       <c r="C36" t="n">
-        <v>67569.36</v>
+        <v>68799.71000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>66735.75999999999</v>
+        <v>68006.17</v>
       </c>
       <c r="E36" t="n">
-        <v>67524.06</v>
+        <v>68308.59</v>
       </c>
       <c r="F36" t="n">
-        <v>553.84</v>
+        <v>784.53</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0116</v>
       </c>
       <c r="H36" t="n">
-        <v>833.6</v>
+        <v>793.54</v>
       </c>
       <c r="I36" t="n">
-        <v>64690.31</v>
+        <v>65902.16</v>
       </c>
       <c r="J36" t="n">
-        <v>66083.21000000001</v>
+        <v>66876.21000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>66391.09</v>
+        <v>67107.25999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>66698.96000000001</v>
+        <v>67338.31</v>
       </c>
       <c r="M36" t="n">
-        <v>67549.35000000001</v>
+        <v>67940.86</v>
       </c>
       <c r="N36" t="n">
-        <v>68399.74000000001</v>
+        <v>68543.42</v>
       </c>
       <c r="O36" t="n">
-        <v>68165.11</v>
+        <v>68402.96000000001</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3533,16 +3533,20 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3552,50 +3556,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>68033.17</v>
+        <v>68811.17</v>
       </c>
       <c r="C37" t="n">
-        <v>68799.71000000001</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>68006.17</v>
+        <v>68471.14999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>68308.59</v>
+        <v>68713.8</v>
       </c>
       <c r="F37" t="n">
-        <v>784.53</v>
+        <v>405.2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0059</v>
       </c>
       <c r="H37" t="n">
-        <v>793.54</v>
+        <v>1137.09</v>
       </c>
       <c r="I37" t="n">
-        <v>65902.16</v>
+        <v>67212.63</v>
       </c>
       <c r="J37" t="n">
-        <v>66876.21000000001</v>
+        <v>67467.88</v>
       </c>
       <c r="K37" t="n">
-        <v>67107.25999999999</v>
+        <v>67911.82000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>67338.31</v>
+        <v>68355.77</v>
       </c>
       <c r="M37" t="n">
-        <v>67940.86</v>
+        <v>68705.36</v>
       </c>
       <c r="N37" t="n">
-        <v>68543.42</v>
+        <v>69054.96000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>68402.96000000001</v>
+        <v>69593.25</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3613,7 +3617,7 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U37" s="8" t="inlineStr">
@@ -3623,10 +3627,10 @@
       </c>
       <c r="V37" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W37" s="11" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3636,50 +3640,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>68811.17</v>
+        <v>68882.06</v>
       </c>
       <c r="C38" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>68471.14999999999</v>
+        <v>68492.03999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>68713.8</v>
+        <v>69220.25</v>
       </c>
       <c r="F38" t="n">
-        <v>405.2</v>
+        <v>506.45</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="H38" t="n">
-        <v>1137.09</v>
+        <v>733.53</v>
       </c>
       <c r="I38" t="n">
-        <v>67212.63</v>
+        <v>67334.05</v>
       </c>
       <c r="J38" t="n">
-        <v>67467.88</v>
+        <v>67413.75</v>
       </c>
       <c r="K38" t="n">
-        <v>67911.82000000001</v>
+        <v>68145.25</v>
       </c>
       <c r="L38" t="n">
-        <v>68355.77</v>
+        <v>68876.75</v>
       </c>
       <c r="M38" t="n">
-        <v>68705.36</v>
+        <v>69282.34</v>
       </c>
       <c r="N38" t="n">
-        <v>69054.96000000001</v>
+        <v>69687.94</v>
       </c>
       <c r="O38" t="n">
-        <v>69593.25</v>
+        <v>70745.34</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3700,90 +3704,94 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>68882.06</v>
+        <v>68847.35000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>69225.57000000001</v>
+        <v>69093.2</v>
       </c>
       <c r="D39" t="n">
-        <v>68492.03999999999</v>
+        <v>67368.96000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>69220.25</v>
+        <v>67460.73</v>
       </c>
       <c r="F39" t="n">
-        <v>506.45</v>
+        <v>-1759.52</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0254</v>
       </c>
       <c r="H39" t="n">
-        <v>733.53</v>
+        <v>1724.24</v>
       </c>
       <c r="I39" t="n">
-        <v>67334.05</v>
+        <v>67758.50999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>67413.75</v>
+        <v>68667.44</v>
       </c>
       <c r="K39" t="n">
-        <v>68145.25</v>
+        <v>68853.48</v>
       </c>
       <c r="L39" t="n">
-        <v>68876.75</v>
+        <v>69039.53</v>
       </c>
       <c r="M39" t="n">
-        <v>69282.34</v>
+        <v>69587.02</v>
       </c>
       <c r="N39" t="n">
-        <v>69687.94</v>
+        <v>70134.5</v>
       </c>
       <c r="O39" t="n">
-        <v>70745.34</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+        <v>69959.10000000001</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3792,73 +3800,69 @@
       </c>
       <c r="W39" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>68847.35000000001</v>
+        <v>66812.27</v>
       </c>
       <c r="C40" t="n">
-        <v>69093.2</v>
+        <v>66833.50999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>67368.96000000001</v>
+        <v>65133.98</v>
       </c>
       <c r="E40" t="n">
-        <v>67460.73</v>
+        <v>65326.42</v>
       </c>
       <c r="F40" t="n">
-        <v>-1759.52</v>
+        <v>-2134.3</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="H40" t="n">
-        <v>1724.24</v>
+        <v>1699.53</v>
       </c>
       <c r="I40" t="n">
-        <v>67758.50999999999</v>
+        <v>65644.72</v>
       </c>
       <c r="J40" t="n">
-        <v>68667.44</v>
+        <v>65351.31</v>
       </c>
       <c r="K40" t="n">
-        <v>68853.48</v>
+        <v>66598.61</v>
       </c>
       <c r="L40" t="n">
-        <v>69039.53</v>
+        <v>67845.89999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>69587.02</v>
+        <v>68322.85000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>70134.5</v>
+        <v>68799.78999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>69959.10000000001</v>
+        <v>70817.45</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -3878,7 +3882,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3888,153 +3892,155 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>66812.27</v>
+        <v>65732.78999999999</v>
       </c>
       <c r="C41" t="n">
-        <v>66833.50999999999</v>
+        <v>66325.32000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>65133.98</v>
+        <v>65652.25</v>
       </c>
       <c r="E41" t="n">
-        <v>65326.42</v>
+        <v>66216.78999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>-2134.3</v>
+        <v>890.37</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H41" t="n">
-        <v>1699.53</v>
+        <v>673.0700000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>65644.72</v>
+        <v>63434.45</v>
       </c>
       <c r="J41" t="n">
-        <v>65351.31</v>
+        <v>63298.23</v>
       </c>
       <c r="K41" t="n">
-        <v>66598.61</v>
+        <v>64476.66</v>
       </c>
       <c r="L41" t="n">
-        <v>67845.89999999999</v>
+        <v>65655.08</v>
       </c>
       <c r="M41" t="n">
-        <v>68322.85000000001</v>
+        <v>66176.19</v>
       </c>
       <c r="N41" t="n">
-        <v>68799.78999999999</v>
+        <v>66697.28999999999</v>
       </c>
       <c r="O41" t="n">
-        <v>70817.45</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
+        <v>68533.03999999999</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>65732.78999999999</v>
+        <v>65427.69</v>
       </c>
       <c r="C42" t="n">
-        <v>66325.32000000001</v>
+        <v>66125.88</v>
       </c>
       <c r="D42" t="n">
-        <v>65652.25</v>
+        <v>65260.22</v>
       </c>
       <c r="E42" t="n">
-        <v>66216.78999999999</v>
+        <v>66016.36</v>
       </c>
       <c r="F42" t="n">
-        <v>890.37</v>
+        <v>-200.43</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.003</v>
       </c>
       <c r="H42" t="n">
-        <v>673.0700000000001</v>
+        <v>865.66</v>
       </c>
       <c r="I42" t="n">
-        <v>63434.45</v>
+        <v>64979.18</v>
       </c>
       <c r="J42" t="n">
-        <v>63298.23</v>
+        <v>65657.72</v>
       </c>
       <c r="K42" t="n">
-        <v>64476.66</v>
+        <v>65880.25</v>
       </c>
       <c r="L42" t="n">
-        <v>65655.08</v>
+        <v>66102.78999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>66176.19</v>
+        <v>66553.32000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>66697.28999999999</v>
+        <v>67003.86</v>
       </c>
       <c r="O42" t="n">
-        <v>68533.03999999999</v>
+        <v>66998.39</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4042,81 +4048,75 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>65427.69</v>
+        <v>65978.95</v>
       </c>
       <c r="C43" t="n">
-        <v>66125.88</v>
+        <v>66257.73</v>
       </c>
       <c r="D43" t="n">
-        <v>65260.22</v>
+        <v>65470.95</v>
       </c>
       <c r="E43" t="n">
-        <v>66016.36</v>
+        <v>65528.09</v>
       </c>
       <c r="F43" t="n">
-        <v>-200.43</v>
+        <v>-488.27</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0074</v>
       </c>
       <c r="H43" t="n">
-        <v>865.66</v>
+        <v>786.78</v>
       </c>
       <c r="I43" t="n">
-        <v>64979.18</v>
+        <v>64394.55</v>
       </c>
       <c r="J43" t="n">
-        <v>65657.72</v>
+        <v>65312.35</v>
       </c>
       <c r="K43" t="n">
-        <v>65880.25</v>
+        <v>65583.53</v>
       </c>
       <c r="L43" t="n">
-        <v>66102.78999999999</v>
+        <v>65854.71000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>66553.32000000001</v>
+        <v>66449.19</v>
       </c>
       <c r="N43" t="n">
-        <v>67003.86</v>
+        <v>67043.67999999999</v>
       </c>
       <c r="O43" t="n">
-        <v>66998.39</v>
+        <v>66991.55</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q43" s="6" t="n">
+        <v/>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4128,157 +4128,161 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>65978.95</v>
+        <v>65195.26</v>
       </c>
       <c r="C44" t="n">
-        <v>66257.73</v>
+        <v>65904.24000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>65470.95</v>
+        <v>64609.47</v>
       </c>
       <c r="E44" t="n">
-        <v>65528.09</v>
+        <v>65856.42999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>-488.27</v>
+        <v>328.34</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.005</v>
       </c>
       <c r="H44" t="n">
-        <v>786.78</v>
+        <v>1294.77</v>
       </c>
       <c r="I44" t="n">
-        <v>64394.55</v>
+        <v>64684.17</v>
       </c>
       <c r="J44" t="n">
-        <v>65312.35</v>
+        <v>64573.19</v>
       </c>
       <c r="K44" t="n">
-        <v>65583.53</v>
+        <v>65134.7</v>
       </c>
       <c r="L44" t="n">
-        <v>65854.71000000001</v>
+        <v>65696.21000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>66449.19</v>
+        <v>65921.48</v>
       </c>
       <c r="N44" t="n">
-        <v>67043.67999999999</v>
+        <v>66146.74000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>66991.55</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
+        <v>67044.5</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>65195.26</v>
+        <v>65604.49000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>65904.24000000001</v>
+        <v>66442.34</v>
       </c>
       <c r="D45" t="n">
-        <v>64609.47</v>
+        <v>65390.55</v>
       </c>
       <c r="E45" t="n">
-        <v>65856.42999999999</v>
+        <v>66262.16</v>
       </c>
       <c r="F45" t="n">
-        <v>328.34</v>
+        <v>405.73</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0062</v>
       </c>
       <c r="H45" t="n">
-        <v>1294.77</v>
+        <v>1051.79</v>
       </c>
       <c r="I45" t="n">
-        <v>64684.17</v>
+        <v>63314.7</v>
       </c>
       <c r="J45" t="n">
-        <v>64573.19</v>
+        <v>64861.44</v>
       </c>
       <c r="K45" t="n">
-        <v>65134.7</v>
+        <v>65209.04</v>
       </c>
       <c r="L45" t="n">
-        <v>65696.21000000001</v>
+        <v>65556.64</v>
       </c>
       <c r="M45" t="n">
-        <v>65921.48</v>
+        <v>66503.82000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>66146.74000000001</v>
+        <v>67450.99000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>67044.5</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67199.02</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
       </c>
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
@@ -4296,64 +4300,64 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>65604.49000000001</v>
+        <v>66775.78</v>
       </c>
       <c r="C46" t="n">
-        <v>66442.34</v>
+        <v>66954.69</v>
       </c>
       <c r="D46" t="n">
-        <v>65390.55</v>
+        <v>65782.59</v>
       </c>
       <c r="E46" t="n">
-        <v>66262.16</v>
+        <v>66131.98</v>
       </c>
       <c r="F46" t="n">
-        <v>405.73</v>
+        <v>-130.18</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.002</v>
       </c>
       <c r="H46" t="n">
-        <v>1051.79</v>
+        <v>1172.09</v>
       </c>
       <c r="I46" t="n">
-        <v>63314.7</v>
+        <v>64338.76</v>
       </c>
       <c r="J46" t="n">
-        <v>64861.44</v>
+        <v>65383.22</v>
       </c>
       <c r="K46" t="n">
-        <v>65209.04</v>
+        <v>65736.25999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>65556.64</v>
+        <v>66089.3</v>
       </c>
       <c r="M46" t="n">
-        <v>66503.82000000001</v>
+        <v>66788.05</v>
       </c>
       <c r="N46" t="n">
-        <v>67450.99000000001</v>
+        <v>67486.8</v>
       </c>
       <c r="O46" t="n">
-        <v>67199.02</v>
+        <v>67494.14</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4366,12 +4370,12 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U46" s="8" t="n">
@@ -4380,64 +4384,64 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>66775.78</v>
+        <v>66104.49000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>66954.69</v>
+        <v>66842.82000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>65782.59</v>
+        <v>66012.2</v>
       </c>
       <c r="E47" t="n">
-        <v>66131.98</v>
+        <v>66405.56</v>
       </c>
       <c r="F47" t="n">
-        <v>-130.18</v>
+        <v>273.59</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0041</v>
       </c>
       <c r="H47" t="n">
-        <v>1172.09</v>
+        <v>830.62</v>
       </c>
       <c r="I47" t="n">
-        <v>64338.76</v>
+        <v>64610.5</v>
       </c>
       <c r="J47" t="n">
-        <v>65383.22</v>
+        <v>64841.55</v>
       </c>
       <c r="K47" t="n">
-        <v>65736.25999999999</v>
+        <v>65545.92999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>66089.3</v>
+        <v>66250.31</v>
       </c>
       <c r="M47" t="n">
-        <v>66788.05</v>
+        <v>66718.02</v>
       </c>
       <c r="N47" t="n">
-        <v>67486.8</v>
+        <v>67185.74000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>67494.14</v>
+        <v>68126.78</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4464,7 +4468,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4478,69 +4482,73 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>66104.49000000001</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C48" t="n">
-        <v>66842.82000000001</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>66012.2</v>
+        <v>64832.1</v>
       </c>
       <c r="E48" t="n">
-        <v>66405.56</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>273.59</v>
+        <v>-93.63</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0014</v>
       </c>
       <c r="H48" t="n">
-        <v>830.62</v>
+        <v>1479.83</v>
       </c>
       <c r="I48" t="n">
-        <v>64610.5</v>
+        <v>65181.59</v>
       </c>
       <c r="J48" t="n">
-        <v>64841.55</v>
+        <v>65563.97</v>
       </c>
       <c r="K48" t="n">
-        <v>65545.92999999999</v>
+        <v>65990.25</v>
       </c>
       <c r="L48" t="n">
-        <v>66250.31</v>
+        <v>66416.53999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>66718.02</v>
+        <v>66820.87</v>
       </c>
       <c r="N48" t="n">
-        <v>67185.74000000001</v>
+        <v>67225.21000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>68126.78</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67673.44</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4548,83 +4556,73 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65668.50999999999</v>
+        <v>65885.47</v>
       </c>
       <c r="C49" t="n">
-        <v>66311.92999999999</v>
+        <v>66525.7</v>
       </c>
       <c r="D49" t="n">
-        <v>64832.1</v>
+        <v>65576.61</v>
       </c>
       <c r="E49" t="n">
-        <v>66311.92999999999</v>
+        <v>66215.34</v>
       </c>
       <c r="F49" t="n">
-        <v>-93.63</v>
+        <v>-96.59</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0015</v>
       </c>
       <c r="H49" t="n">
-        <v>1479.83</v>
+        <v>949.09</v>
       </c>
       <c r="I49" t="n">
-        <v>65181.59</v>
+        <v>63352.27</v>
       </c>
       <c r="J49" t="n">
-        <v>65563.97</v>
+        <v>65202.06</v>
       </c>
       <c r="K49" t="n">
-        <v>65990.25</v>
+        <v>65572.02</v>
       </c>
       <c r="L49" t="n">
-        <v>66416.53999999999</v>
+        <v>65941.97</v>
       </c>
       <c r="M49" t="n">
-        <v>66820.87</v>
+        <v>67051.84</v>
       </c>
       <c r="N49" t="n">
-        <v>67225.21000000001</v>
+        <v>68161.71000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>67673.44</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>67791.75999999999</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4636,73 +4634,83 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65885.47</v>
+        <v>65195.43</v>
       </c>
       <c r="C50" t="n">
-        <v>66525.7</v>
+        <v>65195.43</v>
       </c>
       <c r="D50" t="n">
-        <v>65576.61</v>
+        <v>64215.47</v>
       </c>
       <c r="E50" t="n">
-        <v>66215.34</v>
+        <v>64325.64</v>
       </c>
       <c r="F50" t="n">
-        <v>-96.59</v>
+        <v>-1889.7</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0285</v>
       </c>
       <c r="H50" t="n">
-        <v>949.09</v>
+        <v>979.96</v>
       </c>
       <c r="I50" t="n">
-        <v>63352.27</v>
+        <v>64627.52</v>
       </c>
       <c r="J50" t="n">
-        <v>65202.06</v>
+        <v>65348.34</v>
       </c>
       <c r="K50" t="n">
-        <v>65572.02</v>
+        <v>65740.8</v>
       </c>
       <c r="L50" t="n">
-        <v>65941.97</v>
+        <v>66133.25</v>
       </c>
       <c r="M50" t="n">
-        <v>67051.84</v>
+        <v>66689.89</v>
       </c>
       <c r="N50" t="n">
-        <v>68161.71000000001</v>
+        <v>67246.53</v>
       </c>
       <c r="O50" t="n">
-        <v>67791.75999999999</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>67474.8</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4714,74 +4722,66 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="C51" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="D51" t="n">
-        <v>64215.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E51" t="n">
-        <v>64325.64</v>
+        <v>64214.48</v>
       </c>
       <c r="F51" t="n">
-        <v>-1889.7</v>
+        <v>-111.16</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0017</v>
       </c>
       <c r="H51" t="n">
-        <v>979.96</v>
+        <v>952.01</v>
       </c>
       <c r="I51" t="n">
-        <v>64627.52</v>
+        <v>63235.51</v>
       </c>
       <c r="J51" t="n">
-        <v>65348.34</v>
+        <v>63155.78</v>
       </c>
       <c r="K51" t="n">
-        <v>65740.8</v>
+        <v>63835.66</v>
       </c>
       <c r="L51" t="n">
-        <v>66133.25</v>
+        <v>64515.54</v>
       </c>
       <c r="M51" t="n">
-        <v>66689.89</v>
+        <v>64815.62</v>
       </c>
       <c r="N51" t="n">
-        <v>67246.53</v>
+        <v>65115.7</v>
       </c>
       <c r="O51" t="n">
-        <v>67474.8</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66175.39</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4802,7 +4802,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4812,50 +4812,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>64724.81</v>
+        <v>64498.94</v>
       </c>
       <c r="C52" t="n">
-        <v>64724.81</v>
+        <v>65182.45</v>
       </c>
       <c r="D52" t="n">
-        <v>63772.8</v>
+        <v>64228.47</v>
       </c>
       <c r="E52" t="n">
-        <v>64214.48</v>
+        <v>65020.94</v>
       </c>
       <c r="F52" t="n">
-        <v>-111.16</v>
+        <v>806.46</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="H52" t="n">
-        <v>952.01</v>
+        <v>953.98</v>
       </c>
       <c r="I52" t="n">
-        <v>63235.51</v>
+        <v>62820.79</v>
       </c>
       <c r="J52" t="n">
-        <v>63155.78</v>
+        <v>63245.31</v>
       </c>
       <c r="K52" t="n">
-        <v>63835.66</v>
+        <v>63738.48</v>
       </c>
       <c r="L52" t="n">
-        <v>64515.54</v>
+        <v>64231.64</v>
       </c>
       <c r="M52" t="n">
-        <v>64815.62</v>
+        <v>64690.48</v>
       </c>
       <c r="N52" t="n">
-        <v>65115.7</v>
+        <v>65149.33</v>
       </c>
       <c r="O52" t="n">
-        <v>66175.39</v>
+        <v>65676.82000000001</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4863,79 +4863,85 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64498.94</v>
+        <v>65600.42</v>
       </c>
       <c r="C53" t="n">
-        <v>65182.45</v>
+        <v>66668.71000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>64228.47</v>
+        <v>65600.42</v>
       </c>
       <c r="E53" t="n">
-        <v>65020.94</v>
+        <v>66399.84</v>
       </c>
       <c r="F53" t="n">
-        <v>806.46</v>
+        <v>1378.9</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="H53" t="n">
-        <v>953.98</v>
+        <v>1068.29</v>
       </c>
       <c r="I53" t="n">
-        <v>62820.79</v>
+        <v>63274.49</v>
       </c>
       <c r="J53" t="n">
-        <v>63245.31</v>
+        <v>64224.7</v>
       </c>
       <c r="K53" t="n">
-        <v>63738.48</v>
+        <v>64543.95</v>
       </c>
       <c r="L53" t="n">
-        <v>64231.64</v>
+        <v>64863.2</v>
       </c>
       <c r="M53" t="n">
-        <v>64690.48</v>
+        <v>65497.93</v>
       </c>
       <c r="N53" t="n">
-        <v>65149.33</v>
+        <v>66132.66</v>
       </c>
       <c r="O53" t="n">
-        <v>65676.82000000001</v>
+        <v>66136.42999999999</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4958,171 +4964,167 @@
       </c>
       <c r="U53" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>65600.42</v>
+        <v>65843.69</v>
       </c>
       <c r="C54" t="n">
-        <v>66668.71000000001</v>
+        <v>66791.84</v>
       </c>
       <c r="D54" t="n">
-        <v>65600.42</v>
+        <v>65269.33</v>
       </c>
       <c r="E54" t="n">
-        <v>66399.84</v>
+        <v>65269.33</v>
       </c>
       <c r="F54" t="n">
-        <v>1378.9</v>
+        <v>-1130.52</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.017</v>
       </c>
       <c r="H54" t="n">
-        <v>1068.29</v>
+        <v>1522.52</v>
       </c>
       <c r="I54" t="n">
-        <v>63274.49</v>
+        <v>64532.13</v>
       </c>
       <c r="J54" t="n">
-        <v>64224.7</v>
+        <v>65464.19</v>
       </c>
       <c r="K54" t="n">
-        <v>64543.95</v>
+        <v>65865.7</v>
       </c>
       <c r="L54" t="n">
-        <v>64863.2</v>
+        <v>66267.21000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>65497.93</v>
+        <v>66933.99000000001</v>
       </c>
       <c r="N54" t="n">
-        <v>66132.66</v>
+        <v>67600.77</v>
       </c>
       <c r="O54" t="n">
-        <v>66136.42999999999</v>
+        <v>67737</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
+      <c r="Q54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
+      </c>
       <c r="W54" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>65843.69</v>
+        <v>65087.22</v>
       </c>
       <c r="C55" t="n">
-        <v>66791.84</v>
+        <v>65794.03</v>
       </c>
       <c r="D55" t="n">
-        <v>65269.33</v>
+        <v>65017.68</v>
       </c>
       <c r="E55" t="n">
-        <v>65269.33</v>
+        <v>65142.78</v>
       </c>
       <c r="F55" t="n">
-        <v>-1130.52</v>
+        <v>-126.55</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0019</v>
       </c>
       <c r="H55" t="n">
-        <v>1522.52</v>
+        <v>776.35</v>
       </c>
       <c r="I55" t="n">
-        <v>64532.13</v>
+        <v>63746.81</v>
       </c>
       <c r="J55" t="n">
-        <v>65464.19</v>
+        <v>63366.18</v>
       </c>
       <c r="K55" t="n">
-        <v>65865.7</v>
+        <v>64508.07</v>
       </c>
       <c r="L55" t="n">
-        <v>66267.21000000001</v>
+        <v>65649.96000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>66933.99000000001</v>
+        <v>66030.59</v>
       </c>
       <c r="N55" t="n">
-        <v>67600.77</v>
+        <v>66411.21000000001</v>
       </c>
       <c r="O55" t="n">
-        <v>67737</v>
+        <v>68314.36</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5134,73 +5136,75 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>65087.22</v>
+        <v>64768.53</v>
       </c>
       <c r="C56" t="n">
-        <v>65794.03</v>
+        <v>65270.95</v>
       </c>
       <c r="D56" t="n">
-        <v>65017.68</v>
+        <v>64186.68</v>
       </c>
       <c r="E56" t="n">
-        <v>65142.78</v>
+        <v>65270.95</v>
       </c>
       <c r="F56" t="n">
-        <v>-126.55</v>
+        <v>128.17</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="H56" t="n">
-        <v>776.35</v>
+        <v>1084.27</v>
       </c>
       <c r="I56" t="n">
-        <v>63746.81</v>
+        <v>64241.33</v>
       </c>
       <c r="J56" t="n">
-        <v>63366.18</v>
+        <v>64234.89</v>
       </c>
       <c r="K56" t="n">
-        <v>64508.07</v>
+        <v>64754.61</v>
       </c>
       <c r="L56" t="n">
-        <v>65649.96000000001</v>
+        <v>65274.32</v>
       </c>
       <c r="M56" t="n">
-        <v>66030.59</v>
+        <v>65530.96</v>
       </c>
       <c r="N56" t="n">
-        <v>66411.21000000001</v>
+        <v>65787.60000000001</v>
       </c>
       <c r="O56" t="n">
-        <v>68314.36</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+        <v>66570.38</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
@@ -5216,69 +5220,71 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>64768.53</v>
+        <v>64276.82</v>
       </c>
       <c r="C57" t="n">
-        <v>65270.95</v>
+        <v>64312.02</v>
       </c>
       <c r="D57" t="n">
-        <v>64186.68</v>
+        <v>63208.63</v>
       </c>
       <c r="E57" t="n">
-        <v>65270.95</v>
+        <v>64011.34</v>
       </c>
       <c r="F57" t="n">
-        <v>128.17</v>
+        <v>-1259.61</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H57" t="n">
-        <v>1084.27</v>
+        <v>1103.39</v>
       </c>
       <c r="I57" t="n">
-        <v>64241.33</v>
+        <v>63102.41</v>
       </c>
       <c r="J57" t="n">
-        <v>64234.89</v>
+        <v>64457.75</v>
       </c>
       <c r="K57" t="n">
-        <v>64754.61</v>
+        <v>64728.81</v>
       </c>
       <c r="L57" t="n">
-        <v>65274.32</v>
+        <v>64999.88</v>
       </c>
       <c r="M57" t="n">
-        <v>65530.96</v>
+        <v>65813.08</v>
       </c>
       <c r="N57" t="n">
-        <v>65787.60000000001</v>
+        <v>66626.28999999999</v>
       </c>
       <c r="O57" t="n">
-        <v>66570.38</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66355.22</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
@@ -5288,7 +5294,7 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5300,78 +5306,74 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>64276.82</v>
+        <v>63659.53</v>
       </c>
       <c r="C58" t="n">
-        <v>64312.02</v>
+        <v>63691.53</v>
       </c>
       <c r="D58" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E58" t="n">
-        <v>64011.34</v>
+        <v>63492.99</v>
       </c>
       <c r="F58" t="n">
-        <v>-1259.61</v>
+        <v>-518.35</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0081</v>
       </c>
       <c r="H58" t="n">
-        <v>1103.39</v>
+        <v>965.35</v>
       </c>
       <c r="I58" t="n">
-        <v>63102.41</v>
+        <v>62105.24</v>
       </c>
       <c r="J58" t="n">
-        <v>64457.75</v>
+        <v>63033.46</v>
       </c>
       <c r="K58" t="n">
-        <v>64728.81</v>
+        <v>63459.64</v>
       </c>
       <c r="L58" t="n">
-        <v>64999.88</v>
+        <v>63885.83</v>
       </c>
       <c r="M58" t="n">
-        <v>65813.08</v>
+        <v>64563.04</v>
       </c>
       <c r="N58" t="n">
-        <v>66626.28999999999</v>
+        <v>65240.24</v>
       </c>
       <c r="O58" t="n">
-        <v>66355.22</v>
+        <v>65415.41</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5386,7 +5388,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5396,71 +5398,69 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>63659.53</v>
+        <v>63190.37</v>
       </c>
       <c r="C59" t="n">
-        <v>63691.53</v>
+        <v>64101</v>
       </c>
       <c r="D59" t="n">
-        <v>62726.18</v>
+        <v>63067.18</v>
       </c>
       <c r="E59" t="n">
-        <v>63492.99</v>
+        <v>63484.1</v>
       </c>
       <c r="F59" t="n">
-        <v>-518.35</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0001</v>
       </c>
       <c r="H59" t="n">
-        <v>965.35</v>
+        <v>1033.82</v>
       </c>
       <c r="I59" t="n">
-        <v>62105.24</v>
+        <v>61760.83</v>
       </c>
       <c r="J59" t="n">
-        <v>63033.46</v>
+        <v>62669.7</v>
       </c>
       <c r="K59" t="n">
-        <v>63459.64</v>
+        <v>63010.31</v>
       </c>
       <c r="L59" t="n">
-        <v>63885.83</v>
+        <v>63350.92</v>
       </c>
       <c r="M59" t="n">
-        <v>64563.04</v>
+        <v>63975.66</v>
       </c>
       <c r="N59" t="n">
-        <v>65240.24</v>
+        <v>64600.41</v>
       </c>
       <c r="O59" t="n">
-        <v>65415.41</v>
+        <v>64656.88</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5468,60 +5468,64 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>63190.37</v>
+        <v>63672.13</v>
       </c>
       <c r="C60" t="n">
-        <v>64101</v>
+        <v>63923</v>
       </c>
       <c r="D60" t="n">
-        <v>63067.18</v>
+        <v>63209.92</v>
       </c>
       <c r="E60" t="n">
-        <v>63484.1</v>
+        <v>63923</v>
       </c>
       <c r="F60" t="n">
-        <v>-8.890000000000001</v>
+        <v>438.9</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0069</v>
       </c>
       <c r="H60" t="n">
-        <v>1033.82</v>
+        <v>713.08</v>
       </c>
       <c r="I60" t="n">
-        <v>61760.83</v>
+        <v>62033.36</v>
       </c>
       <c r="J60" t="n">
-        <v>62669.7</v>
+        <v>62400.29</v>
       </c>
       <c r="K60" t="n">
-        <v>63010.31</v>
+        <v>62967.19</v>
       </c>
       <c r="L60" t="n">
-        <v>63350.92</v>
+        <v>63534.1</v>
       </c>
       <c r="M60" t="n">
-        <v>63975.66</v>
+        <v>64001.01</v>
       </c>
       <c r="N60" t="n">
-        <v>64600.41</v>
+        <v>64467.93</v>
       </c>
       <c r="O60" t="n">
-        <v>64656.88</v>
+        <v>65134.82</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5534,12 +5538,12 @@
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U60" s="8" t="n">
@@ -5548,7 +5552,7 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5562,50 +5566,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>63672.13</v>
+        <v>64643.58</v>
       </c>
       <c r="C61" t="n">
-        <v>63923</v>
+        <v>64643.58</v>
       </c>
       <c r="D61" t="n">
-        <v>63209.92</v>
+        <v>63824.56</v>
       </c>
       <c r="E61" t="n">
-        <v>63923</v>
+        <v>64136.25</v>
       </c>
       <c r="F61" t="n">
-        <v>438.9</v>
+        <v>213.25</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0033</v>
       </c>
       <c r="H61" t="n">
-        <v>713.08</v>
+        <v>819.02</v>
       </c>
       <c r="I61" t="n">
-        <v>62033.36</v>
+        <v>62496.84</v>
       </c>
       <c r="J61" t="n">
-        <v>62400.29</v>
+        <v>63388.19</v>
       </c>
       <c r="K61" t="n">
-        <v>62967.19</v>
+        <v>63566.46</v>
       </c>
       <c r="L61" t="n">
-        <v>63534.1</v>
+        <v>63744.73</v>
       </c>
       <c r="M61" t="n">
-        <v>64001.01</v>
+        <v>64279.54</v>
       </c>
       <c r="N61" t="n">
-        <v>64467.93</v>
+        <v>64814.35</v>
       </c>
       <c r="O61" t="n">
-        <v>65134.82</v>
+        <v>64636.08</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5629,67 +5633,69 @@
       <c r="U61" s="8" t="n">
         <v/>
       </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="V61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>64643.58</v>
+        <v>64681.55</v>
       </c>
       <c r="C62" t="n">
-        <v>64643.58</v>
+        <v>65436.57</v>
       </c>
       <c r="D62" t="n">
-        <v>63824.56</v>
+        <v>64403.85</v>
       </c>
       <c r="E62" t="n">
-        <v>64136.25</v>
+        <v>65018.95</v>
       </c>
       <c r="F62" t="n">
-        <v>213.25</v>
+        <v>882.7</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0138</v>
       </c>
       <c r="H62" t="n">
-        <v>819.02</v>
+        <v>1032.72</v>
       </c>
       <c r="I62" t="n">
-        <v>62496.84</v>
+        <v>63005.54</v>
       </c>
       <c r="J62" t="n">
-        <v>63388.19</v>
+        <v>63268.32</v>
       </c>
       <c r="K62" t="n">
-        <v>63566.46</v>
+        <v>63726.74</v>
       </c>
       <c r="L62" t="n">
-        <v>63744.73</v>
+        <v>64185.16</v>
       </c>
       <c r="M62" t="n">
-        <v>64279.54</v>
+        <v>64545.76</v>
       </c>
       <c r="N62" t="n">
-        <v>64814.35</v>
+        <v>64906.36</v>
       </c>
       <c r="O62" t="n">
-        <v>64636.08</v>
+        <v>65462.6</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5707,109 +5713,23 @@
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V62" s="8" t="n">
+        <v/>
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>64681.55</v>
-      </c>
-      <c r="C63" t="n">
-        <v>65436.57</v>
-      </c>
-      <c r="D63" t="n">
-        <v>64403.85</v>
-      </c>
-      <c r="E63" t="n">
-        <v>65018.95</v>
-      </c>
-      <c r="F63" t="n">
-        <v>882.7</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0138</v>
-      </c>
-      <c r="H63" t="n">
-        <v>1032.72</v>
-      </c>
-      <c r="I63" t="n">
-        <v>63005.54</v>
-      </c>
-      <c r="J63" t="n">
-        <v>63268.32</v>
-      </c>
-      <c r="K63" t="n">
-        <v>63726.74</v>
-      </c>
-      <c r="L63" t="n">
-        <v>64185.16</v>
-      </c>
-      <c r="M63" t="n">
-        <v>64545.76</v>
-      </c>
-      <c r="N63" t="n">
-        <v>64906.36</v>
-      </c>
-      <c r="O63" t="n">
-        <v>65462.6</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69615.08</v>
+        <v>70114.09</v>
       </c>
       <c r="C2" t="n">
-        <v>70218.71000000001</v>
+        <v>72594.22</v>
       </c>
       <c r="D2" t="n">
-        <v>68461.10000000001</v>
+        <v>69982.67</v>
       </c>
       <c r="E2" t="n">
-        <v>69174.97</v>
+        <v>72366.34</v>
       </c>
       <c r="F2" t="n">
-        <v>-613.41</v>
+        <v>3191.38</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0461</v>
       </c>
       <c r="H2" t="n">
-        <v>1757.61</v>
+        <v>2611.55</v>
       </c>
       <c r="I2" t="n">
-        <v>66958.33</v>
+        <v>66703.49000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>66250.81</v>
+        <v>67334.89</v>
       </c>
       <c r="K2" t="n">
-        <v>68373.36</v>
+        <v>68296.16</v>
       </c>
       <c r="L2" t="n">
-        <v>70495.89999999999</v>
+        <v>69257.44</v>
       </c>
       <c r="M2" t="n">
-        <v>71203.41</v>
+        <v>70053.77</v>
       </c>
       <c r="N2" t="n">
-        <v>71910.92</v>
+        <v>70850.11</v>
       </c>
       <c r="O2" t="n">
-        <v>75448.49000000001</v>
+        <v>71976.32000000001</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,116 +685,114 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70114.09</v>
+        <v>71587.71000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>72594.22</v>
+        <v>71786.28</v>
       </c>
       <c r="D3" t="n">
-        <v>69982.67</v>
+        <v>68639.84</v>
       </c>
       <c r="E3" t="n">
-        <v>72366.34</v>
+        <v>69360.88</v>
       </c>
       <c r="F3" t="n">
-        <v>3191.38</v>
+        <v>-3005.46</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0461</v>
+        <v>-0.0415</v>
       </c>
       <c r="H3" t="n">
-        <v>2611.55</v>
+        <v>3146.44</v>
       </c>
       <c r="I3" t="n">
-        <v>66703.49000000001</v>
+        <v>67371.12</v>
       </c>
       <c r="J3" t="n">
-        <v>67334.89</v>
+        <v>70293.75</v>
       </c>
       <c r="K3" t="n">
-        <v>68296.16</v>
+        <v>71060.57000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>69257.44</v>
+        <v>71827.39</v>
       </c>
       <c r="M3" t="n">
-        <v>70053.77</v>
+        <v>73672.12</v>
       </c>
       <c r="N3" t="n">
-        <v>70850.11</v>
+        <v>75516.84</v>
       </c>
       <c r="O3" t="n">
-        <v>71976.32000000001</v>
+        <v>75205.77</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -802,67 +800,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71587.71000000001</v>
+        <v>69609.88</v>
       </c>
       <c r="C4" t="n">
-        <v>71786.28</v>
+        <v>69609.88</v>
       </c>
       <c r="D4" t="n">
-        <v>68639.84</v>
+        <v>67997.57000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>69360.88</v>
+        <v>69468.11</v>
       </c>
       <c r="F4" t="n">
-        <v>-3005.46</v>
+        <v>107.23</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0415</v>
+        <v>0.0015</v>
       </c>
       <c r="H4" t="n">
-        <v>3146.44</v>
+        <v>1612.31</v>
       </c>
       <c r="I4" t="n">
-        <v>67371.12</v>
+        <v>65493.41</v>
       </c>
       <c r="J4" t="n">
-        <v>70293.75</v>
+        <v>65788.36</v>
       </c>
       <c r="K4" t="n">
-        <v>71060.57000000001</v>
+        <v>67787.66</v>
       </c>
       <c r="L4" t="n">
-        <v>71827.39</v>
+        <v>69786.97</v>
       </c>
       <c r="M4" t="n">
-        <v>73672.12</v>
+        <v>70934.10000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>75516.84</v>
+        <v>72081.23</v>
       </c>
       <c r="O4" t="n">
-        <v>75205.77</v>
+        <v>74932.72</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -879,55 +873,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69609.88</v>
+        <v>70085.60000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>69609.88</v>
+        <v>70667</v>
       </c>
       <c r="D5" t="n">
-        <v>67997.57000000001</v>
+        <v>69302.19</v>
       </c>
       <c r="E5" t="n">
-        <v>69468.11</v>
+        <v>70062.32000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>107.23</v>
+        <v>594.21</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0086</v>
       </c>
       <c r="H5" t="n">
-        <v>1612.31</v>
+        <v>1364.81</v>
       </c>
       <c r="I5" t="n">
-        <v>65493.41</v>
+        <v>66385.25999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>65788.36</v>
+        <v>68187.99000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>67787.66</v>
+        <v>68661.95</v>
       </c>
       <c r="L5" t="n">
-        <v>69786.97</v>
+        <v>69135.92</v>
       </c>
       <c r="M5" t="n">
-        <v>70934.10000000001</v>
+        <v>70274.27</v>
       </c>
       <c r="N5" t="n">
-        <v>72081.23</v>
+        <v>71412.61</v>
       </c>
       <c r="O5" t="n">
-        <v>74932.72</v>
+        <v>71222.2</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,11 +938,13 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -959,57 +959,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70085.60000000001</v>
+        <v>70774.28</v>
       </c>
       <c r="C6" t="n">
-        <v>70667</v>
+        <v>71962.34</v>
       </c>
       <c r="D6" t="n">
-        <v>69302.19</v>
+        <v>70126.14</v>
       </c>
       <c r="E6" t="n">
-        <v>70062.32000000001</v>
+        <v>70474.96000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>594.21</v>
+        <v>412.64</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0059</v>
       </c>
       <c r="H6" t="n">
-        <v>1364.81</v>
+        <v>1836.2</v>
       </c>
       <c r="I6" t="n">
-        <v>66385.25999999999</v>
+        <v>67937.38</v>
       </c>
       <c r="J6" t="n">
-        <v>68187.99000000001</v>
+        <v>68736.37</v>
       </c>
       <c r="K6" t="n">
-        <v>68661.95</v>
+        <v>69379.91</v>
       </c>
       <c r="L6" t="n">
-        <v>69135.92</v>
+        <v>70023.46000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>70274.27</v>
+        <v>70744.73</v>
       </c>
       <c r="N6" t="n">
-        <v>71412.61</v>
+        <v>71466</v>
       </c>
       <c r="O6" t="n">
-        <v>71222.2</v>
+        <v>72031.81</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,7 +1020,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1030,8 +1030,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U6" s="8" t="n">
-        <v/>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1050,74 +1052,74 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70774.28</v>
+        <v>70039.89</v>
       </c>
       <c r="C7" t="n">
-        <v>71962.34</v>
+        <v>70081.39</v>
       </c>
       <c r="D7" t="n">
-        <v>70126.14</v>
+        <v>68676.25999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>70474.96000000001</v>
+        <v>68733.14999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>412.64</v>
+        <v>-1741.81</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0247</v>
       </c>
       <c r="H7" t="n">
-        <v>1836.2</v>
+        <v>1405.13</v>
       </c>
       <c r="I7" t="n">
-        <v>67937.38</v>
+        <v>68289.94</v>
       </c>
       <c r="J7" t="n">
-        <v>68736.37</v>
+        <v>68354.12</v>
       </c>
       <c r="K7" t="n">
-        <v>69379.91</v>
+        <v>69556.86</v>
       </c>
       <c r="L7" t="n">
-        <v>70023.46000000001</v>
+        <v>70759.60000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>70744.73</v>
+        <v>71393.06</v>
       </c>
       <c r="N7" t="n">
-        <v>71466</v>
+        <v>72026.52</v>
       </c>
       <c r="O7" t="n">
-        <v>72031.81</v>
+        <v>73798.55</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1127,84 +1129,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70039.89</v>
+        <v>68676.06</v>
       </c>
       <c r="C8" t="n">
-        <v>70081.39</v>
+        <v>69788.03</v>
       </c>
       <c r="D8" t="n">
-        <v>68676.25999999999</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>68733.14999999999</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-1741.81</v>
+        <v>1010.92</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0147</v>
       </c>
       <c r="H8" t="n">
-        <v>1405.13</v>
+        <v>2178.54</v>
       </c>
       <c r="I8" t="n">
-        <v>68289.94</v>
+        <v>67271.12</v>
       </c>
       <c r="J8" t="n">
-        <v>68354.12</v>
+        <v>67005.17999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>69556.86</v>
+        <v>68030.58</v>
       </c>
       <c r="L8" t="n">
-        <v>70759.60000000001</v>
+        <v>69055.99000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>71393.06</v>
+        <v>69435.71000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>72026.52</v>
+        <v>69815.44</v>
       </c>
       <c r="O8" t="n">
-        <v>73798.55</v>
+        <v>71486.52</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
@@ -1213,55 +1213,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68676.06</v>
+        <v>69973.34</v>
       </c>
       <c r="C9" t="n">
-        <v>69788.03</v>
+        <v>70384.59</v>
       </c>
       <c r="D9" t="n">
-        <v>67609.49000000001</v>
+        <v>68904.41</v>
       </c>
       <c r="E9" t="n">
-        <v>69744.07000000001</v>
+        <v>69737.69</v>
       </c>
       <c r="F9" t="n">
-        <v>1010.92</v>
+        <v>-6.38</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0001</v>
       </c>
       <c r="H9" t="n">
-        <v>2178.54</v>
+        <v>1480.19</v>
       </c>
       <c r="I9" t="n">
-        <v>67271.12</v>
+        <v>65430.95</v>
       </c>
       <c r="J9" t="n">
-        <v>67005.17999999999</v>
+        <v>68088.19</v>
       </c>
       <c r="K9" t="n">
-        <v>68030.58</v>
+        <v>68654.8</v>
       </c>
       <c r="L9" t="n">
-        <v>69055.99000000001</v>
+        <v>69221.42</v>
       </c>
       <c r="M9" t="n">
-        <v>69435.71000000001</v>
+        <v>70833.34</v>
       </c>
       <c r="N9" t="n">
-        <v>69815.44</v>
+        <v>72445.25999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>71486.52</v>
+        <v>71966.57000000001</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1269,25 +1273,19 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1299,70 +1297,74 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69973.34</v>
+        <v>69460.08</v>
       </c>
       <c r="C10" t="n">
-        <v>70384.59</v>
+        <v>69957.50999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>68904.41</v>
+        <v>68003.92</v>
       </c>
       <c r="E10" t="n">
-        <v>69737.69</v>
+        <v>68256.96000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.38</v>
+        <v>-1480.73</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0212</v>
       </c>
       <c r="H10" t="n">
-        <v>1480.19</v>
+        <v>1953.59</v>
       </c>
       <c r="I10" t="n">
-        <v>65430.95</v>
+        <v>67424.22</v>
       </c>
       <c r="J10" t="n">
-        <v>68088.19</v>
+        <v>68304.09</v>
       </c>
       <c r="K10" t="n">
-        <v>68654.8</v>
+        <v>68997.59</v>
       </c>
       <c r="L10" t="n">
-        <v>69221.42</v>
+        <v>69691.09</v>
       </c>
       <c r="M10" t="n">
-        <v>70833.34</v>
+        <v>70477.78</v>
       </c>
       <c r="N10" t="n">
-        <v>72445.25999999999</v>
+        <v>71264.47</v>
       </c>
       <c r="O10" t="n">
-        <v>71966.57000000001</v>
+        <v>71864.78</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1379,74 +1381,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>69460.08</v>
+        <v>67704.16</v>
       </c>
       <c r="C11" t="n">
-        <v>69957.50999999999</v>
+        <v>68432.67999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>68003.92</v>
+        <v>66819.05</v>
       </c>
       <c r="E11" t="n">
-        <v>68256.96000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="F11" t="n">
-        <v>-1480.73</v>
+        <v>-1437.91</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="H11" t="n">
-        <v>1953.59</v>
+        <v>1613.63</v>
       </c>
       <c r="I11" t="n">
-        <v>67424.22</v>
+        <v>66050.34</v>
       </c>
       <c r="J11" t="n">
-        <v>68304.09</v>
+        <v>65941.5</v>
       </c>
       <c r="K11" t="n">
-        <v>68997.59</v>
+        <v>67280.17</v>
       </c>
       <c r="L11" t="n">
-        <v>69691.09</v>
+        <v>68618.84</v>
       </c>
       <c r="M11" t="n">
-        <v>70477.78</v>
+        <v>69233.75</v>
       </c>
       <c r="N11" t="n">
-        <v>71264.47</v>
+        <v>69848.67</v>
       </c>
       <c r="O11" t="n">
-        <v>71864.78</v>
+        <v>71911.09</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1470,50 +1466,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67704.16</v>
+        <v>67046.37</v>
       </c>
       <c r="C12" t="n">
-        <v>68432.67999999999</v>
+        <v>68447.89</v>
       </c>
       <c r="D12" t="n">
-        <v>66819.05</v>
+        <v>67008.89</v>
       </c>
       <c r="E12" t="n">
-        <v>66819.05</v>
+        <v>67743.85000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1437.91</v>
+        <v>924.8</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0211</v>
+        <v>0.0138</v>
       </c>
       <c r="H12" t="n">
-        <v>1613.63</v>
+        <v>1439</v>
       </c>
       <c r="I12" t="n">
-        <v>66050.34</v>
+        <v>65205.41</v>
       </c>
       <c r="J12" t="n">
-        <v>65941.5</v>
+        <v>64802.01</v>
       </c>
       <c r="K12" t="n">
-        <v>67280.17</v>
+        <v>66012.23</v>
       </c>
       <c r="L12" t="n">
-        <v>68618.84</v>
+        <v>67222.46000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>69233.75</v>
+        <v>67625.86</v>
       </c>
       <c r="N12" t="n">
-        <v>69848.67</v>
+        <v>68029.27</v>
       </c>
       <c r="O12" t="n">
-        <v>71911.09</v>
+        <v>70046.31</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1521,21 +1517,23 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1545,55 +1543,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67046.37</v>
+        <v>68526.72</v>
       </c>
       <c r="C13" t="n">
-        <v>68447.89</v>
+        <v>69374.86</v>
       </c>
       <c r="D13" t="n">
-        <v>67008.89</v>
+        <v>68271.91</v>
       </c>
       <c r="E13" t="n">
-        <v>67743.85000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F13" t="n">
-        <v>924.8</v>
+        <v>813.88</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.012</v>
       </c>
       <c r="H13" t="n">
-        <v>1439</v>
+        <v>1102.95</v>
       </c>
       <c r="I13" t="n">
-        <v>65205.41</v>
+        <v>65569.89</v>
       </c>
       <c r="J13" t="n">
-        <v>64802.01</v>
+        <v>66312.58</v>
       </c>
       <c r="K13" t="n">
-        <v>66012.23</v>
+        <v>67024.35000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>67222.46000000001</v>
+        <v>67736.12</v>
       </c>
       <c r="M13" t="n">
-        <v>67625.86</v>
+        <v>68463.35000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>68029.27</v>
+        <v>69190.58</v>
       </c>
       <c r="O13" t="n">
-        <v>70046.31</v>
+        <v>69886.89</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1604,7 +1606,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1636,74 +1638,76 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>68526.72</v>
+        <v>68410.63</v>
       </c>
       <c r="C14" t="n">
-        <v>69374.86</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>68271.91</v>
+        <v>66653.11</v>
       </c>
       <c r="E14" t="n">
-        <v>68557.73</v>
+        <v>67242.73</v>
       </c>
       <c r="F14" t="n">
-        <v>813.88</v>
+        <v>-1315</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0192</v>
       </c>
       <c r="H14" t="n">
-        <v>1102.95</v>
+        <v>2425.1</v>
       </c>
       <c r="I14" t="n">
-        <v>65569.89</v>
+        <v>67168.95</v>
       </c>
       <c r="J14" t="n">
-        <v>66312.58</v>
+        <v>67321.95</v>
       </c>
       <c r="K14" t="n">
-        <v>67024.35000000001</v>
+        <v>68006.25</v>
       </c>
       <c r="L14" t="n">
-        <v>67736.12</v>
+        <v>68690.55</v>
       </c>
       <c r="M14" t="n">
-        <v>68463.35000000001</v>
+        <v>69109.2</v>
       </c>
       <c r="N14" t="n">
-        <v>69190.58</v>
+        <v>69527.85000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>69886.89</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+        <v>70477.81</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1713,78 +1717,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>68410.63</v>
+        <v>67002.94</v>
       </c>
       <c r="C15" t="n">
-        <v>69078.21000000001</v>
+        <v>67800.17999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>66653.11</v>
+        <v>66268.60000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>67242.73</v>
+        <v>67743.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-1315</v>
+        <v>500.77</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0074</v>
       </c>
       <c r="H15" t="n">
-        <v>2425.1</v>
+        <v>1531.58</v>
       </c>
       <c r="I15" t="n">
-        <v>67168.95</v>
+        <v>64228.01</v>
       </c>
       <c r="J15" t="n">
-        <v>67321.95</v>
+        <v>64506.16</v>
       </c>
       <c r="K15" t="n">
-        <v>68006.25</v>
+        <v>66030.17999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>68690.55</v>
+        <v>67554.19</v>
       </c>
       <c r="M15" t="n">
-        <v>69109.2</v>
+        <v>68455.28</v>
       </c>
       <c r="N15" t="n">
-        <v>69527.85000000001</v>
+        <v>69356.36</v>
       </c>
       <c r="O15" t="n">
-        <v>70477.81</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>71503.31</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1801,55 +1795,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>67002.94</v>
+        <v>67989.74000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>67800.17999999999</v>
+        <v>68798.24000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>66268.60000000001</v>
+        <v>67833.17</v>
       </c>
       <c r="E16" t="n">
-        <v>67743.5</v>
+        <v>68751.50999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>500.77</v>
+        <v>1008.01</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0149</v>
       </c>
       <c r="H16" t="n">
-        <v>1531.58</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>64228.01</v>
+        <v>64737.02</v>
       </c>
       <c r="J16" t="n">
-        <v>64506.16</v>
+        <v>66566.48</v>
       </c>
       <c r="K16" t="n">
-        <v>66030.17999999999</v>
+        <v>66977.71000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>67554.19</v>
+        <v>67388.95</v>
       </c>
       <c r="M16" t="n">
-        <v>68455.28</v>
+        <v>68509.28999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>69356.36</v>
+        <v>69629.63</v>
       </c>
       <c r="O16" t="n">
-        <v>71503.31</v>
+        <v>69331.75999999999</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1860,13 +1858,15 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1881,76 +1881,80 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>67989.74000000001</v>
+        <v>67900.42999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>68798.24000000001</v>
+        <v>68069.82000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>67833.17</v>
+        <v>66499.49000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>68751.50999999999</v>
+        <v>66835.53999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1008.01</v>
+        <v>-1915.97</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0279</v>
       </c>
       <c r="H17" t="n">
-        <v>965.0700000000001</v>
+        <v>1570.33</v>
       </c>
       <c r="I17" t="n">
-        <v>64737.02</v>
+        <v>66868.10000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>66566.48</v>
+        <v>68004.34</v>
       </c>
       <c r="K17" t="n">
-        <v>66977.71000000001</v>
+        <v>68268.97</v>
       </c>
       <c r="L17" t="n">
-        <v>67388.95</v>
+        <v>68533.61</v>
       </c>
       <c r="M17" t="n">
-        <v>68509.28999999999</v>
+        <v>69234.03999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>69629.63</v>
+        <v>69934.48</v>
       </c>
       <c r="O17" t="n">
-        <v>69331.75999999999</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+        <v>69763.31</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1963,59 +1967,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>67900.42999999999</v>
+        <v>66339.85000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>68069.82000000001</v>
+        <v>66441.77</v>
       </c>
       <c r="D18" t="n">
-        <v>66499.49000000001</v>
+        <v>62704.6</v>
       </c>
       <c r="E18" t="n">
-        <v>66835.53999999999</v>
+        <v>64141.12</v>
       </c>
       <c r="F18" t="n">
-        <v>-1915.97</v>
+        <v>-2694.42</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0403</v>
       </c>
       <c r="H18" t="n">
-        <v>1570.33</v>
+        <v>3737.17</v>
       </c>
       <c r="I18" t="n">
-        <v>66868.10000000001</v>
+        <v>64929.16</v>
       </c>
       <c r="J18" t="n">
-        <v>68004.34</v>
+        <v>65040.65</v>
       </c>
       <c r="K18" t="n">
-        <v>68268.97</v>
+        <v>66050.38</v>
       </c>
       <c r="L18" t="n">
-        <v>68533.61</v>
+        <v>67060.10000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>69234.03999999999</v>
+        <v>67620.7</v>
       </c>
       <c r="N18" t="n">
-        <v>69934.48</v>
+        <v>68181.31</v>
       </c>
       <c r="O18" t="n">
-        <v>69763.31</v>
+        <v>69640.14999999999</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2056,74 +2056,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>66339.85000000001</v>
+        <v>64544.05</v>
       </c>
       <c r="C19" t="n">
-        <v>66441.77</v>
+        <v>66232.19</v>
       </c>
       <c r="D19" t="n">
-        <v>62704.6</v>
+        <v>64203.47</v>
       </c>
       <c r="E19" t="n">
-        <v>64141.12</v>
+        <v>66232.19</v>
       </c>
       <c r="F19" t="n">
-        <v>-2694.42</v>
+        <v>2091.07</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0326</v>
       </c>
       <c r="H19" t="n">
-        <v>3737.17</v>
+        <v>2028.72</v>
       </c>
       <c r="I19" t="n">
-        <v>64929.16</v>
+        <v>58967.43</v>
       </c>
       <c r="J19" t="n">
-        <v>65040.65</v>
+        <v>60187.92</v>
       </c>
       <c r="K19" t="n">
-        <v>66050.38</v>
+        <v>62272.54</v>
       </c>
       <c r="L19" t="n">
-        <v>67060.10000000001</v>
+        <v>64357.15</v>
       </c>
       <c r="M19" t="n">
-        <v>67620.7</v>
+        <v>66009.71000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>68181.31</v>
+        <v>67662.25999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>69640.14999999999</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>70178.95</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2135,55 +2131,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>64544.05</v>
+        <v>66449.27</v>
       </c>
       <c r="C20" t="n">
-        <v>66232.19</v>
+        <v>67592.2</v>
       </c>
       <c r="D20" t="n">
-        <v>64203.47</v>
+        <v>65955.60000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>66232.19</v>
+        <v>66115.60000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>2091.07</v>
+        <v>-116.59</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0326</v>
+        <v>-0.0018</v>
       </c>
       <c r="H20" t="n">
-        <v>2028.72</v>
+        <v>1636.6</v>
       </c>
       <c r="I20" t="n">
-        <v>58967.43</v>
+        <v>62174.75</v>
       </c>
       <c r="J20" t="n">
-        <v>60187.92</v>
+        <v>64710.65</v>
       </c>
       <c r="K20" t="n">
-        <v>62272.54</v>
+        <v>65217.83</v>
       </c>
       <c r="L20" t="n">
-        <v>64357.15</v>
+        <v>65725.00999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>66009.71000000001</v>
+        <v>67246.55</v>
       </c>
       <c r="N20" t="n">
-        <v>67662.25999999999</v>
+        <v>68768.09</v>
       </c>
       <c r="O20" t="n">
-        <v>70178.95</v>
+        <v>68260.91</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2194,14 +2194,14 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U20" s="8" t="n">
@@ -2224,50 +2224,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>66449.27</v>
+        <v>66421.00999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>67592.2</v>
+        <v>67022.37</v>
       </c>
       <c r="D21" t="n">
-        <v>65955.60000000001</v>
+        <v>66208.66</v>
       </c>
       <c r="E21" t="n">
-        <v>66115.60000000001</v>
+        <v>66422.60000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-116.59</v>
+        <v>307</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0046</v>
       </c>
       <c r="H21" t="n">
-        <v>1636.6</v>
+        <v>813.71</v>
       </c>
       <c r="I21" t="n">
-        <v>62174.75</v>
+        <v>64319</v>
       </c>
       <c r="J21" t="n">
-        <v>64710.65</v>
+        <v>64149.85</v>
       </c>
       <c r="K21" t="n">
-        <v>65217.83</v>
+        <v>65297.3</v>
       </c>
       <c r="L21" t="n">
-        <v>65725.00999999999</v>
+        <v>66444.75</v>
       </c>
       <c r="M21" t="n">
-        <v>67246.55</v>
+        <v>66933.89999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>68768.09</v>
+        <v>67423.05</v>
       </c>
       <c r="O21" t="n">
-        <v>68260.91</v>
+        <v>69228.8</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2308,69 +2308,73 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>66421.00999999999</v>
+        <v>65584.25</v>
       </c>
       <c r="C22" t="n">
-        <v>67022.37</v>
+        <v>65720.81</v>
       </c>
       <c r="D22" t="n">
-        <v>66208.66</v>
+        <v>64201.03</v>
       </c>
       <c r="E22" t="n">
-        <v>66422.60000000001</v>
+        <v>64611.15</v>
       </c>
       <c r="F22" t="n">
-        <v>307</v>
+        <v>-1811.45</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0273</v>
       </c>
       <c r="H22" t="n">
-        <v>813.71</v>
+        <v>1519.78</v>
       </c>
       <c r="I22" t="n">
-        <v>64319</v>
+        <v>65394.95</v>
       </c>
       <c r="J22" t="n">
-        <v>64149.85</v>
+        <v>65512.44</v>
       </c>
       <c r="K22" t="n">
-        <v>65297.3</v>
+        <v>66015.75</v>
       </c>
       <c r="L22" t="n">
-        <v>66444.75</v>
+        <v>66519.06</v>
       </c>
       <c r="M22" t="n">
-        <v>66933.89999999999</v>
+        <v>66829.46000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>67423.05</v>
+        <v>67139.86</v>
       </c>
       <c r="O22" t="n">
-        <v>69228.8</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67836.08</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2383,78 +2387,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>65584.25</v>
+        <v>65164.98</v>
       </c>
       <c r="C23" t="n">
-        <v>65720.81</v>
+        <v>65220.69</v>
       </c>
       <c r="D23" t="n">
-        <v>64201.03</v>
+        <v>64123.4</v>
       </c>
       <c r="E23" t="n">
-        <v>64611.15</v>
+        <v>64931.19</v>
       </c>
       <c r="F23" t="n">
-        <v>-1811.45</v>
+        <v>320.04</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.005</v>
       </c>
       <c r="H23" t="n">
-        <v>1519.78</v>
+        <v>1097.29</v>
       </c>
       <c r="I23" t="n">
-        <v>65394.95</v>
+        <v>62681.25</v>
       </c>
       <c r="J23" t="n">
-        <v>65512.44</v>
+        <v>62916.48</v>
       </c>
       <c r="K23" t="n">
-        <v>66015.75</v>
+        <v>63851.26</v>
       </c>
       <c r="L23" t="n">
-        <v>66519.06</v>
+        <v>64786.04</v>
       </c>
       <c r="M23" t="n">
-        <v>66829.46000000001</v>
+        <v>65371.04</v>
       </c>
       <c r="N23" t="n">
-        <v>67139.86</v>
+        <v>65956.03999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>67836.08</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67240.59</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2471,68 +2465,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>65164.98</v>
+        <v>64539.92</v>
       </c>
       <c r="C24" t="n">
-        <v>65220.69</v>
+        <v>64573.18</v>
       </c>
       <c r="D24" t="n">
-        <v>64123.4</v>
+        <v>61923.6</v>
       </c>
       <c r="E24" t="n">
-        <v>64931.19</v>
+        <v>62364.92</v>
       </c>
       <c r="F24" t="n">
-        <v>320.04</v>
+        <v>-2566.27</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0395</v>
       </c>
       <c r="H24" t="n">
-        <v>1097.29</v>
+        <v>2649.58</v>
       </c>
       <c r="I24" t="n">
-        <v>62681.25</v>
+        <v>63026.11</v>
       </c>
       <c r="J24" t="n">
-        <v>62916.48</v>
+        <v>63963.47</v>
       </c>
       <c r="K24" t="n">
-        <v>63851.26</v>
+        <v>64382.54</v>
       </c>
       <c r="L24" t="n">
-        <v>64786.04</v>
+        <v>64801.62</v>
       </c>
       <c r="M24" t="n">
-        <v>65371.04</v>
+        <v>65479.84</v>
       </c>
       <c r="N24" t="n">
-        <v>65956.03999999999</v>
+        <v>66158.06</v>
       </c>
       <c r="O24" t="n">
-        <v>67240.59</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+        <v>66317.98</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2549,76 +2553,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>64539.92</v>
+        <v>62734.68</v>
       </c>
       <c r="C25" t="n">
-        <v>64573.18</v>
+        <v>63138.04</v>
       </c>
       <c r="D25" t="n">
-        <v>61923.6</v>
+        <v>60448.9</v>
       </c>
       <c r="E25" t="n">
-        <v>62364.92</v>
+        <v>61434.19</v>
       </c>
       <c r="F25" t="n">
-        <v>-2566.27</v>
+        <v>-930.73</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0149</v>
       </c>
       <c r="H25" t="n">
-        <v>2649.58</v>
+        <v>2689.14</v>
       </c>
       <c r="I25" t="n">
-        <v>63026.11</v>
+        <v>59274.02</v>
       </c>
       <c r="J25" t="n">
-        <v>63963.47</v>
+        <v>59273.61</v>
       </c>
       <c r="K25" t="n">
-        <v>64382.54</v>
+        <v>61040.13</v>
       </c>
       <c r="L25" t="n">
-        <v>64801.62</v>
+        <v>62806.66</v>
       </c>
       <c r="M25" t="n">
-        <v>65479.84</v>
+        <v>63689.71</v>
       </c>
       <c r="N25" t="n">
-        <v>66158.06</v>
+        <v>64572.77</v>
       </c>
       <c r="O25" t="n">
-        <v>66317.98</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>67222.75999999999</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2642,50 +2638,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>62734.68</v>
+        <v>61258.34</v>
       </c>
       <c r="C26" t="n">
-        <v>63138.04</v>
+        <v>62924.84</v>
       </c>
       <c r="D26" t="n">
-        <v>60448.9</v>
+        <v>61049.7</v>
       </c>
       <c r="E26" t="n">
-        <v>61434.19</v>
+        <v>61867.43</v>
       </c>
       <c r="F26" t="n">
-        <v>-930.73</v>
+        <v>433.24</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0071</v>
       </c>
       <c r="H26" t="n">
-        <v>2689.14</v>
+        <v>1875.14</v>
       </c>
       <c r="I26" t="n">
-        <v>59274.02</v>
+        <v>57759.76</v>
       </c>
       <c r="J26" t="n">
-        <v>59273.61</v>
+        <v>58565.41</v>
       </c>
       <c r="K26" t="n">
-        <v>61040.13</v>
+        <v>60089.62</v>
       </c>
       <c r="L26" t="n">
-        <v>62806.66</v>
+        <v>61613.83</v>
       </c>
       <c r="M26" t="n">
-        <v>63689.71</v>
+        <v>62778.76</v>
       </c>
       <c r="N26" t="n">
-        <v>64572.77</v>
+        <v>63943.69</v>
       </c>
       <c r="O26" t="n">
-        <v>67222.75999999999</v>
+        <v>65827.17999999999</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2693,18 +2689,18 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2717,55 +2713,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>61258.34</v>
+        <v>61957.1</v>
       </c>
       <c r="C27" t="n">
-        <v>62924.84</v>
+        <v>65364.73</v>
       </c>
       <c r="D27" t="n">
-        <v>61049.7</v>
+        <v>61948.23</v>
       </c>
       <c r="E27" t="n">
-        <v>61867.43</v>
+        <v>64362.02</v>
       </c>
       <c r="F27" t="n">
-        <v>433.24</v>
+        <v>2494.59</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0403</v>
       </c>
       <c r="H27" t="n">
-        <v>1875.14</v>
+        <v>3416.5</v>
       </c>
       <c r="I27" t="n">
-        <v>57759.76</v>
+        <v>59174.56</v>
       </c>
       <c r="J27" t="n">
-        <v>58565.41</v>
+        <v>59932.37</v>
       </c>
       <c r="K27" t="n">
-        <v>60089.62</v>
+        <v>60929.86</v>
       </c>
       <c r="L27" t="n">
-        <v>61613.83</v>
+        <v>61927.35</v>
       </c>
       <c r="M27" t="n">
-        <v>62778.76</v>
+        <v>62805</v>
       </c>
       <c r="N27" t="n">
-        <v>63943.69</v>
+        <v>63682.65</v>
       </c>
       <c r="O27" t="n">
-        <v>65827.17999999999</v>
+        <v>64799.98</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2776,9 +2776,9 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2786,70 +2786,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>61957.1</v>
+        <v>63834.95</v>
       </c>
       <c r="C28" t="n">
-        <v>65364.73</v>
+        <v>63905.12</v>
       </c>
       <c r="D28" t="n">
-        <v>61948.23</v>
+        <v>62703.47</v>
       </c>
       <c r="E28" t="n">
-        <v>64362.02</v>
+        <v>63754.9</v>
       </c>
       <c r="F28" t="n">
-        <v>2494.59</v>
+        <v>-607.12</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0403</v>
+        <v>-0.0094</v>
       </c>
       <c r="H28" t="n">
-        <v>3416.5</v>
+        <v>1201.65</v>
       </c>
       <c r="I28" t="n">
-        <v>59174.56</v>
+        <v>58531.73</v>
       </c>
       <c r="J28" t="n">
-        <v>59932.37</v>
+        <v>61298.29</v>
       </c>
       <c r="K28" t="n">
-        <v>60929.86</v>
+        <v>62653.77</v>
       </c>
       <c r="L28" t="n">
-        <v>61927.35</v>
+        <v>64009.25</v>
       </c>
       <c r="M28" t="n">
-        <v>62805</v>
+        <v>66070.27</v>
       </c>
       <c r="N28" t="n">
-        <v>63682.65</v>
+        <v>68131.28999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>64799.98</v>
+        <v>68781.23</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2862,78 +2862,76 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>63834.95</v>
+        <v>63995.28</v>
       </c>
       <c r="C29" t="n">
-        <v>63905.12</v>
+        <v>64240.5</v>
       </c>
       <c r="D29" t="n">
-        <v>62703.47</v>
+        <v>62864.43</v>
       </c>
       <c r="E29" t="n">
-        <v>63754.9</v>
+        <v>63957.53</v>
       </c>
       <c r="F29" t="n">
-        <v>-607.12</v>
+        <v>202.63</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0032</v>
       </c>
       <c r="H29" t="n">
-        <v>1201.65</v>
+        <v>1376.07</v>
       </c>
       <c r="I29" t="n">
-        <v>58531.73</v>
+        <v>61501.82</v>
       </c>
       <c r="J29" t="n">
-        <v>61298.29</v>
+        <v>62778.55</v>
       </c>
       <c r="K29" t="n">
-        <v>62653.77</v>
+        <v>63154.07</v>
       </c>
       <c r="L29" t="n">
-        <v>64009.25</v>
+        <v>63529.6</v>
       </c>
       <c r="M29" t="n">
-        <v>66070.27</v>
+        <v>64355.72</v>
       </c>
       <c r="N29" t="n">
-        <v>68131.28999999999</v>
+        <v>65181.85</v>
       </c>
       <c r="O29" t="n">
-        <v>68781.23</v>
+        <v>65106.77</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2941,16 +2939,20 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2963,59 +2965,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63995.28</v>
+        <v>64565.27</v>
       </c>
       <c r="C30" t="n">
-        <v>64240.5</v>
+        <v>66302.52</v>
       </c>
       <c r="D30" t="n">
-        <v>62864.43</v>
+        <v>64555.52</v>
       </c>
       <c r="E30" t="n">
-        <v>63957.53</v>
+        <v>66300.44</v>
       </c>
       <c r="F30" t="n">
-        <v>202.63</v>
+        <v>2342.91</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0366</v>
       </c>
       <c r="H30" t="n">
-        <v>1376.07</v>
+        <v>1747</v>
       </c>
       <c r="I30" t="n">
-        <v>61501.82</v>
+        <v>61488.36</v>
       </c>
       <c r="J30" t="n">
-        <v>62778.55</v>
+        <v>62783.99</v>
       </c>
       <c r="K30" t="n">
-        <v>63154.07</v>
+        <v>63269.5</v>
       </c>
       <c r="L30" t="n">
-        <v>63529.6</v>
+        <v>63755</v>
       </c>
       <c r="M30" t="n">
-        <v>64355.72</v>
+        <v>64645.57</v>
       </c>
       <c r="N30" t="n">
-        <v>65181.85</v>
+        <v>65536.13</v>
       </c>
       <c r="O30" t="n">
-        <v>65106.77</v>
+        <v>65616.57000000001</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3023,26 +3021,28 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
@@ -3054,134 +3054,136 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>64565.27</v>
+        <v>65896</v>
       </c>
       <c r="C31" t="n">
-        <v>66302.52</v>
+        <v>65983.13</v>
       </c>
       <c r="D31" t="n">
-        <v>64555.52</v>
+        <v>64942.07</v>
       </c>
       <c r="E31" t="n">
-        <v>66300.44</v>
+        <v>65683.25999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>2342.91</v>
+        <v>-617.1799999999999</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0366</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>1747</v>
+        <v>1041.06</v>
       </c>
       <c r="I31" t="n">
-        <v>61488.36</v>
+        <v>62808.52</v>
       </c>
       <c r="J31" t="n">
-        <v>62783.99</v>
+        <v>64989.14</v>
       </c>
       <c r="K31" t="n">
-        <v>63269.5</v>
+        <v>65426.94</v>
       </c>
       <c r="L31" t="n">
-        <v>63755</v>
+        <v>65864.73</v>
       </c>
       <c r="M31" t="n">
-        <v>64645.57</v>
+        <v>67173.94</v>
       </c>
       <c r="N31" t="n">
-        <v>65536.13</v>
+        <v>68483.14999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>65616.57000000001</v>
+        <v>68049.53</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>65896</v>
+        <v>65746.13</v>
       </c>
       <c r="C32" t="n">
-        <v>65983.13</v>
+        <v>65990.72</v>
       </c>
       <c r="D32" t="n">
-        <v>64942.07</v>
+        <v>64651.49</v>
       </c>
       <c r="E32" t="n">
-        <v>65683.25999999999</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>-617.1799999999999</v>
+        <v>-76.55</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="H32" t="n">
-        <v>1041.06</v>
+        <v>1339.23</v>
       </c>
       <c r="I32" t="n">
-        <v>62808.52</v>
+        <v>63901.01</v>
       </c>
       <c r="J32" t="n">
-        <v>64989.14</v>
+        <v>64752.52</v>
       </c>
       <c r="K32" t="n">
-        <v>65426.94</v>
+        <v>65162.73</v>
       </c>
       <c r="L32" t="n">
-        <v>65864.73</v>
+        <v>65572.92999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>67173.94</v>
+        <v>66203.78999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>68483.14999999999</v>
+        <v>66834.64999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>68049.53</v>
+        <v>67024.2</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3198,7 +3200,7 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3224,74 +3226,74 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65746.13</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>65990.72</v>
+        <v>67006.84</v>
       </c>
       <c r="D33" t="n">
-        <v>64651.49</v>
+        <v>65848.58</v>
       </c>
       <c r="E33" t="n">
-        <v>65606.71000000001</v>
+        <v>66970.22</v>
       </c>
       <c r="F33" t="n">
-        <v>-76.55</v>
+        <v>1363.51</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0208</v>
       </c>
       <c r="H33" t="n">
-        <v>1339.23</v>
+        <v>1158.27</v>
       </c>
       <c r="I33" t="n">
-        <v>63901.01</v>
+        <v>63312.26</v>
       </c>
       <c r="J33" t="n">
-        <v>64752.52</v>
+        <v>64410.28</v>
       </c>
       <c r="K33" t="n">
-        <v>65162.73</v>
+        <v>64937.1</v>
       </c>
       <c r="L33" t="n">
-        <v>65572.92999999999</v>
+        <v>65463.91</v>
       </c>
       <c r="M33" t="n">
-        <v>66203.78999999999</v>
+        <v>66276.33</v>
       </c>
       <c r="N33" t="n">
-        <v>66834.64999999999</v>
+        <v>67088.75</v>
       </c>
       <c r="O33" t="n">
-        <v>67024.2</v>
+        <v>67329.95</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3301,59 +3303,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>65905.10000000001</v>
+        <v>66994.05</v>
       </c>
       <c r="C34" t="n">
-        <v>67006.84</v>
+        <v>67569.36</v>
       </c>
       <c r="D34" t="n">
-        <v>65848.58</v>
+        <v>66735.75999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>66970.22</v>
+        <v>67524.06</v>
       </c>
       <c r="F34" t="n">
-        <v>1363.51</v>
+        <v>553.84</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="H34" t="n">
-        <v>1158.27</v>
+        <v>833.6</v>
       </c>
       <c r="I34" t="n">
-        <v>63312.26</v>
+        <v>64690.31</v>
       </c>
       <c r="J34" t="n">
-        <v>64410.28</v>
+        <v>66083.21000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>64937.1</v>
+        <v>66391.09</v>
       </c>
       <c r="L34" t="n">
-        <v>65463.91</v>
+        <v>66698.96000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>66276.33</v>
+        <v>67549.35000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>67088.75</v>
+        <v>68399.74000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>67329.95</v>
+        <v>68165.11</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3364,20 +3362,18 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3392,50 +3388,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>66994.05</v>
+        <v>68033.17</v>
       </c>
       <c r="C35" t="n">
-        <v>67569.36</v>
+        <v>68799.71000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>66735.75999999999</v>
+        <v>68006.17</v>
       </c>
       <c r="E35" t="n">
-        <v>67524.06</v>
+        <v>68308.59</v>
       </c>
       <c r="F35" t="n">
-        <v>553.84</v>
+        <v>784.53</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0116</v>
       </c>
       <c r="H35" t="n">
-        <v>833.6</v>
+        <v>793.54</v>
       </c>
       <c r="I35" t="n">
-        <v>64690.31</v>
+        <v>65902.16</v>
       </c>
       <c r="J35" t="n">
-        <v>66083.21000000001</v>
+        <v>66876.21000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>66391.09</v>
+        <v>67107.25999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>66698.96000000001</v>
+        <v>67338.31</v>
       </c>
       <c r="M35" t="n">
-        <v>67549.35000000001</v>
+        <v>67940.86</v>
       </c>
       <c r="N35" t="n">
-        <v>68399.74000000001</v>
+        <v>68543.42</v>
       </c>
       <c r="O35" t="n">
-        <v>68165.11</v>
+        <v>68402.96000000001</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3446,21 +3442,25 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3472,50 +3472,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>68033.17</v>
+        <v>68811.17</v>
       </c>
       <c r="C36" t="n">
-        <v>68799.71000000001</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>68006.17</v>
+        <v>68471.14999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>68308.59</v>
+        <v>68713.8</v>
       </c>
       <c r="F36" t="n">
-        <v>784.53</v>
+        <v>405.2</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0059</v>
       </c>
       <c r="H36" t="n">
-        <v>793.54</v>
+        <v>1137.09</v>
       </c>
       <c r="I36" t="n">
-        <v>65902.16</v>
+        <v>67212.63</v>
       </c>
       <c r="J36" t="n">
-        <v>66876.21000000001</v>
+        <v>67467.88</v>
       </c>
       <c r="K36" t="n">
-        <v>67107.25999999999</v>
+        <v>67911.82000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>67338.31</v>
+        <v>68355.77</v>
       </c>
       <c r="M36" t="n">
-        <v>67940.86</v>
+        <v>68705.36</v>
       </c>
       <c r="N36" t="n">
-        <v>68543.42</v>
+        <v>69054.96000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>68402.96000000001</v>
+        <v>69593.25</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3526,14 +3526,14 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U36" s="8" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="V36" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W36" s="9" t="inlineStr">
@@ -3556,50 +3556,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>68811.17</v>
+        <v>68882.06</v>
       </c>
       <c r="C37" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>68471.14999999999</v>
+        <v>68492.03999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>68713.8</v>
+        <v>69220.25</v>
       </c>
       <c r="F37" t="n">
-        <v>405.2</v>
+        <v>506.45</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="H37" t="n">
-        <v>1137.09</v>
+        <v>733.53</v>
       </c>
       <c r="I37" t="n">
-        <v>67212.63</v>
+        <v>67334.05</v>
       </c>
       <c r="J37" t="n">
-        <v>67467.88</v>
+        <v>67413.75</v>
       </c>
       <c r="K37" t="n">
-        <v>67911.82000000001</v>
+        <v>68145.25</v>
       </c>
       <c r="L37" t="n">
-        <v>68355.77</v>
+        <v>68876.75</v>
       </c>
       <c r="M37" t="n">
-        <v>68705.36</v>
+        <v>69282.34</v>
       </c>
       <c r="N37" t="n">
-        <v>69054.96000000001</v>
+        <v>69687.94</v>
       </c>
       <c r="O37" t="n">
-        <v>69593.25</v>
+        <v>70745.34</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3610,7 +3610,7 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3620,89 +3620,93 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>68882.06</v>
+        <v>68847.35000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>69225.57000000001</v>
+        <v>69093.2</v>
       </c>
       <c r="D38" t="n">
-        <v>68492.03999999999</v>
+        <v>67368.96000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>69220.25</v>
+        <v>67460.73</v>
       </c>
       <c r="F38" t="n">
-        <v>506.45</v>
+        <v>-1759.52</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0254</v>
       </c>
       <c r="H38" t="n">
-        <v>733.53</v>
+        <v>1724.24</v>
       </c>
       <c r="I38" t="n">
-        <v>67334.05</v>
+        <v>67758.50999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>67413.75</v>
+        <v>68667.44</v>
       </c>
       <c r="K38" t="n">
-        <v>68145.25</v>
+        <v>68853.48</v>
       </c>
       <c r="L38" t="n">
-        <v>68876.75</v>
+        <v>69039.53</v>
       </c>
       <c r="M38" t="n">
-        <v>69282.34</v>
+        <v>69587.02</v>
       </c>
       <c r="N38" t="n">
-        <v>69687.94</v>
+        <v>70134.5</v>
       </c>
       <c r="O38" t="n">
-        <v>70745.34</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+        <v>69959.10000000001</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3710,81 +3714,77 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>68847.35000000001</v>
+        <v>66812.27</v>
       </c>
       <c r="C39" t="n">
-        <v>69093.2</v>
+        <v>66833.50999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>67368.96000000001</v>
+        <v>65133.98</v>
       </c>
       <c r="E39" t="n">
-        <v>67460.73</v>
+        <v>65326.42</v>
       </c>
       <c r="F39" t="n">
-        <v>-1759.52</v>
+        <v>-2134.3</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="H39" t="n">
-        <v>1724.24</v>
+        <v>1699.53</v>
       </c>
       <c r="I39" t="n">
-        <v>67758.50999999999</v>
+        <v>65644.72</v>
       </c>
       <c r="J39" t="n">
-        <v>68667.44</v>
+        <v>65351.31</v>
       </c>
       <c r="K39" t="n">
-        <v>68853.48</v>
+        <v>66598.61</v>
       </c>
       <c r="L39" t="n">
-        <v>69039.53</v>
+        <v>67845.89999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>69587.02</v>
+        <v>68322.85000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>70134.5</v>
+        <v>68799.78999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>69959.10000000001</v>
+        <v>70817.45</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3808,74 +3808,70 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>66812.27</v>
+        <v>65732.78999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>66833.50999999999</v>
+        <v>66325.32000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>65133.98</v>
+        <v>65652.25</v>
       </c>
       <c r="E40" t="n">
-        <v>65326.42</v>
+        <v>66216.78999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>-2134.3</v>
+        <v>890.37</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H40" t="n">
-        <v>1699.53</v>
+        <v>673.0700000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>65644.72</v>
+        <v>63434.45</v>
       </c>
       <c r="J40" t="n">
-        <v>65351.31</v>
+        <v>63298.23</v>
       </c>
       <c r="K40" t="n">
-        <v>66598.61</v>
+        <v>64476.66</v>
       </c>
       <c r="L40" t="n">
-        <v>67845.89999999999</v>
+        <v>65655.08</v>
       </c>
       <c r="M40" t="n">
-        <v>68322.85000000001</v>
+        <v>66176.19</v>
       </c>
       <c r="N40" t="n">
-        <v>68799.78999999999</v>
+        <v>66697.28999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>70817.45</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
+        <v>68533.03999999999</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3887,74 +3883,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>65732.78999999999</v>
+        <v>65427.69</v>
       </c>
       <c r="C41" t="n">
-        <v>66325.32000000001</v>
+        <v>66125.88</v>
       </c>
       <c r="D41" t="n">
-        <v>65652.25</v>
+        <v>65260.22</v>
       </c>
       <c r="E41" t="n">
-        <v>66216.78999999999</v>
+        <v>66016.36</v>
       </c>
       <c r="F41" t="n">
-        <v>890.37</v>
+        <v>-200.43</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.003</v>
       </c>
       <c r="H41" t="n">
-        <v>673.0700000000001</v>
+        <v>865.66</v>
       </c>
       <c r="I41" t="n">
-        <v>63434.45</v>
+        <v>64979.18</v>
       </c>
       <c r="J41" t="n">
-        <v>63298.23</v>
+        <v>65657.72</v>
       </c>
       <c r="K41" t="n">
-        <v>64476.66</v>
+        <v>65880.25</v>
       </c>
       <c r="L41" t="n">
-        <v>65655.08</v>
+        <v>66102.78999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>66176.19</v>
+        <v>66553.32000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>66697.28999999999</v>
+        <v>67003.86</v>
       </c>
       <c r="O41" t="n">
-        <v>68533.03999999999</v>
+        <v>66998.39</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3967,76 +3969,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>65427.69</v>
+        <v>65978.95</v>
       </c>
       <c r="C42" t="n">
-        <v>66125.88</v>
+        <v>66257.73</v>
       </c>
       <c r="D42" t="n">
-        <v>65260.22</v>
+        <v>65470.95</v>
       </c>
       <c r="E42" t="n">
-        <v>66016.36</v>
+        <v>65528.09</v>
       </c>
       <c r="F42" t="n">
-        <v>-200.43</v>
+        <v>-488.27</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0074</v>
       </c>
       <c r="H42" t="n">
-        <v>865.66</v>
+        <v>786.78</v>
       </c>
       <c r="I42" t="n">
-        <v>64979.18</v>
+        <v>64394.55</v>
       </c>
       <c r="J42" t="n">
-        <v>65657.72</v>
+        <v>65312.35</v>
       </c>
       <c r="K42" t="n">
-        <v>65880.25</v>
+        <v>65583.53</v>
       </c>
       <c r="L42" t="n">
-        <v>66102.78999999999</v>
+        <v>65854.71000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>66553.32000000001</v>
+        <v>66449.19</v>
       </c>
       <c r="N42" t="n">
-        <v>67003.86</v>
+        <v>67043.67999999999</v>
       </c>
       <c r="O42" t="n">
-        <v>66998.39</v>
+        <v>66991.55</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q42" s="6" t="n">
+        <v/>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4053,75 +4049,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>65978.95</v>
+        <v>65195.26</v>
       </c>
       <c r="C43" t="n">
-        <v>66257.73</v>
+        <v>65904.24000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>65470.95</v>
+        <v>64609.47</v>
       </c>
       <c r="E43" t="n">
-        <v>65528.09</v>
+        <v>65856.42999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>-488.27</v>
+        <v>328.34</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.005</v>
       </c>
       <c r="H43" t="n">
-        <v>786.78</v>
+        <v>1294.77</v>
       </c>
       <c r="I43" t="n">
-        <v>64394.55</v>
+        <v>64684.17</v>
       </c>
       <c r="J43" t="n">
-        <v>65312.35</v>
+        <v>64573.19</v>
       </c>
       <c r="K43" t="n">
-        <v>65583.53</v>
+        <v>65134.7</v>
       </c>
       <c r="L43" t="n">
-        <v>65854.71000000001</v>
+        <v>65696.21000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>66449.19</v>
+        <v>65921.48</v>
       </c>
       <c r="N43" t="n">
-        <v>67043.67999999999</v>
+        <v>66146.74000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>66991.55</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
+        <v>67044.5</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4135,72 +4139,68 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>65195.26</v>
+        <v>65604.49000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>65904.24000000001</v>
+        <v>66442.34</v>
       </c>
       <c r="D44" t="n">
-        <v>64609.47</v>
+        <v>65390.55</v>
       </c>
       <c r="E44" t="n">
-        <v>65856.42999999999</v>
+        <v>66262.16</v>
       </c>
       <c r="F44" t="n">
-        <v>328.34</v>
+        <v>405.73</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0062</v>
       </c>
       <c r="H44" t="n">
-        <v>1294.77</v>
+        <v>1051.79</v>
       </c>
       <c r="I44" t="n">
-        <v>64684.17</v>
+        <v>63314.7</v>
       </c>
       <c r="J44" t="n">
-        <v>64573.19</v>
+        <v>64861.44</v>
       </c>
       <c r="K44" t="n">
-        <v>65134.7</v>
+        <v>65209.04</v>
       </c>
       <c r="L44" t="n">
-        <v>65696.21000000001</v>
+        <v>65556.64</v>
       </c>
       <c r="M44" t="n">
-        <v>65921.48</v>
+        <v>66503.82000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>66146.74000000001</v>
+        <v>67450.99000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>67044.5</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67199.02</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
       </c>
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4223,57 +4223,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>65604.49000000001</v>
+        <v>66775.78</v>
       </c>
       <c r="C45" t="n">
-        <v>66442.34</v>
+        <v>66954.69</v>
       </c>
       <c r="D45" t="n">
-        <v>65390.55</v>
+        <v>65782.59</v>
       </c>
       <c r="E45" t="n">
-        <v>66262.16</v>
+        <v>66131.98</v>
       </c>
       <c r="F45" t="n">
-        <v>405.73</v>
+        <v>-130.18</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.002</v>
       </c>
       <c r="H45" t="n">
-        <v>1051.79</v>
+        <v>1172.09</v>
       </c>
       <c r="I45" t="n">
-        <v>63314.7</v>
+        <v>64338.76</v>
       </c>
       <c r="J45" t="n">
-        <v>64861.44</v>
+        <v>65383.22</v>
       </c>
       <c r="K45" t="n">
-        <v>65209.04</v>
+        <v>65736.25999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>65556.64</v>
+        <v>66089.3</v>
       </c>
       <c r="M45" t="n">
-        <v>66503.82000000001</v>
+        <v>66788.05</v>
       </c>
       <c r="N45" t="n">
-        <v>67450.99000000001</v>
+        <v>67486.8</v>
       </c>
       <c r="O45" t="n">
-        <v>67199.02</v>
+        <v>67494.14</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4284,14 +4284,14 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U45" s="8" t="n">
@@ -4307,57 +4307,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>66775.78</v>
+        <v>66104.49000000001</v>
       </c>
       <c r="C46" t="n">
-        <v>66954.69</v>
+        <v>66842.82000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>65782.59</v>
+        <v>66012.2</v>
       </c>
       <c r="E46" t="n">
-        <v>66131.98</v>
+        <v>66405.56</v>
       </c>
       <c r="F46" t="n">
-        <v>-130.18</v>
+        <v>273.59</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0041</v>
       </c>
       <c r="H46" t="n">
-        <v>1172.09</v>
+        <v>830.62</v>
       </c>
       <c r="I46" t="n">
-        <v>64338.76</v>
+        <v>64610.5</v>
       </c>
       <c r="J46" t="n">
-        <v>65383.22</v>
+        <v>64841.55</v>
       </c>
       <c r="K46" t="n">
-        <v>65736.25999999999</v>
+        <v>65545.92999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>66089.3</v>
+        <v>66250.31</v>
       </c>
       <c r="M46" t="n">
-        <v>66788.05</v>
+        <v>66718.02</v>
       </c>
       <c r="N46" t="n">
-        <v>67486.8</v>
+        <v>67185.74000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>67494.14</v>
+        <v>68126.78</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4368,7 +4368,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4398,69 +4398,73 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>66104.49000000001</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>66842.82000000001</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>66012.2</v>
+        <v>64832.1</v>
       </c>
       <c r="E47" t="n">
-        <v>66405.56</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>273.59</v>
+        <v>-93.63</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0014</v>
       </c>
       <c r="H47" t="n">
-        <v>830.62</v>
+        <v>1479.83</v>
       </c>
       <c r="I47" t="n">
-        <v>64610.5</v>
+        <v>65181.59</v>
       </c>
       <c r="J47" t="n">
-        <v>64841.55</v>
+        <v>65563.97</v>
       </c>
       <c r="K47" t="n">
-        <v>65545.92999999999</v>
+        <v>65990.25</v>
       </c>
       <c r="L47" t="n">
-        <v>66250.31</v>
+        <v>66416.53999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>66718.02</v>
+        <v>66820.87</v>
       </c>
       <c r="N47" t="n">
-        <v>67185.74000000001</v>
+        <v>67225.21000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>68126.78</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+        <v>67673.44</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4473,78 +4477,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65668.50999999999</v>
+        <v>65885.47</v>
       </c>
       <c r="C48" t="n">
-        <v>66311.92999999999</v>
+        <v>66525.7</v>
       </c>
       <c r="D48" t="n">
-        <v>64832.1</v>
+        <v>65576.61</v>
       </c>
       <c r="E48" t="n">
-        <v>66311.92999999999</v>
+        <v>66215.34</v>
       </c>
       <c r="F48" t="n">
-        <v>-93.63</v>
+        <v>-96.59</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0015</v>
       </c>
       <c r="H48" t="n">
-        <v>1479.83</v>
+        <v>949.09</v>
       </c>
       <c r="I48" t="n">
-        <v>65181.59</v>
+        <v>63352.27</v>
       </c>
       <c r="J48" t="n">
-        <v>65563.97</v>
+        <v>65202.06</v>
       </c>
       <c r="K48" t="n">
-        <v>65990.25</v>
+        <v>65572.02</v>
       </c>
       <c r="L48" t="n">
-        <v>66416.53999999999</v>
+        <v>65941.97</v>
       </c>
       <c r="M48" t="n">
-        <v>66820.87</v>
+        <v>67051.84</v>
       </c>
       <c r="N48" t="n">
-        <v>67225.21000000001</v>
+        <v>68161.71000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>67673.44</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67791.75999999999</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4561,68 +4555,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65885.47</v>
+        <v>65195.43</v>
       </c>
       <c r="C49" t="n">
-        <v>66525.7</v>
+        <v>65195.43</v>
       </c>
       <c r="D49" t="n">
-        <v>65576.61</v>
+        <v>64215.47</v>
       </c>
       <c r="E49" t="n">
-        <v>66215.34</v>
+        <v>64325.64</v>
       </c>
       <c r="F49" t="n">
-        <v>-96.59</v>
+        <v>-1889.7</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0285</v>
       </c>
       <c r="H49" t="n">
-        <v>949.09</v>
+        <v>979.96</v>
       </c>
       <c r="I49" t="n">
-        <v>63352.27</v>
+        <v>64627.52</v>
       </c>
       <c r="J49" t="n">
-        <v>65202.06</v>
+        <v>65348.34</v>
       </c>
       <c r="K49" t="n">
-        <v>65572.02</v>
+        <v>65740.8</v>
       </c>
       <c r="L49" t="n">
-        <v>65941.97</v>
+        <v>66133.25</v>
       </c>
       <c r="M49" t="n">
-        <v>67051.84</v>
+        <v>66689.89</v>
       </c>
       <c r="N49" t="n">
-        <v>68161.71000000001</v>
+        <v>67246.53</v>
       </c>
       <c r="O49" t="n">
-        <v>67791.75999999999</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+        <v>67474.8</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4639,78 +4643,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="C50" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="D50" t="n">
-        <v>64215.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E50" t="n">
-        <v>64325.64</v>
+        <v>64214.48</v>
       </c>
       <c r="F50" t="n">
-        <v>-1889.7</v>
+        <v>-111.16</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0017</v>
       </c>
       <c r="H50" t="n">
-        <v>979.96</v>
+        <v>952.01</v>
       </c>
       <c r="I50" t="n">
-        <v>64627.52</v>
+        <v>63235.51</v>
       </c>
       <c r="J50" t="n">
-        <v>65348.34</v>
+        <v>63155.78</v>
       </c>
       <c r="K50" t="n">
-        <v>65740.8</v>
+        <v>63835.66</v>
       </c>
       <c r="L50" t="n">
-        <v>66133.25</v>
+        <v>64515.54</v>
       </c>
       <c r="M50" t="n">
-        <v>66689.89</v>
+        <v>64815.62</v>
       </c>
       <c r="N50" t="n">
-        <v>67246.53</v>
+        <v>65115.7</v>
       </c>
       <c r="O50" t="n">
-        <v>67474.8</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66175.39</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4732,50 +4728,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>64724.81</v>
+        <v>64498.94</v>
       </c>
       <c r="C51" t="n">
-        <v>64724.81</v>
+        <v>65182.45</v>
       </c>
       <c r="D51" t="n">
-        <v>63772.8</v>
+        <v>64228.47</v>
       </c>
       <c r="E51" t="n">
-        <v>64214.48</v>
+        <v>65020.94</v>
       </c>
       <c r="F51" t="n">
-        <v>-111.16</v>
+        <v>806.46</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="H51" t="n">
-        <v>952.01</v>
+        <v>953.98</v>
       </c>
       <c r="I51" t="n">
-        <v>63235.51</v>
+        <v>62820.79</v>
       </c>
       <c r="J51" t="n">
-        <v>63155.78</v>
+        <v>63245.31</v>
       </c>
       <c r="K51" t="n">
-        <v>63835.66</v>
+        <v>63738.48</v>
       </c>
       <c r="L51" t="n">
-        <v>64515.54</v>
+        <v>64231.64</v>
       </c>
       <c r="M51" t="n">
-        <v>64815.62</v>
+        <v>64690.48</v>
       </c>
       <c r="N51" t="n">
-        <v>65115.7</v>
+        <v>65149.33</v>
       </c>
       <c r="O51" t="n">
-        <v>66175.39</v>
+        <v>65676.82000000001</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4783,21 +4779,23 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4807,55 +4805,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>64498.94</v>
+        <v>65600.42</v>
       </c>
       <c r="C52" t="n">
-        <v>65182.45</v>
+        <v>66668.71000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>64228.47</v>
+        <v>65600.42</v>
       </c>
       <c r="E52" t="n">
-        <v>65020.94</v>
+        <v>66399.84</v>
       </c>
       <c r="F52" t="n">
-        <v>806.46</v>
+        <v>1378.9</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="H52" t="n">
-        <v>953.98</v>
+        <v>1068.29</v>
       </c>
       <c r="I52" t="n">
-        <v>62820.79</v>
+        <v>63274.49</v>
       </c>
       <c r="J52" t="n">
-        <v>63245.31</v>
+        <v>64224.7</v>
       </c>
       <c r="K52" t="n">
-        <v>63738.48</v>
+        <v>64543.95</v>
       </c>
       <c r="L52" t="n">
-        <v>64231.64</v>
+        <v>64863.2</v>
       </c>
       <c r="M52" t="n">
-        <v>64690.48</v>
+        <v>65497.93</v>
       </c>
       <c r="N52" t="n">
-        <v>65149.33</v>
+        <v>66132.66</v>
       </c>
       <c r="O52" t="n">
-        <v>65676.82000000001</v>
+        <v>66136.42999999999</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4866,7 +4868,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4878,171 +4880,167 @@
       </c>
       <c r="U52" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W52" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W52" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65600.42</v>
+        <v>65843.69</v>
       </c>
       <c r="C53" t="n">
-        <v>66668.71000000001</v>
+        <v>66791.84</v>
       </c>
       <c r="D53" t="n">
-        <v>65600.42</v>
+        <v>65269.33</v>
       </c>
       <c r="E53" t="n">
-        <v>66399.84</v>
+        <v>65269.33</v>
       </c>
       <c r="F53" t="n">
-        <v>1378.9</v>
+        <v>-1130.52</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.017</v>
       </c>
       <c r="H53" t="n">
-        <v>1068.29</v>
+        <v>1522.52</v>
       </c>
       <c r="I53" t="n">
-        <v>63274.49</v>
+        <v>64532.13</v>
       </c>
       <c r="J53" t="n">
-        <v>64224.7</v>
+        <v>65464.19</v>
       </c>
       <c r="K53" t="n">
-        <v>64543.95</v>
+        <v>65865.7</v>
       </c>
       <c r="L53" t="n">
-        <v>64863.2</v>
+        <v>66267.21000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>65497.93</v>
+        <v>66933.99000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>66132.66</v>
+        <v>67600.77</v>
       </c>
       <c r="O53" t="n">
-        <v>66136.42999999999</v>
+        <v>67737</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W53" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr"/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>65843.69</v>
+        <v>65087.22</v>
       </c>
       <c r="C54" t="n">
-        <v>66791.84</v>
+        <v>65794.03</v>
       </c>
       <c r="D54" t="n">
-        <v>65269.33</v>
+        <v>65017.68</v>
       </c>
       <c r="E54" t="n">
-        <v>65269.33</v>
+        <v>65142.78</v>
       </c>
       <c r="F54" t="n">
-        <v>-1130.52</v>
+        <v>-126.55</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0019</v>
       </c>
       <c r="H54" t="n">
-        <v>1522.52</v>
+        <v>776.35</v>
       </c>
       <c r="I54" t="n">
-        <v>64532.13</v>
+        <v>63746.81</v>
       </c>
       <c r="J54" t="n">
-        <v>65464.19</v>
+        <v>63366.18</v>
       </c>
       <c r="K54" t="n">
-        <v>65865.7</v>
+        <v>64508.07</v>
       </c>
       <c r="L54" t="n">
-        <v>66267.21000000001</v>
+        <v>65649.96000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>66933.99000000001</v>
+        <v>66030.59</v>
       </c>
       <c r="N54" t="n">
-        <v>67600.77</v>
+        <v>66411.21000000001</v>
       </c>
       <c r="O54" t="n">
-        <v>67737</v>
+        <v>68314.36</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5059,70 +5057,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>65087.22</v>
+        <v>64768.53</v>
       </c>
       <c r="C55" t="n">
-        <v>65794.03</v>
+        <v>65270.95</v>
       </c>
       <c r="D55" t="n">
-        <v>65017.68</v>
+        <v>64186.68</v>
       </c>
       <c r="E55" t="n">
-        <v>65142.78</v>
+        <v>65270.95</v>
       </c>
       <c r="F55" t="n">
-        <v>-126.55</v>
+        <v>128.17</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="H55" t="n">
-        <v>776.35</v>
+        <v>1084.27</v>
       </c>
       <c r="I55" t="n">
-        <v>63746.81</v>
+        <v>64241.33</v>
       </c>
       <c r="J55" t="n">
-        <v>63366.18</v>
+        <v>64234.89</v>
       </c>
       <c r="K55" t="n">
-        <v>64508.07</v>
+        <v>64754.61</v>
       </c>
       <c r="L55" t="n">
-        <v>65649.96000000001</v>
+        <v>65274.32</v>
       </c>
       <c r="M55" t="n">
-        <v>66030.59</v>
+        <v>65530.96</v>
       </c>
       <c r="N55" t="n">
-        <v>66411.21000000001</v>
+        <v>65787.60000000001</v>
       </c>
       <c r="O55" t="n">
-        <v>68314.36</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
+        <v>66570.38</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5141,64 +5141,66 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>64768.53</v>
+        <v>64276.82</v>
       </c>
       <c r="C56" t="n">
-        <v>65270.95</v>
+        <v>64312.02</v>
       </c>
       <c r="D56" t="n">
-        <v>64186.68</v>
+        <v>63208.63</v>
       </c>
       <c r="E56" t="n">
-        <v>65270.95</v>
+        <v>64011.34</v>
       </c>
       <c r="F56" t="n">
-        <v>128.17</v>
+        <v>-1259.61</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H56" t="n">
-        <v>1084.27</v>
+        <v>1103.39</v>
       </c>
       <c r="I56" t="n">
-        <v>64241.33</v>
+        <v>63102.41</v>
       </c>
       <c r="J56" t="n">
-        <v>64234.89</v>
+        <v>64457.75</v>
       </c>
       <c r="K56" t="n">
-        <v>64754.61</v>
+        <v>64728.81</v>
       </c>
       <c r="L56" t="n">
-        <v>65274.32</v>
+        <v>64999.88</v>
       </c>
       <c r="M56" t="n">
-        <v>65530.96</v>
+        <v>65813.08</v>
       </c>
       <c r="N56" t="n">
-        <v>65787.60000000001</v>
+        <v>66626.28999999999</v>
       </c>
       <c r="O56" t="n">
-        <v>66570.38</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66355.22</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
@@ -5206,9 +5208,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5225,74 +5227,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>64276.82</v>
+        <v>63659.53</v>
       </c>
       <c r="C57" t="n">
-        <v>64312.02</v>
+        <v>63691.53</v>
       </c>
       <c r="D57" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E57" t="n">
-        <v>64011.34</v>
+        <v>63492.99</v>
       </c>
       <c r="F57" t="n">
-        <v>-1259.61</v>
+        <v>-518.35</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0081</v>
       </c>
       <c r="H57" t="n">
-        <v>1103.39</v>
+        <v>965.35</v>
       </c>
       <c r="I57" t="n">
-        <v>63102.41</v>
+        <v>62105.24</v>
       </c>
       <c r="J57" t="n">
-        <v>64457.75</v>
+        <v>63033.46</v>
       </c>
       <c r="K57" t="n">
-        <v>64728.81</v>
+        <v>63459.64</v>
       </c>
       <c r="L57" t="n">
-        <v>64999.88</v>
+        <v>63885.83</v>
       </c>
       <c r="M57" t="n">
-        <v>65813.08</v>
+        <v>64563.04</v>
       </c>
       <c r="N57" t="n">
-        <v>66626.28999999999</v>
+        <v>65240.24</v>
       </c>
       <c r="O57" t="n">
-        <v>66355.22</v>
+        <v>65415.41</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5316,71 +5314,69 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>63659.53</v>
+        <v>63190.37</v>
       </c>
       <c r="C58" t="n">
-        <v>63691.53</v>
+        <v>64101</v>
       </c>
       <c r="D58" t="n">
-        <v>62726.18</v>
+        <v>63067.18</v>
       </c>
       <c r="E58" t="n">
-        <v>63492.99</v>
+        <v>63484.1</v>
       </c>
       <c r="F58" t="n">
-        <v>-518.35</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0001</v>
       </c>
       <c r="H58" t="n">
-        <v>965.35</v>
+        <v>1033.82</v>
       </c>
       <c r="I58" t="n">
-        <v>62105.24</v>
+        <v>61760.83</v>
       </c>
       <c r="J58" t="n">
-        <v>63033.46</v>
+        <v>62669.7</v>
       </c>
       <c r="K58" t="n">
-        <v>63459.64</v>
+        <v>63010.31</v>
       </c>
       <c r="L58" t="n">
-        <v>63885.83</v>
+        <v>63350.92</v>
       </c>
       <c r="M58" t="n">
-        <v>64563.04</v>
+        <v>63975.66</v>
       </c>
       <c r="N58" t="n">
-        <v>65240.24</v>
+        <v>64600.41</v>
       </c>
       <c r="O58" t="n">
-        <v>65415.41</v>
+        <v>64656.88</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5393,55 +5389,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>63190.37</v>
+        <v>63672.13</v>
       </c>
       <c r="C59" t="n">
-        <v>64101</v>
+        <v>63923</v>
       </c>
       <c r="D59" t="n">
-        <v>63067.18</v>
+        <v>63209.92</v>
       </c>
       <c r="E59" t="n">
-        <v>63484.1</v>
+        <v>63923</v>
       </c>
       <c r="F59" t="n">
-        <v>-8.890000000000001</v>
+        <v>438.9</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0069</v>
       </c>
       <c r="H59" t="n">
-        <v>1033.82</v>
+        <v>713.08</v>
       </c>
       <c r="I59" t="n">
-        <v>61760.83</v>
+        <v>62033.36</v>
       </c>
       <c r="J59" t="n">
-        <v>62669.7</v>
+        <v>62400.29</v>
       </c>
       <c r="K59" t="n">
-        <v>63010.31</v>
+        <v>62967.19</v>
       </c>
       <c r="L59" t="n">
-        <v>63350.92</v>
+        <v>63534.1</v>
       </c>
       <c r="M59" t="n">
-        <v>63975.66</v>
+        <v>64001.01</v>
       </c>
       <c r="N59" t="n">
-        <v>64600.41</v>
+        <v>64467.93</v>
       </c>
       <c r="O59" t="n">
-        <v>64656.88</v>
+        <v>65134.82</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5452,14 +5452,14 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U59" s="8" t="n">
@@ -5482,50 +5482,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>63672.13</v>
+        <v>64643.58</v>
       </c>
       <c r="C60" t="n">
-        <v>63923</v>
+        <v>64643.58</v>
       </c>
       <c r="D60" t="n">
-        <v>63209.92</v>
+        <v>63824.56</v>
       </c>
       <c r="E60" t="n">
-        <v>63923</v>
+        <v>64136.25</v>
       </c>
       <c r="F60" t="n">
-        <v>438.9</v>
+        <v>213.25</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0033</v>
       </c>
       <c r="H60" t="n">
-        <v>713.08</v>
+        <v>819.02</v>
       </c>
       <c r="I60" t="n">
-        <v>62033.36</v>
+        <v>62496.84</v>
       </c>
       <c r="J60" t="n">
-        <v>62400.29</v>
+        <v>63388.19</v>
       </c>
       <c r="K60" t="n">
-        <v>62967.19</v>
+        <v>63566.46</v>
       </c>
       <c r="L60" t="n">
-        <v>63534.1</v>
+        <v>63744.73</v>
       </c>
       <c r="M60" t="n">
-        <v>64001.01</v>
+        <v>64279.54</v>
       </c>
       <c r="N60" t="n">
-        <v>64467.93</v>
+        <v>64814.35</v>
       </c>
       <c r="O60" t="n">
-        <v>65134.82</v>
+        <v>64636.08</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5536,7 +5536,7 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="10" t="inlineStr">
+      <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5549,8 +5549,10 @@
       <c r="U60" s="8" t="n">
         <v/>
       </c>
-      <c r="V60" s="8" t="n">
-        <v/>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W60" s="11" t="inlineStr">
         <is>
@@ -5559,57 +5561,57 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>64643.58</v>
+        <v>64681.55</v>
       </c>
       <c r="C61" t="n">
-        <v>64643.58</v>
+        <v>65436.57</v>
       </c>
       <c r="D61" t="n">
-        <v>63824.56</v>
+        <v>64403.85</v>
       </c>
       <c r="E61" t="n">
-        <v>64136.25</v>
+        <v>65018.95</v>
       </c>
       <c r="F61" t="n">
-        <v>213.25</v>
+        <v>882.7</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0138</v>
       </c>
       <c r="H61" t="n">
-        <v>819.02</v>
+        <v>1032.72</v>
       </c>
       <c r="I61" t="n">
-        <v>62496.84</v>
+        <v>63005.54</v>
       </c>
       <c r="J61" t="n">
-        <v>63388.19</v>
+        <v>63268.32</v>
       </c>
       <c r="K61" t="n">
-        <v>63566.46</v>
+        <v>63726.74</v>
       </c>
       <c r="L61" t="n">
-        <v>63744.73</v>
+        <v>64185.16</v>
       </c>
       <c r="M61" t="n">
-        <v>64279.54</v>
+        <v>64545.76</v>
       </c>
       <c r="N61" t="n">
-        <v>64814.35</v>
+        <v>64906.36</v>
       </c>
       <c r="O61" t="n">
-        <v>64636.08</v>
+        <v>65462.6</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5620,116 +5622,30 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>64681.55</v>
-      </c>
-      <c r="C62" t="n">
-        <v>65436.57</v>
-      </c>
-      <c r="D62" t="n">
-        <v>64403.85</v>
-      </c>
-      <c r="E62" t="n">
-        <v>65018.95</v>
-      </c>
-      <c r="F62" t="n">
-        <v>882.7</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0138</v>
-      </c>
-      <c r="H62" t="n">
-        <v>1032.72</v>
-      </c>
-      <c r="I62" t="n">
-        <v>63005.54</v>
-      </c>
-      <c r="J62" t="n">
-        <v>63268.32</v>
-      </c>
-      <c r="K62" t="n">
-        <v>63726.74</v>
-      </c>
-      <c r="L62" t="n">
-        <v>64185.16</v>
-      </c>
-      <c r="M62" t="n">
-        <v>64545.76</v>
-      </c>
-      <c r="N62" t="n">
-        <v>64906.36</v>
-      </c>
-      <c r="O62" t="n">
-        <v>65462.6</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X61"/>
+  <dimension ref="A1:X60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,83 +634,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70114.09</v>
+        <v>71587.71000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>72594.22</v>
+        <v>71786.28</v>
       </c>
       <c r="D2" t="n">
-        <v>69982.67</v>
+        <v>68639.84</v>
       </c>
       <c r="E2" t="n">
-        <v>72366.34</v>
+        <v>69360.88</v>
       </c>
       <c r="F2" t="n">
-        <v>3191.38</v>
+        <v>-3005.46</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0461</v>
+        <v>-0.0415</v>
       </c>
       <c r="H2" t="n">
-        <v>2611.55</v>
+        <v>3146.44</v>
       </c>
       <c r="I2" t="n">
-        <v>66703.49000000001</v>
+        <v>67371.12</v>
       </c>
       <c r="J2" t="n">
-        <v>67334.89</v>
+        <v>70293.75</v>
       </c>
       <c r="K2" t="n">
-        <v>68296.16</v>
+        <v>71060.57000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>69257.44</v>
+        <v>71827.39</v>
       </c>
       <c r="M2" t="n">
-        <v>70053.77</v>
+        <v>73672.12</v>
       </c>
       <c r="N2" t="n">
-        <v>70850.11</v>
+        <v>75516.84</v>
       </c>
       <c r="O2" t="n">
-        <v>71976.32000000001</v>
+        <v>75205.77</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -718,67 +716,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71587.71000000001</v>
+        <v>69609.88</v>
       </c>
       <c r="C3" t="n">
-        <v>71786.28</v>
+        <v>69609.88</v>
       </c>
       <c r="D3" t="n">
-        <v>68639.84</v>
+        <v>67997.57000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>69360.88</v>
+        <v>69468.11</v>
       </c>
       <c r="F3" t="n">
-        <v>-3005.46</v>
+        <v>107.23</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0415</v>
+        <v>0.0015</v>
       </c>
       <c r="H3" t="n">
-        <v>3146.44</v>
+        <v>1612.31</v>
       </c>
       <c r="I3" t="n">
-        <v>67371.12</v>
+        <v>65493.41</v>
       </c>
       <c r="J3" t="n">
-        <v>70293.75</v>
+        <v>65788.36</v>
       </c>
       <c r="K3" t="n">
-        <v>71060.57000000001</v>
+        <v>67787.66</v>
       </c>
       <c r="L3" t="n">
-        <v>71827.39</v>
+        <v>69786.97</v>
       </c>
       <c r="M3" t="n">
-        <v>73672.12</v>
+        <v>70934.10000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>75516.84</v>
+        <v>72081.23</v>
       </c>
       <c r="O3" t="n">
-        <v>75205.77</v>
+        <v>74932.72</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -790,60 +784,64 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69609.88</v>
+        <v>70085.60000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>69609.88</v>
+        <v>70667</v>
       </c>
       <c r="D4" t="n">
-        <v>67997.57000000001</v>
+        <v>69302.19</v>
       </c>
       <c r="E4" t="n">
-        <v>69468.11</v>
+        <v>70062.32000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>107.23</v>
+        <v>594.21</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0086</v>
       </c>
       <c r="H4" t="n">
-        <v>1612.31</v>
+        <v>1364.81</v>
       </c>
       <c r="I4" t="n">
-        <v>65493.41</v>
+        <v>66385.25999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>65788.36</v>
+        <v>68187.99000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>67787.66</v>
+        <v>68661.95</v>
       </c>
       <c r="L4" t="n">
-        <v>69786.97</v>
+        <v>69135.92</v>
       </c>
       <c r="M4" t="n">
-        <v>70934.10000000001</v>
+        <v>70274.27</v>
       </c>
       <c r="N4" t="n">
-        <v>72081.23</v>
+        <v>71412.61</v>
       </c>
       <c r="O4" t="n">
-        <v>74932.72</v>
+        <v>71222.2</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -856,11 +854,13 @@
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -868,64 +868,64 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70085.60000000001</v>
+        <v>70774.28</v>
       </c>
       <c r="C5" t="n">
-        <v>70667</v>
+        <v>71962.34</v>
       </c>
       <c r="D5" t="n">
-        <v>69302.19</v>
+        <v>70126.14</v>
       </c>
       <c r="E5" t="n">
-        <v>70062.32000000001</v>
+        <v>70474.96000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>594.21</v>
+        <v>412.64</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0059</v>
       </c>
       <c r="H5" t="n">
-        <v>1364.81</v>
+        <v>1836.2</v>
       </c>
       <c r="I5" t="n">
-        <v>66385.25999999999</v>
+        <v>67937.38</v>
       </c>
       <c r="J5" t="n">
-        <v>68187.99000000001</v>
+        <v>68736.37</v>
       </c>
       <c r="K5" t="n">
-        <v>68661.95</v>
+        <v>69379.91</v>
       </c>
       <c r="L5" t="n">
-        <v>69135.92</v>
+        <v>70023.46000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>70274.27</v>
+        <v>70744.73</v>
       </c>
       <c r="N5" t="n">
-        <v>71412.61</v>
+        <v>71466</v>
       </c>
       <c r="O5" t="n">
-        <v>71222.2</v>
+        <v>72031.81</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -936,7 +936,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -946,13 +946,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U5" s="8" t="n">
-        <v/>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -966,218 +968,220 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70774.28</v>
+        <v>70039.89</v>
       </c>
       <c r="C6" t="n">
-        <v>71962.34</v>
+        <v>70081.39</v>
       </c>
       <c r="D6" t="n">
-        <v>70126.14</v>
+        <v>68676.25999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>70474.96000000001</v>
+        <v>68733.14999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>412.64</v>
+        <v>-1741.81</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0247</v>
       </c>
       <c r="H6" t="n">
-        <v>1836.2</v>
+        <v>1405.13</v>
       </c>
       <c r="I6" t="n">
-        <v>67937.38</v>
+        <v>68289.94</v>
       </c>
       <c r="J6" t="n">
-        <v>68736.37</v>
+        <v>68354.12</v>
       </c>
       <c r="K6" t="n">
-        <v>69379.91</v>
+        <v>69556.86</v>
       </c>
       <c r="L6" t="n">
-        <v>70023.46000000001</v>
+        <v>70759.60000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>70744.73</v>
+        <v>71393.06</v>
       </c>
       <c r="N6" t="n">
-        <v>71466</v>
+        <v>72026.52</v>
       </c>
       <c r="O6" t="n">
-        <v>72031.81</v>
+        <v>73798.55</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70039.89</v>
+        <v>68676.06</v>
       </c>
       <c r="C7" t="n">
-        <v>70081.39</v>
+        <v>69788.03</v>
       </c>
       <c r="D7" t="n">
-        <v>68676.25999999999</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>68733.14999999999</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1741.81</v>
+        <v>1010.92</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0147</v>
       </c>
       <c r="H7" t="n">
-        <v>1405.13</v>
+        <v>2178.54</v>
       </c>
       <c r="I7" t="n">
-        <v>68289.94</v>
+        <v>67271.12</v>
       </c>
       <c r="J7" t="n">
-        <v>68354.12</v>
+        <v>67005.17999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>69556.86</v>
+        <v>68030.58</v>
       </c>
       <c r="L7" t="n">
-        <v>70759.60000000001</v>
+        <v>69055.99000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>71393.06</v>
+        <v>69435.71000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>72026.52</v>
+        <v>69815.44</v>
       </c>
       <c r="O7" t="n">
-        <v>73798.55</v>
+        <v>71486.52</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>68676.06</v>
+        <v>69973.34</v>
       </c>
       <c r="C8" t="n">
-        <v>69788.03</v>
+        <v>70384.59</v>
       </c>
       <c r="D8" t="n">
-        <v>67609.49000000001</v>
+        <v>68904.41</v>
       </c>
       <c r="E8" t="n">
-        <v>69744.07000000001</v>
+        <v>69737.69</v>
       </c>
       <c r="F8" t="n">
-        <v>1010.92</v>
+        <v>-6.38</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0001</v>
       </c>
       <c r="H8" t="n">
-        <v>2178.54</v>
+        <v>1480.19</v>
       </c>
       <c r="I8" t="n">
-        <v>67271.12</v>
+        <v>65430.95</v>
       </c>
       <c r="J8" t="n">
-        <v>67005.17999999999</v>
+        <v>68088.19</v>
       </c>
       <c r="K8" t="n">
-        <v>68030.58</v>
+        <v>68654.8</v>
       </c>
       <c r="L8" t="n">
-        <v>69055.99000000001</v>
+        <v>69221.42</v>
       </c>
       <c r="M8" t="n">
-        <v>69435.71000000001</v>
+        <v>70833.34</v>
       </c>
       <c r="N8" t="n">
-        <v>69815.44</v>
+        <v>72445.25999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>71486.52</v>
+        <v>71966.57000000001</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1185,100 +1189,98 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69973.34</v>
+        <v>69460.08</v>
       </c>
       <c r="C9" t="n">
-        <v>70384.59</v>
+        <v>69957.50999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>68904.41</v>
+        <v>68003.92</v>
       </c>
       <c r="E9" t="n">
-        <v>69737.69</v>
+        <v>68256.96000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.38</v>
+        <v>-1480.73</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0212</v>
       </c>
       <c r="H9" t="n">
-        <v>1480.19</v>
+        <v>1953.59</v>
       </c>
       <c r="I9" t="n">
-        <v>65430.95</v>
+        <v>67424.22</v>
       </c>
       <c r="J9" t="n">
-        <v>68088.19</v>
+        <v>68304.09</v>
       </c>
       <c r="K9" t="n">
-        <v>68654.8</v>
+        <v>68997.59</v>
       </c>
       <c r="L9" t="n">
-        <v>69221.42</v>
+        <v>69691.09</v>
       </c>
       <c r="M9" t="n">
-        <v>70833.34</v>
+        <v>70477.78</v>
       </c>
       <c r="N9" t="n">
-        <v>72445.25999999999</v>
+        <v>71264.47</v>
       </c>
       <c r="O9" t="n">
-        <v>71966.57000000001</v>
+        <v>71864.78</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1290,79 +1292,73 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69460.08</v>
+        <v>67704.16</v>
       </c>
       <c r="C10" t="n">
-        <v>69957.50999999999</v>
+        <v>68432.67999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>68003.92</v>
+        <v>66819.05</v>
       </c>
       <c r="E10" t="n">
-        <v>68256.96000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="F10" t="n">
-        <v>-1480.73</v>
+        <v>-1437.91</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="H10" t="n">
-        <v>1953.59</v>
+        <v>1613.63</v>
       </c>
       <c r="I10" t="n">
-        <v>67424.22</v>
+        <v>66050.34</v>
       </c>
       <c r="J10" t="n">
-        <v>68304.09</v>
+        <v>65941.5</v>
       </c>
       <c r="K10" t="n">
-        <v>68997.59</v>
+        <v>67280.17</v>
       </c>
       <c r="L10" t="n">
-        <v>69691.09</v>
+        <v>68618.84</v>
       </c>
       <c r="M10" t="n">
-        <v>70477.78</v>
+        <v>69233.75</v>
       </c>
       <c r="N10" t="n">
-        <v>71264.47</v>
+        <v>69848.67</v>
       </c>
       <c r="O10" t="n">
-        <v>71864.78</v>
+        <v>71911.09</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1376,7 +1372,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1386,50 +1382,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>67704.16</v>
+        <v>67046.37</v>
       </c>
       <c r="C11" t="n">
-        <v>68432.67999999999</v>
+        <v>68447.89</v>
       </c>
       <c r="D11" t="n">
-        <v>66819.05</v>
+        <v>67008.89</v>
       </c>
       <c r="E11" t="n">
-        <v>66819.05</v>
+        <v>67743.85000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1437.91</v>
+        <v>924.8</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0211</v>
+        <v>0.0138</v>
       </c>
       <c r="H11" t="n">
-        <v>1613.63</v>
+        <v>1439</v>
       </c>
       <c r="I11" t="n">
-        <v>66050.34</v>
+        <v>65205.41</v>
       </c>
       <c r="J11" t="n">
-        <v>65941.5</v>
+        <v>64802.01</v>
       </c>
       <c r="K11" t="n">
-        <v>67280.17</v>
+        <v>66012.23</v>
       </c>
       <c r="L11" t="n">
-        <v>68618.84</v>
+        <v>67222.46000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>69233.75</v>
+        <v>67625.86</v>
       </c>
       <c r="N11" t="n">
-        <v>69848.67</v>
+        <v>68029.27</v>
       </c>
       <c r="O11" t="n">
-        <v>71911.09</v>
+        <v>70046.31</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1437,79 +1433,85 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67046.37</v>
+        <v>68526.72</v>
       </c>
       <c r="C12" t="n">
-        <v>68447.89</v>
+        <v>69374.86</v>
       </c>
       <c r="D12" t="n">
-        <v>67008.89</v>
+        <v>68271.91</v>
       </c>
       <c r="E12" t="n">
-        <v>67743.85000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F12" t="n">
-        <v>924.8</v>
+        <v>813.88</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.012</v>
       </c>
       <c r="H12" t="n">
-        <v>1439</v>
+        <v>1102.95</v>
       </c>
       <c r="I12" t="n">
-        <v>65205.41</v>
+        <v>65569.89</v>
       </c>
       <c r="J12" t="n">
-        <v>64802.01</v>
+        <v>66312.58</v>
       </c>
       <c r="K12" t="n">
-        <v>66012.23</v>
+        <v>67024.35000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>67222.46000000001</v>
+        <v>67736.12</v>
       </c>
       <c r="M12" t="n">
-        <v>67625.86</v>
+        <v>68463.35000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>68029.27</v>
+        <v>69190.58</v>
       </c>
       <c r="O12" t="n">
-        <v>70046.31</v>
+        <v>69886.89</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1520,7 +1522,7 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1538,7 +1540,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1552,155 +1554,147 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68526.72</v>
+        <v>68410.63</v>
       </c>
       <c r="C13" t="n">
-        <v>69374.86</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>68271.91</v>
+        <v>66653.11</v>
       </c>
       <c r="E13" t="n">
-        <v>68557.73</v>
+        <v>67242.73</v>
       </c>
       <c r="F13" t="n">
-        <v>813.88</v>
+        <v>-1315</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0192</v>
       </c>
       <c r="H13" t="n">
-        <v>1102.95</v>
+        <v>2425.1</v>
       </c>
       <c r="I13" t="n">
-        <v>65569.89</v>
+        <v>67168.95</v>
       </c>
       <c r="J13" t="n">
-        <v>66312.58</v>
+        <v>67321.95</v>
       </c>
       <c r="K13" t="n">
-        <v>67024.35000000001</v>
+        <v>68006.25</v>
       </c>
       <c r="L13" t="n">
-        <v>67736.12</v>
+        <v>68690.55</v>
       </c>
       <c r="M13" t="n">
-        <v>68463.35000000001</v>
+        <v>69109.2</v>
       </c>
       <c r="N13" t="n">
-        <v>69190.58</v>
+        <v>69527.85000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>69886.89</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+        <v>70477.81</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>68410.63</v>
+        <v>67002.94</v>
       </c>
       <c r="C14" t="n">
-        <v>69078.21000000001</v>
+        <v>67800.17999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>66653.11</v>
+        <v>66268.60000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>67242.73</v>
+        <v>67743.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-1315</v>
+        <v>500.77</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0074</v>
       </c>
       <c r="H14" t="n">
-        <v>2425.1</v>
+        <v>1531.58</v>
       </c>
       <c r="I14" t="n">
-        <v>67168.95</v>
+        <v>64228.01</v>
       </c>
       <c r="J14" t="n">
-        <v>67321.95</v>
+        <v>64506.16</v>
       </c>
       <c r="K14" t="n">
-        <v>68006.25</v>
+        <v>66030.17999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>68690.55</v>
+        <v>67554.19</v>
       </c>
       <c r="M14" t="n">
-        <v>69109.2</v>
+        <v>68455.28</v>
       </c>
       <c r="N14" t="n">
-        <v>69527.85000000001</v>
+        <v>69356.36</v>
       </c>
       <c r="O14" t="n">
-        <v>70477.81</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>71503.31</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1712,60 +1706,64 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67002.94</v>
+        <v>67989.74000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>67800.17999999999</v>
+        <v>68798.24000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>66268.60000000001</v>
+        <v>67833.17</v>
       </c>
       <c r="E15" t="n">
-        <v>67743.5</v>
+        <v>68751.50999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>500.77</v>
+        <v>1008.01</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0149</v>
       </c>
       <c r="H15" t="n">
-        <v>1531.58</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>64228.01</v>
+        <v>64737.02</v>
       </c>
       <c r="J15" t="n">
-        <v>64506.16</v>
+        <v>66566.48</v>
       </c>
       <c r="K15" t="n">
-        <v>66030.17999999999</v>
+        <v>66977.71000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>67554.19</v>
+        <v>67388.95</v>
       </c>
       <c r="M15" t="n">
-        <v>68455.28</v>
+        <v>68509.28999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>69356.36</v>
+        <v>69629.63</v>
       </c>
       <c r="O15" t="n">
-        <v>71503.31</v>
+        <v>69331.75999999999</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1776,13 +1774,15 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1790,83 +1790,87 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>67989.74000000001</v>
+        <v>67900.42999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>68798.24000000001</v>
+        <v>68069.82000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>67833.17</v>
+        <v>66499.49000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>68751.50999999999</v>
+        <v>66835.53999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1008.01</v>
+        <v>-1915.97</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0279</v>
       </c>
       <c r="H16" t="n">
-        <v>965.0700000000001</v>
+        <v>1570.33</v>
       </c>
       <c r="I16" t="n">
-        <v>64737.02</v>
+        <v>66868.10000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>66566.48</v>
+        <v>68004.34</v>
       </c>
       <c r="K16" t="n">
-        <v>66977.71000000001</v>
+        <v>68268.97</v>
       </c>
       <c r="L16" t="n">
-        <v>67388.95</v>
+        <v>68533.61</v>
       </c>
       <c r="M16" t="n">
-        <v>68509.28999999999</v>
+        <v>69234.03999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>69629.63</v>
+        <v>69934.48</v>
       </c>
       <c r="O16" t="n">
-        <v>69331.75999999999</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+        <v>69763.31</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1874,64 +1878,60 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>67900.42999999999</v>
+        <v>66339.85000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>68069.82000000001</v>
+        <v>66441.77</v>
       </c>
       <c r="D17" t="n">
-        <v>66499.49000000001</v>
+        <v>62704.6</v>
       </c>
       <c r="E17" t="n">
-        <v>66835.53999999999</v>
+        <v>64141.12</v>
       </c>
       <c r="F17" t="n">
-        <v>-1915.97</v>
+        <v>-2694.42</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0403</v>
       </c>
       <c r="H17" t="n">
-        <v>1570.33</v>
+        <v>3737.17</v>
       </c>
       <c r="I17" t="n">
-        <v>66868.10000000001</v>
+        <v>64929.16</v>
       </c>
       <c r="J17" t="n">
-        <v>68004.34</v>
+        <v>65040.65</v>
       </c>
       <c r="K17" t="n">
-        <v>68268.97</v>
+        <v>66050.38</v>
       </c>
       <c r="L17" t="n">
-        <v>68533.61</v>
+        <v>67060.10000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>69234.03999999999</v>
+        <v>67620.7</v>
       </c>
       <c r="N17" t="n">
-        <v>69934.48</v>
+        <v>68181.31</v>
       </c>
       <c r="O17" t="n">
-        <v>69763.31</v>
+        <v>69640.14999999999</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1962,7 +1962,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1972,134 +1972,134 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>66339.85000000001</v>
+        <v>64544.05</v>
       </c>
       <c r="C18" t="n">
-        <v>66441.77</v>
+        <v>66232.19</v>
       </c>
       <c r="D18" t="n">
-        <v>62704.6</v>
+        <v>64203.47</v>
       </c>
       <c r="E18" t="n">
-        <v>64141.12</v>
+        <v>66232.19</v>
       </c>
       <c r="F18" t="n">
-        <v>-2694.42</v>
+        <v>2091.07</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0326</v>
       </c>
       <c r="H18" t="n">
-        <v>3737.17</v>
+        <v>2028.72</v>
       </c>
       <c r="I18" t="n">
-        <v>64929.16</v>
+        <v>58967.43</v>
       </c>
       <c r="J18" t="n">
-        <v>65040.65</v>
+        <v>60187.92</v>
       </c>
       <c r="K18" t="n">
-        <v>66050.38</v>
+        <v>62272.54</v>
       </c>
       <c r="L18" t="n">
-        <v>67060.10000000001</v>
+        <v>64357.15</v>
       </c>
       <c r="M18" t="n">
-        <v>67620.7</v>
+        <v>66009.71000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>68181.31</v>
+        <v>67662.25999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>69640.14999999999</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>70178.95</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>64544.05</v>
+        <v>66449.27</v>
       </c>
       <c r="C19" t="n">
-        <v>66232.19</v>
+        <v>67592.2</v>
       </c>
       <c r="D19" t="n">
-        <v>64203.47</v>
+        <v>65955.60000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>66232.19</v>
+        <v>66115.60000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>2091.07</v>
+        <v>-116.59</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0326</v>
+        <v>-0.0018</v>
       </c>
       <c r="H19" t="n">
-        <v>2028.72</v>
+        <v>1636.6</v>
       </c>
       <c r="I19" t="n">
-        <v>58967.43</v>
+        <v>62174.75</v>
       </c>
       <c r="J19" t="n">
-        <v>60187.92</v>
+        <v>64710.65</v>
       </c>
       <c r="K19" t="n">
-        <v>62272.54</v>
+        <v>65217.83</v>
       </c>
       <c r="L19" t="n">
-        <v>64357.15</v>
+        <v>65725.00999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>66009.71000000001</v>
+        <v>67246.55</v>
       </c>
       <c r="N19" t="n">
-        <v>67662.25999999999</v>
+        <v>68768.09</v>
       </c>
       <c r="O19" t="n">
-        <v>70178.95</v>
+        <v>68260.91</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2110,14 +2110,14 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U19" s="8" t="n">
@@ -2126,7 +2126,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2140,50 +2140,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>66449.27</v>
+        <v>66421.00999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>67592.2</v>
+        <v>67022.37</v>
       </c>
       <c r="D20" t="n">
-        <v>65955.60000000001</v>
+        <v>66208.66</v>
       </c>
       <c r="E20" t="n">
-        <v>66115.60000000001</v>
+        <v>66422.60000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-116.59</v>
+        <v>307</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0046</v>
       </c>
       <c r="H20" t="n">
-        <v>1636.6</v>
+        <v>813.71</v>
       </c>
       <c r="I20" t="n">
-        <v>62174.75</v>
+        <v>64319</v>
       </c>
       <c r="J20" t="n">
-        <v>64710.65</v>
+        <v>64149.85</v>
       </c>
       <c r="K20" t="n">
-        <v>65217.83</v>
+        <v>65297.3</v>
       </c>
       <c r="L20" t="n">
-        <v>65725.00999999999</v>
+        <v>66444.75</v>
       </c>
       <c r="M20" t="n">
-        <v>67246.55</v>
+        <v>66933.89999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>68768.09</v>
+        <v>67423.05</v>
       </c>
       <c r="O20" t="n">
-        <v>68260.91</v>
+        <v>69228.8</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2210,7 +2210,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2224,69 +2224,73 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>66421.00999999999</v>
+        <v>65584.25</v>
       </c>
       <c r="C21" t="n">
-        <v>67022.37</v>
+        <v>65720.81</v>
       </c>
       <c r="D21" t="n">
-        <v>66208.66</v>
+        <v>64201.03</v>
       </c>
       <c r="E21" t="n">
-        <v>66422.60000000001</v>
+        <v>64611.15</v>
       </c>
       <c r="F21" t="n">
-        <v>307</v>
+        <v>-1811.45</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0273</v>
       </c>
       <c r="H21" t="n">
-        <v>813.71</v>
+        <v>1519.78</v>
       </c>
       <c r="I21" t="n">
-        <v>64319</v>
+        <v>65394.95</v>
       </c>
       <c r="J21" t="n">
-        <v>64149.85</v>
+        <v>65512.44</v>
       </c>
       <c r="K21" t="n">
-        <v>65297.3</v>
+        <v>66015.75</v>
       </c>
       <c r="L21" t="n">
-        <v>66444.75</v>
+        <v>66519.06</v>
       </c>
       <c r="M21" t="n">
-        <v>66933.89999999999</v>
+        <v>66829.46000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>67423.05</v>
+        <v>67139.86</v>
       </c>
       <c r="O21" t="n">
-        <v>69228.8</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67836.08</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2294,83 +2298,73 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>65584.25</v>
+        <v>65164.98</v>
       </c>
       <c r="C22" t="n">
-        <v>65720.81</v>
+        <v>65220.69</v>
       </c>
       <c r="D22" t="n">
-        <v>64201.03</v>
+        <v>64123.4</v>
       </c>
       <c r="E22" t="n">
-        <v>64611.15</v>
+        <v>64931.19</v>
       </c>
       <c r="F22" t="n">
-        <v>-1811.45</v>
+        <v>320.04</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.005</v>
       </c>
       <c r="H22" t="n">
-        <v>1519.78</v>
+        <v>1097.29</v>
       </c>
       <c r="I22" t="n">
-        <v>65394.95</v>
+        <v>62681.25</v>
       </c>
       <c r="J22" t="n">
-        <v>65512.44</v>
+        <v>62916.48</v>
       </c>
       <c r="K22" t="n">
-        <v>66015.75</v>
+        <v>63851.26</v>
       </c>
       <c r="L22" t="n">
-        <v>66519.06</v>
+        <v>64786.04</v>
       </c>
       <c r="M22" t="n">
-        <v>66829.46000000001</v>
+        <v>65371.04</v>
       </c>
       <c r="N22" t="n">
-        <v>67139.86</v>
+        <v>65956.03999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>67836.08</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67240.59</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2382,73 +2376,83 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>65164.98</v>
+        <v>64539.92</v>
       </c>
       <c r="C23" t="n">
-        <v>65220.69</v>
+        <v>64573.18</v>
       </c>
       <c r="D23" t="n">
-        <v>64123.4</v>
+        <v>61923.6</v>
       </c>
       <c r="E23" t="n">
-        <v>64931.19</v>
+        <v>62364.92</v>
       </c>
       <c r="F23" t="n">
-        <v>320.04</v>
+        <v>-2566.27</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0395</v>
       </c>
       <c r="H23" t="n">
-        <v>1097.29</v>
+        <v>2649.58</v>
       </c>
       <c r="I23" t="n">
-        <v>62681.25</v>
+        <v>63026.11</v>
       </c>
       <c r="J23" t="n">
-        <v>62916.48</v>
+        <v>63963.47</v>
       </c>
       <c r="K23" t="n">
-        <v>63851.26</v>
+        <v>64382.54</v>
       </c>
       <c r="L23" t="n">
-        <v>64786.04</v>
+        <v>64801.62</v>
       </c>
       <c r="M23" t="n">
-        <v>65371.04</v>
+        <v>65479.84</v>
       </c>
       <c r="N23" t="n">
-        <v>65956.03999999999</v>
+        <v>66158.06</v>
       </c>
       <c r="O23" t="n">
-        <v>67240.59</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+        <v>66317.98</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2460,81 +2464,73 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>64539.92</v>
+        <v>62734.68</v>
       </c>
       <c r="C24" t="n">
-        <v>64573.18</v>
+        <v>63138.04</v>
       </c>
       <c r="D24" t="n">
-        <v>61923.6</v>
+        <v>60448.9</v>
       </c>
       <c r="E24" t="n">
-        <v>62364.92</v>
+        <v>61434.19</v>
       </c>
       <c r="F24" t="n">
-        <v>-2566.27</v>
+        <v>-930.73</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0149</v>
       </c>
       <c r="H24" t="n">
-        <v>2649.58</v>
+        <v>2689.14</v>
       </c>
       <c r="I24" t="n">
-        <v>63026.11</v>
+        <v>59274.02</v>
       </c>
       <c r="J24" t="n">
-        <v>63963.47</v>
+        <v>59273.61</v>
       </c>
       <c r="K24" t="n">
-        <v>64382.54</v>
+        <v>61040.13</v>
       </c>
       <c r="L24" t="n">
-        <v>64801.62</v>
+        <v>62806.66</v>
       </c>
       <c r="M24" t="n">
-        <v>65479.84</v>
+        <v>63689.71</v>
       </c>
       <c r="N24" t="n">
-        <v>66158.06</v>
+        <v>64572.77</v>
       </c>
       <c r="O24" t="n">
-        <v>66317.98</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>67222.75999999999</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2548,7 +2544,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2558,50 +2554,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>62734.68</v>
+        <v>61258.34</v>
       </c>
       <c r="C25" t="n">
-        <v>63138.04</v>
+        <v>62924.84</v>
       </c>
       <c r="D25" t="n">
-        <v>60448.9</v>
+        <v>61049.7</v>
       </c>
       <c r="E25" t="n">
-        <v>61434.19</v>
+        <v>61867.43</v>
       </c>
       <c r="F25" t="n">
-        <v>-930.73</v>
+        <v>433.24</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0071</v>
       </c>
       <c r="H25" t="n">
-        <v>2689.14</v>
+        <v>1875.14</v>
       </c>
       <c r="I25" t="n">
-        <v>59274.02</v>
+        <v>57759.76</v>
       </c>
       <c r="J25" t="n">
-        <v>59273.61</v>
+        <v>58565.41</v>
       </c>
       <c r="K25" t="n">
-        <v>61040.13</v>
+        <v>60089.62</v>
       </c>
       <c r="L25" t="n">
-        <v>62806.66</v>
+        <v>61613.83</v>
       </c>
       <c r="M25" t="n">
-        <v>63689.71</v>
+        <v>62778.76</v>
       </c>
       <c r="N25" t="n">
-        <v>64572.77</v>
+        <v>63943.69</v>
       </c>
       <c r="O25" t="n">
-        <v>67222.75999999999</v>
+        <v>65827.17999999999</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2609,18 +2605,18 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2628,60 +2624,64 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>61258.34</v>
+        <v>61957.1</v>
       </c>
       <c r="C26" t="n">
-        <v>62924.84</v>
+        <v>65364.73</v>
       </c>
       <c r="D26" t="n">
-        <v>61049.7</v>
+        <v>61948.23</v>
       </c>
       <c r="E26" t="n">
-        <v>61867.43</v>
+        <v>64362.02</v>
       </c>
       <c r="F26" t="n">
-        <v>433.24</v>
+        <v>2494.59</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0403</v>
       </c>
       <c r="H26" t="n">
-        <v>1875.14</v>
+        <v>3416.5</v>
       </c>
       <c r="I26" t="n">
-        <v>57759.76</v>
+        <v>59174.56</v>
       </c>
       <c r="J26" t="n">
-        <v>58565.41</v>
+        <v>59932.37</v>
       </c>
       <c r="K26" t="n">
-        <v>60089.62</v>
+        <v>60929.86</v>
       </c>
       <c r="L26" t="n">
-        <v>61613.83</v>
+        <v>61927.35</v>
       </c>
       <c r="M26" t="n">
-        <v>62778.76</v>
+        <v>62805</v>
       </c>
       <c r="N26" t="n">
-        <v>63943.69</v>
+        <v>63682.65</v>
       </c>
       <c r="O26" t="n">
-        <v>65827.17999999999</v>
+        <v>64799.98</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2692,9 +2692,9 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2702,70 +2702,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W26" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>61957.1</v>
+        <v>63834.95</v>
       </c>
       <c r="C27" t="n">
-        <v>65364.73</v>
+        <v>63905.12</v>
       </c>
       <c r="D27" t="n">
-        <v>61948.23</v>
+        <v>62703.47</v>
       </c>
       <c r="E27" t="n">
-        <v>64362.02</v>
+        <v>63754.9</v>
       </c>
       <c r="F27" t="n">
-        <v>2494.59</v>
+        <v>-607.12</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0403</v>
+        <v>-0.0094</v>
       </c>
       <c r="H27" t="n">
-        <v>3416.5</v>
+        <v>1201.65</v>
       </c>
       <c r="I27" t="n">
-        <v>59174.56</v>
+        <v>58531.73</v>
       </c>
       <c r="J27" t="n">
-        <v>59932.37</v>
+        <v>61298.29</v>
       </c>
       <c r="K27" t="n">
-        <v>60929.86</v>
+        <v>62653.77</v>
       </c>
       <c r="L27" t="n">
-        <v>61927.35</v>
+        <v>64009.25</v>
       </c>
       <c r="M27" t="n">
-        <v>62805</v>
+        <v>66070.27</v>
       </c>
       <c r="N27" t="n">
-        <v>63682.65</v>
+        <v>68131.28999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>64799.98</v>
+        <v>68781.23</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2778,78 +2778,76 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W27" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>63834.95</v>
+        <v>63995.28</v>
       </c>
       <c r="C28" t="n">
-        <v>63905.12</v>
+        <v>64240.5</v>
       </c>
       <c r="D28" t="n">
-        <v>62703.47</v>
+        <v>62864.43</v>
       </c>
       <c r="E28" t="n">
-        <v>63754.9</v>
+        <v>63957.53</v>
       </c>
       <c r="F28" t="n">
-        <v>-607.12</v>
+        <v>202.63</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0032</v>
       </c>
       <c r="H28" t="n">
-        <v>1201.65</v>
+        <v>1376.07</v>
       </c>
       <c r="I28" t="n">
-        <v>58531.73</v>
+        <v>61501.82</v>
       </c>
       <c r="J28" t="n">
-        <v>61298.29</v>
+        <v>62778.55</v>
       </c>
       <c r="K28" t="n">
-        <v>62653.77</v>
+        <v>63154.07</v>
       </c>
       <c r="L28" t="n">
-        <v>64009.25</v>
+        <v>63529.6</v>
       </c>
       <c r="M28" t="n">
-        <v>66070.27</v>
+        <v>64355.72</v>
       </c>
       <c r="N28" t="n">
-        <v>68131.28999999999</v>
+        <v>65181.85</v>
       </c>
       <c r="O28" t="n">
-        <v>68781.23</v>
+        <v>65106.77</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2857,16 +2855,20 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2874,64 +2876,60 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>63995.28</v>
+        <v>64565.27</v>
       </c>
       <c r="C29" t="n">
-        <v>64240.5</v>
+        <v>66302.52</v>
       </c>
       <c r="D29" t="n">
-        <v>62864.43</v>
+        <v>64555.52</v>
       </c>
       <c r="E29" t="n">
-        <v>63957.53</v>
+        <v>66300.44</v>
       </c>
       <c r="F29" t="n">
-        <v>202.63</v>
+        <v>2342.91</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0366</v>
       </c>
       <c r="H29" t="n">
-        <v>1376.07</v>
+        <v>1747</v>
       </c>
       <c r="I29" t="n">
-        <v>61501.82</v>
+        <v>61488.36</v>
       </c>
       <c r="J29" t="n">
-        <v>62778.55</v>
+        <v>62783.99</v>
       </c>
       <c r="K29" t="n">
-        <v>63154.07</v>
+        <v>63269.5</v>
       </c>
       <c r="L29" t="n">
-        <v>63529.6</v>
+        <v>63755</v>
       </c>
       <c r="M29" t="n">
-        <v>64355.72</v>
+        <v>64645.57</v>
       </c>
       <c r="N29" t="n">
-        <v>65181.85</v>
+        <v>65536.13</v>
       </c>
       <c r="O29" t="n">
-        <v>65106.77</v>
+        <v>65616.57000000001</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2939,28 +2937,30 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2970,134 +2970,136 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>64565.27</v>
+        <v>65896</v>
       </c>
       <c r="C30" t="n">
-        <v>66302.52</v>
+        <v>65983.13</v>
       </c>
       <c r="D30" t="n">
-        <v>64555.52</v>
+        <v>64942.07</v>
       </c>
       <c r="E30" t="n">
-        <v>66300.44</v>
+        <v>65683.25999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>2342.91</v>
+        <v>-617.1799999999999</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0366</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>1747</v>
+        <v>1041.06</v>
       </c>
       <c r="I30" t="n">
-        <v>61488.36</v>
+        <v>62808.52</v>
       </c>
       <c r="J30" t="n">
-        <v>62783.99</v>
+        <v>64989.14</v>
       </c>
       <c r="K30" t="n">
-        <v>63269.5</v>
+        <v>65426.94</v>
       </c>
       <c r="L30" t="n">
-        <v>63755</v>
+        <v>65864.73</v>
       </c>
       <c r="M30" t="n">
-        <v>64645.57</v>
+        <v>67173.94</v>
       </c>
       <c r="N30" t="n">
-        <v>65536.13</v>
+        <v>68483.14999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>65616.57000000001</v>
+        <v>68049.53</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W30" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>65896</v>
+        <v>65746.13</v>
       </c>
       <c r="C31" t="n">
-        <v>65983.13</v>
+        <v>65990.72</v>
       </c>
       <c r="D31" t="n">
-        <v>64942.07</v>
+        <v>64651.49</v>
       </c>
       <c r="E31" t="n">
-        <v>65683.25999999999</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>-617.1799999999999</v>
+        <v>-76.55</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="H31" t="n">
-        <v>1041.06</v>
+        <v>1339.23</v>
       </c>
       <c r="I31" t="n">
-        <v>62808.52</v>
+        <v>63901.01</v>
       </c>
       <c r="J31" t="n">
-        <v>64989.14</v>
+        <v>64752.52</v>
       </c>
       <c r="K31" t="n">
-        <v>65426.94</v>
+        <v>65162.73</v>
       </c>
       <c r="L31" t="n">
-        <v>65864.73</v>
+        <v>65572.92999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>67173.94</v>
+        <v>66203.78999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>68483.14999999999</v>
+        <v>66834.64999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>68049.53</v>
+        <v>67024.2</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3114,7 +3116,7 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3126,7 +3128,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3140,136 +3142,132 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>65746.13</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>65990.72</v>
+        <v>67006.84</v>
       </c>
       <c r="D32" t="n">
-        <v>64651.49</v>
+        <v>65848.58</v>
       </c>
       <c r="E32" t="n">
-        <v>65606.71000000001</v>
+        <v>66970.22</v>
       </c>
       <c r="F32" t="n">
-        <v>-76.55</v>
+        <v>1363.51</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0208</v>
       </c>
       <c r="H32" t="n">
-        <v>1339.23</v>
+        <v>1158.27</v>
       </c>
       <c r="I32" t="n">
-        <v>63901.01</v>
+        <v>63312.26</v>
       </c>
       <c r="J32" t="n">
-        <v>64752.52</v>
+        <v>64410.28</v>
       </c>
       <c r="K32" t="n">
-        <v>65162.73</v>
+        <v>64937.1</v>
       </c>
       <c r="L32" t="n">
-        <v>65572.92999999999</v>
+        <v>65463.91</v>
       </c>
       <c r="M32" t="n">
-        <v>66203.78999999999</v>
+        <v>66276.33</v>
       </c>
       <c r="N32" t="n">
-        <v>66834.64999999999</v>
+        <v>67088.75</v>
       </c>
       <c r="O32" t="n">
-        <v>67024.2</v>
+        <v>67329.95</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65905.10000000001</v>
+        <v>66994.05</v>
       </c>
       <c r="C33" t="n">
-        <v>67006.84</v>
+        <v>67569.36</v>
       </c>
       <c r="D33" t="n">
-        <v>65848.58</v>
+        <v>66735.75999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>66970.22</v>
+        <v>67524.06</v>
       </c>
       <c r="F33" t="n">
-        <v>1363.51</v>
+        <v>553.84</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="H33" t="n">
-        <v>1158.27</v>
+        <v>833.6</v>
       </c>
       <c r="I33" t="n">
-        <v>63312.26</v>
+        <v>64690.31</v>
       </c>
       <c r="J33" t="n">
-        <v>64410.28</v>
+        <v>66083.21000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>64937.1</v>
+        <v>66391.09</v>
       </c>
       <c r="L33" t="n">
-        <v>65463.91</v>
+        <v>66698.96000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>66276.33</v>
+        <v>67549.35000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>67088.75</v>
+        <v>68399.74000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>67329.95</v>
+        <v>68165.11</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3280,25 +3278,23 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3308,50 +3304,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>66994.05</v>
+        <v>68033.17</v>
       </c>
       <c r="C34" t="n">
-        <v>67569.36</v>
+        <v>68799.71000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>66735.75999999999</v>
+        <v>68006.17</v>
       </c>
       <c r="E34" t="n">
-        <v>67524.06</v>
+        <v>68308.59</v>
       </c>
       <c r="F34" t="n">
-        <v>553.84</v>
+        <v>784.53</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0116</v>
       </c>
       <c r="H34" t="n">
-        <v>833.6</v>
+        <v>793.54</v>
       </c>
       <c r="I34" t="n">
-        <v>64690.31</v>
+        <v>65902.16</v>
       </c>
       <c r="J34" t="n">
-        <v>66083.21000000001</v>
+        <v>66876.21000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>66391.09</v>
+        <v>67107.25999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>66698.96000000001</v>
+        <v>67338.31</v>
       </c>
       <c r="M34" t="n">
-        <v>67549.35000000001</v>
+        <v>67940.86</v>
       </c>
       <c r="N34" t="n">
-        <v>68399.74000000001</v>
+        <v>68543.42</v>
       </c>
       <c r="O34" t="n">
-        <v>68165.11</v>
+        <v>68402.96000000001</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3362,23 +3358,27 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3388,50 +3388,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>68033.17</v>
+        <v>68811.17</v>
       </c>
       <c r="C35" t="n">
-        <v>68799.71000000001</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>68006.17</v>
+        <v>68471.14999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>68308.59</v>
+        <v>68713.8</v>
       </c>
       <c r="F35" t="n">
-        <v>784.53</v>
+        <v>405.2</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0059</v>
       </c>
       <c r="H35" t="n">
-        <v>793.54</v>
+        <v>1137.09</v>
       </c>
       <c r="I35" t="n">
-        <v>65902.16</v>
+        <v>67212.63</v>
       </c>
       <c r="J35" t="n">
-        <v>66876.21000000001</v>
+        <v>67467.88</v>
       </c>
       <c r="K35" t="n">
-        <v>67107.25999999999</v>
+        <v>67911.82000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>67338.31</v>
+        <v>68355.77</v>
       </c>
       <c r="M35" t="n">
-        <v>67940.86</v>
+        <v>68705.36</v>
       </c>
       <c r="N35" t="n">
-        <v>68543.42</v>
+        <v>69054.96000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>68402.96000000001</v>
+        <v>69593.25</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3442,14 +3442,14 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U35" s="8" t="inlineStr">
@@ -3459,10 +3459,10 @@
       </c>
       <c r="V35" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W35" s="9" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3472,50 +3472,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>68811.17</v>
+        <v>68882.06</v>
       </c>
       <c r="C36" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>68471.14999999999</v>
+        <v>68492.03999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>68713.8</v>
+        <v>69220.25</v>
       </c>
       <c r="F36" t="n">
-        <v>405.2</v>
+        <v>506.45</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="H36" t="n">
-        <v>1137.09</v>
+        <v>733.53</v>
       </c>
       <c r="I36" t="n">
-        <v>67212.63</v>
+        <v>67334.05</v>
       </c>
       <c r="J36" t="n">
-        <v>67467.88</v>
+        <v>67413.75</v>
       </c>
       <c r="K36" t="n">
-        <v>67911.82000000001</v>
+        <v>68145.25</v>
       </c>
       <c r="L36" t="n">
-        <v>68355.77</v>
+        <v>68876.75</v>
       </c>
       <c r="M36" t="n">
-        <v>68705.36</v>
+        <v>69282.34</v>
       </c>
       <c r="N36" t="n">
-        <v>69054.96000000001</v>
+        <v>69687.94</v>
       </c>
       <c r="O36" t="n">
-        <v>69593.25</v>
+        <v>70745.34</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3526,7 +3526,7 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3536,89 +3536,93 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>68882.06</v>
+        <v>68847.35000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>69225.57000000001</v>
+        <v>69093.2</v>
       </c>
       <c r="D37" t="n">
-        <v>68492.03999999999</v>
+        <v>67368.96000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>69220.25</v>
+        <v>67460.73</v>
       </c>
       <c r="F37" t="n">
-        <v>506.45</v>
+        <v>-1759.52</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0254</v>
       </c>
       <c r="H37" t="n">
-        <v>733.53</v>
+        <v>1724.24</v>
       </c>
       <c r="I37" t="n">
-        <v>67334.05</v>
+        <v>67758.50999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>67413.75</v>
+        <v>68667.44</v>
       </c>
       <c r="K37" t="n">
-        <v>68145.25</v>
+        <v>68853.48</v>
       </c>
       <c r="L37" t="n">
-        <v>68876.75</v>
+        <v>69039.53</v>
       </c>
       <c r="M37" t="n">
-        <v>69282.34</v>
+        <v>69587.02</v>
       </c>
       <c r="N37" t="n">
-        <v>69687.94</v>
+        <v>70134.5</v>
       </c>
       <c r="O37" t="n">
-        <v>70745.34</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+        <v>69959.10000000001</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3628,79 +3632,75 @@
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>68847.35000000001</v>
+        <v>66812.27</v>
       </c>
       <c r="C38" t="n">
-        <v>69093.2</v>
+        <v>66833.50999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>67368.96000000001</v>
+        <v>65133.98</v>
       </c>
       <c r="E38" t="n">
-        <v>67460.73</v>
+        <v>65326.42</v>
       </c>
       <c r="F38" t="n">
-        <v>-1759.52</v>
+        <v>-2134.3</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="H38" t="n">
-        <v>1724.24</v>
+        <v>1699.53</v>
       </c>
       <c r="I38" t="n">
-        <v>67758.50999999999</v>
+        <v>65644.72</v>
       </c>
       <c r="J38" t="n">
-        <v>68667.44</v>
+        <v>65351.31</v>
       </c>
       <c r="K38" t="n">
-        <v>68853.48</v>
+        <v>66598.61</v>
       </c>
       <c r="L38" t="n">
-        <v>69039.53</v>
+        <v>67845.89999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>69587.02</v>
+        <v>68322.85000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>70134.5</v>
+        <v>68799.78999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>69959.10000000001</v>
+        <v>70817.45</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3714,7 +3714,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3724,153 +3724,155 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>66812.27</v>
+        <v>65732.78999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>66833.50999999999</v>
+        <v>66325.32000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>65133.98</v>
+        <v>65652.25</v>
       </c>
       <c r="E39" t="n">
-        <v>65326.42</v>
+        <v>66216.78999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>-2134.3</v>
+        <v>890.37</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H39" t="n">
-        <v>1699.53</v>
+        <v>673.0700000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>65644.72</v>
+        <v>63434.45</v>
       </c>
       <c r="J39" t="n">
-        <v>65351.31</v>
+        <v>63298.23</v>
       </c>
       <c r="K39" t="n">
-        <v>66598.61</v>
+        <v>64476.66</v>
       </c>
       <c r="L39" t="n">
-        <v>67845.89999999999</v>
+        <v>65655.08</v>
       </c>
       <c r="M39" t="n">
-        <v>68322.85000000001</v>
+        <v>66176.19</v>
       </c>
       <c r="N39" t="n">
-        <v>68799.78999999999</v>
+        <v>66697.28999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>70817.45</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
+        <v>68533.03999999999</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>65732.78999999999</v>
+        <v>65427.69</v>
       </c>
       <c r="C40" t="n">
-        <v>66325.32000000001</v>
+        <v>66125.88</v>
       </c>
       <c r="D40" t="n">
-        <v>65652.25</v>
+        <v>65260.22</v>
       </c>
       <c r="E40" t="n">
-        <v>66216.78999999999</v>
+        <v>66016.36</v>
       </c>
       <c r="F40" t="n">
-        <v>890.37</v>
+        <v>-200.43</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.003</v>
       </c>
       <c r="H40" t="n">
-        <v>673.0700000000001</v>
+        <v>865.66</v>
       </c>
       <c r="I40" t="n">
-        <v>63434.45</v>
+        <v>64979.18</v>
       </c>
       <c r="J40" t="n">
-        <v>63298.23</v>
+        <v>65657.72</v>
       </c>
       <c r="K40" t="n">
-        <v>64476.66</v>
+        <v>65880.25</v>
       </c>
       <c r="L40" t="n">
-        <v>65655.08</v>
+        <v>66102.78999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>66176.19</v>
+        <v>66553.32000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>66697.28999999999</v>
+        <v>67003.86</v>
       </c>
       <c r="O40" t="n">
-        <v>68533.03999999999</v>
+        <v>66998.39</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3878,81 +3880,75 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>65427.69</v>
+        <v>65978.95</v>
       </c>
       <c r="C41" t="n">
-        <v>66125.88</v>
+        <v>66257.73</v>
       </c>
       <c r="D41" t="n">
-        <v>65260.22</v>
+        <v>65470.95</v>
       </c>
       <c r="E41" t="n">
-        <v>66016.36</v>
+        <v>65528.09</v>
       </c>
       <c r="F41" t="n">
-        <v>-200.43</v>
+        <v>-488.27</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0074</v>
       </c>
       <c r="H41" t="n">
-        <v>865.66</v>
+        <v>786.78</v>
       </c>
       <c r="I41" t="n">
-        <v>64979.18</v>
+        <v>64394.55</v>
       </c>
       <c r="J41" t="n">
-        <v>65657.72</v>
+        <v>65312.35</v>
       </c>
       <c r="K41" t="n">
-        <v>65880.25</v>
+        <v>65583.53</v>
       </c>
       <c r="L41" t="n">
-        <v>66102.78999999999</v>
+        <v>65854.71000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>66553.32000000001</v>
+        <v>66449.19</v>
       </c>
       <c r="N41" t="n">
-        <v>67003.86</v>
+        <v>67043.67999999999</v>
       </c>
       <c r="O41" t="n">
-        <v>66998.39</v>
+        <v>66991.55</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q41" s="6" t="n">
+        <v/>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3964,159 +3960,163 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>65978.95</v>
+        <v>65195.26</v>
       </c>
       <c r="C42" t="n">
-        <v>66257.73</v>
+        <v>65904.24000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>65470.95</v>
+        <v>64609.47</v>
       </c>
       <c r="E42" t="n">
-        <v>65528.09</v>
+        <v>65856.42999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>-488.27</v>
+        <v>328.34</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.005</v>
       </c>
       <c r="H42" t="n">
-        <v>786.78</v>
+        <v>1294.77</v>
       </c>
       <c r="I42" t="n">
-        <v>64394.55</v>
+        <v>64684.17</v>
       </c>
       <c r="J42" t="n">
-        <v>65312.35</v>
+        <v>64573.19</v>
       </c>
       <c r="K42" t="n">
-        <v>65583.53</v>
+        <v>65134.7</v>
       </c>
       <c r="L42" t="n">
-        <v>65854.71000000001</v>
+        <v>65696.21000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>66449.19</v>
+        <v>65921.48</v>
       </c>
       <c r="N42" t="n">
-        <v>67043.67999999999</v>
+        <v>66146.74000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>66991.55</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
+        <v>67044.5</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>65195.26</v>
+        <v>65604.49000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>65904.24000000001</v>
+        <v>66442.34</v>
       </c>
       <c r="D43" t="n">
-        <v>64609.47</v>
+        <v>65390.55</v>
       </c>
       <c r="E43" t="n">
-        <v>65856.42999999999</v>
+        <v>66262.16</v>
       </c>
       <c r="F43" t="n">
-        <v>328.34</v>
+        <v>405.73</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0062</v>
       </c>
       <c r="H43" t="n">
-        <v>1294.77</v>
+        <v>1051.79</v>
       </c>
       <c r="I43" t="n">
-        <v>64684.17</v>
+        <v>63314.7</v>
       </c>
       <c r="J43" t="n">
-        <v>64573.19</v>
+        <v>64861.44</v>
       </c>
       <c r="K43" t="n">
-        <v>65134.7</v>
+        <v>65209.04</v>
       </c>
       <c r="L43" t="n">
-        <v>65696.21000000001</v>
+        <v>65556.64</v>
       </c>
       <c r="M43" t="n">
-        <v>65921.48</v>
+        <v>66503.82000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>66146.74000000001</v>
+        <v>67450.99000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>67044.5</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67199.02</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
       </c>
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4132,64 +4132,64 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>65604.49000000001</v>
+        <v>66775.78</v>
       </c>
       <c r="C44" t="n">
-        <v>66442.34</v>
+        <v>66954.69</v>
       </c>
       <c r="D44" t="n">
-        <v>65390.55</v>
+        <v>65782.59</v>
       </c>
       <c r="E44" t="n">
-        <v>66262.16</v>
+        <v>66131.98</v>
       </c>
       <c r="F44" t="n">
-        <v>405.73</v>
+        <v>-130.18</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.002</v>
       </c>
       <c r="H44" t="n">
-        <v>1051.79</v>
+        <v>1172.09</v>
       </c>
       <c r="I44" t="n">
-        <v>63314.7</v>
+        <v>64338.76</v>
       </c>
       <c r="J44" t="n">
-        <v>64861.44</v>
+        <v>65383.22</v>
       </c>
       <c r="K44" t="n">
-        <v>65209.04</v>
+        <v>65736.25999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>65556.64</v>
+        <v>66089.3</v>
       </c>
       <c r="M44" t="n">
-        <v>66503.82000000001</v>
+        <v>66788.05</v>
       </c>
       <c r="N44" t="n">
-        <v>67450.99000000001</v>
+        <v>67486.8</v>
       </c>
       <c r="O44" t="n">
-        <v>67199.02</v>
+        <v>67494.14</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4200,14 +4200,14 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U44" s="8" t="n">
@@ -4216,64 +4216,64 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>66775.78</v>
+        <v>66104.49000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>66954.69</v>
+        <v>66842.82000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>65782.59</v>
+        <v>66012.2</v>
       </c>
       <c r="E45" t="n">
-        <v>66131.98</v>
+        <v>66405.56</v>
       </c>
       <c r="F45" t="n">
-        <v>-130.18</v>
+        <v>273.59</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0041</v>
       </c>
       <c r="H45" t="n">
-        <v>1172.09</v>
+        <v>830.62</v>
       </c>
       <c r="I45" t="n">
-        <v>64338.76</v>
+        <v>64610.5</v>
       </c>
       <c r="J45" t="n">
-        <v>65383.22</v>
+        <v>64841.55</v>
       </c>
       <c r="K45" t="n">
-        <v>65736.25999999999</v>
+        <v>65545.92999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>66089.3</v>
+        <v>66250.31</v>
       </c>
       <c r="M45" t="n">
-        <v>66788.05</v>
+        <v>66718.02</v>
       </c>
       <c r="N45" t="n">
-        <v>67486.8</v>
+        <v>67185.74000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>67494.14</v>
+        <v>68126.78</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4284,7 +4284,7 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4300,7 +4300,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4314,69 +4314,73 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>66104.49000000001</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C46" t="n">
-        <v>66842.82000000001</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>66012.2</v>
+        <v>64832.1</v>
       </c>
       <c r="E46" t="n">
-        <v>66405.56</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>273.59</v>
+        <v>-93.63</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0014</v>
       </c>
       <c r="H46" t="n">
-        <v>830.62</v>
+        <v>1479.83</v>
       </c>
       <c r="I46" t="n">
-        <v>64610.5</v>
+        <v>65181.59</v>
       </c>
       <c r="J46" t="n">
-        <v>64841.55</v>
+        <v>65563.97</v>
       </c>
       <c r="K46" t="n">
-        <v>65545.92999999999</v>
+        <v>65990.25</v>
       </c>
       <c r="L46" t="n">
-        <v>66250.31</v>
+        <v>66416.53999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>66718.02</v>
+        <v>66820.87</v>
       </c>
       <c r="N46" t="n">
-        <v>67185.74000000001</v>
+        <v>67225.21000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>68126.78</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+        <v>67673.44</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4384,83 +4388,73 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65668.50999999999</v>
+        <v>65885.47</v>
       </c>
       <c r="C47" t="n">
-        <v>66311.92999999999</v>
+        <v>66525.7</v>
       </c>
       <c r="D47" t="n">
-        <v>64832.1</v>
+        <v>65576.61</v>
       </c>
       <c r="E47" t="n">
-        <v>66311.92999999999</v>
+        <v>66215.34</v>
       </c>
       <c r="F47" t="n">
-        <v>-93.63</v>
+        <v>-96.59</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0015</v>
       </c>
       <c r="H47" t="n">
-        <v>1479.83</v>
+        <v>949.09</v>
       </c>
       <c r="I47" t="n">
-        <v>65181.59</v>
+        <v>63352.27</v>
       </c>
       <c r="J47" t="n">
-        <v>65563.97</v>
+        <v>65202.06</v>
       </c>
       <c r="K47" t="n">
-        <v>65990.25</v>
+        <v>65572.02</v>
       </c>
       <c r="L47" t="n">
-        <v>66416.53999999999</v>
+        <v>65941.97</v>
       </c>
       <c r="M47" t="n">
-        <v>66820.87</v>
+        <v>67051.84</v>
       </c>
       <c r="N47" t="n">
-        <v>67225.21000000001</v>
+        <v>68161.71000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>67673.44</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67791.75999999999</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4472,73 +4466,83 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65885.47</v>
+        <v>65195.43</v>
       </c>
       <c r="C48" t="n">
-        <v>66525.7</v>
+        <v>65195.43</v>
       </c>
       <c r="D48" t="n">
-        <v>65576.61</v>
+        <v>64215.47</v>
       </c>
       <c r="E48" t="n">
-        <v>66215.34</v>
+        <v>64325.64</v>
       </c>
       <c r="F48" t="n">
-        <v>-96.59</v>
+        <v>-1889.7</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0285</v>
       </c>
       <c r="H48" t="n">
-        <v>949.09</v>
+        <v>979.96</v>
       </c>
       <c r="I48" t="n">
-        <v>63352.27</v>
+        <v>64627.52</v>
       </c>
       <c r="J48" t="n">
-        <v>65202.06</v>
+        <v>65348.34</v>
       </c>
       <c r="K48" t="n">
-        <v>65572.02</v>
+        <v>65740.8</v>
       </c>
       <c r="L48" t="n">
-        <v>65941.97</v>
+        <v>66133.25</v>
       </c>
       <c r="M48" t="n">
-        <v>67051.84</v>
+        <v>66689.89</v>
       </c>
       <c r="N48" t="n">
-        <v>68161.71000000001</v>
+        <v>67246.53</v>
       </c>
       <c r="O48" t="n">
-        <v>67791.75999999999</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+        <v>67474.8</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4550,83 +4554,75 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="C49" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="D49" t="n">
-        <v>64215.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E49" t="n">
-        <v>64325.64</v>
+        <v>64214.48</v>
       </c>
       <c r="F49" t="n">
-        <v>-1889.7</v>
+        <v>-111.16</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0017</v>
       </c>
       <c r="H49" t="n">
-        <v>979.96</v>
+        <v>952.01</v>
       </c>
       <c r="I49" t="n">
-        <v>64627.52</v>
+        <v>63235.51</v>
       </c>
       <c r="J49" t="n">
-        <v>65348.34</v>
+        <v>63155.78</v>
       </c>
       <c r="K49" t="n">
-        <v>65740.8</v>
+        <v>63835.66</v>
       </c>
       <c r="L49" t="n">
-        <v>66133.25</v>
+        <v>64515.54</v>
       </c>
       <c r="M49" t="n">
-        <v>66689.89</v>
+        <v>64815.62</v>
       </c>
       <c r="N49" t="n">
-        <v>67246.53</v>
+        <v>65115.7</v>
       </c>
       <c r="O49" t="n">
-        <v>67474.8</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66175.39</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4638,7 +4634,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4648,50 +4644,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>64724.81</v>
+        <v>64498.94</v>
       </c>
       <c r="C50" t="n">
-        <v>64724.81</v>
+        <v>65182.45</v>
       </c>
       <c r="D50" t="n">
-        <v>63772.8</v>
+        <v>64228.47</v>
       </c>
       <c r="E50" t="n">
-        <v>64214.48</v>
+        <v>65020.94</v>
       </c>
       <c r="F50" t="n">
-        <v>-111.16</v>
+        <v>806.46</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="H50" t="n">
-        <v>952.01</v>
+        <v>953.98</v>
       </c>
       <c r="I50" t="n">
-        <v>63235.51</v>
+        <v>62820.79</v>
       </c>
       <c r="J50" t="n">
-        <v>63155.78</v>
+        <v>63245.31</v>
       </c>
       <c r="K50" t="n">
-        <v>63835.66</v>
+        <v>63738.48</v>
       </c>
       <c r="L50" t="n">
-        <v>64515.54</v>
+        <v>64231.64</v>
       </c>
       <c r="M50" t="n">
-        <v>64815.62</v>
+        <v>64690.48</v>
       </c>
       <c r="N50" t="n">
-        <v>65115.7</v>
+        <v>65149.33</v>
       </c>
       <c r="O50" t="n">
-        <v>66175.39</v>
+        <v>65676.82000000001</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4699,79 +4695,85 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>64498.94</v>
+        <v>65600.42</v>
       </c>
       <c r="C51" t="n">
-        <v>65182.45</v>
+        <v>66668.71000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>64228.47</v>
+        <v>65600.42</v>
       </c>
       <c r="E51" t="n">
-        <v>65020.94</v>
+        <v>66399.84</v>
       </c>
       <c r="F51" t="n">
-        <v>806.46</v>
+        <v>1378.9</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="H51" t="n">
-        <v>953.98</v>
+        <v>1068.29</v>
       </c>
       <c r="I51" t="n">
-        <v>62820.79</v>
+        <v>63274.49</v>
       </c>
       <c r="J51" t="n">
-        <v>63245.31</v>
+        <v>64224.7</v>
       </c>
       <c r="K51" t="n">
-        <v>63738.48</v>
+        <v>64543.95</v>
       </c>
       <c r="L51" t="n">
-        <v>64231.64</v>
+        <v>64863.2</v>
       </c>
       <c r="M51" t="n">
-        <v>64690.48</v>
+        <v>65497.93</v>
       </c>
       <c r="N51" t="n">
-        <v>65149.33</v>
+        <v>66132.66</v>
       </c>
       <c r="O51" t="n">
-        <v>65676.82000000001</v>
+        <v>66136.42999999999</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4782,7 +4784,7 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4794,171 +4796,167 @@
       </c>
       <c r="U51" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>65600.42</v>
+        <v>65843.69</v>
       </c>
       <c r="C52" t="n">
-        <v>66668.71000000001</v>
+        <v>66791.84</v>
       </c>
       <c r="D52" t="n">
-        <v>65600.42</v>
+        <v>65269.33</v>
       </c>
       <c r="E52" t="n">
-        <v>66399.84</v>
+        <v>65269.33</v>
       </c>
       <c r="F52" t="n">
-        <v>1378.9</v>
+        <v>-1130.52</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.017</v>
       </c>
       <c r="H52" t="n">
-        <v>1068.29</v>
+        <v>1522.52</v>
       </c>
       <c r="I52" t="n">
-        <v>63274.49</v>
+        <v>64532.13</v>
       </c>
       <c r="J52" t="n">
-        <v>64224.7</v>
+        <v>65464.19</v>
       </c>
       <c r="K52" t="n">
-        <v>64543.95</v>
+        <v>65865.7</v>
       </c>
       <c r="L52" t="n">
-        <v>64863.2</v>
+        <v>66267.21000000001</v>
       </c>
       <c r="M52" t="n">
-        <v>65497.93</v>
+        <v>66933.99000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>66132.66</v>
+        <v>67600.77</v>
       </c>
       <c r="O52" t="n">
-        <v>66136.42999999999</v>
+        <v>67737</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65843.69</v>
+        <v>65087.22</v>
       </c>
       <c r="C53" t="n">
-        <v>66791.84</v>
+        <v>65794.03</v>
       </c>
       <c r="D53" t="n">
-        <v>65269.33</v>
+        <v>65017.68</v>
       </c>
       <c r="E53" t="n">
-        <v>65269.33</v>
+        <v>65142.78</v>
       </c>
       <c r="F53" t="n">
-        <v>-1130.52</v>
+        <v>-126.55</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0019</v>
       </c>
       <c r="H53" t="n">
-        <v>1522.52</v>
+        <v>776.35</v>
       </c>
       <c r="I53" t="n">
-        <v>64532.13</v>
+        <v>63746.81</v>
       </c>
       <c r="J53" t="n">
-        <v>65464.19</v>
+        <v>63366.18</v>
       </c>
       <c r="K53" t="n">
-        <v>65865.7</v>
+        <v>64508.07</v>
       </c>
       <c r="L53" t="n">
-        <v>66267.21000000001</v>
+        <v>65649.96000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>66933.99000000001</v>
+        <v>66030.59</v>
       </c>
       <c r="N53" t="n">
-        <v>67600.77</v>
+        <v>66411.21000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>67737</v>
+        <v>68314.36</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4970,75 +4968,77 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>65087.22</v>
+        <v>64768.53</v>
       </c>
       <c r="C54" t="n">
-        <v>65794.03</v>
+        <v>65270.95</v>
       </c>
       <c r="D54" t="n">
-        <v>65017.68</v>
+        <v>64186.68</v>
       </c>
       <c r="E54" t="n">
-        <v>65142.78</v>
+        <v>65270.95</v>
       </c>
       <c r="F54" t="n">
-        <v>-126.55</v>
+        <v>128.17</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="H54" t="n">
-        <v>776.35</v>
+        <v>1084.27</v>
       </c>
       <c r="I54" t="n">
-        <v>63746.81</v>
+        <v>64241.33</v>
       </c>
       <c r="J54" t="n">
-        <v>63366.18</v>
+        <v>64234.89</v>
       </c>
       <c r="K54" t="n">
-        <v>64508.07</v>
+        <v>64754.61</v>
       </c>
       <c r="L54" t="n">
-        <v>65649.96000000001</v>
+        <v>65274.32</v>
       </c>
       <c r="M54" t="n">
-        <v>66030.59</v>
+        <v>65530.96</v>
       </c>
       <c r="N54" t="n">
-        <v>66411.21000000001</v>
+        <v>65787.60000000001</v>
       </c>
       <c r="O54" t="n">
-        <v>68314.36</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
+        <v>66570.38</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5052,69 +5052,71 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>64768.53</v>
+        <v>64276.82</v>
       </c>
       <c r="C55" t="n">
-        <v>65270.95</v>
+        <v>64312.02</v>
       </c>
       <c r="D55" t="n">
-        <v>64186.68</v>
+        <v>63208.63</v>
       </c>
       <c r="E55" t="n">
-        <v>65270.95</v>
+        <v>64011.34</v>
       </c>
       <c r="F55" t="n">
-        <v>128.17</v>
+        <v>-1259.61</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H55" t="n">
-        <v>1084.27</v>
+        <v>1103.39</v>
       </c>
       <c r="I55" t="n">
-        <v>64241.33</v>
+        <v>63102.41</v>
       </c>
       <c r="J55" t="n">
-        <v>64234.89</v>
+        <v>64457.75</v>
       </c>
       <c r="K55" t="n">
-        <v>64754.61</v>
+        <v>64728.81</v>
       </c>
       <c r="L55" t="n">
-        <v>65274.32</v>
+        <v>64999.88</v>
       </c>
       <c r="M55" t="n">
-        <v>65530.96</v>
+        <v>65813.08</v>
       </c>
       <c r="N55" t="n">
-        <v>65787.60000000001</v>
+        <v>66626.28999999999</v>
       </c>
       <c r="O55" t="n">
-        <v>66570.38</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66355.22</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
@@ -5122,9 +5124,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5136,79 +5138,75 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>64276.82</v>
+        <v>63659.53</v>
       </c>
       <c r="C56" t="n">
-        <v>64312.02</v>
+        <v>63691.53</v>
       </c>
       <c r="D56" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E56" t="n">
-        <v>64011.34</v>
+        <v>63492.99</v>
       </c>
       <c r="F56" t="n">
-        <v>-1259.61</v>
+        <v>-518.35</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0081</v>
       </c>
       <c r="H56" t="n">
-        <v>1103.39</v>
+        <v>965.35</v>
       </c>
       <c r="I56" t="n">
-        <v>63102.41</v>
+        <v>62105.24</v>
       </c>
       <c r="J56" t="n">
-        <v>64457.75</v>
+        <v>63033.46</v>
       </c>
       <c r="K56" t="n">
-        <v>64728.81</v>
+        <v>63459.64</v>
       </c>
       <c r="L56" t="n">
-        <v>64999.88</v>
+        <v>63885.83</v>
       </c>
       <c r="M56" t="n">
-        <v>65813.08</v>
+        <v>64563.04</v>
       </c>
       <c r="N56" t="n">
-        <v>66626.28999999999</v>
+        <v>65240.24</v>
       </c>
       <c r="O56" t="n">
-        <v>66355.22</v>
+        <v>65415.41</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5222,7 +5220,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5232,71 +5230,69 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>63659.53</v>
+        <v>63190.37</v>
       </c>
       <c r="C57" t="n">
-        <v>63691.53</v>
+        <v>64101</v>
       </c>
       <c r="D57" t="n">
-        <v>62726.18</v>
+        <v>63067.18</v>
       </c>
       <c r="E57" t="n">
-        <v>63492.99</v>
+        <v>63484.1</v>
       </c>
       <c r="F57" t="n">
-        <v>-518.35</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0001</v>
       </c>
       <c r="H57" t="n">
-        <v>965.35</v>
+        <v>1033.82</v>
       </c>
       <c r="I57" t="n">
-        <v>62105.24</v>
+        <v>61760.83</v>
       </c>
       <c r="J57" t="n">
-        <v>63033.46</v>
+        <v>62669.7</v>
       </c>
       <c r="K57" t="n">
-        <v>63459.64</v>
+        <v>63010.31</v>
       </c>
       <c r="L57" t="n">
-        <v>63885.83</v>
+        <v>63350.92</v>
       </c>
       <c r="M57" t="n">
-        <v>64563.04</v>
+        <v>63975.66</v>
       </c>
       <c r="N57" t="n">
-        <v>65240.24</v>
+        <v>64600.41</v>
       </c>
       <c r="O57" t="n">
-        <v>65415.41</v>
+        <v>64656.88</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5304,60 +5300,64 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>63190.37</v>
+        <v>63672.13</v>
       </c>
       <c r="C58" t="n">
-        <v>64101</v>
+        <v>63923</v>
       </c>
       <c r="D58" t="n">
-        <v>63067.18</v>
+        <v>63209.92</v>
       </c>
       <c r="E58" t="n">
-        <v>63484.1</v>
+        <v>63923</v>
       </c>
       <c r="F58" t="n">
-        <v>-8.890000000000001</v>
+        <v>438.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0069</v>
       </c>
       <c r="H58" t="n">
-        <v>1033.82</v>
+        <v>713.08</v>
       </c>
       <c r="I58" t="n">
-        <v>61760.83</v>
+        <v>62033.36</v>
       </c>
       <c r="J58" t="n">
-        <v>62669.7</v>
+        <v>62400.29</v>
       </c>
       <c r="K58" t="n">
-        <v>63010.31</v>
+        <v>62967.19</v>
       </c>
       <c r="L58" t="n">
-        <v>63350.92</v>
+        <v>63534.1</v>
       </c>
       <c r="M58" t="n">
-        <v>63975.66</v>
+        <v>64001.01</v>
       </c>
       <c r="N58" t="n">
-        <v>64600.41</v>
+        <v>64467.93</v>
       </c>
       <c r="O58" t="n">
-        <v>64656.88</v>
+        <v>65134.82</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5368,14 +5368,14 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">
@@ -5384,7 +5384,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5398,50 +5398,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>63672.13</v>
+        <v>64643.58</v>
       </c>
       <c r="C59" t="n">
-        <v>63923</v>
+        <v>64643.58</v>
       </c>
       <c r="D59" t="n">
-        <v>63209.92</v>
+        <v>63824.56</v>
       </c>
       <c r="E59" t="n">
-        <v>63923</v>
+        <v>64136.25</v>
       </c>
       <c r="F59" t="n">
-        <v>438.9</v>
+        <v>213.25</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0033</v>
       </c>
       <c r="H59" t="n">
-        <v>713.08</v>
+        <v>819.02</v>
       </c>
       <c r="I59" t="n">
-        <v>62033.36</v>
+        <v>62496.84</v>
       </c>
       <c r="J59" t="n">
-        <v>62400.29</v>
+        <v>63388.19</v>
       </c>
       <c r="K59" t="n">
-        <v>62967.19</v>
+        <v>63566.46</v>
       </c>
       <c r="L59" t="n">
-        <v>63534.1</v>
+        <v>63744.73</v>
       </c>
       <c r="M59" t="n">
-        <v>64001.01</v>
+        <v>64279.54</v>
       </c>
       <c r="N59" t="n">
-        <v>64467.93</v>
+        <v>64814.35</v>
       </c>
       <c r="O59" t="n">
-        <v>65134.82</v>
+        <v>64636.08</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5452,7 +5452,7 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="7" t="inlineStr">
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5465,67 +5465,69 @@
       <c r="U59" s="8" t="n">
         <v/>
       </c>
-      <c r="V59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="V59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>64643.58</v>
+        <v>64681.55</v>
       </c>
       <c r="C60" t="n">
-        <v>64643.58</v>
+        <v>65436.57</v>
       </c>
       <c r="D60" t="n">
-        <v>63824.56</v>
+        <v>64403.85</v>
       </c>
       <c r="E60" t="n">
-        <v>64136.25</v>
+        <v>65018.95</v>
       </c>
       <c r="F60" t="n">
-        <v>213.25</v>
+        <v>882.7</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0138</v>
       </c>
       <c r="H60" t="n">
-        <v>819.02</v>
+        <v>1032.72</v>
       </c>
       <c r="I60" t="n">
-        <v>62496.84</v>
+        <v>63005.54</v>
       </c>
       <c r="J60" t="n">
-        <v>63388.19</v>
+        <v>63268.32</v>
       </c>
       <c r="K60" t="n">
-        <v>63566.46</v>
+        <v>63726.74</v>
       </c>
       <c r="L60" t="n">
-        <v>63744.73</v>
+        <v>64185.16</v>
       </c>
       <c r="M60" t="n">
-        <v>64279.54</v>
+        <v>64545.76</v>
       </c>
       <c r="N60" t="n">
-        <v>64814.35</v>
+        <v>64906.36</v>
       </c>
       <c r="O60" t="n">
-        <v>64636.08</v>
+        <v>65462.6</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5536,116 +5538,30 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="7" t="inlineStr">
+      <c r="S60" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V60" s="8" t="n">
+        <v/>
       </c>
       <c r="W60" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>64681.55</v>
-      </c>
-      <c r="C61" t="n">
-        <v>65436.57</v>
-      </c>
-      <c r="D61" t="n">
-        <v>64403.85</v>
-      </c>
-      <c r="E61" t="n">
-        <v>65018.95</v>
-      </c>
-      <c r="F61" t="n">
-        <v>882.7</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0.0138</v>
-      </c>
-      <c r="H61" t="n">
-        <v>1032.72</v>
-      </c>
-      <c r="I61" t="n">
-        <v>63005.54</v>
-      </c>
-      <c r="J61" t="n">
-        <v>63268.32</v>
-      </c>
-      <c r="K61" t="n">
-        <v>63726.74</v>
-      </c>
-      <c r="L61" t="n">
-        <v>64185.16</v>
-      </c>
-      <c r="M61" t="n">
-        <v>64545.76</v>
-      </c>
-      <c r="N61" t="n">
-        <v>64906.36</v>
-      </c>
-      <c r="O61" t="n">
-        <v>65462.6</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="9" t="inlineStr">
-        <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,11 +110,14 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,67 +637,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71587.71000000001</v>
+        <v>69609.88</v>
       </c>
       <c r="C2" t="n">
-        <v>71786.28</v>
+        <v>69609.88</v>
       </c>
       <c r="D2" t="n">
-        <v>68639.84</v>
+        <v>67997.57000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>69360.88</v>
+        <v>69468.11</v>
       </c>
       <c r="F2" t="n">
-        <v>-3005.46</v>
+        <v>107.23</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0415</v>
+        <v>0.0015</v>
       </c>
       <c r="H2" t="n">
-        <v>3146.44</v>
+        <v>1612.31</v>
       </c>
       <c r="I2" t="n">
-        <v>67371.12</v>
+        <v>65493.41</v>
       </c>
       <c r="J2" t="n">
-        <v>70293.75</v>
+        <v>65788.36</v>
       </c>
       <c r="K2" t="n">
-        <v>71060.57000000001</v>
+        <v>67787.66</v>
       </c>
       <c r="L2" t="n">
-        <v>71827.39</v>
+        <v>69786.97</v>
       </c>
       <c r="M2" t="n">
-        <v>73672.12</v>
+        <v>70934.10000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>75516.84</v>
+        <v>72081.23</v>
       </c>
       <c r="O2" t="n">
-        <v>75205.77</v>
+        <v>74932.72</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -708,58 +707,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69609.88</v>
+        <v>70085.60000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>69609.88</v>
+        <v>70667</v>
       </c>
       <c r="D3" t="n">
-        <v>67997.57000000001</v>
+        <v>69302.19</v>
       </c>
       <c r="E3" t="n">
-        <v>69468.11</v>
+        <v>70062.32000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>107.23</v>
+        <v>594.21</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0086</v>
       </c>
       <c r="H3" t="n">
-        <v>1612.31</v>
+        <v>1364.81</v>
       </c>
       <c r="I3" t="n">
-        <v>65493.41</v>
+        <v>66385.25999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>65788.36</v>
+        <v>68187.99000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>67787.66</v>
+        <v>68661.95</v>
       </c>
       <c r="L3" t="n">
-        <v>69786.97</v>
+        <v>69135.92</v>
       </c>
       <c r="M3" t="n">
-        <v>70934.10000000001</v>
+        <v>70274.27</v>
       </c>
       <c r="N3" t="n">
-        <v>72081.23</v>
+        <v>71412.61</v>
       </c>
       <c r="O3" t="n">
-        <v>74932.72</v>
+        <v>71222.2</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -770,13 +773,15 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -786,62 +791,58 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70085.60000000001</v>
+        <v>70774.28</v>
       </c>
       <c r="C4" t="n">
-        <v>70667</v>
+        <v>71962.34</v>
       </c>
       <c r="D4" t="n">
-        <v>69302.19</v>
+        <v>70126.14</v>
       </c>
       <c r="E4" t="n">
-        <v>70062.32000000001</v>
+        <v>70474.96000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>594.21</v>
+        <v>412.64</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0059</v>
       </c>
       <c r="H4" t="n">
-        <v>1364.81</v>
+        <v>1836.2</v>
       </c>
       <c r="I4" t="n">
-        <v>66385.25999999999</v>
+        <v>67937.38</v>
       </c>
       <c r="J4" t="n">
-        <v>68187.99000000001</v>
+        <v>68736.37</v>
       </c>
       <c r="K4" t="n">
-        <v>68661.95</v>
+        <v>69379.91</v>
       </c>
       <c r="L4" t="n">
-        <v>69135.92</v>
+        <v>70023.46000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>70274.27</v>
+        <v>70744.73</v>
       </c>
       <c r="N4" t="n">
-        <v>71412.61</v>
+        <v>71466</v>
       </c>
       <c r="O4" t="n">
-        <v>71222.2</v>
+        <v>72031.81</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -862,101 +863,99 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U4" s="8" t="n">
-        <v/>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70774.28</v>
+        <v>70039.89</v>
       </c>
       <c r="C5" t="n">
-        <v>71962.34</v>
+        <v>70081.39</v>
       </c>
       <c r="D5" t="n">
-        <v>70126.14</v>
+        <v>68676.25999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>70474.96000000001</v>
+        <v>68733.14999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>412.64</v>
+        <v>-1741.81</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0247</v>
       </c>
       <c r="H5" t="n">
-        <v>1836.2</v>
+        <v>1405.13</v>
       </c>
       <c r="I5" t="n">
-        <v>67937.38</v>
+        <v>68289.94</v>
       </c>
       <c r="J5" t="n">
-        <v>68736.37</v>
+        <v>68354.12</v>
       </c>
       <c r="K5" t="n">
-        <v>69379.91</v>
+        <v>69556.86</v>
       </c>
       <c r="L5" t="n">
-        <v>70023.46000000001</v>
+        <v>70759.60000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>70744.73</v>
+        <v>71393.06</v>
       </c>
       <c r="N5" t="n">
-        <v>71466</v>
+        <v>72026.52</v>
       </c>
       <c r="O5" t="n">
-        <v>72031.81</v>
+        <v>73798.55</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -968,132 +967,138 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70039.89</v>
+        <v>68676.06</v>
       </c>
       <c r="C6" t="n">
-        <v>70081.39</v>
+        <v>69788.03</v>
       </c>
       <c r="D6" t="n">
-        <v>68676.25999999999</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>68733.14999999999</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-1741.81</v>
+        <v>1010.92</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0147</v>
       </c>
       <c r="H6" t="n">
-        <v>1405.13</v>
+        <v>2178.54</v>
       </c>
       <c r="I6" t="n">
-        <v>68289.94</v>
+        <v>67271.12</v>
       </c>
       <c r="J6" t="n">
-        <v>68354.12</v>
+        <v>67005.17999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>69556.86</v>
+        <v>68030.58</v>
       </c>
       <c r="L6" t="n">
-        <v>70759.60000000001</v>
+        <v>69055.99000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>71393.06</v>
+        <v>69435.71000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>72026.52</v>
+        <v>69815.44</v>
       </c>
       <c r="O6" t="n">
-        <v>73798.55</v>
+        <v>71486.52</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>68676.06</v>
+        <v>69973.34</v>
       </c>
       <c r="C7" t="n">
-        <v>69788.03</v>
+        <v>70384.59</v>
       </c>
       <c r="D7" t="n">
-        <v>67609.49000000001</v>
+        <v>68904.41</v>
       </c>
       <c r="E7" t="n">
-        <v>69744.07000000001</v>
+        <v>69737.69</v>
       </c>
       <c r="F7" t="n">
-        <v>1010.92</v>
+        <v>-6.38</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0001</v>
       </c>
       <c r="H7" t="n">
-        <v>2178.54</v>
+        <v>1480.19</v>
       </c>
       <c r="I7" t="n">
-        <v>67271.12</v>
+        <v>65430.95</v>
       </c>
       <c r="J7" t="n">
-        <v>67005.17999999999</v>
+        <v>68088.19</v>
       </c>
       <c r="K7" t="n">
-        <v>68030.58</v>
+        <v>68654.8</v>
       </c>
       <c r="L7" t="n">
-        <v>69055.99000000001</v>
+        <v>69221.42</v>
       </c>
       <c r="M7" t="n">
-        <v>69435.71000000001</v>
+        <v>70833.34</v>
       </c>
       <c r="N7" t="n">
-        <v>69815.44</v>
+        <v>72445.25999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>71486.52</v>
+        <v>71966.57000000001</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1101,32 +1106,26 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1138,63 +1137,67 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69973.34</v>
+        <v>69460.08</v>
       </c>
       <c r="C8" t="n">
-        <v>70384.59</v>
+        <v>69957.50999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>68904.41</v>
+        <v>68003.92</v>
       </c>
       <c r="E8" t="n">
-        <v>69737.69</v>
+        <v>68256.96000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.38</v>
+        <v>-1480.73</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0212</v>
       </c>
       <c r="H8" t="n">
-        <v>1480.19</v>
+        <v>1953.59</v>
       </c>
       <c r="I8" t="n">
-        <v>65430.95</v>
+        <v>67424.22</v>
       </c>
       <c r="J8" t="n">
-        <v>68088.19</v>
+        <v>68304.09</v>
       </c>
       <c r="K8" t="n">
-        <v>68654.8</v>
+        <v>68997.59</v>
       </c>
       <c r="L8" t="n">
-        <v>69221.42</v>
+        <v>69691.09</v>
       </c>
       <c r="M8" t="n">
-        <v>70833.34</v>
+        <v>70477.78</v>
       </c>
       <c r="N8" t="n">
-        <v>72445.25999999999</v>
+        <v>71264.47</v>
       </c>
       <c r="O8" t="n">
-        <v>71966.57000000001</v>
+        <v>71864.78</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1206,78 +1209,72 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69460.08</v>
+        <v>67704.16</v>
       </c>
       <c r="C9" t="n">
-        <v>69957.50999999999</v>
+        <v>68432.67999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>68003.92</v>
+        <v>66819.05</v>
       </c>
       <c r="E9" t="n">
-        <v>68256.96000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="F9" t="n">
-        <v>-1480.73</v>
+        <v>-1437.91</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="H9" t="n">
-        <v>1953.59</v>
+        <v>1613.63</v>
       </c>
       <c r="I9" t="n">
-        <v>67424.22</v>
+        <v>66050.34</v>
       </c>
       <c r="J9" t="n">
-        <v>68304.09</v>
+        <v>65941.5</v>
       </c>
       <c r="K9" t="n">
-        <v>68997.59</v>
+        <v>67280.17</v>
       </c>
       <c r="L9" t="n">
-        <v>69691.09</v>
+        <v>68618.84</v>
       </c>
       <c r="M9" t="n">
-        <v>70477.78</v>
+        <v>69233.75</v>
       </c>
       <c r="N9" t="n">
-        <v>71264.47</v>
+        <v>69848.67</v>
       </c>
       <c r="O9" t="n">
-        <v>71864.78</v>
+        <v>71911.09</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1292,7 +1289,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1302,50 +1299,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>67704.16</v>
+        <v>67046.37</v>
       </c>
       <c r="C10" t="n">
-        <v>68432.67999999999</v>
+        <v>68447.89</v>
       </c>
       <c r="D10" t="n">
-        <v>66819.05</v>
+        <v>67008.89</v>
       </c>
       <c r="E10" t="n">
-        <v>66819.05</v>
+        <v>67743.85000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-1437.91</v>
+        <v>924.8</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0211</v>
+        <v>0.0138</v>
       </c>
       <c r="H10" t="n">
-        <v>1613.63</v>
+        <v>1439</v>
       </c>
       <c r="I10" t="n">
-        <v>66050.34</v>
+        <v>65205.41</v>
       </c>
       <c r="J10" t="n">
-        <v>65941.5</v>
+        <v>64802.01</v>
       </c>
       <c r="K10" t="n">
-        <v>67280.17</v>
+        <v>66012.23</v>
       </c>
       <c r="L10" t="n">
-        <v>68618.84</v>
+        <v>67222.46000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>69233.75</v>
+        <v>67625.86</v>
       </c>
       <c r="N10" t="n">
-        <v>69848.67</v>
+        <v>68029.27</v>
       </c>
       <c r="O10" t="n">
-        <v>71911.09</v>
+        <v>70046.31</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1353,79 +1350,85 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>67046.37</v>
+        <v>68526.72</v>
       </c>
       <c r="C11" t="n">
-        <v>68447.89</v>
+        <v>69374.86</v>
       </c>
       <c r="D11" t="n">
-        <v>67008.89</v>
+        <v>68271.91</v>
       </c>
       <c r="E11" t="n">
-        <v>67743.85000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F11" t="n">
-        <v>924.8</v>
+        <v>813.88</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.012</v>
       </c>
       <c r="H11" t="n">
-        <v>1439</v>
+        <v>1102.95</v>
       </c>
       <c r="I11" t="n">
-        <v>65205.41</v>
+        <v>65569.89</v>
       </c>
       <c r="J11" t="n">
-        <v>64802.01</v>
+        <v>66312.58</v>
       </c>
       <c r="K11" t="n">
-        <v>66012.23</v>
+        <v>67024.35000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>67222.46000000001</v>
+        <v>67736.12</v>
       </c>
       <c r="M11" t="n">
-        <v>67625.86</v>
+        <v>68463.35000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>68029.27</v>
+        <v>69190.58</v>
       </c>
       <c r="O11" t="n">
-        <v>70046.31</v>
+        <v>69886.89</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1454,7 +1457,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1468,155 +1471,147 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>68526.72</v>
+        <v>68410.63</v>
       </c>
       <c r="C12" t="n">
-        <v>69374.86</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>68271.91</v>
+        <v>66653.11</v>
       </c>
       <c r="E12" t="n">
-        <v>68557.73</v>
+        <v>67242.73</v>
       </c>
       <c r="F12" t="n">
-        <v>813.88</v>
+        <v>-1315</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0192</v>
       </c>
       <c r="H12" t="n">
-        <v>1102.95</v>
+        <v>2425.1</v>
       </c>
       <c r="I12" t="n">
-        <v>65569.89</v>
+        <v>67168.95</v>
       </c>
       <c r="J12" t="n">
-        <v>66312.58</v>
+        <v>67321.95</v>
       </c>
       <c r="K12" t="n">
-        <v>67024.35000000001</v>
+        <v>68006.25</v>
       </c>
       <c r="L12" t="n">
-        <v>67736.12</v>
+        <v>68690.55</v>
       </c>
       <c r="M12" t="n">
-        <v>68463.35000000001</v>
+        <v>69109.2</v>
       </c>
       <c r="N12" t="n">
-        <v>69190.58</v>
+        <v>69527.85000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>69886.89</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+        <v>70477.81</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68410.63</v>
+        <v>67002.94</v>
       </c>
       <c r="C13" t="n">
-        <v>69078.21000000001</v>
+        <v>67800.17999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>66653.11</v>
+        <v>66268.60000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>67242.73</v>
+        <v>67743.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-1315</v>
+        <v>500.77</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0074</v>
       </c>
       <c r="H13" t="n">
-        <v>2425.1</v>
+        <v>1531.58</v>
       </c>
       <c r="I13" t="n">
-        <v>67168.95</v>
+        <v>64228.01</v>
       </c>
       <c r="J13" t="n">
-        <v>67321.95</v>
+        <v>64506.16</v>
       </c>
       <c r="K13" t="n">
-        <v>68006.25</v>
+        <v>66030.17999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>68690.55</v>
+        <v>67554.19</v>
       </c>
       <c r="M13" t="n">
-        <v>69109.2</v>
+        <v>68455.28</v>
       </c>
       <c r="N13" t="n">
-        <v>69527.85000000001</v>
+        <v>69356.36</v>
       </c>
       <c r="O13" t="n">
-        <v>70477.81</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>71503.31</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1628,60 +1623,64 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>67002.94</v>
+        <v>67989.74000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>67800.17999999999</v>
+        <v>68798.24000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>66268.60000000001</v>
+        <v>67833.17</v>
       </c>
       <c r="E14" t="n">
-        <v>67743.5</v>
+        <v>68751.50999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>500.77</v>
+        <v>1008.01</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0149</v>
       </c>
       <c r="H14" t="n">
-        <v>1531.58</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>64228.01</v>
+        <v>64737.02</v>
       </c>
       <c r="J14" t="n">
-        <v>64506.16</v>
+        <v>66566.48</v>
       </c>
       <c r="K14" t="n">
-        <v>66030.17999999999</v>
+        <v>66977.71000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>67554.19</v>
+        <v>67388.95</v>
       </c>
       <c r="M14" t="n">
-        <v>68455.28</v>
+        <v>68509.28999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>69356.36</v>
+        <v>69629.63</v>
       </c>
       <c r="O14" t="n">
-        <v>71503.31</v>
+        <v>69331.75999999999</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1694,11 +1693,13 @@
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1706,148 +1707,148 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67989.74000000001</v>
+        <v>67900.42999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>68798.24000000001</v>
+        <v>68069.82000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>67833.17</v>
+        <v>66499.49000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>68751.50999999999</v>
+        <v>66835.53999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1008.01</v>
+        <v>-1915.97</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0279</v>
       </c>
       <c r="H15" t="n">
-        <v>965.0700000000001</v>
+        <v>1570.33</v>
       </c>
       <c r="I15" t="n">
-        <v>64737.02</v>
+        <v>66868.10000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>66566.48</v>
+        <v>68004.34</v>
       </c>
       <c r="K15" t="n">
-        <v>66977.71000000001</v>
+        <v>68268.97</v>
       </c>
       <c r="L15" t="n">
-        <v>67388.95</v>
+        <v>68533.61</v>
       </c>
       <c r="M15" t="n">
-        <v>68509.28999999999</v>
+        <v>69234.03999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>69629.63</v>
+        <v>69934.48</v>
       </c>
       <c r="O15" t="n">
-        <v>69331.75999999999</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+        <v>69763.31</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>67900.42999999999</v>
+        <v>66339.85000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>68069.82000000001</v>
+        <v>66441.77</v>
       </c>
       <c r="D16" t="n">
-        <v>66499.49000000001</v>
+        <v>62704.6</v>
       </c>
       <c r="E16" t="n">
-        <v>66835.53999999999</v>
+        <v>64141.12</v>
       </c>
       <c r="F16" t="n">
-        <v>-1915.97</v>
+        <v>-2694.42</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0403</v>
       </c>
       <c r="H16" t="n">
-        <v>1570.33</v>
+        <v>3737.17</v>
       </c>
       <c r="I16" t="n">
-        <v>66868.10000000001</v>
+        <v>64929.16</v>
       </c>
       <c r="J16" t="n">
-        <v>68004.34</v>
+        <v>65040.65</v>
       </c>
       <c r="K16" t="n">
-        <v>68268.97</v>
+        <v>66050.38</v>
       </c>
       <c r="L16" t="n">
-        <v>68533.61</v>
+        <v>67060.10000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>69234.03999999999</v>
+        <v>67620.7</v>
       </c>
       <c r="N16" t="n">
-        <v>69934.48</v>
+        <v>68181.31</v>
       </c>
       <c r="O16" t="n">
-        <v>69763.31</v>
+        <v>69640.14999999999</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
@@ -1878,7 +1879,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1888,134 +1889,134 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66339.85000000001</v>
+        <v>64544.05</v>
       </c>
       <c r="C17" t="n">
-        <v>66441.77</v>
+        <v>66232.19</v>
       </c>
       <c r="D17" t="n">
-        <v>62704.6</v>
+        <v>64203.47</v>
       </c>
       <c r="E17" t="n">
-        <v>64141.12</v>
+        <v>66232.19</v>
       </c>
       <c r="F17" t="n">
-        <v>-2694.42</v>
+        <v>2091.07</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0326</v>
       </c>
       <c r="H17" t="n">
-        <v>3737.17</v>
+        <v>2028.72</v>
       </c>
       <c r="I17" t="n">
-        <v>64929.16</v>
+        <v>58967.43</v>
       </c>
       <c r="J17" t="n">
-        <v>65040.65</v>
+        <v>60187.92</v>
       </c>
       <c r="K17" t="n">
-        <v>66050.38</v>
+        <v>62272.54</v>
       </c>
       <c r="L17" t="n">
-        <v>67060.10000000001</v>
+        <v>64357.15</v>
       </c>
       <c r="M17" t="n">
-        <v>67620.7</v>
+        <v>66009.71000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>68181.31</v>
+        <v>67662.25999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>69640.14999999999</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>70178.95</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>64544.05</v>
+        <v>66449.27</v>
       </c>
       <c r="C18" t="n">
-        <v>66232.19</v>
+        <v>67592.2</v>
       </c>
       <c r="D18" t="n">
-        <v>64203.47</v>
+        <v>65955.60000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>66232.19</v>
+        <v>66115.60000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>2091.07</v>
+        <v>-116.59</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0326</v>
+        <v>-0.0018</v>
       </c>
       <c r="H18" t="n">
-        <v>2028.72</v>
+        <v>1636.6</v>
       </c>
       <c r="I18" t="n">
-        <v>58967.43</v>
+        <v>62174.75</v>
       </c>
       <c r="J18" t="n">
-        <v>60187.92</v>
+        <v>64710.65</v>
       </c>
       <c r="K18" t="n">
-        <v>62272.54</v>
+        <v>65217.83</v>
       </c>
       <c r="L18" t="n">
-        <v>64357.15</v>
+        <v>65725.00999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>66009.71000000001</v>
+        <v>67246.55</v>
       </c>
       <c r="N18" t="n">
-        <v>67662.25999999999</v>
+        <v>68768.09</v>
       </c>
       <c r="O18" t="n">
-        <v>70178.95</v>
+        <v>68260.91</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2028,12 +2029,12 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U18" s="8" t="n">
@@ -2042,7 +2043,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2056,50 +2057,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>66449.27</v>
+        <v>66421.00999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>67592.2</v>
+        <v>67022.37</v>
       </c>
       <c r="D19" t="n">
-        <v>65955.60000000001</v>
+        <v>66208.66</v>
       </c>
       <c r="E19" t="n">
-        <v>66115.60000000001</v>
+        <v>66422.60000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-116.59</v>
+        <v>307</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0046</v>
       </c>
       <c r="H19" t="n">
-        <v>1636.6</v>
+        <v>813.71</v>
       </c>
       <c r="I19" t="n">
-        <v>62174.75</v>
+        <v>64319</v>
       </c>
       <c r="J19" t="n">
-        <v>64710.65</v>
+        <v>64149.85</v>
       </c>
       <c r="K19" t="n">
-        <v>65217.83</v>
+        <v>65297.3</v>
       </c>
       <c r="L19" t="n">
-        <v>65725.00999999999</v>
+        <v>66444.75</v>
       </c>
       <c r="M19" t="n">
-        <v>67246.55</v>
+        <v>66933.89999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>68768.09</v>
+        <v>67423.05</v>
       </c>
       <c r="O19" t="n">
-        <v>68260.91</v>
+        <v>69228.8</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2110,9 +2111,9 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2126,7 +2127,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2140,69 +2141,73 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>66421.00999999999</v>
+        <v>65584.25</v>
       </c>
       <c r="C20" t="n">
-        <v>67022.37</v>
+        <v>65720.81</v>
       </c>
       <c r="D20" t="n">
-        <v>66208.66</v>
+        <v>64201.03</v>
       </c>
       <c r="E20" t="n">
-        <v>66422.60000000001</v>
+        <v>64611.15</v>
       </c>
       <c r="F20" t="n">
-        <v>307</v>
+        <v>-1811.45</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0273</v>
       </c>
       <c r="H20" t="n">
-        <v>813.71</v>
+        <v>1519.78</v>
       </c>
       <c r="I20" t="n">
-        <v>64319</v>
+        <v>65394.95</v>
       </c>
       <c r="J20" t="n">
-        <v>64149.85</v>
+        <v>65512.44</v>
       </c>
       <c r="K20" t="n">
-        <v>65297.3</v>
+        <v>66015.75</v>
       </c>
       <c r="L20" t="n">
-        <v>66444.75</v>
+        <v>66519.06</v>
       </c>
       <c r="M20" t="n">
-        <v>66933.89999999999</v>
+        <v>66829.46000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>67423.05</v>
+        <v>67139.86</v>
       </c>
       <c r="O20" t="n">
-        <v>69228.8</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+        <v>67836.08</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2210,83 +2215,73 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>65584.25</v>
+        <v>65164.98</v>
       </c>
       <c r="C21" t="n">
-        <v>65720.81</v>
+        <v>65220.69</v>
       </c>
       <c r="D21" t="n">
-        <v>64201.03</v>
+        <v>64123.4</v>
       </c>
       <c r="E21" t="n">
-        <v>64611.15</v>
+        <v>64931.19</v>
       </c>
       <c r="F21" t="n">
-        <v>-1811.45</v>
+        <v>320.04</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.005</v>
       </c>
       <c r="H21" t="n">
-        <v>1519.78</v>
+        <v>1097.29</v>
       </c>
       <c r="I21" t="n">
-        <v>65394.95</v>
+        <v>62681.25</v>
       </c>
       <c r="J21" t="n">
-        <v>65512.44</v>
+        <v>62916.48</v>
       </c>
       <c r="K21" t="n">
-        <v>66015.75</v>
+        <v>63851.26</v>
       </c>
       <c r="L21" t="n">
-        <v>66519.06</v>
+        <v>64786.04</v>
       </c>
       <c r="M21" t="n">
-        <v>66829.46000000001</v>
+        <v>65371.04</v>
       </c>
       <c r="N21" t="n">
-        <v>67139.86</v>
+        <v>65956.03999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>67836.08</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>67240.59</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2298,73 +2293,83 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>65164.98</v>
+        <v>64539.92</v>
       </c>
       <c r="C22" t="n">
-        <v>65220.69</v>
+        <v>64573.18</v>
       </c>
       <c r="D22" t="n">
-        <v>64123.4</v>
+        <v>61923.6</v>
       </c>
       <c r="E22" t="n">
-        <v>64931.19</v>
+        <v>62364.92</v>
       </c>
       <c r="F22" t="n">
-        <v>320.04</v>
+        <v>-2566.27</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0395</v>
       </c>
       <c r="H22" t="n">
-        <v>1097.29</v>
+        <v>2649.58</v>
       </c>
       <c r="I22" t="n">
-        <v>62681.25</v>
+        <v>63026.11</v>
       </c>
       <c r="J22" t="n">
-        <v>62916.48</v>
+        <v>63963.47</v>
       </c>
       <c r="K22" t="n">
-        <v>63851.26</v>
+        <v>64382.54</v>
       </c>
       <c r="L22" t="n">
-        <v>64786.04</v>
+        <v>64801.62</v>
       </c>
       <c r="M22" t="n">
-        <v>65371.04</v>
+        <v>65479.84</v>
       </c>
       <c r="N22" t="n">
-        <v>65956.03999999999</v>
+        <v>66158.06</v>
       </c>
       <c r="O22" t="n">
-        <v>67240.59</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>66317.98</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2376,80 +2381,72 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>64539.92</v>
+        <v>62734.68</v>
       </c>
       <c r="C23" t="n">
-        <v>64573.18</v>
+        <v>63138.04</v>
       </c>
       <c r="D23" t="n">
-        <v>61923.6</v>
+        <v>60448.9</v>
       </c>
       <c r="E23" t="n">
-        <v>62364.92</v>
+        <v>61434.19</v>
       </c>
       <c r="F23" t="n">
-        <v>-2566.27</v>
+        <v>-930.73</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0149</v>
       </c>
       <c r="H23" t="n">
-        <v>2649.58</v>
+        <v>2689.14</v>
       </c>
       <c r="I23" t="n">
-        <v>63026.11</v>
+        <v>59274.02</v>
       </c>
       <c r="J23" t="n">
-        <v>63963.47</v>
+        <v>59273.61</v>
       </c>
       <c r="K23" t="n">
-        <v>64382.54</v>
+        <v>61040.13</v>
       </c>
       <c r="L23" t="n">
-        <v>64801.62</v>
+        <v>62806.66</v>
       </c>
       <c r="M23" t="n">
-        <v>65479.84</v>
+        <v>63689.71</v>
       </c>
       <c r="N23" t="n">
-        <v>66158.06</v>
+        <v>64572.77</v>
       </c>
       <c r="O23" t="n">
-        <v>66317.98</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>67222.75999999999</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -2464,7 +2461,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2474,50 +2471,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>62734.68</v>
+        <v>61258.34</v>
       </c>
       <c r="C24" t="n">
-        <v>63138.04</v>
+        <v>62924.84</v>
       </c>
       <c r="D24" t="n">
-        <v>60448.9</v>
+        <v>61049.7</v>
       </c>
       <c r="E24" t="n">
-        <v>61434.19</v>
+        <v>61867.43</v>
       </c>
       <c r="F24" t="n">
-        <v>-930.73</v>
+        <v>433.24</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0071</v>
       </c>
       <c r="H24" t="n">
-        <v>2689.14</v>
+        <v>1875.14</v>
       </c>
       <c r="I24" t="n">
-        <v>59274.02</v>
+        <v>57759.76</v>
       </c>
       <c r="J24" t="n">
-        <v>59273.61</v>
+        <v>58565.41</v>
       </c>
       <c r="K24" t="n">
-        <v>61040.13</v>
+        <v>60089.62</v>
       </c>
       <c r="L24" t="n">
-        <v>62806.66</v>
+        <v>61613.83</v>
       </c>
       <c r="M24" t="n">
-        <v>63689.71</v>
+        <v>62778.76</v>
       </c>
       <c r="N24" t="n">
-        <v>64572.77</v>
+        <v>63943.69</v>
       </c>
       <c r="O24" t="n">
-        <v>67222.75999999999</v>
+        <v>65827.17999999999</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2525,18 +2522,18 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2544,60 +2541,64 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>61258.34</v>
+        <v>61957.1</v>
       </c>
       <c r="C25" t="n">
-        <v>62924.84</v>
+        <v>65364.73</v>
       </c>
       <c r="D25" t="n">
-        <v>61049.7</v>
+        <v>61948.23</v>
       </c>
       <c r="E25" t="n">
-        <v>61867.43</v>
+        <v>64362.02</v>
       </c>
       <c r="F25" t="n">
-        <v>433.24</v>
+        <v>2494.59</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0403</v>
       </c>
       <c r="H25" t="n">
-        <v>1875.14</v>
+        <v>3416.5</v>
       </c>
       <c r="I25" t="n">
-        <v>57759.76</v>
+        <v>59174.56</v>
       </c>
       <c r="J25" t="n">
-        <v>58565.41</v>
+        <v>59932.37</v>
       </c>
       <c r="K25" t="n">
-        <v>60089.62</v>
+        <v>60929.86</v>
       </c>
       <c r="L25" t="n">
-        <v>61613.83</v>
+        <v>61927.35</v>
       </c>
       <c r="M25" t="n">
-        <v>62778.76</v>
+        <v>62805</v>
       </c>
       <c r="N25" t="n">
-        <v>63943.69</v>
+        <v>63682.65</v>
       </c>
       <c r="O25" t="n">
-        <v>65827.17999999999</v>
+        <v>64799.98</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2610,7 +2611,7 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2618,70 +2619,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>61957.1</v>
+        <v>63834.95</v>
       </c>
       <c r="C26" t="n">
-        <v>65364.73</v>
+        <v>63905.12</v>
       </c>
       <c r="D26" t="n">
-        <v>61948.23</v>
+        <v>62703.47</v>
       </c>
       <c r="E26" t="n">
-        <v>64362.02</v>
+        <v>63754.9</v>
       </c>
       <c r="F26" t="n">
-        <v>2494.59</v>
+        <v>-607.12</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0403</v>
+        <v>-0.0094</v>
       </c>
       <c r="H26" t="n">
-        <v>3416.5</v>
+        <v>1201.65</v>
       </c>
       <c r="I26" t="n">
-        <v>59174.56</v>
+        <v>58531.73</v>
       </c>
       <c r="J26" t="n">
-        <v>59932.37</v>
+        <v>61298.29</v>
       </c>
       <c r="K26" t="n">
-        <v>60929.86</v>
+        <v>62653.77</v>
       </c>
       <c r="L26" t="n">
-        <v>61927.35</v>
+        <v>64009.25</v>
       </c>
       <c r="M26" t="n">
-        <v>62805</v>
+        <v>66070.27</v>
       </c>
       <c r="N26" t="n">
-        <v>63682.65</v>
+        <v>68131.28999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>64799.98</v>
+        <v>68781.23</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2692,80 +2693,78 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63834.95</v>
+        <v>63995.28</v>
       </c>
       <c r="C27" t="n">
-        <v>63905.12</v>
+        <v>64240.5</v>
       </c>
       <c r="D27" t="n">
-        <v>62703.47</v>
+        <v>62864.43</v>
       </c>
       <c r="E27" t="n">
-        <v>63754.9</v>
+        <v>63957.53</v>
       </c>
       <c r="F27" t="n">
-        <v>-607.12</v>
+        <v>202.63</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0032</v>
       </c>
       <c r="H27" t="n">
-        <v>1201.65</v>
+        <v>1376.07</v>
       </c>
       <c r="I27" t="n">
-        <v>58531.73</v>
+        <v>61501.82</v>
       </c>
       <c r="J27" t="n">
-        <v>61298.29</v>
+        <v>62778.55</v>
       </c>
       <c r="K27" t="n">
-        <v>62653.77</v>
+        <v>63154.07</v>
       </c>
       <c r="L27" t="n">
-        <v>64009.25</v>
+        <v>63529.6</v>
       </c>
       <c r="M27" t="n">
-        <v>66070.27</v>
+        <v>64355.72</v>
       </c>
       <c r="N27" t="n">
-        <v>68131.28999999999</v>
+        <v>65181.85</v>
       </c>
       <c r="O27" t="n">
-        <v>68781.23</v>
+        <v>65106.77</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2773,16 +2772,20 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2790,64 +2793,60 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>63995.28</v>
+        <v>64565.27</v>
       </c>
       <c r="C28" t="n">
-        <v>64240.5</v>
+        <v>66302.52</v>
       </c>
       <c r="D28" t="n">
-        <v>62864.43</v>
+        <v>64555.52</v>
       </c>
       <c r="E28" t="n">
-        <v>63957.53</v>
+        <v>66300.44</v>
       </c>
       <c r="F28" t="n">
-        <v>202.63</v>
+        <v>2342.91</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0366</v>
       </c>
       <c r="H28" t="n">
-        <v>1376.07</v>
+        <v>1747</v>
       </c>
       <c r="I28" t="n">
-        <v>61501.82</v>
+        <v>61488.36</v>
       </c>
       <c r="J28" t="n">
-        <v>62778.55</v>
+        <v>62783.99</v>
       </c>
       <c r="K28" t="n">
-        <v>63154.07</v>
+        <v>63269.5</v>
       </c>
       <c r="L28" t="n">
-        <v>63529.6</v>
+        <v>63755</v>
       </c>
       <c r="M28" t="n">
-        <v>64355.72</v>
+        <v>64645.57</v>
       </c>
       <c r="N28" t="n">
-        <v>65181.85</v>
+        <v>65536.13</v>
       </c>
       <c r="O28" t="n">
-        <v>65106.77</v>
+        <v>65616.57000000001</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2855,10 +2854,8 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
@@ -2867,16 +2864,20 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2886,134 +2887,136 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>64565.27</v>
+        <v>65896</v>
       </c>
       <c r="C29" t="n">
-        <v>66302.52</v>
+        <v>65983.13</v>
       </c>
       <c r="D29" t="n">
-        <v>64555.52</v>
+        <v>64942.07</v>
       </c>
       <c r="E29" t="n">
-        <v>66300.44</v>
+        <v>65683.25999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>2342.91</v>
+        <v>-617.1799999999999</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0366</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>1747</v>
+        <v>1041.06</v>
       </c>
       <c r="I29" t="n">
-        <v>61488.36</v>
+        <v>62808.52</v>
       </c>
       <c r="J29" t="n">
-        <v>62783.99</v>
+        <v>64989.14</v>
       </c>
       <c r="K29" t="n">
-        <v>63269.5</v>
+        <v>65426.94</v>
       </c>
       <c r="L29" t="n">
-        <v>63755</v>
+        <v>65864.73</v>
       </c>
       <c r="M29" t="n">
-        <v>64645.57</v>
+        <v>67173.94</v>
       </c>
       <c r="N29" t="n">
-        <v>65536.13</v>
+        <v>68483.14999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>65616.57000000001</v>
+        <v>68049.53</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>65896</v>
+        <v>65746.13</v>
       </c>
       <c r="C30" t="n">
-        <v>65983.13</v>
+        <v>65990.72</v>
       </c>
       <c r="D30" t="n">
-        <v>64942.07</v>
+        <v>64651.49</v>
       </c>
       <c r="E30" t="n">
-        <v>65683.25999999999</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>-617.1799999999999</v>
+        <v>-76.55</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="H30" t="n">
-        <v>1041.06</v>
+        <v>1339.23</v>
       </c>
       <c r="I30" t="n">
-        <v>62808.52</v>
+        <v>63901.01</v>
       </c>
       <c r="J30" t="n">
-        <v>64989.14</v>
+        <v>64752.52</v>
       </c>
       <c r="K30" t="n">
-        <v>65426.94</v>
+        <v>65162.73</v>
       </c>
       <c r="L30" t="n">
-        <v>65864.73</v>
+        <v>65572.92999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>67173.94</v>
+        <v>66203.78999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>68483.14999999999</v>
+        <v>66834.64999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>68049.53</v>
+        <v>67024.2</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3028,9 +3031,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3042,7 +3045,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3056,136 +3059,132 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>65746.13</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>65990.72</v>
+        <v>67006.84</v>
       </c>
       <c r="D31" t="n">
-        <v>64651.49</v>
+        <v>65848.58</v>
       </c>
       <c r="E31" t="n">
-        <v>65606.71000000001</v>
+        <v>66970.22</v>
       </c>
       <c r="F31" t="n">
-        <v>-76.55</v>
+        <v>1363.51</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0208</v>
       </c>
       <c r="H31" t="n">
-        <v>1339.23</v>
+        <v>1158.27</v>
       </c>
       <c r="I31" t="n">
-        <v>63901.01</v>
+        <v>63312.26</v>
       </c>
       <c r="J31" t="n">
-        <v>64752.52</v>
+        <v>64410.28</v>
       </c>
       <c r="K31" t="n">
-        <v>65162.73</v>
+        <v>64937.1</v>
       </c>
       <c r="L31" t="n">
-        <v>65572.92999999999</v>
+        <v>65463.91</v>
       </c>
       <c r="M31" t="n">
-        <v>66203.78999999999</v>
+        <v>66276.33</v>
       </c>
       <c r="N31" t="n">
-        <v>66834.64999999999</v>
+        <v>67088.75</v>
       </c>
       <c r="O31" t="n">
-        <v>67024.2</v>
+        <v>67329.95</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>65905.10000000001</v>
+        <v>66994.05</v>
       </c>
       <c r="C32" t="n">
-        <v>67006.84</v>
+        <v>67569.36</v>
       </c>
       <c r="D32" t="n">
-        <v>65848.58</v>
+        <v>66735.75999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>66970.22</v>
+        <v>67524.06</v>
       </c>
       <c r="F32" t="n">
-        <v>1363.51</v>
+        <v>553.84</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="H32" t="n">
-        <v>1158.27</v>
+        <v>833.6</v>
       </c>
       <c r="I32" t="n">
-        <v>63312.26</v>
+        <v>64690.31</v>
       </c>
       <c r="J32" t="n">
-        <v>64410.28</v>
+        <v>66083.21000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>64937.1</v>
+        <v>66391.09</v>
       </c>
       <c r="L32" t="n">
-        <v>65463.91</v>
+        <v>66698.96000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>66276.33</v>
+        <v>67549.35000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>67088.75</v>
+        <v>68399.74000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>67329.95</v>
+        <v>68165.11</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3203,18 +3202,16 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3224,50 +3221,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>66994.05</v>
+        <v>68033.17</v>
       </c>
       <c r="C33" t="n">
-        <v>67569.36</v>
+        <v>68799.71000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>66735.75999999999</v>
+        <v>68006.17</v>
       </c>
       <c r="E33" t="n">
-        <v>67524.06</v>
+        <v>68308.59</v>
       </c>
       <c r="F33" t="n">
-        <v>553.84</v>
+        <v>784.53</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0116</v>
       </c>
       <c r="H33" t="n">
-        <v>833.6</v>
+        <v>793.54</v>
       </c>
       <c r="I33" t="n">
-        <v>64690.31</v>
+        <v>65902.16</v>
       </c>
       <c r="J33" t="n">
-        <v>66083.21000000001</v>
+        <v>66876.21000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>66391.09</v>
+        <v>67107.25999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>66698.96000000001</v>
+        <v>67338.31</v>
       </c>
       <c r="M33" t="n">
-        <v>67549.35000000001</v>
+        <v>67940.86</v>
       </c>
       <c r="N33" t="n">
-        <v>68399.74000000001</v>
+        <v>68543.42</v>
       </c>
       <c r="O33" t="n">
-        <v>68165.11</v>
+        <v>68402.96000000001</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3285,16 +3282,20 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3304,50 +3305,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>68033.17</v>
+        <v>68811.17</v>
       </c>
       <c r="C34" t="n">
-        <v>68799.71000000001</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>68006.17</v>
+        <v>68471.14999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>68308.59</v>
+        <v>68713.8</v>
       </c>
       <c r="F34" t="n">
-        <v>784.53</v>
+        <v>405.2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0059</v>
       </c>
       <c r="H34" t="n">
-        <v>793.54</v>
+        <v>1137.09</v>
       </c>
       <c r="I34" t="n">
-        <v>65902.16</v>
+        <v>67212.63</v>
       </c>
       <c r="J34" t="n">
-        <v>66876.21000000001</v>
+        <v>67467.88</v>
       </c>
       <c r="K34" t="n">
-        <v>67107.25999999999</v>
+        <v>67911.82000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>67338.31</v>
+        <v>68355.77</v>
       </c>
       <c r="M34" t="n">
-        <v>67940.86</v>
+        <v>68705.36</v>
       </c>
       <c r="N34" t="n">
-        <v>68543.42</v>
+        <v>69054.96000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>68402.96000000001</v>
+        <v>69593.25</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3365,7 +3366,7 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U34" s="8" t="inlineStr">
@@ -3375,10 +3376,10 @@
       </c>
       <c r="V34" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3388,50 +3389,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>68811.17</v>
+        <v>68882.06</v>
       </c>
       <c r="C35" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>68471.14999999999</v>
+        <v>68492.03999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>68713.8</v>
+        <v>69220.25</v>
       </c>
       <c r="F35" t="n">
-        <v>405.2</v>
+        <v>506.45</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="H35" t="n">
-        <v>1137.09</v>
+        <v>733.53</v>
       </c>
       <c r="I35" t="n">
-        <v>67212.63</v>
+        <v>67334.05</v>
       </c>
       <c r="J35" t="n">
-        <v>67467.88</v>
+        <v>67413.75</v>
       </c>
       <c r="K35" t="n">
-        <v>67911.82000000001</v>
+        <v>68145.25</v>
       </c>
       <c r="L35" t="n">
-        <v>68355.77</v>
+        <v>68876.75</v>
       </c>
       <c r="M35" t="n">
-        <v>68705.36</v>
+        <v>69282.34</v>
       </c>
       <c r="N35" t="n">
-        <v>69054.96000000001</v>
+        <v>69687.94</v>
       </c>
       <c r="O35" t="n">
-        <v>69593.25</v>
+        <v>70745.34</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3452,90 +3453,94 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>68882.06</v>
+        <v>68847.35000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>69225.57000000001</v>
+        <v>69093.2</v>
       </c>
       <c r="D36" t="n">
-        <v>68492.03999999999</v>
+        <v>67368.96000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>69220.25</v>
+        <v>67460.73</v>
       </c>
       <c r="F36" t="n">
-        <v>506.45</v>
+        <v>-1759.52</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0254</v>
       </c>
       <c r="H36" t="n">
-        <v>733.53</v>
+        <v>1724.24</v>
       </c>
       <c r="I36" t="n">
-        <v>67334.05</v>
+        <v>67758.50999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>67413.75</v>
+        <v>68667.44</v>
       </c>
       <c r="K36" t="n">
-        <v>68145.25</v>
+        <v>68853.48</v>
       </c>
       <c r="L36" t="n">
-        <v>68876.75</v>
+        <v>69039.53</v>
       </c>
       <c r="M36" t="n">
-        <v>69282.34</v>
+        <v>69587.02</v>
       </c>
       <c r="N36" t="n">
-        <v>69687.94</v>
+        <v>70134.5</v>
       </c>
       <c r="O36" t="n">
-        <v>70745.34</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+        <v>69959.10000000001</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3544,73 +3549,69 @@
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>68847.35000000001</v>
+        <v>66812.27</v>
       </c>
       <c r="C37" t="n">
-        <v>69093.2</v>
+        <v>66833.50999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>67368.96000000001</v>
+        <v>65133.98</v>
       </c>
       <c r="E37" t="n">
-        <v>67460.73</v>
+        <v>65326.42</v>
       </c>
       <c r="F37" t="n">
-        <v>-1759.52</v>
+        <v>-2134.3</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="H37" t="n">
-        <v>1724.24</v>
+        <v>1699.53</v>
       </c>
       <c r="I37" t="n">
-        <v>67758.50999999999</v>
+        <v>65644.72</v>
       </c>
       <c r="J37" t="n">
-        <v>68667.44</v>
+        <v>65351.31</v>
       </c>
       <c r="K37" t="n">
-        <v>68853.48</v>
+        <v>66598.61</v>
       </c>
       <c r="L37" t="n">
-        <v>69039.53</v>
+        <v>67845.89999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>69587.02</v>
+        <v>68322.85000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>70134.5</v>
+        <v>68799.78999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>69959.10000000001</v>
+        <v>70817.45</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -3630,7 +3631,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3640,153 +3641,155 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>66812.27</v>
+        <v>65732.78999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>66833.50999999999</v>
+        <v>66325.32000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>65133.98</v>
+        <v>65652.25</v>
       </c>
       <c r="E38" t="n">
-        <v>65326.42</v>
+        <v>66216.78999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>-2134.3</v>
+        <v>890.37</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H38" t="n">
-        <v>1699.53</v>
+        <v>673.0700000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>65644.72</v>
+        <v>63434.45</v>
       </c>
       <c r="J38" t="n">
-        <v>65351.31</v>
+        <v>63298.23</v>
       </c>
       <c r="K38" t="n">
-        <v>66598.61</v>
+        <v>64476.66</v>
       </c>
       <c r="L38" t="n">
-        <v>67845.89999999999</v>
+        <v>65655.08</v>
       </c>
       <c r="M38" t="n">
-        <v>68322.85000000001</v>
+        <v>66176.19</v>
       </c>
       <c r="N38" t="n">
-        <v>68799.78999999999</v>
+        <v>66697.28999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>70817.45</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
+        <v>68533.03999999999</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>65732.78999999999</v>
+        <v>65427.69</v>
       </c>
       <c r="C39" t="n">
-        <v>66325.32000000001</v>
+        <v>66125.88</v>
       </c>
       <c r="D39" t="n">
-        <v>65652.25</v>
+        <v>65260.22</v>
       </c>
       <c r="E39" t="n">
-        <v>66216.78999999999</v>
+        <v>66016.36</v>
       </c>
       <c r="F39" t="n">
-        <v>890.37</v>
+        <v>-200.43</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.003</v>
       </c>
       <c r="H39" t="n">
-        <v>673.0700000000001</v>
+        <v>865.66</v>
       </c>
       <c r="I39" t="n">
-        <v>63434.45</v>
+        <v>64979.18</v>
       </c>
       <c r="J39" t="n">
-        <v>63298.23</v>
+        <v>65657.72</v>
       </c>
       <c r="K39" t="n">
-        <v>64476.66</v>
+        <v>65880.25</v>
       </c>
       <c r="L39" t="n">
-        <v>65655.08</v>
+        <v>66102.78999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>66176.19</v>
+        <v>66553.32000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>66697.28999999999</v>
+        <v>67003.86</v>
       </c>
       <c r="O39" t="n">
-        <v>68533.03999999999</v>
+        <v>66998.39</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3794,81 +3797,75 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>65427.69</v>
+        <v>65978.95</v>
       </c>
       <c r="C40" t="n">
-        <v>66125.88</v>
+        <v>66257.73</v>
       </c>
       <c r="D40" t="n">
-        <v>65260.22</v>
+        <v>65470.95</v>
       </c>
       <c r="E40" t="n">
-        <v>66016.36</v>
+        <v>65528.09</v>
       </c>
       <c r="F40" t="n">
-        <v>-200.43</v>
+        <v>-488.27</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0074</v>
       </c>
       <c r="H40" t="n">
-        <v>865.66</v>
+        <v>786.78</v>
       </c>
       <c r="I40" t="n">
-        <v>64979.18</v>
+        <v>64394.55</v>
       </c>
       <c r="J40" t="n">
-        <v>65657.72</v>
+        <v>65312.35</v>
       </c>
       <c r="K40" t="n">
-        <v>65880.25</v>
+        <v>65583.53</v>
       </c>
       <c r="L40" t="n">
-        <v>66102.78999999999</v>
+        <v>65854.71000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>66553.32000000001</v>
+        <v>66449.19</v>
       </c>
       <c r="N40" t="n">
-        <v>67003.86</v>
+        <v>67043.67999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>66998.39</v>
+        <v>66991.55</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q40" s="6" t="n">
+        <v/>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3880,157 +3877,161 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>65978.95</v>
+        <v>65195.26</v>
       </c>
       <c r="C41" t="n">
-        <v>66257.73</v>
+        <v>65904.24000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>65470.95</v>
+        <v>64609.47</v>
       </c>
       <c r="E41" t="n">
-        <v>65528.09</v>
+        <v>65856.42999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>-488.27</v>
+        <v>328.34</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.005</v>
       </c>
       <c r="H41" t="n">
-        <v>786.78</v>
+        <v>1294.77</v>
       </c>
       <c r="I41" t="n">
-        <v>64394.55</v>
+        <v>64684.17</v>
       </c>
       <c r="J41" t="n">
-        <v>65312.35</v>
+        <v>64573.19</v>
       </c>
       <c r="K41" t="n">
-        <v>65583.53</v>
+        <v>65134.7</v>
       </c>
       <c r="L41" t="n">
-        <v>65854.71000000001</v>
+        <v>65696.21000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>66449.19</v>
+        <v>65921.48</v>
       </c>
       <c r="N41" t="n">
-        <v>67043.67999999999</v>
+        <v>66146.74000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>66991.55</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
+        <v>67044.5</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>65195.26</v>
+        <v>65604.49000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>65904.24000000001</v>
+        <v>66442.34</v>
       </c>
       <c r="D42" t="n">
-        <v>64609.47</v>
+        <v>65390.55</v>
       </c>
       <c r="E42" t="n">
-        <v>65856.42999999999</v>
+        <v>66262.16</v>
       </c>
       <c r="F42" t="n">
-        <v>328.34</v>
+        <v>405.73</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0062</v>
       </c>
       <c r="H42" t="n">
-        <v>1294.77</v>
+        <v>1051.79</v>
       </c>
       <c r="I42" t="n">
-        <v>64684.17</v>
+        <v>63314.7</v>
       </c>
       <c r="J42" t="n">
-        <v>64573.19</v>
+        <v>64861.44</v>
       </c>
       <c r="K42" t="n">
-        <v>65134.7</v>
+        <v>65209.04</v>
       </c>
       <c r="L42" t="n">
-        <v>65696.21000000001</v>
+        <v>65556.64</v>
       </c>
       <c r="M42" t="n">
-        <v>65921.48</v>
+        <v>66503.82000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>66146.74000000001</v>
+        <v>67450.99000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>67044.5</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67199.02</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
       </c>
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
@@ -4048,64 +4049,64 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>65604.49000000001</v>
+        <v>66775.78</v>
       </c>
       <c r="C43" t="n">
-        <v>66442.34</v>
+        <v>66954.69</v>
       </c>
       <c r="D43" t="n">
-        <v>65390.55</v>
+        <v>65782.59</v>
       </c>
       <c r="E43" t="n">
-        <v>66262.16</v>
+        <v>66131.98</v>
       </c>
       <c r="F43" t="n">
-        <v>405.73</v>
+        <v>-130.18</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.002</v>
       </c>
       <c r="H43" t="n">
-        <v>1051.79</v>
+        <v>1172.09</v>
       </c>
       <c r="I43" t="n">
-        <v>63314.7</v>
+        <v>64338.76</v>
       </c>
       <c r="J43" t="n">
-        <v>64861.44</v>
+        <v>65383.22</v>
       </c>
       <c r="K43" t="n">
-        <v>65209.04</v>
+        <v>65736.25999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>65556.64</v>
+        <v>66089.3</v>
       </c>
       <c r="M43" t="n">
-        <v>66503.82000000001</v>
+        <v>66788.05</v>
       </c>
       <c r="N43" t="n">
-        <v>67450.99000000001</v>
+        <v>67486.8</v>
       </c>
       <c r="O43" t="n">
-        <v>67199.02</v>
+        <v>67494.14</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4118,12 +4119,12 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U43" s="8" t="n">
@@ -4132,64 +4133,64 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>66775.78</v>
+        <v>66104.49000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>66954.69</v>
+        <v>66842.82000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>65782.59</v>
+        <v>66012.2</v>
       </c>
       <c r="E44" t="n">
-        <v>66131.98</v>
+        <v>66405.56</v>
       </c>
       <c r="F44" t="n">
-        <v>-130.18</v>
+        <v>273.59</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0041</v>
       </c>
       <c r="H44" t="n">
-        <v>1172.09</v>
+        <v>830.62</v>
       </c>
       <c r="I44" t="n">
-        <v>64338.76</v>
+        <v>64610.5</v>
       </c>
       <c r="J44" t="n">
-        <v>65383.22</v>
+        <v>64841.55</v>
       </c>
       <c r="K44" t="n">
-        <v>65736.25999999999</v>
+        <v>65545.92999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>66089.3</v>
+        <v>66250.31</v>
       </c>
       <c r="M44" t="n">
-        <v>66788.05</v>
+        <v>66718.02</v>
       </c>
       <c r="N44" t="n">
-        <v>67486.8</v>
+        <v>67185.74000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>67494.14</v>
+        <v>68126.78</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4216,7 +4217,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4230,69 +4231,73 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>66104.49000000001</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C45" t="n">
-        <v>66842.82000000001</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>66012.2</v>
+        <v>64832.1</v>
       </c>
       <c r="E45" t="n">
-        <v>66405.56</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>273.59</v>
+        <v>-93.63</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0014</v>
       </c>
       <c r="H45" t="n">
-        <v>830.62</v>
+        <v>1479.83</v>
       </c>
       <c r="I45" t="n">
-        <v>64610.5</v>
+        <v>65181.59</v>
       </c>
       <c r="J45" t="n">
-        <v>64841.55</v>
+        <v>65563.97</v>
       </c>
       <c r="K45" t="n">
-        <v>65545.92999999999</v>
+        <v>65990.25</v>
       </c>
       <c r="L45" t="n">
-        <v>66250.31</v>
+        <v>66416.53999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>66718.02</v>
+        <v>66820.87</v>
       </c>
       <c r="N45" t="n">
-        <v>67185.74000000001</v>
+        <v>67225.21000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>68126.78</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67673.44</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4300,83 +4305,73 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>65668.50999999999</v>
+        <v>65885.47</v>
       </c>
       <c r="C46" t="n">
-        <v>66311.92999999999</v>
+        <v>66525.7</v>
       </c>
       <c r="D46" t="n">
-        <v>64832.1</v>
+        <v>65576.61</v>
       </c>
       <c r="E46" t="n">
-        <v>66311.92999999999</v>
+        <v>66215.34</v>
       </c>
       <c r="F46" t="n">
-        <v>-93.63</v>
+        <v>-96.59</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0015</v>
       </c>
       <c r="H46" t="n">
-        <v>1479.83</v>
+        <v>949.09</v>
       </c>
       <c r="I46" t="n">
-        <v>65181.59</v>
+        <v>63352.27</v>
       </c>
       <c r="J46" t="n">
-        <v>65563.97</v>
+        <v>65202.06</v>
       </c>
       <c r="K46" t="n">
-        <v>65990.25</v>
+        <v>65572.02</v>
       </c>
       <c r="L46" t="n">
-        <v>66416.53999999999</v>
+        <v>65941.97</v>
       </c>
       <c r="M46" t="n">
-        <v>66820.87</v>
+        <v>67051.84</v>
       </c>
       <c r="N46" t="n">
-        <v>67225.21000000001</v>
+        <v>68161.71000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>67673.44</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>67791.75999999999</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4388,73 +4383,83 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65885.47</v>
+        <v>65195.43</v>
       </c>
       <c r="C47" t="n">
-        <v>66525.7</v>
+        <v>65195.43</v>
       </c>
       <c r="D47" t="n">
-        <v>65576.61</v>
+        <v>64215.47</v>
       </c>
       <c r="E47" t="n">
-        <v>66215.34</v>
+        <v>64325.64</v>
       </c>
       <c r="F47" t="n">
-        <v>-96.59</v>
+        <v>-1889.7</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0285</v>
       </c>
       <c r="H47" t="n">
-        <v>949.09</v>
+        <v>979.96</v>
       </c>
       <c r="I47" t="n">
-        <v>63352.27</v>
+        <v>64627.52</v>
       </c>
       <c r="J47" t="n">
-        <v>65202.06</v>
+        <v>65348.34</v>
       </c>
       <c r="K47" t="n">
-        <v>65572.02</v>
+        <v>65740.8</v>
       </c>
       <c r="L47" t="n">
-        <v>65941.97</v>
+        <v>66133.25</v>
       </c>
       <c r="M47" t="n">
-        <v>67051.84</v>
+        <v>66689.89</v>
       </c>
       <c r="N47" t="n">
-        <v>68161.71000000001</v>
+        <v>67246.53</v>
       </c>
       <c r="O47" t="n">
-        <v>67791.75999999999</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>67474.8</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4466,74 +4471,66 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="C48" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="D48" t="n">
-        <v>64215.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E48" t="n">
-        <v>64325.64</v>
+        <v>64214.48</v>
       </c>
       <c r="F48" t="n">
-        <v>-1889.7</v>
+        <v>-111.16</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0017</v>
       </c>
       <c r="H48" t="n">
-        <v>979.96</v>
+        <v>952.01</v>
       </c>
       <c r="I48" t="n">
-        <v>64627.52</v>
+        <v>63235.51</v>
       </c>
       <c r="J48" t="n">
-        <v>65348.34</v>
+        <v>63155.78</v>
       </c>
       <c r="K48" t="n">
-        <v>65740.8</v>
+        <v>63835.66</v>
       </c>
       <c r="L48" t="n">
-        <v>66133.25</v>
+        <v>64515.54</v>
       </c>
       <c r="M48" t="n">
-        <v>66689.89</v>
+        <v>64815.62</v>
       </c>
       <c r="N48" t="n">
-        <v>67246.53</v>
+        <v>65115.7</v>
       </c>
       <c r="O48" t="n">
-        <v>67474.8</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66175.39</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
@@ -4542,7 +4539,7 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4554,7 +4551,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4564,50 +4561,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>64724.81</v>
+        <v>64498.94</v>
       </c>
       <c r="C49" t="n">
-        <v>64724.81</v>
+        <v>65182.45</v>
       </c>
       <c r="D49" t="n">
-        <v>63772.8</v>
+        <v>64228.47</v>
       </c>
       <c r="E49" t="n">
-        <v>64214.48</v>
+        <v>65020.94</v>
       </c>
       <c r="F49" t="n">
-        <v>-111.16</v>
+        <v>806.46</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="H49" t="n">
-        <v>952.01</v>
+        <v>953.98</v>
       </c>
       <c r="I49" t="n">
-        <v>63235.51</v>
+        <v>62820.79</v>
       </c>
       <c r="J49" t="n">
-        <v>63155.78</v>
+        <v>63245.31</v>
       </c>
       <c r="K49" t="n">
-        <v>63835.66</v>
+        <v>63738.48</v>
       </c>
       <c r="L49" t="n">
-        <v>64515.54</v>
+        <v>64231.64</v>
       </c>
       <c r="M49" t="n">
-        <v>64815.62</v>
+        <v>64690.48</v>
       </c>
       <c r="N49" t="n">
-        <v>65115.7</v>
+        <v>65149.33</v>
       </c>
       <c r="O49" t="n">
-        <v>66175.39</v>
+        <v>65676.82000000001</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4615,79 +4612,85 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>64498.94</v>
+        <v>65600.42</v>
       </c>
       <c r="C50" t="n">
-        <v>65182.45</v>
+        <v>66668.71000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>64228.47</v>
+        <v>65600.42</v>
       </c>
       <c r="E50" t="n">
-        <v>65020.94</v>
+        <v>66399.84</v>
       </c>
       <c r="F50" t="n">
-        <v>806.46</v>
+        <v>1378.9</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="H50" t="n">
-        <v>953.98</v>
+        <v>1068.29</v>
       </c>
       <c r="I50" t="n">
-        <v>62820.79</v>
+        <v>63274.49</v>
       </c>
       <c r="J50" t="n">
-        <v>63245.31</v>
+        <v>64224.7</v>
       </c>
       <c r="K50" t="n">
-        <v>63738.48</v>
+        <v>64543.95</v>
       </c>
       <c r="L50" t="n">
-        <v>64231.64</v>
+        <v>64863.2</v>
       </c>
       <c r="M50" t="n">
-        <v>64690.48</v>
+        <v>65497.93</v>
       </c>
       <c r="N50" t="n">
-        <v>65149.33</v>
+        <v>66132.66</v>
       </c>
       <c r="O50" t="n">
-        <v>65676.82000000001</v>
+        <v>66136.42999999999</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4710,171 +4713,167 @@
       </c>
       <c r="U50" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65600.42</v>
+        <v>65843.69</v>
       </c>
       <c r="C51" t="n">
-        <v>66668.71000000001</v>
+        <v>66791.84</v>
       </c>
       <c r="D51" t="n">
-        <v>65600.42</v>
+        <v>65269.33</v>
       </c>
       <c r="E51" t="n">
-        <v>66399.84</v>
+        <v>65269.33</v>
       </c>
       <c r="F51" t="n">
-        <v>1378.9</v>
+        <v>-1130.52</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.017</v>
       </c>
       <c r="H51" t="n">
-        <v>1068.29</v>
+        <v>1522.52</v>
       </c>
       <c r="I51" t="n">
-        <v>63274.49</v>
+        <v>64532.13</v>
       </c>
       <c r="J51" t="n">
-        <v>64224.7</v>
+        <v>65464.19</v>
       </c>
       <c r="K51" t="n">
-        <v>64543.95</v>
+        <v>65865.7</v>
       </c>
       <c r="L51" t="n">
-        <v>64863.2</v>
+        <v>66267.21000000001</v>
       </c>
       <c r="M51" t="n">
-        <v>65497.93</v>
+        <v>66933.99000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>66132.66</v>
+        <v>67600.77</v>
       </c>
       <c r="O51" t="n">
-        <v>66136.42999999999</v>
+        <v>67737</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
+      <c r="Q51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
+      </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>65843.69</v>
+        <v>65087.22</v>
       </c>
       <c r="C52" t="n">
-        <v>66791.84</v>
+        <v>65794.03</v>
       </c>
       <c r="D52" t="n">
-        <v>65269.33</v>
+        <v>65017.68</v>
       </c>
       <c r="E52" t="n">
-        <v>65269.33</v>
+        <v>65142.78</v>
       </c>
       <c r="F52" t="n">
-        <v>-1130.52</v>
+        <v>-126.55</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0019</v>
       </c>
       <c r="H52" t="n">
-        <v>1522.52</v>
+        <v>776.35</v>
       </c>
       <c r="I52" t="n">
-        <v>64532.13</v>
+        <v>63746.81</v>
       </c>
       <c r="J52" t="n">
-        <v>65464.19</v>
+        <v>63366.18</v>
       </c>
       <c r="K52" t="n">
-        <v>65865.7</v>
+        <v>64508.07</v>
       </c>
       <c r="L52" t="n">
-        <v>66267.21000000001</v>
+        <v>65649.96000000001</v>
       </c>
       <c r="M52" t="n">
-        <v>66933.99000000001</v>
+        <v>66030.59</v>
       </c>
       <c r="N52" t="n">
-        <v>67600.77</v>
+        <v>66411.21000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>67737</v>
+        <v>68314.36</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4886,73 +4885,75 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65087.22</v>
+        <v>64768.53</v>
       </c>
       <c r="C53" t="n">
-        <v>65794.03</v>
+        <v>65270.95</v>
       </c>
       <c r="D53" t="n">
-        <v>65017.68</v>
+        <v>64186.68</v>
       </c>
       <c r="E53" t="n">
-        <v>65142.78</v>
+        <v>65270.95</v>
       </c>
       <c r="F53" t="n">
-        <v>-126.55</v>
+        <v>128.17</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="H53" t="n">
-        <v>776.35</v>
+        <v>1084.27</v>
       </c>
       <c r="I53" t="n">
-        <v>63746.81</v>
+        <v>64241.33</v>
       </c>
       <c r="J53" t="n">
-        <v>63366.18</v>
+        <v>64234.89</v>
       </c>
       <c r="K53" t="n">
-        <v>64508.07</v>
+        <v>64754.61</v>
       </c>
       <c r="L53" t="n">
-        <v>65649.96000000001</v>
+        <v>65274.32</v>
       </c>
       <c r="M53" t="n">
-        <v>66030.59</v>
+        <v>65530.96</v>
       </c>
       <c r="N53" t="n">
-        <v>66411.21000000001</v>
+        <v>65787.60000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>68314.36</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+        <v>66570.38</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
@@ -4968,69 +4969,71 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>64768.53</v>
+        <v>64276.82</v>
       </c>
       <c r="C54" t="n">
-        <v>65270.95</v>
+        <v>64312.02</v>
       </c>
       <c r="D54" t="n">
-        <v>64186.68</v>
+        <v>63208.63</v>
       </c>
       <c r="E54" t="n">
-        <v>65270.95</v>
+        <v>64011.34</v>
       </c>
       <c r="F54" t="n">
-        <v>128.17</v>
+        <v>-1259.61</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H54" t="n">
-        <v>1084.27</v>
+        <v>1103.39</v>
       </c>
       <c r="I54" t="n">
-        <v>64241.33</v>
+        <v>63102.41</v>
       </c>
       <c r="J54" t="n">
-        <v>64234.89</v>
+        <v>64457.75</v>
       </c>
       <c r="K54" t="n">
-        <v>64754.61</v>
+        <v>64728.81</v>
       </c>
       <c r="L54" t="n">
-        <v>65274.32</v>
+        <v>64999.88</v>
       </c>
       <c r="M54" t="n">
-        <v>65530.96</v>
+        <v>65813.08</v>
       </c>
       <c r="N54" t="n">
-        <v>65787.60000000001</v>
+        <v>66626.28999999999</v>
       </c>
       <c r="O54" t="n">
-        <v>66570.38</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66355.22</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
@@ -5040,7 +5043,7 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5052,78 +5055,74 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>64276.82</v>
+        <v>63659.53</v>
       </c>
       <c r="C55" t="n">
-        <v>64312.02</v>
+        <v>63691.53</v>
       </c>
       <c r="D55" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E55" t="n">
-        <v>64011.34</v>
+        <v>63492.99</v>
       </c>
       <c r="F55" t="n">
-        <v>-1259.61</v>
+        <v>-518.35</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0081</v>
       </c>
       <c r="H55" t="n">
-        <v>1103.39</v>
+        <v>965.35</v>
       </c>
       <c r="I55" t="n">
-        <v>63102.41</v>
+        <v>62105.24</v>
       </c>
       <c r="J55" t="n">
-        <v>64457.75</v>
+        <v>63033.46</v>
       </c>
       <c r="K55" t="n">
-        <v>64728.81</v>
+        <v>63459.64</v>
       </c>
       <c r="L55" t="n">
-        <v>64999.88</v>
+        <v>63885.83</v>
       </c>
       <c r="M55" t="n">
-        <v>65813.08</v>
+        <v>64563.04</v>
       </c>
       <c r="N55" t="n">
-        <v>66626.28999999999</v>
+        <v>65240.24</v>
       </c>
       <c r="O55" t="n">
-        <v>66355.22</v>
+        <v>65415.41</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5138,7 +5137,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5148,71 +5147,69 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63659.53</v>
+        <v>63190.37</v>
       </c>
       <c r="C56" t="n">
-        <v>63691.53</v>
+        <v>64101</v>
       </c>
       <c r="D56" t="n">
-        <v>62726.18</v>
+        <v>63067.18</v>
       </c>
       <c r="E56" t="n">
-        <v>63492.99</v>
+        <v>63484.1</v>
       </c>
       <c r="F56" t="n">
-        <v>-518.35</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0001</v>
       </c>
       <c r="H56" t="n">
-        <v>965.35</v>
+        <v>1033.82</v>
       </c>
       <c r="I56" t="n">
-        <v>62105.24</v>
+        <v>61760.83</v>
       </c>
       <c r="J56" t="n">
-        <v>63033.46</v>
+        <v>62669.7</v>
       </c>
       <c r="K56" t="n">
-        <v>63459.64</v>
+        <v>63010.31</v>
       </c>
       <c r="L56" t="n">
-        <v>63885.83</v>
+        <v>63350.92</v>
       </c>
       <c r="M56" t="n">
-        <v>64563.04</v>
+        <v>63975.66</v>
       </c>
       <c r="N56" t="n">
-        <v>65240.24</v>
+        <v>64600.41</v>
       </c>
       <c r="O56" t="n">
-        <v>65415.41</v>
+        <v>64656.88</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5220,60 +5217,64 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>63190.37</v>
+        <v>63672.13</v>
       </c>
       <c r="C57" t="n">
-        <v>64101</v>
+        <v>63923</v>
       </c>
       <c r="D57" t="n">
-        <v>63067.18</v>
+        <v>63209.92</v>
       </c>
       <c r="E57" t="n">
-        <v>63484.1</v>
+        <v>63923</v>
       </c>
       <c r="F57" t="n">
-        <v>-8.890000000000001</v>
+        <v>438.9</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0069</v>
       </c>
       <c r="H57" t="n">
-        <v>1033.82</v>
+        <v>713.08</v>
       </c>
       <c r="I57" t="n">
-        <v>61760.83</v>
+        <v>62033.36</v>
       </c>
       <c r="J57" t="n">
-        <v>62669.7</v>
+        <v>62400.29</v>
       </c>
       <c r="K57" t="n">
-        <v>63010.31</v>
+        <v>62967.19</v>
       </c>
       <c r="L57" t="n">
-        <v>63350.92</v>
+        <v>63534.1</v>
       </c>
       <c r="M57" t="n">
-        <v>63975.66</v>
+        <v>64001.01</v>
       </c>
       <c r="N57" t="n">
-        <v>64600.41</v>
+        <v>64467.93</v>
       </c>
       <c r="O57" t="n">
-        <v>64656.88</v>
+        <v>65134.82</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5286,12 +5287,12 @@
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U57" s="8" t="n">
@@ -5300,7 +5301,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5314,50 +5315,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>63672.13</v>
+        <v>64643.58</v>
       </c>
       <c r="C58" t="n">
-        <v>63923</v>
+        <v>64643.58</v>
       </c>
       <c r="D58" t="n">
-        <v>63209.92</v>
+        <v>63824.56</v>
       </c>
       <c r="E58" t="n">
-        <v>63923</v>
+        <v>64136.25</v>
       </c>
       <c r="F58" t="n">
-        <v>438.9</v>
+        <v>213.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0033</v>
       </c>
       <c r="H58" t="n">
-        <v>713.08</v>
+        <v>819.02</v>
       </c>
       <c r="I58" t="n">
-        <v>62033.36</v>
+        <v>62496.84</v>
       </c>
       <c r="J58" t="n">
-        <v>62400.29</v>
+        <v>63388.19</v>
       </c>
       <c r="K58" t="n">
-        <v>62967.19</v>
+        <v>63566.46</v>
       </c>
       <c r="L58" t="n">
-        <v>63534.1</v>
+        <v>63744.73</v>
       </c>
       <c r="M58" t="n">
-        <v>64001.01</v>
+        <v>64279.54</v>
       </c>
       <c r="N58" t="n">
-        <v>64467.93</v>
+        <v>64814.35</v>
       </c>
       <c r="O58" t="n">
-        <v>65134.82</v>
+        <v>64636.08</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5381,67 +5382,69 @@
       <c r="U58" s="8" t="n">
         <v/>
       </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="V58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>64643.58</v>
+        <v>64681.55</v>
       </c>
       <c r="C59" t="n">
-        <v>64643.58</v>
+        <v>65436.57</v>
       </c>
       <c r="D59" t="n">
-        <v>63824.56</v>
+        <v>64403.85</v>
       </c>
       <c r="E59" t="n">
-        <v>64136.25</v>
+        <v>65018.95</v>
       </c>
       <c r="F59" t="n">
-        <v>213.25</v>
+        <v>882.7</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0138</v>
       </c>
       <c r="H59" t="n">
-        <v>819.02</v>
+        <v>1032.72</v>
       </c>
       <c r="I59" t="n">
-        <v>62496.84</v>
+        <v>63005.54</v>
       </c>
       <c r="J59" t="n">
-        <v>63388.19</v>
+        <v>63268.32</v>
       </c>
       <c r="K59" t="n">
-        <v>63566.46</v>
+        <v>63726.74</v>
       </c>
       <c r="L59" t="n">
-        <v>63744.73</v>
+        <v>64185.16</v>
       </c>
       <c r="M59" t="n">
-        <v>64279.54</v>
+        <v>64545.76</v>
       </c>
       <c r="N59" t="n">
-        <v>64814.35</v>
+        <v>64906.36</v>
       </c>
       <c r="O59" t="n">
-        <v>64636.08</v>
+        <v>65462.6</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5459,78 +5462,76 @@
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V59" s="8" t="n">
+        <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>64681.55</v>
+        <v>65476.44</v>
       </c>
       <c r="C60" t="n">
-        <v>65436.57</v>
+        <v>66249.11</v>
       </c>
       <c r="D60" t="n">
-        <v>64403.85</v>
+        <v>65407.37</v>
       </c>
       <c r="E60" t="n">
-        <v>65018.95</v>
+        <v/>
       </c>
       <c r="F60" t="n">
-        <v>882.7</v>
+        <v/>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0138</v>
+        <v/>
       </c>
       <c r="H60" t="n">
-        <v>1032.72</v>
+        <v>841.74</v>
       </c>
       <c r="I60" t="n">
-        <v>63005.54</v>
+        <v>63371.13</v>
       </c>
       <c r="J60" t="n">
-        <v>63268.32</v>
+        <v>64035.6</v>
       </c>
       <c r="K60" t="n">
-        <v>63726.74</v>
+        <v>64502.59</v>
       </c>
       <c r="L60" t="n">
-        <v>64185.16</v>
+        <v>64969.58</v>
       </c>
       <c r="M60" t="n">
-        <v>64545.76</v>
+        <v>65535.31</v>
       </c>
       <c r="N60" t="n">
-        <v>64906.36</v>
+        <v>66101.03999999999</v>
       </c>
       <c r="O60" t="n">
-        <v>65462.6</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
+        <v>66469.28999999999</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q60" s="6" t="n">
         <v/>
@@ -5538,9 +5539,9 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S60" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
@@ -5550,13 +5551,13 @@
       </c>
       <c r="U60" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,20 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -637,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69609.88</v>
+        <v>70085.60000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>69609.88</v>
+        <v>70667</v>
       </c>
       <c r="D2" t="n">
-        <v>67997.57000000001</v>
+        <v>69302.19</v>
       </c>
       <c r="E2" t="n">
-        <v>69468.11</v>
+        <v>70062.32000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>107.23</v>
+        <v>594.21</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0086</v>
       </c>
       <c r="H2" t="n">
-        <v>1612.31</v>
+        <v>1364.81</v>
       </c>
       <c r="I2" t="n">
-        <v>65493.41</v>
+        <v>66385.25999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>65788.36</v>
+        <v>68187.99000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>67787.66</v>
+        <v>68661.95</v>
       </c>
       <c r="L2" t="n">
-        <v>69786.97</v>
+        <v>69135.92</v>
       </c>
       <c r="M2" t="n">
-        <v>70934.10000000001</v>
+        <v>70274.27</v>
       </c>
       <c r="N2" t="n">
-        <v>72081.23</v>
+        <v>71412.61</v>
       </c>
       <c r="O2" t="n">
-        <v>74932.72</v>
+        <v>71222.2</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -693,11 +690,13 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -710,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70085.60000000001</v>
+        <v>70774.28</v>
       </c>
       <c r="C3" t="n">
-        <v>70667</v>
+        <v>71962.34</v>
       </c>
       <c r="D3" t="n">
-        <v>69302.19</v>
+        <v>70126.14</v>
       </c>
       <c r="E3" t="n">
-        <v>70062.32000000001</v>
+        <v>70474.96000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>594.21</v>
+        <v>412.64</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0059</v>
       </c>
       <c r="H3" t="n">
-        <v>1364.81</v>
+        <v>1836.2</v>
       </c>
       <c r="I3" t="n">
-        <v>66385.25999999999</v>
+        <v>67937.38</v>
       </c>
       <c r="J3" t="n">
-        <v>68187.99000000001</v>
+        <v>68736.37</v>
       </c>
       <c r="K3" t="n">
-        <v>68661.95</v>
+        <v>69379.91</v>
       </c>
       <c r="L3" t="n">
-        <v>69135.92</v>
+        <v>70023.46000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>70274.27</v>
+        <v>70744.73</v>
       </c>
       <c r="N3" t="n">
-        <v>71412.61</v>
+        <v>71466</v>
       </c>
       <c r="O3" t="n">
-        <v>71222.2</v>
+        <v>72031.81</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,7 +768,7 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -783,8 +778,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="8" t="n">
-        <v/>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -799,74 +796,74 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70774.28</v>
+        <v>70039.89</v>
       </c>
       <c r="C4" t="n">
-        <v>71962.34</v>
+        <v>70081.39</v>
       </c>
       <c r="D4" t="n">
-        <v>70126.14</v>
+        <v>68676.25999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>70474.96000000001</v>
+        <v>68733.14999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>412.64</v>
+        <v>-1741.81</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0247</v>
       </c>
       <c r="H4" t="n">
-        <v>1836.2</v>
+        <v>1405.13</v>
       </c>
       <c r="I4" t="n">
-        <v>67937.38</v>
+        <v>68289.94</v>
       </c>
       <c r="J4" t="n">
-        <v>68736.37</v>
+        <v>68354.12</v>
       </c>
       <c r="K4" t="n">
-        <v>69379.91</v>
+        <v>69556.86</v>
       </c>
       <c r="L4" t="n">
-        <v>70023.46000000001</v>
+        <v>70759.60000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>70744.73</v>
+        <v>71393.06</v>
       </c>
       <c r="N4" t="n">
-        <v>71466</v>
+        <v>72026.52</v>
       </c>
       <c r="O4" t="n">
-        <v>72031.81</v>
+        <v>73798.55</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -876,80 +873,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70039.89</v>
+        <v>68676.06</v>
       </c>
       <c r="C5" t="n">
-        <v>70081.39</v>
+        <v>69788.03</v>
       </c>
       <c r="D5" t="n">
-        <v>68676.25999999999</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>68733.14999999999</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1741.81</v>
+        <v>1010.92</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0147</v>
       </c>
       <c r="H5" t="n">
-        <v>1405.13</v>
+        <v>2178.54</v>
       </c>
       <c r="I5" t="n">
-        <v>68289.94</v>
+        <v>67271.12</v>
       </c>
       <c r="J5" t="n">
-        <v>68354.12</v>
+        <v>67005.17999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>69556.86</v>
+        <v>68030.58</v>
       </c>
       <c r="L5" t="n">
-        <v>70759.60000000001</v>
+        <v>69055.99000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>71393.06</v>
+        <v>69435.71000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>72026.52</v>
+        <v>69815.44</v>
       </c>
       <c r="O5" t="n">
-        <v>73798.55</v>
+        <v>71486.52</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
@@ -960,57 +963,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68676.06</v>
+        <v>69973.34</v>
       </c>
       <c r="C6" t="n">
-        <v>69788.03</v>
+        <v>70384.59</v>
       </c>
       <c r="D6" t="n">
-        <v>67609.49000000001</v>
+        <v>68904.41</v>
       </c>
       <c r="E6" t="n">
-        <v>69744.07000000001</v>
+        <v>69737.69</v>
       </c>
       <c r="F6" t="n">
-        <v>1010.92</v>
+        <v>-6.38</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0001</v>
       </c>
       <c r="H6" t="n">
-        <v>2178.54</v>
+        <v>1480.19</v>
       </c>
       <c r="I6" t="n">
-        <v>67271.12</v>
+        <v>65430.95</v>
       </c>
       <c r="J6" t="n">
-        <v>67005.17999999999</v>
+        <v>68088.19</v>
       </c>
       <c r="K6" t="n">
-        <v>68030.58</v>
+        <v>68654.8</v>
       </c>
       <c r="L6" t="n">
-        <v>69055.99000000001</v>
+        <v>69221.42</v>
       </c>
       <c r="M6" t="n">
-        <v>69435.71000000001</v>
+        <v>70833.34</v>
       </c>
       <c r="N6" t="n">
-        <v>69815.44</v>
+        <v>72445.25999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>71486.52</v>
+        <v>71966.57000000001</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1018,25 +1021,19 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1048,70 +1045,74 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69973.34</v>
+        <v>69460.08</v>
       </c>
       <c r="C7" t="n">
-        <v>70384.59</v>
+        <v>69957.50999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>68904.41</v>
+        <v>68003.92</v>
       </c>
       <c r="E7" t="n">
-        <v>69737.69</v>
+        <v>68256.96000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.38</v>
+        <v>-1480.73</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0212</v>
       </c>
       <c r="H7" t="n">
-        <v>1480.19</v>
+        <v>1953.59</v>
       </c>
       <c r="I7" t="n">
-        <v>65430.95</v>
+        <v>67424.22</v>
       </c>
       <c r="J7" t="n">
-        <v>68088.19</v>
+        <v>68304.09</v>
       </c>
       <c r="K7" t="n">
-        <v>68654.8</v>
+        <v>68997.59</v>
       </c>
       <c r="L7" t="n">
-        <v>69221.42</v>
+        <v>69691.09</v>
       </c>
       <c r="M7" t="n">
-        <v>70833.34</v>
+        <v>70477.78</v>
       </c>
       <c r="N7" t="n">
-        <v>72445.25999999999</v>
+        <v>71264.47</v>
       </c>
       <c r="O7" t="n">
-        <v>71966.57000000001</v>
+        <v>71864.78</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1123,79 +1124,73 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69460.08</v>
+        <v>67704.16</v>
       </c>
       <c r="C8" t="n">
-        <v>69957.50999999999</v>
+        <v>68432.67999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>68003.92</v>
+        <v>66819.05</v>
       </c>
       <c r="E8" t="n">
-        <v>68256.96000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="F8" t="n">
-        <v>-1480.73</v>
+        <v>-1437.91</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="H8" t="n">
-        <v>1953.59</v>
+        <v>1613.63</v>
       </c>
       <c r="I8" t="n">
-        <v>67424.22</v>
+        <v>66050.34</v>
       </c>
       <c r="J8" t="n">
-        <v>68304.09</v>
+        <v>65941.5</v>
       </c>
       <c r="K8" t="n">
-        <v>68997.59</v>
+        <v>67280.17</v>
       </c>
       <c r="L8" t="n">
-        <v>69691.09</v>
+        <v>68618.84</v>
       </c>
       <c r="M8" t="n">
-        <v>70477.78</v>
+        <v>69233.75</v>
       </c>
       <c r="N8" t="n">
-        <v>71264.47</v>
+        <v>69848.67</v>
       </c>
       <c r="O8" t="n">
-        <v>71864.78</v>
+        <v>71911.09</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1219,50 +1214,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67704.16</v>
+        <v>67046.37</v>
       </c>
       <c r="C9" t="n">
-        <v>68432.67999999999</v>
+        <v>68447.89</v>
       </c>
       <c r="D9" t="n">
-        <v>66819.05</v>
+        <v>67008.89</v>
       </c>
       <c r="E9" t="n">
-        <v>66819.05</v>
+        <v>67743.85000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-1437.91</v>
+        <v>924.8</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0211</v>
+        <v>0.0138</v>
       </c>
       <c r="H9" t="n">
-        <v>1613.63</v>
+        <v>1439</v>
       </c>
       <c r="I9" t="n">
-        <v>66050.34</v>
+        <v>65205.41</v>
       </c>
       <c r="J9" t="n">
-        <v>65941.5</v>
+        <v>64802.01</v>
       </c>
       <c r="K9" t="n">
-        <v>67280.17</v>
+        <v>66012.23</v>
       </c>
       <c r="L9" t="n">
-        <v>68618.84</v>
+        <v>67222.46000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>69233.75</v>
+        <v>67625.86</v>
       </c>
       <c r="N9" t="n">
-        <v>69848.67</v>
+        <v>68029.27</v>
       </c>
       <c r="O9" t="n">
-        <v>71911.09</v>
+        <v>70046.31</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1270,21 +1265,23 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1294,55 +1291,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>67046.37</v>
+        <v>68526.72</v>
       </c>
       <c r="C10" t="n">
-        <v>68447.89</v>
+        <v>69374.86</v>
       </c>
       <c r="D10" t="n">
-        <v>67008.89</v>
+        <v>68271.91</v>
       </c>
       <c r="E10" t="n">
-        <v>67743.85000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F10" t="n">
-        <v>924.8</v>
+        <v>813.88</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.012</v>
       </c>
       <c r="H10" t="n">
-        <v>1439</v>
+        <v>1102.95</v>
       </c>
       <c r="I10" t="n">
-        <v>65205.41</v>
+        <v>65569.89</v>
       </c>
       <c r="J10" t="n">
-        <v>64802.01</v>
+        <v>66312.58</v>
       </c>
       <c r="K10" t="n">
-        <v>66012.23</v>
+        <v>67024.35000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>67222.46000000001</v>
+        <v>67736.12</v>
       </c>
       <c r="M10" t="n">
-        <v>67625.86</v>
+        <v>68463.35000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>68029.27</v>
+        <v>69190.58</v>
       </c>
       <c r="O10" t="n">
-        <v>70046.31</v>
+        <v>69886.89</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1353,7 +1354,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1385,74 +1386,76 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>68526.72</v>
+        <v>68410.63</v>
       </c>
       <c r="C11" t="n">
-        <v>69374.86</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>68271.91</v>
+        <v>66653.11</v>
       </c>
       <c r="E11" t="n">
-        <v>68557.73</v>
+        <v>67242.73</v>
       </c>
       <c r="F11" t="n">
-        <v>813.88</v>
+        <v>-1315</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0192</v>
       </c>
       <c r="H11" t="n">
-        <v>1102.95</v>
+        <v>2425.1</v>
       </c>
       <c r="I11" t="n">
-        <v>65569.89</v>
+        <v>67168.95</v>
       </c>
       <c r="J11" t="n">
-        <v>66312.58</v>
+        <v>67321.95</v>
       </c>
       <c r="K11" t="n">
-        <v>67024.35000000001</v>
+        <v>68006.25</v>
       </c>
       <c r="L11" t="n">
-        <v>67736.12</v>
+        <v>68690.55</v>
       </c>
       <c r="M11" t="n">
-        <v>68463.35000000001</v>
+        <v>69109.2</v>
       </c>
       <c r="N11" t="n">
-        <v>69190.58</v>
+        <v>69527.85000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>69886.89</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+        <v>70477.81</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1462,78 +1465,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>68410.63</v>
+        <v>67002.94</v>
       </c>
       <c r="C12" t="n">
-        <v>69078.21000000001</v>
+        <v>67800.17999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>66653.11</v>
+        <v>66268.60000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>67242.73</v>
+        <v>67743.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-1315</v>
+        <v>500.77</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0074</v>
       </c>
       <c r="H12" t="n">
-        <v>2425.1</v>
+        <v>1531.58</v>
       </c>
       <c r="I12" t="n">
-        <v>67168.95</v>
+        <v>64228.01</v>
       </c>
       <c r="J12" t="n">
-        <v>67321.95</v>
+        <v>64506.16</v>
       </c>
       <c r="K12" t="n">
-        <v>68006.25</v>
+        <v>66030.17999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>68690.55</v>
+        <v>67554.19</v>
       </c>
       <c r="M12" t="n">
-        <v>69109.2</v>
+        <v>68455.28</v>
       </c>
       <c r="N12" t="n">
-        <v>69527.85000000001</v>
+        <v>69356.36</v>
       </c>
       <c r="O12" t="n">
-        <v>70477.81</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>71503.31</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1550,55 +1543,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67002.94</v>
+        <v>67989.74000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>67800.17999999999</v>
+        <v>68798.24000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>66268.60000000001</v>
+        <v>67833.17</v>
       </c>
       <c r="E13" t="n">
-        <v>67743.5</v>
+        <v>68751.50999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>500.77</v>
+        <v>1008.01</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0149</v>
       </c>
       <c r="H13" t="n">
-        <v>1531.58</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>64228.01</v>
+        <v>64737.02</v>
       </c>
       <c r="J13" t="n">
-        <v>64506.16</v>
+        <v>66566.48</v>
       </c>
       <c r="K13" t="n">
-        <v>66030.17999999999</v>
+        <v>66977.71000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>67554.19</v>
+        <v>67388.95</v>
       </c>
       <c r="M13" t="n">
-        <v>68455.28</v>
+        <v>68509.28999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>69356.36</v>
+        <v>69629.63</v>
       </c>
       <c r="O13" t="n">
-        <v>71503.31</v>
+        <v>69331.75999999999</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1609,13 +1606,15 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1630,76 +1629,80 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>67989.74000000001</v>
+        <v>67900.42999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>68798.24000000001</v>
+        <v>68069.82000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>67833.17</v>
+        <v>66499.49000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>68751.50999999999</v>
+        <v>66835.53999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1008.01</v>
+        <v>-1915.97</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0279</v>
       </c>
       <c r="H14" t="n">
-        <v>965.0700000000001</v>
+        <v>1570.33</v>
       </c>
       <c r="I14" t="n">
-        <v>64737.02</v>
+        <v>66868.10000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>66566.48</v>
+        <v>68004.34</v>
       </c>
       <c r="K14" t="n">
-        <v>66977.71000000001</v>
+        <v>68268.97</v>
       </c>
       <c r="L14" t="n">
-        <v>67388.95</v>
+        <v>68533.61</v>
       </c>
       <c r="M14" t="n">
-        <v>68509.28999999999</v>
+        <v>69234.03999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>69629.63</v>
+        <v>69934.48</v>
       </c>
       <c r="O14" t="n">
-        <v>69331.75999999999</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+        <v>69763.31</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1712,59 +1715,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67900.42999999999</v>
+        <v>66339.85000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>68069.82000000001</v>
+        <v>66441.77</v>
       </c>
       <c r="D15" t="n">
-        <v>66499.49000000001</v>
+        <v>62704.6</v>
       </c>
       <c r="E15" t="n">
-        <v>66835.53999999999</v>
+        <v>64141.12</v>
       </c>
       <c r="F15" t="n">
-        <v>-1915.97</v>
+        <v>-2694.42</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0403</v>
       </c>
       <c r="H15" t="n">
-        <v>1570.33</v>
+        <v>3737.17</v>
       </c>
       <c r="I15" t="n">
-        <v>66868.10000000001</v>
+        <v>64929.16</v>
       </c>
       <c r="J15" t="n">
-        <v>68004.34</v>
+        <v>65040.65</v>
       </c>
       <c r="K15" t="n">
-        <v>68268.97</v>
+        <v>66050.38</v>
       </c>
       <c r="L15" t="n">
-        <v>68533.61</v>
+        <v>67060.10000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>69234.03999999999</v>
+        <v>67620.7</v>
       </c>
       <c r="N15" t="n">
-        <v>69934.48</v>
+        <v>68181.31</v>
       </c>
       <c r="O15" t="n">
-        <v>69763.31</v>
+        <v>69640.14999999999</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -1781,7 +1780,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1805,74 +1804,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>66339.85000000001</v>
+        <v>64544.05</v>
       </c>
       <c r="C16" t="n">
-        <v>66441.77</v>
+        <v>66232.19</v>
       </c>
       <c r="D16" t="n">
-        <v>62704.6</v>
+        <v>64203.47</v>
       </c>
       <c r="E16" t="n">
-        <v>64141.12</v>
+        <v>66232.19</v>
       </c>
       <c r="F16" t="n">
-        <v>-2694.42</v>
+        <v>2091.07</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0326</v>
       </c>
       <c r="H16" t="n">
-        <v>3737.17</v>
+        <v>2028.72</v>
       </c>
       <c r="I16" t="n">
-        <v>64929.16</v>
+        <v>58967.43</v>
       </c>
       <c r="J16" t="n">
-        <v>65040.65</v>
+        <v>60187.92</v>
       </c>
       <c r="K16" t="n">
-        <v>66050.38</v>
+        <v>62272.54</v>
       </c>
       <c r="L16" t="n">
-        <v>67060.10000000001</v>
+        <v>64357.15</v>
       </c>
       <c r="M16" t="n">
-        <v>67620.7</v>
+        <v>66009.71000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>68181.31</v>
+        <v>67662.25999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>69640.14999999999</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
+        <v>70178.95</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1884,55 +1879,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>64544.05</v>
+        <v>66449.27</v>
       </c>
       <c r="C17" t="n">
-        <v>66232.19</v>
+        <v>67592.2</v>
       </c>
       <c r="D17" t="n">
-        <v>64203.47</v>
+        <v>65955.60000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>66232.19</v>
+        <v>66115.60000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>2091.07</v>
+        <v>-116.59</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0326</v>
+        <v>-0.0018</v>
       </c>
       <c r="H17" t="n">
-        <v>2028.72</v>
+        <v>1636.6</v>
       </c>
       <c r="I17" t="n">
-        <v>58967.43</v>
+        <v>62174.75</v>
       </c>
       <c r="J17" t="n">
-        <v>60187.92</v>
+        <v>64710.65</v>
       </c>
       <c r="K17" t="n">
-        <v>62272.54</v>
+        <v>65217.83</v>
       </c>
       <c r="L17" t="n">
-        <v>64357.15</v>
+        <v>65725.00999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>66009.71000000001</v>
+        <v>67246.55</v>
       </c>
       <c r="N17" t="n">
-        <v>67662.25999999999</v>
+        <v>68768.09</v>
       </c>
       <c r="O17" t="n">
-        <v>70178.95</v>
+        <v>68260.91</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1943,14 +1942,14 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U17" s="8" t="n">
@@ -1973,50 +1972,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>66449.27</v>
+        <v>66421.00999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>67592.2</v>
+        <v>67022.37</v>
       </c>
       <c r="D18" t="n">
-        <v>65955.60000000001</v>
+        <v>66208.66</v>
       </c>
       <c r="E18" t="n">
-        <v>66115.60000000001</v>
+        <v>66422.60000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-116.59</v>
+        <v>307</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0046</v>
       </c>
       <c r="H18" t="n">
-        <v>1636.6</v>
+        <v>813.71</v>
       </c>
       <c r="I18" t="n">
-        <v>62174.75</v>
+        <v>64319</v>
       </c>
       <c r="J18" t="n">
-        <v>64710.65</v>
+        <v>64149.85</v>
       </c>
       <c r="K18" t="n">
-        <v>65217.83</v>
+        <v>65297.3</v>
       </c>
       <c r="L18" t="n">
-        <v>65725.00999999999</v>
+        <v>66444.75</v>
       </c>
       <c r="M18" t="n">
-        <v>67246.55</v>
+        <v>66933.89999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>68768.09</v>
+        <v>67423.05</v>
       </c>
       <c r="O18" t="n">
-        <v>68260.91</v>
+        <v>69228.8</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2029,7 +2028,7 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2057,69 +2056,73 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>66421.00999999999</v>
+        <v>65584.25</v>
       </c>
       <c r="C19" t="n">
-        <v>67022.37</v>
+        <v>65720.81</v>
       </c>
       <c r="D19" t="n">
-        <v>66208.66</v>
+        <v>64201.03</v>
       </c>
       <c r="E19" t="n">
-        <v>66422.60000000001</v>
+        <v>64611.15</v>
       </c>
       <c r="F19" t="n">
-        <v>307</v>
+        <v>-1811.45</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0273</v>
       </c>
       <c r="H19" t="n">
-        <v>813.71</v>
+        <v>1519.78</v>
       </c>
       <c r="I19" t="n">
-        <v>64319</v>
+        <v>65394.95</v>
       </c>
       <c r="J19" t="n">
-        <v>64149.85</v>
+        <v>65512.44</v>
       </c>
       <c r="K19" t="n">
-        <v>65297.3</v>
+        <v>66015.75</v>
       </c>
       <c r="L19" t="n">
-        <v>66444.75</v>
+        <v>66519.06</v>
       </c>
       <c r="M19" t="n">
-        <v>66933.89999999999</v>
+        <v>66829.46000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>67423.05</v>
+        <v>67139.86</v>
       </c>
       <c r="O19" t="n">
-        <v>69228.8</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67836.08</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2132,78 +2135,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>65584.25</v>
+        <v>65164.98</v>
       </c>
       <c r="C20" t="n">
-        <v>65720.81</v>
+        <v>65220.69</v>
       </c>
       <c r="D20" t="n">
-        <v>64201.03</v>
+        <v>64123.4</v>
       </c>
       <c r="E20" t="n">
-        <v>64611.15</v>
+        <v>64931.19</v>
       </c>
       <c r="F20" t="n">
-        <v>-1811.45</v>
+        <v>320.04</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.005</v>
       </c>
       <c r="H20" t="n">
-        <v>1519.78</v>
+        <v>1097.29</v>
       </c>
       <c r="I20" t="n">
-        <v>65394.95</v>
+        <v>62681.25</v>
       </c>
       <c r="J20" t="n">
-        <v>65512.44</v>
+        <v>62916.48</v>
       </c>
       <c r="K20" t="n">
-        <v>66015.75</v>
+        <v>63851.26</v>
       </c>
       <c r="L20" t="n">
-        <v>66519.06</v>
+        <v>64786.04</v>
       </c>
       <c r="M20" t="n">
-        <v>66829.46000000001</v>
+        <v>65371.04</v>
       </c>
       <c r="N20" t="n">
-        <v>67139.86</v>
+        <v>65956.03999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>67836.08</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67240.59</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2220,68 +2213,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>65164.98</v>
+        <v>64539.92</v>
       </c>
       <c r="C21" t="n">
-        <v>65220.69</v>
+        <v>64573.18</v>
       </c>
       <c r="D21" t="n">
-        <v>64123.4</v>
+        <v>61923.6</v>
       </c>
       <c r="E21" t="n">
-        <v>64931.19</v>
+        <v>62364.92</v>
       </c>
       <c r="F21" t="n">
-        <v>320.04</v>
+        <v>-2566.27</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0395</v>
       </c>
       <c r="H21" t="n">
-        <v>1097.29</v>
+        <v>2649.58</v>
       </c>
       <c r="I21" t="n">
-        <v>62681.25</v>
+        <v>63026.11</v>
       </c>
       <c r="J21" t="n">
-        <v>62916.48</v>
+        <v>63963.47</v>
       </c>
       <c r="K21" t="n">
-        <v>63851.26</v>
+        <v>64382.54</v>
       </c>
       <c r="L21" t="n">
-        <v>64786.04</v>
+        <v>64801.62</v>
       </c>
       <c r="M21" t="n">
-        <v>65371.04</v>
+        <v>65479.84</v>
       </c>
       <c r="N21" t="n">
-        <v>65956.03999999999</v>
+        <v>66158.06</v>
       </c>
       <c r="O21" t="n">
-        <v>67240.59</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+        <v>66317.98</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2298,76 +2301,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>64539.92</v>
+        <v>62734.68</v>
       </c>
       <c r="C22" t="n">
-        <v>64573.18</v>
+        <v>63138.04</v>
       </c>
       <c r="D22" t="n">
-        <v>61923.6</v>
+        <v>60448.9</v>
       </c>
       <c r="E22" t="n">
-        <v>62364.92</v>
+        <v>61434.19</v>
       </c>
       <c r="F22" t="n">
-        <v>-2566.27</v>
+        <v>-930.73</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0149</v>
       </c>
       <c r="H22" t="n">
-        <v>2649.58</v>
+        <v>2689.14</v>
       </c>
       <c r="I22" t="n">
-        <v>63026.11</v>
+        <v>59274.02</v>
       </c>
       <c r="J22" t="n">
-        <v>63963.47</v>
+        <v>59273.61</v>
       </c>
       <c r="K22" t="n">
-        <v>64382.54</v>
+        <v>61040.13</v>
       </c>
       <c r="L22" t="n">
-        <v>64801.62</v>
+        <v>62806.66</v>
       </c>
       <c r="M22" t="n">
-        <v>65479.84</v>
+        <v>63689.71</v>
       </c>
       <c r="N22" t="n">
-        <v>66158.06</v>
+        <v>64572.77</v>
       </c>
       <c r="O22" t="n">
-        <v>66317.98</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>67222.75999999999</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2391,50 +2386,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>62734.68</v>
+        <v>61258.34</v>
       </c>
       <c r="C23" t="n">
-        <v>63138.04</v>
+        <v>62924.84</v>
       </c>
       <c r="D23" t="n">
-        <v>60448.9</v>
+        <v>61049.7</v>
       </c>
       <c r="E23" t="n">
-        <v>61434.19</v>
+        <v>61867.43</v>
       </c>
       <c r="F23" t="n">
-        <v>-930.73</v>
+        <v>433.24</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0071</v>
       </c>
       <c r="H23" t="n">
-        <v>2689.14</v>
+        <v>1875.14</v>
       </c>
       <c r="I23" t="n">
-        <v>59274.02</v>
+        <v>57759.76</v>
       </c>
       <c r="J23" t="n">
-        <v>59273.61</v>
+        <v>58565.41</v>
       </c>
       <c r="K23" t="n">
-        <v>61040.13</v>
+        <v>60089.62</v>
       </c>
       <c r="L23" t="n">
-        <v>62806.66</v>
+        <v>61613.83</v>
       </c>
       <c r="M23" t="n">
-        <v>63689.71</v>
+        <v>62778.76</v>
       </c>
       <c r="N23" t="n">
-        <v>64572.77</v>
+        <v>63943.69</v>
       </c>
       <c r="O23" t="n">
-        <v>67222.75999999999</v>
+        <v>65827.17999999999</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2442,18 +2437,18 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2466,55 +2461,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>61258.34</v>
+        <v>61957.1</v>
       </c>
       <c r="C24" t="n">
-        <v>62924.84</v>
+        <v>65364.73</v>
       </c>
       <c r="D24" t="n">
-        <v>61049.7</v>
+        <v>61948.23</v>
       </c>
       <c r="E24" t="n">
-        <v>61867.43</v>
+        <v>64362.02</v>
       </c>
       <c r="F24" t="n">
-        <v>433.24</v>
+        <v>2494.59</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0403</v>
       </c>
       <c r="H24" t="n">
-        <v>1875.14</v>
+        <v>3416.5</v>
       </c>
       <c r="I24" t="n">
-        <v>57759.76</v>
+        <v>59174.56</v>
       </c>
       <c r="J24" t="n">
-        <v>58565.41</v>
+        <v>59932.37</v>
       </c>
       <c r="K24" t="n">
-        <v>60089.62</v>
+        <v>60929.86</v>
       </c>
       <c r="L24" t="n">
-        <v>61613.83</v>
+        <v>61927.35</v>
       </c>
       <c r="M24" t="n">
-        <v>62778.76</v>
+        <v>62805</v>
       </c>
       <c r="N24" t="n">
-        <v>63943.69</v>
+        <v>63682.65</v>
       </c>
       <c r="O24" t="n">
-        <v>65827.17999999999</v>
+        <v>64799.98</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2525,9 +2524,9 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2535,70 +2534,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>61957.1</v>
+        <v>63834.95</v>
       </c>
       <c r="C25" t="n">
-        <v>65364.73</v>
+        <v>63905.12</v>
       </c>
       <c r="D25" t="n">
-        <v>61948.23</v>
+        <v>62703.47</v>
       </c>
       <c r="E25" t="n">
-        <v>64362.02</v>
+        <v>63754.9</v>
       </c>
       <c r="F25" t="n">
-        <v>2494.59</v>
+        <v>-607.12</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0403</v>
+        <v>-0.0094</v>
       </c>
       <c r="H25" t="n">
-        <v>3416.5</v>
+        <v>1201.65</v>
       </c>
       <c r="I25" t="n">
-        <v>59174.56</v>
+        <v>58531.73</v>
       </c>
       <c r="J25" t="n">
-        <v>59932.37</v>
+        <v>61298.29</v>
       </c>
       <c r="K25" t="n">
-        <v>60929.86</v>
+        <v>62653.77</v>
       </c>
       <c r="L25" t="n">
-        <v>61927.35</v>
+        <v>64009.25</v>
       </c>
       <c r="M25" t="n">
-        <v>62805</v>
+        <v>66070.27</v>
       </c>
       <c r="N25" t="n">
-        <v>63682.65</v>
+        <v>68131.28999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>64799.98</v>
+        <v>68781.23</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2611,78 +2610,76 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63834.95</v>
+        <v>63995.28</v>
       </c>
       <c r="C26" t="n">
-        <v>63905.12</v>
+        <v>64240.5</v>
       </c>
       <c r="D26" t="n">
-        <v>62703.47</v>
+        <v>62864.43</v>
       </c>
       <c r="E26" t="n">
-        <v>63754.9</v>
+        <v>63957.53</v>
       </c>
       <c r="F26" t="n">
-        <v>-607.12</v>
+        <v>202.63</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0032</v>
       </c>
       <c r="H26" t="n">
-        <v>1201.65</v>
+        <v>1376.07</v>
       </c>
       <c r="I26" t="n">
-        <v>58531.73</v>
+        <v>61501.82</v>
       </c>
       <c r="J26" t="n">
-        <v>61298.29</v>
+        <v>62778.55</v>
       </c>
       <c r="K26" t="n">
-        <v>62653.77</v>
+        <v>63154.07</v>
       </c>
       <c r="L26" t="n">
-        <v>64009.25</v>
+        <v>63529.6</v>
       </c>
       <c r="M26" t="n">
-        <v>66070.27</v>
+        <v>64355.72</v>
       </c>
       <c r="N26" t="n">
-        <v>68131.28999999999</v>
+        <v>65181.85</v>
       </c>
       <c r="O26" t="n">
-        <v>68781.23</v>
+        <v>65106.77</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2690,16 +2687,20 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2712,59 +2713,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63995.28</v>
+        <v>64565.27</v>
       </c>
       <c r="C27" t="n">
-        <v>64240.5</v>
+        <v>66302.52</v>
       </c>
       <c r="D27" t="n">
-        <v>62864.43</v>
+        <v>64555.52</v>
       </c>
       <c r="E27" t="n">
-        <v>63957.53</v>
+        <v>66300.44</v>
       </c>
       <c r="F27" t="n">
-        <v>202.63</v>
+        <v>2342.91</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0366</v>
       </c>
       <c r="H27" t="n">
-        <v>1376.07</v>
+        <v>1747</v>
       </c>
       <c r="I27" t="n">
-        <v>61501.82</v>
+        <v>61488.36</v>
       </c>
       <c r="J27" t="n">
-        <v>62778.55</v>
+        <v>62783.99</v>
       </c>
       <c r="K27" t="n">
-        <v>63154.07</v>
+        <v>63269.5</v>
       </c>
       <c r="L27" t="n">
-        <v>63529.6</v>
+        <v>63755</v>
       </c>
       <c r="M27" t="n">
-        <v>64355.72</v>
+        <v>64645.57</v>
       </c>
       <c r="N27" t="n">
-        <v>65181.85</v>
+        <v>65536.13</v>
       </c>
       <c r="O27" t="n">
-        <v>65106.77</v>
+        <v>65616.57000000001</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2772,26 +2769,28 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
@@ -2803,134 +2802,136 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>64565.27</v>
+        <v>65896</v>
       </c>
       <c r="C28" t="n">
-        <v>66302.52</v>
+        <v>65983.13</v>
       </c>
       <c r="D28" t="n">
-        <v>64555.52</v>
+        <v>64942.07</v>
       </c>
       <c r="E28" t="n">
-        <v>66300.44</v>
+        <v>65683.25999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>2342.91</v>
+        <v>-617.1799999999999</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0366</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>1747</v>
+        <v>1041.06</v>
       </c>
       <c r="I28" t="n">
-        <v>61488.36</v>
+        <v>62808.52</v>
       </c>
       <c r="J28" t="n">
-        <v>62783.99</v>
+        <v>64989.14</v>
       </c>
       <c r="K28" t="n">
-        <v>63269.5</v>
+        <v>65426.94</v>
       </c>
       <c r="L28" t="n">
-        <v>63755</v>
+        <v>65864.73</v>
       </c>
       <c r="M28" t="n">
-        <v>64645.57</v>
+        <v>67173.94</v>
       </c>
       <c r="N28" t="n">
-        <v>65536.13</v>
+        <v>68483.14999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>65616.57000000001</v>
+        <v>68049.53</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>65896</v>
+        <v>65746.13</v>
       </c>
       <c r="C29" t="n">
-        <v>65983.13</v>
+        <v>65990.72</v>
       </c>
       <c r="D29" t="n">
-        <v>64942.07</v>
+        <v>64651.49</v>
       </c>
       <c r="E29" t="n">
-        <v>65683.25999999999</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>-617.1799999999999</v>
+        <v>-76.55</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="H29" t="n">
-        <v>1041.06</v>
+        <v>1339.23</v>
       </c>
       <c r="I29" t="n">
-        <v>62808.52</v>
+        <v>63901.01</v>
       </c>
       <c r="J29" t="n">
-        <v>64989.14</v>
+        <v>64752.52</v>
       </c>
       <c r="K29" t="n">
-        <v>65426.94</v>
+        <v>65162.73</v>
       </c>
       <c r="L29" t="n">
-        <v>65864.73</v>
+        <v>65572.92999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>67173.94</v>
+        <v>66203.78999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>68483.14999999999</v>
+        <v>66834.64999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>68049.53</v>
+        <v>67024.2</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2947,7 +2948,7 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2973,74 +2974,74 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>65746.13</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>65990.72</v>
+        <v>67006.84</v>
       </c>
       <c r="D30" t="n">
-        <v>64651.49</v>
+        <v>65848.58</v>
       </c>
       <c r="E30" t="n">
-        <v>65606.71000000001</v>
+        <v>66970.22</v>
       </c>
       <c r="F30" t="n">
-        <v>-76.55</v>
+        <v>1363.51</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0208</v>
       </c>
       <c r="H30" t="n">
-        <v>1339.23</v>
+        <v>1158.27</v>
       </c>
       <c r="I30" t="n">
-        <v>63901.01</v>
+        <v>63312.26</v>
       </c>
       <c r="J30" t="n">
-        <v>64752.52</v>
+        <v>64410.28</v>
       </c>
       <c r="K30" t="n">
-        <v>65162.73</v>
+        <v>64937.1</v>
       </c>
       <c r="L30" t="n">
-        <v>65572.92999999999</v>
+        <v>65463.91</v>
       </c>
       <c r="M30" t="n">
-        <v>66203.78999999999</v>
+        <v>66276.33</v>
       </c>
       <c r="N30" t="n">
-        <v>66834.64999999999</v>
+        <v>67088.75</v>
       </c>
       <c r="O30" t="n">
-        <v>67024.2</v>
+        <v>67329.95</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3050,59 +3051,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>65905.10000000001</v>
+        <v>66994.05</v>
       </c>
       <c r="C31" t="n">
-        <v>67006.84</v>
+        <v>67569.36</v>
       </c>
       <c r="D31" t="n">
-        <v>65848.58</v>
+        <v>66735.75999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>66970.22</v>
+        <v>67524.06</v>
       </c>
       <c r="F31" t="n">
-        <v>1363.51</v>
+        <v>553.84</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="H31" t="n">
-        <v>1158.27</v>
+        <v>833.6</v>
       </c>
       <c r="I31" t="n">
-        <v>63312.26</v>
+        <v>64690.31</v>
       </c>
       <c r="J31" t="n">
-        <v>64410.28</v>
+        <v>66083.21000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>64937.1</v>
+        <v>66391.09</v>
       </c>
       <c r="L31" t="n">
-        <v>65463.91</v>
+        <v>66698.96000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>66276.33</v>
+        <v>67549.35000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>67088.75</v>
+        <v>68399.74000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>67329.95</v>
+        <v>68165.11</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3113,20 +3110,18 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3141,50 +3136,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>66994.05</v>
+        <v>68033.17</v>
       </c>
       <c r="C32" t="n">
-        <v>67569.36</v>
+        <v>68799.71000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>66735.75999999999</v>
+        <v>68006.17</v>
       </c>
       <c r="E32" t="n">
-        <v>67524.06</v>
+        <v>68308.59</v>
       </c>
       <c r="F32" t="n">
-        <v>553.84</v>
+        <v>784.53</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0116</v>
       </c>
       <c r="H32" t="n">
-        <v>833.6</v>
+        <v>793.54</v>
       </c>
       <c r="I32" t="n">
-        <v>64690.31</v>
+        <v>65902.16</v>
       </c>
       <c r="J32" t="n">
-        <v>66083.21000000001</v>
+        <v>66876.21000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>66391.09</v>
+        <v>67107.25999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>66698.96000000001</v>
+        <v>67338.31</v>
       </c>
       <c r="M32" t="n">
-        <v>67549.35000000001</v>
+        <v>67940.86</v>
       </c>
       <c r="N32" t="n">
-        <v>68399.74000000001</v>
+        <v>68543.42</v>
       </c>
       <c r="O32" t="n">
-        <v>68165.11</v>
+        <v>68402.96000000001</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3195,21 +3190,25 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
@@ -3221,50 +3220,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>68033.17</v>
+        <v>68811.17</v>
       </c>
       <c r="C33" t="n">
-        <v>68799.71000000001</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>68006.17</v>
+        <v>68471.14999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>68308.59</v>
+        <v>68713.8</v>
       </c>
       <c r="F33" t="n">
-        <v>784.53</v>
+        <v>405.2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0059</v>
       </c>
       <c r="H33" t="n">
-        <v>793.54</v>
+        <v>1137.09</v>
       </c>
       <c r="I33" t="n">
-        <v>65902.16</v>
+        <v>67212.63</v>
       </c>
       <c r="J33" t="n">
-        <v>66876.21000000001</v>
+        <v>67467.88</v>
       </c>
       <c r="K33" t="n">
-        <v>67107.25999999999</v>
+        <v>67911.82000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>67338.31</v>
+        <v>68355.77</v>
       </c>
       <c r="M33" t="n">
-        <v>67940.86</v>
+        <v>68705.36</v>
       </c>
       <c r="N33" t="n">
-        <v>68543.42</v>
+        <v>69054.96000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>68402.96000000001</v>
+        <v>69593.25</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3275,14 +3274,14 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U33" s="8" t="inlineStr">
@@ -3292,7 +3291,7 @@
       </c>
       <c r="V33" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W33" s="9" t="inlineStr">
@@ -3305,50 +3304,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>68811.17</v>
+        <v>68882.06</v>
       </c>
       <c r="C34" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>68471.14999999999</v>
+        <v>68492.03999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>68713.8</v>
+        <v>69220.25</v>
       </c>
       <c r="F34" t="n">
-        <v>405.2</v>
+        <v>506.45</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="H34" t="n">
-        <v>1137.09</v>
+        <v>733.53</v>
       </c>
       <c r="I34" t="n">
-        <v>67212.63</v>
+        <v>67334.05</v>
       </c>
       <c r="J34" t="n">
-        <v>67467.88</v>
+        <v>67413.75</v>
       </c>
       <c r="K34" t="n">
-        <v>67911.82000000001</v>
+        <v>68145.25</v>
       </c>
       <c r="L34" t="n">
-        <v>68355.77</v>
+        <v>68876.75</v>
       </c>
       <c r="M34" t="n">
-        <v>68705.36</v>
+        <v>69282.34</v>
       </c>
       <c r="N34" t="n">
-        <v>69054.96000000001</v>
+        <v>69687.94</v>
       </c>
       <c r="O34" t="n">
-        <v>69593.25</v>
+        <v>70745.34</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3359,7 +3358,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3369,89 +3368,93 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>68882.06</v>
+        <v>68847.35000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>69225.57000000001</v>
+        <v>69093.2</v>
       </c>
       <c r="D35" t="n">
-        <v>68492.03999999999</v>
+        <v>67368.96000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>69220.25</v>
+        <v>67460.73</v>
       </c>
       <c r="F35" t="n">
-        <v>506.45</v>
+        <v>-1759.52</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0254</v>
       </c>
       <c r="H35" t="n">
-        <v>733.53</v>
+        <v>1724.24</v>
       </c>
       <c r="I35" t="n">
-        <v>67334.05</v>
+        <v>67758.50999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>67413.75</v>
+        <v>68667.44</v>
       </c>
       <c r="K35" t="n">
-        <v>68145.25</v>
+        <v>68853.48</v>
       </c>
       <c r="L35" t="n">
-        <v>68876.75</v>
+        <v>69039.53</v>
       </c>
       <c r="M35" t="n">
-        <v>69282.34</v>
+        <v>69587.02</v>
       </c>
       <c r="N35" t="n">
-        <v>69687.94</v>
+        <v>70134.5</v>
       </c>
       <c r="O35" t="n">
-        <v>70745.34</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+        <v>69959.10000000001</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3459,81 +3462,77 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>68847.35000000001</v>
+        <v>66812.27</v>
       </c>
       <c r="C36" t="n">
-        <v>69093.2</v>
+        <v>66833.50999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>67368.96000000001</v>
+        <v>65133.98</v>
       </c>
       <c r="E36" t="n">
-        <v>67460.73</v>
+        <v>65326.42</v>
       </c>
       <c r="F36" t="n">
-        <v>-1759.52</v>
+        <v>-2134.3</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="H36" t="n">
-        <v>1724.24</v>
+        <v>1699.53</v>
       </c>
       <c r="I36" t="n">
-        <v>67758.50999999999</v>
+        <v>65644.72</v>
       </c>
       <c r="J36" t="n">
-        <v>68667.44</v>
+        <v>65351.31</v>
       </c>
       <c r="K36" t="n">
-        <v>68853.48</v>
+        <v>66598.61</v>
       </c>
       <c r="L36" t="n">
-        <v>69039.53</v>
+        <v>67845.89999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>69587.02</v>
+        <v>68322.85000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>70134.5</v>
+        <v>68799.78999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>69959.10000000001</v>
+        <v>70817.45</v>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3557,74 +3556,70 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>66812.27</v>
+        <v>65732.78999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>66833.50999999999</v>
+        <v>66325.32000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>65133.98</v>
+        <v>65652.25</v>
       </c>
       <c r="E37" t="n">
-        <v>65326.42</v>
+        <v>66216.78999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>-2134.3</v>
+        <v>890.37</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H37" t="n">
-        <v>1699.53</v>
+        <v>673.0700000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>65644.72</v>
+        <v>63434.45</v>
       </c>
       <c r="J37" t="n">
-        <v>65351.31</v>
+        <v>63298.23</v>
       </c>
       <c r="K37" t="n">
-        <v>66598.61</v>
+        <v>64476.66</v>
       </c>
       <c r="L37" t="n">
-        <v>67845.89999999999</v>
+        <v>65655.08</v>
       </c>
       <c r="M37" t="n">
-        <v>68322.85000000001</v>
+        <v>66176.19</v>
       </c>
       <c r="N37" t="n">
-        <v>68799.78999999999</v>
+        <v>66697.28999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>70817.45</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
+        <v>68533.03999999999</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3636,74 +3631,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>65732.78999999999</v>
+        <v>65427.69</v>
       </c>
       <c r="C38" t="n">
-        <v>66325.32000000001</v>
+        <v>66125.88</v>
       </c>
       <c r="D38" t="n">
-        <v>65652.25</v>
+        <v>65260.22</v>
       </c>
       <c r="E38" t="n">
-        <v>66216.78999999999</v>
+        <v>66016.36</v>
       </c>
       <c r="F38" t="n">
-        <v>890.37</v>
+        <v>-200.43</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.003</v>
       </c>
       <c r="H38" t="n">
-        <v>673.0700000000001</v>
+        <v>865.66</v>
       </c>
       <c r="I38" t="n">
-        <v>63434.45</v>
+        <v>64979.18</v>
       </c>
       <c r="J38" t="n">
-        <v>63298.23</v>
+        <v>65657.72</v>
       </c>
       <c r="K38" t="n">
-        <v>64476.66</v>
+        <v>65880.25</v>
       </c>
       <c r="L38" t="n">
-        <v>65655.08</v>
+        <v>66102.78999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>66176.19</v>
+        <v>66553.32000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>66697.28999999999</v>
+        <v>67003.86</v>
       </c>
       <c r="O38" t="n">
-        <v>68533.03999999999</v>
+        <v>66998.39</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3716,76 +3717,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>65427.69</v>
+        <v>65978.95</v>
       </c>
       <c r="C39" t="n">
-        <v>66125.88</v>
+        <v>66257.73</v>
       </c>
       <c r="D39" t="n">
-        <v>65260.22</v>
+        <v>65470.95</v>
       </c>
       <c r="E39" t="n">
-        <v>66016.36</v>
+        <v>65528.09</v>
       </c>
       <c r="F39" t="n">
-        <v>-200.43</v>
+        <v>-488.27</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0074</v>
       </c>
       <c r="H39" t="n">
-        <v>865.66</v>
+        <v>786.78</v>
       </c>
       <c r="I39" t="n">
-        <v>64979.18</v>
+        <v>64394.55</v>
       </c>
       <c r="J39" t="n">
-        <v>65657.72</v>
+        <v>65312.35</v>
       </c>
       <c r="K39" t="n">
-        <v>65880.25</v>
+        <v>65583.53</v>
       </c>
       <c r="L39" t="n">
-        <v>66102.78999999999</v>
+        <v>65854.71000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>66553.32000000001</v>
+        <v>66449.19</v>
       </c>
       <c r="N39" t="n">
-        <v>67003.86</v>
+        <v>67043.67999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>66998.39</v>
+        <v>66991.55</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q39" s="6" t="n">
+        <v/>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3802,75 +3797,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>65978.95</v>
+        <v>65195.26</v>
       </c>
       <c r="C40" t="n">
-        <v>66257.73</v>
+        <v>65904.24000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>65470.95</v>
+        <v>64609.47</v>
       </c>
       <c r="E40" t="n">
-        <v>65528.09</v>
+        <v>65856.42999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>-488.27</v>
+        <v>328.34</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.005</v>
       </c>
       <c r="H40" t="n">
-        <v>786.78</v>
+        <v>1294.77</v>
       </c>
       <c r="I40" t="n">
-        <v>64394.55</v>
+        <v>64684.17</v>
       </c>
       <c r="J40" t="n">
-        <v>65312.35</v>
+        <v>64573.19</v>
       </c>
       <c r="K40" t="n">
-        <v>65583.53</v>
+        <v>65134.7</v>
       </c>
       <c r="L40" t="n">
-        <v>65854.71000000001</v>
+        <v>65696.21000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>66449.19</v>
+        <v>65921.48</v>
       </c>
       <c r="N40" t="n">
-        <v>67043.67999999999</v>
+        <v>66146.74000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>66991.55</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
+        <v>67044.5</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3884,72 +3887,68 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>65195.26</v>
+        <v>65604.49000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>65904.24000000001</v>
+        <v>66442.34</v>
       </c>
       <c r="D41" t="n">
-        <v>64609.47</v>
+        <v>65390.55</v>
       </c>
       <c r="E41" t="n">
-        <v>65856.42999999999</v>
+        <v>66262.16</v>
       </c>
       <c r="F41" t="n">
-        <v>328.34</v>
+        <v>405.73</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0062</v>
       </c>
       <c r="H41" t="n">
-        <v>1294.77</v>
+        <v>1051.79</v>
       </c>
       <c r="I41" t="n">
-        <v>64684.17</v>
+        <v>63314.7</v>
       </c>
       <c r="J41" t="n">
-        <v>64573.19</v>
+        <v>64861.44</v>
       </c>
       <c r="K41" t="n">
-        <v>65134.7</v>
+        <v>65209.04</v>
       </c>
       <c r="L41" t="n">
-        <v>65696.21000000001</v>
+        <v>65556.64</v>
       </c>
       <c r="M41" t="n">
-        <v>65921.48</v>
+        <v>66503.82000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>66146.74000000001</v>
+        <v>67450.99000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>67044.5</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67199.02</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
       </c>
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3972,57 +3971,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>65604.49000000001</v>
+        <v>66775.78</v>
       </c>
       <c r="C42" t="n">
-        <v>66442.34</v>
+        <v>66954.69</v>
       </c>
       <c r="D42" t="n">
-        <v>65390.55</v>
+        <v>65782.59</v>
       </c>
       <c r="E42" t="n">
-        <v>66262.16</v>
+        <v>66131.98</v>
       </c>
       <c r="F42" t="n">
-        <v>405.73</v>
+        <v>-130.18</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.002</v>
       </c>
       <c r="H42" t="n">
-        <v>1051.79</v>
+        <v>1172.09</v>
       </c>
       <c r="I42" t="n">
-        <v>63314.7</v>
+        <v>64338.76</v>
       </c>
       <c r="J42" t="n">
-        <v>64861.44</v>
+        <v>65383.22</v>
       </c>
       <c r="K42" t="n">
-        <v>65209.04</v>
+        <v>65736.25999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>65556.64</v>
+        <v>66089.3</v>
       </c>
       <c r="M42" t="n">
-        <v>66503.82000000001</v>
+        <v>66788.05</v>
       </c>
       <c r="N42" t="n">
-        <v>67450.99000000001</v>
+        <v>67486.8</v>
       </c>
       <c r="O42" t="n">
-        <v>67199.02</v>
+        <v>67494.14</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4033,14 +4032,14 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U42" s="8" t="n">
@@ -4056,57 +4055,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>66775.78</v>
+        <v>66104.49000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>66954.69</v>
+        <v>66842.82000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>65782.59</v>
+        <v>66012.2</v>
       </c>
       <c r="E43" t="n">
-        <v>66131.98</v>
+        <v>66405.56</v>
       </c>
       <c r="F43" t="n">
-        <v>-130.18</v>
+        <v>273.59</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0041</v>
       </c>
       <c r="H43" t="n">
-        <v>1172.09</v>
+        <v>830.62</v>
       </c>
       <c r="I43" t="n">
-        <v>64338.76</v>
+        <v>64610.5</v>
       </c>
       <c r="J43" t="n">
-        <v>65383.22</v>
+        <v>64841.55</v>
       </c>
       <c r="K43" t="n">
-        <v>65736.25999999999</v>
+        <v>65545.92999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>66089.3</v>
+        <v>66250.31</v>
       </c>
       <c r="M43" t="n">
-        <v>66788.05</v>
+        <v>66718.02</v>
       </c>
       <c r="N43" t="n">
-        <v>67486.8</v>
+        <v>67185.74000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>67494.14</v>
+        <v>68126.78</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4117,7 +4116,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4147,69 +4146,73 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>66104.49000000001</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>66842.82000000001</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>66012.2</v>
+        <v>64832.1</v>
       </c>
       <c r="E44" t="n">
-        <v>66405.56</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>273.59</v>
+        <v>-93.63</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0014</v>
       </c>
       <c r="H44" t="n">
-        <v>830.62</v>
+        <v>1479.83</v>
       </c>
       <c r="I44" t="n">
-        <v>64610.5</v>
+        <v>65181.59</v>
       </c>
       <c r="J44" t="n">
-        <v>64841.55</v>
+        <v>65563.97</v>
       </c>
       <c r="K44" t="n">
-        <v>65545.92999999999</v>
+        <v>65990.25</v>
       </c>
       <c r="L44" t="n">
-        <v>66250.31</v>
+        <v>66416.53999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>66718.02</v>
+        <v>66820.87</v>
       </c>
       <c r="N44" t="n">
-        <v>67185.74000000001</v>
+        <v>67225.21000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>68126.78</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+        <v>67673.44</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4222,78 +4225,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>65668.50999999999</v>
+        <v>65885.47</v>
       </c>
       <c r="C45" t="n">
-        <v>66311.92999999999</v>
+        <v>66525.7</v>
       </c>
       <c r="D45" t="n">
-        <v>64832.1</v>
+        <v>65576.61</v>
       </c>
       <c r="E45" t="n">
-        <v>66311.92999999999</v>
+        <v>66215.34</v>
       </c>
       <c r="F45" t="n">
-        <v>-93.63</v>
+        <v>-96.59</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0015</v>
       </c>
       <c r="H45" t="n">
-        <v>1479.83</v>
+        <v>949.09</v>
       </c>
       <c r="I45" t="n">
-        <v>65181.59</v>
+        <v>63352.27</v>
       </c>
       <c r="J45" t="n">
-        <v>65563.97</v>
+        <v>65202.06</v>
       </c>
       <c r="K45" t="n">
-        <v>65990.25</v>
+        <v>65572.02</v>
       </c>
       <c r="L45" t="n">
-        <v>66416.53999999999</v>
+        <v>65941.97</v>
       </c>
       <c r="M45" t="n">
-        <v>66820.87</v>
+        <v>67051.84</v>
       </c>
       <c r="N45" t="n">
-        <v>67225.21000000001</v>
+        <v>68161.71000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>67673.44</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67791.75999999999</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4310,68 +4303,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>65885.47</v>
+        <v>65195.43</v>
       </c>
       <c r="C46" t="n">
-        <v>66525.7</v>
+        <v>65195.43</v>
       </c>
       <c r="D46" t="n">
-        <v>65576.61</v>
+        <v>64215.47</v>
       </c>
       <c r="E46" t="n">
-        <v>66215.34</v>
+        <v>64325.64</v>
       </c>
       <c r="F46" t="n">
-        <v>-96.59</v>
+        <v>-1889.7</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0285</v>
       </c>
       <c r="H46" t="n">
-        <v>949.09</v>
+        <v>979.96</v>
       </c>
       <c r="I46" t="n">
-        <v>63352.27</v>
+        <v>64627.52</v>
       </c>
       <c r="J46" t="n">
-        <v>65202.06</v>
+        <v>65348.34</v>
       </c>
       <c r="K46" t="n">
-        <v>65572.02</v>
+        <v>65740.8</v>
       </c>
       <c r="L46" t="n">
-        <v>65941.97</v>
+        <v>66133.25</v>
       </c>
       <c r="M46" t="n">
-        <v>67051.84</v>
+        <v>66689.89</v>
       </c>
       <c r="N46" t="n">
-        <v>68161.71000000001</v>
+        <v>67246.53</v>
       </c>
       <c r="O46" t="n">
-        <v>67791.75999999999</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+        <v>67474.8</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4388,78 +4391,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="C47" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="D47" t="n">
-        <v>64215.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E47" t="n">
-        <v>64325.64</v>
+        <v>64214.48</v>
       </c>
       <c r="F47" t="n">
-        <v>-1889.7</v>
+        <v>-111.16</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0017</v>
       </c>
       <c r="H47" t="n">
-        <v>979.96</v>
+        <v>952.01</v>
       </c>
       <c r="I47" t="n">
-        <v>64627.52</v>
+        <v>63235.51</v>
       </c>
       <c r="J47" t="n">
-        <v>65348.34</v>
+        <v>63155.78</v>
       </c>
       <c r="K47" t="n">
-        <v>65740.8</v>
+        <v>63835.66</v>
       </c>
       <c r="L47" t="n">
-        <v>66133.25</v>
+        <v>64515.54</v>
       </c>
       <c r="M47" t="n">
-        <v>66689.89</v>
+        <v>64815.62</v>
       </c>
       <c r="N47" t="n">
-        <v>67246.53</v>
+        <v>65115.7</v>
       </c>
       <c r="O47" t="n">
-        <v>67474.8</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66175.39</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4481,50 +4476,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>64724.81</v>
+        <v>64498.94</v>
       </c>
       <c r="C48" t="n">
-        <v>64724.81</v>
+        <v>65182.45</v>
       </c>
       <c r="D48" t="n">
-        <v>63772.8</v>
+        <v>64228.47</v>
       </c>
       <c r="E48" t="n">
-        <v>64214.48</v>
+        <v>65020.94</v>
       </c>
       <c r="F48" t="n">
-        <v>-111.16</v>
+        <v>806.46</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="H48" t="n">
-        <v>952.01</v>
+        <v>953.98</v>
       </c>
       <c r="I48" t="n">
-        <v>63235.51</v>
+        <v>62820.79</v>
       </c>
       <c r="J48" t="n">
-        <v>63155.78</v>
+        <v>63245.31</v>
       </c>
       <c r="K48" t="n">
-        <v>63835.66</v>
+        <v>63738.48</v>
       </c>
       <c r="L48" t="n">
-        <v>64515.54</v>
+        <v>64231.64</v>
       </c>
       <c r="M48" t="n">
-        <v>64815.62</v>
+        <v>64690.48</v>
       </c>
       <c r="N48" t="n">
-        <v>65115.7</v>
+        <v>65149.33</v>
       </c>
       <c r="O48" t="n">
-        <v>66175.39</v>
+        <v>65676.82000000001</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4532,21 +4527,23 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4556,55 +4553,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>64498.94</v>
+        <v>65600.42</v>
       </c>
       <c r="C49" t="n">
-        <v>65182.45</v>
+        <v>66668.71000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>64228.47</v>
+        <v>65600.42</v>
       </c>
       <c r="E49" t="n">
-        <v>65020.94</v>
+        <v>66399.84</v>
       </c>
       <c r="F49" t="n">
-        <v>806.46</v>
+        <v>1378.9</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="H49" t="n">
-        <v>953.98</v>
+        <v>1068.29</v>
       </c>
       <c r="I49" t="n">
-        <v>62820.79</v>
+        <v>63274.49</v>
       </c>
       <c r="J49" t="n">
-        <v>63245.31</v>
+        <v>64224.7</v>
       </c>
       <c r="K49" t="n">
-        <v>63738.48</v>
+        <v>64543.95</v>
       </c>
       <c r="L49" t="n">
-        <v>64231.64</v>
+        <v>64863.2</v>
       </c>
       <c r="M49" t="n">
-        <v>64690.48</v>
+        <v>65497.93</v>
       </c>
       <c r="N49" t="n">
-        <v>65149.33</v>
+        <v>66132.66</v>
       </c>
       <c r="O49" t="n">
-        <v>65676.82000000001</v>
+        <v>66136.42999999999</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4615,7 +4616,7 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4627,171 +4628,167 @@
       </c>
       <c r="U49" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65600.42</v>
+        <v>65843.69</v>
       </c>
       <c r="C50" t="n">
-        <v>66668.71000000001</v>
+        <v>66791.84</v>
       </c>
       <c r="D50" t="n">
-        <v>65600.42</v>
+        <v>65269.33</v>
       </c>
       <c r="E50" t="n">
-        <v>66399.84</v>
+        <v>65269.33</v>
       </c>
       <c r="F50" t="n">
-        <v>1378.9</v>
+        <v>-1130.52</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.017</v>
       </c>
       <c r="H50" t="n">
-        <v>1068.29</v>
+        <v>1522.52</v>
       </c>
       <c r="I50" t="n">
-        <v>63274.49</v>
+        <v>64532.13</v>
       </c>
       <c r="J50" t="n">
-        <v>64224.7</v>
+        <v>65464.19</v>
       </c>
       <c r="K50" t="n">
-        <v>64543.95</v>
+        <v>65865.7</v>
       </c>
       <c r="L50" t="n">
-        <v>64863.2</v>
+        <v>66267.21000000001</v>
       </c>
       <c r="M50" t="n">
-        <v>65497.93</v>
+        <v>66933.99000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>66132.66</v>
+        <v>67600.77</v>
       </c>
       <c r="O50" t="n">
-        <v>66136.42999999999</v>
+        <v>67737</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W50" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr"/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W50" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65843.69</v>
+        <v>65087.22</v>
       </c>
       <c r="C51" t="n">
-        <v>66791.84</v>
+        <v>65794.03</v>
       </c>
       <c r="D51" t="n">
-        <v>65269.33</v>
+        <v>65017.68</v>
       </c>
       <c r="E51" t="n">
-        <v>65269.33</v>
+        <v>65142.78</v>
       </c>
       <c r="F51" t="n">
-        <v>-1130.52</v>
+        <v>-126.55</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0019</v>
       </c>
       <c r="H51" t="n">
-        <v>1522.52</v>
+        <v>776.35</v>
       </c>
       <c r="I51" t="n">
-        <v>64532.13</v>
+        <v>63746.81</v>
       </c>
       <c r="J51" t="n">
-        <v>65464.19</v>
+        <v>63366.18</v>
       </c>
       <c r="K51" t="n">
-        <v>65865.7</v>
+        <v>64508.07</v>
       </c>
       <c r="L51" t="n">
-        <v>66267.21000000001</v>
+        <v>65649.96000000001</v>
       </c>
       <c r="M51" t="n">
-        <v>66933.99000000001</v>
+        <v>66030.59</v>
       </c>
       <c r="N51" t="n">
-        <v>67600.77</v>
+        <v>66411.21000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>67737</v>
+        <v>68314.36</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4808,70 +4805,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>65087.22</v>
+        <v>64768.53</v>
       </c>
       <c r="C52" t="n">
-        <v>65794.03</v>
+        <v>65270.95</v>
       </c>
       <c r="D52" t="n">
-        <v>65017.68</v>
+        <v>64186.68</v>
       </c>
       <c r="E52" t="n">
-        <v>65142.78</v>
+        <v>65270.95</v>
       </c>
       <c r="F52" t="n">
-        <v>-126.55</v>
+        <v>128.17</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="H52" t="n">
-        <v>776.35</v>
+        <v>1084.27</v>
       </c>
       <c r="I52" t="n">
-        <v>63746.81</v>
+        <v>64241.33</v>
       </c>
       <c r="J52" t="n">
-        <v>63366.18</v>
+        <v>64234.89</v>
       </c>
       <c r="K52" t="n">
-        <v>64508.07</v>
+        <v>64754.61</v>
       </c>
       <c r="L52" t="n">
-        <v>65649.96000000001</v>
+        <v>65274.32</v>
       </c>
       <c r="M52" t="n">
-        <v>66030.59</v>
+        <v>65530.96</v>
       </c>
       <c r="N52" t="n">
-        <v>66411.21000000001</v>
+        <v>65787.60000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>68314.36</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
+        <v>66570.38</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4890,64 +4889,66 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64768.53</v>
+        <v>64276.82</v>
       </c>
       <c r="C53" t="n">
-        <v>65270.95</v>
+        <v>64312.02</v>
       </c>
       <c r="D53" t="n">
-        <v>64186.68</v>
+        <v>63208.63</v>
       </c>
       <c r="E53" t="n">
-        <v>65270.95</v>
+        <v>64011.34</v>
       </c>
       <c r="F53" t="n">
-        <v>128.17</v>
+        <v>-1259.61</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H53" t="n">
-        <v>1084.27</v>
+        <v>1103.39</v>
       </c>
       <c r="I53" t="n">
-        <v>64241.33</v>
+        <v>63102.41</v>
       </c>
       <c r="J53" t="n">
-        <v>64234.89</v>
+        <v>64457.75</v>
       </c>
       <c r="K53" t="n">
-        <v>64754.61</v>
+        <v>64728.81</v>
       </c>
       <c r="L53" t="n">
-        <v>65274.32</v>
+        <v>64999.88</v>
       </c>
       <c r="M53" t="n">
-        <v>65530.96</v>
+        <v>65813.08</v>
       </c>
       <c r="N53" t="n">
-        <v>65787.60000000001</v>
+        <v>66626.28999999999</v>
       </c>
       <c r="O53" t="n">
-        <v>66570.38</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66355.22</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
@@ -4955,9 +4956,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4974,74 +4975,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>64276.82</v>
+        <v>63659.53</v>
       </c>
       <c r="C54" t="n">
-        <v>64312.02</v>
+        <v>63691.53</v>
       </c>
       <c r="D54" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E54" t="n">
-        <v>64011.34</v>
+        <v>63492.99</v>
       </c>
       <c r="F54" t="n">
-        <v>-1259.61</v>
+        <v>-518.35</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0081</v>
       </c>
       <c r="H54" t="n">
-        <v>1103.39</v>
+        <v>965.35</v>
       </c>
       <c r="I54" t="n">
-        <v>63102.41</v>
+        <v>62105.24</v>
       </c>
       <c r="J54" t="n">
-        <v>64457.75</v>
+        <v>63033.46</v>
       </c>
       <c r="K54" t="n">
-        <v>64728.81</v>
+        <v>63459.64</v>
       </c>
       <c r="L54" t="n">
-        <v>64999.88</v>
+        <v>63885.83</v>
       </c>
       <c r="M54" t="n">
-        <v>65813.08</v>
+        <v>64563.04</v>
       </c>
       <c r="N54" t="n">
-        <v>66626.28999999999</v>
+        <v>65240.24</v>
       </c>
       <c r="O54" t="n">
-        <v>66355.22</v>
+        <v>65415.41</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5065,71 +5062,69 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>63659.53</v>
+        <v>63190.37</v>
       </c>
       <c r="C55" t="n">
-        <v>63691.53</v>
+        <v>64101</v>
       </c>
       <c r="D55" t="n">
-        <v>62726.18</v>
+        <v>63067.18</v>
       </c>
       <c r="E55" t="n">
-        <v>63492.99</v>
+        <v>63484.1</v>
       </c>
       <c r="F55" t="n">
-        <v>-518.35</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0001</v>
       </c>
       <c r="H55" t="n">
-        <v>965.35</v>
+        <v>1033.82</v>
       </c>
       <c r="I55" t="n">
-        <v>62105.24</v>
+        <v>61760.83</v>
       </c>
       <c r="J55" t="n">
-        <v>63033.46</v>
+        <v>62669.7</v>
       </c>
       <c r="K55" t="n">
-        <v>63459.64</v>
+        <v>63010.31</v>
       </c>
       <c r="L55" t="n">
-        <v>63885.83</v>
+        <v>63350.92</v>
       </c>
       <c r="M55" t="n">
-        <v>64563.04</v>
+        <v>63975.66</v>
       </c>
       <c r="N55" t="n">
-        <v>65240.24</v>
+        <v>64600.41</v>
       </c>
       <c r="O55" t="n">
-        <v>65415.41</v>
+        <v>64656.88</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5142,55 +5137,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63190.37</v>
+        <v>63672.13</v>
       </c>
       <c r="C56" t="n">
-        <v>64101</v>
+        <v>63923</v>
       </c>
       <c r="D56" t="n">
-        <v>63067.18</v>
+        <v>63209.92</v>
       </c>
       <c r="E56" t="n">
-        <v>63484.1</v>
+        <v>63923</v>
       </c>
       <c r="F56" t="n">
-        <v>-8.890000000000001</v>
+        <v>438.9</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0069</v>
       </c>
       <c r="H56" t="n">
-        <v>1033.82</v>
+        <v>713.08</v>
       </c>
       <c r="I56" t="n">
-        <v>61760.83</v>
+        <v>62033.36</v>
       </c>
       <c r="J56" t="n">
-        <v>62669.7</v>
+        <v>62400.29</v>
       </c>
       <c r="K56" t="n">
-        <v>63010.31</v>
+        <v>62967.19</v>
       </c>
       <c r="L56" t="n">
-        <v>63350.92</v>
+        <v>63534.1</v>
       </c>
       <c r="M56" t="n">
-        <v>63975.66</v>
+        <v>64001.01</v>
       </c>
       <c r="N56" t="n">
-        <v>64600.41</v>
+        <v>64467.93</v>
       </c>
       <c r="O56" t="n">
-        <v>64656.88</v>
+        <v>65134.82</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5201,14 +5200,14 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U56" s="8" t="n">
@@ -5231,50 +5230,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>63672.13</v>
+        <v>64643.58</v>
       </c>
       <c r="C57" t="n">
-        <v>63923</v>
+        <v>64643.58</v>
       </c>
       <c r="D57" t="n">
-        <v>63209.92</v>
+        <v>63824.56</v>
       </c>
       <c r="E57" t="n">
-        <v>63923</v>
+        <v>64136.25</v>
       </c>
       <c r="F57" t="n">
-        <v>438.9</v>
+        <v>213.25</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0033</v>
       </c>
       <c r="H57" t="n">
-        <v>713.08</v>
+        <v>819.02</v>
       </c>
       <c r="I57" t="n">
-        <v>62033.36</v>
+        <v>62496.84</v>
       </c>
       <c r="J57" t="n">
-        <v>62400.29</v>
+        <v>63388.19</v>
       </c>
       <c r="K57" t="n">
-        <v>62967.19</v>
+        <v>63566.46</v>
       </c>
       <c r="L57" t="n">
-        <v>63534.1</v>
+        <v>63744.73</v>
       </c>
       <c r="M57" t="n">
-        <v>64001.01</v>
+        <v>64279.54</v>
       </c>
       <c r="N57" t="n">
-        <v>64467.93</v>
+        <v>64814.35</v>
       </c>
       <c r="O57" t="n">
-        <v>65134.82</v>
+        <v>64636.08</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5285,7 +5284,7 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5298,8 +5297,10 @@
       <c r="U57" s="8" t="n">
         <v/>
       </c>
-      <c r="V57" s="8" t="n">
-        <v/>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W57" s="11" t="inlineStr">
         <is>
@@ -5308,57 +5309,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>64643.58</v>
+        <v>64681.55</v>
       </c>
       <c r="C58" t="n">
-        <v>64643.58</v>
+        <v>65436.57</v>
       </c>
       <c r="D58" t="n">
-        <v>63824.56</v>
+        <v>64403.85</v>
       </c>
       <c r="E58" t="n">
-        <v>64136.25</v>
+        <v>65018.95</v>
       </c>
       <c r="F58" t="n">
-        <v>213.25</v>
+        <v>882.7</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0138</v>
       </c>
       <c r="H58" t="n">
-        <v>819.02</v>
+        <v>1032.72</v>
       </c>
       <c r="I58" t="n">
-        <v>62496.84</v>
+        <v>63005.54</v>
       </c>
       <c r="J58" t="n">
-        <v>63388.19</v>
+        <v>63268.32</v>
       </c>
       <c r="K58" t="n">
-        <v>63566.46</v>
+        <v>63726.74</v>
       </c>
       <c r="L58" t="n">
-        <v>63744.73</v>
+        <v>64185.16</v>
       </c>
       <c r="M58" t="n">
-        <v>64279.54</v>
+        <v>64545.76</v>
       </c>
       <c r="N58" t="n">
-        <v>64814.35</v>
+        <v>64906.36</v>
       </c>
       <c r="O58" t="n">
-        <v>64636.08</v>
+        <v>65462.6</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5369,82 +5370,78 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>64681.55</v>
+        <v>65476.44</v>
       </c>
       <c r="C59" t="n">
-        <v>65436.57</v>
+        <v>66249.11</v>
       </c>
       <c r="D59" t="n">
-        <v>64403.85</v>
+        <v>65407.37</v>
       </c>
       <c r="E59" t="n">
-        <v>65018.95</v>
+        <v>65513.99</v>
       </c>
       <c r="F59" t="n">
-        <v>882.7</v>
+        <v>495.04</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.0076</v>
       </c>
       <c r="H59" t="n">
-        <v>1032.72</v>
+        <v>841.74</v>
       </c>
       <c r="I59" t="n">
-        <v>63005.54</v>
+        <v>63371.13</v>
       </c>
       <c r="J59" t="n">
-        <v>63268.32</v>
+        <v>64035.6</v>
       </c>
       <c r="K59" t="n">
-        <v>63726.74</v>
+        <v>64502.59</v>
       </c>
       <c r="L59" t="n">
-        <v>64185.16</v>
+        <v>64969.58</v>
       </c>
       <c r="M59" t="n">
-        <v>64545.76</v>
+        <v>65535.31</v>
       </c>
       <c r="N59" t="n">
-        <v>64906.36</v>
+        <v>66101.03999999999</v>
       </c>
       <c r="O59" t="n">
-        <v>65462.6</v>
+        <v>66469.28999999999</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5455,19 +5452,19 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U59" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V59" s="8" t="n">
@@ -5483,75 +5480,73 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>65476.44</v>
+        <v>65639.62</v>
       </c>
       <c r="C60" t="n">
-        <v>66249.11</v>
+        <v>66410.27</v>
       </c>
       <c r="D60" t="n">
-        <v>65407.37</v>
+        <v>65639.62</v>
       </c>
       <c r="E60" t="n">
-        <v/>
+        <v>66364.2</v>
       </c>
       <c r="F60" t="n">
-        <v/>
+        <v>850.21</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v/>
+        <v>0.013</v>
       </c>
       <c r="H60" t="n">
-        <v>841.74</v>
+        <v>770.66</v>
       </c>
       <c r="I60" t="n">
-        <v>63371.13</v>
+        <v>64565.63</v>
       </c>
       <c r="J60" t="n">
-        <v>64035.6</v>
+        <v>64515.12</v>
       </c>
       <c r="K60" t="n">
-        <v>64502.59</v>
+        <v>65093.12</v>
       </c>
       <c r="L60" t="n">
-        <v>64969.58</v>
+        <v>65671.11</v>
       </c>
       <c r="M60" t="n">
-        <v>65535.31</v>
+        <v>65934.86</v>
       </c>
       <c r="N60" t="n">
-        <v>66101.03999999999</v>
+        <v>66198.60000000001</v>
       </c>
       <c r="O60" t="n">
-        <v>66469.28999999999</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
+        <v>67090.85000000001</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V60" s="8" t="n">

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,50 +637,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70085.60000000001</v>
+        <v>70774.28</v>
       </c>
       <c r="C2" t="n">
-        <v>70667</v>
+        <v>71962.34</v>
       </c>
       <c r="D2" t="n">
-        <v>69302.19</v>
+        <v>70126.14</v>
       </c>
       <c r="E2" t="n">
-        <v>70062.32000000001</v>
+        <v>70474.96000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>594.21</v>
+        <v>412.64</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0059</v>
       </c>
       <c r="H2" t="n">
-        <v>1364.81</v>
+        <v>1836.2</v>
       </c>
       <c r="I2" t="n">
-        <v>66385.25999999999</v>
+        <v>67937.38</v>
       </c>
       <c r="J2" t="n">
-        <v>68187.99000000001</v>
+        <v>68736.37</v>
       </c>
       <c r="K2" t="n">
-        <v>68661.95</v>
+        <v>69379.91</v>
       </c>
       <c r="L2" t="n">
-        <v>69135.92</v>
+        <v>70023.46000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>70274.27</v>
+        <v>70744.73</v>
       </c>
       <c r="N2" t="n">
-        <v>71412.61</v>
+        <v>71466</v>
       </c>
       <c r="O2" t="n">
-        <v>71222.2</v>
+        <v>72031.81</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,8 +701,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -714,74 +719,74 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70774.28</v>
+        <v>70039.89</v>
       </c>
       <c r="C3" t="n">
-        <v>71962.34</v>
+        <v>70081.39</v>
       </c>
       <c r="D3" t="n">
-        <v>70126.14</v>
+        <v>68676.25999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>70474.96000000001</v>
+        <v>68733.14999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>412.64</v>
+        <v>-1741.81</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0247</v>
       </c>
       <c r="H3" t="n">
-        <v>1836.2</v>
+        <v>1405.13</v>
       </c>
       <c r="I3" t="n">
-        <v>67937.38</v>
+        <v>68289.94</v>
       </c>
       <c r="J3" t="n">
-        <v>68736.37</v>
+        <v>68354.12</v>
       </c>
       <c r="K3" t="n">
-        <v>69379.91</v>
+        <v>69556.86</v>
       </c>
       <c r="L3" t="n">
-        <v>70023.46000000001</v>
+        <v>70759.60000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>70744.73</v>
+        <v>71393.06</v>
       </c>
       <c r="N3" t="n">
-        <v>71466</v>
+        <v>72026.52</v>
       </c>
       <c r="O3" t="n">
-        <v>72031.81</v>
+        <v>73798.55</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -791,80 +796,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70039.89</v>
+        <v>68676.06</v>
       </c>
       <c r="C4" t="n">
-        <v>70081.39</v>
+        <v>69788.03</v>
       </c>
       <c r="D4" t="n">
-        <v>68676.25999999999</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>68733.14999999999</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-1741.81</v>
+        <v>1010.92</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0147</v>
       </c>
       <c r="H4" t="n">
-        <v>1405.13</v>
+        <v>2178.54</v>
       </c>
       <c r="I4" t="n">
-        <v>68289.94</v>
+        <v>67271.12</v>
       </c>
       <c r="J4" t="n">
-        <v>68354.12</v>
+        <v>67005.17999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>69556.86</v>
+        <v>68030.58</v>
       </c>
       <c r="L4" t="n">
-        <v>70759.60000000001</v>
+        <v>69055.99000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>71393.06</v>
+        <v>69435.71000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>72026.52</v>
+        <v>69815.44</v>
       </c>
       <c r="O4" t="n">
-        <v>73798.55</v>
+        <v>71486.52</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
@@ -875,57 +886,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68676.06</v>
+        <v>69973.34</v>
       </c>
       <c r="C5" t="n">
-        <v>69788.03</v>
+        <v>70384.59</v>
       </c>
       <c r="D5" t="n">
-        <v>67609.49000000001</v>
+        <v>68904.41</v>
       </c>
       <c r="E5" t="n">
-        <v>69744.07000000001</v>
+        <v>69737.69</v>
       </c>
       <c r="F5" t="n">
-        <v>1010.92</v>
+        <v>-6.38</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0001</v>
       </c>
       <c r="H5" t="n">
-        <v>2178.54</v>
+        <v>1480.19</v>
       </c>
       <c r="I5" t="n">
-        <v>67271.12</v>
+        <v>65430.95</v>
       </c>
       <c r="J5" t="n">
-        <v>67005.17999999999</v>
+        <v>68088.19</v>
       </c>
       <c r="K5" t="n">
-        <v>68030.58</v>
+        <v>68654.8</v>
       </c>
       <c r="L5" t="n">
-        <v>69055.99000000001</v>
+        <v>69221.42</v>
       </c>
       <c r="M5" t="n">
-        <v>69435.71000000001</v>
+        <v>70833.34</v>
       </c>
       <c r="N5" t="n">
-        <v>69815.44</v>
+        <v>72445.25999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>71486.52</v>
+        <v>71966.57000000001</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -933,25 +944,19 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R5" s="6" t="n">
+        <v/>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -963,70 +968,74 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69973.34</v>
+        <v>69460.08</v>
       </c>
       <c r="C6" t="n">
-        <v>70384.59</v>
+        <v>69957.50999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>68904.41</v>
+        <v>68003.92</v>
       </c>
       <c r="E6" t="n">
-        <v>69737.69</v>
+        <v>68256.96000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.38</v>
+        <v>-1480.73</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0212</v>
       </c>
       <c r="H6" t="n">
-        <v>1480.19</v>
+        <v>1953.59</v>
       </c>
       <c r="I6" t="n">
-        <v>65430.95</v>
+        <v>67424.22</v>
       </c>
       <c r="J6" t="n">
-        <v>68088.19</v>
+        <v>68304.09</v>
       </c>
       <c r="K6" t="n">
-        <v>68654.8</v>
+        <v>68997.59</v>
       </c>
       <c r="L6" t="n">
-        <v>69221.42</v>
+        <v>69691.09</v>
       </c>
       <c r="M6" t="n">
-        <v>70833.34</v>
+        <v>70477.78</v>
       </c>
       <c r="N6" t="n">
-        <v>72445.25999999999</v>
+        <v>71264.47</v>
       </c>
       <c r="O6" t="n">
-        <v>71966.57000000001</v>
+        <v>71864.78</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1038,76 +1047,70 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69460.08</v>
+        <v>67704.16</v>
       </c>
       <c r="C7" t="n">
-        <v>69957.50999999999</v>
+        <v>68432.67999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>68003.92</v>
+        <v>66819.05</v>
       </c>
       <c r="E7" t="n">
-        <v>68256.96000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="F7" t="n">
-        <v>-1480.73</v>
+        <v>-1437.91</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="H7" t="n">
-        <v>1953.59</v>
+        <v>1613.63</v>
       </c>
       <c r="I7" t="n">
-        <v>67424.22</v>
+        <v>66050.34</v>
       </c>
       <c r="J7" t="n">
-        <v>68304.09</v>
+        <v>65941.5</v>
       </c>
       <c r="K7" t="n">
-        <v>68997.59</v>
+        <v>67280.17</v>
       </c>
       <c r="L7" t="n">
-        <v>69691.09</v>
+        <v>68618.84</v>
       </c>
       <c r="M7" t="n">
-        <v>70477.78</v>
+        <v>69233.75</v>
       </c>
       <c r="N7" t="n">
-        <v>71264.47</v>
+        <v>69848.67</v>
       </c>
       <c r="O7" t="n">
-        <v>71864.78</v>
+        <v>71911.09</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
@@ -1134,50 +1137,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>67704.16</v>
+        <v>67046.37</v>
       </c>
       <c r="C8" t="n">
-        <v>68432.67999999999</v>
+        <v>68447.89</v>
       </c>
       <c r="D8" t="n">
-        <v>66819.05</v>
+        <v>67008.89</v>
       </c>
       <c r="E8" t="n">
-        <v>66819.05</v>
+        <v>67743.85000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-1437.91</v>
+        <v>924.8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0211</v>
+        <v>0.0138</v>
       </c>
       <c r="H8" t="n">
-        <v>1613.63</v>
+        <v>1439</v>
       </c>
       <c r="I8" t="n">
-        <v>66050.34</v>
+        <v>65205.41</v>
       </c>
       <c r="J8" t="n">
-        <v>65941.5</v>
+        <v>64802.01</v>
       </c>
       <c r="K8" t="n">
-        <v>67280.17</v>
+        <v>66012.23</v>
       </c>
       <c r="L8" t="n">
-        <v>68618.84</v>
+        <v>67222.46000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>69233.75</v>
+        <v>67625.86</v>
       </c>
       <c r="N8" t="n">
-        <v>69848.67</v>
+        <v>68029.27</v>
       </c>
       <c r="O8" t="n">
-        <v>71911.09</v>
+        <v>70046.31</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1185,21 +1188,23 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1209,55 +1214,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67046.37</v>
+        <v>68526.72</v>
       </c>
       <c r="C9" t="n">
-        <v>68447.89</v>
+        <v>69374.86</v>
       </c>
       <c r="D9" t="n">
-        <v>67008.89</v>
+        <v>68271.91</v>
       </c>
       <c r="E9" t="n">
-        <v>67743.85000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F9" t="n">
-        <v>924.8</v>
+        <v>813.88</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.012</v>
       </c>
       <c r="H9" t="n">
-        <v>1439</v>
+        <v>1102.95</v>
       </c>
       <c r="I9" t="n">
-        <v>65205.41</v>
+        <v>65569.89</v>
       </c>
       <c r="J9" t="n">
-        <v>64802.01</v>
+        <v>66312.58</v>
       </c>
       <c r="K9" t="n">
-        <v>66012.23</v>
+        <v>67024.35000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>67222.46000000001</v>
+        <v>67736.12</v>
       </c>
       <c r="M9" t="n">
-        <v>67625.86</v>
+        <v>68463.35000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>68029.27</v>
+        <v>69190.58</v>
       </c>
       <c r="O9" t="n">
-        <v>70046.31</v>
+        <v>69886.89</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1300,74 +1309,76 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68526.72</v>
+        <v>68410.63</v>
       </c>
       <c r="C10" t="n">
-        <v>69374.86</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>68271.91</v>
+        <v>66653.11</v>
       </c>
       <c r="E10" t="n">
-        <v>68557.73</v>
+        <v>67242.73</v>
       </c>
       <c r="F10" t="n">
-        <v>813.88</v>
+        <v>-1315</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0192</v>
       </c>
       <c r="H10" t="n">
-        <v>1102.95</v>
+        <v>2425.1</v>
       </c>
       <c r="I10" t="n">
-        <v>65569.89</v>
+        <v>67168.95</v>
       </c>
       <c r="J10" t="n">
-        <v>66312.58</v>
+        <v>67321.95</v>
       </c>
       <c r="K10" t="n">
-        <v>67024.35000000001</v>
+        <v>68006.25</v>
       </c>
       <c r="L10" t="n">
-        <v>67736.12</v>
+        <v>68690.55</v>
       </c>
       <c r="M10" t="n">
-        <v>68463.35000000001</v>
+        <v>69109.2</v>
       </c>
       <c r="N10" t="n">
-        <v>69190.58</v>
+        <v>69527.85000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>69886.89</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
+        <v>70477.81</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1377,78 +1388,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>68410.63</v>
+        <v>67002.94</v>
       </c>
       <c r="C11" t="n">
-        <v>69078.21000000001</v>
+        <v>67800.17999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>66653.11</v>
+        <v>66268.60000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>67242.73</v>
+        <v>67743.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-1315</v>
+        <v>500.77</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0074</v>
       </c>
       <c r="H11" t="n">
-        <v>2425.1</v>
+        <v>1531.58</v>
       </c>
       <c r="I11" t="n">
-        <v>67168.95</v>
+        <v>64228.01</v>
       </c>
       <c r="J11" t="n">
-        <v>67321.95</v>
+        <v>64506.16</v>
       </c>
       <c r="K11" t="n">
-        <v>68006.25</v>
+        <v>66030.17999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>68690.55</v>
+        <v>67554.19</v>
       </c>
       <c r="M11" t="n">
-        <v>69109.2</v>
+        <v>68455.28</v>
       </c>
       <c r="N11" t="n">
-        <v>69527.85000000001</v>
+        <v>69356.36</v>
       </c>
       <c r="O11" t="n">
-        <v>70477.81</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>71503.31</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1465,55 +1466,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67002.94</v>
+        <v>67989.74000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>67800.17999999999</v>
+        <v>68798.24000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>66268.60000000001</v>
+        <v>67833.17</v>
       </c>
       <c r="E12" t="n">
-        <v>67743.5</v>
+        <v>68751.50999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>500.77</v>
+        <v>1008.01</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0149</v>
       </c>
       <c r="H12" t="n">
-        <v>1531.58</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>64228.01</v>
+        <v>64737.02</v>
       </c>
       <c r="J12" t="n">
-        <v>64506.16</v>
+        <v>66566.48</v>
       </c>
       <c r="K12" t="n">
-        <v>66030.17999999999</v>
+        <v>66977.71000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>67554.19</v>
+        <v>67388.95</v>
       </c>
       <c r="M12" t="n">
-        <v>68455.28</v>
+        <v>68509.28999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>69356.36</v>
+        <v>69629.63</v>
       </c>
       <c r="O12" t="n">
-        <v>71503.31</v>
+        <v>69331.75999999999</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1526,11 +1531,13 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1545,77 +1552,81 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67989.74000000001</v>
+        <v>67900.42999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>68798.24000000001</v>
+        <v>68069.82000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>67833.17</v>
+        <v>66499.49000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>68751.50999999999</v>
+        <v>66835.53999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1008.01</v>
+        <v>-1915.97</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0279</v>
       </c>
       <c r="H13" t="n">
-        <v>965.0700000000001</v>
+        <v>1570.33</v>
       </c>
       <c r="I13" t="n">
-        <v>64737.02</v>
+        <v>66868.10000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>66566.48</v>
+        <v>68004.34</v>
       </c>
       <c r="K13" t="n">
-        <v>66977.71000000001</v>
+        <v>68268.97</v>
       </c>
       <c r="L13" t="n">
-        <v>67388.95</v>
+        <v>68533.61</v>
       </c>
       <c r="M13" t="n">
-        <v>68509.28999999999</v>
+        <v>69234.03999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>69629.63</v>
+        <v>69934.48</v>
       </c>
       <c r="O13" t="n">
-        <v>69331.75999999999</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
+        <v>69763.31</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1627,59 +1638,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>67900.42999999999</v>
+        <v>66339.85000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>68069.82000000001</v>
+        <v>66441.77</v>
       </c>
       <c r="D14" t="n">
-        <v>66499.49000000001</v>
+        <v>62704.6</v>
       </c>
       <c r="E14" t="n">
-        <v>66835.53999999999</v>
+        <v>64141.12</v>
       </c>
       <c r="F14" t="n">
-        <v>-1915.97</v>
+        <v>-2694.42</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0403</v>
       </c>
       <c r="H14" t="n">
-        <v>1570.33</v>
+        <v>3737.17</v>
       </c>
       <c r="I14" t="n">
-        <v>66868.10000000001</v>
+        <v>64929.16</v>
       </c>
       <c r="J14" t="n">
-        <v>68004.34</v>
+        <v>65040.65</v>
       </c>
       <c r="K14" t="n">
-        <v>68268.97</v>
+        <v>66050.38</v>
       </c>
       <c r="L14" t="n">
-        <v>68533.61</v>
+        <v>67060.10000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>69234.03999999999</v>
+        <v>67620.7</v>
       </c>
       <c r="N14" t="n">
-        <v>69934.48</v>
+        <v>68181.31</v>
       </c>
       <c r="O14" t="n">
-        <v>69763.31</v>
+        <v>69640.14999999999</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -1720,74 +1727,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66339.85000000001</v>
+        <v>64544.05</v>
       </c>
       <c r="C15" t="n">
-        <v>66441.77</v>
+        <v>66232.19</v>
       </c>
       <c r="D15" t="n">
-        <v>62704.6</v>
+        <v>64203.47</v>
       </c>
       <c r="E15" t="n">
-        <v>64141.12</v>
+        <v>66232.19</v>
       </c>
       <c r="F15" t="n">
-        <v>-2694.42</v>
+        <v>2091.07</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0326</v>
       </c>
       <c r="H15" t="n">
-        <v>3737.17</v>
+        <v>2028.72</v>
       </c>
       <c r="I15" t="n">
-        <v>64929.16</v>
+        <v>58967.43</v>
       </c>
       <c r="J15" t="n">
-        <v>65040.65</v>
+        <v>60187.92</v>
       </c>
       <c r="K15" t="n">
-        <v>66050.38</v>
+        <v>62272.54</v>
       </c>
       <c r="L15" t="n">
-        <v>67060.10000000001</v>
+        <v>64357.15</v>
       </c>
       <c r="M15" t="n">
-        <v>67620.7</v>
+        <v>66009.71000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>68181.31</v>
+        <v>67662.25999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>69640.14999999999</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
+        <v>70178.95</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1799,55 +1802,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>64544.05</v>
+        <v>66449.27</v>
       </c>
       <c r="C16" t="n">
-        <v>66232.19</v>
+        <v>67592.2</v>
       </c>
       <c r="D16" t="n">
-        <v>64203.47</v>
+        <v>65955.60000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>66232.19</v>
+        <v>66115.60000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>2091.07</v>
+        <v>-116.59</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0326</v>
+        <v>-0.0018</v>
       </c>
       <c r="H16" t="n">
-        <v>2028.72</v>
+        <v>1636.6</v>
       </c>
       <c r="I16" t="n">
-        <v>58967.43</v>
+        <v>62174.75</v>
       </c>
       <c r="J16" t="n">
-        <v>60187.92</v>
+        <v>64710.65</v>
       </c>
       <c r="K16" t="n">
-        <v>62272.54</v>
+        <v>65217.83</v>
       </c>
       <c r="L16" t="n">
-        <v>64357.15</v>
+        <v>65725.00999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>66009.71000000001</v>
+        <v>67246.55</v>
       </c>
       <c r="N16" t="n">
-        <v>67662.25999999999</v>
+        <v>68768.09</v>
       </c>
       <c r="O16" t="n">
-        <v>70178.95</v>
+        <v>68260.91</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1860,12 +1867,12 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U16" s="8" t="n">
@@ -1888,50 +1895,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66449.27</v>
+        <v>66421.00999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>67592.2</v>
+        <v>67022.37</v>
       </c>
       <c r="D17" t="n">
-        <v>65955.60000000001</v>
+        <v>66208.66</v>
       </c>
       <c r="E17" t="n">
-        <v>66115.60000000001</v>
+        <v>66422.60000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-116.59</v>
+        <v>307</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0046</v>
       </c>
       <c r="H17" t="n">
-        <v>1636.6</v>
+        <v>813.71</v>
       </c>
       <c r="I17" t="n">
-        <v>62174.75</v>
+        <v>64319</v>
       </c>
       <c r="J17" t="n">
-        <v>64710.65</v>
+        <v>64149.85</v>
       </c>
       <c r="K17" t="n">
-        <v>65217.83</v>
+        <v>65297.3</v>
       </c>
       <c r="L17" t="n">
-        <v>65725.00999999999</v>
+        <v>66444.75</v>
       </c>
       <c r="M17" t="n">
-        <v>67246.55</v>
+        <v>66933.89999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>68768.09</v>
+        <v>67423.05</v>
       </c>
       <c r="O17" t="n">
-        <v>68260.91</v>
+        <v>69228.8</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1942,9 +1949,9 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
@@ -1972,69 +1979,73 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>66421.00999999999</v>
+        <v>65584.25</v>
       </c>
       <c r="C18" t="n">
-        <v>67022.37</v>
+        <v>65720.81</v>
       </c>
       <c r="D18" t="n">
-        <v>66208.66</v>
+        <v>64201.03</v>
       </c>
       <c r="E18" t="n">
-        <v>66422.60000000001</v>
+        <v>64611.15</v>
       </c>
       <c r="F18" t="n">
-        <v>307</v>
+        <v>-1811.45</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0273</v>
       </c>
       <c r="H18" t="n">
-        <v>813.71</v>
+        <v>1519.78</v>
       </c>
       <c r="I18" t="n">
-        <v>64319</v>
+        <v>65394.95</v>
       </c>
       <c r="J18" t="n">
-        <v>64149.85</v>
+        <v>65512.44</v>
       </c>
       <c r="K18" t="n">
-        <v>65297.3</v>
+        <v>66015.75</v>
       </c>
       <c r="L18" t="n">
-        <v>66444.75</v>
+        <v>66519.06</v>
       </c>
       <c r="M18" t="n">
-        <v>66933.89999999999</v>
+        <v>66829.46000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>67423.05</v>
+        <v>67139.86</v>
       </c>
       <c r="O18" t="n">
-        <v>69228.8</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+        <v>67836.08</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2047,78 +2058,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>65584.25</v>
+        <v>65164.98</v>
       </c>
       <c r="C19" t="n">
-        <v>65720.81</v>
+        <v>65220.69</v>
       </c>
       <c r="D19" t="n">
-        <v>64201.03</v>
+        <v>64123.4</v>
       </c>
       <c r="E19" t="n">
-        <v>64611.15</v>
+        <v>64931.19</v>
       </c>
       <c r="F19" t="n">
-        <v>-1811.45</v>
+        <v>320.04</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.005</v>
       </c>
       <c r="H19" t="n">
-        <v>1519.78</v>
+        <v>1097.29</v>
       </c>
       <c r="I19" t="n">
-        <v>65394.95</v>
+        <v>62681.25</v>
       </c>
       <c r="J19" t="n">
-        <v>65512.44</v>
+        <v>62916.48</v>
       </c>
       <c r="K19" t="n">
-        <v>66015.75</v>
+        <v>63851.26</v>
       </c>
       <c r="L19" t="n">
-        <v>66519.06</v>
+        <v>64786.04</v>
       </c>
       <c r="M19" t="n">
-        <v>66829.46000000001</v>
+        <v>65371.04</v>
       </c>
       <c r="N19" t="n">
-        <v>67139.86</v>
+        <v>65956.03999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>67836.08</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>67240.59</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2135,68 +2136,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>65164.98</v>
+        <v>64539.92</v>
       </c>
       <c r="C20" t="n">
-        <v>65220.69</v>
+        <v>64573.18</v>
       </c>
       <c r="D20" t="n">
-        <v>64123.4</v>
+        <v>61923.6</v>
       </c>
       <c r="E20" t="n">
-        <v>64931.19</v>
+        <v>62364.92</v>
       </c>
       <c r="F20" t="n">
-        <v>320.04</v>
+        <v>-2566.27</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0395</v>
       </c>
       <c r="H20" t="n">
-        <v>1097.29</v>
+        <v>2649.58</v>
       </c>
       <c r="I20" t="n">
-        <v>62681.25</v>
+        <v>63026.11</v>
       </c>
       <c r="J20" t="n">
-        <v>62916.48</v>
+        <v>63963.47</v>
       </c>
       <c r="K20" t="n">
-        <v>63851.26</v>
+        <v>64382.54</v>
       </c>
       <c r="L20" t="n">
-        <v>64786.04</v>
+        <v>64801.62</v>
       </c>
       <c r="M20" t="n">
-        <v>65371.04</v>
+        <v>65479.84</v>
       </c>
       <c r="N20" t="n">
-        <v>65956.03999999999</v>
+        <v>66158.06</v>
       </c>
       <c r="O20" t="n">
-        <v>67240.59</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>66317.98</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2213,73 +2224,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>64539.92</v>
+        <v>62734.68</v>
       </c>
       <c r="C21" t="n">
-        <v>64573.18</v>
+        <v>63138.04</v>
       </c>
       <c r="D21" t="n">
-        <v>61923.6</v>
+        <v>60448.9</v>
       </c>
       <c r="E21" t="n">
-        <v>62364.92</v>
+        <v>61434.19</v>
       </c>
       <c r="F21" t="n">
-        <v>-2566.27</v>
+        <v>-930.73</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0149</v>
       </c>
       <c r="H21" t="n">
-        <v>2649.58</v>
+        <v>2689.14</v>
       </c>
       <c r="I21" t="n">
-        <v>63026.11</v>
+        <v>59274.02</v>
       </c>
       <c r="J21" t="n">
-        <v>63963.47</v>
+        <v>59273.61</v>
       </c>
       <c r="K21" t="n">
-        <v>64382.54</v>
+        <v>61040.13</v>
       </c>
       <c r="L21" t="n">
-        <v>64801.62</v>
+        <v>62806.66</v>
       </c>
       <c r="M21" t="n">
-        <v>65479.84</v>
+        <v>63689.71</v>
       </c>
       <c r="N21" t="n">
-        <v>66158.06</v>
+        <v>64572.77</v>
       </c>
       <c r="O21" t="n">
-        <v>66317.98</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>67222.75999999999</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
@@ -2306,50 +2309,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>62734.68</v>
+        <v>61258.34</v>
       </c>
       <c r="C22" t="n">
-        <v>63138.04</v>
+        <v>62924.84</v>
       </c>
       <c r="D22" t="n">
-        <v>60448.9</v>
+        <v>61049.7</v>
       </c>
       <c r="E22" t="n">
-        <v>61434.19</v>
+        <v>61867.43</v>
       </c>
       <c r="F22" t="n">
-        <v>-930.73</v>
+        <v>433.24</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0071</v>
       </c>
       <c r="H22" t="n">
-        <v>2689.14</v>
+        <v>1875.14</v>
       </c>
       <c r="I22" t="n">
-        <v>59274.02</v>
+        <v>57759.76</v>
       </c>
       <c r="J22" t="n">
-        <v>59273.61</v>
+        <v>58565.41</v>
       </c>
       <c r="K22" t="n">
-        <v>61040.13</v>
+        <v>60089.62</v>
       </c>
       <c r="L22" t="n">
-        <v>62806.66</v>
+        <v>61613.83</v>
       </c>
       <c r="M22" t="n">
-        <v>63689.71</v>
+        <v>62778.76</v>
       </c>
       <c r="N22" t="n">
-        <v>64572.77</v>
+        <v>63943.69</v>
       </c>
       <c r="O22" t="n">
-        <v>67222.75999999999</v>
+        <v>65827.17999999999</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2357,18 +2360,18 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2381,55 +2384,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>61258.34</v>
+        <v>61957.1</v>
       </c>
       <c r="C23" t="n">
-        <v>62924.84</v>
+        <v>65364.73</v>
       </c>
       <c r="D23" t="n">
-        <v>61049.7</v>
+        <v>61948.23</v>
       </c>
       <c r="E23" t="n">
-        <v>61867.43</v>
+        <v>64362.02</v>
       </c>
       <c r="F23" t="n">
-        <v>433.24</v>
+        <v>2494.59</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0403</v>
       </c>
       <c r="H23" t="n">
-        <v>1875.14</v>
+        <v>3416.5</v>
       </c>
       <c r="I23" t="n">
-        <v>57759.76</v>
+        <v>59174.56</v>
       </c>
       <c r="J23" t="n">
-        <v>58565.41</v>
+        <v>59932.37</v>
       </c>
       <c r="K23" t="n">
-        <v>60089.62</v>
+        <v>60929.86</v>
       </c>
       <c r="L23" t="n">
-        <v>61613.83</v>
+        <v>61927.35</v>
       </c>
       <c r="M23" t="n">
-        <v>62778.76</v>
+        <v>62805</v>
       </c>
       <c r="N23" t="n">
-        <v>63943.69</v>
+        <v>63682.65</v>
       </c>
       <c r="O23" t="n">
-        <v>65827.17999999999</v>
+        <v>64799.98</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2442,7 +2449,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2450,70 +2457,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>61957.1</v>
+        <v>63834.95</v>
       </c>
       <c r="C24" t="n">
-        <v>65364.73</v>
+        <v>63905.12</v>
       </c>
       <c r="D24" t="n">
-        <v>61948.23</v>
+        <v>62703.47</v>
       </c>
       <c r="E24" t="n">
-        <v>64362.02</v>
+        <v>63754.9</v>
       </c>
       <c r="F24" t="n">
-        <v>2494.59</v>
+        <v>-607.12</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0403</v>
+        <v>-0.0094</v>
       </c>
       <c r="H24" t="n">
-        <v>3416.5</v>
+        <v>1201.65</v>
       </c>
       <c r="I24" t="n">
-        <v>59174.56</v>
+        <v>58531.73</v>
       </c>
       <c r="J24" t="n">
-        <v>59932.37</v>
+        <v>61298.29</v>
       </c>
       <c r="K24" t="n">
-        <v>60929.86</v>
+        <v>62653.77</v>
       </c>
       <c r="L24" t="n">
-        <v>61927.35</v>
+        <v>64009.25</v>
       </c>
       <c r="M24" t="n">
-        <v>62805</v>
+        <v>66070.27</v>
       </c>
       <c r="N24" t="n">
-        <v>63682.65</v>
+        <v>68131.28999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>64799.98</v>
+        <v>68781.23</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2524,80 +2531,78 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63834.95</v>
+        <v>63995.28</v>
       </c>
       <c r="C25" t="n">
-        <v>63905.12</v>
+        <v>64240.5</v>
       </c>
       <c r="D25" t="n">
-        <v>62703.47</v>
+        <v>62864.43</v>
       </c>
       <c r="E25" t="n">
-        <v>63754.9</v>
+        <v>63957.53</v>
       </c>
       <c r="F25" t="n">
-        <v>-607.12</v>
+        <v>202.63</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0032</v>
       </c>
       <c r="H25" t="n">
-        <v>1201.65</v>
+        <v>1376.07</v>
       </c>
       <c r="I25" t="n">
-        <v>58531.73</v>
+        <v>61501.82</v>
       </c>
       <c r="J25" t="n">
-        <v>61298.29</v>
+        <v>62778.55</v>
       </c>
       <c r="K25" t="n">
-        <v>62653.77</v>
+        <v>63154.07</v>
       </c>
       <c r="L25" t="n">
-        <v>64009.25</v>
+        <v>63529.6</v>
       </c>
       <c r="M25" t="n">
-        <v>66070.27</v>
+        <v>64355.72</v>
       </c>
       <c r="N25" t="n">
-        <v>68131.28999999999</v>
+        <v>65181.85</v>
       </c>
       <c r="O25" t="n">
-        <v>68781.23</v>
+        <v>65106.77</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2605,16 +2610,20 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2627,59 +2636,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63995.28</v>
+        <v>64565.27</v>
       </c>
       <c r="C26" t="n">
-        <v>64240.5</v>
+        <v>66302.52</v>
       </c>
       <c r="D26" t="n">
-        <v>62864.43</v>
+        <v>64555.52</v>
       </c>
       <c r="E26" t="n">
-        <v>63957.53</v>
+        <v>66300.44</v>
       </c>
       <c r="F26" t="n">
-        <v>202.63</v>
+        <v>2342.91</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0366</v>
       </c>
       <c r="H26" t="n">
-        <v>1376.07</v>
+        <v>1747</v>
       </c>
       <c r="I26" t="n">
-        <v>61501.82</v>
+        <v>61488.36</v>
       </c>
       <c r="J26" t="n">
-        <v>62778.55</v>
+        <v>62783.99</v>
       </c>
       <c r="K26" t="n">
-        <v>63154.07</v>
+        <v>63269.5</v>
       </c>
       <c r="L26" t="n">
-        <v>63529.6</v>
+        <v>63755</v>
       </c>
       <c r="M26" t="n">
-        <v>64355.72</v>
+        <v>64645.57</v>
       </c>
       <c r="N26" t="n">
-        <v>65181.85</v>
+        <v>65536.13</v>
       </c>
       <c r="O26" t="n">
-        <v>65106.77</v>
+        <v>65616.57000000001</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2687,10 +2692,8 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
@@ -2699,14 +2702,18 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
@@ -2718,134 +2725,136 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64565.27</v>
+        <v>65896</v>
       </c>
       <c r="C27" t="n">
-        <v>66302.52</v>
+        <v>65983.13</v>
       </c>
       <c r="D27" t="n">
-        <v>64555.52</v>
+        <v>64942.07</v>
       </c>
       <c r="E27" t="n">
-        <v>66300.44</v>
+        <v>65683.25999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>2342.91</v>
+        <v>-617.1799999999999</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0366</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>1747</v>
+        <v>1041.06</v>
       </c>
       <c r="I27" t="n">
-        <v>61488.36</v>
+        <v>62808.52</v>
       </c>
       <c r="J27" t="n">
-        <v>62783.99</v>
+        <v>64989.14</v>
       </c>
       <c r="K27" t="n">
-        <v>63269.5</v>
+        <v>65426.94</v>
       </c>
       <c r="L27" t="n">
-        <v>63755</v>
+        <v>65864.73</v>
       </c>
       <c r="M27" t="n">
-        <v>64645.57</v>
+        <v>67173.94</v>
       </c>
       <c r="N27" t="n">
-        <v>65536.13</v>
+        <v>68483.14999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>65616.57000000001</v>
+        <v>68049.53</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>65896</v>
+        <v>65746.13</v>
       </c>
       <c r="C28" t="n">
-        <v>65983.13</v>
+        <v>65990.72</v>
       </c>
       <c r="D28" t="n">
-        <v>64942.07</v>
+        <v>64651.49</v>
       </c>
       <c r="E28" t="n">
-        <v>65683.25999999999</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-617.1799999999999</v>
+        <v>-76.55</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="H28" t="n">
-        <v>1041.06</v>
+        <v>1339.23</v>
       </c>
       <c r="I28" t="n">
-        <v>62808.52</v>
+        <v>63901.01</v>
       </c>
       <c r="J28" t="n">
-        <v>64989.14</v>
+        <v>64752.52</v>
       </c>
       <c r="K28" t="n">
-        <v>65426.94</v>
+        <v>65162.73</v>
       </c>
       <c r="L28" t="n">
-        <v>65864.73</v>
+        <v>65572.92999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>67173.94</v>
+        <v>66203.78999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>68483.14999999999</v>
+        <v>66834.64999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>68049.53</v>
+        <v>67024.2</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2860,9 +2869,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2888,74 +2897,74 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>65746.13</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>65990.72</v>
+        <v>67006.84</v>
       </c>
       <c r="D29" t="n">
-        <v>64651.49</v>
+        <v>65848.58</v>
       </c>
       <c r="E29" t="n">
-        <v>65606.71000000001</v>
+        <v>66970.22</v>
       </c>
       <c r="F29" t="n">
-        <v>-76.55</v>
+        <v>1363.51</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0208</v>
       </c>
       <c r="H29" t="n">
-        <v>1339.23</v>
+        <v>1158.27</v>
       </c>
       <c r="I29" t="n">
-        <v>63901.01</v>
+        <v>63312.26</v>
       </c>
       <c r="J29" t="n">
-        <v>64752.52</v>
+        <v>64410.28</v>
       </c>
       <c r="K29" t="n">
-        <v>65162.73</v>
+        <v>64937.1</v>
       </c>
       <c r="L29" t="n">
-        <v>65572.92999999999</v>
+        <v>65463.91</v>
       </c>
       <c r="M29" t="n">
-        <v>66203.78999999999</v>
+        <v>66276.33</v>
       </c>
       <c r="N29" t="n">
-        <v>66834.64999999999</v>
+        <v>67088.75</v>
       </c>
       <c r="O29" t="n">
-        <v>67024.2</v>
+        <v>67329.95</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2965,59 +2974,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>65905.10000000001</v>
+        <v>66994.05</v>
       </c>
       <c r="C30" t="n">
-        <v>67006.84</v>
+        <v>67569.36</v>
       </c>
       <c r="D30" t="n">
-        <v>65848.58</v>
+        <v>66735.75999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>66970.22</v>
+        <v>67524.06</v>
       </c>
       <c r="F30" t="n">
-        <v>1363.51</v>
+        <v>553.84</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="H30" t="n">
-        <v>1158.27</v>
+        <v>833.6</v>
       </c>
       <c r="I30" t="n">
-        <v>63312.26</v>
+        <v>64690.31</v>
       </c>
       <c r="J30" t="n">
-        <v>64410.28</v>
+        <v>66083.21000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>64937.1</v>
+        <v>66391.09</v>
       </c>
       <c r="L30" t="n">
-        <v>65463.91</v>
+        <v>66698.96000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>66276.33</v>
+        <v>67549.35000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>67088.75</v>
+        <v>68399.74000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>67329.95</v>
+        <v>68165.11</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3035,13 +3040,11 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3056,50 +3059,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>66994.05</v>
+        <v>68033.17</v>
       </c>
       <c r="C31" t="n">
-        <v>67569.36</v>
+        <v>68799.71000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>66735.75999999999</v>
+        <v>68006.17</v>
       </c>
       <c r="E31" t="n">
-        <v>67524.06</v>
+        <v>68308.59</v>
       </c>
       <c r="F31" t="n">
-        <v>553.84</v>
+        <v>784.53</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0116</v>
       </c>
       <c r="H31" t="n">
-        <v>833.6</v>
+        <v>793.54</v>
       </c>
       <c r="I31" t="n">
-        <v>64690.31</v>
+        <v>65902.16</v>
       </c>
       <c r="J31" t="n">
-        <v>66083.21000000001</v>
+        <v>66876.21000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>66391.09</v>
+        <v>67107.25999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>66698.96000000001</v>
+        <v>67338.31</v>
       </c>
       <c r="M31" t="n">
-        <v>67549.35000000001</v>
+        <v>67940.86</v>
       </c>
       <c r="N31" t="n">
-        <v>68399.74000000001</v>
+        <v>68543.42</v>
       </c>
       <c r="O31" t="n">
-        <v>68165.11</v>
+        <v>68402.96000000001</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3117,14 +3120,18 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
@@ -3136,50 +3143,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>68033.17</v>
+        <v>68811.17</v>
       </c>
       <c r="C32" t="n">
-        <v>68799.71000000001</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>68006.17</v>
+        <v>68471.14999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>68308.59</v>
+        <v>68713.8</v>
       </c>
       <c r="F32" t="n">
-        <v>784.53</v>
+        <v>405.2</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0059</v>
       </c>
       <c r="H32" t="n">
-        <v>793.54</v>
+        <v>1137.09</v>
       </c>
       <c r="I32" t="n">
-        <v>65902.16</v>
+        <v>67212.63</v>
       </c>
       <c r="J32" t="n">
-        <v>66876.21000000001</v>
+        <v>67467.88</v>
       </c>
       <c r="K32" t="n">
-        <v>67107.25999999999</v>
+        <v>67911.82000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>67338.31</v>
+        <v>68355.77</v>
       </c>
       <c r="M32" t="n">
-        <v>67940.86</v>
+        <v>68705.36</v>
       </c>
       <c r="N32" t="n">
-        <v>68543.42</v>
+        <v>69054.96000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>68402.96000000001</v>
+        <v>69593.25</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3197,7 +3204,7 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U32" s="8" t="inlineStr">
@@ -3207,7 +3214,7 @@
       </c>
       <c r="V32" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W32" s="9" t="inlineStr">
@@ -3220,50 +3227,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>68811.17</v>
+        <v>68882.06</v>
       </c>
       <c r="C33" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>68471.14999999999</v>
+        <v>68492.03999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>68713.8</v>
+        <v>69220.25</v>
       </c>
       <c r="F33" t="n">
-        <v>405.2</v>
+        <v>506.45</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="H33" t="n">
-        <v>1137.09</v>
+        <v>733.53</v>
       </c>
       <c r="I33" t="n">
-        <v>67212.63</v>
+        <v>67334.05</v>
       </c>
       <c r="J33" t="n">
-        <v>67467.88</v>
+        <v>67413.75</v>
       </c>
       <c r="K33" t="n">
-        <v>67911.82000000001</v>
+        <v>68145.25</v>
       </c>
       <c r="L33" t="n">
-        <v>68355.77</v>
+        <v>68876.75</v>
       </c>
       <c r="M33" t="n">
-        <v>68705.36</v>
+        <v>69282.34</v>
       </c>
       <c r="N33" t="n">
-        <v>69054.96000000001</v>
+        <v>69687.94</v>
       </c>
       <c r="O33" t="n">
-        <v>69593.25</v>
+        <v>70745.34</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3284,163 +3291,163 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>68882.06</v>
+        <v>68847.35000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>69225.57000000001</v>
+        <v>69093.2</v>
       </c>
       <c r="D34" t="n">
-        <v>68492.03999999999</v>
+        <v>67368.96000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>69220.25</v>
+        <v>67460.73</v>
       </c>
       <c r="F34" t="n">
-        <v>506.45</v>
+        <v>-1759.52</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0254</v>
       </c>
       <c r="H34" t="n">
-        <v>733.53</v>
+        <v>1724.24</v>
       </c>
       <c r="I34" t="n">
-        <v>67334.05</v>
+        <v>67758.50999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>67413.75</v>
+        <v>68667.44</v>
       </c>
       <c r="K34" t="n">
-        <v>68145.25</v>
+        <v>68853.48</v>
       </c>
       <c r="L34" t="n">
-        <v>68876.75</v>
+        <v>69039.53</v>
       </c>
       <c r="M34" t="n">
-        <v>69282.34</v>
+        <v>69587.02</v>
       </c>
       <c r="N34" t="n">
-        <v>69687.94</v>
+        <v>70134.5</v>
       </c>
       <c r="O34" t="n">
-        <v>70745.34</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
+        <v>69959.10000000001</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>68847.35000000001</v>
+        <v>66812.27</v>
       </c>
       <c r="C35" t="n">
-        <v>69093.2</v>
+        <v>66833.50999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>67368.96000000001</v>
+        <v>65133.98</v>
       </c>
       <c r="E35" t="n">
-        <v>67460.73</v>
+        <v>65326.42</v>
       </c>
       <c r="F35" t="n">
-        <v>-1759.52</v>
+        <v>-2134.3</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="H35" t="n">
-        <v>1724.24</v>
+        <v>1699.53</v>
       </c>
       <c r="I35" t="n">
-        <v>67758.50999999999</v>
+        <v>65644.72</v>
       </c>
       <c r="J35" t="n">
-        <v>68667.44</v>
+        <v>65351.31</v>
       </c>
       <c r="K35" t="n">
-        <v>68853.48</v>
+        <v>66598.61</v>
       </c>
       <c r="L35" t="n">
-        <v>69039.53</v>
+        <v>67845.89999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>69587.02</v>
+        <v>68322.85000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>70134.5</v>
+        <v>68799.78999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>69959.10000000001</v>
+        <v>70817.45</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -3472,74 +3479,70 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>66812.27</v>
+        <v>65732.78999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>66833.50999999999</v>
+        <v>66325.32000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>65133.98</v>
+        <v>65652.25</v>
       </c>
       <c r="E36" t="n">
-        <v>65326.42</v>
+        <v>66216.78999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-2134.3</v>
+        <v>890.37</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H36" t="n">
-        <v>1699.53</v>
+        <v>673.0700000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>65644.72</v>
+        <v>63434.45</v>
       </c>
       <c r="J36" t="n">
-        <v>65351.31</v>
+        <v>63298.23</v>
       </c>
       <c r="K36" t="n">
-        <v>66598.61</v>
+        <v>64476.66</v>
       </c>
       <c r="L36" t="n">
-        <v>67845.89999999999</v>
+        <v>65655.08</v>
       </c>
       <c r="M36" t="n">
-        <v>68322.85000000001</v>
+        <v>66176.19</v>
       </c>
       <c r="N36" t="n">
-        <v>68799.78999999999</v>
+        <v>66697.28999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>70817.45</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
+        <v>68533.03999999999</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3551,74 +3554,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>65732.78999999999</v>
+        <v>65427.69</v>
       </c>
       <c r="C37" t="n">
-        <v>66325.32000000001</v>
+        <v>66125.88</v>
       </c>
       <c r="D37" t="n">
-        <v>65652.25</v>
+        <v>65260.22</v>
       </c>
       <c r="E37" t="n">
-        <v>66216.78999999999</v>
+        <v>66016.36</v>
       </c>
       <c r="F37" t="n">
-        <v>890.37</v>
+        <v>-200.43</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.003</v>
       </c>
       <c r="H37" t="n">
-        <v>673.0700000000001</v>
+        <v>865.66</v>
       </c>
       <c r="I37" t="n">
-        <v>63434.45</v>
+        <v>64979.18</v>
       </c>
       <c r="J37" t="n">
-        <v>63298.23</v>
+        <v>65657.72</v>
       </c>
       <c r="K37" t="n">
-        <v>64476.66</v>
+        <v>65880.25</v>
       </c>
       <c r="L37" t="n">
-        <v>65655.08</v>
+        <v>66102.78999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>66176.19</v>
+        <v>66553.32000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>66697.28999999999</v>
+        <v>67003.86</v>
       </c>
       <c r="O37" t="n">
-        <v>68533.03999999999</v>
+        <v>66998.39</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3631,76 +3640,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>65427.69</v>
+        <v>65978.95</v>
       </c>
       <c r="C38" t="n">
-        <v>66125.88</v>
+        <v>66257.73</v>
       </c>
       <c r="D38" t="n">
-        <v>65260.22</v>
+        <v>65470.95</v>
       </c>
       <c r="E38" t="n">
-        <v>66016.36</v>
+        <v>65528.09</v>
       </c>
       <c r="F38" t="n">
-        <v>-200.43</v>
+        <v>-488.27</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0074</v>
       </c>
       <c r="H38" t="n">
-        <v>865.66</v>
+        <v>786.78</v>
       </c>
       <c r="I38" t="n">
-        <v>64979.18</v>
+        <v>64394.55</v>
       </c>
       <c r="J38" t="n">
-        <v>65657.72</v>
+        <v>65312.35</v>
       </c>
       <c r="K38" t="n">
-        <v>65880.25</v>
+        <v>65583.53</v>
       </c>
       <c r="L38" t="n">
-        <v>66102.78999999999</v>
+        <v>65854.71000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>66553.32000000001</v>
+        <v>66449.19</v>
       </c>
       <c r="N38" t="n">
-        <v>67003.86</v>
+        <v>67043.67999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>66998.39</v>
+        <v>66991.55</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q38" s="6" t="n">
+        <v/>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3717,75 +3720,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>65978.95</v>
+        <v>65195.26</v>
       </c>
       <c r="C39" t="n">
-        <v>66257.73</v>
+        <v>65904.24000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>65470.95</v>
+        <v>64609.47</v>
       </c>
       <c r="E39" t="n">
-        <v>65528.09</v>
+        <v>65856.42999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>-488.27</v>
+        <v>328.34</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.005</v>
       </c>
       <c r="H39" t="n">
-        <v>786.78</v>
+        <v>1294.77</v>
       </c>
       <c r="I39" t="n">
-        <v>64394.55</v>
+        <v>64684.17</v>
       </c>
       <c r="J39" t="n">
-        <v>65312.35</v>
+        <v>64573.19</v>
       </c>
       <c r="K39" t="n">
-        <v>65583.53</v>
+        <v>65134.7</v>
       </c>
       <c r="L39" t="n">
-        <v>65854.71000000001</v>
+        <v>65696.21000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>66449.19</v>
+        <v>65921.48</v>
       </c>
       <c r="N39" t="n">
-        <v>67043.67999999999</v>
+        <v>66146.74000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>66991.55</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
+        <v>67044.5</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3799,70 +3810,66 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>65195.26</v>
+        <v>65604.49000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>65904.24000000001</v>
+        <v>66442.34</v>
       </c>
       <c r="D40" t="n">
-        <v>64609.47</v>
+        <v>65390.55</v>
       </c>
       <c r="E40" t="n">
-        <v>65856.42999999999</v>
+        <v>66262.16</v>
       </c>
       <c r="F40" t="n">
-        <v>328.34</v>
+        <v>405.73</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0062</v>
       </c>
       <c r="H40" t="n">
-        <v>1294.77</v>
+        <v>1051.79</v>
       </c>
       <c r="I40" t="n">
-        <v>64684.17</v>
+        <v>63314.7</v>
       </c>
       <c r="J40" t="n">
-        <v>64573.19</v>
+        <v>64861.44</v>
       </c>
       <c r="K40" t="n">
-        <v>65134.7</v>
+        <v>65209.04</v>
       </c>
       <c r="L40" t="n">
-        <v>65696.21000000001</v>
+        <v>65556.64</v>
       </c>
       <c r="M40" t="n">
-        <v>65921.48</v>
+        <v>66503.82000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>66146.74000000001</v>
+        <v>67450.99000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>67044.5</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67199.02</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
       </c>
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
@@ -3887,57 +3894,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>65604.49000000001</v>
+        <v>66775.78</v>
       </c>
       <c r="C41" t="n">
-        <v>66442.34</v>
+        <v>66954.69</v>
       </c>
       <c r="D41" t="n">
-        <v>65390.55</v>
+        <v>65782.59</v>
       </c>
       <c r="E41" t="n">
-        <v>66262.16</v>
+        <v>66131.98</v>
       </c>
       <c r="F41" t="n">
-        <v>405.73</v>
+        <v>-130.18</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.002</v>
       </c>
       <c r="H41" t="n">
-        <v>1051.79</v>
+        <v>1172.09</v>
       </c>
       <c r="I41" t="n">
-        <v>63314.7</v>
+        <v>64338.76</v>
       </c>
       <c r="J41" t="n">
-        <v>64861.44</v>
+        <v>65383.22</v>
       </c>
       <c r="K41" t="n">
-        <v>65209.04</v>
+        <v>65736.25999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>65556.64</v>
+        <v>66089.3</v>
       </c>
       <c r="M41" t="n">
-        <v>66503.82000000001</v>
+        <v>66788.05</v>
       </c>
       <c r="N41" t="n">
-        <v>67450.99000000001</v>
+        <v>67486.8</v>
       </c>
       <c r="O41" t="n">
-        <v>67199.02</v>
+        <v>67494.14</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3950,12 +3957,12 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U41" s="8" t="n">
@@ -3971,57 +3978,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>66775.78</v>
+        <v>66104.49000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>66954.69</v>
+        <v>66842.82000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>65782.59</v>
+        <v>66012.2</v>
       </c>
       <c r="E42" t="n">
-        <v>66131.98</v>
+        <v>66405.56</v>
       </c>
       <c r="F42" t="n">
-        <v>-130.18</v>
+        <v>273.59</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0041</v>
       </c>
       <c r="H42" t="n">
-        <v>1172.09</v>
+        <v>830.62</v>
       </c>
       <c r="I42" t="n">
-        <v>64338.76</v>
+        <v>64610.5</v>
       </c>
       <c r="J42" t="n">
-        <v>65383.22</v>
+        <v>64841.55</v>
       </c>
       <c r="K42" t="n">
-        <v>65736.25999999999</v>
+        <v>65545.92999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>66089.3</v>
+        <v>66250.31</v>
       </c>
       <c r="M42" t="n">
-        <v>66788.05</v>
+        <v>66718.02</v>
       </c>
       <c r="N42" t="n">
-        <v>67486.8</v>
+        <v>67185.74000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>67494.14</v>
+        <v>68126.78</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4062,69 +4069,73 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>66104.49000000001</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C43" t="n">
-        <v>66842.82000000001</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>66012.2</v>
+        <v>64832.1</v>
       </c>
       <c r="E43" t="n">
-        <v>66405.56</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>273.59</v>
+        <v>-93.63</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0014</v>
       </c>
       <c r="H43" t="n">
-        <v>830.62</v>
+        <v>1479.83</v>
       </c>
       <c r="I43" t="n">
-        <v>64610.5</v>
+        <v>65181.59</v>
       </c>
       <c r="J43" t="n">
-        <v>64841.55</v>
+        <v>65563.97</v>
       </c>
       <c r="K43" t="n">
-        <v>65545.92999999999</v>
+        <v>65990.25</v>
       </c>
       <c r="L43" t="n">
-        <v>66250.31</v>
+        <v>66416.53999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>66718.02</v>
+        <v>66820.87</v>
       </c>
       <c r="N43" t="n">
-        <v>67185.74000000001</v>
+        <v>67225.21000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>68126.78</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67673.44</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4137,78 +4148,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>65668.50999999999</v>
+        <v>65885.47</v>
       </c>
       <c r="C44" t="n">
-        <v>66311.92999999999</v>
+        <v>66525.7</v>
       </c>
       <c r="D44" t="n">
-        <v>64832.1</v>
+        <v>65576.61</v>
       </c>
       <c r="E44" t="n">
-        <v>66311.92999999999</v>
+        <v>66215.34</v>
       </c>
       <c r="F44" t="n">
-        <v>-93.63</v>
+        <v>-96.59</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0015</v>
       </c>
       <c r="H44" t="n">
-        <v>1479.83</v>
+        <v>949.09</v>
       </c>
       <c r="I44" t="n">
-        <v>65181.59</v>
+        <v>63352.27</v>
       </c>
       <c r="J44" t="n">
-        <v>65563.97</v>
+        <v>65202.06</v>
       </c>
       <c r="K44" t="n">
-        <v>65990.25</v>
+        <v>65572.02</v>
       </c>
       <c r="L44" t="n">
-        <v>66416.53999999999</v>
+        <v>65941.97</v>
       </c>
       <c r="M44" t="n">
-        <v>66820.87</v>
+        <v>67051.84</v>
       </c>
       <c r="N44" t="n">
-        <v>67225.21000000001</v>
+        <v>68161.71000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>67673.44</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>67791.75999999999</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4225,68 +4226,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>65885.47</v>
+        <v>65195.43</v>
       </c>
       <c r="C45" t="n">
-        <v>66525.7</v>
+        <v>65195.43</v>
       </c>
       <c r="D45" t="n">
-        <v>65576.61</v>
+        <v>64215.47</v>
       </c>
       <c r="E45" t="n">
-        <v>66215.34</v>
+        <v>64325.64</v>
       </c>
       <c r="F45" t="n">
-        <v>-96.59</v>
+        <v>-1889.7</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0285</v>
       </c>
       <c r="H45" t="n">
-        <v>949.09</v>
+        <v>979.96</v>
       </c>
       <c r="I45" t="n">
-        <v>63352.27</v>
+        <v>64627.52</v>
       </c>
       <c r="J45" t="n">
-        <v>65202.06</v>
+        <v>65348.34</v>
       </c>
       <c r="K45" t="n">
-        <v>65572.02</v>
+        <v>65740.8</v>
       </c>
       <c r="L45" t="n">
-        <v>65941.97</v>
+        <v>66133.25</v>
       </c>
       <c r="M45" t="n">
-        <v>67051.84</v>
+        <v>66689.89</v>
       </c>
       <c r="N45" t="n">
-        <v>68161.71000000001</v>
+        <v>67246.53</v>
       </c>
       <c r="O45" t="n">
-        <v>67791.75999999999</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>67474.8</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4303,69 +4314,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="C46" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="D46" t="n">
-        <v>64215.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E46" t="n">
-        <v>64325.64</v>
+        <v>64214.48</v>
       </c>
       <c r="F46" t="n">
-        <v>-1889.7</v>
+        <v>-111.16</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0017</v>
       </c>
       <c r="H46" t="n">
-        <v>979.96</v>
+        <v>952.01</v>
       </c>
       <c r="I46" t="n">
-        <v>64627.52</v>
+        <v>63235.51</v>
       </c>
       <c r="J46" t="n">
-        <v>65348.34</v>
+        <v>63155.78</v>
       </c>
       <c r="K46" t="n">
-        <v>65740.8</v>
+        <v>63835.66</v>
       </c>
       <c r="L46" t="n">
-        <v>66133.25</v>
+        <v>64515.54</v>
       </c>
       <c r="M46" t="n">
-        <v>66689.89</v>
+        <v>64815.62</v>
       </c>
       <c r="N46" t="n">
-        <v>67246.53</v>
+        <v>65115.7</v>
       </c>
       <c r="O46" t="n">
-        <v>67474.8</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66175.39</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
@@ -4374,7 +4377,7 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4396,50 +4399,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>64724.81</v>
+        <v>64498.94</v>
       </c>
       <c r="C47" t="n">
-        <v>64724.81</v>
+        <v>65182.45</v>
       </c>
       <c r="D47" t="n">
-        <v>63772.8</v>
+        <v>64228.47</v>
       </c>
       <c r="E47" t="n">
-        <v>64214.48</v>
+        <v>65020.94</v>
       </c>
       <c r="F47" t="n">
-        <v>-111.16</v>
+        <v>806.46</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="H47" t="n">
-        <v>952.01</v>
+        <v>953.98</v>
       </c>
       <c r="I47" t="n">
-        <v>63235.51</v>
+        <v>62820.79</v>
       </c>
       <c r="J47" t="n">
-        <v>63155.78</v>
+        <v>63245.31</v>
       </c>
       <c r="K47" t="n">
-        <v>63835.66</v>
+        <v>63738.48</v>
       </c>
       <c r="L47" t="n">
-        <v>64515.54</v>
+        <v>64231.64</v>
       </c>
       <c r="M47" t="n">
-        <v>64815.62</v>
+        <v>64690.48</v>
       </c>
       <c r="N47" t="n">
-        <v>65115.7</v>
+        <v>65149.33</v>
       </c>
       <c r="O47" t="n">
-        <v>66175.39</v>
+        <v>65676.82000000001</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4447,21 +4450,23 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4471,55 +4476,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>64498.94</v>
+        <v>65600.42</v>
       </c>
       <c r="C48" t="n">
-        <v>65182.45</v>
+        <v>66668.71000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>64228.47</v>
+        <v>65600.42</v>
       </c>
       <c r="E48" t="n">
-        <v>65020.94</v>
+        <v>66399.84</v>
       </c>
       <c r="F48" t="n">
-        <v>806.46</v>
+        <v>1378.9</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="H48" t="n">
-        <v>953.98</v>
+        <v>1068.29</v>
       </c>
       <c r="I48" t="n">
-        <v>62820.79</v>
+        <v>63274.49</v>
       </c>
       <c r="J48" t="n">
-        <v>63245.31</v>
+        <v>64224.7</v>
       </c>
       <c r="K48" t="n">
-        <v>63738.48</v>
+        <v>64543.95</v>
       </c>
       <c r="L48" t="n">
-        <v>64231.64</v>
+        <v>64863.2</v>
       </c>
       <c r="M48" t="n">
-        <v>64690.48</v>
+        <v>65497.93</v>
       </c>
       <c r="N48" t="n">
-        <v>65149.33</v>
+        <v>66132.66</v>
       </c>
       <c r="O48" t="n">
-        <v>65676.82000000001</v>
+        <v>66136.42999999999</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4542,171 +4551,167 @@
       </c>
       <c r="U48" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W48" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W48" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65600.42</v>
+        <v>65843.69</v>
       </c>
       <c r="C49" t="n">
-        <v>66668.71000000001</v>
+        <v>66791.84</v>
       </c>
       <c r="D49" t="n">
-        <v>65600.42</v>
+        <v>65269.33</v>
       </c>
       <c r="E49" t="n">
-        <v>66399.84</v>
+        <v>65269.33</v>
       </c>
       <c r="F49" t="n">
-        <v>1378.9</v>
+        <v>-1130.52</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.017</v>
       </c>
       <c r="H49" t="n">
-        <v>1068.29</v>
+        <v>1522.52</v>
       </c>
       <c r="I49" t="n">
-        <v>63274.49</v>
+        <v>64532.13</v>
       </c>
       <c r="J49" t="n">
-        <v>64224.7</v>
+        <v>65464.19</v>
       </c>
       <c r="K49" t="n">
-        <v>64543.95</v>
+        <v>65865.7</v>
       </c>
       <c r="L49" t="n">
-        <v>64863.2</v>
+        <v>66267.21000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>65497.93</v>
+        <v>66933.99000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>66132.66</v>
+        <v>67600.77</v>
       </c>
       <c r="O49" t="n">
-        <v>66136.42999999999</v>
+        <v>67737</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
+      <c r="Q49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W49" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65843.69</v>
+        <v>65087.22</v>
       </c>
       <c r="C50" t="n">
-        <v>66791.84</v>
+        <v>65794.03</v>
       </c>
       <c r="D50" t="n">
-        <v>65269.33</v>
+        <v>65017.68</v>
       </c>
       <c r="E50" t="n">
-        <v>65269.33</v>
+        <v>65142.78</v>
       </c>
       <c r="F50" t="n">
-        <v>-1130.52</v>
+        <v>-126.55</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0019</v>
       </c>
       <c r="H50" t="n">
-        <v>1522.52</v>
+        <v>776.35</v>
       </c>
       <c r="I50" t="n">
-        <v>64532.13</v>
+        <v>63746.81</v>
       </c>
       <c r="J50" t="n">
-        <v>65464.19</v>
+        <v>63366.18</v>
       </c>
       <c r="K50" t="n">
-        <v>65865.7</v>
+        <v>64508.07</v>
       </c>
       <c r="L50" t="n">
-        <v>66267.21000000001</v>
+        <v>65649.96000000001</v>
       </c>
       <c r="M50" t="n">
-        <v>66933.99000000001</v>
+        <v>66030.59</v>
       </c>
       <c r="N50" t="n">
-        <v>67600.77</v>
+        <v>66411.21000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>67737</v>
+        <v>68314.36</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4723,68 +4728,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65087.22</v>
+        <v>64768.53</v>
       </c>
       <c r="C51" t="n">
-        <v>65794.03</v>
+        <v>65270.95</v>
       </c>
       <c r="D51" t="n">
-        <v>65017.68</v>
+        <v>64186.68</v>
       </c>
       <c r="E51" t="n">
-        <v>65142.78</v>
+        <v>65270.95</v>
       </c>
       <c r="F51" t="n">
-        <v>-126.55</v>
+        <v>128.17</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="H51" t="n">
-        <v>776.35</v>
+        <v>1084.27</v>
       </c>
       <c r="I51" t="n">
-        <v>63746.81</v>
+        <v>64241.33</v>
       </c>
       <c r="J51" t="n">
-        <v>63366.18</v>
+        <v>64234.89</v>
       </c>
       <c r="K51" t="n">
-        <v>64508.07</v>
+        <v>64754.61</v>
       </c>
       <c r="L51" t="n">
-        <v>65649.96000000001</v>
+        <v>65274.32</v>
       </c>
       <c r="M51" t="n">
-        <v>66030.59</v>
+        <v>65530.96</v>
       </c>
       <c r="N51" t="n">
-        <v>66411.21000000001</v>
+        <v>65787.60000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>68314.36</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+        <v>66570.38</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
@@ -4805,64 +4812,66 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>64768.53</v>
+        <v>64276.82</v>
       </c>
       <c r="C52" t="n">
-        <v>65270.95</v>
+        <v>64312.02</v>
       </c>
       <c r="D52" t="n">
-        <v>64186.68</v>
+        <v>63208.63</v>
       </c>
       <c r="E52" t="n">
-        <v>65270.95</v>
+        <v>64011.34</v>
       </c>
       <c r="F52" t="n">
-        <v>128.17</v>
+        <v>-1259.61</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H52" t="n">
-        <v>1084.27</v>
+        <v>1103.39</v>
       </c>
       <c r="I52" t="n">
-        <v>64241.33</v>
+        <v>63102.41</v>
       </c>
       <c r="J52" t="n">
-        <v>64234.89</v>
+        <v>64457.75</v>
       </c>
       <c r="K52" t="n">
-        <v>64754.61</v>
+        <v>64728.81</v>
       </c>
       <c r="L52" t="n">
-        <v>65274.32</v>
+        <v>64999.88</v>
       </c>
       <c r="M52" t="n">
-        <v>65530.96</v>
+        <v>65813.08</v>
       </c>
       <c r="N52" t="n">
-        <v>65787.60000000001</v>
+        <v>66626.28999999999</v>
       </c>
       <c r="O52" t="n">
-        <v>66570.38</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66355.22</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
@@ -4872,7 +4881,7 @@
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4889,71 +4898,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64276.82</v>
+        <v>63659.53</v>
       </c>
       <c r="C53" t="n">
-        <v>64312.02</v>
+        <v>63691.53</v>
       </c>
       <c r="D53" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E53" t="n">
-        <v>64011.34</v>
+        <v>63492.99</v>
       </c>
       <c r="F53" t="n">
-        <v>-1259.61</v>
+        <v>-518.35</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0081</v>
       </c>
       <c r="H53" t="n">
-        <v>1103.39</v>
+        <v>965.35</v>
       </c>
       <c r="I53" t="n">
-        <v>63102.41</v>
+        <v>62105.24</v>
       </c>
       <c r="J53" t="n">
-        <v>64457.75</v>
+        <v>63033.46</v>
       </c>
       <c r="K53" t="n">
-        <v>64728.81</v>
+        <v>63459.64</v>
       </c>
       <c r="L53" t="n">
-        <v>64999.88</v>
+        <v>63885.83</v>
       </c>
       <c r="M53" t="n">
-        <v>65813.08</v>
+        <v>64563.04</v>
       </c>
       <c r="N53" t="n">
-        <v>66626.28999999999</v>
+        <v>65240.24</v>
       </c>
       <c r="O53" t="n">
-        <v>66355.22</v>
+        <v>65415.41</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
@@ -4980,71 +4985,69 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>63659.53</v>
+        <v>63190.37</v>
       </c>
       <c r="C54" t="n">
-        <v>63691.53</v>
+        <v>64101</v>
       </c>
       <c r="D54" t="n">
-        <v>62726.18</v>
+        <v>63067.18</v>
       </c>
       <c r="E54" t="n">
-        <v>63492.99</v>
+        <v>63484.1</v>
       </c>
       <c r="F54" t="n">
-        <v>-518.35</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0001</v>
       </c>
       <c r="H54" t="n">
-        <v>965.35</v>
+        <v>1033.82</v>
       </c>
       <c r="I54" t="n">
-        <v>62105.24</v>
+        <v>61760.83</v>
       </c>
       <c r="J54" t="n">
-        <v>63033.46</v>
+        <v>62669.7</v>
       </c>
       <c r="K54" t="n">
-        <v>63459.64</v>
+        <v>63010.31</v>
       </c>
       <c r="L54" t="n">
-        <v>63885.83</v>
+        <v>63350.92</v>
       </c>
       <c r="M54" t="n">
-        <v>64563.04</v>
+        <v>63975.66</v>
       </c>
       <c r="N54" t="n">
-        <v>65240.24</v>
+        <v>64600.41</v>
       </c>
       <c r="O54" t="n">
-        <v>65415.41</v>
+        <v>64656.88</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5057,55 +5060,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>63190.37</v>
+        <v>63672.13</v>
       </c>
       <c r="C55" t="n">
-        <v>64101</v>
+        <v>63923</v>
       </c>
       <c r="D55" t="n">
-        <v>63067.18</v>
+        <v>63209.92</v>
       </c>
       <c r="E55" t="n">
-        <v>63484.1</v>
+        <v>63923</v>
       </c>
       <c r="F55" t="n">
-        <v>-8.890000000000001</v>
+        <v>438.9</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0069</v>
       </c>
       <c r="H55" t="n">
-        <v>1033.82</v>
+        <v>713.08</v>
       </c>
       <c r="I55" t="n">
-        <v>61760.83</v>
+        <v>62033.36</v>
       </c>
       <c r="J55" t="n">
-        <v>62669.7</v>
+        <v>62400.29</v>
       </c>
       <c r="K55" t="n">
-        <v>63010.31</v>
+        <v>62967.19</v>
       </c>
       <c r="L55" t="n">
-        <v>63350.92</v>
+        <v>63534.1</v>
       </c>
       <c r="M55" t="n">
-        <v>63975.66</v>
+        <v>64001.01</v>
       </c>
       <c r="N55" t="n">
-        <v>64600.41</v>
+        <v>64467.93</v>
       </c>
       <c r="O55" t="n">
-        <v>64656.88</v>
+        <v>65134.82</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5118,12 +5125,12 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U55" s="8" t="n">
@@ -5146,50 +5153,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63672.13</v>
+        <v>64643.58</v>
       </c>
       <c r="C56" t="n">
-        <v>63923</v>
+        <v>64643.58</v>
       </c>
       <c r="D56" t="n">
-        <v>63209.92</v>
+        <v>63824.56</v>
       </c>
       <c r="E56" t="n">
-        <v>63923</v>
+        <v>64136.25</v>
       </c>
       <c r="F56" t="n">
-        <v>438.9</v>
+        <v>213.25</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0033</v>
       </c>
       <c r="H56" t="n">
-        <v>713.08</v>
+        <v>819.02</v>
       </c>
       <c r="I56" t="n">
-        <v>62033.36</v>
+        <v>62496.84</v>
       </c>
       <c r="J56" t="n">
-        <v>62400.29</v>
+        <v>63388.19</v>
       </c>
       <c r="K56" t="n">
-        <v>62967.19</v>
+        <v>63566.46</v>
       </c>
       <c r="L56" t="n">
-        <v>63534.1</v>
+        <v>63744.73</v>
       </c>
       <c r="M56" t="n">
-        <v>64001.01</v>
+        <v>64279.54</v>
       </c>
       <c r="N56" t="n">
-        <v>64467.93</v>
+        <v>64814.35</v>
       </c>
       <c r="O56" t="n">
-        <v>65134.82</v>
+        <v>64636.08</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5213,8 +5220,10 @@
       <c r="U56" s="8" t="n">
         <v/>
       </c>
-      <c r="V56" s="8" t="n">
-        <v/>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W56" s="11" t="inlineStr">
         <is>
@@ -5223,57 +5232,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>64643.58</v>
+        <v>64681.55</v>
       </c>
       <c r="C57" t="n">
-        <v>64643.58</v>
+        <v>65436.57</v>
       </c>
       <c r="D57" t="n">
-        <v>63824.56</v>
+        <v>64403.85</v>
       </c>
       <c r="E57" t="n">
-        <v>64136.25</v>
+        <v>65018.95</v>
       </c>
       <c r="F57" t="n">
-        <v>213.25</v>
+        <v>882.7</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0138</v>
       </c>
       <c r="H57" t="n">
-        <v>819.02</v>
+        <v>1032.72</v>
       </c>
       <c r="I57" t="n">
-        <v>62496.84</v>
+        <v>63005.54</v>
       </c>
       <c r="J57" t="n">
-        <v>63388.19</v>
+        <v>63268.32</v>
       </c>
       <c r="K57" t="n">
-        <v>63566.46</v>
+        <v>63726.74</v>
       </c>
       <c r="L57" t="n">
-        <v>63744.73</v>
+        <v>64185.16</v>
       </c>
       <c r="M57" t="n">
-        <v>64279.54</v>
+        <v>64545.76</v>
       </c>
       <c r="N57" t="n">
-        <v>64814.35</v>
+        <v>64906.36</v>
       </c>
       <c r="O57" t="n">
-        <v>64636.08</v>
+        <v>65462.6</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5291,75 +5300,71 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>64681.55</v>
+        <v>65476.44</v>
       </c>
       <c r="C58" t="n">
-        <v>65436.57</v>
+        <v>66249.11</v>
       </c>
       <c r="D58" t="n">
-        <v>64403.85</v>
+        <v>65407.37</v>
       </c>
       <c r="E58" t="n">
-        <v>65018.95</v>
+        <v>65513.99</v>
       </c>
       <c r="F58" t="n">
-        <v>882.7</v>
+        <v>495.04</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.0076</v>
       </c>
       <c r="H58" t="n">
-        <v>1032.72</v>
+        <v>841.74</v>
       </c>
       <c r="I58" t="n">
-        <v>63005.54</v>
+        <v>63371.13</v>
       </c>
       <c r="J58" t="n">
-        <v>63268.32</v>
+        <v>64035.6</v>
       </c>
       <c r="K58" t="n">
-        <v>63726.74</v>
+        <v>64502.59</v>
       </c>
       <c r="L58" t="n">
-        <v>64185.16</v>
+        <v>64969.58</v>
       </c>
       <c r="M58" t="n">
-        <v>64545.76</v>
+        <v>65535.31</v>
       </c>
       <c r="N58" t="n">
-        <v>64906.36</v>
+        <v>66101.03999999999</v>
       </c>
       <c r="O58" t="n">
-        <v>65462.6</v>
+        <v>66469.28999999999</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5377,12 +5382,12 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V58" s="8" t="n">
@@ -5398,50 +5403,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>65476.44</v>
+        <v>65639.62</v>
       </c>
       <c r="C59" t="n">
-        <v>66249.11</v>
+        <v>66410.27</v>
       </c>
       <c r="D59" t="n">
-        <v>65407.37</v>
+        <v>65639.62</v>
       </c>
       <c r="E59" t="n">
-        <v>65513.99</v>
+        <v>66364.2</v>
       </c>
       <c r="F59" t="n">
-        <v>495.04</v>
+        <v>850.21</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.013</v>
       </c>
       <c r="H59" t="n">
-        <v>841.74</v>
+        <v>770.66</v>
       </c>
       <c r="I59" t="n">
-        <v>63371.13</v>
+        <v>64565.63</v>
       </c>
       <c r="J59" t="n">
-        <v>64035.6</v>
+        <v>64515.12</v>
       </c>
       <c r="K59" t="n">
-        <v>64502.59</v>
+        <v>65093.12</v>
       </c>
       <c r="L59" t="n">
-        <v>64969.58</v>
+        <v>65671.11</v>
       </c>
       <c r="M59" t="n">
-        <v>65535.31</v>
+        <v>65934.86</v>
       </c>
       <c r="N59" t="n">
-        <v>66101.03999999999</v>
+        <v>66198.60000000001</v>
       </c>
       <c r="O59" t="n">
-        <v>66469.28999999999</v>
+        <v>67090.85000000001</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5459,12 +5464,12 @@
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V59" s="8" t="n">
@@ -5480,63 +5485,67 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>65639.62</v>
+        <v>66505.94</v>
       </c>
       <c r="C60" t="n">
-        <v>66410.27</v>
+        <v>67034.74000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>65639.62</v>
+        <v>65877.62</v>
       </c>
       <c r="E60" t="n">
-        <v>66364.2</v>
+        <v/>
       </c>
       <c r="F60" t="n">
-        <v>850.21</v>
+        <v/>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.013</v>
+        <v/>
       </c>
       <c r="H60" t="n">
-        <v>770.66</v>
+        <v>1157.12</v>
       </c>
       <c r="I60" t="n">
-        <v>64565.63</v>
+        <v>64868.96</v>
       </c>
       <c r="J60" t="n">
-        <v>64515.12</v>
+        <v>65763.17999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>65093.12</v>
+        <v>65978.88</v>
       </c>
       <c r="L60" t="n">
-        <v>65671.11</v>
+        <v>66194.57000000001</v>
       </c>
       <c r="M60" t="n">
-        <v>65934.86</v>
+        <v>66749.53</v>
       </c>
       <c r="N60" t="n">
-        <v>66198.60000000001</v>
+        <v>67304.49000000001</v>
       </c>
       <c r="O60" t="n">
-        <v>67090.85000000001</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
+        <v>67180.92999999999</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
@@ -5544,10 +5553,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U60" s="8" t="n">
+        <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -637,74 +637,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70774.28</v>
+        <v>70039.89</v>
       </c>
       <c r="C2" t="n">
-        <v>71962.34</v>
+        <v>70081.39</v>
       </c>
       <c r="D2" t="n">
-        <v>70126.14</v>
+        <v>68676.25999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>70474.96000000001</v>
+        <v>68733.14999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>412.64</v>
+        <v>-1741.81</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0247</v>
       </c>
       <c r="H2" t="n">
-        <v>1836.2</v>
+        <v>1405.13</v>
       </c>
       <c r="I2" t="n">
-        <v>67937.38</v>
+        <v>68289.94</v>
       </c>
       <c r="J2" t="n">
-        <v>68736.37</v>
+        <v>68354.12</v>
       </c>
       <c r="K2" t="n">
-        <v>69379.91</v>
+        <v>69556.86</v>
       </c>
       <c r="L2" t="n">
-        <v>70023.46000000001</v>
+        <v>70759.60000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>70744.73</v>
+        <v>71393.06</v>
       </c>
       <c r="N2" t="n">
-        <v>71466</v>
+        <v>72026.52</v>
       </c>
       <c r="O2" t="n">
-        <v>72031.81</v>
+        <v>73798.55</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -714,80 +714,86 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70039.89</v>
+        <v>68676.06</v>
       </c>
       <c r="C3" t="n">
-        <v>70081.39</v>
+        <v>69788.03</v>
       </c>
       <c r="D3" t="n">
-        <v>68676.25999999999</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>68733.14999999999</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-1741.81</v>
+        <v>1010.92</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0147</v>
       </c>
       <c r="H3" t="n">
-        <v>1405.13</v>
+        <v>2178.54</v>
       </c>
       <c r="I3" t="n">
-        <v>68289.94</v>
+        <v>67271.12</v>
       </c>
       <c r="J3" t="n">
-        <v>68354.12</v>
+        <v>67005.17999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>69556.86</v>
+        <v>68030.58</v>
       </c>
       <c r="L3" t="n">
-        <v>70759.60000000001</v>
+        <v>69055.99000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>71393.06</v>
+        <v>69435.71000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>72026.52</v>
+        <v>69815.44</v>
       </c>
       <c r="O3" t="n">
-        <v>73798.55</v>
+        <v>71486.52</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
@@ -798,57 +804,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68676.06</v>
+        <v>69973.34</v>
       </c>
       <c r="C4" t="n">
-        <v>69788.03</v>
+        <v>70384.59</v>
       </c>
       <c r="D4" t="n">
-        <v>67609.49000000001</v>
+        <v>68904.41</v>
       </c>
       <c r="E4" t="n">
-        <v>69744.07000000001</v>
+        <v>69737.69</v>
       </c>
       <c r="F4" t="n">
-        <v>1010.92</v>
+        <v>-6.38</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0001</v>
       </c>
       <c r="H4" t="n">
-        <v>2178.54</v>
+        <v>1480.19</v>
       </c>
       <c r="I4" t="n">
-        <v>67271.12</v>
+        <v>65430.95</v>
       </c>
       <c r="J4" t="n">
-        <v>67005.17999999999</v>
+        <v>68088.19</v>
       </c>
       <c r="K4" t="n">
-        <v>68030.58</v>
+        <v>68654.8</v>
       </c>
       <c r="L4" t="n">
-        <v>69055.99000000001</v>
+        <v>69221.42</v>
       </c>
       <c r="M4" t="n">
-        <v>69435.71000000001</v>
+        <v>70833.34</v>
       </c>
       <c r="N4" t="n">
-        <v>69815.44</v>
+        <v>72445.25999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>71486.52</v>
+        <v>71966.57000000001</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -856,25 +862,19 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -886,70 +886,74 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69973.34</v>
+        <v>69460.08</v>
       </c>
       <c r="C5" t="n">
-        <v>70384.59</v>
+        <v>69957.50999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>68904.41</v>
+        <v>68003.92</v>
       </c>
       <c r="E5" t="n">
-        <v>69737.69</v>
+        <v>68256.96000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-6.38</v>
+        <v>-1480.73</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0212</v>
       </c>
       <c r="H5" t="n">
-        <v>1480.19</v>
+        <v>1953.59</v>
       </c>
       <c r="I5" t="n">
-        <v>65430.95</v>
+        <v>67424.22</v>
       </c>
       <c r="J5" t="n">
-        <v>68088.19</v>
+        <v>68304.09</v>
       </c>
       <c r="K5" t="n">
-        <v>68654.8</v>
+        <v>68997.59</v>
       </c>
       <c r="L5" t="n">
-        <v>69221.42</v>
+        <v>69691.09</v>
       </c>
       <c r="M5" t="n">
-        <v>70833.34</v>
+        <v>70477.78</v>
       </c>
       <c r="N5" t="n">
-        <v>72445.25999999999</v>
+        <v>71264.47</v>
       </c>
       <c r="O5" t="n">
-        <v>71966.57000000001</v>
+        <v>71864.78</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -961,79 +965,73 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69460.08</v>
+        <v>67704.16</v>
       </c>
       <c r="C6" t="n">
-        <v>69957.50999999999</v>
+        <v>68432.67999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>68003.92</v>
+        <v>66819.05</v>
       </c>
       <c r="E6" t="n">
-        <v>68256.96000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="F6" t="n">
-        <v>-1480.73</v>
+        <v>-1437.91</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="H6" t="n">
-        <v>1953.59</v>
+        <v>1613.63</v>
       </c>
       <c r="I6" t="n">
-        <v>67424.22</v>
+        <v>66050.34</v>
       </c>
       <c r="J6" t="n">
-        <v>68304.09</v>
+        <v>65941.5</v>
       </c>
       <c r="K6" t="n">
-        <v>68997.59</v>
+        <v>67280.17</v>
       </c>
       <c r="L6" t="n">
-        <v>69691.09</v>
+        <v>68618.84</v>
       </c>
       <c r="M6" t="n">
-        <v>70477.78</v>
+        <v>69233.75</v>
       </c>
       <c r="N6" t="n">
-        <v>71264.47</v>
+        <v>69848.67</v>
       </c>
       <c r="O6" t="n">
-        <v>71864.78</v>
+        <v>71911.09</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1057,50 +1055,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67704.16</v>
+        <v>67046.37</v>
       </c>
       <c r="C7" t="n">
-        <v>68432.67999999999</v>
+        <v>68447.89</v>
       </c>
       <c r="D7" t="n">
-        <v>66819.05</v>
+        <v>67008.89</v>
       </c>
       <c r="E7" t="n">
-        <v>66819.05</v>
+        <v>67743.85000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1437.91</v>
+        <v>924.8</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0211</v>
+        <v>0.0138</v>
       </c>
       <c r="H7" t="n">
-        <v>1613.63</v>
+        <v>1439</v>
       </c>
       <c r="I7" t="n">
-        <v>66050.34</v>
+        <v>65205.41</v>
       </c>
       <c r="J7" t="n">
-        <v>65941.5</v>
+        <v>64802.01</v>
       </c>
       <c r="K7" t="n">
-        <v>67280.17</v>
+        <v>66012.23</v>
       </c>
       <c r="L7" t="n">
-        <v>68618.84</v>
+        <v>67222.46000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>69233.75</v>
+        <v>67625.86</v>
       </c>
       <c r="N7" t="n">
-        <v>69848.67</v>
+        <v>68029.27</v>
       </c>
       <c r="O7" t="n">
-        <v>71911.09</v>
+        <v>70046.31</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1108,21 +1106,23 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1132,55 +1132,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>67046.37</v>
+        <v>68526.72</v>
       </c>
       <c r="C8" t="n">
-        <v>68447.89</v>
+        <v>69374.86</v>
       </c>
       <c r="D8" t="n">
-        <v>67008.89</v>
+        <v>68271.91</v>
       </c>
       <c r="E8" t="n">
-        <v>67743.85000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F8" t="n">
-        <v>924.8</v>
+        <v>813.88</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.012</v>
       </c>
       <c r="H8" t="n">
-        <v>1439</v>
+        <v>1102.95</v>
       </c>
       <c r="I8" t="n">
-        <v>65205.41</v>
+        <v>65569.89</v>
       </c>
       <c r="J8" t="n">
-        <v>64802.01</v>
+        <v>66312.58</v>
       </c>
       <c r="K8" t="n">
-        <v>66012.23</v>
+        <v>67024.35000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>67222.46000000001</v>
+        <v>67736.12</v>
       </c>
       <c r="M8" t="n">
-        <v>67625.86</v>
+        <v>68463.35000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>68029.27</v>
+        <v>69190.58</v>
       </c>
       <c r="O8" t="n">
-        <v>70046.31</v>
+        <v>69886.89</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,7 +1195,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1223,74 +1227,76 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68526.72</v>
+        <v>68410.63</v>
       </c>
       <c r="C9" t="n">
-        <v>69374.86</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>68271.91</v>
+        <v>66653.11</v>
       </c>
       <c r="E9" t="n">
-        <v>68557.73</v>
+        <v>67242.73</v>
       </c>
       <c r="F9" t="n">
-        <v>813.88</v>
+        <v>-1315</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0192</v>
       </c>
       <c r="H9" t="n">
-        <v>1102.95</v>
+        <v>2425.1</v>
       </c>
       <c r="I9" t="n">
-        <v>65569.89</v>
+        <v>67168.95</v>
       </c>
       <c r="J9" t="n">
-        <v>66312.58</v>
+        <v>67321.95</v>
       </c>
       <c r="K9" t="n">
-        <v>67024.35000000001</v>
+        <v>68006.25</v>
       </c>
       <c r="L9" t="n">
-        <v>67736.12</v>
+        <v>68690.55</v>
       </c>
       <c r="M9" t="n">
-        <v>68463.35000000001</v>
+        <v>69109.2</v>
       </c>
       <c r="N9" t="n">
-        <v>69190.58</v>
+        <v>69527.85000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>69886.89</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+        <v>70477.81</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1300,78 +1306,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68410.63</v>
+        <v>67002.94</v>
       </c>
       <c r="C10" t="n">
-        <v>69078.21000000001</v>
+        <v>67800.17999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>66653.11</v>
+        <v>66268.60000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>67242.73</v>
+        <v>67743.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-1315</v>
+        <v>500.77</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0074</v>
       </c>
       <c r="H10" t="n">
-        <v>2425.1</v>
+        <v>1531.58</v>
       </c>
       <c r="I10" t="n">
-        <v>67168.95</v>
+        <v>64228.01</v>
       </c>
       <c r="J10" t="n">
-        <v>67321.95</v>
+        <v>64506.16</v>
       </c>
       <c r="K10" t="n">
-        <v>68006.25</v>
+        <v>66030.17999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>68690.55</v>
+        <v>67554.19</v>
       </c>
       <c r="M10" t="n">
-        <v>69109.2</v>
+        <v>68455.28</v>
       </c>
       <c r="N10" t="n">
-        <v>69527.85000000001</v>
+        <v>69356.36</v>
       </c>
       <c r="O10" t="n">
-        <v>70477.81</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>71503.31</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1388,55 +1384,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>67002.94</v>
+        <v>67989.74000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>67800.17999999999</v>
+        <v>68798.24000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>66268.60000000001</v>
+        <v>67833.17</v>
       </c>
       <c r="E11" t="n">
-        <v>67743.5</v>
+        <v>68751.50999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>500.77</v>
+        <v>1008.01</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0149</v>
       </c>
       <c r="H11" t="n">
-        <v>1531.58</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>64228.01</v>
+        <v>64737.02</v>
       </c>
       <c r="J11" t="n">
-        <v>64506.16</v>
+        <v>66566.48</v>
       </c>
       <c r="K11" t="n">
-        <v>66030.17999999999</v>
+        <v>66977.71000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>67554.19</v>
+        <v>67388.95</v>
       </c>
       <c r="M11" t="n">
-        <v>68455.28</v>
+        <v>68509.28999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>69356.36</v>
+        <v>69629.63</v>
       </c>
       <c r="O11" t="n">
-        <v>71503.31</v>
+        <v>69331.75999999999</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1447,13 +1447,15 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1468,76 +1470,80 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67989.74000000001</v>
+        <v>67900.42999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>68798.24000000001</v>
+        <v>68069.82000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>67833.17</v>
+        <v>66499.49000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>68751.50999999999</v>
+        <v>66835.53999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1008.01</v>
+        <v>-1915.97</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0279</v>
       </c>
       <c r="H12" t="n">
-        <v>965.0700000000001</v>
+        <v>1570.33</v>
       </c>
       <c r="I12" t="n">
-        <v>64737.02</v>
+        <v>66868.10000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>66566.48</v>
+        <v>68004.34</v>
       </c>
       <c r="K12" t="n">
-        <v>66977.71000000001</v>
+        <v>68268.97</v>
       </c>
       <c r="L12" t="n">
-        <v>67388.95</v>
+        <v>68533.61</v>
       </c>
       <c r="M12" t="n">
-        <v>68509.28999999999</v>
+        <v>69234.03999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>69629.63</v>
+        <v>69934.48</v>
       </c>
       <c r="O12" t="n">
-        <v>69331.75999999999</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+        <v>69763.31</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1550,59 +1556,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67900.42999999999</v>
+        <v>66339.85000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>68069.82000000001</v>
+        <v>66441.77</v>
       </c>
       <c r="D13" t="n">
-        <v>66499.49000000001</v>
+        <v>62704.6</v>
       </c>
       <c r="E13" t="n">
-        <v>66835.53999999999</v>
+        <v>64141.12</v>
       </c>
       <c r="F13" t="n">
-        <v>-1915.97</v>
+        <v>-2694.42</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0403</v>
       </c>
       <c r="H13" t="n">
-        <v>1570.33</v>
+        <v>3737.17</v>
       </c>
       <c r="I13" t="n">
-        <v>66868.10000000001</v>
+        <v>64929.16</v>
       </c>
       <c r="J13" t="n">
-        <v>68004.34</v>
+        <v>65040.65</v>
       </c>
       <c r="K13" t="n">
-        <v>68268.97</v>
+        <v>66050.38</v>
       </c>
       <c r="L13" t="n">
-        <v>68533.61</v>
+        <v>67060.10000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>69234.03999999999</v>
+        <v>67620.7</v>
       </c>
       <c r="N13" t="n">
-        <v>69934.48</v>
+        <v>68181.31</v>
       </c>
       <c r="O13" t="n">
-        <v>69763.31</v>
+        <v>69640.14999999999</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -1619,7 +1621,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1643,74 +1645,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>66339.85000000001</v>
+        <v>64544.05</v>
       </c>
       <c r="C14" t="n">
-        <v>66441.77</v>
+        <v>66232.19</v>
       </c>
       <c r="D14" t="n">
-        <v>62704.6</v>
+        <v>64203.47</v>
       </c>
       <c r="E14" t="n">
-        <v>64141.12</v>
+        <v>66232.19</v>
       </c>
       <c r="F14" t="n">
-        <v>-2694.42</v>
+        <v>2091.07</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0326</v>
       </c>
       <c r="H14" t="n">
-        <v>3737.17</v>
+        <v>2028.72</v>
       </c>
       <c r="I14" t="n">
-        <v>64929.16</v>
+        <v>58967.43</v>
       </c>
       <c r="J14" t="n">
-        <v>65040.65</v>
+        <v>60187.92</v>
       </c>
       <c r="K14" t="n">
-        <v>66050.38</v>
+        <v>62272.54</v>
       </c>
       <c r="L14" t="n">
-        <v>67060.10000000001</v>
+        <v>64357.15</v>
       </c>
       <c r="M14" t="n">
-        <v>67620.7</v>
+        <v>66009.71000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>68181.31</v>
+        <v>67662.25999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>69640.14999999999</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
+        <v>70178.95</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1722,55 +1720,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>64544.05</v>
+        <v>66449.27</v>
       </c>
       <c r="C15" t="n">
-        <v>66232.19</v>
+        <v>67592.2</v>
       </c>
       <c r="D15" t="n">
-        <v>64203.47</v>
+        <v>65955.60000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>66232.19</v>
+        <v>66115.60000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>2091.07</v>
+        <v>-116.59</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0326</v>
+        <v>-0.0018</v>
       </c>
       <c r="H15" t="n">
-        <v>2028.72</v>
+        <v>1636.6</v>
       </c>
       <c r="I15" t="n">
-        <v>58967.43</v>
+        <v>62174.75</v>
       </c>
       <c r="J15" t="n">
-        <v>60187.92</v>
+        <v>64710.65</v>
       </c>
       <c r="K15" t="n">
-        <v>62272.54</v>
+        <v>65217.83</v>
       </c>
       <c r="L15" t="n">
-        <v>64357.15</v>
+        <v>65725.00999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>66009.71000000001</v>
+        <v>67246.55</v>
       </c>
       <c r="N15" t="n">
-        <v>67662.25999999999</v>
+        <v>68768.09</v>
       </c>
       <c r="O15" t="n">
-        <v>70178.95</v>
+        <v>68260.91</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1781,14 +1783,14 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U15" s="8" t="n">
@@ -1811,50 +1813,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>66449.27</v>
+        <v>66421.00999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>67592.2</v>
+        <v>67022.37</v>
       </c>
       <c r="D16" t="n">
-        <v>65955.60000000001</v>
+        <v>66208.66</v>
       </c>
       <c r="E16" t="n">
-        <v>66115.60000000001</v>
+        <v>66422.60000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-116.59</v>
+        <v>307</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0046</v>
       </c>
       <c r="H16" t="n">
-        <v>1636.6</v>
+        <v>813.71</v>
       </c>
       <c r="I16" t="n">
-        <v>62174.75</v>
+        <v>64319</v>
       </c>
       <c r="J16" t="n">
-        <v>64710.65</v>
+        <v>64149.85</v>
       </c>
       <c r="K16" t="n">
-        <v>65217.83</v>
+        <v>65297.3</v>
       </c>
       <c r="L16" t="n">
-        <v>65725.00999999999</v>
+        <v>66444.75</v>
       </c>
       <c r="M16" t="n">
-        <v>67246.55</v>
+        <v>66933.89999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>68768.09</v>
+        <v>67423.05</v>
       </c>
       <c r="O16" t="n">
-        <v>68260.91</v>
+        <v>69228.8</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1867,7 +1869,7 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -1895,69 +1897,73 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66421.00999999999</v>
+        <v>65584.25</v>
       </c>
       <c r="C17" t="n">
-        <v>67022.37</v>
+        <v>65720.81</v>
       </c>
       <c r="D17" t="n">
-        <v>66208.66</v>
+        <v>64201.03</v>
       </c>
       <c r="E17" t="n">
-        <v>66422.60000000001</v>
+        <v>64611.15</v>
       </c>
       <c r="F17" t="n">
-        <v>307</v>
+        <v>-1811.45</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0273</v>
       </c>
       <c r="H17" t="n">
-        <v>813.71</v>
+        <v>1519.78</v>
       </c>
       <c r="I17" t="n">
-        <v>64319</v>
+        <v>65394.95</v>
       </c>
       <c r="J17" t="n">
-        <v>64149.85</v>
+        <v>65512.44</v>
       </c>
       <c r="K17" t="n">
-        <v>65297.3</v>
+        <v>66015.75</v>
       </c>
       <c r="L17" t="n">
-        <v>66444.75</v>
+        <v>66519.06</v>
       </c>
       <c r="M17" t="n">
-        <v>66933.89999999999</v>
+        <v>66829.46000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>67423.05</v>
+        <v>67139.86</v>
       </c>
       <c r="O17" t="n">
-        <v>69228.8</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67836.08</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1970,78 +1976,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>65584.25</v>
+        <v>65164.98</v>
       </c>
       <c r="C18" t="n">
-        <v>65720.81</v>
+        <v>65220.69</v>
       </c>
       <c r="D18" t="n">
-        <v>64201.03</v>
+        <v>64123.4</v>
       </c>
       <c r="E18" t="n">
-        <v>64611.15</v>
+        <v>64931.19</v>
       </c>
       <c r="F18" t="n">
-        <v>-1811.45</v>
+        <v>320.04</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.005</v>
       </c>
       <c r="H18" t="n">
-        <v>1519.78</v>
+        <v>1097.29</v>
       </c>
       <c r="I18" t="n">
-        <v>65394.95</v>
+        <v>62681.25</v>
       </c>
       <c r="J18" t="n">
-        <v>65512.44</v>
+        <v>62916.48</v>
       </c>
       <c r="K18" t="n">
-        <v>66015.75</v>
+        <v>63851.26</v>
       </c>
       <c r="L18" t="n">
-        <v>66519.06</v>
+        <v>64786.04</v>
       </c>
       <c r="M18" t="n">
-        <v>66829.46000000001</v>
+        <v>65371.04</v>
       </c>
       <c r="N18" t="n">
-        <v>67139.86</v>
+        <v>65956.03999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>67836.08</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67240.59</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2058,68 +2054,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>65164.98</v>
+        <v>64539.92</v>
       </c>
       <c r="C19" t="n">
-        <v>65220.69</v>
+        <v>64573.18</v>
       </c>
       <c r="D19" t="n">
-        <v>64123.4</v>
+        <v>61923.6</v>
       </c>
       <c r="E19" t="n">
-        <v>64931.19</v>
+        <v>62364.92</v>
       </c>
       <c r="F19" t="n">
-        <v>320.04</v>
+        <v>-2566.27</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0395</v>
       </c>
       <c r="H19" t="n">
-        <v>1097.29</v>
+        <v>2649.58</v>
       </c>
       <c r="I19" t="n">
-        <v>62681.25</v>
+        <v>63026.11</v>
       </c>
       <c r="J19" t="n">
-        <v>62916.48</v>
+        <v>63963.47</v>
       </c>
       <c r="K19" t="n">
-        <v>63851.26</v>
+        <v>64382.54</v>
       </c>
       <c r="L19" t="n">
-        <v>64786.04</v>
+        <v>64801.62</v>
       </c>
       <c r="M19" t="n">
-        <v>65371.04</v>
+        <v>65479.84</v>
       </c>
       <c r="N19" t="n">
-        <v>65956.03999999999</v>
+        <v>66158.06</v>
       </c>
       <c r="O19" t="n">
-        <v>67240.59</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+        <v>66317.98</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2136,76 +2142,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>64539.92</v>
+        <v>62734.68</v>
       </c>
       <c r="C20" t="n">
-        <v>64573.18</v>
+        <v>63138.04</v>
       </c>
       <c r="D20" t="n">
-        <v>61923.6</v>
+        <v>60448.9</v>
       </c>
       <c r="E20" t="n">
-        <v>62364.92</v>
+        <v>61434.19</v>
       </c>
       <c r="F20" t="n">
-        <v>-2566.27</v>
+        <v>-930.73</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0149</v>
       </c>
       <c r="H20" t="n">
-        <v>2649.58</v>
+        <v>2689.14</v>
       </c>
       <c r="I20" t="n">
-        <v>63026.11</v>
+        <v>59274.02</v>
       </c>
       <c r="J20" t="n">
-        <v>63963.47</v>
+        <v>59273.61</v>
       </c>
       <c r="K20" t="n">
-        <v>64382.54</v>
+        <v>61040.13</v>
       </c>
       <c r="L20" t="n">
-        <v>64801.62</v>
+        <v>62806.66</v>
       </c>
       <c r="M20" t="n">
-        <v>65479.84</v>
+        <v>63689.71</v>
       </c>
       <c r="N20" t="n">
-        <v>66158.06</v>
+        <v>64572.77</v>
       </c>
       <c r="O20" t="n">
-        <v>66317.98</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>67222.75999999999</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2229,50 +2227,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>62734.68</v>
+        <v>61258.34</v>
       </c>
       <c r="C21" t="n">
-        <v>63138.04</v>
+        <v>62924.84</v>
       </c>
       <c r="D21" t="n">
-        <v>60448.9</v>
+        <v>61049.7</v>
       </c>
       <c r="E21" t="n">
-        <v>61434.19</v>
+        <v>61867.43</v>
       </c>
       <c r="F21" t="n">
-        <v>-930.73</v>
+        <v>433.24</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0071</v>
       </c>
       <c r="H21" t="n">
-        <v>2689.14</v>
+        <v>1875.14</v>
       </c>
       <c r="I21" t="n">
-        <v>59274.02</v>
+        <v>57759.76</v>
       </c>
       <c r="J21" t="n">
-        <v>59273.61</v>
+        <v>58565.41</v>
       </c>
       <c r="K21" t="n">
-        <v>61040.13</v>
+        <v>60089.62</v>
       </c>
       <c r="L21" t="n">
-        <v>62806.66</v>
+        <v>61613.83</v>
       </c>
       <c r="M21" t="n">
-        <v>63689.71</v>
+        <v>62778.76</v>
       </c>
       <c r="N21" t="n">
-        <v>64572.77</v>
+        <v>63943.69</v>
       </c>
       <c r="O21" t="n">
-        <v>67222.75999999999</v>
+        <v>65827.17999999999</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2280,18 +2278,18 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2304,55 +2302,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>61258.34</v>
+        <v>61957.1</v>
       </c>
       <c r="C22" t="n">
-        <v>62924.84</v>
+        <v>65364.73</v>
       </c>
       <c r="D22" t="n">
-        <v>61049.7</v>
+        <v>61948.23</v>
       </c>
       <c r="E22" t="n">
-        <v>61867.43</v>
+        <v>64362.02</v>
       </c>
       <c r="F22" t="n">
-        <v>433.24</v>
+        <v>2494.59</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0403</v>
       </c>
       <c r="H22" t="n">
-        <v>1875.14</v>
+        <v>3416.5</v>
       </c>
       <c r="I22" t="n">
-        <v>57759.76</v>
+        <v>59174.56</v>
       </c>
       <c r="J22" t="n">
-        <v>58565.41</v>
+        <v>59932.37</v>
       </c>
       <c r="K22" t="n">
-        <v>60089.62</v>
+        <v>60929.86</v>
       </c>
       <c r="L22" t="n">
-        <v>61613.83</v>
+        <v>61927.35</v>
       </c>
       <c r="M22" t="n">
-        <v>62778.76</v>
+        <v>62805</v>
       </c>
       <c r="N22" t="n">
-        <v>63943.69</v>
+        <v>63682.65</v>
       </c>
       <c r="O22" t="n">
-        <v>65827.17999999999</v>
+        <v>64799.98</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2363,9 +2365,9 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2373,70 +2375,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>61957.1</v>
+        <v>63834.95</v>
       </c>
       <c r="C23" t="n">
-        <v>65364.73</v>
+        <v>63905.12</v>
       </c>
       <c r="D23" t="n">
-        <v>61948.23</v>
+        <v>62703.47</v>
       </c>
       <c r="E23" t="n">
-        <v>64362.02</v>
+        <v>63754.9</v>
       </c>
       <c r="F23" t="n">
-        <v>2494.59</v>
+        <v>-607.12</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0403</v>
+        <v>-0.0094</v>
       </c>
       <c r="H23" t="n">
-        <v>3416.5</v>
+        <v>1201.65</v>
       </c>
       <c r="I23" t="n">
-        <v>59174.56</v>
+        <v>58531.73</v>
       </c>
       <c r="J23" t="n">
-        <v>59932.37</v>
+        <v>61298.29</v>
       </c>
       <c r="K23" t="n">
-        <v>60929.86</v>
+        <v>62653.77</v>
       </c>
       <c r="L23" t="n">
-        <v>61927.35</v>
+        <v>64009.25</v>
       </c>
       <c r="M23" t="n">
-        <v>62805</v>
+        <v>66070.27</v>
       </c>
       <c r="N23" t="n">
-        <v>63682.65</v>
+        <v>68131.28999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>64799.98</v>
+        <v>68781.23</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2449,78 +2451,76 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63834.95</v>
+        <v>63995.28</v>
       </c>
       <c r="C24" t="n">
-        <v>63905.12</v>
+        <v>64240.5</v>
       </c>
       <c r="D24" t="n">
-        <v>62703.47</v>
+        <v>62864.43</v>
       </c>
       <c r="E24" t="n">
-        <v>63754.9</v>
+        <v>63957.53</v>
       </c>
       <c r="F24" t="n">
-        <v>-607.12</v>
+        <v>202.63</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0032</v>
       </c>
       <c r="H24" t="n">
-        <v>1201.65</v>
+        <v>1376.07</v>
       </c>
       <c r="I24" t="n">
-        <v>58531.73</v>
+        <v>61501.82</v>
       </c>
       <c r="J24" t="n">
-        <v>61298.29</v>
+        <v>62778.55</v>
       </c>
       <c r="K24" t="n">
-        <v>62653.77</v>
+        <v>63154.07</v>
       </c>
       <c r="L24" t="n">
-        <v>64009.25</v>
+        <v>63529.6</v>
       </c>
       <c r="M24" t="n">
-        <v>66070.27</v>
+        <v>64355.72</v>
       </c>
       <c r="N24" t="n">
-        <v>68131.28999999999</v>
+        <v>65181.85</v>
       </c>
       <c r="O24" t="n">
-        <v>68781.23</v>
+        <v>65106.77</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2528,16 +2528,20 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2550,59 +2554,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63995.28</v>
+        <v>64565.27</v>
       </c>
       <c r="C25" t="n">
-        <v>64240.5</v>
+        <v>66302.52</v>
       </c>
       <c r="D25" t="n">
-        <v>62864.43</v>
+        <v>64555.52</v>
       </c>
       <c r="E25" t="n">
-        <v>63957.53</v>
+        <v>66300.44</v>
       </c>
       <c r="F25" t="n">
-        <v>202.63</v>
+        <v>2342.91</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0366</v>
       </c>
       <c r="H25" t="n">
-        <v>1376.07</v>
+        <v>1747</v>
       </c>
       <c r="I25" t="n">
-        <v>61501.82</v>
+        <v>61488.36</v>
       </c>
       <c r="J25" t="n">
-        <v>62778.55</v>
+        <v>62783.99</v>
       </c>
       <c r="K25" t="n">
-        <v>63154.07</v>
+        <v>63269.5</v>
       </c>
       <c r="L25" t="n">
-        <v>63529.6</v>
+        <v>63755</v>
       </c>
       <c r="M25" t="n">
-        <v>64355.72</v>
+        <v>64645.57</v>
       </c>
       <c r="N25" t="n">
-        <v>65181.85</v>
+        <v>65536.13</v>
       </c>
       <c r="O25" t="n">
-        <v>65106.77</v>
+        <v>65616.57000000001</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2610,26 +2610,28 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
@@ -2641,134 +2643,136 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>64565.27</v>
+        <v>65896</v>
       </c>
       <c r="C26" t="n">
-        <v>66302.52</v>
+        <v>65983.13</v>
       </c>
       <c r="D26" t="n">
-        <v>64555.52</v>
+        <v>64942.07</v>
       </c>
       <c r="E26" t="n">
-        <v>66300.44</v>
+        <v>65683.25999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>2342.91</v>
+        <v>-617.1799999999999</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0366</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>1747</v>
+        <v>1041.06</v>
       </c>
       <c r="I26" t="n">
-        <v>61488.36</v>
+        <v>62808.52</v>
       </c>
       <c r="J26" t="n">
-        <v>62783.99</v>
+        <v>64989.14</v>
       </c>
       <c r="K26" t="n">
-        <v>63269.5</v>
+        <v>65426.94</v>
       </c>
       <c r="L26" t="n">
-        <v>63755</v>
+        <v>65864.73</v>
       </c>
       <c r="M26" t="n">
-        <v>64645.57</v>
+        <v>67173.94</v>
       </c>
       <c r="N26" t="n">
-        <v>65536.13</v>
+        <v>68483.14999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>65616.57000000001</v>
+        <v>68049.53</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>65896</v>
+        <v>65746.13</v>
       </c>
       <c r="C27" t="n">
-        <v>65983.13</v>
+        <v>65990.72</v>
       </c>
       <c r="D27" t="n">
-        <v>64942.07</v>
+        <v>64651.49</v>
       </c>
       <c r="E27" t="n">
-        <v>65683.25999999999</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-617.1799999999999</v>
+        <v>-76.55</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="H27" t="n">
-        <v>1041.06</v>
+        <v>1339.23</v>
       </c>
       <c r="I27" t="n">
-        <v>62808.52</v>
+        <v>63901.01</v>
       </c>
       <c r="J27" t="n">
-        <v>64989.14</v>
+        <v>64752.52</v>
       </c>
       <c r="K27" t="n">
-        <v>65426.94</v>
+        <v>65162.73</v>
       </c>
       <c r="L27" t="n">
-        <v>65864.73</v>
+        <v>65572.92999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>67173.94</v>
+        <v>66203.78999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>68483.14999999999</v>
+        <v>66834.64999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>68049.53</v>
+        <v>67024.2</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2785,7 +2789,7 @@
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2811,74 +2815,74 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>65746.13</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>65990.72</v>
+        <v>67006.84</v>
       </c>
       <c r="D28" t="n">
-        <v>64651.49</v>
+        <v>65848.58</v>
       </c>
       <c r="E28" t="n">
-        <v>65606.71000000001</v>
+        <v>66970.22</v>
       </c>
       <c r="F28" t="n">
-        <v>-76.55</v>
+        <v>1363.51</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0208</v>
       </c>
       <c r="H28" t="n">
-        <v>1339.23</v>
+        <v>1158.27</v>
       </c>
       <c r="I28" t="n">
-        <v>63901.01</v>
+        <v>63312.26</v>
       </c>
       <c r="J28" t="n">
-        <v>64752.52</v>
+        <v>64410.28</v>
       </c>
       <c r="K28" t="n">
-        <v>65162.73</v>
+        <v>64937.1</v>
       </c>
       <c r="L28" t="n">
-        <v>65572.92999999999</v>
+        <v>65463.91</v>
       </c>
       <c r="M28" t="n">
-        <v>66203.78999999999</v>
+        <v>66276.33</v>
       </c>
       <c r="N28" t="n">
-        <v>66834.64999999999</v>
+        <v>67088.75</v>
       </c>
       <c r="O28" t="n">
-        <v>67024.2</v>
+        <v>67329.95</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2888,59 +2892,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>65905.10000000001</v>
+        <v>66994.05</v>
       </c>
       <c r="C29" t="n">
-        <v>67006.84</v>
+        <v>67569.36</v>
       </c>
       <c r="D29" t="n">
-        <v>65848.58</v>
+        <v>66735.75999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>66970.22</v>
+        <v>67524.06</v>
       </c>
       <c r="F29" t="n">
-        <v>1363.51</v>
+        <v>553.84</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="H29" t="n">
-        <v>1158.27</v>
+        <v>833.6</v>
       </c>
       <c r="I29" t="n">
-        <v>63312.26</v>
+        <v>64690.31</v>
       </c>
       <c r="J29" t="n">
-        <v>64410.28</v>
+        <v>66083.21000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>64937.1</v>
+        <v>66391.09</v>
       </c>
       <c r="L29" t="n">
-        <v>65463.91</v>
+        <v>66698.96000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>66276.33</v>
+        <v>67549.35000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>67088.75</v>
+        <v>68399.74000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>67329.95</v>
+        <v>68165.11</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2951,20 +2951,18 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2979,50 +2977,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>66994.05</v>
+        <v>68033.17</v>
       </c>
       <c r="C30" t="n">
-        <v>67569.36</v>
+        <v>68799.71000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>66735.75999999999</v>
+        <v>68006.17</v>
       </c>
       <c r="E30" t="n">
-        <v>67524.06</v>
+        <v>68308.59</v>
       </c>
       <c r="F30" t="n">
-        <v>553.84</v>
+        <v>784.53</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0116</v>
       </c>
       <c r="H30" t="n">
-        <v>833.6</v>
+        <v>793.54</v>
       </c>
       <c r="I30" t="n">
-        <v>64690.31</v>
+        <v>65902.16</v>
       </c>
       <c r="J30" t="n">
-        <v>66083.21000000001</v>
+        <v>66876.21000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>66391.09</v>
+        <v>67107.25999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>66698.96000000001</v>
+        <v>67338.31</v>
       </c>
       <c r="M30" t="n">
-        <v>67549.35000000001</v>
+        <v>67940.86</v>
       </c>
       <c r="N30" t="n">
-        <v>68399.74000000001</v>
+        <v>68543.42</v>
       </c>
       <c r="O30" t="n">
-        <v>68165.11</v>
+        <v>68402.96000000001</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3033,21 +3031,25 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
@@ -3059,50 +3061,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>68033.17</v>
+        <v>68811.17</v>
       </c>
       <c r="C31" t="n">
-        <v>68799.71000000001</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>68006.17</v>
+        <v>68471.14999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>68308.59</v>
+        <v>68713.8</v>
       </c>
       <c r="F31" t="n">
-        <v>784.53</v>
+        <v>405.2</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0059</v>
       </c>
       <c r="H31" t="n">
-        <v>793.54</v>
+        <v>1137.09</v>
       </c>
       <c r="I31" t="n">
-        <v>65902.16</v>
+        <v>67212.63</v>
       </c>
       <c r="J31" t="n">
-        <v>66876.21000000001</v>
+        <v>67467.88</v>
       </c>
       <c r="K31" t="n">
-        <v>67107.25999999999</v>
+        <v>67911.82000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>67338.31</v>
+        <v>68355.77</v>
       </c>
       <c r="M31" t="n">
-        <v>67940.86</v>
+        <v>68705.36</v>
       </c>
       <c r="N31" t="n">
-        <v>68543.42</v>
+        <v>69054.96000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>68402.96000000001</v>
+        <v>69593.25</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3113,14 +3115,14 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U31" s="8" t="inlineStr">
@@ -3130,7 +3132,7 @@
       </c>
       <c r="V31" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W31" s="9" t="inlineStr">
@@ -3143,50 +3145,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>68811.17</v>
+        <v>68882.06</v>
       </c>
       <c r="C32" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>68471.14999999999</v>
+        <v>68492.03999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>68713.8</v>
+        <v>69220.25</v>
       </c>
       <c r="F32" t="n">
-        <v>405.2</v>
+        <v>506.45</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="H32" t="n">
-        <v>1137.09</v>
+        <v>733.53</v>
       </c>
       <c r="I32" t="n">
-        <v>67212.63</v>
+        <v>67334.05</v>
       </c>
       <c r="J32" t="n">
-        <v>67467.88</v>
+        <v>67413.75</v>
       </c>
       <c r="K32" t="n">
-        <v>67911.82000000001</v>
+        <v>68145.25</v>
       </c>
       <c r="L32" t="n">
-        <v>68355.77</v>
+        <v>68876.75</v>
       </c>
       <c r="M32" t="n">
-        <v>68705.36</v>
+        <v>69282.34</v>
       </c>
       <c r="N32" t="n">
-        <v>69054.96000000001</v>
+        <v>69687.94</v>
       </c>
       <c r="O32" t="n">
-        <v>69593.25</v>
+        <v>70745.34</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3197,7 +3199,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3207,89 +3209,93 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>68882.06</v>
+        <v>68847.35000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>69225.57000000001</v>
+        <v>69093.2</v>
       </c>
       <c r="D33" t="n">
-        <v>68492.03999999999</v>
+        <v>67368.96000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>69220.25</v>
+        <v>67460.73</v>
       </c>
       <c r="F33" t="n">
-        <v>506.45</v>
+        <v>-1759.52</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0254</v>
       </c>
       <c r="H33" t="n">
-        <v>733.53</v>
+        <v>1724.24</v>
       </c>
       <c r="I33" t="n">
-        <v>67334.05</v>
+        <v>67758.50999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>67413.75</v>
+        <v>68667.44</v>
       </c>
       <c r="K33" t="n">
-        <v>68145.25</v>
+        <v>68853.48</v>
       </c>
       <c r="L33" t="n">
-        <v>68876.75</v>
+        <v>69039.53</v>
       </c>
       <c r="M33" t="n">
-        <v>69282.34</v>
+        <v>69587.02</v>
       </c>
       <c r="N33" t="n">
-        <v>69687.94</v>
+        <v>70134.5</v>
       </c>
       <c r="O33" t="n">
-        <v>70745.34</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+        <v>69959.10000000001</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3297,81 +3303,77 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>68847.35000000001</v>
+        <v>66812.27</v>
       </c>
       <c r="C34" t="n">
-        <v>69093.2</v>
+        <v>66833.50999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>67368.96000000001</v>
+        <v>65133.98</v>
       </c>
       <c r="E34" t="n">
-        <v>67460.73</v>
+        <v>65326.42</v>
       </c>
       <c r="F34" t="n">
-        <v>-1759.52</v>
+        <v>-2134.3</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="H34" t="n">
-        <v>1724.24</v>
+        <v>1699.53</v>
       </c>
       <c r="I34" t="n">
-        <v>67758.50999999999</v>
+        <v>65644.72</v>
       </c>
       <c r="J34" t="n">
-        <v>68667.44</v>
+        <v>65351.31</v>
       </c>
       <c r="K34" t="n">
-        <v>68853.48</v>
+        <v>66598.61</v>
       </c>
       <c r="L34" t="n">
-        <v>69039.53</v>
+        <v>67845.89999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>69587.02</v>
+        <v>68322.85000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>70134.5</v>
+        <v>68799.78999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>69959.10000000001</v>
+        <v>70817.45</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3395,74 +3397,70 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>66812.27</v>
+        <v>65732.78999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>66833.50999999999</v>
+        <v>66325.32000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>65133.98</v>
+        <v>65652.25</v>
       </c>
       <c r="E35" t="n">
-        <v>65326.42</v>
+        <v>66216.78999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>-2134.3</v>
+        <v>890.37</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H35" t="n">
-        <v>1699.53</v>
+        <v>673.0700000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>65644.72</v>
+        <v>63434.45</v>
       </c>
       <c r="J35" t="n">
-        <v>65351.31</v>
+        <v>63298.23</v>
       </c>
       <c r="K35" t="n">
-        <v>66598.61</v>
+        <v>64476.66</v>
       </c>
       <c r="L35" t="n">
-        <v>67845.89999999999</v>
+        <v>65655.08</v>
       </c>
       <c r="M35" t="n">
-        <v>68322.85000000001</v>
+        <v>66176.19</v>
       </c>
       <c r="N35" t="n">
-        <v>68799.78999999999</v>
+        <v>66697.28999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>70817.45</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
+        <v>68533.03999999999</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3474,74 +3472,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>65732.78999999999</v>
+        <v>65427.69</v>
       </c>
       <c r="C36" t="n">
-        <v>66325.32000000001</v>
+        <v>66125.88</v>
       </c>
       <c r="D36" t="n">
-        <v>65652.25</v>
+        <v>65260.22</v>
       </c>
       <c r="E36" t="n">
-        <v>66216.78999999999</v>
+        <v>66016.36</v>
       </c>
       <c r="F36" t="n">
-        <v>890.37</v>
+        <v>-200.43</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.003</v>
       </c>
       <c r="H36" t="n">
-        <v>673.0700000000001</v>
+        <v>865.66</v>
       </c>
       <c r="I36" t="n">
-        <v>63434.45</v>
+        <v>64979.18</v>
       </c>
       <c r="J36" t="n">
-        <v>63298.23</v>
+        <v>65657.72</v>
       </c>
       <c r="K36" t="n">
-        <v>64476.66</v>
+        <v>65880.25</v>
       </c>
       <c r="L36" t="n">
-        <v>65655.08</v>
+        <v>66102.78999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>66176.19</v>
+        <v>66553.32000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>66697.28999999999</v>
+        <v>67003.86</v>
       </c>
       <c r="O36" t="n">
-        <v>68533.03999999999</v>
+        <v>66998.39</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3554,76 +3558,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>65427.69</v>
+        <v>65978.95</v>
       </c>
       <c r="C37" t="n">
-        <v>66125.88</v>
+        <v>66257.73</v>
       </c>
       <c r="D37" t="n">
-        <v>65260.22</v>
+        <v>65470.95</v>
       </c>
       <c r="E37" t="n">
-        <v>66016.36</v>
+        <v>65528.09</v>
       </c>
       <c r="F37" t="n">
-        <v>-200.43</v>
+        <v>-488.27</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0074</v>
       </c>
       <c r="H37" t="n">
-        <v>865.66</v>
+        <v>786.78</v>
       </c>
       <c r="I37" t="n">
-        <v>64979.18</v>
+        <v>64394.55</v>
       </c>
       <c r="J37" t="n">
-        <v>65657.72</v>
+        <v>65312.35</v>
       </c>
       <c r="K37" t="n">
-        <v>65880.25</v>
+        <v>65583.53</v>
       </c>
       <c r="L37" t="n">
-        <v>66102.78999999999</v>
+        <v>65854.71000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>66553.32000000001</v>
+        <v>66449.19</v>
       </c>
       <c r="N37" t="n">
-        <v>67003.86</v>
+        <v>67043.67999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>66998.39</v>
+        <v>66991.55</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q37" s="6" t="n">
+        <v/>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3640,75 +3638,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>65978.95</v>
+        <v>65195.26</v>
       </c>
       <c r="C38" t="n">
-        <v>66257.73</v>
+        <v>65904.24000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>65470.95</v>
+        <v>64609.47</v>
       </c>
       <c r="E38" t="n">
-        <v>65528.09</v>
+        <v>65856.42999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>-488.27</v>
+        <v>328.34</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.005</v>
       </c>
       <c r="H38" t="n">
-        <v>786.78</v>
+        <v>1294.77</v>
       </c>
       <c r="I38" t="n">
-        <v>64394.55</v>
+        <v>64684.17</v>
       </c>
       <c r="J38" t="n">
-        <v>65312.35</v>
+        <v>64573.19</v>
       </c>
       <c r="K38" t="n">
-        <v>65583.53</v>
+        <v>65134.7</v>
       </c>
       <c r="L38" t="n">
-        <v>65854.71000000001</v>
+        <v>65696.21000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>66449.19</v>
+        <v>65921.48</v>
       </c>
       <c r="N38" t="n">
-        <v>67043.67999999999</v>
+        <v>66146.74000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>66991.55</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
+        <v>67044.5</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3722,72 +3728,68 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>65195.26</v>
+        <v>65604.49000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>65904.24000000001</v>
+        <v>66442.34</v>
       </c>
       <c r="D39" t="n">
-        <v>64609.47</v>
+        <v>65390.55</v>
       </c>
       <c r="E39" t="n">
-        <v>65856.42999999999</v>
+        <v>66262.16</v>
       </c>
       <c r="F39" t="n">
-        <v>328.34</v>
+        <v>405.73</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0062</v>
       </c>
       <c r="H39" t="n">
-        <v>1294.77</v>
+        <v>1051.79</v>
       </c>
       <c r="I39" t="n">
-        <v>64684.17</v>
+        <v>63314.7</v>
       </c>
       <c r="J39" t="n">
-        <v>64573.19</v>
+        <v>64861.44</v>
       </c>
       <c r="K39" t="n">
-        <v>65134.7</v>
+        <v>65209.04</v>
       </c>
       <c r="L39" t="n">
-        <v>65696.21000000001</v>
+        <v>65556.64</v>
       </c>
       <c r="M39" t="n">
-        <v>65921.48</v>
+        <v>66503.82000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>66146.74000000001</v>
+        <v>67450.99000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>67044.5</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67199.02</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
       </c>
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3810,57 +3812,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>65604.49000000001</v>
+        <v>66775.78</v>
       </c>
       <c r="C40" t="n">
-        <v>66442.34</v>
+        <v>66954.69</v>
       </c>
       <c r="D40" t="n">
-        <v>65390.55</v>
+        <v>65782.59</v>
       </c>
       <c r="E40" t="n">
-        <v>66262.16</v>
+        <v>66131.98</v>
       </c>
       <c r="F40" t="n">
-        <v>405.73</v>
+        <v>-130.18</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.002</v>
       </c>
       <c r="H40" t="n">
-        <v>1051.79</v>
+        <v>1172.09</v>
       </c>
       <c r="I40" t="n">
-        <v>63314.7</v>
+        <v>64338.76</v>
       </c>
       <c r="J40" t="n">
-        <v>64861.44</v>
+        <v>65383.22</v>
       </c>
       <c r="K40" t="n">
-        <v>65209.04</v>
+        <v>65736.25999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>65556.64</v>
+        <v>66089.3</v>
       </c>
       <c r="M40" t="n">
-        <v>66503.82000000001</v>
+        <v>66788.05</v>
       </c>
       <c r="N40" t="n">
-        <v>67450.99000000001</v>
+        <v>67486.8</v>
       </c>
       <c r="O40" t="n">
-        <v>67199.02</v>
+        <v>67494.14</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3871,14 +3873,14 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U40" s="8" t="n">
@@ -3894,57 +3896,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>66775.78</v>
+        <v>66104.49000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>66954.69</v>
+        <v>66842.82000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>65782.59</v>
+        <v>66012.2</v>
       </c>
       <c r="E41" t="n">
-        <v>66131.98</v>
+        <v>66405.56</v>
       </c>
       <c r="F41" t="n">
-        <v>-130.18</v>
+        <v>273.59</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0041</v>
       </c>
       <c r="H41" t="n">
-        <v>1172.09</v>
+        <v>830.62</v>
       </c>
       <c r="I41" t="n">
-        <v>64338.76</v>
+        <v>64610.5</v>
       </c>
       <c r="J41" t="n">
-        <v>65383.22</v>
+        <v>64841.55</v>
       </c>
       <c r="K41" t="n">
-        <v>65736.25999999999</v>
+        <v>65545.92999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>66089.3</v>
+        <v>66250.31</v>
       </c>
       <c r="M41" t="n">
-        <v>66788.05</v>
+        <v>66718.02</v>
       </c>
       <c r="N41" t="n">
-        <v>67486.8</v>
+        <v>67185.74000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>67494.14</v>
+        <v>68126.78</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3955,7 +3957,7 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3985,69 +3987,73 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>66104.49000000001</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>66842.82000000001</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>66012.2</v>
+        <v>64832.1</v>
       </c>
       <c r="E42" t="n">
-        <v>66405.56</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>273.59</v>
+        <v>-93.63</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0014</v>
       </c>
       <c r="H42" t="n">
-        <v>830.62</v>
+        <v>1479.83</v>
       </c>
       <c r="I42" t="n">
-        <v>64610.5</v>
+        <v>65181.59</v>
       </c>
       <c r="J42" t="n">
-        <v>64841.55</v>
+        <v>65563.97</v>
       </c>
       <c r="K42" t="n">
-        <v>65545.92999999999</v>
+        <v>65990.25</v>
       </c>
       <c r="L42" t="n">
-        <v>66250.31</v>
+        <v>66416.53999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>66718.02</v>
+        <v>66820.87</v>
       </c>
       <c r="N42" t="n">
-        <v>67185.74000000001</v>
+        <v>67225.21000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>68126.78</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+        <v>67673.44</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4060,78 +4066,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>65668.50999999999</v>
+        <v>65885.47</v>
       </c>
       <c r="C43" t="n">
-        <v>66311.92999999999</v>
+        <v>66525.7</v>
       </c>
       <c r="D43" t="n">
-        <v>64832.1</v>
+        <v>65576.61</v>
       </c>
       <c r="E43" t="n">
-        <v>66311.92999999999</v>
+        <v>66215.34</v>
       </c>
       <c r="F43" t="n">
-        <v>-93.63</v>
+        <v>-96.59</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0015</v>
       </c>
       <c r="H43" t="n">
-        <v>1479.83</v>
+        <v>949.09</v>
       </c>
       <c r="I43" t="n">
-        <v>65181.59</v>
+        <v>63352.27</v>
       </c>
       <c r="J43" t="n">
-        <v>65563.97</v>
+        <v>65202.06</v>
       </c>
       <c r="K43" t="n">
-        <v>65990.25</v>
+        <v>65572.02</v>
       </c>
       <c r="L43" t="n">
-        <v>66416.53999999999</v>
+        <v>65941.97</v>
       </c>
       <c r="M43" t="n">
-        <v>66820.87</v>
+        <v>67051.84</v>
       </c>
       <c r="N43" t="n">
-        <v>67225.21000000001</v>
+        <v>68161.71000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>67673.44</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67791.75999999999</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4148,68 +4144,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>65885.47</v>
+        <v>65195.43</v>
       </c>
       <c r="C44" t="n">
-        <v>66525.7</v>
+        <v>65195.43</v>
       </c>
       <c r="D44" t="n">
-        <v>65576.61</v>
+        <v>64215.47</v>
       </c>
       <c r="E44" t="n">
-        <v>66215.34</v>
+        <v>64325.64</v>
       </c>
       <c r="F44" t="n">
-        <v>-96.59</v>
+        <v>-1889.7</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0285</v>
       </c>
       <c r="H44" t="n">
-        <v>949.09</v>
+        <v>979.96</v>
       </c>
       <c r="I44" t="n">
-        <v>63352.27</v>
+        <v>64627.52</v>
       </c>
       <c r="J44" t="n">
-        <v>65202.06</v>
+        <v>65348.34</v>
       </c>
       <c r="K44" t="n">
-        <v>65572.02</v>
+        <v>65740.8</v>
       </c>
       <c r="L44" t="n">
-        <v>65941.97</v>
+        <v>66133.25</v>
       </c>
       <c r="M44" t="n">
-        <v>67051.84</v>
+        <v>66689.89</v>
       </c>
       <c r="N44" t="n">
-        <v>68161.71000000001</v>
+        <v>67246.53</v>
       </c>
       <c r="O44" t="n">
-        <v>67791.75999999999</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+        <v>67474.8</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4226,78 +4232,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="C45" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="D45" t="n">
-        <v>64215.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E45" t="n">
-        <v>64325.64</v>
+        <v>64214.48</v>
       </c>
       <c r="F45" t="n">
-        <v>-1889.7</v>
+        <v>-111.16</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0017</v>
       </c>
       <c r="H45" t="n">
-        <v>979.96</v>
+        <v>952.01</v>
       </c>
       <c r="I45" t="n">
-        <v>64627.52</v>
+        <v>63235.51</v>
       </c>
       <c r="J45" t="n">
-        <v>65348.34</v>
+        <v>63155.78</v>
       </c>
       <c r="K45" t="n">
-        <v>65740.8</v>
+        <v>63835.66</v>
       </c>
       <c r="L45" t="n">
-        <v>66133.25</v>
+        <v>64515.54</v>
       </c>
       <c r="M45" t="n">
-        <v>66689.89</v>
+        <v>64815.62</v>
       </c>
       <c r="N45" t="n">
-        <v>67246.53</v>
+        <v>65115.7</v>
       </c>
       <c r="O45" t="n">
-        <v>67474.8</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66175.39</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4319,50 +4317,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>64724.81</v>
+        <v>64498.94</v>
       </c>
       <c r="C46" t="n">
-        <v>64724.81</v>
+        <v>65182.45</v>
       </c>
       <c r="D46" t="n">
-        <v>63772.8</v>
+        <v>64228.47</v>
       </c>
       <c r="E46" t="n">
-        <v>64214.48</v>
+        <v>65020.94</v>
       </c>
       <c r="F46" t="n">
-        <v>-111.16</v>
+        <v>806.46</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="H46" t="n">
-        <v>952.01</v>
+        <v>953.98</v>
       </c>
       <c r="I46" t="n">
-        <v>63235.51</v>
+        <v>62820.79</v>
       </c>
       <c r="J46" t="n">
-        <v>63155.78</v>
+        <v>63245.31</v>
       </c>
       <c r="K46" t="n">
-        <v>63835.66</v>
+        <v>63738.48</v>
       </c>
       <c r="L46" t="n">
-        <v>64515.54</v>
+        <v>64231.64</v>
       </c>
       <c r="M46" t="n">
-        <v>64815.62</v>
+        <v>64690.48</v>
       </c>
       <c r="N46" t="n">
-        <v>65115.7</v>
+        <v>65149.33</v>
       </c>
       <c r="O46" t="n">
-        <v>66175.39</v>
+        <v>65676.82000000001</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4370,21 +4368,23 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4394,55 +4394,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>64498.94</v>
+        <v>65600.42</v>
       </c>
       <c r="C47" t="n">
-        <v>65182.45</v>
+        <v>66668.71000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>64228.47</v>
+        <v>65600.42</v>
       </c>
       <c r="E47" t="n">
-        <v>65020.94</v>
+        <v>66399.84</v>
       </c>
       <c r="F47" t="n">
-        <v>806.46</v>
+        <v>1378.9</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="H47" t="n">
-        <v>953.98</v>
+        <v>1068.29</v>
       </c>
       <c r="I47" t="n">
-        <v>62820.79</v>
+        <v>63274.49</v>
       </c>
       <c r="J47" t="n">
-        <v>63245.31</v>
+        <v>64224.7</v>
       </c>
       <c r="K47" t="n">
-        <v>63738.48</v>
+        <v>64543.95</v>
       </c>
       <c r="L47" t="n">
-        <v>64231.64</v>
+        <v>64863.2</v>
       </c>
       <c r="M47" t="n">
-        <v>64690.48</v>
+        <v>65497.93</v>
       </c>
       <c r="N47" t="n">
-        <v>65149.33</v>
+        <v>66132.66</v>
       </c>
       <c r="O47" t="n">
-        <v>65676.82000000001</v>
+        <v>66136.42999999999</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4453,7 +4457,7 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4465,171 +4469,167 @@
       </c>
       <c r="U47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W47" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W47" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65600.42</v>
+        <v>65843.69</v>
       </c>
       <c r="C48" t="n">
-        <v>66668.71000000001</v>
+        <v>66791.84</v>
       </c>
       <c r="D48" t="n">
-        <v>65600.42</v>
+        <v>65269.33</v>
       </c>
       <c r="E48" t="n">
-        <v>66399.84</v>
+        <v>65269.33</v>
       </c>
       <c r="F48" t="n">
-        <v>1378.9</v>
+        <v>-1130.52</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.017</v>
       </c>
       <c r="H48" t="n">
-        <v>1068.29</v>
+        <v>1522.52</v>
       </c>
       <c r="I48" t="n">
-        <v>63274.49</v>
+        <v>64532.13</v>
       </c>
       <c r="J48" t="n">
-        <v>64224.7</v>
+        <v>65464.19</v>
       </c>
       <c r="K48" t="n">
-        <v>64543.95</v>
+        <v>65865.7</v>
       </c>
       <c r="L48" t="n">
-        <v>64863.2</v>
+        <v>66267.21000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>65497.93</v>
+        <v>66933.99000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>66132.66</v>
+        <v>67600.77</v>
       </c>
       <c r="O48" t="n">
-        <v>66136.42999999999</v>
+        <v>67737</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W48" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr"/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W48" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65843.69</v>
+        <v>65087.22</v>
       </c>
       <c r="C49" t="n">
-        <v>66791.84</v>
+        <v>65794.03</v>
       </c>
       <c r="D49" t="n">
-        <v>65269.33</v>
+        <v>65017.68</v>
       </c>
       <c r="E49" t="n">
-        <v>65269.33</v>
+        <v>65142.78</v>
       </c>
       <c r="F49" t="n">
-        <v>-1130.52</v>
+        <v>-126.55</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0019</v>
       </c>
       <c r="H49" t="n">
-        <v>1522.52</v>
+        <v>776.35</v>
       </c>
       <c r="I49" t="n">
-        <v>64532.13</v>
+        <v>63746.81</v>
       </c>
       <c r="J49" t="n">
-        <v>65464.19</v>
+        <v>63366.18</v>
       </c>
       <c r="K49" t="n">
-        <v>65865.7</v>
+        <v>64508.07</v>
       </c>
       <c r="L49" t="n">
-        <v>66267.21000000001</v>
+        <v>65649.96000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>66933.99000000001</v>
+        <v>66030.59</v>
       </c>
       <c r="N49" t="n">
-        <v>67600.77</v>
+        <v>66411.21000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>67737</v>
+        <v>68314.36</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4646,70 +4646,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65087.22</v>
+        <v>64768.53</v>
       </c>
       <c r="C50" t="n">
-        <v>65794.03</v>
+        <v>65270.95</v>
       </c>
       <c r="D50" t="n">
-        <v>65017.68</v>
+        <v>64186.68</v>
       </c>
       <c r="E50" t="n">
-        <v>65142.78</v>
+        <v>65270.95</v>
       </c>
       <c r="F50" t="n">
-        <v>-126.55</v>
+        <v>128.17</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="H50" t="n">
-        <v>776.35</v>
+        <v>1084.27</v>
       </c>
       <c r="I50" t="n">
-        <v>63746.81</v>
+        <v>64241.33</v>
       </c>
       <c r="J50" t="n">
-        <v>63366.18</v>
+        <v>64234.89</v>
       </c>
       <c r="K50" t="n">
-        <v>64508.07</v>
+        <v>64754.61</v>
       </c>
       <c r="L50" t="n">
-        <v>65649.96000000001</v>
+        <v>65274.32</v>
       </c>
       <c r="M50" t="n">
-        <v>66030.59</v>
+        <v>65530.96</v>
       </c>
       <c r="N50" t="n">
-        <v>66411.21000000001</v>
+        <v>65787.60000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>68314.36</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
+        <v>66570.38</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4728,64 +4730,66 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>64768.53</v>
+        <v>64276.82</v>
       </c>
       <c r="C51" t="n">
-        <v>65270.95</v>
+        <v>64312.02</v>
       </c>
       <c r="D51" t="n">
-        <v>64186.68</v>
+        <v>63208.63</v>
       </c>
       <c r="E51" t="n">
-        <v>65270.95</v>
+        <v>64011.34</v>
       </c>
       <c r="F51" t="n">
-        <v>128.17</v>
+        <v>-1259.61</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H51" t="n">
-        <v>1084.27</v>
+        <v>1103.39</v>
       </c>
       <c r="I51" t="n">
-        <v>64241.33</v>
+        <v>63102.41</v>
       </c>
       <c r="J51" t="n">
-        <v>64234.89</v>
+        <v>64457.75</v>
       </c>
       <c r="K51" t="n">
-        <v>64754.61</v>
+        <v>64728.81</v>
       </c>
       <c r="L51" t="n">
-        <v>65274.32</v>
+        <v>64999.88</v>
       </c>
       <c r="M51" t="n">
-        <v>65530.96</v>
+        <v>65813.08</v>
       </c>
       <c r="N51" t="n">
-        <v>65787.60000000001</v>
+        <v>66626.28999999999</v>
       </c>
       <c r="O51" t="n">
-        <v>66570.38</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66355.22</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
@@ -4793,9 +4797,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4812,74 +4816,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>64276.82</v>
+        <v>63659.53</v>
       </c>
       <c r="C52" t="n">
-        <v>64312.02</v>
+        <v>63691.53</v>
       </c>
       <c r="D52" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E52" t="n">
-        <v>64011.34</v>
+        <v>63492.99</v>
       </c>
       <c r="F52" t="n">
-        <v>-1259.61</v>
+        <v>-518.35</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0081</v>
       </c>
       <c r="H52" t="n">
-        <v>1103.39</v>
+        <v>965.35</v>
       </c>
       <c r="I52" t="n">
-        <v>63102.41</v>
+        <v>62105.24</v>
       </c>
       <c r="J52" t="n">
-        <v>64457.75</v>
+        <v>63033.46</v>
       </c>
       <c r="K52" t="n">
-        <v>64728.81</v>
+        <v>63459.64</v>
       </c>
       <c r="L52" t="n">
-        <v>64999.88</v>
+        <v>63885.83</v>
       </c>
       <c r="M52" t="n">
-        <v>65813.08</v>
+        <v>64563.04</v>
       </c>
       <c r="N52" t="n">
-        <v>66626.28999999999</v>
+        <v>65240.24</v>
       </c>
       <c r="O52" t="n">
-        <v>66355.22</v>
+        <v>65415.41</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4903,71 +4903,69 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>63659.53</v>
+        <v>63190.37</v>
       </c>
       <c r="C53" t="n">
-        <v>63691.53</v>
+        <v>64101</v>
       </c>
       <c r="D53" t="n">
-        <v>62726.18</v>
+        <v>63067.18</v>
       </c>
       <c r="E53" t="n">
-        <v>63492.99</v>
+        <v>63484.1</v>
       </c>
       <c r="F53" t="n">
-        <v>-518.35</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0001</v>
       </c>
       <c r="H53" t="n">
-        <v>965.35</v>
+        <v>1033.82</v>
       </c>
       <c r="I53" t="n">
-        <v>62105.24</v>
+        <v>61760.83</v>
       </c>
       <c r="J53" t="n">
-        <v>63033.46</v>
+        <v>62669.7</v>
       </c>
       <c r="K53" t="n">
-        <v>63459.64</v>
+        <v>63010.31</v>
       </c>
       <c r="L53" t="n">
-        <v>63885.83</v>
+        <v>63350.92</v>
       </c>
       <c r="M53" t="n">
-        <v>64563.04</v>
+        <v>63975.66</v>
       </c>
       <c r="N53" t="n">
-        <v>65240.24</v>
+        <v>64600.41</v>
       </c>
       <c r="O53" t="n">
-        <v>65415.41</v>
+        <v>64656.88</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4980,55 +4978,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>63190.37</v>
+        <v>63672.13</v>
       </c>
       <c r="C54" t="n">
-        <v>64101</v>
+        <v>63923</v>
       </c>
       <c r="D54" t="n">
-        <v>63067.18</v>
+        <v>63209.92</v>
       </c>
       <c r="E54" t="n">
-        <v>63484.1</v>
+        <v>63923</v>
       </c>
       <c r="F54" t="n">
-        <v>-8.890000000000001</v>
+        <v>438.9</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0069</v>
       </c>
       <c r="H54" t="n">
-        <v>1033.82</v>
+        <v>713.08</v>
       </c>
       <c r="I54" t="n">
-        <v>61760.83</v>
+        <v>62033.36</v>
       </c>
       <c r="J54" t="n">
-        <v>62669.7</v>
+        <v>62400.29</v>
       </c>
       <c r="K54" t="n">
-        <v>63010.31</v>
+        <v>62967.19</v>
       </c>
       <c r="L54" t="n">
-        <v>63350.92</v>
+        <v>63534.1</v>
       </c>
       <c r="M54" t="n">
-        <v>63975.66</v>
+        <v>64001.01</v>
       </c>
       <c r="N54" t="n">
-        <v>64600.41</v>
+        <v>64467.93</v>
       </c>
       <c r="O54" t="n">
-        <v>64656.88</v>
+        <v>65134.82</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5039,14 +5041,14 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U54" s="8" t="n">
@@ -5069,50 +5071,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>63672.13</v>
+        <v>64643.58</v>
       </c>
       <c r="C55" t="n">
-        <v>63923</v>
+        <v>64643.58</v>
       </c>
       <c r="D55" t="n">
-        <v>63209.92</v>
+        <v>63824.56</v>
       </c>
       <c r="E55" t="n">
-        <v>63923</v>
+        <v>64136.25</v>
       </c>
       <c r="F55" t="n">
-        <v>438.9</v>
+        <v>213.25</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0033</v>
       </c>
       <c r="H55" t="n">
-        <v>713.08</v>
+        <v>819.02</v>
       </c>
       <c r="I55" t="n">
-        <v>62033.36</v>
+        <v>62496.84</v>
       </c>
       <c r="J55" t="n">
-        <v>62400.29</v>
+        <v>63388.19</v>
       </c>
       <c r="K55" t="n">
-        <v>62967.19</v>
+        <v>63566.46</v>
       </c>
       <c r="L55" t="n">
-        <v>63534.1</v>
+        <v>63744.73</v>
       </c>
       <c r="M55" t="n">
-        <v>64001.01</v>
+        <v>64279.54</v>
       </c>
       <c r="N55" t="n">
-        <v>64467.93</v>
+        <v>64814.35</v>
       </c>
       <c r="O55" t="n">
-        <v>65134.82</v>
+        <v>64636.08</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5123,7 +5125,7 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5136,8 +5138,10 @@
       <c r="U55" s="8" t="n">
         <v/>
       </c>
-      <c r="V55" s="8" t="n">
-        <v/>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
@@ -5146,57 +5150,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>64643.58</v>
+        <v>64681.55</v>
       </c>
       <c r="C56" t="n">
-        <v>64643.58</v>
+        <v>65436.57</v>
       </c>
       <c r="D56" t="n">
-        <v>63824.56</v>
+        <v>64403.85</v>
       </c>
       <c r="E56" t="n">
-        <v>64136.25</v>
+        <v>65018.95</v>
       </c>
       <c r="F56" t="n">
-        <v>213.25</v>
+        <v>882.7</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0138</v>
       </c>
       <c r="H56" t="n">
-        <v>819.02</v>
+        <v>1032.72</v>
       </c>
       <c r="I56" t="n">
-        <v>62496.84</v>
+        <v>63005.54</v>
       </c>
       <c r="J56" t="n">
-        <v>63388.19</v>
+        <v>63268.32</v>
       </c>
       <c r="K56" t="n">
-        <v>63566.46</v>
+        <v>63726.74</v>
       </c>
       <c r="L56" t="n">
-        <v>63744.73</v>
+        <v>64185.16</v>
       </c>
       <c r="M56" t="n">
-        <v>64279.54</v>
+        <v>64545.76</v>
       </c>
       <c r="N56" t="n">
-        <v>64814.35</v>
+        <v>64906.36</v>
       </c>
       <c r="O56" t="n">
-        <v>64636.08</v>
+        <v>65462.6</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5207,82 +5211,78 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>64681.55</v>
+        <v>65476.44</v>
       </c>
       <c r="C57" t="n">
-        <v>65436.57</v>
+        <v>66249.11</v>
       </c>
       <c r="D57" t="n">
-        <v>64403.85</v>
+        <v>65407.37</v>
       </c>
       <c r="E57" t="n">
-        <v>65018.95</v>
+        <v>65513.99</v>
       </c>
       <c r="F57" t="n">
-        <v>882.7</v>
+        <v>495.04</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.0076</v>
       </c>
       <c r="H57" t="n">
-        <v>1032.72</v>
+        <v>841.74</v>
       </c>
       <c r="I57" t="n">
-        <v>63005.54</v>
+        <v>63371.13</v>
       </c>
       <c r="J57" t="n">
-        <v>63268.32</v>
+        <v>64035.6</v>
       </c>
       <c r="K57" t="n">
-        <v>63726.74</v>
+        <v>64502.59</v>
       </c>
       <c r="L57" t="n">
-        <v>64185.16</v>
+        <v>64969.58</v>
       </c>
       <c r="M57" t="n">
-        <v>64545.76</v>
+        <v>65535.31</v>
       </c>
       <c r="N57" t="n">
-        <v>64906.36</v>
+        <v>66101.03999999999</v>
       </c>
       <c r="O57" t="n">
-        <v>65462.6</v>
+        <v>66469.28999999999</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5293,19 +5293,19 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U57" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V57" s="8" t="n">
@@ -5321,50 +5321,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>65476.44</v>
+        <v>65639.62</v>
       </c>
       <c r="C58" t="n">
-        <v>66249.11</v>
+        <v>66410.27</v>
       </c>
       <c r="D58" t="n">
-        <v>65407.37</v>
+        <v>65639.62</v>
       </c>
       <c r="E58" t="n">
-        <v>65513.99</v>
+        <v>66364.2</v>
       </c>
       <c r="F58" t="n">
-        <v>495.04</v>
+        <v>850.21</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.013</v>
       </c>
       <c r="H58" t="n">
-        <v>841.74</v>
+        <v>770.66</v>
       </c>
       <c r="I58" t="n">
-        <v>63371.13</v>
+        <v>64565.63</v>
       </c>
       <c r="J58" t="n">
-        <v>64035.6</v>
+        <v>64515.12</v>
       </c>
       <c r="K58" t="n">
-        <v>64502.59</v>
+        <v>65093.12</v>
       </c>
       <c r="L58" t="n">
-        <v>64969.58</v>
+        <v>65671.11</v>
       </c>
       <c r="M58" t="n">
-        <v>65535.31</v>
+        <v>65934.86</v>
       </c>
       <c r="N58" t="n">
-        <v>66101.03999999999</v>
+        <v>66198.60000000001</v>
       </c>
       <c r="O58" t="n">
-        <v>66469.28999999999</v>
+        <v>67090.85000000001</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5375,19 +5375,19 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V58" s="8" t="n">
@@ -5403,50 +5403,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>65639.62</v>
+        <v>66505.94</v>
       </c>
       <c r="C59" t="n">
-        <v>66410.27</v>
+        <v>67034.74000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>65639.62</v>
+        <v>65877.62</v>
       </c>
       <c r="E59" t="n">
-        <v>66364.2</v>
+        <v>65877.62</v>
       </c>
       <c r="F59" t="n">
-        <v>850.21</v>
+        <v>-486.59</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0073</v>
       </c>
       <c r="H59" t="n">
-        <v>770.66</v>
+        <v>1157.12</v>
       </c>
       <c r="I59" t="n">
-        <v>64565.63</v>
+        <v>64868.96</v>
       </c>
       <c r="J59" t="n">
-        <v>64515.12</v>
+        <v>65763.17999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>65093.12</v>
+        <v>65978.88</v>
       </c>
       <c r="L59" t="n">
-        <v>65671.11</v>
+        <v>66194.57000000001</v>
       </c>
       <c r="M59" t="n">
-        <v>65934.86</v>
+        <v>66749.53</v>
       </c>
       <c r="N59" t="n">
-        <v>66198.60000000001</v>
+        <v>67304.49000000001</v>
       </c>
       <c r="O59" t="n">
-        <v>67090.85000000001</v>
+        <v>67180.92999999999</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5454,12 +5454,14 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
@@ -5467,10 +5469,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5480,22 +5480,26 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>66505.94</v>
+        <v>65557.99000000001</v>
       </c>
       <c r="C60" t="n">
-        <v>67034.74000000001</v>
+        <v>65805.08</v>
       </c>
       <c r="D60" t="n">
-        <v>65877.62</v>
+        <v>64699.49</v>
       </c>
       <c r="E60" t="n">
         <v/>
@@ -5507,28 +5511,28 @@
         <v/>
       </c>
       <c r="H60" t="n">
-        <v>1157.12</v>
+        <v>1105.59</v>
       </c>
       <c r="I60" t="n">
-        <v>64868.96</v>
+        <v>64720.49</v>
       </c>
       <c r="J60" t="n">
-        <v>65763.17999999999</v>
+        <v>64431.21</v>
       </c>
       <c r="K60" t="n">
-        <v>65978.88</v>
+        <v>65299.05</v>
       </c>
       <c r="L60" t="n">
-        <v>66194.57000000001</v>
+        <v>66166.89999999999</v>
       </c>
       <c r="M60" t="n">
-        <v>66749.53</v>
+        <v>66456.17999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>67304.49000000001</v>
+        <v>66745.46000000001</v>
       </c>
       <c r="O60" t="n">
-        <v>67180.92999999999</v>
+        <v>68191.87</v>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
@@ -5548,10 +5552,8 @@
           <t>=</t>
         </is>
       </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5564,7 +5566,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -637,75 +637,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70039.89</v>
+        <v>68676.06</v>
       </c>
       <c r="C2" t="n">
-        <v>70081.39</v>
+        <v>69788.03</v>
       </c>
       <c r="D2" t="n">
-        <v>68676.25999999999</v>
+        <v>67609.49000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>68733.14999999999</v>
+        <v>69744.07000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-1741.81</v>
+        <v>1010.92</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0247</v>
+        <v>0.0147</v>
       </c>
       <c r="H2" t="n">
-        <v>1405.13</v>
+        <v>2178.54</v>
       </c>
       <c r="I2" t="n">
-        <v>68289.94</v>
+        <v>67271.12</v>
       </c>
       <c r="J2" t="n">
-        <v>68354.12</v>
+        <v>67005.17999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>69556.86</v>
+        <v>68030.58</v>
       </c>
       <c r="L2" t="n">
-        <v>70759.60000000001</v>
+        <v>69055.99000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>71393.06</v>
+        <v>69435.71000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>72026.52</v>
+        <v>69815.44</v>
       </c>
       <c r="O2" t="n">
-        <v>73798.55</v>
+        <v>71486.52</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
@@ -716,57 +718,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68676.06</v>
+        <v>69973.34</v>
       </c>
       <c r="C3" t="n">
-        <v>69788.03</v>
+        <v>70384.59</v>
       </c>
       <c r="D3" t="n">
-        <v>67609.49000000001</v>
+        <v>68904.41</v>
       </c>
       <c r="E3" t="n">
-        <v>69744.07000000001</v>
+        <v>69737.69</v>
       </c>
       <c r="F3" t="n">
-        <v>1010.92</v>
+        <v>-6.38</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0001</v>
       </c>
       <c r="H3" t="n">
-        <v>2178.54</v>
+        <v>1480.19</v>
       </c>
       <c r="I3" t="n">
-        <v>67271.12</v>
+        <v>65430.95</v>
       </c>
       <c r="J3" t="n">
-        <v>67005.17999999999</v>
+        <v>68088.19</v>
       </c>
       <c r="K3" t="n">
-        <v>68030.58</v>
+        <v>68654.8</v>
       </c>
       <c r="L3" t="n">
-        <v>69055.99000000001</v>
+        <v>69221.42</v>
       </c>
       <c r="M3" t="n">
-        <v>69435.71000000001</v>
+        <v>70833.34</v>
       </c>
       <c r="N3" t="n">
-        <v>69815.44</v>
+        <v>72445.25999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>71486.52</v>
+        <v>71966.57000000001</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,25 +776,19 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -804,70 +800,74 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69973.34</v>
+        <v>69460.08</v>
       </c>
       <c r="C4" t="n">
-        <v>70384.59</v>
+        <v>69957.50999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>68904.41</v>
+        <v>68003.92</v>
       </c>
       <c r="E4" t="n">
-        <v>69737.69</v>
+        <v>68256.96000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.38</v>
+        <v>-1480.73</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0212</v>
       </c>
       <c r="H4" t="n">
-        <v>1480.19</v>
+        <v>1953.59</v>
       </c>
       <c r="I4" t="n">
-        <v>65430.95</v>
+        <v>67424.22</v>
       </c>
       <c r="J4" t="n">
-        <v>68088.19</v>
+        <v>68304.09</v>
       </c>
       <c r="K4" t="n">
-        <v>68654.8</v>
+        <v>68997.59</v>
       </c>
       <c r="L4" t="n">
-        <v>69221.42</v>
+        <v>69691.09</v>
       </c>
       <c r="M4" t="n">
-        <v>70833.34</v>
+        <v>70477.78</v>
       </c>
       <c r="N4" t="n">
-        <v>72445.25999999999</v>
+        <v>71264.47</v>
       </c>
       <c r="O4" t="n">
-        <v>71966.57000000001</v>
+        <v>71864.78</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -879,79 +879,73 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69460.08</v>
+        <v>67704.16</v>
       </c>
       <c r="C5" t="n">
-        <v>69957.50999999999</v>
+        <v>68432.67999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>68003.92</v>
+        <v>66819.05</v>
       </c>
       <c r="E5" t="n">
-        <v>68256.96000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="F5" t="n">
-        <v>-1480.73</v>
+        <v>-1437.91</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="H5" t="n">
-        <v>1953.59</v>
+        <v>1613.63</v>
       </c>
       <c r="I5" t="n">
-        <v>67424.22</v>
+        <v>66050.34</v>
       </c>
       <c r="J5" t="n">
-        <v>68304.09</v>
+        <v>65941.5</v>
       </c>
       <c r="K5" t="n">
-        <v>68997.59</v>
+        <v>67280.17</v>
       </c>
       <c r="L5" t="n">
-        <v>69691.09</v>
+        <v>68618.84</v>
       </c>
       <c r="M5" t="n">
-        <v>70477.78</v>
+        <v>69233.75</v>
       </c>
       <c r="N5" t="n">
-        <v>71264.47</v>
+        <v>69848.67</v>
       </c>
       <c r="O5" t="n">
-        <v>71864.78</v>
+        <v>71911.09</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -975,50 +969,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>67704.16</v>
+        <v>67046.37</v>
       </c>
       <c r="C6" t="n">
-        <v>68432.67999999999</v>
+        <v>68447.89</v>
       </c>
       <c r="D6" t="n">
-        <v>66819.05</v>
+        <v>67008.89</v>
       </c>
       <c r="E6" t="n">
-        <v>66819.05</v>
+        <v>67743.85000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-1437.91</v>
+        <v>924.8</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0211</v>
+        <v>0.0138</v>
       </c>
       <c r="H6" t="n">
-        <v>1613.63</v>
+        <v>1439</v>
       </c>
       <c r="I6" t="n">
-        <v>66050.34</v>
+        <v>65205.41</v>
       </c>
       <c r="J6" t="n">
-        <v>65941.5</v>
+        <v>64802.01</v>
       </c>
       <c r="K6" t="n">
-        <v>67280.17</v>
+        <v>66012.23</v>
       </c>
       <c r="L6" t="n">
-        <v>68618.84</v>
+        <v>67222.46000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>69233.75</v>
+        <v>67625.86</v>
       </c>
       <c r="N6" t="n">
-        <v>69848.67</v>
+        <v>68029.27</v>
       </c>
       <c r="O6" t="n">
-        <v>71911.09</v>
+        <v>70046.31</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1026,21 +1020,23 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1050,55 +1046,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67046.37</v>
+        <v>68526.72</v>
       </c>
       <c r="C7" t="n">
-        <v>68447.89</v>
+        <v>69374.86</v>
       </c>
       <c r="D7" t="n">
-        <v>67008.89</v>
+        <v>68271.91</v>
       </c>
       <c r="E7" t="n">
-        <v>67743.85000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F7" t="n">
-        <v>924.8</v>
+        <v>813.88</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.012</v>
       </c>
       <c r="H7" t="n">
-        <v>1439</v>
+        <v>1102.95</v>
       </c>
       <c r="I7" t="n">
-        <v>65205.41</v>
+        <v>65569.89</v>
       </c>
       <c r="J7" t="n">
-        <v>64802.01</v>
+        <v>66312.58</v>
       </c>
       <c r="K7" t="n">
-        <v>66012.23</v>
+        <v>67024.35000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>67222.46000000001</v>
+        <v>67736.12</v>
       </c>
       <c r="M7" t="n">
-        <v>67625.86</v>
+        <v>68463.35000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>68029.27</v>
+        <v>69190.58</v>
       </c>
       <c r="O7" t="n">
-        <v>70046.31</v>
+        <v>69886.89</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1109,7 +1109,7 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1141,74 +1141,76 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>68526.72</v>
+        <v>68410.63</v>
       </c>
       <c r="C8" t="n">
-        <v>69374.86</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>68271.91</v>
+        <v>66653.11</v>
       </c>
       <c r="E8" t="n">
-        <v>68557.73</v>
+        <v>67242.73</v>
       </c>
       <c r="F8" t="n">
-        <v>813.88</v>
+        <v>-1315</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0192</v>
       </c>
       <c r="H8" t="n">
-        <v>1102.95</v>
+        <v>2425.1</v>
       </c>
       <c r="I8" t="n">
-        <v>65569.89</v>
+        <v>67168.95</v>
       </c>
       <c r="J8" t="n">
-        <v>66312.58</v>
+        <v>67321.95</v>
       </c>
       <c r="K8" t="n">
-        <v>67024.35000000001</v>
+        <v>68006.25</v>
       </c>
       <c r="L8" t="n">
-        <v>67736.12</v>
+        <v>68690.55</v>
       </c>
       <c r="M8" t="n">
-        <v>68463.35000000001</v>
+        <v>69109.2</v>
       </c>
       <c r="N8" t="n">
-        <v>69190.58</v>
+        <v>69527.85000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>69886.89</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+        <v>70477.81</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1218,78 +1220,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68410.63</v>
+        <v>67002.94</v>
       </c>
       <c r="C9" t="n">
-        <v>69078.21000000001</v>
+        <v>67800.17999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>66653.11</v>
+        <v>66268.60000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>67242.73</v>
+        <v>67743.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-1315</v>
+        <v>500.77</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0074</v>
       </c>
       <c r="H9" t="n">
-        <v>2425.1</v>
+        <v>1531.58</v>
       </c>
       <c r="I9" t="n">
-        <v>67168.95</v>
+        <v>64228.01</v>
       </c>
       <c r="J9" t="n">
-        <v>67321.95</v>
+        <v>64506.16</v>
       </c>
       <c r="K9" t="n">
-        <v>68006.25</v>
+        <v>66030.17999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>68690.55</v>
+        <v>67554.19</v>
       </c>
       <c r="M9" t="n">
-        <v>69109.2</v>
+        <v>68455.28</v>
       </c>
       <c r="N9" t="n">
-        <v>69527.85000000001</v>
+        <v>69356.36</v>
       </c>
       <c r="O9" t="n">
-        <v>70477.81</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>71503.31</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1306,55 +1298,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>67002.94</v>
+        <v>67989.74000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>67800.17999999999</v>
+        <v>68798.24000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>66268.60000000001</v>
+        <v>67833.17</v>
       </c>
       <c r="E10" t="n">
-        <v>67743.5</v>
+        <v>68751.50999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>500.77</v>
+        <v>1008.01</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0149</v>
       </c>
       <c r="H10" t="n">
-        <v>1531.58</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>64228.01</v>
+        <v>64737.02</v>
       </c>
       <c r="J10" t="n">
-        <v>64506.16</v>
+        <v>66566.48</v>
       </c>
       <c r="K10" t="n">
-        <v>66030.17999999999</v>
+        <v>66977.71000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>67554.19</v>
+        <v>67388.95</v>
       </c>
       <c r="M10" t="n">
-        <v>68455.28</v>
+        <v>68509.28999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>69356.36</v>
+        <v>69629.63</v>
       </c>
       <c r="O10" t="n">
-        <v>71503.31</v>
+        <v>69331.75999999999</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1365,13 +1361,15 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1386,76 +1384,80 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>67989.74000000001</v>
+        <v>67900.42999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>68798.24000000001</v>
+        <v>68069.82000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>67833.17</v>
+        <v>66499.49000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>68751.50999999999</v>
+        <v>66835.53999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>1008.01</v>
+        <v>-1915.97</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0279</v>
       </c>
       <c r="H11" t="n">
-        <v>965.0700000000001</v>
+        <v>1570.33</v>
       </c>
       <c r="I11" t="n">
-        <v>64737.02</v>
+        <v>66868.10000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>66566.48</v>
+        <v>68004.34</v>
       </c>
       <c r="K11" t="n">
-        <v>66977.71000000001</v>
+        <v>68268.97</v>
       </c>
       <c r="L11" t="n">
-        <v>67388.95</v>
+        <v>68533.61</v>
       </c>
       <c r="M11" t="n">
-        <v>68509.28999999999</v>
+        <v>69234.03999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>69629.63</v>
+        <v>69934.48</v>
       </c>
       <c r="O11" t="n">
-        <v>69331.75999999999</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+        <v>69763.31</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1468,59 +1470,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67900.42999999999</v>
+        <v>66339.85000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>68069.82000000001</v>
+        <v>66441.77</v>
       </c>
       <c r="D12" t="n">
-        <v>66499.49000000001</v>
+        <v>62704.6</v>
       </c>
       <c r="E12" t="n">
-        <v>66835.53999999999</v>
+        <v>64141.12</v>
       </c>
       <c r="F12" t="n">
-        <v>-1915.97</v>
+        <v>-2694.42</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0403</v>
       </c>
       <c r="H12" t="n">
-        <v>1570.33</v>
+        <v>3737.17</v>
       </c>
       <c r="I12" t="n">
-        <v>66868.10000000001</v>
+        <v>64929.16</v>
       </c>
       <c r="J12" t="n">
-        <v>68004.34</v>
+        <v>65040.65</v>
       </c>
       <c r="K12" t="n">
-        <v>68268.97</v>
+        <v>66050.38</v>
       </c>
       <c r="L12" t="n">
-        <v>68533.61</v>
+        <v>67060.10000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>69234.03999999999</v>
+        <v>67620.7</v>
       </c>
       <c r="N12" t="n">
-        <v>69934.48</v>
+        <v>68181.31</v>
       </c>
       <c r="O12" t="n">
-        <v>69763.31</v>
+        <v>69640.14999999999</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -1537,7 +1535,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1561,74 +1559,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>66339.85000000001</v>
+        <v>64544.05</v>
       </c>
       <c r="C13" t="n">
-        <v>66441.77</v>
+        <v>66232.19</v>
       </c>
       <c r="D13" t="n">
-        <v>62704.6</v>
+        <v>64203.47</v>
       </c>
       <c r="E13" t="n">
-        <v>64141.12</v>
+        <v>66232.19</v>
       </c>
       <c r="F13" t="n">
-        <v>-2694.42</v>
+        <v>2091.07</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0326</v>
       </c>
       <c r="H13" t="n">
-        <v>3737.17</v>
+        <v>2028.72</v>
       </c>
       <c r="I13" t="n">
-        <v>64929.16</v>
+        <v>58967.43</v>
       </c>
       <c r="J13" t="n">
-        <v>65040.65</v>
+        <v>60187.92</v>
       </c>
       <c r="K13" t="n">
-        <v>66050.38</v>
+        <v>62272.54</v>
       </c>
       <c r="L13" t="n">
-        <v>67060.10000000001</v>
+        <v>64357.15</v>
       </c>
       <c r="M13" t="n">
-        <v>67620.7</v>
+        <v>66009.71000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>68181.31</v>
+        <v>67662.25999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>69640.14999999999</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
+        <v>70178.95</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1640,55 +1634,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>64544.05</v>
+        <v>66449.27</v>
       </c>
       <c r="C14" t="n">
-        <v>66232.19</v>
+        <v>67592.2</v>
       </c>
       <c r="D14" t="n">
-        <v>64203.47</v>
+        <v>65955.60000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>66232.19</v>
+        <v>66115.60000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>2091.07</v>
+        <v>-116.59</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0326</v>
+        <v>-0.0018</v>
       </c>
       <c r="H14" t="n">
-        <v>2028.72</v>
+        <v>1636.6</v>
       </c>
       <c r="I14" t="n">
-        <v>58967.43</v>
+        <v>62174.75</v>
       </c>
       <c r="J14" t="n">
-        <v>60187.92</v>
+        <v>64710.65</v>
       </c>
       <c r="K14" t="n">
-        <v>62272.54</v>
+        <v>65217.83</v>
       </c>
       <c r="L14" t="n">
-        <v>64357.15</v>
+        <v>65725.00999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>66009.71000000001</v>
+        <v>67246.55</v>
       </c>
       <c r="N14" t="n">
-        <v>67662.25999999999</v>
+        <v>68768.09</v>
       </c>
       <c r="O14" t="n">
-        <v>70178.95</v>
+        <v>68260.91</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1699,14 +1697,14 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U14" s="8" t="n">
@@ -1729,50 +1727,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66449.27</v>
+        <v>66421.00999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>67592.2</v>
+        <v>67022.37</v>
       </c>
       <c r="D15" t="n">
-        <v>65955.60000000001</v>
+        <v>66208.66</v>
       </c>
       <c r="E15" t="n">
-        <v>66115.60000000001</v>
+        <v>66422.60000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-116.59</v>
+        <v>307</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0046</v>
       </c>
       <c r="H15" t="n">
-        <v>1636.6</v>
+        <v>813.71</v>
       </c>
       <c r="I15" t="n">
-        <v>62174.75</v>
+        <v>64319</v>
       </c>
       <c r="J15" t="n">
-        <v>64710.65</v>
+        <v>64149.85</v>
       </c>
       <c r="K15" t="n">
-        <v>65217.83</v>
+        <v>65297.3</v>
       </c>
       <c r="L15" t="n">
-        <v>65725.00999999999</v>
+        <v>66444.75</v>
       </c>
       <c r="M15" t="n">
-        <v>67246.55</v>
+        <v>66933.89999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>68768.09</v>
+        <v>67423.05</v>
       </c>
       <c r="O15" t="n">
-        <v>68260.91</v>
+        <v>69228.8</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1785,7 +1783,7 @@
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
@@ -1813,69 +1811,73 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>66421.00999999999</v>
+        <v>65584.25</v>
       </c>
       <c r="C16" t="n">
-        <v>67022.37</v>
+        <v>65720.81</v>
       </c>
       <c r="D16" t="n">
-        <v>66208.66</v>
+        <v>64201.03</v>
       </c>
       <c r="E16" t="n">
-        <v>66422.60000000001</v>
+        <v>64611.15</v>
       </c>
       <c r="F16" t="n">
-        <v>307</v>
+        <v>-1811.45</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0273</v>
       </c>
       <c r="H16" t="n">
-        <v>813.71</v>
+        <v>1519.78</v>
       </c>
       <c r="I16" t="n">
-        <v>64319</v>
+        <v>65394.95</v>
       </c>
       <c r="J16" t="n">
-        <v>64149.85</v>
+        <v>65512.44</v>
       </c>
       <c r="K16" t="n">
-        <v>65297.3</v>
+        <v>66015.75</v>
       </c>
       <c r="L16" t="n">
-        <v>66444.75</v>
+        <v>66519.06</v>
       </c>
       <c r="M16" t="n">
-        <v>66933.89999999999</v>
+        <v>66829.46000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>67423.05</v>
+        <v>67139.86</v>
       </c>
       <c r="O16" t="n">
-        <v>69228.8</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67836.08</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1888,78 +1890,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>65584.25</v>
+        <v>65164.98</v>
       </c>
       <c r="C17" t="n">
-        <v>65720.81</v>
+        <v>65220.69</v>
       </c>
       <c r="D17" t="n">
-        <v>64201.03</v>
+        <v>64123.4</v>
       </c>
       <c r="E17" t="n">
-        <v>64611.15</v>
+        <v>64931.19</v>
       </c>
       <c r="F17" t="n">
-        <v>-1811.45</v>
+        <v>320.04</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.005</v>
       </c>
       <c r="H17" t="n">
-        <v>1519.78</v>
+        <v>1097.29</v>
       </c>
       <c r="I17" t="n">
-        <v>65394.95</v>
+        <v>62681.25</v>
       </c>
       <c r="J17" t="n">
-        <v>65512.44</v>
+        <v>62916.48</v>
       </c>
       <c r="K17" t="n">
-        <v>66015.75</v>
+        <v>63851.26</v>
       </c>
       <c r="L17" t="n">
-        <v>66519.06</v>
+        <v>64786.04</v>
       </c>
       <c r="M17" t="n">
-        <v>66829.46000000001</v>
+        <v>65371.04</v>
       </c>
       <c r="N17" t="n">
-        <v>67139.86</v>
+        <v>65956.03999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>67836.08</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67240.59</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1976,68 +1968,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>65164.98</v>
+        <v>64539.92</v>
       </c>
       <c r="C18" t="n">
-        <v>65220.69</v>
+        <v>64573.18</v>
       </c>
       <c r="D18" t="n">
-        <v>64123.4</v>
+        <v>61923.6</v>
       </c>
       <c r="E18" t="n">
-        <v>64931.19</v>
+        <v>62364.92</v>
       </c>
       <c r="F18" t="n">
-        <v>320.04</v>
+        <v>-2566.27</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0395</v>
       </c>
       <c r="H18" t="n">
-        <v>1097.29</v>
+        <v>2649.58</v>
       </c>
       <c r="I18" t="n">
-        <v>62681.25</v>
+        <v>63026.11</v>
       </c>
       <c r="J18" t="n">
-        <v>62916.48</v>
+        <v>63963.47</v>
       </c>
       <c r="K18" t="n">
-        <v>63851.26</v>
+        <v>64382.54</v>
       </c>
       <c r="L18" t="n">
-        <v>64786.04</v>
+        <v>64801.62</v>
       </c>
       <c r="M18" t="n">
-        <v>65371.04</v>
+        <v>65479.84</v>
       </c>
       <c r="N18" t="n">
-        <v>65956.03999999999</v>
+        <v>66158.06</v>
       </c>
       <c r="O18" t="n">
-        <v>67240.59</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+        <v>66317.98</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2054,76 +2056,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>64539.92</v>
+        <v>62734.68</v>
       </c>
       <c r="C19" t="n">
-        <v>64573.18</v>
+        <v>63138.04</v>
       </c>
       <c r="D19" t="n">
-        <v>61923.6</v>
+        <v>60448.9</v>
       </c>
       <c r="E19" t="n">
-        <v>62364.92</v>
+        <v>61434.19</v>
       </c>
       <c r="F19" t="n">
-        <v>-2566.27</v>
+        <v>-930.73</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0149</v>
       </c>
       <c r="H19" t="n">
-        <v>2649.58</v>
+        <v>2689.14</v>
       </c>
       <c r="I19" t="n">
-        <v>63026.11</v>
+        <v>59274.02</v>
       </c>
       <c r="J19" t="n">
-        <v>63963.47</v>
+        <v>59273.61</v>
       </c>
       <c r="K19" t="n">
-        <v>64382.54</v>
+        <v>61040.13</v>
       </c>
       <c r="L19" t="n">
-        <v>64801.62</v>
+        <v>62806.66</v>
       </c>
       <c r="M19" t="n">
-        <v>65479.84</v>
+        <v>63689.71</v>
       </c>
       <c r="N19" t="n">
-        <v>66158.06</v>
+        <v>64572.77</v>
       </c>
       <c r="O19" t="n">
-        <v>66317.98</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>67222.75999999999</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2147,50 +2141,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>62734.68</v>
+        <v>61258.34</v>
       </c>
       <c r="C20" t="n">
-        <v>63138.04</v>
+        <v>62924.84</v>
       </c>
       <c r="D20" t="n">
-        <v>60448.9</v>
+        <v>61049.7</v>
       </c>
       <c r="E20" t="n">
-        <v>61434.19</v>
+        <v>61867.43</v>
       </c>
       <c r="F20" t="n">
-        <v>-930.73</v>
+        <v>433.24</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0071</v>
       </c>
       <c r="H20" t="n">
-        <v>2689.14</v>
+        <v>1875.14</v>
       </c>
       <c r="I20" t="n">
-        <v>59274.02</v>
+        <v>57759.76</v>
       </c>
       <c r="J20" t="n">
-        <v>59273.61</v>
+        <v>58565.41</v>
       </c>
       <c r="K20" t="n">
-        <v>61040.13</v>
+        <v>60089.62</v>
       </c>
       <c r="L20" t="n">
-        <v>62806.66</v>
+        <v>61613.83</v>
       </c>
       <c r="M20" t="n">
-        <v>63689.71</v>
+        <v>62778.76</v>
       </c>
       <c r="N20" t="n">
-        <v>64572.77</v>
+        <v>63943.69</v>
       </c>
       <c r="O20" t="n">
-        <v>67222.75999999999</v>
+        <v>65827.17999999999</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2198,18 +2192,18 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R20" s="6" t="n">
+        <v/>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2222,55 +2216,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>61258.34</v>
+        <v>61957.1</v>
       </c>
       <c r="C21" t="n">
-        <v>62924.84</v>
+        <v>65364.73</v>
       </c>
       <c r="D21" t="n">
-        <v>61049.7</v>
+        <v>61948.23</v>
       </c>
       <c r="E21" t="n">
-        <v>61867.43</v>
+        <v>64362.02</v>
       </c>
       <c r="F21" t="n">
-        <v>433.24</v>
+        <v>2494.59</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0403</v>
       </c>
       <c r="H21" t="n">
-        <v>1875.14</v>
+        <v>3416.5</v>
       </c>
       <c r="I21" t="n">
-        <v>57759.76</v>
+        <v>59174.56</v>
       </c>
       <c r="J21" t="n">
-        <v>58565.41</v>
+        <v>59932.37</v>
       </c>
       <c r="K21" t="n">
-        <v>60089.62</v>
+        <v>60929.86</v>
       </c>
       <c r="L21" t="n">
-        <v>61613.83</v>
+        <v>61927.35</v>
       </c>
       <c r="M21" t="n">
-        <v>62778.76</v>
+        <v>62805</v>
       </c>
       <c r="N21" t="n">
-        <v>63943.69</v>
+        <v>63682.65</v>
       </c>
       <c r="O21" t="n">
-        <v>65827.17999999999</v>
+        <v>64799.98</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2281,9 +2279,9 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2291,70 +2289,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>61957.1</v>
+        <v>63834.95</v>
       </c>
       <c r="C22" t="n">
-        <v>65364.73</v>
+        <v>63905.12</v>
       </c>
       <c r="D22" t="n">
-        <v>61948.23</v>
+        <v>62703.47</v>
       </c>
       <c r="E22" t="n">
-        <v>64362.02</v>
+        <v>63754.9</v>
       </c>
       <c r="F22" t="n">
-        <v>2494.59</v>
+        <v>-607.12</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0403</v>
+        <v>-0.0094</v>
       </c>
       <c r="H22" t="n">
-        <v>3416.5</v>
+        <v>1201.65</v>
       </c>
       <c r="I22" t="n">
-        <v>59174.56</v>
+        <v>58531.73</v>
       </c>
       <c r="J22" t="n">
-        <v>59932.37</v>
+        <v>61298.29</v>
       </c>
       <c r="K22" t="n">
-        <v>60929.86</v>
+        <v>62653.77</v>
       </c>
       <c r="L22" t="n">
-        <v>61927.35</v>
+        <v>64009.25</v>
       </c>
       <c r="M22" t="n">
-        <v>62805</v>
+        <v>66070.27</v>
       </c>
       <c r="N22" t="n">
-        <v>63682.65</v>
+        <v>68131.28999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>64799.98</v>
+        <v>68781.23</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2367,78 +2365,76 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>63834.95</v>
+        <v>63995.28</v>
       </c>
       <c r="C23" t="n">
-        <v>63905.12</v>
+        <v>64240.5</v>
       </c>
       <c r="D23" t="n">
-        <v>62703.47</v>
+        <v>62864.43</v>
       </c>
       <c r="E23" t="n">
-        <v>63754.9</v>
+        <v>63957.53</v>
       </c>
       <c r="F23" t="n">
-        <v>-607.12</v>
+        <v>202.63</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0032</v>
       </c>
       <c r="H23" t="n">
-        <v>1201.65</v>
+        <v>1376.07</v>
       </c>
       <c r="I23" t="n">
-        <v>58531.73</v>
+        <v>61501.82</v>
       </c>
       <c r="J23" t="n">
-        <v>61298.29</v>
+        <v>62778.55</v>
       </c>
       <c r="K23" t="n">
-        <v>62653.77</v>
+        <v>63154.07</v>
       </c>
       <c r="L23" t="n">
-        <v>64009.25</v>
+        <v>63529.6</v>
       </c>
       <c r="M23" t="n">
-        <v>66070.27</v>
+        <v>64355.72</v>
       </c>
       <c r="N23" t="n">
-        <v>68131.28999999999</v>
+        <v>65181.85</v>
       </c>
       <c r="O23" t="n">
-        <v>68781.23</v>
+        <v>65106.77</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2446,16 +2442,20 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2468,59 +2468,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63995.28</v>
+        <v>64565.27</v>
       </c>
       <c r="C24" t="n">
-        <v>64240.5</v>
+        <v>66302.52</v>
       </c>
       <c r="D24" t="n">
-        <v>62864.43</v>
+        <v>64555.52</v>
       </c>
       <c r="E24" t="n">
-        <v>63957.53</v>
+        <v>66300.44</v>
       </c>
       <c r="F24" t="n">
-        <v>202.63</v>
+        <v>2342.91</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0366</v>
       </c>
       <c r="H24" t="n">
-        <v>1376.07</v>
+        <v>1747</v>
       </c>
       <c r="I24" t="n">
-        <v>61501.82</v>
+        <v>61488.36</v>
       </c>
       <c r="J24" t="n">
-        <v>62778.55</v>
+        <v>62783.99</v>
       </c>
       <c r="K24" t="n">
-        <v>63154.07</v>
+        <v>63269.5</v>
       </c>
       <c r="L24" t="n">
-        <v>63529.6</v>
+        <v>63755</v>
       </c>
       <c r="M24" t="n">
-        <v>64355.72</v>
+        <v>64645.57</v>
       </c>
       <c r="N24" t="n">
-        <v>65181.85</v>
+        <v>65536.13</v>
       </c>
       <c r="O24" t="n">
-        <v>65106.77</v>
+        <v>65616.57000000001</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2528,26 +2524,28 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
@@ -2559,134 +2557,136 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>64565.27</v>
+        <v>65896</v>
       </c>
       <c r="C25" t="n">
-        <v>66302.52</v>
+        <v>65983.13</v>
       </c>
       <c r="D25" t="n">
-        <v>64555.52</v>
+        <v>64942.07</v>
       </c>
       <c r="E25" t="n">
-        <v>66300.44</v>
+        <v>65683.25999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>2342.91</v>
+        <v>-617.1799999999999</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0366</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>1747</v>
+        <v>1041.06</v>
       </c>
       <c r="I25" t="n">
-        <v>61488.36</v>
+        <v>62808.52</v>
       </c>
       <c r="J25" t="n">
-        <v>62783.99</v>
+        <v>64989.14</v>
       </c>
       <c r="K25" t="n">
-        <v>63269.5</v>
+        <v>65426.94</v>
       </c>
       <c r="L25" t="n">
-        <v>63755</v>
+        <v>65864.73</v>
       </c>
       <c r="M25" t="n">
-        <v>64645.57</v>
+        <v>67173.94</v>
       </c>
       <c r="N25" t="n">
-        <v>65536.13</v>
+        <v>68483.14999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>65616.57000000001</v>
+        <v>68049.53</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>65896</v>
+        <v>65746.13</v>
       </c>
       <c r="C26" t="n">
-        <v>65983.13</v>
+        <v>65990.72</v>
       </c>
       <c r="D26" t="n">
-        <v>64942.07</v>
+        <v>64651.49</v>
       </c>
       <c r="E26" t="n">
-        <v>65683.25999999999</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-617.1799999999999</v>
+        <v>-76.55</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="H26" t="n">
-        <v>1041.06</v>
+        <v>1339.23</v>
       </c>
       <c r="I26" t="n">
-        <v>62808.52</v>
+        <v>63901.01</v>
       </c>
       <c r="J26" t="n">
-        <v>64989.14</v>
+        <v>64752.52</v>
       </c>
       <c r="K26" t="n">
-        <v>65426.94</v>
+        <v>65162.73</v>
       </c>
       <c r="L26" t="n">
-        <v>65864.73</v>
+        <v>65572.92999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>67173.94</v>
+        <v>66203.78999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>68483.14999999999</v>
+        <v>66834.64999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>68049.53</v>
+        <v>67024.2</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2729,74 +2729,74 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>65746.13</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>65990.72</v>
+        <v>67006.84</v>
       </c>
       <c r="D27" t="n">
-        <v>64651.49</v>
+        <v>65848.58</v>
       </c>
       <c r="E27" t="n">
-        <v>65606.71000000001</v>
+        <v>66970.22</v>
       </c>
       <c r="F27" t="n">
-        <v>-76.55</v>
+        <v>1363.51</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0208</v>
       </c>
       <c r="H27" t="n">
-        <v>1339.23</v>
+        <v>1158.27</v>
       </c>
       <c r="I27" t="n">
-        <v>63901.01</v>
+        <v>63312.26</v>
       </c>
       <c r="J27" t="n">
-        <v>64752.52</v>
+        <v>64410.28</v>
       </c>
       <c r="K27" t="n">
-        <v>65162.73</v>
+        <v>64937.1</v>
       </c>
       <c r="L27" t="n">
-        <v>65572.92999999999</v>
+        <v>65463.91</v>
       </c>
       <c r="M27" t="n">
-        <v>66203.78999999999</v>
+        <v>66276.33</v>
       </c>
       <c r="N27" t="n">
-        <v>66834.64999999999</v>
+        <v>67088.75</v>
       </c>
       <c r="O27" t="n">
-        <v>67024.2</v>
+        <v>67329.95</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2806,59 +2806,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>65905.10000000001</v>
+        <v>66994.05</v>
       </c>
       <c r="C28" t="n">
-        <v>67006.84</v>
+        <v>67569.36</v>
       </c>
       <c r="D28" t="n">
-        <v>65848.58</v>
+        <v>66735.75999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>66970.22</v>
+        <v>67524.06</v>
       </c>
       <c r="F28" t="n">
-        <v>1363.51</v>
+        <v>553.84</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="H28" t="n">
-        <v>1158.27</v>
+        <v>833.6</v>
       </c>
       <c r="I28" t="n">
-        <v>63312.26</v>
+        <v>64690.31</v>
       </c>
       <c r="J28" t="n">
-        <v>64410.28</v>
+        <v>66083.21000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>64937.1</v>
+        <v>66391.09</v>
       </c>
       <c r="L28" t="n">
-        <v>65463.91</v>
+        <v>66698.96000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>66276.33</v>
+        <v>67549.35000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>67088.75</v>
+        <v>68399.74000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>67329.95</v>
+        <v>68165.11</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2869,20 +2865,18 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2897,50 +2891,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>66994.05</v>
+        <v>68033.17</v>
       </c>
       <c r="C29" t="n">
-        <v>67569.36</v>
+        <v>68799.71000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>66735.75999999999</v>
+        <v>68006.17</v>
       </c>
       <c r="E29" t="n">
-        <v>67524.06</v>
+        <v>68308.59</v>
       </c>
       <c r="F29" t="n">
-        <v>553.84</v>
+        <v>784.53</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0116</v>
       </c>
       <c r="H29" t="n">
-        <v>833.6</v>
+        <v>793.54</v>
       </c>
       <c r="I29" t="n">
-        <v>64690.31</v>
+        <v>65902.16</v>
       </c>
       <c r="J29" t="n">
-        <v>66083.21000000001</v>
+        <v>66876.21000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>66391.09</v>
+        <v>67107.25999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>66698.96000000001</v>
+        <v>67338.31</v>
       </c>
       <c r="M29" t="n">
-        <v>67549.35000000001</v>
+        <v>67940.86</v>
       </c>
       <c r="N29" t="n">
-        <v>68399.74000000001</v>
+        <v>68543.42</v>
       </c>
       <c r="O29" t="n">
-        <v>68165.11</v>
+        <v>68402.96000000001</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2951,21 +2945,25 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
@@ -2977,50 +2975,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>68033.17</v>
+        <v>68811.17</v>
       </c>
       <c r="C30" t="n">
-        <v>68799.71000000001</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>68006.17</v>
+        <v>68471.14999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>68308.59</v>
+        <v>68713.8</v>
       </c>
       <c r="F30" t="n">
-        <v>784.53</v>
+        <v>405.2</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0059</v>
       </c>
       <c r="H30" t="n">
-        <v>793.54</v>
+        <v>1137.09</v>
       </c>
       <c r="I30" t="n">
-        <v>65902.16</v>
+        <v>67212.63</v>
       </c>
       <c r="J30" t="n">
-        <v>66876.21000000001</v>
+        <v>67467.88</v>
       </c>
       <c r="K30" t="n">
-        <v>67107.25999999999</v>
+        <v>67911.82000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>67338.31</v>
+        <v>68355.77</v>
       </c>
       <c r="M30" t="n">
-        <v>67940.86</v>
+        <v>68705.36</v>
       </c>
       <c r="N30" t="n">
-        <v>68543.42</v>
+        <v>69054.96000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>68402.96000000001</v>
+        <v>69593.25</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3031,14 +3029,14 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U30" s="8" t="inlineStr">
@@ -3048,7 +3046,7 @@
       </c>
       <c r="V30" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W30" s="9" t="inlineStr">
@@ -3061,50 +3059,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>68811.17</v>
+        <v>68882.06</v>
       </c>
       <c r="C31" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>68471.14999999999</v>
+        <v>68492.03999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>68713.8</v>
+        <v>69220.25</v>
       </c>
       <c r="F31" t="n">
-        <v>405.2</v>
+        <v>506.45</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="H31" t="n">
-        <v>1137.09</v>
+        <v>733.53</v>
       </c>
       <c r="I31" t="n">
-        <v>67212.63</v>
+        <v>67334.05</v>
       </c>
       <c r="J31" t="n">
-        <v>67467.88</v>
+        <v>67413.75</v>
       </c>
       <c r="K31" t="n">
-        <v>67911.82000000001</v>
+        <v>68145.25</v>
       </c>
       <c r="L31" t="n">
-        <v>68355.77</v>
+        <v>68876.75</v>
       </c>
       <c r="M31" t="n">
-        <v>68705.36</v>
+        <v>69282.34</v>
       </c>
       <c r="N31" t="n">
-        <v>69054.96000000001</v>
+        <v>69687.94</v>
       </c>
       <c r="O31" t="n">
-        <v>69593.25</v>
+        <v>70745.34</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3115,7 +3113,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3125,89 +3123,93 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>68882.06</v>
+        <v>68847.35000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>69225.57000000001</v>
+        <v>69093.2</v>
       </c>
       <c r="D32" t="n">
-        <v>68492.03999999999</v>
+        <v>67368.96000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>69220.25</v>
+        <v>67460.73</v>
       </c>
       <c r="F32" t="n">
-        <v>506.45</v>
+        <v>-1759.52</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0254</v>
       </c>
       <c r="H32" t="n">
-        <v>733.53</v>
+        <v>1724.24</v>
       </c>
       <c r="I32" t="n">
-        <v>67334.05</v>
+        <v>67758.50999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>67413.75</v>
+        <v>68667.44</v>
       </c>
       <c r="K32" t="n">
-        <v>68145.25</v>
+        <v>68853.48</v>
       </c>
       <c r="L32" t="n">
-        <v>68876.75</v>
+        <v>69039.53</v>
       </c>
       <c r="M32" t="n">
-        <v>69282.34</v>
+        <v>69587.02</v>
       </c>
       <c r="N32" t="n">
-        <v>69687.94</v>
+        <v>70134.5</v>
       </c>
       <c r="O32" t="n">
-        <v>70745.34</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+        <v>69959.10000000001</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3215,81 +3217,77 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>68847.35000000001</v>
+        <v>66812.27</v>
       </c>
       <c r="C33" t="n">
-        <v>69093.2</v>
+        <v>66833.50999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>67368.96000000001</v>
+        <v>65133.98</v>
       </c>
       <c r="E33" t="n">
-        <v>67460.73</v>
+        <v>65326.42</v>
       </c>
       <c r="F33" t="n">
-        <v>-1759.52</v>
+        <v>-2134.3</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="H33" t="n">
-        <v>1724.24</v>
+        <v>1699.53</v>
       </c>
       <c r="I33" t="n">
-        <v>67758.50999999999</v>
+        <v>65644.72</v>
       </c>
       <c r="J33" t="n">
-        <v>68667.44</v>
+        <v>65351.31</v>
       </c>
       <c r="K33" t="n">
-        <v>68853.48</v>
+        <v>66598.61</v>
       </c>
       <c r="L33" t="n">
-        <v>69039.53</v>
+        <v>67845.89999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>69587.02</v>
+        <v>68322.85000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>70134.5</v>
+        <v>68799.78999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>69959.10000000001</v>
+        <v>70817.45</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3313,74 +3311,70 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>66812.27</v>
+        <v>65732.78999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>66833.50999999999</v>
+        <v>66325.32000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>65133.98</v>
+        <v>65652.25</v>
       </c>
       <c r="E34" t="n">
-        <v>65326.42</v>
+        <v>66216.78999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>-2134.3</v>
+        <v>890.37</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H34" t="n">
-        <v>1699.53</v>
+        <v>673.0700000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>65644.72</v>
+        <v>63434.45</v>
       </c>
       <c r="J34" t="n">
-        <v>65351.31</v>
+        <v>63298.23</v>
       </c>
       <c r="K34" t="n">
-        <v>66598.61</v>
+        <v>64476.66</v>
       </c>
       <c r="L34" t="n">
-        <v>67845.89999999999</v>
+        <v>65655.08</v>
       </c>
       <c r="M34" t="n">
-        <v>68322.85000000001</v>
+        <v>66176.19</v>
       </c>
       <c r="N34" t="n">
-        <v>68799.78999999999</v>
+        <v>66697.28999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>70817.45</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
+        <v>68533.03999999999</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3392,74 +3386,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>65732.78999999999</v>
+        <v>65427.69</v>
       </c>
       <c r="C35" t="n">
-        <v>66325.32000000001</v>
+        <v>66125.88</v>
       </c>
       <c r="D35" t="n">
-        <v>65652.25</v>
+        <v>65260.22</v>
       </c>
       <c r="E35" t="n">
-        <v>66216.78999999999</v>
+        <v>66016.36</v>
       </c>
       <c r="F35" t="n">
-        <v>890.37</v>
+        <v>-200.43</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.003</v>
       </c>
       <c r="H35" t="n">
-        <v>673.0700000000001</v>
+        <v>865.66</v>
       </c>
       <c r="I35" t="n">
-        <v>63434.45</v>
+        <v>64979.18</v>
       </c>
       <c r="J35" t="n">
-        <v>63298.23</v>
+        <v>65657.72</v>
       </c>
       <c r="K35" t="n">
-        <v>64476.66</v>
+        <v>65880.25</v>
       </c>
       <c r="L35" t="n">
-        <v>65655.08</v>
+        <v>66102.78999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>66176.19</v>
+        <v>66553.32000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>66697.28999999999</v>
+        <v>67003.86</v>
       </c>
       <c r="O35" t="n">
-        <v>68533.03999999999</v>
+        <v>66998.39</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3472,76 +3472,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>65427.69</v>
+        <v>65978.95</v>
       </c>
       <c r="C36" t="n">
-        <v>66125.88</v>
+        <v>66257.73</v>
       </c>
       <c r="D36" t="n">
-        <v>65260.22</v>
+        <v>65470.95</v>
       </c>
       <c r="E36" t="n">
-        <v>66016.36</v>
+        <v>65528.09</v>
       </c>
       <c r="F36" t="n">
-        <v>-200.43</v>
+        <v>-488.27</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0074</v>
       </c>
       <c r="H36" t="n">
-        <v>865.66</v>
+        <v>786.78</v>
       </c>
       <c r="I36" t="n">
-        <v>64979.18</v>
+        <v>64394.55</v>
       </c>
       <c r="J36" t="n">
-        <v>65657.72</v>
+        <v>65312.35</v>
       </c>
       <c r="K36" t="n">
-        <v>65880.25</v>
+        <v>65583.53</v>
       </c>
       <c r="L36" t="n">
-        <v>66102.78999999999</v>
+        <v>65854.71000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>66553.32000000001</v>
+        <v>66449.19</v>
       </c>
       <c r="N36" t="n">
-        <v>67003.86</v>
+        <v>67043.67999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>66998.39</v>
+        <v>66991.55</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q36" s="6" t="n">
+        <v/>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3558,75 +3552,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>65978.95</v>
+        <v>65195.26</v>
       </c>
       <c r="C37" t="n">
-        <v>66257.73</v>
+        <v>65904.24000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>65470.95</v>
+        <v>64609.47</v>
       </c>
       <c r="E37" t="n">
-        <v>65528.09</v>
+        <v>65856.42999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>-488.27</v>
+        <v>328.34</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.005</v>
       </c>
       <c r="H37" t="n">
-        <v>786.78</v>
+        <v>1294.77</v>
       </c>
       <c r="I37" t="n">
-        <v>64394.55</v>
+        <v>64684.17</v>
       </c>
       <c r="J37" t="n">
-        <v>65312.35</v>
+        <v>64573.19</v>
       </c>
       <c r="K37" t="n">
-        <v>65583.53</v>
+        <v>65134.7</v>
       </c>
       <c r="L37" t="n">
-        <v>65854.71000000001</v>
+        <v>65696.21000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>66449.19</v>
+        <v>65921.48</v>
       </c>
       <c r="N37" t="n">
-        <v>67043.67999999999</v>
+        <v>66146.74000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>66991.55</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
+        <v>67044.5</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3640,72 +3642,68 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>65195.26</v>
+        <v>65604.49000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>65904.24000000001</v>
+        <v>66442.34</v>
       </c>
       <c r="D38" t="n">
-        <v>64609.47</v>
+        <v>65390.55</v>
       </c>
       <c r="E38" t="n">
-        <v>65856.42999999999</v>
+        <v>66262.16</v>
       </c>
       <c r="F38" t="n">
-        <v>328.34</v>
+        <v>405.73</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0062</v>
       </c>
       <c r="H38" t="n">
-        <v>1294.77</v>
+        <v>1051.79</v>
       </c>
       <c r="I38" t="n">
-        <v>64684.17</v>
+        <v>63314.7</v>
       </c>
       <c r="J38" t="n">
-        <v>64573.19</v>
+        <v>64861.44</v>
       </c>
       <c r="K38" t="n">
-        <v>65134.7</v>
+        <v>65209.04</v>
       </c>
       <c r="L38" t="n">
-        <v>65696.21000000001</v>
+        <v>65556.64</v>
       </c>
       <c r="M38" t="n">
-        <v>65921.48</v>
+        <v>66503.82000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>66146.74000000001</v>
+        <v>67450.99000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>67044.5</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67199.02</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
       </c>
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3728,57 +3726,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>65604.49000000001</v>
+        <v>66775.78</v>
       </c>
       <c r="C39" t="n">
-        <v>66442.34</v>
+        <v>66954.69</v>
       </c>
       <c r="D39" t="n">
-        <v>65390.55</v>
+        <v>65782.59</v>
       </c>
       <c r="E39" t="n">
-        <v>66262.16</v>
+        <v>66131.98</v>
       </c>
       <c r="F39" t="n">
-        <v>405.73</v>
+        <v>-130.18</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.002</v>
       </c>
       <c r="H39" t="n">
-        <v>1051.79</v>
+        <v>1172.09</v>
       </c>
       <c r="I39" t="n">
-        <v>63314.7</v>
+        <v>64338.76</v>
       </c>
       <c r="J39" t="n">
-        <v>64861.44</v>
+        <v>65383.22</v>
       </c>
       <c r="K39" t="n">
-        <v>65209.04</v>
+        <v>65736.25999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>65556.64</v>
+        <v>66089.3</v>
       </c>
       <c r="M39" t="n">
-        <v>66503.82000000001</v>
+        <v>66788.05</v>
       </c>
       <c r="N39" t="n">
-        <v>67450.99000000001</v>
+        <v>67486.8</v>
       </c>
       <c r="O39" t="n">
-        <v>67199.02</v>
+        <v>67494.14</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3789,14 +3787,14 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U39" s="8" t="n">
@@ -3812,57 +3810,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>66775.78</v>
+        <v>66104.49000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>66954.69</v>
+        <v>66842.82000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>65782.59</v>
+        <v>66012.2</v>
       </c>
       <c r="E40" t="n">
-        <v>66131.98</v>
+        <v>66405.56</v>
       </c>
       <c r="F40" t="n">
-        <v>-130.18</v>
+        <v>273.59</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0041</v>
       </c>
       <c r="H40" t="n">
-        <v>1172.09</v>
+        <v>830.62</v>
       </c>
       <c r="I40" t="n">
-        <v>64338.76</v>
+        <v>64610.5</v>
       </c>
       <c r="J40" t="n">
-        <v>65383.22</v>
+        <v>64841.55</v>
       </c>
       <c r="K40" t="n">
-        <v>65736.25999999999</v>
+        <v>65545.92999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>66089.3</v>
+        <v>66250.31</v>
       </c>
       <c r="M40" t="n">
-        <v>66788.05</v>
+        <v>66718.02</v>
       </c>
       <c r="N40" t="n">
-        <v>67486.8</v>
+        <v>67185.74000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>67494.14</v>
+        <v>68126.78</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3873,7 +3871,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3903,69 +3901,73 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>66104.49000000001</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C41" t="n">
-        <v>66842.82000000001</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>66012.2</v>
+        <v>64832.1</v>
       </c>
       <c r="E41" t="n">
-        <v>66405.56</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>273.59</v>
+        <v>-93.63</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0014</v>
       </c>
       <c r="H41" t="n">
-        <v>830.62</v>
+        <v>1479.83</v>
       </c>
       <c r="I41" t="n">
-        <v>64610.5</v>
+        <v>65181.59</v>
       </c>
       <c r="J41" t="n">
-        <v>64841.55</v>
+        <v>65563.97</v>
       </c>
       <c r="K41" t="n">
-        <v>65545.92999999999</v>
+        <v>65990.25</v>
       </c>
       <c r="L41" t="n">
-        <v>66250.31</v>
+        <v>66416.53999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>66718.02</v>
+        <v>66820.87</v>
       </c>
       <c r="N41" t="n">
-        <v>67185.74000000001</v>
+        <v>67225.21000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>68126.78</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+        <v>67673.44</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3978,78 +3980,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>65668.50999999999</v>
+        <v>65885.47</v>
       </c>
       <c r="C42" t="n">
-        <v>66311.92999999999</v>
+        <v>66525.7</v>
       </c>
       <c r="D42" t="n">
-        <v>64832.1</v>
+        <v>65576.61</v>
       </c>
       <c r="E42" t="n">
-        <v>66311.92999999999</v>
+        <v>66215.34</v>
       </c>
       <c r="F42" t="n">
-        <v>-93.63</v>
+        <v>-96.59</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0015</v>
       </c>
       <c r="H42" t="n">
-        <v>1479.83</v>
+        <v>949.09</v>
       </c>
       <c r="I42" t="n">
-        <v>65181.59</v>
+        <v>63352.27</v>
       </c>
       <c r="J42" t="n">
-        <v>65563.97</v>
+        <v>65202.06</v>
       </c>
       <c r="K42" t="n">
-        <v>65990.25</v>
+        <v>65572.02</v>
       </c>
       <c r="L42" t="n">
-        <v>66416.53999999999</v>
+        <v>65941.97</v>
       </c>
       <c r="M42" t="n">
-        <v>66820.87</v>
+        <v>67051.84</v>
       </c>
       <c r="N42" t="n">
-        <v>67225.21000000001</v>
+        <v>68161.71000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>67673.44</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67791.75999999999</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4066,68 +4058,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>65885.47</v>
+        <v>65195.43</v>
       </c>
       <c r="C43" t="n">
-        <v>66525.7</v>
+        <v>65195.43</v>
       </c>
       <c r="D43" t="n">
-        <v>65576.61</v>
+        <v>64215.47</v>
       </c>
       <c r="E43" t="n">
-        <v>66215.34</v>
+        <v>64325.64</v>
       </c>
       <c r="F43" t="n">
-        <v>-96.59</v>
+        <v>-1889.7</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0285</v>
       </c>
       <c r="H43" t="n">
-        <v>949.09</v>
+        <v>979.96</v>
       </c>
       <c r="I43" t="n">
-        <v>63352.27</v>
+        <v>64627.52</v>
       </c>
       <c r="J43" t="n">
-        <v>65202.06</v>
+        <v>65348.34</v>
       </c>
       <c r="K43" t="n">
-        <v>65572.02</v>
+        <v>65740.8</v>
       </c>
       <c r="L43" t="n">
-        <v>65941.97</v>
+        <v>66133.25</v>
       </c>
       <c r="M43" t="n">
-        <v>67051.84</v>
+        <v>66689.89</v>
       </c>
       <c r="N43" t="n">
-        <v>68161.71000000001</v>
+        <v>67246.53</v>
       </c>
       <c r="O43" t="n">
-        <v>67791.75999999999</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+        <v>67474.8</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4144,78 +4146,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="C44" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="D44" t="n">
-        <v>64215.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E44" t="n">
-        <v>64325.64</v>
+        <v>64214.48</v>
       </c>
       <c r="F44" t="n">
-        <v>-1889.7</v>
+        <v>-111.16</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0017</v>
       </c>
       <c r="H44" t="n">
-        <v>979.96</v>
+        <v>952.01</v>
       </c>
       <c r="I44" t="n">
-        <v>64627.52</v>
+        <v>63235.51</v>
       </c>
       <c r="J44" t="n">
-        <v>65348.34</v>
+        <v>63155.78</v>
       </c>
       <c r="K44" t="n">
-        <v>65740.8</v>
+        <v>63835.66</v>
       </c>
       <c r="L44" t="n">
-        <v>66133.25</v>
+        <v>64515.54</v>
       </c>
       <c r="M44" t="n">
-        <v>66689.89</v>
+        <v>64815.62</v>
       </c>
       <c r="N44" t="n">
-        <v>67246.53</v>
+        <v>65115.7</v>
       </c>
       <c r="O44" t="n">
-        <v>67474.8</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66175.39</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4237,50 +4231,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>64724.81</v>
+        <v>64498.94</v>
       </c>
       <c r="C45" t="n">
-        <v>64724.81</v>
+        <v>65182.45</v>
       </c>
       <c r="D45" t="n">
-        <v>63772.8</v>
+        <v>64228.47</v>
       </c>
       <c r="E45" t="n">
-        <v>64214.48</v>
+        <v>65020.94</v>
       </c>
       <c r="F45" t="n">
-        <v>-111.16</v>
+        <v>806.46</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="H45" t="n">
-        <v>952.01</v>
+        <v>953.98</v>
       </c>
       <c r="I45" t="n">
-        <v>63235.51</v>
+        <v>62820.79</v>
       </c>
       <c r="J45" t="n">
-        <v>63155.78</v>
+        <v>63245.31</v>
       </c>
       <c r="K45" t="n">
-        <v>63835.66</v>
+        <v>63738.48</v>
       </c>
       <c r="L45" t="n">
-        <v>64515.54</v>
+        <v>64231.64</v>
       </c>
       <c r="M45" t="n">
-        <v>64815.62</v>
+        <v>64690.48</v>
       </c>
       <c r="N45" t="n">
-        <v>65115.7</v>
+        <v>65149.33</v>
       </c>
       <c r="O45" t="n">
-        <v>66175.39</v>
+        <v>65676.82000000001</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4288,21 +4282,23 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4312,55 +4308,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>64498.94</v>
+        <v>65600.42</v>
       </c>
       <c r="C46" t="n">
-        <v>65182.45</v>
+        <v>66668.71000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>64228.47</v>
+        <v>65600.42</v>
       </c>
       <c r="E46" t="n">
-        <v>65020.94</v>
+        <v>66399.84</v>
       </c>
       <c r="F46" t="n">
-        <v>806.46</v>
+        <v>1378.9</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="H46" t="n">
-        <v>953.98</v>
+        <v>1068.29</v>
       </c>
       <c r="I46" t="n">
-        <v>62820.79</v>
+        <v>63274.49</v>
       </c>
       <c r="J46" t="n">
-        <v>63245.31</v>
+        <v>64224.7</v>
       </c>
       <c r="K46" t="n">
-        <v>63738.48</v>
+        <v>64543.95</v>
       </c>
       <c r="L46" t="n">
-        <v>64231.64</v>
+        <v>64863.2</v>
       </c>
       <c r="M46" t="n">
-        <v>64690.48</v>
+        <v>65497.93</v>
       </c>
       <c r="N46" t="n">
-        <v>65149.33</v>
+        <v>66132.66</v>
       </c>
       <c r="O46" t="n">
-        <v>65676.82000000001</v>
+        <v>66136.42999999999</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4371,7 +4371,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4383,171 +4383,167 @@
       </c>
       <c r="U46" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65600.42</v>
+        <v>65843.69</v>
       </c>
       <c r="C47" t="n">
-        <v>66668.71000000001</v>
+        <v>66791.84</v>
       </c>
       <c r="D47" t="n">
-        <v>65600.42</v>
+        <v>65269.33</v>
       </c>
       <c r="E47" t="n">
-        <v>66399.84</v>
+        <v>65269.33</v>
       </c>
       <c r="F47" t="n">
-        <v>1378.9</v>
+        <v>-1130.52</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.017</v>
       </c>
       <c r="H47" t="n">
-        <v>1068.29</v>
+        <v>1522.52</v>
       </c>
       <c r="I47" t="n">
-        <v>63274.49</v>
+        <v>64532.13</v>
       </c>
       <c r="J47" t="n">
-        <v>64224.7</v>
+        <v>65464.19</v>
       </c>
       <c r="K47" t="n">
-        <v>64543.95</v>
+        <v>65865.7</v>
       </c>
       <c r="L47" t="n">
-        <v>64863.2</v>
+        <v>66267.21000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>65497.93</v>
+        <v>66933.99000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>66132.66</v>
+        <v>67600.77</v>
       </c>
       <c r="O47" t="n">
-        <v>66136.42999999999</v>
+        <v>67737</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W47" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr"/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W47" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65843.69</v>
+        <v>65087.22</v>
       </c>
       <c r="C48" t="n">
-        <v>66791.84</v>
+        <v>65794.03</v>
       </c>
       <c r="D48" t="n">
-        <v>65269.33</v>
+        <v>65017.68</v>
       </c>
       <c r="E48" t="n">
-        <v>65269.33</v>
+        <v>65142.78</v>
       </c>
       <c r="F48" t="n">
-        <v>-1130.52</v>
+        <v>-126.55</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0019</v>
       </c>
       <c r="H48" t="n">
-        <v>1522.52</v>
+        <v>776.35</v>
       </c>
       <c r="I48" t="n">
-        <v>64532.13</v>
+        <v>63746.81</v>
       </c>
       <c r="J48" t="n">
-        <v>65464.19</v>
+        <v>63366.18</v>
       </c>
       <c r="K48" t="n">
-        <v>65865.7</v>
+        <v>64508.07</v>
       </c>
       <c r="L48" t="n">
-        <v>66267.21000000001</v>
+        <v>65649.96000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>66933.99000000001</v>
+        <v>66030.59</v>
       </c>
       <c r="N48" t="n">
-        <v>67600.77</v>
+        <v>66411.21000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>67737</v>
+        <v>68314.36</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4564,70 +4560,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65087.22</v>
+        <v>64768.53</v>
       </c>
       <c r="C49" t="n">
-        <v>65794.03</v>
+        <v>65270.95</v>
       </c>
       <c r="D49" t="n">
-        <v>65017.68</v>
+        <v>64186.68</v>
       </c>
       <c r="E49" t="n">
-        <v>65142.78</v>
+        <v>65270.95</v>
       </c>
       <c r="F49" t="n">
-        <v>-126.55</v>
+        <v>128.17</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="H49" t="n">
-        <v>776.35</v>
+        <v>1084.27</v>
       </c>
       <c r="I49" t="n">
-        <v>63746.81</v>
+        <v>64241.33</v>
       </c>
       <c r="J49" t="n">
-        <v>63366.18</v>
+        <v>64234.89</v>
       </c>
       <c r="K49" t="n">
-        <v>64508.07</v>
+        <v>64754.61</v>
       </c>
       <c r="L49" t="n">
-        <v>65649.96000000001</v>
+        <v>65274.32</v>
       </c>
       <c r="M49" t="n">
-        <v>66030.59</v>
+        <v>65530.96</v>
       </c>
       <c r="N49" t="n">
-        <v>66411.21000000001</v>
+        <v>65787.60000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>68314.36</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
+        <v>66570.38</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4646,64 +4644,66 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>64768.53</v>
+        <v>64276.82</v>
       </c>
       <c r="C50" t="n">
-        <v>65270.95</v>
+        <v>64312.02</v>
       </c>
       <c r="D50" t="n">
-        <v>64186.68</v>
+        <v>63208.63</v>
       </c>
       <c r="E50" t="n">
-        <v>65270.95</v>
+        <v>64011.34</v>
       </c>
       <c r="F50" t="n">
-        <v>128.17</v>
+        <v>-1259.61</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H50" t="n">
-        <v>1084.27</v>
+        <v>1103.39</v>
       </c>
       <c r="I50" t="n">
-        <v>64241.33</v>
+        <v>63102.41</v>
       </c>
       <c r="J50" t="n">
-        <v>64234.89</v>
+        <v>64457.75</v>
       </c>
       <c r="K50" t="n">
-        <v>64754.61</v>
+        <v>64728.81</v>
       </c>
       <c r="L50" t="n">
-        <v>65274.32</v>
+        <v>64999.88</v>
       </c>
       <c r="M50" t="n">
-        <v>65530.96</v>
+        <v>65813.08</v>
       </c>
       <c r="N50" t="n">
-        <v>65787.60000000001</v>
+        <v>66626.28999999999</v>
       </c>
       <c r="O50" t="n">
-        <v>66570.38</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66355.22</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
@@ -4711,9 +4711,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4730,74 +4730,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>64276.82</v>
+        <v>63659.53</v>
       </c>
       <c r="C51" t="n">
-        <v>64312.02</v>
+        <v>63691.53</v>
       </c>
       <c r="D51" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E51" t="n">
-        <v>64011.34</v>
+        <v>63492.99</v>
       </c>
       <c r="F51" t="n">
-        <v>-1259.61</v>
+        <v>-518.35</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0081</v>
       </c>
       <c r="H51" t="n">
-        <v>1103.39</v>
+        <v>965.35</v>
       </c>
       <c r="I51" t="n">
-        <v>63102.41</v>
+        <v>62105.24</v>
       </c>
       <c r="J51" t="n">
-        <v>64457.75</v>
+        <v>63033.46</v>
       </c>
       <c r="K51" t="n">
-        <v>64728.81</v>
+        <v>63459.64</v>
       </c>
       <c r="L51" t="n">
-        <v>64999.88</v>
+        <v>63885.83</v>
       </c>
       <c r="M51" t="n">
-        <v>65813.08</v>
+        <v>64563.04</v>
       </c>
       <c r="N51" t="n">
-        <v>66626.28999999999</v>
+        <v>65240.24</v>
       </c>
       <c r="O51" t="n">
-        <v>66355.22</v>
+        <v>65415.41</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4821,71 +4817,69 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63659.53</v>
+        <v>63190.37</v>
       </c>
       <c r="C52" t="n">
-        <v>63691.53</v>
+        <v>64101</v>
       </c>
       <c r="D52" t="n">
-        <v>62726.18</v>
+        <v>63067.18</v>
       </c>
       <c r="E52" t="n">
-        <v>63492.99</v>
+        <v>63484.1</v>
       </c>
       <c r="F52" t="n">
-        <v>-518.35</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0001</v>
       </c>
       <c r="H52" t="n">
-        <v>965.35</v>
+        <v>1033.82</v>
       </c>
       <c r="I52" t="n">
-        <v>62105.24</v>
+        <v>61760.83</v>
       </c>
       <c r="J52" t="n">
-        <v>63033.46</v>
+        <v>62669.7</v>
       </c>
       <c r="K52" t="n">
-        <v>63459.64</v>
+        <v>63010.31</v>
       </c>
       <c r="L52" t="n">
-        <v>63885.83</v>
+        <v>63350.92</v>
       </c>
       <c r="M52" t="n">
-        <v>64563.04</v>
+        <v>63975.66</v>
       </c>
       <c r="N52" t="n">
-        <v>65240.24</v>
+        <v>64600.41</v>
       </c>
       <c r="O52" t="n">
-        <v>65415.41</v>
+        <v>64656.88</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4898,55 +4892,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>63190.37</v>
+        <v>63672.13</v>
       </c>
       <c r="C53" t="n">
-        <v>64101</v>
+        <v>63923</v>
       </c>
       <c r="D53" t="n">
-        <v>63067.18</v>
+        <v>63209.92</v>
       </c>
       <c r="E53" t="n">
-        <v>63484.1</v>
+        <v>63923</v>
       </c>
       <c r="F53" t="n">
-        <v>-8.890000000000001</v>
+        <v>438.9</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0069</v>
       </c>
       <c r="H53" t="n">
-        <v>1033.82</v>
+        <v>713.08</v>
       </c>
       <c r="I53" t="n">
-        <v>61760.83</v>
+        <v>62033.36</v>
       </c>
       <c r="J53" t="n">
-        <v>62669.7</v>
+        <v>62400.29</v>
       </c>
       <c r="K53" t="n">
-        <v>63010.31</v>
+        <v>62967.19</v>
       </c>
       <c r="L53" t="n">
-        <v>63350.92</v>
+        <v>63534.1</v>
       </c>
       <c r="M53" t="n">
-        <v>63975.66</v>
+        <v>64001.01</v>
       </c>
       <c r="N53" t="n">
-        <v>64600.41</v>
+        <v>64467.93</v>
       </c>
       <c r="O53" t="n">
-        <v>64656.88</v>
+        <v>65134.82</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4957,14 +4955,14 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U53" s="8" t="n">
@@ -4987,50 +4985,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>63672.13</v>
+        <v>64643.58</v>
       </c>
       <c r="C54" t="n">
-        <v>63923</v>
+        <v>64643.58</v>
       </c>
       <c r="D54" t="n">
-        <v>63209.92</v>
+        <v>63824.56</v>
       </c>
       <c r="E54" t="n">
-        <v>63923</v>
+        <v>64136.25</v>
       </c>
       <c r="F54" t="n">
-        <v>438.9</v>
+        <v>213.25</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0033</v>
       </c>
       <c r="H54" t="n">
-        <v>713.08</v>
+        <v>819.02</v>
       </c>
       <c r="I54" t="n">
-        <v>62033.36</v>
+        <v>62496.84</v>
       </c>
       <c r="J54" t="n">
-        <v>62400.29</v>
+        <v>63388.19</v>
       </c>
       <c r="K54" t="n">
-        <v>62967.19</v>
+        <v>63566.46</v>
       </c>
       <c r="L54" t="n">
-        <v>63534.1</v>
+        <v>63744.73</v>
       </c>
       <c r="M54" t="n">
-        <v>64001.01</v>
+        <v>64279.54</v>
       </c>
       <c r="N54" t="n">
-        <v>64467.93</v>
+        <v>64814.35</v>
       </c>
       <c r="O54" t="n">
-        <v>65134.82</v>
+        <v>64636.08</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5041,7 +5039,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5054,8 +5052,10 @@
       <c r="U54" s="8" t="n">
         <v/>
       </c>
-      <c r="V54" s="8" t="n">
-        <v/>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W54" s="11" t="inlineStr">
         <is>
@@ -5064,57 +5064,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>64643.58</v>
+        <v>64681.55</v>
       </c>
       <c r="C55" t="n">
-        <v>64643.58</v>
+        <v>65436.57</v>
       </c>
       <c r="D55" t="n">
-        <v>63824.56</v>
+        <v>64403.85</v>
       </c>
       <c r="E55" t="n">
-        <v>64136.25</v>
+        <v>65018.95</v>
       </c>
       <c r="F55" t="n">
-        <v>213.25</v>
+        <v>882.7</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0138</v>
       </c>
       <c r="H55" t="n">
-        <v>819.02</v>
+        <v>1032.72</v>
       </c>
       <c r="I55" t="n">
-        <v>62496.84</v>
+        <v>63005.54</v>
       </c>
       <c r="J55" t="n">
-        <v>63388.19</v>
+        <v>63268.32</v>
       </c>
       <c r="K55" t="n">
-        <v>63566.46</v>
+        <v>63726.74</v>
       </c>
       <c r="L55" t="n">
-        <v>63744.73</v>
+        <v>64185.16</v>
       </c>
       <c r="M55" t="n">
-        <v>64279.54</v>
+        <v>64545.76</v>
       </c>
       <c r="N55" t="n">
-        <v>64814.35</v>
+        <v>64906.36</v>
       </c>
       <c r="O55" t="n">
-        <v>64636.08</v>
+        <v>65462.6</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5125,82 +5125,78 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>64681.55</v>
+        <v>65476.44</v>
       </c>
       <c r="C56" t="n">
-        <v>65436.57</v>
+        <v>66249.11</v>
       </c>
       <c r="D56" t="n">
-        <v>64403.85</v>
+        <v>65407.37</v>
       </c>
       <c r="E56" t="n">
-        <v>65018.95</v>
+        <v>65513.99</v>
       </c>
       <c r="F56" t="n">
-        <v>882.7</v>
+        <v>495.04</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.0076</v>
       </c>
       <c r="H56" t="n">
-        <v>1032.72</v>
+        <v>841.74</v>
       </c>
       <c r="I56" t="n">
-        <v>63005.54</v>
+        <v>63371.13</v>
       </c>
       <c r="J56" t="n">
-        <v>63268.32</v>
+        <v>64035.6</v>
       </c>
       <c r="K56" t="n">
-        <v>63726.74</v>
+        <v>64502.59</v>
       </c>
       <c r="L56" t="n">
-        <v>64185.16</v>
+        <v>64969.58</v>
       </c>
       <c r="M56" t="n">
-        <v>64545.76</v>
+        <v>65535.31</v>
       </c>
       <c r="N56" t="n">
-        <v>64906.36</v>
+        <v>66101.03999999999</v>
       </c>
       <c r="O56" t="n">
-        <v>65462.6</v>
+        <v>66469.28999999999</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5211,19 +5207,19 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U56" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V56" s="8" t="n">
@@ -5239,50 +5235,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>65476.44</v>
+        <v>65639.62</v>
       </c>
       <c r="C57" t="n">
-        <v>66249.11</v>
+        <v>66410.27</v>
       </c>
       <c r="D57" t="n">
-        <v>65407.37</v>
+        <v>65639.62</v>
       </c>
       <c r="E57" t="n">
-        <v>65513.99</v>
+        <v>66364.2</v>
       </c>
       <c r="F57" t="n">
-        <v>495.04</v>
+        <v>850.21</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.013</v>
       </c>
       <c r="H57" t="n">
-        <v>841.74</v>
+        <v>770.66</v>
       </c>
       <c r="I57" t="n">
-        <v>63371.13</v>
+        <v>64565.63</v>
       </c>
       <c r="J57" t="n">
-        <v>64035.6</v>
+        <v>64515.12</v>
       </c>
       <c r="K57" t="n">
-        <v>64502.59</v>
+        <v>65093.12</v>
       </c>
       <c r="L57" t="n">
-        <v>64969.58</v>
+        <v>65671.11</v>
       </c>
       <c r="M57" t="n">
-        <v>65535.31</v>
+        <v>65934.86</v>
       </c>
       <c r="N57" t="n">
-        <v>66101.03999999999</v>
+        <v>66198.60000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>66469.28999999999</v>
+        <v>67090.85000000001</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5293,19 +5289,19 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V57" s="8" t="n">
@@ -5321,50 +5317,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>65639.62</v>
+        <v>66505.94</v>
       </c>
       <c r="C58" t="n">
-        <v>66410.27</v>
+        <v>67034.74000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>65639.62</v>
+        <v>65877.62</v>
       </c>
       <c r="E58" t="n">
-        <v>66364.2</v>
+        <v>65877.62</v>
       </c>
       <c r="F58" t="n">
-        <v>850.21</v>
+        <v>-486.59</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0073</v>
       </c>
       <c r="H58" t="n">
-        <v>770.66</v>
+        <v>1157.12</v>
       </c>
       <c r="I58" t="n">
-        <v>64565.63</v>
+        <v>64868.96</v>
       </c>
       <c r="J58" t="n">
-        <v>64515.12</v>
+        <v>65763.17999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>65093.12</v>
+        <v>65978.88</v>
       </c>
       <c r="L58" t="n">
-        <v>65671.11</v>
+        <v>66194.57000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>65934.86</v>
+        <v>66749.53</v>
       </c>
       <c r="N58" t="n">
-        <v>66198.60000000001</v>
+        <v>67304.49000000001</v>
       </c>
       <c r="O58" t="n">
-        <v>67090.85000000001</v>
+        <v>67180.92999999999</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5372,12 +5368,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5385,10 +5383,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5398,58 +5394,64 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>66505.94</v>
+        <v>65557.99000000001</v>
       </c>
       <c r="C59" t="n">
-        <v>67034.74000000001</v>
+        <v>65805.08</v>
       </c>
       <c r="D59" t="n">
-        <v>65877.62</v>
+        <v>64699.49</v>
       </c>
       <c r="E59" t="n">
-        <v>65877.62</v>
+        <v>65481.27</v>
       </c>
       <c r="F59" t="n">
-        <v>-486.59</v>
+        <v>-396.35</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.006</v>
       </c>
       <c r="H59" t="n">
-        <v>1157.12</v>
+        <v>1105.59</v>
       </c>
       <c r="I59" t="n">
-        <v>64868.96</v>
+        <v>64720.49</v>
       </c>
       <c r="J59" t="n">
-        <v>65763.17999999999</v>
+        <v>64431.21</v>
       </c>
       <c r="K59" t="n">
-        <v>65978.88</v>
+        <v>65299.05</v>
       </c>
       <c r="L59" t="n">
-        <v>66194.57000000001</v>
+        <v>66166.89999999999</v>
       </c>
       <c r="M59" t="n">
-        <v>66749.53</v>
+        <v>66456.17999999999</v>
       </c>
       <c r="N59" t="n">
-        <v>67304.49000000001</v>
+        <v>66745.46000000001</v>
       </c>
       <c r="O59" t="n">
-        <v>67180.92999999999</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
+        <v>68191.87</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q59" s="6" t="n">
         <v/>
@@ -5459,15 +5461,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="7" t="inlineStr">
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5482,24 +5482,24 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>65557.99000000001</v>
+        <v>66128.59</v>
       </c>
       <c r="C60" t="n">
-        <v>65805.08</v>
+        <v>66946.14</v>
       </c>
       <c r="D60" t="n">
-        <v>64699.49</v>
+        <v>66014.48</v>
       </c>
       <c r="E60" t="n">
         <v/>
@@ -5511,28 +5511,28 @@
         <v/>
       </c>
       <c r="H60" t="n">
-        <v>1105.59</v>
+        <v>931.66</v>
       </c>
       <c r="I60" t="n">
-        <v>64720.49</v>
+        <v>63593.9</v>
       </c>
       <c r="J60" t="n">
-        <v>64431.21</v>
+        <v>64490.17</v>
       </c>
       <c r="K60" t="n">
-        <v>65299.05</v>
+        <v>64928.47</v>
       </c>
       <c r="L60" t="n">
-        <v>66166.89999999999</v>
+        <v>65366.78</v>
       </c>
       <c r="M60" t="n">
-        <v>66456.17999999999</v>
+        <v>66034.06</v>
       </c>
       <c r="N60" t="n">
-        <v>66745.46000000001</v>
+        <v>66701.35000000001</v>
       </c>
       <c r="O60" t="n">
-        <v>68191.87</v>
+        <v>66910.67</v>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
@@ -5542,35 +5542,35 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="12" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -637,50 +637,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68676.06</v>
+        <v>69973.34</v>
       </c>
       <c r="C2" t="n">
-        <v>69788.03</v>
+        <v>70384.59</v>
       </c>
       <c r="D2" t="n">
-        <v>67609.49000000001</v>
+        <v>68904.41</v>
       </c>
       <c r="E2" t="n">
-        <v>69744.07000000001</v>
+        <v>69737.69</v>
       </c>
       <c r="F2" t="n">
-        <v>1010.92</v>
+        <v>-6.38</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0001</v>
       </c>
       <c r="H2" t="n">
-        <v>2178.54</v>
+        <v>1480.19</v>
       </c>
       <c r="I2" t="n">
-        <v>67271.12</v>
+        <v>65430.95</v>
       </c>
       <c r="J2" t="n">
-        <v>67005.17999999999</v>
+        <v>68088.19</v>
       </c>
       <c r="K2" t="n">
-        <v>68030.58</v>
+        <v>68654.8</v>
       </c>
       <c r="L2" t="n">
-        <v>69055.99000000001</v>
+        <v>69221.42</v>
       </c>
       <c r="M2" t="n">
-        <v>69435.71000000001</v>
+        <v>70833.34</v>
       </c>
       <c r="N2" t="n">
-        <v>69815.44</v>
+        <v>72445.25999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>71486.52</v>
+        <v>71966.57000000001</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -688,25 +688,19 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -718,70 +712,74 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69973.34</v>
+        <v>69460.08</v>
       </c>
       <c r="C3" t="n">
-        <v>70384.59</v>
+        <v>69957.50999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>68904.41</v>
+        <v>68003.92</v>
       </c>
       <c r="E3" t="n">
-        <v>69737.69</v>
+        <v>68256.96000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.38</v>
+        <v>-1480.73</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0212</v>
       </c>
       <c r="H3" t="n">
-        <v>1480.19</v>
+        <v>1953.59</v>
       </c>
       <c r="I3" t="n">
-        <v>65430.95</v>
+        <v>67424.22</v>
       </c>
       <c r="J3" t="n">
-        <v>68088.19</v>
+        <v>68304.09</v>
       </c>
       <c r="K3" t="n">
-        <v>68654.8</v>
+        <v>68997.59</v>
       </c>
       <c r="L3" t="n">
-        <v>69221.42</v>
+        <v>69691.09</v>
       </c>
       <c r="M3" t="n">
-        <v>70833.34</v>
+        <v>70477.78</v>
       </c>
       <c r="N3" t="n">
-        <v>72445.25999999999</v>
+        <v>71264.47</v>
       </c>
       <c r="O3" t="n">
-        <v>71966.57000000001</v>
+        <v>71864.78</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -793,76 +791,70 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69460.08</v>
+        <v>67704.16</v>
       </c>
       <c r="C4" t="n">
-        <v>69957.50999999999</v>
+        <v>68432.67999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>68003.92</v>
+        <v>66819.05</v>
       </c>
       <c r="E4" t="n">
-        <v>68256.96000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="F4" t="n">
-        <v>-1480.73</v>
+        <v>-1437.91</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="H4" t="n">
-        <v>1953.59</v>
+        <v>1613.63</v>
       </c>
       <c r="I4" t="n">
-        <v>67424.22</v>
+        <v>66050.34</v>
       </c>
       <c r="J4" t="n">
-        <v>68304.09</v>
+        <v>65941.5</v>
       </c>
       <c r="K4" t="n">
-        <v>68997.59</v>
+        <v>67280.17</v>
       </c>
       <c r="L4" t="n">
-        <v>69691.09</v>
+        <v>68618.84</v>
       </c>
       <c r="M4" t="n">
-        <v>70477.78</v>
+        <v>69233.75</v>
       </c>
       <c r="N4" t="n">
-        <v>71264.47</v>
+        <v>69848.67</v>
       </c>
       <c r="O4" t="n">
-        <v>71864.78</v>
+        <v>71911.09</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
@@ -889,50 +881,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67704.16</v>
+        <v>67046.37</v>
       </c>
       <c r="C5" t="n">
-        <v>68432.67999999999</v>
+        <v>68447.89</v>
       </c>
       <c r="D5" t="n">
-        <v>66819.05</v>
+        <v>67008.89</v>
       </c>
       <c r="E5" t="n">
-        <v>66819.05</v>
+        <v>67743.85000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1437.91</v>
+        <v>924.8</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0211</v>
+        <v>0.0138</v>
       </c>
       <c r="H5" t="n">
-        <v>1613.63</v>
+        <v>1439</v>
       </c>
       <c r="I5" t="n">
-        <v>66050.34</v>
+        <v>65205.41</v>
       </c>
       <c r="J5" t="n">
-        <v>65941.5</v>
+        <v>64802.01</v>
       </c>
       <c r="K5" t="n">
-        <v>67280.17</v>
+        <v>66012.23</v>
       </c>
       <c r="L5" t="n">
-        <v>68618.84</v>
+        <v>67222.46000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>69233.75</v>
+        <v>67625.86</v>
       </c>
       <c r="N5" t="n">
-        <v>69848.67</v>
+        <v>68029.27</v>
       </c>
       <c r="O5" t="n">
-        <v>71911.09</v>
+        <v>70046.31</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,21 +932,23 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -964,55 +958,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>67046.37</v>
+        <v>68526.72</v>
       </c>
       <c r="C6" t="n">
-        <v>68447.89</v>
+        <v>69374.86</v>
       </c>
       <c r="D6" t="n">
-        <v>67008.89</v>
+        <v>68271.91</v>
       </c>
       <c r="E6" t="n">
-        <v>67743.85000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F6" t="n">
-        <v>924.8</v>
+        <v>813.88</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.012</v>
       </c>
       <c r="H6" t="n">
-        <v>1439</v>
+        <v>1102.95</v>
       </c>
       <c r="I6" t="n">
-        <v>65205.41</v>
+        <v>65569.89</v>
       </c>
       <c r="J6" t="n">
-        <v>64802.01</v>
+        <v>66312.58</v>
       </c>
       <c r="K6" t="n">
-        <v>66012.23</v>
+        <v>67024.35000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>67222.46000000001</v>
+        <v>67736.12</v>
       </c>
       <c r="M6" t="n">
-        <v>67625.86</v>
+        <v>68463.35000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>68029.27</v>
+        <v>69190.58</v>
       </c>
       <c r="O6" t="n">
-        <v>70046.31</v>
+        <v>69886.89</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1055,74 +1053,76 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>68526.72</v>
+        <v>68410.63</v>
       </c>
       <c r="C7" t="n">
-        <v>69374.86</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>68271.91</v>
+        <v>66653.11</v>
       </c>
       <c r="E7" t="n">
-        <v>68557.73</v>
+        <v>67242.73</v>
       </c>
       <c r="F7" t="n">
-        <v>813.88</v>
+        <v>-1315</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0192</v>
       </c>
       <c r="H7" t="n">
-        <v>1102.95</v>
+        <v>2425.1</v>
       </c>
       <c r="I7" t="n">
-        <v>65569.89</v>
+        <v>67168.95</v>
       </c>
       <c r="J7" t="n">
-        <v>66312.58</v>
+        <v>67321.95</v>
       </c>
       <c r="K7" t="n">
-        <v>67024.35000000001</v>
+        <v>68006.25</v>
       </c>
       <c r="L7" t="n">
-        <v>67736.12</v>
+        <v>68690.55</v>
       </c>
       <c r="M7" t="n">
-        <v>68463.35000000001</v>
+        <v>69109.2</v>
       </c>
       <c r="N7" t="n">
-        <v>69190.58</v>
+        <v>69527.85000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>69886.89</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+        <v>70477.81</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1132,78 +1132,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>68410.63</v>
+        <v>67002.94</v>
       </c>
       <c r="C8" t="n">
-        <v>69078.21000000001</v>
+        <v>67800.17999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>66653.11</v>
+        <v>66268.60000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>67242.73</v>
+        <v>67743.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-1315</v>
+        <v>500.77</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0074</v>
       </c>
       <c r="H8" t="n">
-        <v>2425.1</v>
+        <v>1531.58</v>
       </c>
       <c r="I8" t="n">
-        <v>67168.95</v>
+        <v>64228.01</v>
       </c>
       <c r="J8" t="n">
-        <v>67321.95</v>
+        <v>64506.16</v>
       </c>
       <c r="K8" t="n">
-        <v>68006.25</v>
+        <v>66030.17999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>68690.55</v>
+        <v>67554.19</v>
       </c>
       <c r="M8" t="n">
-        <v>69109.2</v>
+        <v>68455.28</v>
       </c>
       <c r="N8" t="n">
-        <v>69527.85000000001</v>
+        <v>69356.36</v>
       </c>
       <c r="O8" t="n">
-        <v>70477.81</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>71503.31</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1220,55 +1210,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67002.94</v>
+        <v>67989.74000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>67800.17999999999</v>
+        <v>68798.24000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>66268.60000000001</v>
+        <v>67833.17</v>
       </c>
       <c r="E9" t="n">
-        <v>67743.5</v>
+        <v>68751.50999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>500.77</v>
+        <v>1008.01</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0149</v>
       </c>
       <c r="H9" t="n">
-        <v>1531.58</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>64228.01</v>
+        <v>64737.02</v>
       </c>
       <c r="J9" t="n">
-        <v>64506.16</v>
+        <v>66566.48</v>
       </c>
       <c r="K9" t="n">
-        <v>66030.17999999999</v>
+        <v>66977.71000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>67554.19</v>
+        <v>67388.95</v>
       </c>
       <c r="M9" t="n">
-        <v>68455.28</v>
+        <v>68509.28999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>69356.36</v>
+        <v>69629.63</v>
       </c>
       <c r="O9" t="n">
-        <v>71503.31</v>
+        <v>69331.75999999999</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1281,11 +1275,13 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1300,77 +1296,81 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>67989.74000000001</v>
+        <v>67900.42999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>68798.24000000001</v>
+        <v>68069.82000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>67833.17</v>
+        <v>66499.49000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>68751.50999999999</v>
+        <v>66835.53999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>1008.01</v>
+        <v>-1915.97</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0279</v>
       </c>
       <c r="H10" t="n">
-        <v>965.0700000000001</v>
+        <v>1570.33</v>
       </c>
       <c r="I10" t="n">
-        <v>64737.02</v>
+        <v>66868.10000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>66566.48</v>
+        <v>68004.34</v>
       </c>
       <c r="K10" t="n">
-        <v>66977.71000000001</v>
+        <v>68268.97</v>
       </c>
       <c r="L10" t="n">
-        <v>67388.95</v>
+        <v>68533.61</v>
       </c>
       <c r="M10" t="n">
-        <v>68509.28999999999</v>
+        <v>69234.03999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>69629.63</v>
+        <v>69934.48</v>
       </c>
       <c r="O10" t="n">
-        <v>69331.75999999999</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
+        <v>69763.31</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1382,59 +1382,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>67900.42999999999</v>
+        <v>66339.85000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>68069.82000000001</v>
+        <v>66441.77</v>
       </c>
       <c r="D11" t="n">
-        <v>66499.49000000001</v>
+        <v>62704.6</v>
       </c>
       <c r="E11" t="n">
-        <v>66835.53999999999</v>
+        <v>64141.12</v>
       </c>
       <c r="F11" t="n">
-        <v>-1915.97</v>
+        <v>-2694.42</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0403</v>
       </c>
       <c r="H11" t="n">
-        <v>1570.33</v>
+        <v>3737.17</v>
       </c>
       <c r="I11" t="n">
-        <v>66868.10000000001</v>
+        <v>64929.16</v>
       </c>
       <c r="J11" t="n">
-        <v>68004.34</v>
+        <v>65040.65</v>
       </c>
       <c r="K11" t="n">
-        <v>68268.97</v>
+        <v>66050.38</v>
       </c>
       <c r="L11" t="n">
-        <v>68533.61</v>
+        <v>67060.10000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>69234.03999999999</v>
+        <v>67620.7</v>
       </c>
       <c r="N11" t="n">
-        <v>69934.48</v>
+        <v>68181.31</v>
       </c>
       <c r="O11" t="n">
-        <v>69763.31</v>
+        <v>69640.14999999999</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -1475,74 +1471,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>66339.85000000001</v>
+        <v>64544.05</v>
       </c>
       <c r="C12" t="n">
-        <v>66441.77</v>
+        <v>66232.19</v>
       </c>
       <c r="D12" t="n">
-        <v>62704.6</v>
+        <v>64203.47</v>
       </c>
       <c r="E12" t="n">
-        <v>64141.12</v>
+        <v>66232.19</v>
       </c>
       <c r="F12" t="n">
-        <v>-2694.42</v>
+        <v>2091.07</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0326</v>
       </c>
       <c r="H12" t="n">
-        <v>3737.17</v>
+        <v>2028.72</v>
       </c>
       <c r="I12" t="n">
-        <v>64929.16</v>
+        <v>58967.43</v>
       </c>
       <c r="J12" t="n">
-        <v>65040.65</v>
+        <v>60187.92</v>
       </c>
       <c r="K12" t="n">
-        <v>66050.38</v>
+        <v>62272.54</v>
       </c>
       <c r="L12" t="n">
-        <v>67060.10000000001</v>
+        <v>64357.15</v>
       </c>
       <c r="M12" t="n">
-        <v>67620.7</v>
+        <v>66009.71000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>68181.31</v>
+        <v>67662.25999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>69640.14999999999</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
+        <v>70178.95</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1554,55 +1546,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64544.05</v>
+        <v>66449.27</v>
       </c>
       <c r="C13" t="n">
-        <v>66232.19</v>
+        <v>67592.2</v>
       </c>
       <c r="D13" t="n">
-        <v>64203.47</v>
+        <v>65955.60000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>66232.19</v>
+        <v>66115.60000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>2091.07</v>
+        <v>-116.59</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0326</v>
+        <v>-0.0018</v>
       </c>
       <c r="H13" t="n">
-        <v>2028.72</v>
+        <v>1636.6</v>
       </c>
       <c r="I13" t="n">
-        <v>58967.43</v>
+        <v>62174.75</v>
       </c>
       <c r="J13" t="n">
-        <v>60187.92</v>
+        <v>64710.65</v>
       </c>
       <c r="K13" t="n">
-        <v>62272.54</v>
+        <v>65217.83</v>
       </c>
       <c r="L13" t="n">
-        <v>64357.15</v>
+        <v>65725.00999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>66009.71000000001</v>
+        <v>67246.55</v>
       </c>
       <c r="N13" t="n">
-        <v>67662.25999999999</v>
+        <v>68768.09</v>
       </c>
       <c r="O13" t="n">
-        <v>70178.95</v>
+        <v>68260.91</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1615,12 +1611,12 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U13" s="8" t="n">
@@ -1643,50 +1639,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>66449.27</v>
+        <v>66421.00999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>67592.2</v>
+        <v>67022.37</v>
       </c>
       <c r="D14" t="n">
-        <v>65955.60000000001</v>
+        <v>66208.66</v>
       </c>
       <c r="E14" t="n">
-        <v>66115.60000000001</v>
+        <v>66422.60000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-116.59</v>
+        <v>307</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0046</v>
       </c>
       <c r="H14" t="n">
-        <v>1636.6</v>
+        <v>813.71</v>
       </c>
       <c r="I14" t="n">
-        <v>62174.75</v>
+        <v>64319</v>
       </c>
       <c r="J14" t="n">
-        <v>64710.65</v>
+        <v>64149.85</v>
       </c>
       <c r="K14" t="n">
-        <v>65217.83</v>
+        <v>65297.3</v>
       </c>
       <c r="L14" t="n">
-        <v>65725.00999999999</v>
+        <v>66444.75</v>
       </c>
       <c r="M14" t="n">
-        <v>67246.55</v>
+        <v>66933.89999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>68768.09</v>
+        <v>67423.05</v>
       </c>
       <c r="O14" t="n">
-        <v>68260.91</v>
+        <v>69228.8</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1697,9 +1693,9 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
@@ -1727,69 +1723,73 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66421.00999999999</v>
+        <v>65584.25</v>
       </c>
       <c r="C15" t="n">
-        <v>67022.37</v>
+        <v>65720.81</v>
       </c>
       <c r="D15" t="n">
-        <v>66208.66</v>
+        <v>64201.03</v>
       </c>
       <c r="E15" t="n">
-        <v>66422.60000000001</v>
+        <v>64611.15</v>
       </c>
       <c r="F15" t="n">
-        <v>307</v>
+        <v>-1811.45</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0273</v>
       </c>
       <c r="H15" t="n">
-        <v>813.71</v>
+        <v>1519.78</v>
       </c>
       <c r="I15" t="n">
-        <v>64319</v>
+        <v>65394.95</v>
       </c>
       <c r="J15" t="n">
-        <v>64149.85</v>
+        <v>65512.44</v>
       </c>
       <c r="K15" t="n">
-        <v>65297.3</v>
+        <v>66015.75</v>
       </c>
       <c r="L15" t="n">
-        <v>66444.75</v>
+        <v>66519.06</v>
       </c>
       <c r="M15" t="n">
-        <v>66933.89999999999</v>
+        <v>66829.46000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>67423.05</v>
+        <v>67139.86</v>
       </c>
       <c r="O15" t="n">
-        <v>69228.8</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+        <v>67836.08</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1802,78 +1802,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>65584.25</v>
+        <v>65164.98</v>
       </c>
       <c r="C16" t="n">
-        <v>65720.81</v>
+        <v>65220.69</v>
       </c>
       <c r="D16" t="n">
-        <v>64201.03</v>
+        <v>64123.4</v>
       </c>
       <c r="E16" t="n">
-        <v>64611.15</v>
+        <v>64931.19</v>
       </c>
       <c r="F16" t="n">
-        <v>-1811.45</v>
+        <v>320.04</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.005</v>
       </c>
       <c r="H16" t="n">
-        <v>1519.78</v>
+        <v>1097.29</v>
       </c>
       <c r="I16" t="n">
-        <v>65394.95</v>
+        <v>62681.25</v>
       </c>
       <c r="J16" t="n">
-        <v>65512.44</v>
+        <v>62916.48</v>
       </c>
       <c r="K16" t="n">
-        <v>66015.75</v>
+        <v>63851.26</v>
       </c>
       <c r="L16" t="n">
-        <v>66519.06</v>
+        <v>64786.04</v>
       </c>
       <c r="M16" t="n">
-        <v>66829.46000000001</v>
+        <v>65371.04</v>
       </c>
       <c r="N16" t="n">
-        <v>67139.86</v>
+        <v>65956.03999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>67836.08</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>67240.59</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1890,68 +1880,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>65164.98</v>
+        <v>64539.92</v>
       </c>
       <c r="C17" t="n">
-        <v>65220.69</v>
+        <v>64573.18</v>
       </c>
       <c r="D17" t="n">
-        <v>64123.4</v>
+        <v>61923.6</v>
       </c>
       <c r="E17" t="n">
-        <v>64931.19</v>
+        <v>62364.92</v>
       </c>
       <c r="F17" t="n">
-        <v>320.04</v>
+        <v>-2566.27</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0395</v>
       </c>
       <c r="H17" t="n">
-        <v>1097.29</v>
+        <v>2649.58</v>
       </c>
       <c r="I17" t="n">
-        <v>62681.25</v>
+        <v>63026.11</v>
       </c>
       <c r="J17" t="n">
-        <v>62916.48</v>
+        <v>63963.47</v>
       </c>
       <c r="K17" t="n">
-        <v>63851.26</v>
+        <v>64382.54</v>
       </c>
       <c r="L17" t="n">
-        <v>64786.04</v>
+        <v>64801.62</v>
       </c>
       <c r="M17" t="n">
-        <v>65371.04</v>
+        <v>65479.84</v>
       </c>
       <c r="N17" t="n">
-        <v>65956.03999999999</v>
+        <v>66158.06</v>
       </c>
       <c r="O17" t="n">
-        <v>67240.59</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>66317.98</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1968,73 +1968,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>64539.92</v>
+        <v>62734.68</v>
       </c>
       <c r="C18" t="n">
-        <v>64573.18</v>
+        <v>63138.04</v>
       </c>
       <c r="D18" t="n">
-        <v>61923.6</v>
+        <v>60448.9</v>
       </c>
       <c r="E18" t="n">
-        <v>62364.92</v>
+        <v>61434.19</v>
       </c>
       <c r="F18" t="n">
-        <v>-2566.27</v>
+        <v>-930.73</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0149</v>
       </c>
       <c r="H18" t="n">
-        <v>2649.58</v>
+        <v>2689.14</v>
       </c>
       <c r="I18" t="n">
-        <v>63026.11</v>
+        <v>59274.02</v>
       </c>
       <c r="J18" t="n">
-        <v>63963.47</v>
+        <v>59273.61</v>
       </c>
       <c r="K18" t="n">
-        <v>64382.54</v>
+        <v>61040.13</v>
       </c>
       <c r="L18" t="n">
-        <v>64801.62</v>
+        <v>62806.66</v>
       </c>
       <c r="M18" t="n">
-        <v>65479.84</v>
+        <v>63689.71</v>
       </c>
       <c r="N18" t="n">
-        <v>66158.06</v>
+        <v>64572.77</v>
       </c>
       <c r="O18" t="n">
-        <v>66317.98</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>67222.75999999999</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
@@ -2061,50 +2053,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>62734.68</v>
+        <v>61258.34</v>
       </c>
       <c r="C19" t="n">
-        <v>63138.04</v>
+        <v>62924.84</v>
       </c>
       <c r="D19" t="n">
-        <v>60448.9</v>
+        <v>61049.7</v>
       </c>
       <c r="E19" t="n">
-        <v>61434.19</v>
+        <v>61867.43</v>
       </c>
       <c r="F19" t="n">
-        <v>-930.73</v>
+        <v>433.24</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0071</v>
       </c>
       <c r="H19" t="n">
-        <v>2689.14</v>
+        <v>1875.14</v>
       </c>
       <c r="I19" t="n">
-        <v>59274.02</v>
+        <v>57759.76</v>
       </c>
       <c r="J19" t="n">
-        <v>59273.61</v>
+        <v>58565.41</v>
       </c>
       <c r="K19" t="n">
-        <v>61040.13</v>
+        <v>60089.62</v>
       </c>
       <c r="L19" t="n">
-        <v>62806.66</v>
+        <v>61613.83</v>
       </c>
       <c r="M19" t="n">
-        <v>63689.71</v>
+        <v>62778.76</v>
       </c>
       <c r="N19" t="n">
-        <v>64572.77</v>
+        <v>63943.69</v>
       </c>
       <c r="O19" t="n">
-        <v>67222.75999999999</v>
+        <v>65827.17999999999</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2112,18 +2104,18 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2136,55 +2128,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>61258.34</v>
+        <v>61957.1</v>
       </c>
       <c r="C20" t="n">
-        <v>62924.84</v>
+        <v>65364.73</v>
       </c>
       <c r="D20" t="n">
-        <v>61049.7</v>
+        <v>61948.23</v>
       </c>
       <c r="E20" t="n">
-        <v>61867.43</v>
+        <v>64362.02</v>
       </c>
       <c r="F20" t="n">
-        <v>433.24</v>
+        <v>2494.59</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0403</v>
       </c>
       <c r="H20" t="n">
-        <v>1875.14</v>
+        <v>3416.5</v>
       </c>
       <c r="I20" t="n">
-        <v>57759.76</v>
+        <v>59174.56</v>
       </c>
       <c r="J20" t="n">
-        <v>58565.41</v>
+        <v>59932.37</v>
       </c>
       <c r="K20" t="n">
-        <v>60089.62</v>
+        <v>60929.86</v>
       </c>
       <c r="L20" t="n">
-        <v>61613.83</v>
+        <v>61927.35</v>
       </c>
       <c r="M20" t="n">
-        <v>62778.76</v>
+        <v>62805</v>
       </c>
       <c r="N20" t="n">
-        <v>63943.69</v>
+        <v>63682.65</v>
       </c>
       <c r="O20" t="n">
-        <v>65827.17999999999</v>
+        <v>64799.98</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2197,7 +2193,7 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2205,70 +2201,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>61957.1</v>
+        <v>63834.95</v>
       </c>
       <c r="C21" t="n">
-        <v>65364.73</v>
+        <v>63905.12</v>
       </c>
       <c r="D21" t="n">
-        <v>61948.23</v>
+        <v>62703.47</v>
       </c>
       <c r="E21" t="n">
-        <v>64362.02</v>
+        <v>63754.9</v>
       </c>
       <c r="F21" t="n">
-        <v>2494.59</v>
+        <v>-607.12</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0403</v>
+        <v>-0.0094</v>
       </c>
       <c r="H21" t="n">
-        <v>3416.5</v>
+        <v>1201.65</v>
       </c>
       <c r="I21" t="n">
-        <v>59174.56</v>
+        <v>58531.73</v>
       </c>
       <c r="J21" t="n">
-        <v>59932.37</v>
+        <v>61298.29</v>
       </c>
       <c r="K21" t="n">
-        <v>60929.86</v>
+        <v>62653.77</v>
       </c>
       <c r="L21" t="n">
-        <v>61927.35</v>
+        <v>64009.25</v>
       </c>
       <c r="M21" t="n">
-        <v>62805</v>
+        <v>66070.27</v>
       </c>
       <c r="N21" t="n">
-        <v>63682.65</v>
+        <v>68131.28999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>64799.98</v>
+        <v>68781.23</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2279,80 +2275,78 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63834.95</v>
+        <v>63995.28</v>
       </c>
       <c r="C22" t="n">
-        <v>63905.12</v>
+        <v>64240.5</v>
       </c>
       <c r="D22" t="n">
-        <v>62703.47</v>
+        <v>62864.43</v>
       </c>
       <c r="E22" t="n">
-        <v>63754.9</v>
+        <v>63957.53</v>
       </c>
       <c r="F22" t="n">
-        <v>-607.12</v>
+        <v>202.63</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0032</v>
       </c>
       <c r="H22" t="n">
-        <v>1201.65</v>
+        <v>1376.07</v>
       </c>
       <c r="I22" t="n">
-        <v>58531.73</v>
+        <v>61501.82</v>
       </c>
       <c r="J22" t="n">
-        <v>61298.29</v>
+        <v>62778.55</v>
       </c>
       <c r="K22" t="n">
-        <v>62653.77</v>
+        <v>63154.07</v>
       </c>
       <c r="L22" t="n">
-        <v>64009.25</v>
+        <v>63529.6</v>
       </c>
       <c r="M22" t="n">
-        <v>66070.27</v>
+        <v>64355.72</v>
       </c>
       <c r="N22" t="n">
-        <v>68131.28999999999</v>
+        <v>65181.85</v>
       </c>
       <c r="O22" t="n">
-        <v>68781.23</v>
+        <v>65106.77</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2360,16 +2354,20 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2382,59 +2380,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>63995.28</v>
+        <v>64565.27</v>
       </c>
       <c r="C23" t="n">
-        <v>64240.5</v>
+        <v>66302.52</v>
       </c>
       <c r="D23" t="n">
-        <v>62864.43</v>
+        <v>64555.52</v>
       </c>
       <c r="E23" t="n">
-        <v>63957.53</v>
+        <v>66300.44</v>
       </c>
       <c r="F23" t="n">
-        <v>202.63</v>
+        <v>2342.91</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0366</v>
       </c>
       <c r="H23" t="n">
-        <v>1376.07</v>
+        <v>1747</v>
       </c>
       <c r="I23" t="n">
-        <v>61501.82</v>
+        <v>61488.36</v>
       </c>
       <c r="J23" t="n">
-        <v>62778.55</v>
+        <v>62783.99</v>
       </c>
       <c r="K23" t="n">
-        <v>63154.07</v>
+        <v>63269.5</v>
       </c>
       <c r="L23" t="n">
-        <v>63529.6</v>
+        <v>63755</v>
       </c>
       <c r="M23" t="n">
-        <v>64355.72</v>
+        <v>64645.57</v>
       </c>
       <c r="N23" t="n">
-        <v>65181.85</v>
+        <v>65536.13</v>
       </c>
       <c r="O23" t="n">
-        <v>65106.77</v>
+        <v>65616.57000000001</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2442,10 +2436,8 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
@@ -2454,14 +2446,18 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
@@ -2473,134 +2469,136 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>64565.27</v>
+        <v>65896</v>
       </c>
       <c r="C24" t="n">
-        <v>66302.52</v>
+        <v>65983.13</v>
       </c>
       <c r="D24" t="n">
-        <v>64555.52</v>
+        <v>64942.07</v>
       </c>
       <c r="E24" t="n">
-        <v>66300.44</v>
+        <v>65683.25999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>2342.91</v>
+        <v>-617.1799999999999</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0366</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>1747</v>
+        <v>1041.06</v>
       </c>
       <c r="I24" t="n">
-        <v>61488.36</v>
+        <v>62808.52</v>
       </c>
       <c r="J24" t="n">
-        <v>62783.99</v>
+        <v>64989.14</v>
       </c>
       <c r="K24" t="n">
-        <v>63269.5</v>
+        <v>65426.94</v>
       </c>
       <c r="L24" t="n">
-        <v>63755</v>
+        <v>65864.73</v>
       </c>
       <c r="M24" t="n">
-        <v>64645.57</v>
+        <v>67173.94</v>
       </c>
       <c r="N24" t="n">
-        <v>65536.13</v>
+        <v>68483.14999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>65616.57000000001</v>
+        <v>68049.53</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65896</v>
+        <v>65746.13</v>
       </c>
       <c r="C25" t="n">
-        <v>65983.13</v>
+        <v>65990.72</v>
       </c>
       <c r="D25" t="n">
-        <v>64942.07</v>
+        <v>64651.49</v>
       </c>
       <c r="E25" t="n">
-        <v>65683.25999999999</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-617.1799999999999</v>
+        <v>-76.55</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="H25" t="n">
-        <v>1041.06</v>
+        <v>1339.23</v>
       </c>
       <c r="I25" t="n">
-        <v>62808.52</v>
+        <v>63901.01</v>
       </c>
       <c r="J25" t="n">
-        <v>64989.14</v>
+        <v>64752.52</v>
       </c>
       <c r="K25" t="n">
-        <v>65426.94</v>
+        <v>65162.73</v>
       </c>
       <c r="L25" t="n">
-        <v>65864.73</v>
+        <v>65572.92999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>67173.94</v>
+        <v>66203.78999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>68483.14999999999</v>
+        <v>66834.64999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>68049.53</v>
+        <v>67024.2</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2615,9 +2613,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2643,74 +2641,74 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>65746.13</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>65990.72</v>
+        <v>67006.84</v>
       </c>
       <c r="D26" t="n">
-        <v>64651.49</v>
+        <v>65848.58</v>
       </c>
       <c r="E26" t="n">
-        <v>65606.71000000001</v>
+        <v>66970.22</v>
       </c>
       <c r="F26" t="n">
-        <v>-76.55</v>
+        <v>1363.51</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0208</v>
       </c>
       <c r="H26" t="n">
-        <v>1339.23</v>
+        <v>1158.27</v>
       </c>
       <c r="I26" t="n">
-        <v>63901.01</v>
+        <v>63312.26</v>
       </c>
       <c r="J26" t="n">
-        <v>64752.52</v>
+        <v>64410.28</v>
       </c>
       <c r="K26" t="n">
-        <v>65162.73</v>
+        <v>64937.1</v>
       </c>
       <c r="L26" t="n">
-        <v>65572.92999999999</v>
+        <v>65463.91</v>
       </c>
       <c r="M26" t="n">
-        <v>66203.78999999999</v>
+        <v>66276.33</v>
       </c>
       <c r="N26" t="n">
-        <v>66834.64999999999</v>
+        <v>67088.75</v>
       </c>
       <c r="O26" t="n">
-        <v>67024.2</v>
+        <v>67329.95</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2720,59 +2718,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>65905.10000000001</v>
+        <v>66994.05</v>
       </c>
       <c r="C27" t="n">
-        <v>67006.84</v>
+        <v>67569.36</v>
       </c>
       <c r="D27" t="n">
-        <v>65848.58</v>
+        <v>66735.75999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>66970.22</v>
+        <v>67524.06</v>
       </c>
       <c r="F27" t="n">
-        <v>1363.51</v>
+        <v>553.84</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="H27" t="n">
-        <v>1158.27</v>
+        <v>833.6</v>
       </c>
       <c r="I27" t="n">
-        <v>63312.26</v>
+        <v>64690.31</v>
       </c>
       <c r="J27" t="n">
-        <v>64410.28</v>
+        <v>66083.21000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>64937.1</v>
+        <v>66391.09</v>
       </c>
       <c r="L27" t="n">
-        <v>65463.91</v>
+        <v>66698.96000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>66276.33</v>
+        <v>67549.35000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>67088.75</v>
+        <v>68399.74000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>67329.95</v>
+        <v>68165.11</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2790,13 +2784,11 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2811,50 +2803,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>66994.05</v>
+        <v>68033.17</v>
       </c>
       <c r="C28" t="n">
-        <v>67569.36</v>
+        <v>68799.71000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>66735.75999999999</v>
+        <v>68006.17</v>
       </c>
       <c r="E28" t="n">
-        <v>67524.06</v>
+        <v>68308.59</v>
       </c>
       <c r="F28" t="n">
-        <v>553.84</v>
+        <v>784.53</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0116</v>
       </c>
       <c r="H28" t="n">
-        <v>833.6</v>
+        <v>793.54</v>
       </c>
       <c r="I28" t="n">
-        <v>64690.31</v>
+        <v>65902.16</v>
       </c>
       <c r="J28" t="n">
-        <v>66083.21000000001</v>
+        <v>66876.21000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>66391.09</v>
+        <v>67107.25999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>66698.96000000001</v>
+        <v>67338.31</v>
       </c>
       <c r="M28" t="n">
-        <v>67549.35000000001</v>
+        <v>67940.86</v>
       </c>
       <c r="N28" t="n">
-        <v>68399.74000000001</v>
+        <v>68543.42</v>
       </c>
       <c r="O28" t="n">
-        <v>68165.11</v>
+        <v>68402.96000000001</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2872,14 +2864,18 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
@@ -2891,50 +2887,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>68033.17</v>
+        <v>68811.17</v>
       </c>
       <c r="C29" t="n">
-        <v>68799.71000000001</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>68006.17</v>
+        <v>68471.14999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>68308.59</v>
+        <v>68713.8</v>
       </c>
       <c r="F29" t="n">
-        <v>784.53</v>
+        <v>405.2</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0059</v>
       </c>
       <c r="H29" t="n">
-        <v>793.54</v>
+        <v>1137.09</v>
       </c>
       <c r="I29" t="n">
-        <v>65902.16</v>
+        <v>67212.63</v>
       </c>
       <c r="J29" t="n">
-        <v>66876.21000000001</v>
+        <v>67467.88</v>
       </c>
       <c r="K29" t="n">
-        <v>67107.25999999999</v>
+        <v>67911.82000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>67338.31</v>
+        <v>68355.77</v>
       </c>
       <c r="M29" t="n">
-        <v>67940.86</v>
+        <v>68705.36</v>
       </c>
       <c r="N29" t="n">
-        <v>68543.42</v>
+        <v>69054.96000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>68402.96000000001</v>
+        <v>69593.25</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2952,7 +2948,7 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U29" s="8" t="inlineStr">
@@ -2962,7 +2958,7 @@
       </c>
       <c r="V29" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W29" s="9" t="inlineStr">
@@ -2975,50 +2971,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>68811.17</v>
+        <v>68882.06</v>
       </c>
       <c r="C30" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>68471.14999999999</v>
+        <v>68492.03999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>68713.8</v>
+        <v>69220.25</v>
       </c>
       <c r="F30" t="n">
-        <v>405.2</v>
+        <v>506.45</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="H30" t="n">
-        <v>1137.09</v>
+        <v>733.53</v>
       </c>
       <c r="I30" t="n">
-        <v>67212.63</v>
+        <v>67334.05</v>
       </c>
       <c r="J30" t="n">
-        <v>67467.88</v>
+        <v>67413.75</v>
       </c>
       <c r="K30" t="n">
-        <v>67911.82000000001</v>
+        <v>68145.25</v>
       </c>
       <c r="L30" t="n">
-        <v>68355.77</v>
+        <v>68876.75</v>
       </c>
       <c r="M30" t="n">
-        <v>68705.36</v>
+        <v>69282.34</v>
       </c>
       <c r="N30" t="n">
-        <v>69054.96000000001</v>
+        <v>69687.94</v>
       </c>
       <c r="O30" t="n">
-        <v>69593.25</v>
+        <v>70745.34</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3039,163 +3035,163 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>68882.06</v>
+        <v>68847.35000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>69225.57000000001</v>
+        <v>69093.2</v>
       </c>
       <c r="D31" t="n">
-        <v>68492.03999999999</v>
+        <v>67368.96000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>69220.25</v>
+        <v>67460.73</v>
       </c>
       <c r="F31" t="n">
-        <v>506.45</v>
+        <v>-1759.52</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0254</v>
       </c>
       <c r="H31" t="n">
-        <v>733.53</v>
+        <v>1724.24</v>
       </c>
       <c r="I31" t="n">
-        <v>67334.05</v>
+        <v>67758.50999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>67413.75</v>
+        <v>68667.44</v>
       </c>
       <c r="K31" t="n">
-        <v>68145.25</v>
+        <v>68853.48</v>
       </c>
       <c r="L31" t="n">
-        <v>68876.75</v>
+        <v>69039.53</v>
       </c>
       <c r="M31" t="n">
-        <v>69282.34</v>
+        <v>69587.02</v>
       </c>
       <c r="N31" t="n">
-        <v>69687.94</v>
+        <v>70134.5</v>
       </c>
       <c r="O31" t="n">
-        <v>70745.34</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
+        <v>69959.10000000001</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W31" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>68847.35000000001</v>
+        <v>66812.27</v>
       </c>
       <c r="C32" t="n">
-        <v>69093.2</v>
+        <v>66833.50999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>67368.96000000001</v>
+        <v>65133.98</v>
       </c>
       <c r="E32" t="n">
-        <v>67460.73</v>
+        <v>65326.42</v>
       </c>
       <c r="F32" t="n">
-        <v>-1759.52</v>
+        <v>-2134.3</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="H32" t="n">
-        <v>1724.24</v>
+        <v>1699.53</v>
       </c>
       <c r="I32" t="n">
-        <v>67758.50999999999</v>
+        <v>65644.72</v>
       </c>
       <c r="J32" t="n">
-        <v>68667.44</v>
+        <v>65351.31</v>
       </c>
       <c r="K32" t="n">
-        <v>68853.48</v>
+        <v>66598.61</v>
       </c>
       <c r="L32" t="n">
-        <v>69039.53</v>
+        <v>67845.89999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>69587.02</v>
+        <v>68322.85000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>70134.5</v>
+        <v>68799.78999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>69959.10000000001</v>
+        <v>70817.45</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -3227,74 +3223,70 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>66812.27</v>
+        <v>65732.78999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>66833.50999999999</v>
+        <v>66325.32000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>65133.98</v>
+        <v>65652.25</v>
       </c>
       <c r="E33" t="n">
-        <v>65326.42</v>
+        <v>66216.78999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>-2134.3</v>
+        <v>890.37</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H33" t="n">
-        <v>1699.53</v>
+        <v>673.0700000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>65644.72</v>
+        <v>63434.45</v>
       </c>
       <c r="J33" t="n">
-        <v>65351.31</v>
+        <v>63298.23</v>
       </c>
       <c r="K33" t="n">
-        <v>66598.61</v>
+        <v>64476.66</v>
       </c>
       <c r="L33" t="n">
-        <v>67845.89999999999</v>
+        <v>65655.08</v>
       </c>
       <c r="M33" t="n">
-        <v>68322.85000000001</v>
+        <v>66176.19</v>
       </c>
       <c r="N33" t="n">
-        <v>68799.78999999999</v>
+        <v>66697.28999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>70817.45</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
+        <v>68533.03999999999</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3306,74 +3298,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>65732.78999999999</v>
+        <v>65427.69</v>
       </c>
       <c r="C34" t="n">
-        <v>66325.32000000001</v>
+        <v>66125.88</v>
       </c>
       <c r="D34" t="n">
-        <v>65652.25</v>
+        <v>65260.22</v>
       </c>
       <c r="E34" t="n">
-        <v>66216.78999999999</v>
+        <v>66016.36</v>
       </c>
       <c r="F34" t="n">
-        <v>890.37</v>
+        <v>-200.43</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.003</v>
       </c>
       <c r="H34" t="n">
-        <v>673.0700000000001</v>
+        <v>865.66</v>
       </c>
       <c r="I34" t="n">
-        <v>63434.45</v>
+        <v>64979.18</v>
       </c>
       <c r="J34" t="n">
-        <v>63298.23</v>
+        <v>65657.72</v>
       </c>
       <c r="K34" t="n">
-        <v>64476.66</v>
+        <v>65880.25</v>
       </c>
       <c r="L34" t="n">
-        <v>65655.08</v>
+        <v>66102.78999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>66176.19</v>
+        <v>66553.32000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>66697.28999999999</v>
+        <v>67003.86</v>
       </c>
       <c r="O34" t="n">
-        <v>68533.03999999999</v>
+        <v>66998.39</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3386,76 +3384,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>65427.69</v>
+        <v>65978.95</v>
       </c>
       <c r="C35" t="n">
-        <v>66125.88</v>
+        <v>66257.73</v>
       </c>
       <c r="D35" t="n">
-        <v>65260.22</v>
+        <v>65470.95</v>
       </c>
       <c r="E35" t="n">
-        <v>66016.36</v>
+        <v>65528.09</v>
       </c>
       <c r="F35" t="n">
-        <v>-200.43</v>
+        <v>-488.27</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0074</v>
       </c>
       <c r="H35" t="n">
-        <v>865.66</v>
+        <v>786.78</v>
       </c>
       <c r="I35" t="n">
-        <v>64979.18</v>
+        <v>64394.55</v>
       </c>
       <c r="J35" t="n">
-        <v>65657.72</v>
+        <v>65312.35</v>
       </c>
       <c r="K35" t="n">
-        <v>65880.25</v>
+        <v>65583.53</v>
       </c>
       <c r="L35" t="n">
-        <v>66102.78999999999</v>
+        <v>65854.71000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>66553.32000000001</v>
+        <v>66449.19</v>
       </c>
       <c r="N35" t="n">
-        <v>67003.86</v>
+        <v>67043.67999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>66998.39</v>
+        <v>66991.55</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q35" s="6" t="n">
+        <v/>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3472,75 +3464,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>65978.95</v>
+        <v>65195.26</v>
       </c>
       <c r="C36" t="n">
-        <v>66257.73</v>
+        <v>65904.24000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>65470.95</v>
+        <v>64609.47</v>
       </c>
       <c r="E36" t="n">
-        <v>65528.09</v>
+        <v>65856.42999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-488.27</v>
+        <v>328.34</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0074</v>
+        <v>0.005</v>
       </c>
       <c r="H36" t="n">
-        <v>786.78</v>
+        <v>1294.77</v>
       </c>
       <c r="I36" t="n">
-        <v>64394.55</v>
+        <v>64684.17</v>
       </c>
       <c r="J36" t="n">
-        <v>65312.35</v>
+        <v>64573.19</v>
       </c>
       <c r="K36" t="n">
-        <v>65583.53</v>
+        <v>65134.7</v>
       </c>
       <c r="L36" t="n">
-        <v>65854.71000000001</v>
+        <v>65696.21000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>66449.19</v>
+        <v>65921.48</v>
       </c>
       <c r="N36" t="n">
-        <v>67043.67999999999</v>
+        <v>66146.74000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>66991.55</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
+        <v>67044.5</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3554,70 +3554,66 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>65195.26</v>
+        <v>65604.49000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>65904.24000000001</v>
+        <v>66442.34</v>
       </c>
       <c r="D37" t="n">
-        <v>64609.47</v>
+        <v>65390.55</v>
       </c>
       <c r="E37" t="n">
-        <v>65856.42999999999</v>
+        <v>66262.16</v>
       </c>
       <c r="F37" t="n">
-        <v>328.34</v>
+        <v>405.73</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0062</v>
       </c>
       <c r="H37" t="n">
-        <v>1294.77</v>
+        <v>1051.79</v>
       </c>
       <c r="I37" t="n">
-        <v>64684.17</v>
+        <v>63314.7</v>
       </c>
       <c r="J37" t="n">
-        <v>64573.19</v>
+        <v>64861.44</v>
       </c>
       <c r="K37" t="n">
-        <v>65134.7</v>
+        <v>65209.04</v>
       </c>
       <c r="L37" t="n">
-        <v>65696.21000000001</v>
+        <v>65556.64</v>
       </c>
       <c r="M37" t="n">
-        <v>65921.48</v>
+        <v>66503.82000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>66146.74000000001</v>
+        <v>67450.99000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>67044.5</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67199.02</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
       </c>
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
@@ -3642,57 +3638,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>65604.49000000001</v>
+        <v>66775.78</v>
       </c>
       <c r="C38" t="n">
-        <v>66442.34</v>
+        <v>66954.69</v>
       </c>
       <c r="D38" t="n">
-        <v>65390.55</v>
+        <v>65782.59</v>
       </c>
       <c r="E38" t="n">
-        <v>66262.16</v>
+        <v>66131.98</v>
       </c>
       <c r="F38" t="n">
-        <v>405.73</v>
+        <v>-130.18</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.002</v>
       </c>
       <c r="H38" t="n">
-        <v>1051.79</v>
+        <v>1172.09</v>
       </c>
       <c r="I38" t="n">
-        <v>63314.7</v>
+        <v>64338.76</v>
       </c>
       <c r="J38" t="n">
-        <v>64861.44</v>
+        <v>65383.22</v>
       </c>
       <c r="K38" t="n">
-        <v>65209.04</v>
+        <v>65736.25999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>65556.64</v>
+        <v>66089.3</v>
       </c>
       <c r="M38" t="n">
-        <v>66503.82000000001</v>
+        <v>66788.05</v>
       </c>
       <c r="N38" t="n">
-        <v>67450.99000000001</v>
+        <v>67486.8</v>
       </c>
       <c r="O38" t="n">
-        <v>67199.02</v>
+        <v>67494.14</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3705,12 +3701,12 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U38" s="8" t="n">
@@ -3726,57 +3722,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>66775.78</v>
+        <v>66104.49000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>66954.69</v>
+        <v>66842.82000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>65782.59</v>
+        <v>66012.2</v>
       </c>
       <c r="E39" t="n">
-        <v>66131.98</v>
+        <v>66405.56</v>
       </c>
       <c r="F39" t="n">
-        <v>-130.18</v>
+        <v>273.59</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0041</v>
       </c>
       <c r="H39" t="n">
-        <v>1172.09</v>
+        <v>830.62</v>
       </c>
       <c r="I39" t="n">
-        <v>64338.76</v>
+        <v>64610.5</v>
       </c>
       <c r="J39" t="n">
-        <v>65383.22</v>
+        <v>64841.55</v>
       </c>
       <c r="K39" t="n">
-        <v>65736.25999999999</v>
+        <v>65545.92999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>66089.3</v>
+        <v>66250.31</v>
       </c>
       <c r="M39" t="n">
-        <v>66788.05</v>
+        <v>66718.02</v>
       </c>
       <c r="N39" t="n">
-        <v>67486.8</v>
+        <v>67185.74000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>67494.14</v>
+        <v>68126.78</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3817,69 +3813,73 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>66104.49000000001</v>
+        <v>65668.50999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>66842.82000000001</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>66012.2</v>
+        <v>64832.1</v>
       </c>
       <c r="E40" t="n">
-        <v>66405.56</v>
+        <v>66311.92999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>273.59</v>
+        <v>-93.63</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0041</v>
+        <v>-0.0014</v>
       </c>
       <c r="H40" t="n">
-        <v>830.62</v>
+        <v>1479.83</v>
       </c>
       <c r="I40" t="n">
-        <v>64610.5</v>
+        <v>65181.59</v>
       </c>
       <c r="J40" t="n">
-        <v>64841.55</v>
+        <v>65563.97</v>
       </c>
       <c r="K40" t="n">
-        <v>65545.92999999999</v>
+        <v>65990.25</v>
       </c>
       <c r="L40" t="n">
-        <v>66250.31</v>
+        <v>66416.53999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>66718.02</v>
+        <v>66820.87</v>
       </c>
       <c r="N40" t="n">
-        <v>67185.74000000001</v>
+        <v>67225.21000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>68126.78</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67673.44</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3892,78 +3892,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>65668.50999999999</v>
+        <v>65885.47</v>
       </c>
       <c r="C41" t="n">
-        <v>66311.92999999999</v>
+        <v>66525.7</v>
       </c>
       <c r="D41" t="n">
-        <v>64832.1</v>
+        <v>65576.61</v>
       </c>
       <c r="E41" t="n">
-        <v>66311.92999999999</v>
+        <v>66215.34</v>
       </c>
       <c r="F41" t="n">
-        <v>-93.63</v>
+        <v>-96.59</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0014</v>
+        <v>-0.0015</v>
       </c>
       <c r="H41" t="n">
-        <v>1479.83</v>
+        <v>949.09</v>
       </c>
       <c r="I41" t="n">
-        <v>65181.59</v>
+        <v>63352.27</v>
       </c>
       <c r="J41" t="n">
-        <v>65563.97</v>
+        <v>65202.06</v>
       </c>
       <c r="K41" t="n">
-        <v>65990.25</v>
+        <v>65572.02</v>
       </c>
       <c r="L41" t="n">
-        <v>66416.53999999999</v>
+        <v>65941.97</v>
       </c>
       <c r="M41" t="n">
-        <v>66820.87</v>
+        <v>67051.84</v>
       </c>
       <c r="N41" t="n">
-        <v>67225.21000000001</v>
+        <v>68161.71000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>67673.44</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>67791.75999999999</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3980,68 +3970,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>65885.47</v>
+        <v>65195.43</v>
       </c>
       <c r="C42" t="n">
-        <v>66525.7</v>
+        <v>65195.43</v>
       </c>
       <c r="D42" t="n">
-        <v>65576.61</v>
+        <v>64215.47</v>
       </c>
       <c r="E42" t="n">
-        <v>66215.34</v>
+        <v>64325.64</v>
       </c>
       <c r="F42" t="n">
-        <v>-96.59</v>
+        <v>-1889.7</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0285</v>
       </c>
       <c r="H42" t="n">
-        <v>949.09</v>
+        <v>979.96</v>
       </c>
       <c r="I42" t="n">
-        <v>63352.27</v>
+        <v>64627.52</v>
       </c>
       <c r="J42" t="n">
-        <v>65202.06</v>
+        <v>65348.34</v>
       </c>
       <c r="K42" t="n">
-        <v>65572.02</v>
+        <v>65740.8</v>
       </c>
       <c r="L42" t="n">
-        <v>65941.97</v>
+        <v>66133.25</v>
       </c>
       <c r="M42" t="n">
-        <v>67051.84</v>
+        <v>66689.89</v>
       </c>
       <c r="N42" t="n">
-        <v>68161.71000000001</v>
+        <v>67246.53</v>
       </c>
       <c r="O42" t="n">
-        <v>67791.75999999999</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>67474.8</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4058,69 +4058,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="C43" t="n">
-        <v>65195.43</v>
+        <v>64724.81</v>
       </c>
       <c r="D43" t="n">
-        <v>64215.47</v>
+        <v>63772.8</v>
       </c>
       <c r="E43" t="n">
-        <v>64325.64</v>
+        <v>64214.48</v>
       </c>
       <c r="F43" t="n">
-        <v>-1889.7</v>
+        <v>-111.16</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0017</v>
       </c>
       <c r="H43" t="n">
-        <v>979.96</v>
+        <v>952.01</v>
       </c>
       <c r="I43" t="n">
-        <v>64627.52</v>
+        <v>63235.51</v>
       </c>
       <c r="J43" t="n">
-        <v>65348.34</v>
+        <v>63155.78</v>
       </c>
       <c r="K43" t="n">
-        <v>65740.8</v>
+        <v>63835.66</v>
       </c>
       <c r="L43" t="n">
-        <v>66133.25</v>
+        <v>64515.54</v>
       </c>
       <c r="M43" t="n">
-        <v>66689.89</v>
+        <v>64815.62</v>
       </c>
       <c r="N43" t="n">
-        <v>67246.53</v>
+        <v>65115.7</v>
       </c>
       <c r="O43" t="n">
-        <v>67474.8</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66175.39</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
@@ -4129,7 +4121,7 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4151,50 +4143,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>64724.81</v>
+        <v>64498.94</v>
       </c>
       <c r="C44" t="n">
-        <v>64724.81</v>
+        <v>65182.45</v>
       </c>
       <c r="D44" t="n">
-        <v>63772.8</v>
+        <v>64228.47</v>
       </c>
       <c r="E44" t="n">
-        <v>64214.48</v>
+        <v>65020.94</v>
       </c>
       <c r="F44" t="n">
-        <v>-111.16</v>
+        <v>806.46</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0126</v>
       </c>
       <c r="H44" t="n">
-        <v>952.01</v>
+        <v>953.98</v>
       </c>
       <c r="I44" t="n">
-        <v>63235.51</v>
+        <v>62820.79</v>
       </c>
       <c r="J44" t="n">
-        <v>63155.78</v>
+        <v>63245.31</v>
       </c>
       <c r="K44" t="n">
-        <v>63835.66</v>
+        <v>63738.48</v>
       </c>
       <c r="L44" t="n">
-        <v>64515.54</v>
+        <v>64231.64</v>
       </c>
       <c r="M44" t="n">
-        <v>64815.62</v>
+        <v>64690.48</v>
       </c>
       <c r="N44" t="n">
-        <v>65115.7</v>
+        <v>65149.33</v>
       </c>
       <c r="O44" t="n">
-        <v>66175.39</v>
+        <v>65676.82000000001</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4202,21 +4194,23 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4226,55 +4220,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>64498.94</v>
+        <v>65600.42</v>
       </c>
       <c r="C45" t="n">
-        <v>65182.45</v>
+        <v>66668.71000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>64228.47</v>
+        <v>65600.42</v>
       </c>
       <c r="E45" t="n">
-        <v>65020.94</v>
+        <v>66399.84</v>
       </c>
       <c r="F45" t="n">
-        <v>806.46</v>
+        <v>1378.9</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0212</v>
       </c>
       <c r="H45" t="n">
-        <v>953.98</v>
+        <v>1068.29</v>
       </c>
       <c r="I45" t="n">
-        <v>62820.79</v>
+        <v>63274.49</v>
       </c>
       <c r="J45" t="n">
-        <v>63245.31</v>
+        <v>64224.7</v>
       </c>
       <c r="K45" t="n">
-        <v>63738.48</v>
+        <v>64543.95</v>
       </c>
       <c r="L45" t="n">
-        <v>64231.64</v>
+        <v>64863.2</v>
       </c>
       <c r="M45" t="n">
-        <v>64690.48</v>
+        <v>65497.93</v>
       </c>
       <c r="N45" t="n">
-        <v>65149.33</v>
+        <v>66132.66</v>
       </c>
       <c r="O45" t="n">
-        <v>65676.82000000001</v>
+        <v>66136.42999999999</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4297,171 +4295,167 @@
       </c>
       <c r="U45" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W45" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>65600.42</v>
+        <v>65843.69</v>
       </c>
       <c r="C46" t="n">
-        <v>66668.71000000001</v>
+        <v>66791.84</v>
       </c>
       <c r="D46" t="n">
-        <v>65600.42</v>
+        <v>65269.33</v>
       </c>
       <c r="E46" t="n">
-        <v>66399.84</v>
+        <v>65269.33</v>
       </c>
       <c r="F46" t="n">
-        <v>1378.9</v>
+        <v>-1130.52</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.017</v>
       </c>
       <c r="H46" t="n">
-        <v>1068.29</v>
+        <v>1522.52</v>
       </c>
       <c r="I46" t="n">
-        <v>63274.49</v>
+        <v>64532.13</v>
       </c>
       <c r="J46" t="n">
-        <v>64224.7</v>
+        <v>65464.19</v>
       </c>
       <c r="K46" t="n">
-        <v>64543.95</v>
+        <v>65865.7</v>
       </c>
       <c r="L46" t="n">
-        <v>64863.2</v>
+        <v>66267.21000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>65497.93</v>
+        <v>66933.99000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>66132.66</v>
+        <v>67600.77</v>
       </c>
       <c r="O46" t="n">
-        <v>66136.42999999999</v>
+        <v>67737</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
+      <c r="Q46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>65843.69</v>
+        <v>65087.22</v>
       </c>
       <c r="C47" t="n">
-        <v>66791.84</v>
+        <v>65794.03</v>
       </c>
       <c r="D47" t="n">
-        <v>65269.33</v>
+        <v>65017.68</v>
       </c>
       <c r="E47" t="n">
-        <v>65269.33</v>
+        <v>65142.78</v>
       </c>
       <c r="F47" t="n">
-        <v>-1130.52</v>
+        <v>-126.55</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0019</v>
       </c>
       <c r="H47" t="n">
-        <v>1522.52</v>
+        <v>776.35</v>
       </c>
       <c r="I47" t="n">
-        <v>64532.13</v>
+        <v>63746.81</v>
       </c>
       <c r="J47" t="n">
-        <v>65464.19</v>
+        <v>63366.18</v>
       </c>
       <c r="K47" t="n">
-        <v>65865.7</v>
+        <v>64508.07</v>
       </c>
       <c r="L47" t="n">
-        <v>66267.21000000001</v>
+        <v>65649.96000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>66933.99000000001</v>
+        <v>66030.59</v>
       </c>
       <c r="N47" t="n">
-        <v>67600.77</v>
+        <v>66411.21000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>67737</v>
+        <v>68314.36</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4478,68 +4472,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65087.22</v>
+        <v>64768.53</v>
       </c>
       <c r="C48" t="n">
-        <v>65794.03</v>
+        <v>65270.95</v>
       </c>
       <c r="D48" t="n">
-        <v>65017.68</v>
+        <v>64186.68</v>
       </c>
       <c r="E48" t="n">
-        <v>65142.78</v>
+        <v>65270.95</v>
       </c>
       <c r="F48" t="n">
-        <v>-126.55</v>
+        <v>128.17</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0019</v>
+        <v>0.002</v>
       </c>
       <c r="H48" t="n">
-        <v>776.35</v>
+        <v>1084.27</v>
       </c>
       <c r="I48" t="n">
-        <v>63746.81</v>
+        <v>64241.33</v>
       </c>
       <c r="J48" t="n">
-        <v>63366.18</v>
+        <v>64234.89</v>
       </c>
       <c r="K48" t="n">
-        <v>64508.07</v>
+        <v>64754.61</v>
       </c>
       <c r="L48" t="n">
-        <v>65649.96000000001</v>
+        <v>65274.32</v>
       </c>
       <c r="M48" t="n">
-        <v>66030.59</v>
+        <v>65530.96</v>
       </c>
       <c r="N48" t="n">
-        <v>66411.21000000001</v>
+        <v>65787.60000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>68314.36</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+        <v>66570.38</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
@@ -4560,64 +4556,66 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>64768.53</v>
+        <v>64276.82</v>
       </c>
       <c r="C49" t="n">
-        <v>65270.95</v>
+        <v>64312.02</v>
       </c>
       <c r="D49" t="n">
-        <v>64186.68</v>
+        <v>63208.63</v>
       </c>
       <c r="E49" t="n">
-        <v>65270.95</v>
+        <v>64011.34</v>
       </c>
       <c r="F49" t="n">
-        <v>128.17</v>
+        <v>-1259.61</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H49" t="n">
-        <v>1084.27</v>
+        <v>1103.39</v>
       </c>
       <c r="I49" t="n">
-        <v>64241.33</v>
+        <v>63102.41</v>
       </c>
       <c r="J49" t="n">
-        <v>64234.89</v>
+        <v>64457.75</v>
       </c>
       <c r="K49" t="n">
-        <v>64754.61</v>
+        <v>64728.81</v>
       </c>
       <c r="L49" t="n">
-        <v>65274.32</v>
+        <v>64999.88</v>
       </c>
       <c r="M49" t="n">
-        <v>65530.96</v>
+        <v>65813.08</v>
       </c>
       <c r="N49" t="n">
-        <v>65787.60000000001</v>
+        <v>66626.28999999999</v>
       </c>
       <c r="O49" t="n">
-        <v>66570.38</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66355.22</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
@@ -4627,7 +4625,7 @@
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4644,71 +4642,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>64276.82</v>
+        <v>63659.53</v>
       </c>
       <c r="C50" t="n">
-        <v>64312.02</v>
+        <v>63691.53</v>
       </c>
       <c r="D50" t="n">
-        <v>63208.63</v>
+        <v>62726.18</v>
       </c>
       <c r="E50" t="n">
-        <v>64011.34</v>
+        <v>63492.99</v>
       </c>
       <c r="F50" t="n">
-        <v>-1259.61</v>
+        <v>-518.35</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0081</v>
       </c>
       <c r="H50" t="n">
-        <v>1103.39</v>
+        <v>965.35</v>
       </c>
       <c r="I50" t="n">
-        <v>63102.41</v>
+        <v>62105.24</v>
       </c>
       <c r="J50" t="n">
-        <v>64457.75</v>
+        <v>63033.46</v>
       </c>
       <c r="K50" t="n">
-        <v>64728.81</v>
+        <v>63459.64</v>
       </c>
       <c r="L50" t="n">
-        <v>64999.88</v>
+        <v>63885.83</v>
       </c>
       <c r="M50" t="n">
-        <v>65813.08</v>
+        <v>64563.04</v>
       </c>
       <c r="N50" t="n">
-        <v>66626.28999999999</v>
+        <v>65240.24</v>
       </c>
       <c r="O50" t="n">
-        <v>66355.22</v>
+        <v>65415.41</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
@@ -4735,71 +4729,69 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>63659.53</v>
+        <v>63190.37</v>
       </c>
       <c r="C51" t="n">
-        <v>63691.53</v>
+        <v>64101</v>
       </c>
       <c r="D51" t="n">
-        <v>62726.18</v>
+        <v>63067.18</v>
       </c>
       <c r="E51" t="n">
-        <v>63492.99</v>
+        <v>63484.1</v>
       </c>
       <c r="F51" t="n">
-        <v>-518.35</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0081</v>
+        <v>-0.0001</v>
       </c>
       <c r="H51" t="n">
-        <v>965.35</v>
+        <v>1033.82</v>
       </c>
       <c r="I51" t="n">
-        <v>62105.24</v>
+        <v>61760.83</v>
       </c>
       <c r="J51" t="n">
-        <v>63033.46</v>
+        <v>62669.7</v>
       </c>
       <c r="K51" t="n">
-        <v>63459.64</v>
+        <v>63010.31</v>
       </c>
       <c r="L51" t="n">
-        <v>63885.83</v>
+        <v>63350.92</v>
       </c>
       <c r="M51" t="n">
-        <v>64563.04</v>
+        <v>63975.66</v>
       </c>
       <c r="N51" t="n">
-        <v>65240.24</v>
+        <v>64600.41</v>
       </c>
       <c r="O51" t="n">
-        <v>65415.41</v>
+        <v>64656.88</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4812,55 +4804,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63190.37</v>
+        <v>63672.13</v>
       </c>
       <c r="C52" t="n">
-        <v>64101</v>
+        <v>63923</v>
       </c>
       <c r="D52" t="n">
-        <v>63067.18</v>
+        <v>63209.92</v>
       </c>
       <c r="E52" t="n">
-        <v>63484.1</v>
+        <v>63923</v>
       </c>
       <c r="F52" t="n">
-        <v>-8.890000000000001</v>
+        <v>438.9</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0069</v>
       </c>
       <c r="H52" t="n">
-        <v>1033.82</v>
+        <v>713.08</v>
       </c>
       <c r="I52" t="n">
-        <v>61760.83</v>
+        <v>62033.36</v>
       </c>
       <c r="J52" t="n">
-        <v>62669.7</v>
+        <v>62400.29</v>
       </c>
       <c r="K52" t="n">
-        <v>63010.31</v>
+        <v>62967.19</v>
       </c>
       <c r="L52" t="n">
-        <v>63350.92</v>
+        <v>63534.1</v>
       </c>
       <c r="M52" t="n">
-        <v>63975.66</v>
+        <v>64001.01</v>
       </c>
       <c r="N52" t="n">
-        <v>64600.41</v>
+        <v>64467.93</v>
       </c>
       <c r="O52" t="n">
-        <v>64656.88</v>
+        <v>65134.82</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4873,12 +4869,12 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U52" s="8" t="n">
@@ -4901,50 +4897,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>63672.13</v>
+        <v>64643.58</v>
       </c>
       <c r="C53" t="n">
-        <v>63923</v>
+        <v>64643.58</v>
       </c>
       <c r="D53" t="n">
-        <v>63209.92</v>
+        <v>63824.56</v>
       </c>
       <c r="E53" t="n">
-        <v>63923</v>
+        <v>64136.25</v>
       </c>
       <c r="F53" t="n">
-        <v>438.9</v>
+        <v>213.25</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0033</v>
       </c>
       <c r="H53" t="n">
-        <v>713.08</v>
+        <v>819.02</v>
       </c>
       <c r="I53" t="n">
-        <v>62033.36</v>
+        <v>62496.84</v>
       </c>
       <c r="J53" t="n">
-        <v>62400.29</v>
+        <v>63388.19</v>
       </c>
       <c r="K53" t="n">
-        <v>62967.19</v>
+        <v>63566.46</v>
       </c>
       <c r="L53" t="n">
-        <v>63534.1</v>
+        <v>63744.73</v>
       </c>
       <c r="M53" t="n">
-        <v>64001.01</v>
+        <v>64279.54</v>
       </c>
       <c r="N53" t="n">
-        <v>64467.93</v>
+        <v>64814.35</v>
       </c>
       <c r="O53" t="n">
-        <v>65134.82</v>
+        <v>64636.08</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4968,8 +4964,10 @@
       <c r="U53" s="8" t="n">
         <v/>
       </c>
-      <c r="V53" s="8" t="n">
-        <v/>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W53" s="11" t="inlineStr">
         <is>
@@ -4978,57 +4976,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>64643.58</v>
+        <v>64681.55</v>
       </c>
       <c r="C54" t="n">
-        <v>64643.58</v>
+        <v>65436.57</v>
       </c>
       <c r="D54" t="n">
-        <v>63824.56</v>
+        <v>64403.85</v>
       </c>
       <c r="E54" t="n">
-        <v>64136.25</v>
+        <v>65018.95</v>
       </c>
       <c r="F54" t="n">
-        <v>213.25</v>
+        <v>882.7</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0138</v>
       </c>
       <c r="H54" t="n">
-        <v>819.02</v>
+        <v>1032.72</v>
       </c>
       <c r="I54" t="n">
-        <v>62496.84</v>
+        <v>63005.54</v>
       </c>
       <c r="J54" t="n">
-        <v>63388.19</v>
+        <v>63268.32</v>
       </c>
       <c r="K54" t="n">
-        <v>63566.46</v>
+        <v>63726.74</v>
       </c>
       <c r="L54" t="n">
-        <v>63744.73</v>
+        <v>64185.16</v>
       </c>
       <c r="M54" t="n">
-        <v>64279.54</v>
+        <v>64545.76</v>
       </c>
       <c r="N54" t="n">
-        <v>64814.35</v>
+        <v>64906.36</v>
       </c>
       <c r="O54" t="n">
-        <v>64636.08</v>
+        <v>65462.6</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5046,75 +5044,71 @@
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>64681.55</v>
+        <v>65476.44</v>
       </c>
       <c r="C55" t="n">
-        <v>65436.57</v>
+        <v>66249.11</v>
       </c>
       <c r="D55" t="n">
-        <v>64403.85</v>
+        <v>65407.37</v>
       </c>
       <c r="E55" t="n">
-        <v>65018.95</v>
+        <v>65513.99</v>
       </c>
       <c r="F55" t="n">
-        <v>882.7</v>
+        <v>495.04</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.0076</v>
       </c>
       <c r="H55" t="n">
-        <v>1032.72</v>
+        <v>841.74</v>
       </c>
       <c r="I55" t="n">
-        <v>63005.54</v>
+        <v>63371.13</v>
       </c>
       <c r="J55" t="n">
-        <v>63268.32</v>
+        <v>64035.6</v>
       </c>
       <c r="K55" t="n">
-        <v>63726.74</v>
+        <v>64502.59</v>
       </c>
       <c r="L55" t="n">
-        <v>64185.16</v>
+        <v>64969.58</v>
       </c>
       <c r="M55" t="n">
-        <v>64545.76</v>
+        <v>65535.31</v>
       </c>
       <c r="N55" t="n">
-        <v>64906.36</v>
+        <v>66101.03999999999</v>
       </c>
       <c r="O55" t="n">
-        <v>65462.6</v>
+        <v>66469.28999999999</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5132,12 +5126,12 @@
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U55" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V55" s="8" t="n">
@@ -5153,50 +5147,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>65476.44</v>
+        <v>65639.62</v>
       </c>
       <c r="C56" t="n">
-        <v>66249.11</v>
+        <v>66410.27</v>
       </c>
       <c r="D56" t="n">
-        <v>65407.37</v>
+        <v>65639.62</v>
       </c>
       <c r="E56" t="n">
-        <v>65513.99</v>
+        <v>66364.2</v>
       </c>
       <c r="F56" t="n">
-        <v>495.04</v>
+        <v>850.21</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.013</v>
       </c>
       <c r="H56" t="n">
-        <v>841.74</v>
+        <v>770.66</v>
       </c>
       <c r="I56" t="n">
-        <v>63371.13</v>
+        <v>64565.63</v>
       </c>
       <c r="J56" t="n">
-        <v>64035.6</v>
+        <v>64515.12</v>
       </c>
       <c r="K56" t="n">
-        <v>64502.59</v>
+        <v>65093.12</v>
       </c>
       <c r="L56" t="n">
-        <v>64969.58</v>
+        <v>65671.11</v>
       </c>
       <c r="M56" t="n">
-        <v>65535.31</v>
+        <v>65934.86</v>
       </c>
       <c r="N56" t="n">
-        <v>66101.03999999999</v>
+        <v>66198.60000000001</v>
       </c>
       <c r="O56" t="n">
-        <v>66469.28999999999</v>
+        <v>67090.85000000001</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5214,12 +5208,12 @@
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V56" s="8" t="n">
@@ -5235,50 +5229,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>65639.62</v>
+        <v>66505.94</v>
       </c>
       <c r="C57" t="n">
-        <v>66410.27</v>
+        <v>67034.74000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>65639.62</v>
+        <v>65877.62</v>
       </c>
       <c r="E57" t="n">
-        <v>66364.2</v>
+        <v>65877.62</v>
       </c>
       <c r="F57" t="n">
-        <v>850.21</v>
+        <v>-486.59</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0073</v>
       </c>
       <c r="H57" t="n">
-        <v>770.66</v>
+        <v>1157.12</v>
       </c>
       <c r="I57" t="n">
-        <v>64565.63</v>
+        <v>64868.96</v>
       </c>
       <c r="J57" t="n">
-        <v>64515.12</v>
+        <v>65763.17999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>65093.12</v>
+        <v>65978.88</v>
       </c>
       <c r="L57" t="n">
-        <v>65671.11</v>
+        <v>66194.57000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>65934.86</v>
+        <v>66749.53</v>
       </c>
       <c r="N57" t="n">
-        <v>66198.60000000001</v>
+        <v>67304.49000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>67090.85000000001</v>
+        <v>67180.92999999999</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5286,12 +5280,14 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
@@ -5299,10 +5295,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5312,58 +5306,64 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>66505.94</v>
+        <v>65557.99000000001</v>
       </c>
       <c r="C58" t="n">
-        <v>67034.74000000001</v>
+        <v>65805.08</v>
       </c>
       <c r="D58" t="n">
-        <v>65877.62</v>
+        <v>64699.49</v>
       </c>
       <c r="E58" t="n">
-        <v>65877.62</v>
+        <v>65481.27</v>
       </c>
       <c r="F58" t="n">
-        <v>-486.59</v>
+        <v>-396.35</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.006</v>
       </c>
       <c r="H58" t="n">
-        <v>1157.12</v>
+        <v>1105.59</v>
       </c>
       <c r="I58" t="n">
-        <v>64868.96</v>
+        <v>64720.49</v>
       </c>
       <c r="J58" t="n">
-        <v>65763.17999999999</v>
+        <v>64431.21</v>
       </c>
       <c r="K58" t="n">
-        <v>65978.88</v>
+        <v>65299.05</v>
       </c>
       <c r="L58" t="n">
-        <v>66194.57000000001</v>
+        <v>66166.89999999999</v>
       </c>
       <c r="M58" t="n">
-        <v>66749.53</v>
+        <v>66456.17999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>67304.49000000001</v>
+        <v>66745.46000000001</v>
       </c>
       <c r="O58" t="n">
-        <v>67180.92999999999</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+        <v>68191.87</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5378,10 +5378,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5396,110 +5394,108 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>65557.99000000001</v>
+        <v>66128.59</v>
       </c>
       <c r="C59" t="n">
-        <v>65805.08</v>
+        <v>66946.14</v>
       </c>
       <c r="D59" t="n">
-        <v>64699.49</v>
+        <v>66014.48</v>
       </c>
       <c r="E59" t="n">
-        <v>65481.27</v>
+        <v>66753.72</v>
       </c>
       <c r="F59" t="n">
-        <v>-396.35</v>
+        <v>1272.45</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0194</v>
       </c>
       <c r="H59" t="n">
-        <v>1105.59</v>
+        <v>931.66</v>
       </c>
       <c r="I59" t="n">
-        <v>64720.49</v>
+        <v>63593.9</v>
       </c>
       <c r="J59" t="n">
-        <v>64431.21</v>
+        <v>64490.17</v>
       </c>
       <c r="K59" t="n">
-        <v>65299.05</v>
+        <v>64928.47</v>
       </c>
       <c r="L59" t="n">
-        <v>66166.89999999999</v>
+        <v>65366.78</v>
       </c>
       <c r="M59" t="n">
-        <v>66456.17999999999</v>
+        <v>66034.06</v>
       </c>
       <c r="N59" t="n">
-        <v>66745.46000000001</v>
+        <v>66701.35000000001</v>
       </c>
       <c r="O59" t="n">
-        <v>68191.87</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>66910.67</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
       </c>
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>66128.59</v>
+        <v>67106.52</v>
       </c>
       <c r="C60" t="n">
-        <v>66946.14</v>
+        <v>68995.3</v>
       </c>
       <c r="D60" t="n">
-        <v>66014.48</v>
+        <v>67081.66</v>
       </c>
       <c r="E60" t="n">
         <v/>
@@ -5511,28 +5507,28 @@
         <v/>
       </c>
       <c r="H60" t="n">
-        <v>931.66</v>
+        <v>1913.64</v>
       </c>
       <c r="I60" t="n">
-        <v>63593.9</v>
+        <v>65082.81</v>
       </c>
       <c r="J60" t="n">
-        <v>64490.17</v>
+        <v>65958.75999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>64928.47</v>
+        <v>66287.89</v>
       </c>
       <c r="L60" t="n">
-        <v>65366.78</v>
+        <v>66617.00999999999</v>
       </c>
       <c r="M60" t="n">
-        <v>66034.06</v>
+        <v>67219.55</v>
       </c>
       <c r="N60" t="n">
-        <v>66701.35000000001</v>
+        <v>67822.09</v>
       </c>
       <c r="O60" t="n">
-        <v>66910.67</v>
+        <v>67877.8</v>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>

--- a/three_gate/analysis/N225_daily.xlsx
+++ b/three_gate/analysis/N225_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,20 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -637,63 +634,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69973.34</v>
+        <v>69460.08</v>
       </c>
       <c r="C2" t="n">
-        <v>70384.59</v>
+        <v>69957.50999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>68904.41</v>
+        <v>68003.92</v>
       </c>
       <c r="E2" t="n">
-        <v>69737.69</v>
+        <v>68256.96000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.38</v>
+        <v>-1480.73</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0001</v>
+        <v>-0.0212</v>
       </c>
       <c r="H2" t="n">
-        <v>1480.19</v>
+        <v>1953.59</v>
       </c>
       <c r="I2" t="n">
-        <v>65430.95</v>
+        <v>67424.22</v>
       </c>
       <c r="J2" t="n">
-        <v>68088.19</v>
+        <v>68304.09</v>
       </c>
       <c r="K2" t="n">
-        <v>68654.8</v>
+        <v>68997.59</v>
       </c>
       <c r="L2" t="n">
-        <v>69221.42</v>
+        <v>69691.09</v>
       </c>
       <c r="M2" t="n">
-        <v>70833.34</v>
+        <v>70477.78</v>
       </c>
       <c r="N2" t="n">
-        <v>72445.25999999999</v>
+        <v>71264.47</v>
       </c>
       <c r="O2" t="n">
-        <v>71966.57000000001</v>
+        <v>71864.78</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -707,77 +708,71 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69460.08</v>
+        <v>67704.16</v>
       </c>
       <c r="C3" t="n">
-        <v>69957.50999999999</v>
+        <v>68432.67999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>68003.92</v>
+        <v>66819.05</v>
       </c>
       <c r="E3" t="n">
-        <v>68256.96000000001</v>
+        <v>66819.05</v>
       </c>
       <c r="F3" t="n">
-        <v>-1480.73</v>
+        <v>-1437.91</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="H3" t="n">
-        <v>1953.59</v>
+        <v>1613.63</v>
       </c>
       <c r="I3" t="n">
-        <v>67424.22</v>
+        <v>66050.34</v>
       </c>
       <c r="J3" t="n">
-        <v>68304.09</v>
+        <v>65941.5</v>
       </c>
       <c r="K3" t="n">
-        <v>68997.59</v>
+        <v>67280.17</v>
       </c>
       <c r="L3" t="n">
-        <v>69691.09</v>
+        <v>68618.84</v>
       </c>
       <c r="M3" t="n">
-        <v>70477.78</v>
+        <v>69233.75</v>
       </c>
       <c r="N3" t="n">
-        <v>71264.47</v>
+        <v>69848.67</v>
       </c>
       <c r="O3" t="n">
-        <v>71864.78</v>
+        <v>71911.09</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -791,7 +786,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -801,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67704.16</v>
+        <v>67046.37</v>
       </c>
       <c r="C4" t="n">
-        <v>68432.67999999999</v>
+        <v>68447.89</v>
       </c>
       <c r="D4" t="n">
-        <v>66819.05</v>
+        <v>67008.89</v>
       </c>
       <c r="E4" t="n">
-        <v>66819.05</v>
+        <v>67743.85000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-1437.91</v>
+        <v>924.8</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0211</v>
+        <v>0.0138</v>
       </c>
       <c r="H4" t="n">
-        <v>1613.63</v>
+        <v>1439</v>
       </c>
       <c r="I4" t="n">
-        <v>66050.34</v>
+        <v>65205.41</v>
       </c>
       <c r="J4" t="n">
-        <v>65941.5</v>
+        <v>64802.01</v>
       </c>
       <c r="K4" t="n">
-        <v>67280.17</v>
+        <v>66012.23</v>
       </c>
       <c r="L4" t="n">
-        <v>68618.84</v>
+        <v>67222.46000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>69233.75</v>
+        <v>67625.86</v>
       </c>
       <c r="N4" t="n">
-        <v>69848.67</v>
+        <v>68029.27</v>
       </c>
       <c r="O4" t="n">
-        <v>71911.09</v>
+        <v>70046.31</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -852,79 +847,85 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67046.37</v>
+        <v>68526.72</v>
       </c>
       <c r="C5" t="n">
-        <v>68447.89</v>
+        <v>69374.86</v>
       </c>
       <c r="D5" t="n">
-        <v>67008.89</v>
+        <v>68271.91</v>
       </c>
       <c r="E5" t="n">
-        <v>67743.85000000001</v>
+        <v>68557.73</v>
       </c>
       <c r="F5" t="n">
-        <v>924.8</v>
+        <v>813.88</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.012</v>
       </c>
       <c r="H5" t="n">
-        <v>1439</v>
+        <v>1102.95</v>
       </c>
       <c r="I5" t="n">
-        <v>65205.41</v>
+        <v>65569.89</v>
       </c>
       <c r="J5" t="n">
-        <v>64802.01</v>
+        <v>66312.58</v>
       </c>
       <c r="K5" t="n">
-        <v>66012.23</v>
+        <v>67024.35000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>67222.46000000001</v>
+        <v>67736.12</v>
       </c>
       <c r="M5" t="n">
-        <v>67625.86</v>
+        <v>68463.35000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>68029.27</v>
+        <v>69190.58</v>
       </c>
       <c r="O5" t="n">
-        <v>70046.31</v>
+        <v>69886.89</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -935,7 +936,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -953,7 +954,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -967,155 +968,147 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68526.72</v>
+        <v>68410.63</v>
       </c>
       <c r="C6" t="n">
-        <v>69374.86</v>
+        <v>69078.21000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>68271.91</v>
+        <v>66653.11</v>
       </c>
       <c r="E6" t="n">
-        <v>68557.73</v>
+        <v>67242.73</v>
       </c>
       <c r="F6" t="n">
-        <v>813.88</v>
+        <v>-1315</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0192</v>
       </c>
       <c r="H6" t="n">
-        <v>1102.95</v>
+        <v>2425.1</v>
       </c>
       <c r="I6" t="n">
-        <v>65569.89</v>
+        <v>67168.95</v>
       </c>
       <c r="J6" t="n">
-        <v>66312.58</v>
+        <v>67321.95</v>
       </c>
       <c r="K6" t="n">
-        <v>67024.35000000001</v>
+        <v>68006.25</v>
       </c>
       <c r="L6" t="n">
-        <v>67736.12</v>
+        <v>68690.55</v>
       </c>
       <c r="M6" t="n">
-        <v>68463.35000000001</v>
+        <v>69109.2</v>
       </c>
       <c r="N6" t="n">
-        <v>69190.58</v>
+        <v>69527.85000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>69886.89</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+        <v>70477.81</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>68410.63</v>
+        <v>67002.94</v>
       </c>
       <c r="C7" t="n">
-        <v>69078.21000000001</v>
+        <v>67800.17999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>66653.11</v>
+        <v>66268.60000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>67242.73</v>
+        <v>67743.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-1315</v>
+        <v>500.77</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0192</v>
+        <v>0.0074</v>
       </c>
       <c r="H7" t="n">
-        <v>2425.1</v>
+        <v>1531.58</v>
       </c>
       <c r="I7" t="n">
-        <v>67168.95</v>
+        <v>64228.01</v>
       </c>
       <c r="J7" t="n">
-        <v>67321.95</v>
+        <v>64506.16</v>
       </c>
       <c r="K7" t="n">
-        <v>68006.25</v>
+        <v>66030.17999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>68690.55</v>
+        <v>67554.19</v>
       </c>
       <c r="M7" t="n">
-        <v>69109.2</v>
+        <v>68455.28</v>
       </c>
       <c r="N7" t="n">
-        <v>69527.85000000001</v>
+        <v>69356.36</v>
       </c>
       <c r="O7" t="n">
-        <v>70477.81</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>71503.31</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1127,60 +1120,64 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>67002.94</v>
+        <v>67989.74000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>67800.17999999999</v>
+        <v>68798.24000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>66268.60000000001</v>
+        <v>67833.17</v>
       </c>
       <c r="E8" t="n">
-        <v>67743.5</v>
+        <v>68751.50999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>500.77</v>
+        <v>1008.01</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0149</v>
       </c>
       <c r="H8" t="n">
-        <v>1531.58</v>
+        <v>965.0700000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>64228.01</v>
+        <v>64737.02</v>
       </c>
       <c r="J8" t="n">
-        <v>64506.16</v>
+        <v>66566.48</v>
       </c>
       <c r="K8" t="n">
-        <v>66030.17999999999</v>
+        <v>66977.71000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>67554.19</v>
+        <v>67388.95</v>
       </c>
       <c r="M8" t="n">
-        <v>68455.28</v>
+        <v>68509.28999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>69356.36</v>
+        <v>69629.63</v>
       </c>
       <c r="O8" t="n">
-        <v>71503.31</v>
+        <v>69331.75999999999</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,13 +1188,15 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1205,83 +1204,87 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67989.74000000001</v>
+        <v>67900.42999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>68798.24000000001</v>
+        <v>68069.82000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>67833.17</v>
+        <v>66499.49000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>68751.50999999999</v>
+        <v>66835.53999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>1008.01</v>
+        <v>-1915.97</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0149</v>
+        <v>-0.0279</v>
       </c>
       <c r="H9" t="n">
-        <v>965.0700000000001</v>
+        <v>1570.33</v>
       </c>
       <c r="I9" t="n">
-        <v>64737.02</v>
+        <v>66868.10000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>66566.48</v>
+        <v>68004.34</v>
       </c>
       <c r="K9" t="n">
-        <v>66977.71000000001</v>
+        <v>68268.97</v>
       </c>
       <c r="L9" t="n">
-        <v>67388.95</v>
+        <v>68533.61</v>
       </c>
       <c r="M9" t="n">
-        <v>68509.28999999999</v>
+        <v>69234.03999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>69629.63</v>
+        <v>69934.48</v>
       </c>
       <c r="O9" t="n">
-        <v>69331.75999999999</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+        <v>69763.31</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1289,64 +1292,60 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>67900.42999999999</v>
+        <v>66339.85000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>68069.82000000001</v>
+        <v>66441.77</v>
       </c>
       <c r="D10" t="n">
-        <v>66499.49000000001</v>
+        <v>62704.6</v>
       </c>
       <c r="E10" t="n">
-        <v>66835.53999999999</v>
+        <v>64141.12</v>
       </c>
       <c r="F10" t="n">
-        <v>-1915.97</v>
+        <v>-2694.42</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0403</v>
       </c>
       <c r="H10" t="n">
-        <v>1570.33</v>
+        <v>3737.17</v>
       </c>
       <c r="I10" t="n">
-        <v>66868.10000000001</v>
+        <v>64929.16</v>
       </c>
       <c r="J10" t="n">
-        <v>68004.34</v>
+        <v>65040.65</v>
       </c>
       <c r="K10" t="n">
-        <v>68268.97</v>
+        <v>66050.38</v>
       </c>
       <c r="L10" t="n">
-        <v>68533.61</v>
+        <v>67060.10000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>69234.03999999999</v>
+        <v>67620.7</v>
       </c>
       <c r="N10" t="n">
-        <v>69934.48</v>
+        <v>68181.31</v>
       </c>
       <c r="O10" t="n">
-        <v>69763.31</v>
+        <v>69640.14999999999</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -1363,7 +1362,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1377,7 +1376,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1387,134 +1386,134 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>66339.85000000001</v>
+        <v>64544.05</v>
       </c>
       <c r="C11" t="n">
-        <v>66441.77</v>
+        <v>66232.19</v>
       </c>
       <c r="D11" t="n">
-        <v>62704.6</v>
+        <v>64203.47</v>
       </c>
       <c r="E11" t="n">
-        <v>64141.12</v>
+        <v>66232.19</v>
       </c>
       <c r="F11" t="n">
-        <v>-2694.42</v>
+        <v>2091.07</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0403</v>
+        <v>0.0326</v>
       </c>
       <c r="H11" t="n">
-        <v>3737.17</v>
+        <v>2028.72</v>
       </c>
       <c r="I11" t="n">
-        <v>64929.16</v>
+        <v>58967.43</v>
       </c>
       <c r="J11" t="n">
-        <v>65040.65</v>
+        <v>60187.92</v>
       </c>
       <c r="K11" t="n">
-        <v>66050.38</v>
+        <v>62272.54</v>
       </c>
       <c r="L11" t="n">
-        <v>67060.10000000001</v>
+        <v>64357.15</v>
       </c>
       <c r="M11" t="n">
-        <v>67620.7</v>
+        <v>66009.71000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>68181.31</v>
+        <v>67662.25999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>69640.14999999999</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
+        <v>70178.95</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>64544.05</v>
+        <v>66449.27</v>
       </c>
       <c r="C12" t="n">
-        <v>66232.19</v>
+        <v>67592.2</v>
       </c>
       <c r="D12" t="n">
-        <v>64203.47</v>
+        <v>65955.60000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>66232.19</v>
+        <v>66115.60000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>2091.07</v>
+        <v>-116.59</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0326</v>
+        <v>-0.0018</v>
       </c>
       <c r="H12" t="n">
-        <v>2028.72</v>
+        <v>1636.6</v>
       </c>
       <c r="I12" t="n">
-        <v>58967.43</v>
+        <v>62174.75</v>
       </c>
       <c r="J12" t="n">
-        <v>60187.92</v>
+        <v>64710.65</v>
       </c>
       <c r="K12" t="n">
-        <v>62272.54</v>
+        <v>65217.83</v>
       </c>
       <c r="L12" t="n">
-        <v>64357.15</v>
+        <v>65725.00999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>66009.71000000001</v>
+        <v>67246.55</v>
       </c>
       <c r="N12" t="n">
-        <v>67662.25999999999</v>
+        <v>68768.09</v>
       </c>
       <c r="O12" t="n">
-        <v>70178.95</v>
+        <v>68260.91</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1525,14 +1524,14 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U12" s="8" t="n">
@@ -1541,7 +1540,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1555,50 +1554,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>66449.27</v>
+        <v>66421.00999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>67592.2</v>
+        <v>67022.37</v>
       </c>
       <c r="D13" t="n">
-        <v>65955.60000000001</v>
+        <v>66208.66</v>
       </c>
       <c r="E13" t="n">
-        <v>66115.60000000001</v>
+        <v>66422.60000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-116.59</v>
+        <v>307</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0046</v>
       </c>
       <c r="H13" t="n">
-        <v>1636.6</v>
+        <v>813.71</v>
       </c>
       <c r="I13" t="n">
-        <v>62174.75</v>
+        <v>64319</v>
       </c>
       <c r="J13" t="n">
-        <v>64710.65</v>
+        <v>64149.85</v>
       </c>
       <c r="K13" t="n">
-        <v>65217.83</v>
+        <v>65297.3</v>
       </c>
       <c r="L13" t="n">
-        <v>65725.00999999999</v>
+        <v>66444.75</v>
       </c>
       <c r="M13" t="n">
-        <v>67246.55</v>
+        <v>66933.89999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>68768.09</v>
+        <v>67423.05</v>
       </c>
       <c r="O13" t="n">
-        <v>68260.91</v>
+        <v>69228.8</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1611,7 +1610,7 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
@@ -1625,7 +1624,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1639,69 +1638,73 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>66421.00999999999</v>
+        <v>65584.25</v>
       </c>
       <c r="C14" t="n">
-        <v>67022.37</v>
+        <v>65720.81</v>
       </c>
       <c r="D14" t="n">
-        <v>66208.66</v>
+        <v>64201.03</v>
       </c>
       <c r="E14" t="n">
-        <v>66422.60000000001</v>
+        <v>64611.15</v>
       </c>
       <c r="F14" t="n">
-        <v>307</v>
+        <v>-1811.45</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0273</v>
       </c>
       <c r="H14" t="n">
-        <v>813.71</v>
+        <v>1519.78</v>
       </c>
       <c r="I14" t="n">
-        <v>64319</v>
+        <v>65394.95</v>
       </c>
       <c r="J14" t="n">
-        <v>64149.85</v>
+        <v>65512.44</v>
       </c>
       <c r="K14" t="n">
-        <v>65297.3</v>
+        <v>66015.75</v>
       </c>
       <c r="L14" t="n">
-        <v>66444.75</v>
+        <v>66519.06</v>
       </c>
       <c r="M14" t="n">
-        <v>66933.89999999999</v>
+        <v>66829.46000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>67423.05</v>
+        <v>67139.86</v>
       </c>
       <c r="O14" t="n">
-        <v>69228.8</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67836.08</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1709,83 +1712,73 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>65584.25</v>
+        <v>65164.98</v>
       </c>
       <c r="C15" t="n">
-        <v>65720.81</v>
+        <v>65220.69</v>
       </c>
       <c r="D15" t="n">
-        <v>64201.03</v>
+        <v>64123.4</v>
       </c>
       <c r="E15" t="n">
-        <v>64611.15</v>
+        <v>64931.19</v>
       </c>
       <c r="F15" t="n">
-        <v>-1811.45</v>
+        <v>320.04</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.005</v>
       </c>
       <c r="H15" t="n">
-        <v>1519.78</v>
+        <v>1097.29</v>
       </c>
       <c r="I15" t="n">
-        <v>65394.95</v>
+        <v>62681.25</v>
       </c>
       <c r="J15" t="n">
-        <v>65512.44</v>
+        <v>62916.48</v>
       </c>
       <c r="K15" t="n">
-        <v>66015.75</v>
+        <v>63851.26</v>
       </c>
       <c r="L15" t="n">
-        <v>66519.06</v>
+        <v>64786.04</v>
       </c>
       <c r="M15" t="n">
-        <v>66829.46000000001</v>
+        <v>65371.04</v>
       </c>
       <c r="N15" t="n">
-        <v>67139.86</v>
+        <v>65956.03999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>67836.08</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>67240.59</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1797,73 +1790,83 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>65164.98</v>
+        <v>64539.92</v>
       </c>
       <c r="C16" t="n">
-        <v>65220.69</v>
+        <v>64573.18</v>
       </c>
       <c r="D16" t="n">
-        <v>64123.4</v>
+        <v>61923.6</v>
       </c>
       <c r="E16" t="n">
-        <v>64931.19</v>
+        <v>62364.92</v>
       </c>
       <c r="F16" t="n">
-        <v>320.04</v>
+        <v>-2566.27</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0395</v>
       </c>
       <c r="H16" t="n">
-        <v>1097.29</v>
+        <v>2649.58</v>
       </c>
       <c r="I16" t="n">
-        <v>62681.25</v>
+        <v>63026.11</v>
       </c>
       <c r="J16" t="n">
-        <v>62916.48</v>
+        <v>63963.47</v>
       </c>
       <c r="K16" t="n">
-        <v>63851.26</v>
+        <v>64382.54</v>
       </c>
       <c r="L16" t="n">
-        <v>64786.04</v>
+        <v>64801.62</v>
       </c>
       <c r="M16" t="n">
-        <v>65371.04</v>
+        <v>65479.84</v>
       </c>
       <c r="N16" t="n">
-        <v>65956.03999999999</v>
+        <v>66158.06</v>
       </c>
       <c r="O16" t="n">
-        <v>67240.59</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+        <v>66317.98</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1875,81 +1878,73 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>64539.92</v>
+        <v>62734.68</v>
       </c>
       <c r="C17" t="n">
-        <v>64573.18</v>
+        <v>63138.04</v>
       </c>
       <c r="D17" t="n">
-        <v>61923.6</v>
+        <v>60448.9</v>
       </c>
       <c r="E17" t="n">
-        <v>62364.92</v>
+        <v>61434.19</v>
       </c>
       <c r="F17" t="n">
-        <v>-2566.27</v>
+        <v>-930.73</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0395</v>
+        <v>-0.0149</v>
       </c>
       <c r="H17" t="n">
-        <v>2649.58</v>
+        <v>2689.14</v>
       </c>
       <c r="I17" t="n">
-        <v>63026.11</v>
+        <v>59274.02</v>
       </c>
       <c r="J17" t="n">
-        <v>63963.47</v>
+        <v>59273.61</v>
       </c>
       <c r="K17" t="n">
-        <v>64382.54</v>
+        <v>61040.13</v>
       </c>
       <c r="L17" t="n">
-        <v>64801.62</v>
+        <v>62806.66</v>
       </c>
       <c r="M17" t="n">
-        <v>65479.84</v>
+        <v>63689.71</v>
       </c>
       <c r="N17" t="n">
-        <v>66158.06</v>
+        <v>64572.77</v>
       </c>
       <c r="O17" t="n">
-        <v>66317.98</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>67222.75999999999</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1963,7 +1958,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1973,50 +1968,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>62734.68</v>
+        <v>61258.34</v>
       </c>
       <c r="C18" t="n">
-        <v>63138.04</v>
+        <v>62924.84</v>
       </c>
       <c r="D18" t="n">
-        <v>60448.9</v>
+        <v>61049.7</v>
       </c>
       <c r="E18" t="n">
-        <v>61434.19</v>
+        <v>61867.43</v>
       </c>
       <c r="F18" t="n">
-        <v>-930.73</v>
+        <v>433.24</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0071</v>
       </c>
       <c r="H18" t="n">
-        <v>2689.14</v>
+        <v>1875.14</v>
       </c>
       <c r="I18" t="n">
-        <v>59274.02</v>
+        <v>57759.76</v>
       </c>
       <c r="J18" t="n">
-        <v>59273.61</v>
+        <v>58565.41</v>
       </c>
       <c r="K18" t="n">
-        <v>61040.13</v>
+        <v>60089.62</v>
       </c>
       <c r="L18" t="n">
-        <v>62806.66</v>
+        <v>61613.83</v>
       </c>
       <c r="M18" t="n">
-        <v>63689.71</v>
+        <v>62778.76</v>
       </c>
       <c r="N18" t="n">
-        <v>64572.77</v>
+        <v>63943.69</v>
       </c>
       <c r="O18" t="n">
-        <v>67222.75999999999</v>
+        <v>65827.17999999999</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2024,18 +2019,18 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2043,60 +2038,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>61258.34</v>
+        <v>61957.1</v>
       </c>
       <c r="C19" t="n">
-        <v>62924.84</v>
+        <v>65364.73</v>
       </c>
       <c r="D19" t="n">
-        <v>61049.7</v>
+        <v>61948.23</v>
       </c>
       <c r="E19" t="n">
-        <v>61867.43</v>
+        <v>64362.02</v>
       </c>
       <c r="F19" t="n">
-        <v>433.24</v>
+        <v>2494.59</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0403</v>
       </c>
       <c r="H19" t="n">
-        <v>1875.14</v>
+        <v>3416.5</v>
       </c>
       <c r="I19" t="n">
-        <v>57759.76</v>
+        <v>59174.56</v>
       </c>
       <c r="J19" t="n">
-        <v>58565.41</v>
+        <v>59932.37</v>
       </c>
       <c r="K19" t="n">
-        <v>60089.62</v>
+        <v>60929.86</v>
       </c>
       <c r="L19" t="n">
-        <v>61613.83</v>
+        <v>61927.35</v>
       </c>
       <c r="M19" t="n">
-        <v>62778.76</v>
+        <v>62805</v>
       </c>
       <c r="N19" t="n">
-        <v>63943.69</v>
+        <v>63682.65</v>
       </c>
       <c r="O19" t="n">
-        <v>65827.17999999999</v>
+        <v>64799.98</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2107,9 +2106,9 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2117,70 +2116,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W19" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>61957.1</v>
+        <v>63834.95</v>
       </c>
       <c r="C20" t="n">
-        <v>65364.73</v>
+        <v>63905.12</v>
       </c>
       <c r="D20" t="n">
-        <v>61948.23</v>
+        <v>62703.47</v>
       </c>
       <c r="E20" t="n">
-        <v>64362.02</v>
+        <v>63754.9</v>
       </c>
       <c r="F20" t="n">
-        <v>2494.59</v>
+        <v>-607.12</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0403</v>
+        <v>-0.0094</v>
       </c>
       <c r="H20" t="n">
-        <v>3416.5</v>
+        <v>1201.65</v>
       </c>
       <c r="I20" t="n">
-        <v>59174.56</v>
+        <v>58531.73</v>
       </c>
       <c r="J20" t="n">
-        <v>59932.37</v>
+        <v>61298.29</v>
       </c>
       <c r="K20" t="n">
-        <v>60929.86</v>
+        <v>62653.77</v>
       </c>
       <c r="L20" t="n">
-        <v>61927.35</v>
+        <v>64009.25</v>
       </c>
       <c r="M20" t="n">
-        <v>62805</v>
+        <v>66070.27</v>
       </c>
       <c r="N20" t="n">
-        <v>63682.65</v>
+        <v>68131.28999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>64799.98</v>
+        <v>68781.23</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2193,78 +2192,76 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W20" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63834.95</v>
+        <v>63995.28</v>
       </c>
       <c r="C21" t="n">
-        <v>63905.12</v>
+        <v>64240.5</v>
       </c>
       <c r="D21" t="n">
-        <v>62703.47</v>
+        <v>62864.43</v>
       </c>
       <c r="E21" t="n">
-        <v>63754.9</v>
+        <v>63957.53</v>
       </c>
       <c r="F21" t="n">
-        <v>-607.12</v>
+        <v>202.63</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0094</v>
+        <v>0.0032</v>
       </c>
       <c r="H21" t="n">
-        <v>1201.65</v>
+        <v>1376.07</v>
       </c>
       <c r="I21" t="n">
-        <v>58531.73</v>
+        <v>61501.82</v>
       </c>
       <c r="J21" t="n">
-        <v>61298.29</v>
+        <v>62778.55</v>
       </c>
       <c r="K21" t="n">
-        <v>62653.77</v>
+        <v>63154.07</v>
       </c>
       <c r="L21" t="n">
-        <v>64009.25</v>
+        <v>63529.6</v>
       </c>
       <c r="M21" t="n">
-        <v>66070.27</v>
+        <v>64355.72</v>
       </c>
       <c r="N21" t="n">
-        <v>68131.28999999999</v>
+        <v>65181.85</v>
       </c>
       <c r="O21" t="n">
-        <v>68781.23</v>
+        <v>65106.77</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2272,16 +2269,20 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2289,64 +2290,60 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63995.28</v>
+        <v>64565.27</v>
       </c>
       <c r="C22" t="n">
-        <v>64240.5</v>
+        <v>66302.52</v>
       </c>
       <c r="D22" t="n">
-        <v>62864.43</v>
+        <v>64555.52</v>
       </c>
       <c r="E22" t="n">
-        <v>63957.53</v>
+        <v>66300.44</v>
       </c>
       <c r="F22" t="n">
-        <v>202.63</v>
+        <v>2342.91</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0366</v>
       </c>
       <c r="H22" t="n">
-        <v>1376.07</v>
+        <v>1747</v>
       </c>
       <c r="I22" t="n">
-        <v>61501.82</v>
+        <v>61488.36</v>
       </c>
       <c r="J22" t="n">
-        <v>62778.55</v>
+        <v>62783.99</v>
       </c>
       <c r="K22" t="n">
-        <v>63154.07</v>
+        <v>63269.5</v>
       </c>
       <c r="L22" t="n">
-        <v>63529.6</v>
+        <v>63755</v>
       </c>
       <c r="M22" t="n">
-        <v>64355.72</v>
+        <v>64645.57</v>
       </c>
       <c r="N22" t="n">
-        <v>65181.85</v>
+        <v>65536.13</v>
       </c>
       <c r="O22" t="n">
-        <v>65106.77</v>
+        <v>65616.57000000001</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2354,28 +2351,30 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2385,134 +2384,136 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>64565.27</v>
+        <v>65896</v>
       </c>
       <c r="C23" t="n">
-        <v>66302.52</v>
+        <v>65983.13</v>
       </c>
       <c r="D23" t="n">
-        <v>64555.52</v>
+        <v>64942.07</v>
       </c>
       <c r="E23" t="n">
-        <v>66300.44</v>
+        <v>65683.25999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>2342.91</v>
+        <v>-617.1799999999999</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0366</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>1747</v>
+        <v>1041.06</v>
       </c>
       <c r="I23" t="n">
-        <v>61488.36</v>
+        <v>62808.52</v>
       </c>
       <c r="J23" t="n">
-        <v>62783.99</v>
+        <v>64989.14</v>
       </c>
       <c r="K23" t="n">
-        <v>63269.5</v>
+        <v>65426.94</v>
       </c>
       <c r="L23" t="n">
-        <v>63755</v>
+        <v>65864.73</v>
       </c>
       <c r="M23" t="n">
-        <v>64645.57</v>
+        <v>67173.94</v>
       </c>
       <c r="N23" t="n">
-        <v>65536.13</v>
+        <v>68483.14999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>65616.57000000001</v>
+        <v>68049.53</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W23" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>65896</v>
+        <v>65746.13</v>
       </c>
       <c r="C24" t="n">
-        <v>65983.13</v>
+        <v>65990.72</v>
       </c>
       <c r="D24" t="n">
-        <v>64942.07</v>
+        <v>64651.49</v>
       </c>
       <c r="E24" t="n">
-        <v>65683.25999999999</v>
+        <v>65606.71000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-617.1799999999999</v>
+        <v>-76.55</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0012</v>
       </c>
       <c r="H24" t="n">
-        <v>1041.06</v>
+        <v>1339.23</v>
       </c>
       <c r="I24" t="n">
-        <v>62808.52</v>
+        <v>63901.01</v>
       </c>
       <c r="J24" t="n">
-        <v>64989.14</v>
+        <v>64752.52</v>
       </c>
       <c r="K24" t="n">
-        <v>65426.94</v>
+        <v>65162.73</v>
       </c>
       <c r="L24" t="n">
-        <v>65864.73</v>
+        <v>65572.92999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>67173.94</v>
+        <v>66203.78999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>68483.14999999999</v>
+        <v>66834.64999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>68049.53</v>
+        <v>67024.2</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2529,7 +2530,7 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2541,7 +2542,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2555,136 +2556,132 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65746.13</v>
+        <v>65905.10000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>65990.72</v>
+        <v>67006.84</v>
       </c>
       <c r="D25" t="n">
-        <v>64651.49</v>
+        <v>65848.58</v>
       </c>
       <c r="E25" t="n">
-        <v>65606.71000000001</v>
+        <v>66970.22</v>
       </c>
       <c r="F25" t="n">
-        <v>-76.55</v>
+        <v>1363.51</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0012</v>
+        <v>0.0208</v>
       </c>
       <c r="H25" t="n">
-        <v>1339.23</v>
+        <v>1158.27</v>
       </c>
       <c r="I25" t="n">
-        <v>63901.01</v>
+        <v>63312.26</v>
       </c>
       <c r="J25" t="n">
-        <v>64752.52</v>
+        <v>64410.28</v>
       </c>
       <c r="K25" t="n">
-        <v>65162.73</v>
+        <v>64937.1</v>
       </c>
       <c r="L25" t="n">
-        <v>65572.92999999999</v>
+        <v>65463.91</v>
       </c>
       <c r="M25" t="n">
-        <v>66203.78999999999</v>
+        <v>66276.33</v>
       </c>
       <c r="N25" t="n">
-        <v>66834.64999999999</v>
+        <v>67088.75</v>
       </c>
       <c r="O25" t="n">
-        <v>67024.2</v>
+        <v>67329.95</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>65905.10000000001</v>
+        <v>66994.05</v>
       </c>
       <c r="C26" t="n">
-        <v>67006.84</v>
+        <v>67569.36</v>
       </c>
       <c r="D26" t="n">
-        <v>65848.58</v>
+        <v>66735.75999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>66970.22</v>
+        <v>67524.06</v>
       </c>
       <c r="F26" t="n">
-        <v>1363.51</v>
+        <v>553.84</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0083</v>
       </c>
       <c r="H26" t="n">
-        <v>1158.27</v>
+        <v>833.6</v>
       </c>
       <c r="I26" t="n">
-        <v>63312.26</v>
+        <v>64690.31</v>
       </c>
       <c r="J26" t="n">
-        <v>64410.28</v>
+        <v>66083.21000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>64937.1</v>
+        <v>66391.09</v>
       </c>
       <c r="L26" t="n">
-        <v>65463.91</v>
+        <v>66698.96000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>66276.33</v>
+        <v>67549.35000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>67088.75</v>
+        <v>68399.74000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>67329.95</v>
+        <v>68165.11</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2695,25 +2692,23 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2723,50 +2718,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>66994.05</v>
+        <v>68033.17</v>
       </c>
       <c r="C27" t="n">
-        <v>67569.36</v>
+        <v>68799.71000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>66735.75999999999</v>
+        <v>68006.17</v>
       </c>
       <c r="E27" t="n">
-        <v>67524.06</v>
+        <v>68308.59</v>
       </c>
       <c r="F27" t="n">
-        <v>553.84</v>
+        <v>784.53</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.0116</v>
       </c>
       <c r="H27" t="n">
-        <v>833.6</v>
+        <v>793.54</v>
       </c>
       <c r="I27" t="n">
-        <v>64690.31</v>
+        <v>65902.16</v>
       </c>
       <c r="J27" t="n">
-        <v>66083.21000000001</v>
+        <v>66876.21000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>66391.09</v>
+        <v>67107.25999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>66698.96000000001</v>
+        <v>67338.31</v>
       </c>
       <c r="M27" t="n">
-        <v>67549.35000000001</v>
+        <v>67940.86</v>
       </c>
       <c r="N27" t="n">
-        <v>68399.74000000001</v>
+        <v>68543.42</v>
       </c>
       <c r="O27" t="n">
-        <v>68165.11</v>
+        <v>68402.96000000001</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2777,23 +2772,27 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2803,50 +2802,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>68033.17</v>
+        <v>68811.17</v>
       </c>
       <c r="C28" t="n">
-        <v>68799.71000000001</v>
+        <v>69608.24000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>68006.17</v>
+        <v>68471.14999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>68308.59</v>
+        <v>68713.8</v>
       </c>
       <c r="F28" t="n">
-        <v>784.53</v>
+        <v>405.2</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0059</v>
       </c>
       <c r="H28" t="n">
-        <v>793.54</v>
+        <v>1137.09</v>
       </c>
       <c r="I28" t="n">
-        <v>65902.16</v>
+        <v>67212.63</v>
       </c>
       <c r="J28" t="n">
-        <v>66876.21000000001</v>
+        <v>67467.88</v>
       </c>
       <c r="K28" t="n">
-        <v>67107.25999999999</v>
+        <v>67911.82000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>67338.31</v>
+        <v>68355.77</v>
       </c>
       <c r="M28" t="n">
-        <v>67940.86</v>
+        <v>68705.36</v>
       </c>
       <c r="N28" t="n">
-        <v>68543.42</v>
+        <v>69054.96000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>68402.96000000001</v>
+        <v>69593.25</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2857,14 +2856,14 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U28" s="8" t="inlineStr">
@@ -2874,10 +2873,10 @@
       </c>
       <c r="V28" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W28" s="9" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2887,50 +2886,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>68811.17</v>
+        <v>68882.06</v>
       </c>
       <c r="C29" t="n">
-        <v>69608.24000000001</v>
+        <v>69225.57000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>68471.14999999999</v>
+        <v>68492.03999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>68713.8</v>
+        <v>69220.25</v>
       </c>
       <c r="F29" t="n">
-        <v>405.2</v>
+        <v>506.45</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0074</v>
       </c>
       <c r="H29" t="n">
-        <v>1137.09</v>
+        <v>733.53</v>
       </c>
       <c r="I29" t="n">
-        <v>67212.63</v>
+        <v>67334.05</v>
       </c>
       <c r="J29" t="n">
-        <v>67467.88</v>
+        <v>67413.75</v>
       </c>
       <c r="K29" t="n">
-        <v>67911.82000000001</v>
+        <v>68145.25</v>
       </c>
       <c r="L29" t="n">
-        <v>68355.77</v>
+        <v>68876.75</v>
       </c>
       <c r="M29" t="n">
-        <v>68705.36</v>
+        <v>69282.34</v>
       </c>
       <c r="N29" t="n">
-        <v>69054.96000000001</v>
+        <v>69687.94</v>
       </c>
       <c r="O29" t="n">
-        <v>69593.25</v>
+        <v>70745.34</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2941,7 +2940,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2951,89 +2950,93 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>68882.06</v>
+        <v>68847.35000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>69225.57000000001</v>
+        <v>69093.2</v>
       </c>
       <c r="D30" t="n">
-        <v>68492.03999999999</v>
+        <v>67368.96000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>69220.25</v>
+        <v>67460.73</v>
       </c>
       <c r="F30" t="n">
-        <v>506.45</v>
+        <v>-1759.52</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0074</v>
+        <v>-0.0254</v>
       </c>
       <c r="H30" t="n">
-        <v>733.53</v>
+        <v>1724.24</v>
       </c>
       <c r="I30" t="n">
-        <v>67334.05</v>
+        <v>67758.50999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>67413.75</v>
+        <v>68667.44</v>
       </c>
       <c r="K30" t="n">
-        <v>68145.25</v>
+        <v>68853.48</v>
       </c>
       <c r="L30" t="n">
-        <v>68876.75</v>
+        <v>69039.53</v>
       </c>
       <c r="M30" t="n">
-        <v>69282.34</v>
+        <v>69587.02</v>
       </c>
       <c r="N30" t="n">
-        <v>69687.94</v>
+        <v>70134.5</v>
       </c>
       <c r="O30" t="n">
-        <v>70745.34</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+        <v>69959.10000000001</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3043,79 +3046,75 @@
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>68847.35000000001</v>
+        <v>66812.27</v>
       </c>
       <c r="C31" t="n">
-        <v>69093.2</v>
+        <v>66833.50999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>67368.96000000001</v>
+        <v>65133.98</v>
       </c>
       <c r="E31" t="n">
-        <v>67460.73</v>
+        <v>65326.42</v>
       </c>
       <c r="F31" t="n">
-        <v>-1759.52</v>
+        <v>-2134.3</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0316</v>
       </c>
       <c r="H31" t="n">
-        <v>1724.24</v>
+        <v>1699.53</v>
       </c>
       <c r="I31" t="n">
-        <v>67758.50999999999</v>
+        <v>65644.72</v>
       </c>
       <c r="J31" t="n">
-        <v>68667.44</v>
+        <v>65351.31</v>
       </c>
       <c r="K31" t="n">
-        <v>68853.48</v>
+        <v>66598.61</v>
       </c>
       <c r="L31" t="n">
-        <v>69039.53</v>
+        <v>67845.89999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>69587.02</v>
+        <v>68322.85000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>70134.5</v>
+        <v>68799.78999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>69959.10000000001</v>
+        <v>70817.45</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3129,7 +3128,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3139,153 +3138,155 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>66812.27</v>
+        <v>65732.78999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>66833.50999999999</v>
+        <v>66325.32000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>65133.98</v>
+        <v>65652.25</v>
       </c>
       <c r="E32" t="n">
-        <v>65326.42</v>
+        <v>66216.78999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>-2134.3</v>
+        <v>890.37</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0316</v>
+        <v>0.0136</v>
       </c>
       <c r="H32" t="n">
-        <v>1699.53</v>
+        <v>673.0700000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>65644.72</v>
+        <v>63434.45</v>
       </c>
       <c r="J32" t="n">
-        <v>65351.31</v>
+        <v>63298.23</v>
       </c>
       <c r="K32" t="n">
-        <v>66598.61</v>
+        <v>64476.66</v>
       </c>
       <c r="L32" t="n">
-        <v>67845.89999999999</v>
+        <v>65655.08</v>
       </c>
       <c r="M32" t="n">
-        <v>68322.85000000001</v>
+        <v>66176.19</v>
       </c>
       <c r="N32" t="n">
-        <v>68799.78999999999</v>
+        <v>66697.28999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>70817.45</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
+        <v>68533.03999999999</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65732.78999999999</v>
+        <v>65427.69</v>
       </c>
       <c r="C33" t="n">
-        <v>66325.32000000001</v>
+        <v>66125.88</v>
       </c>
       <c r="D33" t="n">
-        <v>65652.25</v>
+        <v>65260.22</v>
       </c>
       <c r="E33" t="n">
-        <v>66216.78999999999</v>
+        <v>66016.36</v>
       </c>
       <c r="F33" t="n">
-        <v>890.37</v>
+        <v>-200.43</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.003</v>
       </c>
       <c r="H33" t="n">
-        <v>673.0700000000001</v>
+        <v>865.66</v>
       </c>
       <c r="I33" t="n">
-        <v>63434.45</v>
+        <v>64979.18</v>
       </c>
       <c r="J33" t="n">
-        <v>63298.23</v>
+        <v>65657.72</v>
       </c>
       <c r="K33" t="n">
-        <v>64476.66</v>
+        <v>65880.25</v>
       </c>
       <c r="L33" t="n">
-        <v>65655.08</v>
+        <v>66102.78999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>66176.19</v>
+        <v>66553.32000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>66697.28999999999</v>
+        <v>67003.86</v>
       </c>
       <c r="O33" t="n">
-        <v>68533.03999999999</v>
+        <v>66998.39</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>